--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -942,12 +942,12 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Python 3.12 / FastAPI / uvicorn, в контейнере (multi-stage `Dockerfile`), поднимается `docker compose up`. Внутри: Triage, поиск по базе знаний, шесть путей ответа, FSM.</t>
+          <t>Python 3.12 + веб-фреймворк FastAPI + сервер запуска uvicorn (ASGI: принимает HTTP-запросы и вызывает код FastAPI). В контейнере (multi-stage `Dockerfile`), поднимается `docker compose up`. Внутри: Triage, поиск по базе знаний, шесть путей ответа, FSM.</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Go и Node.js. Отклонены: нет зрелого RAG/PII-инструментария (LiteLLM, sentence-transformers, Presidio живут в Python), а RAG-логика обязана быть внутри одного контейнера. Выигрыш Go в конкурентности не нужен: узкое место — задержка внешней модели.</t>
+          <t>Язык: Go и Node.js — отклонены: нет зрелого RAG/PII-инструментария (LiteLLM, sentence-transformers, Presidio живут в Python), а RAG-логика обязана быть внутри одного контейнера; выигрыш Go в конкурентности не нужен, узкое место — задержка внешней модели. Фреймворк: FastAPI выбран против Flask, Django REST Framework и Litestar — родные async и потоковый ответ, pydantic-схемы и OpenAPI из тех же моделей, лёгкий вес; Flask и DRF дублируют описание моделей и требуют расширений, Litestar не даёт выигрыша при меньшем сообществе. Сервер: uvicorn выбран против Hypercorn, Daphne, Granian и gunicorn — стандартный сервер FastAPI, минимум настроек; остальным нечего добавить проекту (внешний трафик и TLS закрывает Ingress, скорость Rust-ядра не нужна, менеджер процессов заменяет Kubernetes). Подробно — ADR-200.</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Python / FastAPI, Deployment в Kubernetes, секреты из Vault.</t>
+          <t>Python / FastAPI, uvicorn без режима перезагрузки и без подключённых каталогов; Deployment в Kubernetes, секреты из Vault.</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -269,6 +269,9 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -277,9 +280,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Правила по ключевым словам (основной путь) + запасной k-NN по эмбеддингам, когда правила молчат. Запасной классификатор типа обращения покрывает 7 из 16 типов.</t>
+          <t>Python, без модели на основном пути. Тема (путь ответа): подстроки и регулярные выражения — `TOPIC_MARKERS`, `TARIFF_PATTERNS`, `WATER_QUALITY_PATTERNS`, `TEMPLATE_PATTERNS`, `ACCOUNT_PATTERNS` в `app/agents/triage.py`. Тип обращения (регистрация): словарь ключевых слов `KEYWORDS` в `app/taxonomy.py`, слова взяты из 136 настоящих обращений (охват 75%, точность 65%). Когда правила молчат — запасной k-NN по эмбеддингам (косинусная близость к размеченным примерам `EXAMPLES` в `app/agents/topic_fallback.py` и `app/agents/inquiry_type_fallback.py`); эмбеддер — `multilingual-e5-small` на CPU, тот же, что у поиска (вторая модель не грузится). Запасной классификатор типа знает 7 из 16 типов.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1023,22 +1023,22 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>9 типов из 16 не покрыты запасным классификатором: реальные тексты по ним — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет).</t>
+          <t>9 типов из 16 запасной классификатор не знает: refund, debt, payment, penalty, accrual_recalculation, inquiry_cancellation, meter_reacceptance, meter_reacceptance_auto, other. По ним работают только ключевые слова. Реальные тексты по этим типам — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет). Пороги k-NN подобраны замером на e5-small и не переносятся на другую модель.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Расширение запасного классификатора на оставшиеся девять типов; устранение найденных ложных срабатываний.</t>
+          <t>Расширение запасного классификатора на оставшиеся девять типов; устранение найденных ложных срабатываний; пересчёт порогов k-NN под новую модель эмбеддингов.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Тот же приём: правила + k-NN, порог и разрыв близости подбираются замером.</t>
+          <t>Правила и словарь — как сейчас; k-NN на эмбеддингах BGE-M3 (GPU) — тем же эмбеддером, что и поиск.</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Чтобы обращения по всем типам справочника регистрировались автоматически.</t>
+          <t>Чтобы обращения по всем типам справочника регистрировались автоматически. Пороги надо подбирать заново: их величина — свойство пары «модель + примеры».</t>
         </is>
       </c>
       <c r="J5" s="17" t="n">
@@ -1052,19 +1052,27 @@
           <t>Из блока ADR-600: Качество поиска и классификации</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="15" t="n"/>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="16" t="n"/>
-      <c r="R5" s="15" t="n"/>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>Как на MVP (изменений нет).</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>Те же правила; k-NN на BGE-M3.</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>Собственная модель генерации на тираже классификацию не затрагивает: k-NN использует эмбеддер поиска.</t>
+        </is>
+      </c>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="9" t="n"/>
       <c r="S5" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-600</t>
+          <t>ADR-300; ADR-600; app/agents/triage.py; app/taxonomy.py</t>
         </is>
       </c>
     </row>
@@ -1335,13 +1343,13 @@
           <t>Включается по триггеру (нагрузка, требование ИБ отказаться от внешних API, падение SLA провайдера), не по дате. Одна карта с запасом покрывает пик 3,4–6,75 запроса.</t>
         </is>
       </c>
-      <c r="P9" s="19" t="n">
+      <c r="P9" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" s="19" t="n">
+      <c r="Q9" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="R9" s="20" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
@@ -1407,16 +1415,24 @@
           <t>Из блока ADR-600: Качество поиска и классификации</t>
         </is>
       </c>
-      <c r="M10" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="15" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="16" t="n"/>
-      <c r="R10" s="15" t="n"/>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>Как на MVP (изменений нет).</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>BGE-M3 на том же GPU-пуле.</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>Модель поиска не зависит от того, чья модель генерирует ответ; карта A100 на тираже нужна только генерации.</t>
+        </is>
+      </c>
+      <c r="P10" s="19" t="n"/>
+      <c r="Q10" s="19" t="n"/>
+      <c r="R10" s="9" t="n"/>
       <c r="S10" s="9" t="inlineStr">
         <is>
           <t>ADR-300; ADR-500</t>
@@ -2006,13 +2022,13 @@
           <t>От результата зависит, можно ли доверить агенту роль на self-hosted модели.</t>
         </is>
       </c>
-      <c r="P18" s="19" t="n">
+      <c r="P18" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" s="19" t="n">
+      <c r="Q18" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="R18" s="20" t="inlineStr">
+      <c r="R18" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
@@ -2306,13 +2322,13 @@
           <t>Kubernetes сейчас лишь подразумевается; для тиража нужна зафиксированная платформа, включая GPU-пулы.</t>
         </is>
       </c>
-      <c r="P22" s="19" t="n">
+      <c r="P22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" s="19" t="n">
+      <c r="Q22" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="R22" s="20" t="inlineStr">
+      <c r="R22" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
@@ -2469,7 +2485,7 @@
       <c r="A25" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -2528,7 +2544,7 @@
       <c r="A26" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -2599,7 +2615,7 @@
       <c r="A27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -2639,13 +2655,13 @@
           <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
         </is>
       </c>
-      <c r="J27" s="19" t="n">
+      <c r="J27" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="19" t="n">
+      <c r="K27" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="20" t="inlineStr">
+      <c r="L27" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
@@ -2670,7 +2686,7 @@
       <c r="A28" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -2710,13 +2726,13 @@
           <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
         </is>
       </c>
-      <c r="J28" s="19" t="n">
+      <c r="J28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="19" t="n">
+      <c r="K28" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L28" s="20" t="inlineStr">
+      <c r="L28" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
@@ -2741,7 +2757,7 @@
       <c r="A29" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -2781,8 +2797,8 @@
           <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
         </is>
       </c>
-      <c r="J29" s="22" t="n"/>
-      <c r="K29" s="22" t="n"/>
+      <c r="J29" s="19" t="n"/>
+      <c r="K29" s="19" t="n"/>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="14" t="inlineStr">
         <is>
@@ -2804,7 +2820,7 @@
       <c r="A30" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -2859,7 +2875,7 @@
       <c r="A31" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -2899,8 +2915,8 @@
           <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
         </is>
       </c>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="22" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="9" t="inlineStr">
         <is>
@@ -2917,8 +2933,8 @@
           <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
         </is>
       </c>
-      <c r="P31" s="22" t="n"/>
-      <c r="Q31" s="22" t="n"/>
+      <c r="P31" s="19" t="n"/>
+      <c r="Q31" s="19" t="n"/>
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="inlineStr">
         <is>
@@ -2930,7 +2946,7 @@
       <c r="A32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3201,8 +3217,8 @@
           <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
         </is>
       </c>
-      <c r="P35" s="22" t="n"/>
-      <c r="Q35" s="22" t="n"/>
+      <c r="P35" s="19" t="n"/>
+      <c r="Q35" s="19" t="n"/>
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="inlineStr">
         <is>
@@ -3264,13 +3280,13 @@
           <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
         </is>
       </c>
-      <c r="P36" s="19" t="n">
+      <c r="P36" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="Q36" s="19" t="n">
+      <c r="Q36" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="R36" s="20" t="inlineStr">
+      <c r="R36" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники и допущения" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$S$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$S$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Python, без модели на основном пути. Тема (путь ответа): подстроки и регулярные выражения — `TOPIC_MARKERS`, `TARIFF_PATTERNS`, `WATER_QUALITY_PATTERNS`, `TEMPLATE_PATTERNS`, `ACCOUNT_PATTERNS` в `app/agents/triage.py`. Тип обращения (регистрация): словарь ключевых слов `KEYWORDS` в `app/taxonomy.py`, слова взяты из 136 настоящих обращений (охват 75%, точность 65%). Когда правила молчат — запасной k-NN по эмбеддингам (косинусная близость к размеченным примерам `EXAMPLES` в `app/agents/topic_fallback.py` и `app/agents/inquiry_type_fallback.py`); эмбеддер — `multilingual-e5-small` на CPU, тот же, что у поиска (вторая модель не грузится). Запасной классификатор типа знает 7 из 16 типов.</t>
+          <t>Python, без модели на основном пути. Тема (путь ответа): подстроки и регулярные выражения — `TOPIC_MARKERS`, `TARIFF_PATTERNS`, `WATER_QUALITY_PATTERNS`, `TEMPLATE_PATTERNS`, `ACCOUNT_PATTERNS` в `app/agents/triage.py`. Тип обращения (регистрация): словарь ключевых слов `KEYWORDS` в `app/taxonomy.py`, слова взяты из 136 настоящих обращений (охват 75%, точность 65%). Когда правила молчат — запасной k-NN по эмбеддингам (косинусная близость к размеченным примерам `EXAMPLES` в `app/agents/topic_fallback.py` и `app/agents/inquiry_type_fallback.py`); эмбеддер — `multilingual-e5-small` на CPU, тот же, что у поиска (вторая модель не грузится). Запасной классификатор типа знает 7 из 16 типов. Все правила и слова по каждому типу и теме, их проработка и этап сведены в таблице `Inquiry_Types.xlsx`.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Расширение запасного классификатора на оставшиеся девять типов; устранение найденных ложных срабатываний; пересчёт порогов k-NN под новую модель эмбеддингов.</t>
+          <t>Сначала анализ всех типов на живых обращениях (строка «Анализ всех типов…» ниже), затем заново собранная таблица типов; расширение запасного классификатора на оставшиеся девять типов; устранение найденных ложных срабатываний; пересчёт порогов k-NN под новую модель эмбеддингов.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-600; app/agents/triage.py; app/taxonomy.py</t>
+          <t>ADR-300; ADR-600; Inquiry_Types.xlsx; app/agents/triage.py; app/taxonomy.py</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>`multilingual-e5-small` на CPU: 0,46 ГБ, 22 мс на запрос — с запасом укладывается в бюджет 100 мс.</t>
+          <t>`multilingual-e5-small` на CPU: 0,46 ГБ, 22 мс на запрос — с запасом укладывается в бюджет 100 мс. Стек: библиотека sentence-transformers (`SentenceTransformerEmbedder`, `app/kb/search.py`); модель задаётся параметром `embedding_model` (`app/config.py`); тот же эмбеддер использует запасной классификатор Triage.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>BGE-M3: 4,25 ГБ, 210 мс на CPU (вдвое выше бюджета), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
+          <t>Сравнение моделей проведено в ADR-300, раздел 2 (задержка и размер — замер `scripts/measure_search_models.py`); замер поиска на прототипе — `golden_set/measurement.json` (e5-small: 20 из 20 на вопросах корпуса, 12 из 30 на первом месте и 23 из 30 в первой тройке на живых формулировках). Кандидаты: BGE-M3: 4,25 ГБ, 210 мс на CPU (вдвое выше бюджета), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>BGE-M3 на GPU (общий сервис для онлайн-поиска и индексации).</t>
+          <t>BGE-M3 на GPU (общий сервис для онлайн-поиска и индексации) — предварительный выбор: окончательно модель выбирается заново после анализа всех типов на живых обращениях (строка «Анализ всех типов…»).</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>Модель поиска не зависит от того, чья модель генерирует ответ; карта A100 на тираже нужна только генерации.</t>
+          <t>Модель поиска не зависит от того, чья модель генерирует ответ; карта A100 на тираже нужна только генерации. Модель для тиража подтверждается повторным решением по живой статистике MVP.</t>
         </is>
       </c>
       <c r="P10" s="19" t="n"/>
@@ -1435,7 +1435,7 @@
       <c r="R10" s="9" t="n"/>
       <c r="S10" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-500</t>
+          <t>ADR-300; ADR-500; golden_set/measurement.json; scripts/measure_search_models.py</t>
         </is>
       </c>
     </row>
@@ -3297,47 +3297,134 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="C38" s="25" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»).</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="L37" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Анализ типов на живых данных</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
+        <is>
+          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
+        </is>
+      </c>
+      <c r="P37" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
+      <c r="S37" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="25" t="inlineStr">
         <is>
           <t>Цвет ячеек с оценкой:</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="C39" s="26" t="n"/>
-      <c r="D39" s="27" t="inlineStr">
+    <row r="40">
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="C40" s="28" t="n"/>
-      <c r="D40" s="27" t="inlineStr">
+    <row r="41">
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="C41" s="29" t="n"/>
-      <c r="D41" s="27" t="inlineStr">
+    <row r="42">
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="C42" s="30" t="n"/>
-      <c r="D42" s="27" t="inlineStr">
+    <row r="43">
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="27" t="inlineStr">
         <is>
           <t>изменений на этом этапе нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S36"/>
+  <autoFilter ref="A2:S37"/>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="G1:L1"/>
@@ -3355,7 +3442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3449,11 +3536,11 @@
         </is>
       </c>
       <c r="B5" s="33">
-        <f>SUM('Матрица'!$J$3:$J$36)</f>
+        <f>SUM('Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="C5" s="33">
-        <f>SUM('Матрица'!$K$3:$K$36)</f>
+        <f>SUM('Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
       <c r="D5" s="33">
@@ -3465,27 +3552,27 @@
         <v/>
       </c>
       <c r="F5" s="34">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"ADR-600",'Матрица'!$J$3:$J$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"ADR-600",'Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="G5" s="34">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"ADR-600",'Матрица'!$K$3:$K$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"ADR-600",'Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
       <c r="H5" s="35">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока*",'Матрица'!$J$3:$J$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока*",'Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="I5" s="35">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока*",'Матрица'!$K$3:$K$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока*",'Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
       <c r="J5" s="36">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Оценка автора",'Матрица'!$J$3:$J$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Оценка автора",'Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="K5" s="36">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Оценка автора",'Матрица'!$K$3:$K$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Оценка автора",'Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
     </row>
@@ -3496,11 +3583,11 @@
         </is>
       </c>
       <c r="B6" s="33">
-        <f>SUM('Матрица'!$P$3:$P$36)</f>
+        <f>SUM('Матрица'!$P$3:$P$37)</f>
         <v/>
       </c>
       <c r="C6" s="33">
-        <f>SUM('Матрица'!$Q$3:$Q$36)</f>
+        <f>SUM('Матрица'!$Q$3:$Q$37)</f>
         <v/>
       </c>
       <c r="D6" s="33">
@@ -3512,27 +3599,27 @@
         <v/>
       </c>
       <c r="F6" s="34">
-        <f>SUMIF('Матрица'!$R$3:$R$36,"ADR-600",'Матрица'!$P$3:$P$36)</f>
+        <f>SUMIF('Матрица'!$R$3:$R$37,"ADR-600",'Матрица'!$P$3:$P$37)</f>
         <v/>
       </c>
       <c r="G6" s="34">
-        <f>SUMIF('Матрица'!$R$3:$R$36,"ADR-600",'Матрица'!$Q$3:$Q$36)</f>
+        <f>SUMIF('Матрица'!$R$3:$R$37,"ADR-600",'Матрица'!$Q$3:$Q$37)</f>
         <v/>
       </c>
       <c r="H6" s="35">
-        <f>SUMIF('Матрица'!$R$3:$R$36,"Из блока*",'Матрица'!$P$3:$P$36)</f>
+        <f>SUMIF('Матрица'!$R$3:$R$37,"Из блока*",'Матрица'!$P$3:$P$37)</f>
         <v/>
       </c>
       <c r="I6" s="35">
-        <f>SUMIF('Матрица'!$R$3:$R$36,"Из блока*",'Матрица'!$Q$3:$Q$36)</f>
+        <f>SUMIF('Матрица'!$R$3:$R$37,"Из блока*",'Матрица'!$Q$3:$Q$37)</f>
         <v/>
       </c>
       <c r="J6" s="36">
-        <f>SUMIF('Матрица'!$R$3:$R$36,"Оценка автора",'Матрица'!$P$3:$P$36)</f>
+        <f>SUMIF('Матрица'!$R$3:$R$37,"Оценка автора",'Матрица'!$P$3:$P$37)</f>
         <v/>
       </c>
       <c r="K6" s="36">
-        <f>SUMIF('Матрица'!$R$3:$R$36,"Оценка автора",'Матрица'!$Q$3:$Q$36)</f>
+        <f>SUMIF('Матрица'!$R$3:$R$37,"Оценка автора",'Матрица'!$Q$3:$Q$37)</f>
         <v/>
       </c>
     </row>
@@ -3691,11 +3778,11 @@
         <v>10</v>
       </c>
       <c r="D15" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: P0",'Матрица'!$J$3:$J$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: P0",'Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: P0",'Матрица'!$K$3:$K$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: P0",'Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
       <c r="F15" s="43">
@@ -3721,11 +3808,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: Согласования",'Матрица'!$J$3:$J$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Согласования",'Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: Согласования",'Матрица'!$K$3:$K$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Согласования",'Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
       <c r="F16" s="43">
@@ -3751,11 +3838,11 @@
         <v>15</v>
       </c>
       <c r="D17" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$J$3:$J$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="E17" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$K$3:$K$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
       <c r="F17" s="43">
@@ -3781,11 +3868,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$J$3:$J$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="E18" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$K$3:$K$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
       <c r="F18" s="43">
@@ -3811,11 +3898,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: Документация и ИБ",'Матрица'!$J$3:$J$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$J$3:$J$37)</f>
         <v/>
       </c>
       <c r="E19" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$36,"Из блока ADR-600: Документация и ИБ",'Матрица'!$K$3:$K$36)</f>
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$K$3:$K$37)</f>
         <v/>
       </c>
       <c r="F19" s="43">
@@ -3831,109 +3918,106 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>Анализ типов на живых данных</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" s="33">
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$J$3:$J$37)</f>
+        <v/>
+      </c>
+      <c r="E20" s="33">
+        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$K$3:$K$37)</f>
+        <v/>
+      </c>
+      <c r="F20" s="43">
+        <f>IF(AND(D20=B20,E20=C20),"да","НЕТ")</f>
+        <v/>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>13–19 чел-дн (ADR-600, дополнительно к блоку «Качество поиска и классификации»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
           <t>Итого по блокам</t>
         </is>
       </c>
-      <c r="B20" s="37">
-        <f>SUM(B15:B19)</f>
-        <v/>
-      </c>
-      <c r="C20" s="37">
-        <f>SUM(C15:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="37">
-        <f>SUM(D15:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="37">
-        <f>SUM(E15:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="44">
-        <f>IF(AND(D20=B20,E20=C20),"да","НЕТ")</f>
-        <v/>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>ADR-600 называет итог ≈9–13 недель (≈45–65 чел-дн); сумма блоков 46,5–70,5 — округление в самом ADR-600</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="42" t="inlineStr">
+      <c r="B21" s="37">
+        <f>SUM(B15:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="37">
+        <f>SUM(C15:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="37">
+        <f>SUM(D15:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="37">
+        <f>SUM(E15:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="44">
+        <f>IF(AND(D21=B21,E21=C21),"да","НЕТ")</f>
+        <v/>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>ADR-600 называет итог ≈12–18 недель (≈60–90 чел-дн); сумма блоков 59,5–89,5 — округление в самом ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>Затраты, которые не выражаются человеко-днями</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Контур</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Значение / комментарий</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>От</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>До</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Единица</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Источник</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Токены генерации (YandexGPT Pro, 0,8 ₽ за 1000 токенов)</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>≈146 ₽/мес при базовом сценарии (10% визитов, 30% до модели) — ≈1 698 ₽/мес при максимальном (50%, 70%)</t>
-        </is>
-      </c>
-      <c r="D24" s="41" t="n">
-        <v>146</v>
-      </c>
-      <c r="E24" s="41" t="n">
-        <v>1698</v>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>₽/мес</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>ADR-500</t>
         </is>
       </c>
     </row>
@@ -3945,24 +4029,28 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>GPU-сервер под эмбеддинги и реранкер</t>
+          <t>Токены генерации (YandexGPT Pro, 0,8 ₽ за 1000 токенов)</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Не оценён отдельной строкой сметы</t>
-        </is>
-      </c>
-      <c r="D25" s="41" t="n"/>
-      <c r="E25" s="41" t="n"/>
+          <t>≈146 ₽/мес при базовом сценарии (10% визитов, 30% до модели) — ≈1 698 ₽/мес при максимальном (50%, 70%)</t>
+        </is>
+      </c>
+      <c r="D25" s="41" t="n">
+        <v>146</v>
+      </c>
+      <c r="E25" s="41" t="n">
+        <v>1698</v>
+      </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>₽</t>
+          <t>₽/мес</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>ADR-500 (открытый пункт)</t>
+          <t>ADR-500</t>
         </is>
       </c>
     </row>
@@ -3974,12 +4062,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
+          <t>GPU-сервер под эмбеддинги и реранкер</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Не оценены</t>
+          <t>Не оценён отдельной строкой сметы</t>
         </is>
       </c>
       <c r="D26" s="41" t="n"/>
@@ -3998,25 +4086,21 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Карта A100 80 ГБ (покупка)</t>
+          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером)</t>
-        </is>
-      </c>
-      <c r="D27" s="41" t="n">
-        <v>927000</v>
-      </c>
-      <c r="E27" s="41" t="n">
-        <v>2368080</v>
-      </c>
+          <t>Не оценены</t>
+        </is>
+      </c>
+      <c r="D27" s="41" t="n"/>
+      <c r="E27" s="41" t="n"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>₽</t>
@@ -4024,7 +4108,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
@@ -4036,29 +4120,62 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
+          <t>Карта A100 80 ГБ (покупка)</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером)</t>
+        </is>
+      </c>
+      <c r="D28" s="41" t="n">
+        <v>927000</v>
+      </c>
+      <c r="E28" s="41" t="n">
+        <v>2368080</v>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>₽</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>ADR-500</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Тираж</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
           <t>Сервер-хост, электричество, размещение, обслуживание GPU</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Не оценены</t>
         </is>
       </c>
-      <c r="D28" s="41" t="n"/>
-      <c r="E28" s="41" t="n"/>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="D29" s="41" t="n"/>
+      <c r="E29" s="41" t="n"/>
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>₽</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>Все суммы в ₽ — прогнозная модель, не смета: CAPEX/OPEX не утверждены владельцем (ADR-500). Закупка GPU — недели или месяцы лид-тайма, не разработка.</t>
         </is>
@@ -4081,7 +4198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4163,7 +4280,7 @@
       </c>
       <c r="C6" s="47" t="inlineStr">
         <is>
-          <t>Сумма задач перехода к тиражу в ADR-600 — 15–23 чел-дн (3–5 + 5 + 2–3 + 5–10), сам документ округляет до «3–4 недель» (15–20). В таблице — построчные значения.</t>
+          <t>Сумма задач перехода к тиражу в ADR-600 — 17–26 чел-дн (3–5 + 5 + 2–3 + 5–10 + 2–3), сам документ округляет до «≈3,5–5 недель». В таблице — построчные значения.</t>
         </is>
       </c>
     </row>
@@ -4942,104 +5059,131 @@
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="42" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9">
+        <f>'Матрица'!A37</f>
+        <v/>
+      </c>
+      <c r="B38" s="9">
+        <f>'Матрица'!C37</f>
+        <v/>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D38" s="33">
+        <f>'Матрица'!J37</f>
+        <v/>
+      </c>
+      <c r="E38" s="33">
+        <f>'Матрица'!K37</f>
+        <v/>
+      </c>
+      <c r="F38" s="18">
+        <f>'Матрица'!L37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="42" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -5047,10 +5191,10 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C40:F40"/>
     <mergeCell ref="C47:F47"/>
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C48:F48"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C42:F42"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1072,7 +1072,7 @@
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-600; Inquiry_Types.xlsx; app/agents/triage.py; app/taxonomy.py</t>
+          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       <c r="R10" s="9" t="n"/>
       <c r="S10" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-500; golden_set/measurement.json; scripts/measure_search_models.py</t>
+          <t>ADR-300; ADR-500</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1092,17 +1092,17 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>LiteLLM с единым OpenAI-совместимым интерфейсом. Внутри контейнера Backend как модуль: Quota → PII-фильтр → LiteLLM → Guardrails. К шлюзу ходит только Backend.</t>
+          <t>Python-модуль внутри контейнера Backend (`app/gateway/`), работает по цепочке: лимиты запросов (Redis) → обезличивание (Presidio + русская модель spaCy + собственные распознаватели) → вызов модели через LiteLLM → проверка ответа на потоке (регулярные выражения) → запись события использования (Postgres) и метрики (prometheus-client). LiteLLM подключён библиотекой (`Router`) внутри процесса по конфигурации `litellm_config.yaml`: единый OpenAI-совместимый интерфейс, повторы и переключение на запасного провайдера при сбое; YandexGPT вызывается через OpenAI-совместимый адрес. К шлюзу ходит только Backend.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Свой клиент на каждого провайдера отклонён: дублирование ради контроля, который LiteLLM уже даёт (retry, circuit breaker, 100+ адаптеров).</t>
+          <t>Свой клиент на каждого провайдера отклонён: дублирование ради контроля, который LiteLLM уже даёт (100+ адаптеров, единый интерфейс, повторы и circuit breaker). Отдельный прокси-сервер LiteLLM на прототипе не взят: это второй процесс со своим портом и конфигурацией, на машине с 15 ГБ памяти тесно; библиотека принимает тот же список моделей и цепочки запасных провайдеров, формат файла совместим с прокси. Смена провайдера — правка переменной `LLM_PROVIDER`, код не меняется: это условие ADR-200 (минимум два провайдера с автопереключением). Весь нужный инструментарий (LiteLLM, Presidio, sentence-transformers) существует в Python — тот же язык, что у Backend. Зарубежные провайдеры исключены: 152-ФЗ.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Отдельного контейнера нет — шлюз пока внутри Backend.</t>
+          <t>Отдельного контейнера нет — шлюз пока внутри Backend. GigaChat на прототипе недоступен (нужны сертификаты НУЦ), поэтому целевой основной провайдер MVP на машине прототипа не проверен. Проверки ответа — регулярные выражения; тонкие случаи (тон, обоснованность) ловятся слабо, обоснованность оценивает отдельный судья.</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Python / LiteLLM, отдельный Deployment.</t>
+          <t>Python / LiteLLM (Router или прокси — решается при выносе; формат конфигурации совместим), отдельный Deployment; Redis для лимитов; Presidio; события использования — в ClickHouse; GigaChat Pro основной, YandexGPT резерв.</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1038,14 +1038,14 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Чтобы обращения по всем типам справочника регистрировались автоматически. Пороги надо подбирать заново: их величина — свойство пары «модель + примеры».</t>
+          <t>Чтобы обращения по всем типам справочника регистрировались автоматически. Пороги надо подбирать заново: их величина — свойство пары «модель + примеры». Оценка в этой строке — только расширение классификатора и подбор порогов: 2–3 недели после появления размеченного корпуса (ADR-600). Анализ на живых данных и пересборка таблицы — 13–19 чел-дн в строке «Анализ всех типов…»; вместе с ним работа над классификатором — 23–34 чел-дн.</t>
         </is>
       </c>
       <c r="J5" s="17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K5" s="17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="B17" s="33" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C17" s="33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D17" s="33">
         <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$J$3:$J$37)</f>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>2–3 недели</t>
+          <t>≈3,5–5 недель: расширение классификатора 10–15 чел-дн + сравнение моделей 3–4 + реранкер 2–3 + судья 2–3</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>ADR-600 называет итог ≈12–18 недель (≈60–90 чел-дн); сумма блоков 59,5–89,5 — округление в самом ADR-600</t>
+          <t>ADR-600 называет итог ≈13–20 недель (≈65–100 чел-дн); сумма блоков 66,5–99,5 — округление в самом ADR-600</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники и допущения" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$S$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -697,28 +697,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -729,34 +732,37 @@
       </c>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Сейчас (прототип)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>MVP — 8 000 абонентов</t>
         </is>
       </c>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="3" t="n"/>
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Тираж — 90 000 абонентов</t>
         </is>
       </c>
-      <c r="N1" s="4" t="n"/>
-      <c r="O1" s="4" t="n"/>
-      <c r="P1" s="4" t="n"/>
       <c r="Q1" s="4" t="n"/>
       <c r="R1" s="4" t="n"/>
-      <c r="S1" s="1" t="inlineStr"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="1" t="inlineStr"/>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -774,82 +780,97 @@
           <t>Контейнер / связь</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Технология и стек (выбрано, работает сейчас)</t>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Какие контейнеры затрагивает</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
+          <t>Технология и стек (что именно используется)</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Как реализовано сейчас</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
           <t>С чем сравнивали и почему выбрано</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Где сравнение (документ, раздел)</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Проблемы</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Что будет</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Стек</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Почему</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Доработки, чел-дн (мин)</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Доработки, чел-дн (макс)</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>Основа оценки</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>Что будет</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="Q2" s="8" t="inlineStr">
         <is>
           <t>Стек</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="R2" s="8" t="inlineStr">
         <is>
           <t>Почему</t>
         </is>
       </c>
-      <c r="P2" s="8" t="inlineStr">
+      <c r="S2" s="8" t="inlineStr">
         <is>
           <t>Доработки, чел-дн (мин)</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="inlineStr">
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>Доработки, чел-дн (макс)</t>
         </is>
       </c>
-      <c r="R2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>Основа оценки</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
@@ -871,56 +892,71 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
+          <t>AI-виджет; Backend (на прототипе отдаёт статику виджета)</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>HTML + JavaScript без фреймворка и сборки + CSS (каталог `web/`); поток ответа — fetch и чтение SSE</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
           <t>Три статических файла: HTML / JS / CSS (`web/`), отдаются самим Backend; ответ приходит потоком (SSE). Оформлен как личный кабинет.</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>React/TS (целевой) на прототипе отклонён: ничего архитектурного не проверил бы, но потребовал бы второго процесса на демонстрации.</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — причина выбора для прототипа записана в ADR-100 («Что сдано») и в примечании C3/C4_L3_Widget.html; выбор React/TS для MVP не сравнивался, он указан в C4_Deployment.html</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Это демо-стенд, а не продукт. Нет настоящей SSO: абонент выбирается из справочника, идентификатор берётся из метаданных запроса.</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Виджет, встроенный в личный кабинет, с SSO-сессией.</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>React / TypeScript, сборка в образ `ai-widget`, за Ingress (nginx).</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Встраивание в существующий ЛК; целевая схема развёртывания (`C4_Deployment`).</t>
         </is>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="M3" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K3" s="12" t="n">
+      <c r="N3" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M3" s="14" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N3" s="15" t="n"/>
-      <c r="O3" s="15" t="n"/>
-      <c r="P3" s="16" t="n"/>
-      <c r="Q3" s="16" t="n"/>
+      <c r="Q3" s="15" t="n"/>
       <c r="R3" s="15" t="n"/>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="S3" s="16" t="n"/>
+      <c r="T3" s="16" t="n"/>
+      <c r="U3" s="15" t="n"/>
+      <c r="V3" s="9" t="inlineStr">
         <is>
           <t>ADR-100; C4_L3_Widget; C4_Deployment</t>
         </is>
@@ -942,56 +978,71 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Python 3.12; FastAPI; uvicorn; pydantic v2; httpx; контейнер docker (multi-stage)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
           <t>Python 3.12 + веб-фреймворк FastAPI + сервер запуска uvicorn (ASGI: принимает HTTP-запросы и вызывает код FastAPI). В контейнере (multi-stage `Dockerfile`), поднимается `docker compose up`. Внутри: Triage, поиск по базе знаний, шесть путей ответа, FSM.</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Язык: Go и Node.js — отклонены: нет зрелого RAG/PII-инструментария (LiteLLM, sentence-transformers, Presidio живут в Python), а RAG-логика обязана быть внутри одного контейнера; выигрыш Go в конкурентности не нужен, узкое место — задержка внешней модели. Фреймворк: FastAPI выбран против Flask, Django REST Framework и Litestar — родные async и потоковый ответ, pydantic-схемы и OpenAPI из тех же моделей, лёгкий вес; Flask и DRF дублируют описание моделей и требуют расширений, Litestar не даёт выигрыша при меньшем сообществе. Сервер: uvicorn выбран против Hypercorn, Daphne, Granian и gunicorn — стандартный сервер FastAPI, минимум настроек; остальным нечего добавить проекту (внешний трафик и TLS закрывает Ingress, скорость Rust-ядра не нужна, менеджер процессов заменяет Kubernetes). Подробно — ADR-200.</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200: «Почему Python, а не Go или Node.js», «Почему FastAPI, а не другой Python-фреймворк», «Почему uvicorn»</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Проверка «идентификатор абонента принадлежит сессии» на шагах записи спроектирована, но не реализована (открытый P1). В compose включён режим разработки (`--reload`, подключённые каталоги).</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Те же контейнеры в Kubernetes, несколько реплик; проверка привязки абонента к сессии на каждом шаге записи; продовый режим запуска.</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>Python / FastAPI, uvicorn без режима перезагрузки и без подключённых каталогов; Deployment в Kubernetes, секреты из Vault.</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>Без привязки сессии запись от имени абонента включать нельзя (риск подмены, ADR-400).</t>
         </is>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="M4" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="N4" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="L4" s="18" t="inlineStr">
+      <c r="O4" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N4" s="15" t="n"/>
-      <c r="O4" s="15" t="n"/>
-      <c r="P4" s="16" t="n"/>
-      <c r="Q4" s="16" t="n"/>
+      <c r="Q4" s="15" t="n"/>
       <c r="R4" s="15" t="n"/>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="S4" s="16" t="n"/>
+      <c r="T4" s="16" t="n"/>
+      <c r="U4" s="15" t="n"/>
+      <c r="V4" s="9" t="inlineStr">
         <is>
           <t>ADR-200; ADR-400; ADR-600</t>
         </is>
@@ -1013,64 +1064,79 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
+          <t>Backend (модуль Triage); embedding-inference (эмбеддер для запасного k-NN)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Python: регулярные выражения `re` и словарь ключевых слов; запасной k-NN — sentence-transformers, multilingual-e5-small (CPU), косинусная близость</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
           <t>Python, без модели на основном пути. Тема (путь ответа): подстроки и регулярные выражения — `TOPIC_MARKERS`, `TARIFF_PATTERNS`, `WATER_QUALITY_PATTERNS`, `TEMPLATE_PATTERNS`, `ACCOUNT_PATTERNS` в `app/agents/triage.py`. Тип обращения (регистрация): словарь ключевых слов `KEYWORDS` в `app/taxonomy.py`, слова взяты из 136 настоящих обращений (охват 75%, точность 65%). Когда правила молчат — запасной k-NN по эмбеддингам (косинусная близость к размеченным примерам `EXAMPLES` в `app/agents/topic_fallback.py` и `app/agents/inquiry_type_fallback.py`); эмбеддер — `multilingual-e5-small` на CPU, тот же, что у поиска (вторая модель не грузится). Запасной классификатор типа знает 7 из 16 типов. Все правила и слова по каждому типу и теме, их проработка и этап сведены в таблице `Inquiry_Types.xlsx`.</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Отдельный вызов LLM на каждый запрос отклонён: стоимость и задержка ради задачи, которую решают правила. k-NN переиспользует уже загруженный эмбеддер, вторая модель не нужна.</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 1 «Классификация» (правила / LLM-классификатор / k-NN); слова и статистика — Inquiry_Types.xlsx</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>9 типов из 16 запасной классификатор не знает: refund, debt, payment, penalty, accrual_recalculation, inquiry_cancellation, meter_reacceptance, meter_reacceptance_auto, other. По ним работают только ключевые слова. Реальные тексты по этим типам — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет). Пороги k-NN подобраны замером на e5-small и не переносятся на другую модель.</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>Сначала анализ всех типов на живых обращениях (строка «Анализ всех типов…» ниже), затем заново собранная таблица типов; расширение запасного классификатора на оставшиеся девять типов; устранение найденных ложных срабатываний; пересчёт порогов k-NN под новую модель эмбеддингов.</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Правила и словарь — как сейчас; k-NN на эмбеддингах BGE-M3 (GPU) — тем же эмбеддером, что и поиск.</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>Чтобы обращения по всем типам справочника регистрировались автоматически. Пороги надо подбирать заново: их величина — свойство пары «модель + примеры». Оценка в этой строке — только расширение классификатора и подбор порогов: 2–3 недели после появления размеченного корпуса (ADR-600). Анализ на живых данных и пересборка таблицы — 13–19 чел-дн в строке «Анализ всех типов…»; вместе с ним работа над классификатором — 23–34 чел-дн.</t>
         </is>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="M5" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="N5" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="L5" s="18" t="inlineStr">
+      <c r="O5" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Качество поиска и классификации</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>Как на MVP (изменений нет).</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>Те же правила; k-NN на BGE-M3.</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>Собственная модель генерации на тираже классификацию не затрагивает: k-NN использует эмбеддер поиска.</t>
         </is>
       </c>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="19" t="n"/>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="inlineStr">
         <is>
           <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
         </is>
@@ -1092,56 +1158,71 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
+          <t>LLM Gateway (сейчас внутри Backend); Redis (лимиты); LLM Provider; Postgres / ClickHouse (события использования)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Python; LiteLLM (Router); Redis; Presidio + spaCy (обезличивание); prometheus-client; PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
           <t>Python-модуль внутри контейнера Backend (`app/gateway/`), работает по цепочке: лимиты запросов (Redis) → обезличивание (Presidio + русская модель spaCy + собственные распознаватели) → вызов модели через LiteLLM → проверка ответа на потоке (регулярные выражения) → запись события использования (Postgres) и метрики (prometheus-client). LiteLLM подключён библиотекой (`Router`) внутри процесса по конфигурации `litellm_config.yaml`: единый OpenAI-совместимый интерфейс, повторы и переключение на запасного провайдера при сбое; YandexGPT вызывается через OpenAI-совместимый адрес. К шлюзу ходит только Backend.</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Свой клиент на каждого провайдера отклонён: дублирование ради контроля, который LiteLLM уже даёт (100+ адаптеров, единый интерфейс, повторы и circuit breaker). Отдельный прокси-сервер LiteLLM на прототипе не взят: это второй процесс со своим портом и конфигурацией, на машине с 15 ГБ памяти тесно; библиотека принимает тот же список моделей и цепочки запасных провайдеров, формат файла совместим с прокси. Смена провайдера — правка переменной `LLM_PROVIDER`, код не меняется: это условие ADR-200 (минимум два провайдера с автопереключением). Весь нужный инструментарий (LiteLLM, Presidio, sentence-transformers) существует в Python — тот же язык, что у Backend. Зарубежные провайдеры исключены: 152-ФЗ.</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «LLM-хостинг»: таблица стратегии и шлюза, подраздел «Как устроен шлюз к модели»</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Отдельного контейнера нет — шлюз пока внутри Backend. GigaChat на прототипе недоступен (нужны сертификаты НУЦ), поэтому целевой основной провайдер MVP на машине прототипа не проверен. Проверки ответа — регулярные выражения; тонкие случаи (тон, обоснованность) ловятся слабо, обоснованность оценивает отдельный судья.</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Отдельный контейнер `llm-gateway`; через него ходят и Backend, и агент записи.</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Python / LiteLLM (Router или прокси — решается при выносе; формат конфигурации совместим), отдельный Deployment; Redis для лимитов; Presidio; события использования — в ClickHouse; GigaChat Pro основной, YandexGPT резерв.</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>Единый обязательный путь для всех потребителей: обхода обезличивания на Этапе 2 быть не должно.</t>
         </is>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="M6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="N6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="16" t="n"/>
+      <c r="Q6" s="15" t="n"/>
       <c r="R6" s="15" t="n"/>
-      <c r="S6" s="9" t="inlineStr">
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="15" t="n"/>
+      <c r="V6" s="9" t="inlineStr">
         <is>
           <t>ADR-200; C4_L3_LLM</t>
         </is>
@@ -1163,40 +1244,55 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
+          <t>LLM Gateway (Backend)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Python; Presidio (analyzer, anonymizer); spaCy ru_core_news_md; собственные распознаватели СНИЛС, ИНН, лицевого счёта, телефона, email</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
           <t>Presidio + собственные распознаватели (СНИЛС и ИНН с контрольными суммами, лицевой счёт, телефон, email), русская модель spaCy. Стоит в шлюзе до обращения к провайдеру.</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Базовый набор Presidio не годился: лицевой счёт определялся как телефон, одна почта получала три метки. Поэтому распознаватели разделены на собственные и Presidio.</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — состав и правило «ПДн не покидают периметр» — ADR-400, раздел «Закрыто сейчас»; сравнение вариантов обезличивания в пакет не входит</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Эмбеддинг запроса минует фильтр, поэтому онлайн-эмбеддинги допустимы только локальные (внешний API для запроса запрещён).</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
+      <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
-      <c r="M7" s="14" t="inlineStr">
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="15" t="n"/>
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="16" t="n"/>
+      <c r="Q7" s="15" t="n"/>
       <c r="R7" s="15" t="n"/>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="S7" s="16" t="n"/>
+      <c r="T7" s="16" t="n"/>
+      <c r="U7" s="15" t="n"/>
+      <c r="V7" s="9" t="inlineStr">
         <is>
           <t>ADR-400; ADR-300</t>
         </is>
@@ -1218,56 +1314,71 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
+          <t>LLM Gateway (проверки на потоке); Backend (фоновая оценка); Ollama (локальная модель судьи на прототипе)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Python: регулярные выражения для проверок на потоке; судья — LiteLLM → Qwen2.5-7B через Ollama (прототип), YandexGPT (MVP)</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
           <t>Синхронно (до 50 мс): ПДн в ответе, тон, разглашение промпта — при нарушении поток обрывается. Асинхронно: судья обоснованности (локальная Qwen2.5-7B через Ollama), не блокирует выдачу.</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Судья не может совпадать с отвечающей моделью: при совпадении оценка пропускается и это фиксируется — лучше пропуск, чем завышенная оценка.</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 5 «Судья качества ответа» (модели судьи); проверки на потоке — сравнения нет</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Судья слабый, оценка предварительная (provisional): пороги качества не откалиброваны на размеченном наборе.</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>Судья на другом провайдере, чем отвечающая модель; калибровка порогов.</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>YandexGPT как судья при GigaChat Pro в роли отвечающей модели.</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>Независимость оценки обеспечена конструктивно, а не договорённостью.</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="M8" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="N8" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="18" t="inlineStr">
+      <c r="O8" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Качество поиска и классификации</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr">
+      <c r="P8" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="16" t="n"/>
+      <c r="Q8" s="15" t="n"/>
       <c r="R8" s="15" t="n"/>
-      <c r="S8" s="9" t="inlineStr">
+      <c r="S8" s="16" t="n"/>
+      <c r="T8" s="16" t="n"/>
+      <c r="U8" s="15" t="n"/>
+      <c r="V8" s="9" t="inlineStr">
         <is>
           <t>ADR-300; C4_L3_LLM</t>
         </is>
@@ -1289,72 +1400,87 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
+          <t>LLM Gateway; внешний LLM Provider (YandexGPT / GigaChat); Ollama (тесты)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>YandexGPT Pro (управляемый API, РФ); LiteLLM; Qwen2.5-7B через Ollama для тестов</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
           <t>YandexGPT Pro — управляемый API в РФ. Для тестов локально Qwen2.5-7B (Ollama). Время до первого куска ≈0,6 с (ориентир 0,5 с).</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>GigaChat технически недоступен на машине прототипа (нужны корневые сертификаты НУЦ; отключать проверку TLS недопустимо). Зарубежные провайдеры отклонены на всех этапах: 152-ФЗ.</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 4 «Генерация ответа абоненту» и подраздел «Сравнение семейства self-hosted-модели»; стоимость — ADR-500</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Качество ответов не измерено на собственном эталонном наборе; выбор модели по репутации.</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>GigaChat Pro как основная, YandexGPT как резерв с автопереключением.</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>Управляемые API в РФ через LLM Gateway.</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Ранее выбран основным по совокупности; резерв защищает от отказа провайдера.</t>
         </is>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="M9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="N9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="P9" s="9" t="inlineStr">
         <is>
           <t>Собственная модель в закрытом контуре, внешние API остаются до срабатывания триггера.</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="Q9" s="9" t="inlineStr">
         <is>
           <t>Qwen2.5-32B INT4, vLLM, 1× GPU A100 80 ГБ.</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="R9" s="9" t="inlineStr">
         <is>
           <t>Включается по триггеру (нагрузка, требование ИБ отказаться от внешних API, падение SLA провайдера), не по дате. Одна карта с запасом покрывает пик 3,4–6,75 запроса.</t>
         </is>
       </c>
-      <c r="P9" s="20" t="n">
+      <c r="S9" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" s="20" t="n">
+      <c r="T9" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="R9" s="21" t="inlineStr">
+      <c r="U9" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
       </c>
-      <c r="S9" s="9" t="inlineStr">
+      <c r="V9" s="9" t="inlineStr">
         <is>
           <t>ADR-300; ADR-500; ADR-600</t>
         </is>
@@ -1376,64 +1502,79 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
+          <t>Backend (поиск); embedding-inference (MVP); ETL индексации; Qdrant; Triage (запасной k-NN)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers; multilingual-e5-small (CPU) на прототипе; BGE-M3 (GPU) на MVP</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
           <t>`multilingual-e5-small` на CPU: 0,46 ГБ, 22 мс на запрос — с запасом укладывается в бюджет 100 мс. Стек: библиотека sentence-transformers (`SentenceTransformerEmbedder`, `app/kb/search.py`); модель задаётся параметром `embedding_model` (`app/config.py`); тот же эмбеддер использует запасной классификатор Triage.</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Сравнение моделей проведено в ADR-300, раздел 2 (задержка и размер — замер `scripts/measure_search_models.py`); замер поиска на прототипе — `golden_set/measurement.json` (e5-small: 20 из 20 на вопросах корпуса, 12 из 30 на первом месте и 23 из 30 в первой тройке на живых формулировках). Кандидаты: BGE-M3: 4,25 ГБ, 210 мс на CPU (вдвое выше бюджета), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 2 «Эмбеддинги»; замер поиска — golden_set/measurement.json; скрипт замера — scripts/measure_search_models.py</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Смена модели — самое дорогое решение для отмены: версия хранится в каждом векторе, смена = полная переиндексация. Сравнение e5-small и BGE-M3 по качеству не проведено.</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>BGE-M3 на GPU (общий сервис для онлайн-поиска и индексации) — предварительный выбор: окончательно модель выбирается заново после анализа всех типов на живых обращениях (строка «Анализ всех типов…»).</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>BGE-M3, сервис `embedding-inference` на узле с GPU.</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>Многоязычная модель, по репутации лучше на русском; решение принимается один раз на этап после замера на эталонном наборе.</t>
         </is>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="M10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="N10" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="O10" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Качество поиска и классификации</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="P10" s="9" t="inlineStr">
         <is>
           <t>Как на MVP (изменений нет).</t>
         </is>
       </c>
-      <c r="N10" s="9" t="inlineStr">
+      <c r="Q10" s="9" t="inlineStr">
         <is>
           <t>BGE-M3 на том же GPU-пуле.</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="R10" s="9" t="inlineStr">
         <is>
           <t>Модель поиска не зависит от того, чья модель генерирует ответ; карта A100 на тираже нужна только генерации. Модель для тиража подтверждается повторным решением по живой статистике MVP.</t>
         </is>
       </c>
-      <c r="P10" s="19" t="n"/>
-      <c r="Q10" s="19" t="n"/>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="9" t="inlineStr">
+      <c r="S10" s="19" t="n"/>
+      <c r="T10" s="19" t="n"/>
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="inlineStr">
         <is>
           <t>ADR-300; ADR-500</t>
         </is>
@@ -1455,56 +1596,71 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
+          <t>Backend (поиск); reranker-inference (MVP); ETL индексации (офлайн-роль)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>sentence-transformers (кросс-энкодер); BAAI/bge-reranker-v2-m3; на прототипе выключен</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
           <t>Реализован и проверен, но выключен (`RERANKER_ENABLED=false`): кросс-энкодер BGE-reranker-v2-m3 на CPU считает 5,8–25 с при бюджете 100 мс.</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU.</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 3 «Переранжирование»; замер — golden_set/reranking.json</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Онлайн-роль зависит от GPU. Офлайн-роль (выбор представительного чанка среди дублей) не подтверждена: модель обучена на паре «запрос — документ», а запроса при индексации нет.</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Включён в онлайн-поиске; замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство.</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>BGE-reranker-v2-m3, сервис `reranker-inference` на GPU.</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>Уточнение выдачи; на GPU укладывается в бюджет задержки.</t>
         </is>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="M11" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="K11" s="17" t="n">
+      <c r="N11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="O11" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Качество поиска и классификации</t>
         </is>
       </c>
-      <c r="M11" s="14" t="inlineStr">
+      <c r="P11" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N11" s="15" t="n"/>
-      <c r="O11" s="15" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="16" t="n"/>
+      <c r="Q11" s="15" t="n"/>
       <c r="R11" s="15" t="n"/>
-      <c r="S11" s="9" t="inlineStr">
+      <c r="S11" s="16" t="n"/>
+      <c r="T11" s="16" t="n"/>
+      <c r="U11" s="15" t="n"/>
+      <c r="V11" s="9" t="inlineStr">
         <is>
           <t>ADR-300; C3/C4_L3_ETL_RAG_1</t>
         </is>
@@ -1526,56 +1682,71 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
+          <t>Qdrant; Backend (читает); ETL индексации (пишет)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Qdrant (docker `qdrant/qdrant`); клиент qdrant-client; индекс HNSW (m=16, ef=128); payload-индексы; blue-green алиасы коллекций</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
           <t>Qdrant в `docker compose`; в коде по умолчанию корпус в памяти. Есть фильтр по типу обращения и переключение индекса без остановки поиска (blue-green алиас).</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>pgvector: не тянет фильтрацию по payload на нужном объёме. Milvus: тяжелее в эксплуатации при том же результате.</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «Хранилища»: строка «Векторный поиск (целевое)» (pgvector, Milvus)</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Образ в compose не привязан к версии (`latest`) — для продакшена версию надо зафиксировать.</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Qdrant self-hosted в Kubernetes на быстром диске, с резервным копированием.</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>Qdrant, StatefulSet + PVC на NVMe.</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>Целевое хранилище векторов; миграция — смена конфигурации, код уже проверен на реальном сервере.</t>
         </is>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M12" s="14" t="inlineStr">
+      <c r="P12" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
+      <c r="Q12" s="15" t="n"/>
       <c r="R12" s="15" t="n"/>
-      <c r="S12" s="9" t="inlineStr">
+      <c r="S12" s="16" t="n"/>
+      <c r="T12" s="16" t="n"/>
+      <c r="U12" s="15" t="n"/>
+      <c r="V12" s="9" t="inlineStr">
         <is>
           <t>ADR-200; ADR-100</t>
         </is>
@@ -1597,56 +1768,71 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
+          <t>Кэш профиля; Backend (читает); K8s CronJob (пересчёт, MVP); Биллинг и Диспетчерская (источники)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>PostgreSQL (слепки на прототипе, материализованное представление на MVP); Redis; клиент psycopg 3</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
           <t>Слепки внешних систем в Postgres (пример Биллинга и ЛК: 200 счетов, 203 счётчика, 1323 начисления); профиль читается из них.</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Не формальный Feature Store (Feast/Tecton): материализованная таблица плюс быстрый слой Redis. Одну и ту же таблицу читают и офлайн-оценка, и онлайн-инференс — против расхождения обучения и обслуживания.</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — довод «не Feast/Tecton» записан в Data_Flow_Diagrams.html, страница 1, блок «Кэш профиля абонента»</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Периодического пересчёта из живых систем на прототипе нет: данные — слепок из присланного примера.</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>Пересчёт агрегата по расписанию из Биллинга (XML-RPC) и Диспетчерской (REST).</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>Kubernetes CronJob → Postgres (материализованное представление) + Redis.</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>Ответ читает готовый агрегат за O(1), без обращения к первичным системам; тот же примитив, что уже используется для резервного копирования.</t>
         </is>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="O13" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M13" s="14" t="inlineStr">
+      <c r="P13" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="15" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="16" t="n"/>
+      <c r="Q13" s="15" t="n"/>
       <c r="R13" s="15" t="n"/>
-      <c r="S13" s="9" t="inlineStr">
+      <c r="S13" s="16" t="n"/>
+      <c r="T13" s="16" t="n"/>
+      <c r="U13" s="15" t="n"/>
+      <c r="V13" s="9" t="inlineStr">
         <is>
           <t>ADR-200; Data_Flow_Diagrams</t>
         </is>
@@ -1668,56 +1854,71 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
+          <t>Redis; LLM Gateway (лимиты); Backend (сессии диалога)</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Redis 7 (docker `redis:7-alpine`); клиент redis-py</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
           <t>Redis 7 в `docker compose`. Лимиты: фиксированная минута, при недоступности хранилища запросы отклоняются (503), а не пропускаются.</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Счётчики в памяти без Redis (пропуск при сбое) отклонены: лимиты теряются при перезапуске и перестают работать в момент сбоя.</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «Хранилища»: строка «Состояние сессии, квоты» (счётчики в памяти без Redis отклонены)</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>Фиксированное окно даёт двойной лимит на стыке минут — на десятках запросов в минуту это несущественно.</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>Redis в кластере на постоянном диске.</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Redis, StatefulSet + PVC.</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>Состояние и счётчики должны переживать перезапуск пода.</t>
         </is>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L14" s="13" t="inlineStr">
+      <c r="O14" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr">
+      <c r="P14" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="16" t="n"/>
+      <c r="Q14" s="15" t="n"/>
       <c r="R14" s="15" t="n"/>
-      <c r="S14" s="9" t="inlineStr">
+      <c r="S14" s="16" t="n"/>
+      <c r="T14" s="16" t="n"/>
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="9" t="inlineStr">
         <is>
           <t>ADR-200; ADR-400</t>
         </is>
@@ -1739,56 +1940,71 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
+          <t>Postgres; Backend (обращения, профили); LLM Gateway (события использования); Сервис работы с обращениями</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>PostgreSQL 16 (docker `postgres:16-alpine`); драйвер psycopg 3; SQL-скрипты инициализации `docker/postgres/init/`</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
           <t>Postgres 16 в `docker compose`: слепки Биллинга, ЛК и обращений, таблицы обращений, `usage_events`, `quality_reports`.</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Одна база вместо двух на объёме одного стенда.</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — роль базы записана в ADR-200 («Хранилища») и ADR-100 (таблица «упрощённая замена»); сравнение СУБД в пакет не входит</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>На прототипе обращения пишутся прямо в таблицу — микросервиса владельца в закрытой сети нет; слепки вместо живых систем.</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Postgres в Kubernetes только для состояния и обращений; слепки уходят — данные идут через API владельцев.</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Postgres, StatefulSet + PVC, резервное копирование.</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Целевая схема: своей копии чужих данных быть не должно.</t>
         </is>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L15" s="13" t="inlineStr">
+      <c r="O15" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr">
+      <c r="P15" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N15" s="15" t="n"/>
-      <c r="O15" s="15" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="16" t="n"/>
+      <c r="Q15" s="15" t="n"/>
       <c r="R15" s="15" t="n"/>
-      <c r="S15" s="9" t="inlineStr">
+      <c r="S15" s="16" t="n"/>
+      <c r="T15" s="16" t="n"/>
+      <c r="U15" s="15" t="n"/>
+      <c r="V15" s="9" t="inlineStr">
         <is>
           <t>ADR-100; ADR-200</t>
         </is>
@@ -1810,56 +2026,71 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
+          <t>ClickHouse (MVP); LLM Gateway (события использования); Guardrails и судья (отчёты качества)</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Прототип — PostgreSQL (те же таблицы); MVP — ClickHouse</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
           <t>Не развёрнут: те же таблицы (`usage_events`, `quality_reports`) лежат в Postgres; запись — best-effort, не роняет ответ.</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>ClickHouse с первого дня — вторая СУБД ради объёма одного стенда.</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «Хранилища»: строки «Телеметрия»; ADR-100, таблица «упрощённая замена»; сравнения ClickHouse с другими аналитическими базами нет</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>Произвольная нарезка аналитики (по абоненту, типу, модели) на объёме MVP в Postgres будет тормозить.</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Аналитика токенов, стоимости и качества в ClickHouse, запись асинхронной пачкой.</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>ClickHouse, StatefulSet + PVC.</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>Целевое хранилище телеметрии; переезд — смена DSN и диалекта запросов записи, не бизнес-логики.</t>
         </is>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L16" s="13" t="inlineStr">
+      <c r="O16" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr">
+      <c r="P16" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
+      <c r="Q16" s="15" t="n"/>
       <c r="R16" s="15" t="n"/>
-      <c r="S16" s="9" t="inlineStr">
+      <c r="S16" s="16" t="n"/>
+      <c r="T16" s="16" t="n"/>
+      <c r="U16" s="15" t="n"/>
+      <c r="V16" s="9" t="inlineStr">
         <is>
           <t>ADR-100; ADR-200</t>
         </is>
@@ -1881,72 +2112,87 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
+          <t>ETL индексации; Qdrant; embedding-inference; хранилище документов базы знаний</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Python-скрипт `scripts/reindex_kb.py` (сервис `reindex` в docker compose); MVP — K8s CronJob (Celery Beat)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
           <t>Сервис `reindex` в compose: одноразовый прогон при подъёме стека (`scripts/reindex_kb.py`), запись в новую коллекцию и атомарное переключение алиаса; Backend только подключается к готовому индексу.</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Airflow отклонён: для редких некритичных по задержке обновлений хватает планировщика (Celery Beat / CronJob).</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — довод «планировщик под редкие обновления» записан в Data_Flow_Diagrams.html, страница 1, блок «ETL Worker — Ingest», «без Airflow» — в блоке «K8s CronJob» той же страницы; окно запуска — C4_Deployment.html</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>Изоляция GPU между индексацией и онлайн-ответами не решена: массовая переиндексация может увеличить задержку ответа. Свежие документы попадают в индекс с задержкой до ночного окна.</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Ночное окно 02:00–05:00: забор документов, очистка, эмбеддинги на GPU, полный реиндекс.</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>Kubernetes CronJob (Celery Beat), окно обслуживания, жёсткая граница по времени.</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>Не успели — задание прерывается, продолжение в следующем окне; индекс не повреждается, алиас переключается после полного успеха.</t>
         </is>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L17" s="13" t="inlineStr">
+      <c r="O17" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="P17" s="9" t="inlineStr">
         <is>
           <t>Изоляция GPU между индексацией и онлайн-инференсом.</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="Q17" s="9" t="inlineStr">
         <is>
           <t>Приоритетные очереди либо отдельный GPU-пул.</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="R17" s="9" t="inlineStr">
         <is>
           <t>Появляется вторая постоянная нагрузка на GPU (генерация), и индексация не должна её задерживать.</t>
         </is>
       </c>
-      <c r="P17" s="12" t="n">
+      <c r="S17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="Q17" s="12" t="n">
+      <c r="T17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="R17" s="13" t="inlineStr">
+      <c r="U17" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="S17" s="9" t="inlineStr">
+      <c r="V17" s="9" t="inlineStr">
         <is>
           <t>ADR-400; ADR-600; C4_Deployment</t>
         </is>
@@ -1968,72 +2214,87 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
+          <t>Agent Orchestrator; Backend; Session State Store (Redis / PostgreSQL); LLM Gateway</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Python; собственный конечный автомат (`app/fsm.py`) на перечислениях; сессии в Redis / PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
           <t>Свой конечный автомат (`app/fsm.py`), покрыт тестами, в продакшене не включён. Регистрация обращений идёт упрощённым путём напрямую в таблицу.</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>LangGraph — кандидат, не выбран: усложнение ради возможностей, которые пока не нужны.</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «Backend и оркестрация»: строка «Оркестрация агента» (свой FSM против LangGraph)</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос.</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>Включение агента: состояние ожидания подтверждения, идемпотентность, аудит (в том числе отказов абонента), проверка черновика до показа.</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>Свой FSM, Draft Validator, Audit Writer, Session State Store.</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>Запись данных без подтверждённого сценария дороже по ошибке, чем консультация; ни одна запись без явного подтверждения абонента.</t>
         </is>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="M18" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="17" t="n">
+      <c r="N18" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="L18" s="18" t="inlineStr">
+      <c r="O18" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="P18" s="9" t="inlineStr">
         <is>
           <t>Оценка function-calling для роли агента у провайдеров РФ.</t>
         </is>
       </c>
-      <c r="N18" s="9" t="inlineStr">
+      <c r="Q18" s="9" t="inlineStr">
         <is>
           <t>Прогон эталонных сценариев через кандидатов.</t>
         </is>
       </c>
-      <c r="O18" s="9" t="inlineStr">
+      <c r="R18" s="9" t="inlineStr">
         <is>
           <t>От результата зависит, можно ли доверить агенту роль на self-hosted модели.</t>
         </is>
       </c>
-      <c r="P18" s="20" t="n">
+      <c r="S18" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" s="20" t="n">
+      <c r="T18" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="R18" s="21" t="inlineStr">
+      <c r="U18" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
       </c>
-      <c r="S18" s="9" t="inlineStr">
+      <c r="V18" s="9" t="inlineStr">
         <is>
           <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
         </is>
@@ -2055,56 +2316,71 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
+          <t>Billing Adapter; Биллинг (внешняя система); Agent Orchestrator (HITL Gate)</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Python; XML-RPC-клиент к API Биллинга; ключ идемпотентности</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
           <t>Не реализован (запись отложена на Этап 2). Чтение идёт из слепка в Postgres.</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Прямой доступ к чужой БД запрещён: только через API владельца.</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — способ доступа задан ограничением «только через API владельца» — ADR-400 («Закрыто сейчас»), ADR-100</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>Сигнатуры API Биллинга от владельца ещё не получены; write-доступ к чужой legacy-системе — отдельная интеграция.</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Запись показаний и операций в Биллинг через XML-RPC с ключом идемпотентности.</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>Отдельный контейнер `Billing Adapter`, XML-RPC API Биллинга.</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>Единственный разрешённый путь записи в Биллинг; повтор запроса не создаёт дубль.</t>
         </is>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="M19" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="N19" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="L19" s="18" t="inlineStr">
+      <c r="O19" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr">
+      <c r="P19" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="16" t="n"/>
+      <c r="Q19" s="15" t="n"/>
       <c r="R19" s="15" t="n"/>
-      <c r="S19" s="9" t="inlineStr">
+      <c r="S19" s="16" t="n"/>
+      <c r="T19" s="16" t="n"/>
+      <c r="U19" s="15" t="n"/>
+      <c r="V19" s="9" t="inlineStr">
         <is>
           <t>ADR-100; ADR-400</t>
         </is>
@@ -2126,56 +2402,71 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
+          <t>Сервис работы с обращениями; Микросервис обращений и Диспетчерская (внешние); Agent Orchestrator; Postgres</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Python; на прототипе запись в таблицу Postgres, на Этапе 2 — HTTP API владельца (сигнатуры не получены)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
           <t>Обращение пишется в собственную таблицу Postgres, минуя Orchestrator (`app/inquiries/store.py`).</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Целевой путь — внешний микросервис обращений; на прототипе доступа к нему нет.</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — путь описан в ADR-100 (таблица «Что явно отложено»)</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>Микросервис обращений и его API не готовы принимать реальные запросы; код типов обращений не согласован с владельцем.</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>Регистрация через API микросервиса обращений; аварийные заявки — в Диспетчерскую (выбор маршрута по типу).</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>Отдельный контейнер, Route Selector: emergency → Диспетчерская, остальные типы → микросервис.</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>Обращения должны попадать в систему-владельца, откуда их читают подрядчики и конвейер дообучения.</t>
         </is>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="M20" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="K20" s="17" t="n">
+      <c r="N20" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="L20" s="18" t="inlineStr">
+      <c r="O20" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr">
+      <c r="P20" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="16" t="n"/>
+      <c r="Q20" s="15" t="n"/>
       <c r="R20" s="15" t="n"/>
-      <c r="S20" s="9" t="inlineStr">
+      <c r="S20" s="16" t="n"/>
+      <c r="T20" s="16" t="n"/>
+      <c r="U20" s="15" t="n"/>
+      <c r="V20" s="9" t="inlineStr">
         <is>
           <t>ADR-100; ADR-600</t>
         </is>
@@ -2197,56 +2488,71 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
+          <t>Document Generator; Backend (выдача бланка); S3 / MinIO (MVP)</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Прототип — Python: шаблоны бланков и HTML-лист на печать; MVP — PDF-библиотека (не выбрана) + S3 / MinIO</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
           <t>Готовый бланк отдаётся HTML-листом для печати из каталога (семь образцов по ПП РФ № 644/776).</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>PDF и S3/MinIO нужны только при путях записи — для консультации избыточны.</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — путь описан в ADR-100 (таблица «Что явно отложено»); библиотека PDF не выбрана</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Настоящие бланки заявлений не согласованы с владельцем — используются образцы.</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Рендер PDF из шаблона и слотов, хранение в объектном хранилище, ссылка с ограниченным сроком жизни.</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>Генерация PDF (библиотека в ADR не выбрана) + S3 / MinIO.</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>Документ, вложенный в диалог, должен быть файлом, а не страницей печати.</t>
         </is>
       </c>
-      <c r="J21" s="17" t="n">
+      <c r="M21" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="K21" s="17" t="n">
+      <c r="N21" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="L21" s="18" t="inlineStr">
+      <c r="O21" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr">
+      <c r="P21" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="16" t="n"/>
+      <c r="Q21" s="15" t="n"/>
       <c r="R21" s="15" t="n"/>
-      <c r="S21" s="9" t="inlineStr">
+      <c r="S21" s="16" t="n"/>
+      <c r="T21" s="16" t="n"/>
+      <c r="U21" s="15" t="n"/>
+      <c r="V21" s="9" t="inlineStr">
         <is>
           <t>ADR-100; ADR-600</t>
         </is>
@@ -2268,72 +2574,87 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
+          <t>Все контейнеры (Backend, LLM Gateway, Qdrant, Redis, Postgres, ClickHouse, ETL, GPU-сервисы)</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Прототип — Docker Compose на одной машине; MVP — Kubernetes (nginx Ingress, cert-manager)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
           <t>`docker compose` на одной машине: postgres, redis, qdrant, reindex, backend.</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Compose на нескольких хостах не переживает отказ узла; Docker Swarm — мёртвая экосистема. Для одного разработчика и одного хоста Kubernetes избыточен.</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе»</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>Целевая платформа (Kubernetes) пока только подразумевается, отдельного ADR нет.</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>Kubernetes на собственном железе в закрытом контуре: пространства имён, Ingress, TLS-сертификаты.</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>Kubernetes, nginx Ingress, cert-manager.</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>Отказоустойчивость и обновления без остановки; требование целевого развёртывания.</t>
         </is>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L22" s="13" t="inlineStr">
+      <c r="O22" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="P22" s="9" t="inlineStr">
         <is>
           <t>Формализация целевой инфраплатформы отдельным ADR.</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr">
+      <c r="Q22" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O22" s="9" t="inlineStr">
+      <c r="R22" s="9" t="inlineStr">
         <is>
           <t>Kubernetes сейчас лишь подразумевается; для тиража нужна зафиксированная платформа, включая GPU-пулы.</t>
         </is>
       </c>
-      <c r="P22" s="20" t="n">
+      <c r="S22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" s="20" t="n">
+      <c r="T22" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="R22" s="21" t="inlineStr">
+      <c r="U22" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
       </c>
-      <c r="S22" s="9" t="inlineStr">
+      <c r="V22" s="9" t="inlineStr">
         <is>
           <t>ADR-200; ADR-600; C4_Deployment</t>
         </is>
@@ -2355,56 +2676,71 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
+          <t>Backend; LLM Gateway (ключи провайдеров); все контейнеры (конфигурация)</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (опционально); MVP — Vault Agent Injector</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
           <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Опционально Vault в dev-режиме.</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения. Хранение только в CI/CD без Vault дублирует секрет в двух местах.</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «Секреты и конфигурация»; ADR-400 («Что добавляется в контуре MVP»)</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>Dev-режим Vault сам по себе не безопаснее переменной окружения — это репетиция интеграции, а не защита.</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>Vault Agent Injector: секреты попадают в под через sidecar.</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>HashiCorp Vault в Kubernetes.</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>Единый источник истины и отзыв доступа без пересборки образа.</t>
         </is>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L23" s="13" t="inlineStr">
+      <c r="O23" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr">
+      <c r="P23" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N23" s="15" t="n"/>
-      <c r="O23" s="15" t="n"/>
-      <c r="P23" s="16" t="n"/>
-      <c r="Q23" s="16" t="n"/>
+      <c r="Q23" s="15" t="n"/>
       <c r="R23" s="15" t="n"/>
-      <c r="S23" s="9" t="inlineStr">
+      <c r="S23" s="16" t="n"/>
+      <c r="T23" s="16" t="n"/>
+      <c r="U23" s="15" t="n"/>
+      <c r="V23" s="9" t="inlineStr">
         <is>
           <t>ADR-200; ADR-400</t>
         </is>
@@ -2426,56 +2762,71 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); отдельные контейнеры Prometheus, Grafana, Loki, Alertmanager (MVP)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Prometheus, Grafana, Loki, Alertmanager</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
           <t>Метрики Prometheus на отдельном порту, события потока в панели стенда. Дашбордов и сбора логов нет.</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Сравнение не проводилось: инструменты взяты в составе целевой схемы развёртывания.</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — состав MVP зафиксирован в C4_Deployment.html; выбор инструментов не оформлялся</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>Метрики есть, но собирать и показывать их нечему.</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>Полный стек наблюдаемости: метрики, дашборды, логи, оповещения; в логах только отчёт об обезличивании, без значений ПДн.</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>Prometheus, Grafana, Loki, Alertmanager.</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах.</t>
         </is>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="13" t="inlineStr">
+      <c r="O24" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="M24" s="14" t="inlineStr">
+      <c r="P24" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="16" t="n"/>
-      <c r="Q24" s="16" t="n"/>
+      <c r="Q24" s="15" t="n"/>
       <c r="R24" s="15" t="n"/>
-      <c r="S24" s="9" t="inlineStr">
+      <c r="S24" s="16" t="n"/>
+      <c r="T24" s="16" t="n"/>
+      <c r="U24" s="15" t="n"/>
+      <c r="V24" s="9" t="inlineStr">
         <is>
           <t>C4_Deployment; ADR-500</t>
         </is>
@@ -2497,44 +2848,59 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
+          <t>AI-виджет; Backend</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
           <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Сравнение не проводилось: протокол задан контрактом API, потоковая выдача — требованием проекта.</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — контракт описан в API_Spec.yaml; поток ответа обязателен (ADR-100)</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n"/>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="K25" s="15" t="n"/>
+      <c r="L25" s="15" t="inlineStr">
         <is>
           <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
         </is>
       </c>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="15" t="n"/>
-      <c r="M25" s="14" t="inlineStr">
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="16" t="n"/>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N25" s="15" t="n"/>
-      <c r="O25" s="15" t="n"/>
-      <c r="P25" s="16" t="n"/>
-      <c r="Q25" s="16" t="n"/>
+      <c r="Q25" s="15" t="n"/>
       <c r="R25" s="15" t="n"/>
-      <c r="S25" s="9" t="inlineStr">
+      <c r="S25" s="16" t="n"/>
+      <c r="T25" s="16" t="n"/>
+      <c r="U25" s="15" t="n"/>
+      <c r="V25" s="9" t="inlineStr">
         <is>
           <t>API_Spec.yaml</t>
         </is>
@@ -2556,56 +2922,71 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
+          <t>Backend; Платформа ЛК (внешняя)</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
           <t>Не подключена: абонент выбирается из справочника стенда.</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — интеграция не начата: ADR-400, раздел «Не входит в объём Этапа 1»</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
         </is>
       </c>
-      <c r="J26" s="17" t="n">
+      <c r="M26" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="K26" s="17" t="n">
+      <c r="N26" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="L26" s="18" t="inlineStr">
+      <c r="O26" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr">
+      <c r="P26" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="16" t="n"/>
-      <c r="Q26" s="16" t="n"/>
+      <c r="Q26" s="15" t="n"/>
       <c r="R26" s="15" t="n"/>
-      <c r="S26" s="9" t="inlineStr">
+      <c r="S26" s="16" t="n"/>
+      <c r="T26" s="16" t="n"/>
+      <c r="U26" s="15" t="n"/>
+      <c r="V26" s="9" t="inlineStr">
         <is>
           <t>ADR-400; ADR-600</t>
         </is>
@@ -2627,56 +3008,71 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
+          <t>Backend; Кэш профиля (пересчёт из Биллинга); Биллинг (внешняя)</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
           <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — способ доступа задан ограничением «только через API владельца» — ADR-400</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Сигнатуры API Биллинга от владельца не получены.</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Свежие факты запрашиваются у Биллинга в момент вопроса.</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>XML-RPC API Биллинга.</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
         </is>
       </c>
-      <c r="J27" s="20" t="n">
+      <c r="M27" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="20" t="n">
+      <c r="N27" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="21" t="inlineStr">
+      <c r="O27" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
       </c>
-      <c r="M27" s="14" t="inlineStr">
+      <c r="P27" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N27" s="15" t="n"/>
-      <c r="O27" s="15" t="n"/>
-      <c r="P27" s="16" t="n"/>
-      <c r="Q27" s="16" t="n"/>
+      <c r="Q27" s="15" t="n"/>
       <c r="R27" s="15" t="n"/>
-      <c r="S27" s="9" t="inlineStr">
+      <c r="S27" s="16" t="n"/>
+      <c r="T27" s="16" t="n"/>
+      <c r="U27" s="15" t="n"/>
+      <c r="V27" s="9" t="inlineStr">
         <is>
           <t>ADR-400; ADR-600</t>
         </is>
@@ -2698,56 +3094,71 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
+          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
           <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>Прямой доступ к чужой БД запрещён.</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — способ доступа задан ограничением «только через API владельца» — ADR-400; ADR-100</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>REST API Диспетчерской.</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
         </is>
       </c>
-      <c r="J28" s="20" t="n">
+      <c r="M28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="20" t="n">
+      <c r="N28" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L28" s="21" t="inlineStr">
+      <c r="O28" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
       </c>
-      <c r="M28" s="14" t="inlineStr">
+      <c r="P28" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="16" t="n"/>
-      <c r="Q28" s="16" t="n"/>
+      <c r="Q28" s="15" t="n"/>
       <c r="R28" s="15" t="n"/>
-      <c r="S28" s="9" t="inlineStr">
+      <c r="S28" s="16" t="n"/>
+      <c r="T28" s="16" t="n"/>
+      <c r="U28" s="15" t="n"/>
+      <c r="V28" s="9" t="inlineStr">
         <is>
           <t>ADR-100; ADR-400; ADR-600</t>
         </is>
@@ -2769,48 +3180,63 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
+          <t>Backend; LLM Gateway</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
           <t>Вызов внутри одного процесса.</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>HTTP внутри кластера.</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
         </is>
       </c>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-      <c r="L29" s="9" t="n"/>
-      <c r="M29" s="14" t="inlineStr">
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="19" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N29" s="15" t="n"/>
-      <c r="O29" s="15" t="n"/>
-      <c r="P29" s="16" t="n"/>
-      <c r="Q29" s="16" t="n"/>
+      <c r="Q29" s="15" t="n"/>
       <c r="R29" s="15" t="n"/>
-      <c r="S29" s="9" t="inlineStr">
+      <c r="S29" s="16" t="n"/>
+      <c r="T29" s="16" t="n"/>
+      <c r="U29" s="15" t="n"/>
+      <c r="V29" s="9" t="inlineStr">
         <is>
           <t>ADR-200</t>
         </is>
@@ -2832,40 +3258,55 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
+          <t>Backend; Qdrant</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>qdrant-client по HTTP (порт 6333)</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
           <t>HTTP (порт 6333); запись — отдельным сервисом, Backend только читает готовый индекс.</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Вариант доступа не сравнивался: клиент — штатный для выбранной базы.</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «Хранилища»</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="J30" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
+      <c r="K30" s="15" t="n"/>
       <c r="L30" s="15" t="n"/>
-      <c r="M30" s="14" t="inlineStr">
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="16" t="n"/>
-      <c r="Q30" s="16" t="n"/>
+      <c r="Q30" s="15" t="n"/>
       <c r="R30" s="15" t="n"/>
-      <c r="S30" s="9" t="inlineStr">
+      <c r="S30" s="16" t="n"/>
+      <c r="T30" s="16" t="n"/>
+      <c r="U30" s="15" t="n"/>
+      <c r="V30" s="9" t="inlineStr">
         <is>
           <t>ADR-200</t>
         </is>
@@ -2887,56 +3328,71 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
+          <t>LLM Gateway; внешний LLM Provider</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
           <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>HTTPS, сертификаты НУЦ Минцифры.</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
         </is>
       </c>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="9" t="inlineStr">
         <is>
           <t>Вызов собственной модели внутри закрытого контура.</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="Q31" s="9" t="inlineStr">
         <is>
           <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
         </is>
       </c>
-      <c r="O31" s="9" t="inlineStr">
+      <c r="R31" s="9" t="inlineStr">
         <is>
           <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
         </is>
       </c>
-      <c r="P31" s="19" t="n"/>
-      <c r="Q31" s="19" t="n"/>
-      <c r="R31" s="9" t="n"/>
-      <c r="S31" s="9" t="inlineStr">
+      <c r="S31" s="19" t="n"/>
+      <c r="T31" s="19" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="9" t="inlineStr">
         <is>
           <t>ADR-400; ADR-300</t>
         </is>
@@ -2958,44 +3414,59 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
+          <t>ETL индексации; Qdrant</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
           <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Способ переиндексации не сравнивался с другими: выбран режим без остановки поиска.</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, раздел «Хранилища» (Qdrant: переиндексация без остановки поиска)</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="inlineStr">
         <is>
           <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
         </is>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="14" t="inlineStr">
+      <c r="M32" s="16" t="n"/>
+      <c r="N32" s="16" t="n"/>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="16" t="n"/>
-      <c r="Q32" s="16" t="n"/>
+      <c r="Q32" s="15" t="n"/>
       <c r="R32" s="15" t="n"/>
-      <c r="S32" s="9" t="inlineStr">
+      <c r="S32" s="16" t="n"/>
+      <c r="T32" s="16" t="n"/>
+      <c r="U32" s="15" t="n"/>
+      <c r="V32" s="9" t="inlineStr">
         <is>
           <t>ADR-200</t>
         </is>
@@ -3017,60 +3488,75 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
+          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
           <t>Есть прогнозная модель, не смета: числа не утверждены владельцем (открытый P0).</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии.</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — расчёт — Capacity_Report.html; стоимость — ADR-500</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Разброс оценок нагрузки — 25-кратный; без статистики ЛК и колл-центра смета остаётся диапазоном.</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой.</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Разброс оценок нагрузки — 25-кратный; без статистики ЛК и колл-центра смета остаётся диапазоном.</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой.</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Без этого нельзя защищать бюджет.</t>
         </is>
       </c>
-      <c r="J33" s="24" t="n">
+      <c r="M33" s="24" t="n">
         <v>7.5</v>
       </c>
-      <c r="K33" s="17" t="n">
+      <c r="N33" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="L33" s="18" t="inlineStr">
+      <c r="O33" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: P0</t>
         </is>
       </c>
-      <c r="M33" s="14" t="inlineStr">
+      <c r="P33" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N33" s="15" t="n"/>
-      <c r="O33" s="15" t="inlineStr">
+      <c r="Q33" s="15" t="n"/>
+      <c r="R33" s="15" t="inlineStr">
         <is>
           <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
         </is>
       </c>
-      <c r="P33" s="16" t="n"/>
-      <c r="Q33" s="16" t="n"/>
-      <c r="R33" s="15" t="n"/>
-      <c r="S33" s="9" t="inlineStr">
+      <c r="S33" s="16" t="n"/>
+      <c r="T33" s="16" t="n"/>
+      <c r="U33" s="15" t="n"/>
+      <c r="V33" s="9" t="inlineStr">
         <is>
           <t>ADR-500; ADR-600</t>
         </is>
@@ -3092,56 +3578,71 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
+          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Справочники и тексты в коде и данных; не технология</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
           <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки.</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии.</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Календарный срок определяет владелец, не команда.</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Внедрение полученных ответов в справочники и тексты.</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Календарный срок определяет владелец, не команда.</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>Внедрение полученных ответов в справочники и тексты.</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>Разработки не требуют — требуют ответа от водоканала.</t>
         </is>
       </c>
-      <c r="J34" s="17" t="n">
+      <c r="M34" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="17" t="n">
+      <c r="N34" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="L34" s="18" t="inlineStr">
+      <c r="O34" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Согласования</t>
         </is>
       </c>
-      <c r="M34" s="14" t="inlineStr">
+      <c r="P34" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="N34" s="15" t="n"/>
-      <c r="O34" s="15" t="n"/>
-      <c r="P34" s="16" t="n"/>
-      <c r="Q34" s="16" t="n"/>
+      <c r="Q34" s="15" t="n"/>
       <c r="R34" s="15" t="n"/>
-      <c r="S34" s="9" t="inlineStr">
+      <c r="S34" s="16" t="n"/>
+      <c r="T34" s="16" t="n"/>
+      <c r="U34" s="15" t="n"/>
+      <c r="V34" s="9" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
@@ -3163,64 +3664,79 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
+          <t>Все (сквозная работа)</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Документы и диаграммы пакета сдачи</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
           <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии.</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Сравнения нет — состав — ADR-600, раздел «Документация и согласование ИБ»</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Календарный срок определяет служба ИБ водоканала.</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Календарный срок определяет служба ИБ водоканала.</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
+        </is>
+      </c>
+      <c r="M35" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" s="24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O35" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Документация и ИБ</t>
+        </is>
+      </c>
+      <c r="P35" s="9" t="inlineStr">
+        <is>
+          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
+        </is>
+      </c>
+      <c r="Q35" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
-        </is>
-      </c>
-      <c r="J35" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K35" s="24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L35" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Документация и ИБ</t>
-        </is>
-      </c>
-      <c r="M35" s="9" t="inlineStr">
-        <is>
-          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
-        </is>
-      </c>
-      <c r="N35" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O35" s="9" t="inlineStr">
+      <c r="R35" s="9" t="inlineStr">
         <is>
           <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
         </is>
       </c>
-      <c r="P35" s="19" t="n"/>
-      <c r="Q35" s="19" t="n"/>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="inlineStr">
+      <c r="S35" s="19" t="n"/>
+      <c r="T35" s="19" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="inlineStr">
         <is>
           <t>ADR-400; ADR-600</t>
         </is>
@@ -3242,56 +3758,71 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
+          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
           <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (разрыв размеров, русский слабее) и открытых весов GigaChat (менее зрелый инструментарий).</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
+      <c r="K36" s="15" t="n"/>
       <c r="L36" s="15" t="n"/>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="16" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="9" t="inlineStr">
         <is>
           <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
         </is>
       </c>
-      <c r="N36" s="9" t="inlineStr">
+      <c r="Q36" s="9" t="inlineStr">
         <is>
           <t>Qwen2.5-32B INT4, vLLM.</t>
         </is>
       </c>
-      <c r="O36" s="9" t="inlineStr">
+      <c r="R36" s="9" t="inlineStr">
         <is>
           <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
         </is>
       </c>
-      <c r="P36" s="20" t="n">
+      <c r="S36" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="Q36" s="20" t="n">
+      <c r="T36" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="R36" s="21" t="inlineStr">
+      <c r="U36" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
       </c>
-      <c r="S36" s="9" t="inlineStr">
+      <c r="V36" s="9" t="inlineStr">
         <is>
           <t>ADR-300; ADR-500; ADR-600</t>
         </is>
@@ -3313,72 +3844,87 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
+          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
           <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»).</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
         </is>
       </c>
-      <c r="J37" s="17" t="n">
+      <c r="M37" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="K37" s="17" t="n">
+      <c r="N37" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="L37" s="18" t="inlineStr">
+      <c r="O37" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Анализ типов на живых данных</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="P37" s="9" t="inlineStr">
         <is>
           <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr">
+      <c r="Q37" s="9" t="inlineStr">
         <is>
           <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
         </is>
       </c>
-      <c r="O37" s="9" t="inlineStr">
+      <c r="R37" s="9" t="inlineStr">
         <is>
           <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
         </is>
       </c>
-      <c r="P37" s="20" t="n">
+      <c r="S37" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="Q37" s="20" t="n">
+      <c r="T37" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="R37" s="21" t="inlineStr">
+      <c r="U37" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
         </is>
       </c>
-      <c r="S37" s="9" t="inlineStr">
+      <c r="V37" s="9" t="inlineStr">
         <is>
           <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
         </is>
@@ -3424,12 +3970,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S37"/>
+  <autoFilter ref="A2:V37"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="P1:U1"/>
+    <mergeCell ref="J1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -3536,11 +4082,11 @@
         </is>
       </c>
       <c r="B5" s="33">
-        <f>SUM('Матрица'!$J$3:$J$37)</f>
+        <f>SUM('Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="C5" s="33">
-        <f>SUM('Матрица'!$K$3:$K$37)</f>
+        <f>SUM('Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="D5" s="33">
@@ -3552,27 +4098,27 @@
         <v/>
       </c>
       <c r="F5" s="34">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"ADR-600",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"ADR-600",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="G5" s="34">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"ADR-600",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"ADR-600",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="H5" s="35">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока*",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока*",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="I5" s="35">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока*",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока*",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="J5" s="36">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Оценка автора",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Оценка автора",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="K5" s="36">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Оценка автора",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Оценка автора",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -3583,11 +4129,11 @@
         </is>
       </c>
       <c r="B6" s="33">
-        <f>SUM('Матрица'!$P$3:$P$37)</f>
+        <f>SUM('Матрица'!$S$3:$S$37)</f>
         <v/>
       </c>
       <c r="C6" s="33">
-        <f>SUM('Матрица'!$Q$3:$Q$37)</f>
+        <f>SUM('Матрица'!$T$3:$T$37)</f>
         <v/>
       </c>
       <c r="D6" s="33">
@@ -3599,27 +4145,27 @@
         <v/>
       </c>
       <c r="F6" s="34">
-        <f>SUMIF('Матрица'!$R$3:$R$37,"ADR-600",'Матрица'!$P$3:$P$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"ADR-600",'Матрица'!$S$3:$S$37)</f>
         <v/>
       </c>
       <c r="G6" s="34">
-        <f>SUMIF('Матрица'!$R$3:$R$37,"ADR-600",'Матрица'!$Q$3:$Q$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"ADR-600",'Матрица'!$T$3:$T$37)</f>
         <v/>
       </c>
       <c r="H6" s="35">
-        <f>SUMIF('Матрица'!$R$3:$R$37,"Из блока*",'Матрица'!$P$3:$P$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"Из блока*",'Матрица'!$S$3:$S$37)</f>
         <v/>
       </c>
       <c r="I6" s="35">
-        <f>SUMIF('Матрица'!$R$3:$R$37,"Из блока*",'Матрица'!$Q$3:$Q$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"Из блока*",'Матрица'!$T$3:$T$37)</f>
         <v/>
       </c>
       <c r="J6" s="36">
-        <f>SUMIF('Матрица'!$R$3:$R$37,"Оценка автора",'Матрица'!$P$3:$P$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"Оценка автора",'Матрица'!$S$3:$S$37)</f>
         <v/>
       </c>
       <c r="K6" s="36">
-        <f>SUMIF('Матрица'!$R$3:$R$37,"Оценка автора",'Матрица'!$Q$3:$Q$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"Оценка автора",'Матрица'!$T$3:$T$37)</f>
         <v/>
       </c>
     </row>
@@ -3778,11 +4324,11 @@
         <v>10</v>
       </c>
       <c r="D15" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: P0",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: P0",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F15" s="43">
@@ -3808,11 +4354,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Согласования",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Согласования",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F16" s="43">
@@ -3838,11 +4384,11 @@
         <v>25</v>
       </c>
       <c r="D17" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E17" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F17" s="43">
@@ -3868,11 +4414,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E18" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F18" s="43">
@@ -3898,11 +4444,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E19" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F19" s="43">
@@ -3928,11 +4474,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$J$3:$J$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E20" s="33">
-        <f>SUMIF('Матрица'!$L$3:$L$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$K$3:$K$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F20" s="43">
@@ -4372,15 +4918,15 @@
         </is>
       </c>
       <c r="D12" s="33">
-        <f>'Матрица'!J3</f>
+        <f>'Матрица'!M3</f>
         <v/>
       </c>
       <c r="E12" s="33">
-        <f>'Матрица'!K3</f>
+        <f>'Матрица'!N3</f>
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>'Матрица'!L3</f>
+        <f>'Матрица'!O3</f>
         <v/>
       </c>
     </row>
@@ -4399,15 +4945,15 @@
         </is>
       </c>
       <c r="D13" s="33">
-        <f>'Матрица'!J4</f>
+        <f>'Матрица'!M4</f>
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>'Матрица'!K4</f>
+        <f>'Матрица'!N4</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>'Матрица'!L4</f>
+        <f>'Матрица'!O4</f>
         <v/>
       </c>
     </row>
@@ -4426,15 +4972,15 @@
         </is>
       </c>
       <c r="D14" s="33">
-        <f>'Матрица'!J5</f>
+        <f>'Матрица'!M5</f>
         <v/>
       </c>
       <c r="E14" s="33">
-        <f>'Матрица'!K5</f>
+        <f>'Матрица'!N5</f>
         <v/>
       </c>
       <c r="F14" s="18">
-        <f>'Матрица'!L5</f>
+        <f>'Матрица'!O5</f>
         <v/>
       </c>
     </row>
@@ -4453,15 +4999,15 @@
         </is>
       </c>
       <c r="D15" s="33">
-        <f>'Матрица'!J6</f>
+        <f>'Матрица'!M6</f>
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>'Матрица'!K6</f>
+        <f>'Матрица'!N6</f>
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>'Матрица'!L6</f>
+        <f>'Матрица'!O6</f>
         <v/>
       </c>
     </row>
@@ -4480,15 +5026,15 @@
         </is>
       </c>
       <c r="D16" s="33">
-        <f>'Матрица'!J8</f>
+        <f>'Матрица'!M8</f>
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>'Матрица'!K8</f>
+        <f>'Матрица'!N8</f>
         <v/>
       </c>
       <c r="F16" s="18">
-        <f>'Матрица'!L8</f>
+        <f>'Матрица'!O8</f>
         <v/>
       </c>
     </row>
@@ -4507,15 +5053,15 @@
         </is>
       </c>
       <c r="D17" s="33">
-        <f>'Матрица'!J9</f>
+        <f>'Матрица'!M9</f>
         <v/>
       </c>
       <c r="E17" s="33">
-        <f>'Матрица'!K9</f>
+        <f>'Матрица'!N9</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>'Матрица'!L9</f>
+        <f>'Матрица'!O9</f>
         <v/>
       </c>
     </row>
@@ -4534,15 +5080,15 @@
         </is>
       </c>
       <c r="D18" s="33">
-        <f>'Матрица'!J10</f>
+        <f>'Матрица'!M10</f>
         <v/>
       </c>
       <c r="E18" s="33">
-        <f>'Матрица'!K10</f>
+        <f>'Матрица'!N10</f>
         <v/>
       </c>
       <c r="F18" s="18">
-        <f>'Матрица'!L10</f>
+        <f>'Матрица'!O10</f>
         <v/>
       </c>
     </row>
@@ -4561,15 +5107,15 @@
         </is>
       </c>
       <c r="D19" s="33">
-        <f>'Матрица'!J11</f>
+        <f>'Матрица'!M11</f>
         <v/>
       </c>
       <c r="E19" s="33">
-        <f>'Матрица'!K11</f>
+        <f>'Матрица'!N11</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>'Матрица'!L11</f>
+        <f>'Матрица'!O11</f>
         <v/>
       </c>
     </row>
@@ -4588,15 +5134,15 @@
         </is>
       </c>
       <c r="D20" s="33">
-        <f>'Матрица'!J12</f>
+        <f>'Матрица'!M12</f>
         <v/>
       </c>
       <c r="E20" s="33">
-        <f>'Матрица'!K12</f>
+        <f>'Матрица'!N12</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>'Матрица'!L12</f>
+        <f>'Матрица'!O12</f>
         <v/>
       </c>
     </row>
@@ -4615,15 +5161,15 @@
         </is>
       </c>
       <c r="D21" s="33">
-        <f>'Матрица'!J13</f>
+        <f>'Матрица'!M13</f>
         <v/>
       </c>
       <c r="E21" s="33">
-        <f>'Матрица'!K13</f>
+        <f>'Матрица'!N13</f>
         <v/>
       </c>
       <c r="F21" s="13">
-        <f>'Матрица'!L13</f>
+        <f>'Матрица'!O13</f>
         <v/>
       </c>
     </row>
@@ -4642,15 +5188,15 @@
         </is>
       </c>
       <c r="D22" s="33">
-        <f>'Матрица'!J14</f>
+        <f>'Матрица'!M14</f>
         <v/>
       </c>
       <c r="E22" s="33">
-        <f>'Матрица'!K14</f>
+        <f>'Матрица'!N14</f>
         <v/>
       </c>
       <c r="F22" s="13">
-        <f>'Матрица'!L14</f>
+        <f>'Матрица'!O14</f>
         <v/>
       </c>
     </row>
@@ -4669,15 +5215,15 @@
         </is>
       </c>
       <c r="D23" s="33">
-        <f>'Матрица'!J15</f>
+        <f>'Матрица'!M15</f>
         <v/>
       </c>
       <c r="E23" s="33">
-        <f>'Матрица'!K15</f>
+        <f>'Матрица'!N15</f>
         <v/>
       </c>
       <c r="F23" s="13">
-        <f>'Матрица'!L15</f>
+        <f>'Матрица'!O15</f>
         <v/>
       </c>
     </row>
@@ -4696,15 +5242,15 @@
         </is>
       </c>
       <c r="D24" s="33">
-        <f>'Матрица'!J16</f>
+        <f>'Матрица'!M16</f>
         <v/>
       </c>
       <c r="E24" s="33">
-        <f>'Матрица'!K16</f>
+        <f>'Матрица'!N16</f>
         <v/>
       </c>
       <c r="F24" s="13">
-        <f>'Матрица'!L16</f>
+        <f>'Матрица'!O16</f>
         <v/>
       </c>
     </row>
@@ -4723,15 +5269,15 @@
         </is>
       </c>
       <c r="D25" s="33">
-        <f>'Матрица'!J17</f>
+        <f>'Матрица'!M17</f>
         <v/>
       </c>
       <c r="E25" s="33">
-        <f>'Матрица'!K17</f>
+        <f>'Матрица'!N17</f>
         <v/>
       </c>
       <c r="F25" s="13">
-        <f>'Матрица'!L17</f>
+        <f>'Матрица'!O17</f>
         <v/>
       </c>
     </row>
@@ -4750,15 +5296,15 @@
         </is>
       </c>
       <c r="D26" s="33">
-        <f>'Матрица'!P17</f>
+        <f>'Матрица'!S17</f>
         <v/>
       </c>
       <c r="E26" s="33">
-        <f>'Матрица'!Q17</f>
+        <f>'Матрица'!T17</f>
         <v/>
       </c>
       <c r="F26" s="13">
-        <f>'Матрица'!R17</f>
+        <f>'Матрица'!U17</f>
         <v/>
       </c>
     </row>
@@ -4777,15 +5323,15 @@
         </is>
       </c>
       <c r="D27" s="33">
-        <f>'Матрица'!J18</f>
+        <f>'Матрица'!M18</f>
         <v/>
       </c>
       <c r="E27" s="33">
-        <f>'Матрица'!K18</f>
+        <f>'Матрица'!N18</f>
         <v/>
       </c>
       <c r="F27" s="18">
-        <f>'Матрица'!L18</f>
+        <f>'Матрица'!O18</f>
         <v/>
       </c>
     </row>
@@ -4804,15 +5350,15 @@
         </is>
       </c>
       <c r="D28" s="33">
-        <f>'Матрица'!J19</f>
+        <f>'Матрица'!M19</f>
         <v/>
       </c>
       <c r="E28" s="33">
-        <f>'Матрица'!K19</f>
+        <f>'Матрица'!N19</f>
         <v/>
       </c>
       <c r="F28" s="18">
-        <f>'Матрица'!L19</f>
+        <f>'Матрица'!O19</f>
         <v/>
       </c>
     </row>
@@ -4831,15 +5377,15 @@
         </is>
       </c>
       <c r="D29" s="33">
-        <f>'Матрица'!J20</f>
+        <f>'Матрица'!M20</f>
         <v/>
       </c>
       <c r="E29" s="33">
-        <f>'Матрица'!K20</f>
+        <f>'Матрица'!N20</f>
         <v/>
       </c>
       <c r="F29" s="18">
-        <f>'Матрица'!L20</f>
+        <f>'Матрица'!O20</f>
         <v/>
       </c>
     </row>
@@ -4858,15 +5404,15 @@
         </is>
       </c>
       <c r="D30" s="33">
-        <f>'Матрица'!J21</f>
+        <f>'Матрица'!M21</f>
         <v/>
       </c>
       <c r="E30" s="33">
-        <f>'Матрица'!K21</f>
+        <f>'Матрица'!N21</f>
         <v/>
       </c>
       <c r="F30" s="18">
-        <f>'Матрица'!L21</f>
+        <f>'Матрица'!O21</f>
         <v/>
       </c>
     </row>
@@ -4885,15 +5431,15 @@
         </is>
       </c>
       <c r="D31" s="33">
-        <f>'Матрица'!J22</f>
+        <f>'Матрица'!M22</f>
         <v/>
       </c>
       <c r="E31" s="33">
-        <f>'Матрица'!K22</f>
+        <f>'Матрица'!N22</f>
         <v/>
       </c>
       <c r="F31" s="13">
-        <f>'Матрица'!L22</f>
+        <f>'Матрица'!O22</f>
         <v/>
       </c>
     </row>
@@ -4912,15 +5458,15 @@
         </is>
       </c>
       <c r="D32" s="33">
-        <f>'Матрица'!J23</f>
+        <f>'Матрица'!M23</f>
         <v/>
       </c>
       <c r="E32" s="33">
-        <f>'Матрица'!K23</f>
+        <f>'Матрица'!N23</f>
         <v/>
       </c>
       <c r="F32" s="13">
-        <f>'Матрица'!L23</f>
+        <f>'Матрица'!O23</f>
         <v/>
       </c>
     </row>
@@ -4939,15 +5485,15 @@
         </is>
       </c>
       <c r="D33" s="33">
-        <f>'Матрица'!J24</f>
+        <f>'Матрица'!M24</f>
         <v/>
       </c>
       <c r="E33" s="33">
-        <f>'Матрица'!K24</f>
+        <f>'Матрица'!N24</f>
         <v/>
       </c>
       <c r="F33" s="13">
-        <f>'Матрица'!L24</f>
+        <f>'Матрица'!O24</f>
         <v/>
       </c>
     </row>
@@ -4966,15 +5512,15 @@
         </is>
       </c>
       <c r="D34" s="33">
-        <f>'Матрица'!J26</f>
+        <f>'Матрица'!M26</f>
         <v/>
       </c>
       <c r="E34" s="33">
-        <f>'Матрица'!K26</f>
+        <f>'Матрица'!N26</f>
         <v/>
       </c>
       <c r="F34" s="18">
-        <f>'Матрица'!L26</f>
+        <f>'Матрица'!O26</f>
         <v/>
       </c>
     </row>
@@ -4993,15 +5539,15 @@
         </is>
       </c>
       <c r="D35" s="33">
-        <f>'Матрица'!J33</f>
+        <f>'Матрица'!M33</f>
         <v/>
       </c>
       <c r="E35" s="33">
-        <f>'Матрица'!K33</f>
+        <f>'Матрица'!N33</f>
         <v/>
       </c>
       <c r="F35" s="18">
-        <f>'Матрица'!L33</f>
+        <f>'Матрица'!O33</f>
         <v/>
       </c>
     </row>
@@ -5020,15 +5566,15 @@
         </is>
       </c>
       <c r="D36" s="33">
-        <f>'Матрица'!J34</f>
+        <f>'Матрица'!M34</f>
         <v/>
       </c>
       <c r="E36" s="33">
-        <f>'Матрица'!K34</f>
+        <f>'Матрица'!N34</f>
         <v/>
       </c>
       <c r="F36" s="18">
-        <f>'Матрица'!L34</f>
+        <f>'Матрица'!O34</f>
         <v/>
       </c>
     </row>
@@ -5047,15 +5593,15 @@
         </is>
       </c>
       <c r="D37" s="33">
-        <f>'Матрица'!J35</f>
+        <f>'Матрица'!M35</f>
         <v/>
       </c>
       <c r="E37" s="33">
-        <f>'Матрица'!K35</f>
+        <f>'Матрица'!N35</f>
         <v/>
       </c>
       <c r="F37" s="18">
-        <f>'Матрица'!L35</f>
+        <f>'Матрица'!O35</f>
         <v/>
       </c>
     </row>
@@ -5074,15 +5620,15 @@
         </is>
       </c>
       <c r="D38" s="33">
-        <f>'Матрица'!J37</f>
+        <f>'Матрица'!M37</f>
         <v/>
       </c>
       <c r="E38" s="33">
-        <f>'Матрица'!K37</f>
+        <f>'Матрица'!N37</f>
         <v/>
       </c>
       <c r="F38" s="18">
-        <f>'Матрица'!L37</f>
+        <f>'Матрица'!O37</f>
         <v/>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — причина выбора для прототипа записана в ADR-100 («Что сдано») и в примечании C3/C4_L3_Widget.html; выбор React/TS для MVP не сравнивался, он указан в C4_Deployment.html</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Интерфейс абонента: виджет»</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Базовый набор Presidio не годился: лицевой счёт определялся как телефон, одна почта получала три метки. Поэтому распознаватели разделены на собственные и Presidio.</t>
+          <t>Presidio + собственные распознаватели выбраны против «только регулярных выражений» (не находят ФИО), русского NER вроде Natasha (закрывает только ФИО) и внешнего сервиса (данные уходят за периметр, запрещено). Базовый набор Presidio один не годился: лицевой счёт определялся как телефон, одна почта получала три метки.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — состав и правило «ПДн не покидают периметр» — ADR-400, раздел «Закрыто сейчас»; сравнение вариантов обезличивания в пакет не входит</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Почему Presidio и собственные распознаватели»</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Судья не может совпадать с отвечающей моделью: при совпадении оценка пропускается и это фиксируется — лучше пропуск, чем завышенная оценка.</t>
+          <t>Проверки на потоке — регулярные выражения (бюджет менее 50 мс на кусок; ML-модель токсичности и LLM-судья в бюджет не укладываются, внешний сервис уносит данные за периметр). Судья не может совпадать с отвечающей моделью: при совпадении оценка пропускается и это фиксируется.</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 5 «Судья качества ответа» (модели судьи); проверки на потоке — сравнения нет</t>
+          <t>ADR-300, раздел 5 «Судья качества ответа» (модели судьи); ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Почему проверки ответа — регулярные выражения на потоке» (проверки на потоке)</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Хранилища»: строка «Векторный поиск (целевое)» (pgvector, Milvus)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (и строка «Векторный поиск (целевое)» в таблице «Хранилища»)</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — довод «не Feast/Tecton» записан в Data_Flow_Diagrams.html, страница 1, блок «Кэш профиля абонента»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему кэш профиля — таблица и Redis, а не Feature Store»</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Счётчики в памяти без Redis (пропуск при сбое) отклонены: лимиты теряются при перезапуске и перестают работать в момент сбоя.</t>
+          <t>Redis выбран против Memcached (нет структур для сессии), таблицы счётчиков в Postgres (нагрузка на основную базу) и счётчиков в памяти процесса (лимиты обнуляются при перезапуске, fail-open).</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Хранилища»: строка «Состояние сессии, квоты» (счётчики в памяти без Redis отклонены)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему PostgreSQL и Redis»</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Одна база вместо двух на объёме одного стенда.</t>
+          <t>PostgreSQL выбран против MySQL/MariaDB (нет материализованных представлений) и SQLite (один файл, не для нескольких сервисов). Одна база вместо двух на объёме одного стенда.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — роль базы записана в ADR-200 («Хранилища») и ADR-100 (таблица «упрощённая замена»); сравнение СУБД в пакет не входит</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему PostgreSQL и Redis»</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>ClickHouse с первого дня — вторая СУБД ради объёма одного стенда.</t>
+          <t>ClickHouse — целевой выбор против PostgreSQL (годится для стенда, при росте замедляется), TimescaleDB (остаётся строковым хранилищем) и OpenSearch (тяжелее без выигрыша). На прототипе ClickHouse не нужен: вторая СУБД ради объёма одного стенда.</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Хранилища»: строки «Телеметрия»; ADR-100, таблица «упрощённая замена»; сравнения ClickHouse с другими аналитическими базами нет</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему ClickHouse для телеметрии»</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Airflow отклонён: для редких некритичных по задержке обновлений хватает планировщика (Celery Beat / CronJob).</t>
+          <t>Планировщик по расписанию выбран против Airflow (платформа ради одного задания) и cron внутри Backend (нет изоляции от ответов абонентам).</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — довод «планировщик под редкие обновления» записан в Data_Flow_Diagrams.html, страница 1, блок «ETL Worker — Ingest», «без Airflow» — в блоке «K8s CronJob» той же страницы; окно запуска — C4_Deployment.html</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему индексация — задание по расписанию, а не Airflow»</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — способ доступа задан ограничением «только через API владельца» — ADR-400 («Закрыто сейчас»), ADR-100</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — путь описан в ADR-100 (таблица «Что явно отложено»)</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»; ADR-100, таблица «Что явно отложено»</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — путь описан в ADR-100 (таблица «Что явно отложено»); библиотека PDF не выбрана</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Документы Этапа 2: PDF и хранилище файлов (решение не принято)»</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Сравнение не проводилось: инструменты взяты в составе целевой схемы развёртывания.</t>
+          <t>Prometheus + Grafana + Loki + Alertmanager выбраны против ELK/OpenSearch, Zabbix и облачного мониторинга: закрытый контур (152-ФЗ), метрики Kubernetes и приложения, недорогие логи (Loki индексирует метки, а не текст). Сравнение по документации; пробного развёртывания альтернатив не было.</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — состав MVP зафиксирован в C4_Deployment.html; выбор инструментов не оформлялся</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Prometheus, Grafana, Loki и Alertmanager»</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Сравнение не проводилось: протокол задан контрактом API, потоковая выдача — требованием проекта.</t>
+          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — контракт описан в API_Spec.yaml; поток ответа обязателен (ADR-100)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — интеграция не начата: ADR-400, раздел «Не входит в объём Этапа 1»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — способ доступа задан ограничением «только через API владельца» — ADR-400</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — способ доступа задан ограничением «только через API владельца» — ADR-400; ADR-100</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Вариант доступа не сравнивался: клиент — штатный для выбранной базы.</t>
+          <t>Клиент по HTTP, а не gRPC: задержка HTTP-вызова — единицы миллисекунд при бюджете поиска 100 мс, gRPC добавил бы зависимость без выигрыша.</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Хранилища»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Способ переиндексации не сравнивался с другими: выбран режим без остановки поиска.</t>
+          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Хранилища» (Qdrant: переиндексация без остановки поиска)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — расчёт — Capacity_Report.html; стоимость — ADR-500</t>
+          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
+          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>Сравнения нет — состав — ADR-600, раздел «Документация и согласование ИБ»</t>
+          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники и допущения" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Синхронно (до 50 мс): ПДн в ответе, тон, разглашение промпта — при нарушении поток обрывается. Асинхронно: судья обоснованности (локальная Qwen2.5-7B через Ollama), не блокирует выдачу.</t>
+          <t>Назначение: проверить ответ модели до показа абоненту — персональные данные, недопустимый тон, разглашение внутренних инструкций. Синхронно (до 50 мс): ПДн в ответе, тон, разглашение промпта — при нарушении поток обрывается. Асинхронно: судья обоснованности (локальная Qwen2.5-7B через Ollama), не блокирует выдачу.</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>Судья слабый, оценка предварительная (provisional): пороги качества не откалиброваны на размеченном наборе.</t>
+          <t>Проверки на потоке подобраны без живых ответов модели: частота ложных блокировок и пропусков неизвестна. Судья слабый, оценка предварительная (provisional): пороги качества не откалиброваны на размеченном наборе.</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>Судья на другом провайдере, чем отвечающая модель; калибровка порогов.</t>
+          <t>Судья на другом провайдере, чем отвечающая модель; калибровка порогов. Проверка работоспособности проверок на живых данных (ложные блокировки, пропуски ПДн, тона и разглашения промпта) — в строке «Проверка на живых данных: Guardrails и выбор провайдера» ниже.</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Качество ответов не измерено на собственном эталонном наборе; выбор модели по репутации.</t>
+          <t>Ни YandexGPT, ни GigaChat не проверены на живых вопросах абонентов; GigaChat на прототипе недоступен. Качество ответов не измерено на собственном эталонном наборе; выбор модели по репутации.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>GigaChat Pro как основная, YandexGPT как резерв с автопереключением.</t>
+          <t>GigaChat Pro как основная, YandexGPT как резерв с автопереключением — предварительно: оба провайдера проверяются на ограниченном объёме живых вопросов, после чего принимается решение об основном и запасном (строка «Проверка на живых данных…» ниже).</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -3930,47 +3930,133 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="C39" s="25" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит.</t>
+        </is>
+      </c>
+      <c r="M38" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N38" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="O38" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
+        </is>
+      </c>
+      <c r="P38" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q38" s="15" t="n"/>
+      <c r="R38" s="15" t="n"/>
+      <c r="S38" s="16" t="n"/>
+      <c r="T38" s="16" t="n"/>
+      <c r="U38" s="15" t="n"/>
+      <c r="V38" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300; ADR-400; ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="25" t="inlineStr">
         <is>
           <t>Цвет ячеек с оценкой:</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="27" t="inlineStr">
+    <row r="41">
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="C41" s="28" t="n"/>
-      <c r="D41" s="27" t="inlineStr">
+    <row r="42">
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="C42" s="29" t="n"/>
-      <c r="D42" s="27" t="inlineStr">
+    <row r="43">
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="27" t="inlineStr">
         <is>
           <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="27" t="inlineStr">
+    <row r="44">
+      <c r="C44" s="30" t="n"/>
+      <c r="D44" s="27" t="inlineStr">
         <is>
           <t>изменений на этом этапе нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V37"/>
+  <autoFilter ref="A2:V38"/>
   <mergeCells count="4">
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
@@ -3988,7 +4074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4082,11 +4168,11 @@
         </is>
       </c>
       <c r="B5" s="33">
-        <f>SUM('Матрица'!$M$3:$M$37)</f>
+        <f>SUM('Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="C5" s="33">
-        <f>SUM('Матрица'!$N$3:$N$37)</f>
+        <f>SUM('Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="D5" s="33">
@@ -4098,27 +4184,27 @@
         <v/>
       </c>
       <c r="F5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"ADR-600",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="G5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"ADR-600",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="H5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока*",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="I5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока*",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="J5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Оценка автора",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="K5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Оценка автора",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
     </row>
@@ -4129,11 +4215,11 @@
         </is>
       </c>
       <c r="B6" s="33">
-        <f>SUM('Матрица'!$S$3:$S$37)</f>
+        <f>SUM('Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
       <c r="C6" s="33">
-        <f>SUM('Матрица'!$T$3:$T$37)</f>
+        <f>SUM('Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
       <c r="D6" s="33">
@@ -4145,27 +4231,27 @@
         <v/>
       </c>
       <c r="F6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"ADR-600",'Матрица'!$S$3:$S$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
       <c r="G6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"ADR-600",'Матрица'!$T$3:$T$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
       <c r="H6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"Из блока*",'Матрица'!$S$3:$S$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
       <c r="I6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"Из блока*",'Матрица'!$T$3:$T$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
       <c r="J6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"Оценка автора",'Матрица'!$S$3:$S$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
       <c r="K6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"Оценка автора",'Матрица'!$T$3:$T$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
     </row>
@@ -4324,11 +4410,11 @@
         <v>10</v>
       </c>
       <c r="D15" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F15" s="43">
@@ -4354,11 +4440,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F16" s="43">
@@ -4384,11 +4470,11 @@
         <v>25</v>
       </c>
       <c r="D17" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E17" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F17" s="43">
@@ -4414,11 +4500,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E18" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F18" s="43">
@@ -4444,11 +4530,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E19" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F19" s="43">
@@ -4474,11 +4560,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E20" s="33">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F20" s="43">
@@ -4494,109 +4580,106 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
+          <t>Проверка Guardrails и провайдеров на живых данных</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="D21" s="33">
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$38)</f>
+        <v/>
+      </c>
+      <c r="E21" s="33">
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$38)</f>
+        <v/>
+      </c>
+      <c r="F21" s="43">
+        <f>IF(AND(D21=B21,E21=C21),"да","НЕТ")</f>
+        <v/>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>10–16 чел-дн (ADR-600): выборка 1–2, Guardrails 4–6, сравнение провайдеров 4–6, решение 1–2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>Итого по блокам</t>
         </is>
       </c>
-      <c r="B21" s="37">
-        <f>SUM(B15:B20)</f>
-        <v/>
-      </c>
-      <c r="C21" s="37">
-        <f>SUM(C15:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="37">
-        <f>SUM(D15:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="37">
-        <f>SUM(E15:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="44">
-        <f>IF(AND(D21=B21,E21=C21),"да","НЕТ")</f>
-        <v/>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>ADR-600 называет итог ≈13–20 недель (≈65–100 чел-дн); сумма блоков 66,5–99,5 — округление в самом ADR-600</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="B22" s="37">
+        <f>SUM(B15:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="37">
+        <f>SUM(C15:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="37">
+        <f>SUM(D15:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="37">
+        <f>SUM(E15:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="44">
+        <f>IF(AND(D22=B22,E22=C22),"да","НЕТ")</f>
+        <v/>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>ADR-600 называет итог ≈15–23 недели (≈75–115 чел-дн); сумма блоков 76,5–115,5 — округление в самом ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>Затраты, которые не выражаются человеко-днями</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Контур</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Значение / комментарий</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>От</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>До</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Единица</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Источник</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Токены генерации (YandexGPT Pro, 0,8 ₽ за 1000 токенов)</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>≈146 ₽/мес при базовом сценарии (10% визитов, 30% до модели) — ≈1 698 ₽/мес при максимальном (50%, 70%)</t>
-        </is>
-      </c>
-      <c r="D25" s="41" t="n">
-        <v>146</v>
-      </c>
-      <c r="E25" s="41" t="n">
-        <v>1698</v>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>₽/мес</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>ADR-500</t>
         </is>
       </c>
     </row>
@@ -4608,24 +4691,28 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>GPU-сервер под эмбеддинги и реранкер</t>
+          <t>Токены генерации (YandexGPT Pro, 0,8 ₽ за 1000 токенов)</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Не оценён отдельной строкой сметы</t>
-        </is>
-      </c>
-      <c r="D26" s="41" t="n"/>
-      <c r="E26" s="41" t="n"/>
+          <t>≈146 ₽/мес при базовом сценарии (10% визитов, 30% до модели) — ≈1 698 ₽/мес при максимальном (50%, 70%)</t>
+        </is>
+      </c>
+      <c r="D26" s="41" t="n">
+        <v>146</v>
+      </c>
+      <c r="E26" s="41" t="n">
+        <v>1698</v>
+      </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>₽</t>
+          <t>₽/мес</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>ADR-500 (открытый пункт)</t>
+          <t>ADR-500</t>
         </is>
       </c>
     </row>
@@ -4637,12 +4724,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
+          <t>GPU-сервер под эмбеддинги и реранкер</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Не оценены</t>
+          <t>Не оценён отдельной строкой сметы</t>
         </is>
       </c>
       <c r="D27" s="41" t="n"/>
@@ -4661,25 +4748,21 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Карта A100 80 ГБ (покупка)</t>
+          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером)</t>
-        </is>
-      </c>
-      <c r="D28" s="41" t="n">
-        <v>927000</v>
-      </c>
-      <c r="E28" s="41" t="n">
-        <v>2368080</v>
-      </c>
+          <t>Не оценены</t>
+        </is>
+      </c>
+      <c r="D28" s="41" t="n"/>
+      <c r="E28" s="41" t="n"/>
       <c r="F28" s="9" t="inlineStr">
         <is>
           <t>₽</t>
@@ -4687,7 +4770,7 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
@@ -4699,29 +4782,62 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
+          <t>Карта A100 80 ГБ (покупка)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером)</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="n">
+        <v>927000</v>
+      </c>
+      <c r="E29" s="41" t="n">
+        <v>2368080</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>₽</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>ADR-500</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Тираж</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
           <t>Сервер-хост, электричество, размещение, обслуживание GPU</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Не оценены</t>
         </is>
       </c>
-      <c r="D29" s="41" t="n"/>
-      <c r="E29" s="41" t="n"/>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="D30" s="41" t="n"/>
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>₽</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Все суммы в ₽ — прогнозная модель, не смета: CAPEX/OPEX не утверждены владельцем (ADR-500). Закупка GPU — недели или месяцы лид-тайма, не разработка.</t>
         </is>
@@ -4744,7 +4860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5632,104 +5748,131 @@
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="42" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9">
+        <f>'Матрица'!A38</f>
+        <v/>
+      </c>
+      <c r="B39" s="9">
+        <f>'Матрица'!C38</f>
+        <v/>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D39" s="33">
+        <f>'Матрица'!M38</f>
+        <v/>
+      </c>
+      <c r="E39" s="33">
+        <f>'Матрица'!N38</f>
+        <v/>
+      </c>
+      <c r="F39" s="18">
+        <f>'Матрица'!O38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="42" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -5737,18 +5880,18 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C47:F47"/>
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C49:F49"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C47:F47"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C44:F44"/>
   </mergeCells>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1415,7 +1415,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>GigaChat технически недоступен на машине прототипа (нужны корневые сертификаты НУЦ; отключать проверку TLS недопустимо). Зарубежные провайдеры отклонены на всех этапах: 152-ФЗ.</t>
+          <t>GigaChat технически недоступен на машине прототипа (нужны корневые сертификаты НУЦ; отключать проверку TLS недопустимо). Зарубежные провайдеры отклонены на всех этапах: 152-ФЗ. Собственная модель тиража: Qwen2.5-32B выбран против Llama 3.x и открытых весов GigaChat — лицензия Apache 2.0, сильный русский среди открытых моделей, одно семейство 7B (уже используется для тестов) → 32B без переделки, 32B в INT4 помещается на одну карту A100 (34 ГБ весов плюс запас под кэш). Выбор сделан по репутации модели, на своём эталонном наборе не проверен; прогон запланирован при переходе к тиражу (3–5 чел-дн, ADR-600).</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>Правила и словарь — как сейчас; k-NN на эмбеддингах BGE-M3 (GPU) — тем же эмбеддером, что и поиск.</t>
+          <t>Правила и словарь — как сейчас; k-NN на эмбеддере поиска (предварительно BGE-M3, GPU); пороги подбираются заново, окончательная модель — по итогам анализа на живых обращениях.</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>Те же правила; k-NN на BGE-M3.</t>
+          <t>Те же правила; k-NN на эмбеддере поиска (модель — по решению для MVP и тиража).</t>
         </is>
       </c>
       <c r="R5" s="9" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Сравнение моделей проведено в ADR-300, раздел 2 (задержка и размер — замер `scripts/measure_search_models.py`); замер поиска на прототипе — `golden_set/measurement.json` (e5-small: 20 из 20 на вопросах корпуса, 12 из 30 на первом месте и 23 из 30 в первой тройке на живых формулировках). Кандидаты: BGE-M3: 4,25 ГБ, 210 мс на CPU (вдвое выше бюджета), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
+          <t>Сравнение моделей проведено в ADR-300, раздел 2 (задержка и размер — замер `scripts/measure_search_models.py`); замер поиска на прототипе — `golden_set/measurement.json` (e5-small: 20 из 20 на вопросах корпуса, 12 из 30 на первом месте и 23 из 30 в первой тройке на живых формулировках). Почему BGE-M3 для MVP: многоязычная, длинные тексты, общий каркас с реранкером BGE-reranker-v2-m3 — это свойства модели, а не замер на своих данных; подробно и с перечнем кандидатов — ADR-300, «Почему BGE-M3 — кандидат для MVP и что будет сравниваться». Кандидаты: BGE-M3: 4,25 ГБ, 210 мс на CPU (вдвое выше бюджета), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 2 «Эмбеддинги»; замер поиска — golden_set/measurement.json; скрипт замера — scripts/measure_search_models.py</t>
+          <t>ADR-300, раздел 2 «Эмбеддинги» и подраздел «Почему BGE-M3 — кандидат для MVP и что будет сравниваться»; замер поиска — golden_set/measurement.json; скрипт замера — scripts/measure_search_models.py</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1532,7 +1532,7 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>BGE-M3 на GPU (общий сервис для онлайн-поиска и индексации) — предварительный выбор: окончательно модель выбирается заново после анализа всех типов на живых обращениях (строка «Анализ всех типов…»).</t>
+          <t>BGE-M3 на GPU (общий сервис для онлайн-поиска и индексации) — предварительный выбор: окончательно модель выбирается по тесту 4–5 моделей (e5-small, e5-large, BGE-M3, модели, дообученные на русском) на размеченном наборе из живых обращений; пороги подбираются под каждую модель (ADR-600, «Тест моделей эмбеддингов для MVP»). Размеченный набор берётся из строки «Анализ всех типов…».</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="M10" s="17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N10" s="17" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O10" s="18" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="B17" s="33" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C17" s="33" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D17" s="33">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$38)</f>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>≈3,5–5 недель: расширение классификатора 10–15 чел-дн + сравнение моделей 3–4 + реранкер 2–3 + судья 2–3</t>
+          <t>≈5–7 недель: расширение классификатора 10–15 чел-дн + тест моделей эмбеддингов 10–14 + реранкер 2–3 + судья 2–3</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>ADR-600 называет итог ≈15–23 недели (≈75–115 чел-дн); сумма блоков 76,5–115,5 — округление в самом ADR-600</t>
+          <t>ADR-600 называет итог ≈17–25 недель (≈85–125 чел-дн); сумма блоков 83,5–125,5 — округление в самом ADR-600</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Почему Presidio и собственные распознаватели»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Почему Presidio и собственные распознаватели»; подраздел «Модель разбора языка для обезличивания: что будет сравниваться»</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -1272,16 +1272,32 @@
           <t>Эмбеддинг запроса минует фильтр, поэтому онлайн-эмбеддинги допустимы только локальные (внешний API для запроса запрещён).</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K7" s="15" t="n"/>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="16" t="n"/>
-      <c r="N7" s="16" t="n"/>
-      <c r="O7" s="15" t="n"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Проверка полноты обезличивания на размеченных живых обращениях (ФИО, адрес, телефон, лицевой счёт, почта): сколько ПДн пропущено; сравнение моделей разбора языка (spaCy md / sm / lg, Natasha); правка распознавателей.</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Presidio + spaCy (модель выбирается по замеру) + собственные распознаватели; скрипты замера полноты и точности.</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Для 152-ФЗ пропуск ПДн опаснее ложной находки, а полнота на живых данных не измерялась: измерены только ложные находки на 136 обращениях.</t>
+        </is>
+      </c>
+      <c r="M7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Качество поиска и классификации</t>
+        </is>
+      </c>
       <c r="P7" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -1294,7 +1310,7 @@
       <c r="U7" s="15" t="n"/>
       <c r="V7" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-300</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1350,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 5 «Судья качества ответа» (модели судьи); ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Почему проверки ответа — регулярные выражения на потоке» (проверки на потоке)</t>
+          <t>ADR-300, раздел 5 «Судья качества ответа» и подраздел «Судья качества: какие модели и что будет сравниваться»; ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Почему проверки ответа — регулярные выражения на потоке» (проверки на потоке)</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -1344,12 +1360,12 @@
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>Судья на другом провайдере, чем отвечающая модель; калибровка порогов. Проверка работоспособности проверок на живых данных (ложные блокировки, пропуски ПДн, тона и разглашения промпта) — в строке «Проверка на живых данных: Guardrails и выбор провайдера» ниже.</t>
+          <t>Судья на другом провайдере, чем отвечающая модель; тест нескольких моделей судьи (Qwen2.5-7B, Qwen2.5-14B/32B, YandexGPT, GigaChat Pro) против ручной разметки 100–200 живых ответов; калибровка порогов (6–9 чел-дн). Проверка работоспособности проверок на живых данных (ложные блокировки, пропуски ПДн, тона и разглашения промпта) — в строке «Проверка на живых данных: Guardrails и выбор провайдера» ниже.</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>YandexGPT как судья при GigaChat Pro в роли отвечающей модели.</t>
+          <t>Судья — YandexGPT при отвечающем GigaChat Pro или наоборот (по решению об основном провайдере); выбор модели судьи — по замеру согласия с человеком.</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
@@ -1358,10 +1374,10 @@
         </is>
       </c>
       <c r="M8" s="17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N8" s="17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O8" s="18" t="inlineStr">
         <is>
@@ -1611,12 +1627,12 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU.</t>
+          <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU. BGE-reranker-v2-m3 выбран как целевой: многоязычный, из того же семейства, что BGE-M3, и проверен на 30 живых формулировках (первое место у 21 из 30 вместо 7, MRR 0,79 вместо 0,52). Другие реранкеры (jina-reranker-v2, mMiniLM, bge-reranker-v2-gemma) не измерялись.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 3 «Переранжирование»; замер — golden_set/reranking.json</t>
+          <t>ADR-300, раздел 3 «Переранжирование» и подраздел «Почему BGE-reranker-v2-m3 — кандидат для MVP и что будет сравниваться»; замер — golden_set/reranking.json</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1626,7 +1642,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Включён в онлайн-поиске; замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство.</t>
+          <t>Включён в онлайн-поиске; замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (5–7 чел-дн) — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -1640,10 +1656,10 @@
         </is>
       </c>
       <c r="M11" s="17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N11" s="17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O11" s="18" t="inlineStr">
         <is>
@@ -4464,10 +4480,10 @@
         </is>
       </c>
       <c r="B17" s="33" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C17" s="33" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D17" s="33">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$38)</f>
@@ -4483,7 +4499,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>≈5–7 недель: расширение классификатора 10–15 чел-дн + тест моделей эмбеддингов 10–14 + реранкер 2–3 + судья 2–3</t>
+          <t>≈7,5–11 недель: классификатор 10–15 + эмбеддинги 10–14 + реранкер 7–10 + судья 6–9 + полнота обезличивания 4–6</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4651,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>ADR-600 называет итог ≈17–25 недель (≈85–125 чел-дн); сумма блоков 83,5–125,5 — округление в самом ADR-600</t>
+          <t>ADR-600 называет итог ≈19–29 недель (≈95–145 чел-дн); сумма блоков 96,5–144,5 — округление в самом ADR-600</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5129,11 +5145,11 @@
     </row>
     <row r="16">
       <c r="A16" s="9">
-        <f>'Матрица'!A8</f>
+        <f>'Матрица'!A7</f>
         <v/>
       </c>
       <c r="B16" s="9">
-        <f>'Матрица'!C8</f>
+        <f>'Матрица'!C7</f>
         <v/>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5142,25 +5158,25 @@
         </is>
       </c>
       <c r="D16" s="33">
-        <f>'Матрица'!M8</f>
+        <f>'Матрица'!M7</f>
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>'Матрица'!N8</f>
+        <f>'Матрица'!N7</f>
         <v/>
       </c>
       <c r="F16" s="18">
-        <f>'Матрица'!O8</f>
+        <f>'Матрица'!O7</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9">
-        <f>'Матрица'!A9</f>
+        <f>'Матрица'!A8</f>
         <v/>
       </c>
       <c r="B17" s="9">
-        <f>'Матрица'!C9</f>
+        <f>'Матрица'!C8</f>
         <v/>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5169,25 +5185,25 @@
         </is>
       </c>
       <c r="D17" s="33">
-        <f>'Матрица'!M9</f>
+        <f>'Матрица'!M8</f>
         <v/>
       </c>
       <c r="E17" s="33">
-        <f>'Матрица'!N9</f>
-        <v/>
-      </c>
-      <c r="F17" s="13">
-        <f>'Матрица'!O9</f>
+        <f>'Матрица'!N8</f>
+        <v/>
+      </c>
+      <c r="F17" s="18">
+        <f>'Матрица'!O8</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>'Матрица'!A10</f>
+        <f>'Матрица'!A9</f>
         <v/>
       </c>
       <c r="B18" s="9">
-        <f>'Матрица'!C10</f>
+        <f>'Матрица'!C9</f>
         <v/>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5196,25 +5212,25 @@
         </is>
       </c>
       <c r="D18" s="33">
-        <f>'Матрица'!M10</f>
+        <f>'Матрица'!M9</f>
         <v/>
       </c>
       <c r="E18" s="33">
-        <f>'Матрица'!N10</f>
-        <v/>
-      </c>
-      <c r="F18" s="18">
-        <f>'Матрица'!O10</f>
+        <f>'Матрица'!N9</f>
+        <v/>
+      </c>
+      <c r="F18" s="13">
+        <f>'Матрица'!O9</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9">
-        <f>'Матрица'!A11</f>
+        <f>'Матрица'!A10</f>
         <v/>
       </c>
       <c r="B19" s="9">
-        <f>'Матрица'!C11</f>
+        <f>'Матрица'!C10</f>
         <v/>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5223,25 +5239,25 @@
         </is>
       </c>
       <c r="D19" s="33">
-        <f>'Матрица'!M11</f>
+        <f>'Матрица'!M10</f>
         <v/>
       </c>
       <c r="E19" s="33">
-        <f>'Матрица'!N11</f>
+        <f>'Матрица'!N10</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>'Матрица'!O11</f>
+        <f>'Матрица'!O10</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9">
-        <f>'Матрица'!A12</f>
+        <f>'Матрица'!A11</f>
         <v/>
       </c>
       <c r="B20" s="9">
-        <f>'Матрица'!C12</f>
+        <f>'Матрица'!C11</f>
         <v/>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5250,25 +5266,25 @@
         </is>
       </c>
       <c r="D20" s="33">
-        <f>'Матрица'!M12</f>
+        <f>'Матрица'!M11</f>
         <v/>
       </c>
       <c r="E20" s="33">
-        <f>'Матрица'!N12</f>
-        <v/>
-      </c>
-      <c r="F20" s="13">
-        <f>'Матрица'!O12</f>
+        <f>'Матрица'!N11</f>
+        <v/>
+      </c>
+      <c r="F20" s="18">
+        <f>'Матрица'!O11</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>'Матрица'!A13</f>
+        <f>'Матрица'!A12</f>
         <v/>
       </c>
       <c r="B21" s="9">
-        <f>'Матрица'!C13</f>
+        <f>'Матрица'!C12</f>
         <v/>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5277,25 +5293,25 @@
         </is>
       </c>
       <c r="D21" s="33">
-        <f>'Матрица'!M13</f>
+        <f>'Матрица'!M12</f>
         <v/>
       </c>
       <c r="E21" s="33">
-        <f>'Матрица'!N13</f>
+        <f>'Матрица'!N12</f>
         <v/>
       </c>
       <c r="F21" s="13">
-        <f>'Матрица'!O13</f>
+        <f>'Матрица'!O12</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9">
-        <f>'Матрица'!A14</f>
+        <f>'Матрица'!A13</f>
         <v/>
       </c>
       <c r="B22" s="9">
-        <f>'Матрица'!C14</f>
+        <f>'Матрица'!C13</f>
         <v/>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -5304,25 +5320,25 @@
         </is>
       </c>
       <c r="D22" s="33">
-        <f>'Матрица'!M14</f>
+        <f>'Матрица'!M13</f>
         <v/>
       </c>
       <c r="E22" s="33">
-        <f>'Матрица'!N14</f>
+        <f>'Матрица'!N13</f>
         <v/>
       </c>
       <c r="F22" s="13">
-        <f>'Матрица'!O14</f>
+        <f>'Матрица'!O13</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9">
-        <f>'Матрица'!A15</f>
+        <f>'Матрица'!A14</f>
         <v/>
       </c>
       <c r="B23" s="9">
-        <f>'Матрица'!C15</f>
+        <f>'Матрица'!C14</f>
         <v/>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5331,25 +5347,25 @@
         </is>
       </c>
       <c r="D23" s="33">
-        <f>'Матрица'!M15</f>
+        <f>'Матрица'!M14</f>
         <v/>
       </c>
       <c r="E23" s="33">
-        <f>'Матрица'!N15</f>
+        <f>'Матрица'!N14</f>
         <v/>
       </c>
       <c r="F23" s="13">
-        <f>'Матрица'!O15</f>
+        <f>'Матрица'!O14</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9">
-        <f>'Матрица'!A16</f>
+        <f>'Матрица'!A15</f>
         <v/>
       </c>
       <c r="B24" s="9">
-        <f>'Матрица'!C16</f>
+        <f>'Матрица'!C15</f>
         <v/>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -5358,25 +5374,25 @@
         </is>
       </c>
       <c r="D24" s="33">
-        <f>'Матрица'!M16</f>
+        <f>'Матрица'!M15</f>
         <v/>
       </c>
       <c r="E24" s="33">
-        <f>'Матрица'!N16</f>
+        <f>'Матрица'!N15</f>
         <v/>
       </c>
       <c r="F24" s="13">
-        <f>'Матрица'!O16</f>
+        <f>'Матрица'!O15</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9">
-        <f>'Матрица'!A17</f>
+        <f>'Матрица'!A16</f>
         <v/>
       </c>
       <c r="B25" s="9">
-        <f>'Матрица'!C17</f>
+        <f>'Матрица'!C16</f>
         <v/>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5385,15 +5401,15 @@
         </is>
       </c>
       <c r="D25" s="33">
-        <f>'Матрица'!M17</f>
+        <f>'Матрица'!M16</f>
         <v/>
       </c>
       <c r="E25" s="33">
-        <f>'Матрица'!N17</f>
+        <f>'Матрица'!N16</f>
         <v/>
       </c>
       <c r="F25" s="13">
-        <f>'Матрица'!O17</f>
+        <f>'Матрица'!O16</f>
         <v/>
       </c>
     </row>
@@ -5408,56 +5424,56 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="D26" s="33">
-        <f>'Матрица'!S17</f>
+        <f>'Матрица'!M17</f>
         <v/>
       </c>
       <c r="E26" s="33">
-        <f>'Матрица'!T17</f>
+        <f>'Матрица'!N17</f>
         <v/>
       </c>
       <c r="F26" s="13">
-        <f>'Матрица'!U17</f>
+        <f>'Матрица'!O17</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9">
-        <f>'Матрица'!A18</f>
+        <f>'Матрица'!A17</f>
         <v/>
       </c>
       <c r="B27" s="9">
-        <f>'Матрица'!C18</f>
+        <f>'Матрица'!C17</f>
         <v/>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Тираж</t>
         </is>
       </c>
       <c r="D27" s="33">
-        <f>'Матрица'!M18</f>
+        <f>'Матрица'!S17</f>
         <v/>
       </c>
       <c r="E27" s="33">
-        <f>'Матрица'!N18</f>
-        <v/>
-      </c>
-      <c r="F27" s="18">
-        <f>'Матрица'!O18</f>
+        <f>'Матрица'!T17</f>
+        <v/>
+      </c>
+      <c r="F27" s="13">
+        <f>'Матрица'!U17</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9">
-        <f>'Матрица'!A19</f>
+        <f>'Матрица'!A18</f>
         <v/>
       </c>
       <c r="B28" s="9">
-        <f>'Матрица'!C19</f>
+        <f>'Матрица'!C18</f>
         <v/>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -5466,25 +5482,25 @@
         </is>
       </c>
       <c r="D28" s="33">
-        <f>'Матрица'!M19</f>
+        <f>'Матрица'!M18</f>
         <v/>
       </c>
       <c r="E28" s="33">
-        <f>'Матрица'!N19</f>
+        <f>'Матрица'!N18</f>
         <v/>
       </c>
       <c r="F28" s="18">
-        <f>'Матрица'!O19</f>
+        <f>'Матрица'!O18</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9">
-        <f>'Матрица'!A20</f>
+        <f>'Матрица'!A19</f>
         <v/>
       </c>
       <c r="B29" s="9">
-        <f>'Матрица'!C20</f>
+        <f>'Матрица'!C19</f>
         <v/>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -5493,25 +5509,25 @@
         </is>
       </c>
       <c r="D29" s="33">
-        <f>'Матрица'!M20</f>
+        <f>'Матрица'!M19</f>
         <v/>
       </c>
       <c r="E29" s="33">
-        <f>'Матрица'!N20</f>
+        <f>'Матрица'!N19</f>
         <v/>
       </c>
       <c r="F29" s="18">
-        <f>'Матрица'!O20</f>
+        <f>'Матрица'!O19</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9">
-        <f>'Матрица'!A21</f>
+        <f>'Матрица'!A20</f>
         <v/>
       </c>
       <c r="B30" s="9">
-        <f>'Матрица'!C21</f>
+        <f>'Матрица'!C20</f>
         <v/>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -5520,25 +5536,25 @@
         </is>
       </c>
       <c r="D30" s="33">
-        <f>'Матрица'!M21</f>
+        <f>'Матрица'!M20</f>
         <v/>
       </c>
       <c r="E30" s="33">
-        <f>'Матрица'!N21</f>
+        <f>'Матрица'!N20</f>
         <v/>
       </c>
       <c r="F30" s="18">
-        <f>'Матрица'!O21</f>
+        <f>'Матрица'!O20</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9">
-        <f>'Матрица'!A22</f>
+        <f>'Матрица'!A21</f>
         <v/>
       </c>
       <c r="B31" s="9">
-        <f>'Матрица'!C22</f>
+        <f>'Матрица'!C21</f>
         <v/>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -5547,25 +5563,25 @@
         </is>
       </c>
       <c r="D31" s="33">
-        <f>'Матрица'!M22</f>
+        <f>'Матрица'!M21</f>
         <v/>
       </c>
       <c r="E31" s="33">
-        <f>'Матрица'!N22</f>
-        <v/>
-      </c>
-      <c r="F31" s="13">
-        <f>'Матрица'!O22</f>
+        <f>'Матрица'!N21</f>
+        <v/>
+      </c>
+      <c r="F31" s="18">
+        <f>'Матрица'!O21</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9">
-        <f>'Матрица'!A23</f>
+        <f>'Матрица'!A22</f>
         <v/>
       </c>
       <c r="B32" s="9">
-        <f>'Матрица'!C23</f>
+        <f>'Матрица'!C22</f>
         <v/>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -5574,25 +5590,25 @@
         </is>
       </c>
       <c r="D32" s="33">
-        <f>'Матрица'!M23</f>
+        <f>'Матрица'!M22</f>
         <v/>
       </c>
       <c r="E32" s="33">
-        <f>'Матрица'!N23</f>
+        <f>'Матрица'!N22</f>
         <v/>
       </c>
       <c r="F32" s="13">
-        <f>'Матрица'!O23</f>
+        <f>'Матрица'!O22</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9">
-        <f>'Матрица'!A24</f>
+        <f>'Матрица'!A23</f>
         <v/>
       </c>
       <c r="B33" s="9">
-        <f>'Матрица'!C24</f>
+        <f>'Матрица'!C23</f>
         <v/>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -5601,25 +5617,25 @@
         </is>
       </c>
       <c r="D33" s="33">
-        <f>'Матрица'!M24</f>
+        <f>'Матрица'!M23</f>
         <v/>
       </c>
       <c r="E33" s="33">
-        <f>'Матрица'!N24</f>
+        <f>'Матрица'!N23</f>
         <v/>
       </c>
       <c r="F33" s="13">
-        <f>'Матрица'!O24</f>
+        <f>'Матрица'!O23</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9">
-        <f>'Матрица'!A26</f>
+        <f>'Матрица'!A24</f>
         <v/>
       </c>
       <c r="B34" s="9">
-        <f>'Матрица'!C26</f>
+        <f>'Матрица'!C24</f>
         <v/>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -5628,25 +5644,25 @@
         </is>
       </c>
       <c r="D34" s="33">
-        <f>'Матрица'!M26</f>
+        <f>'Матрица'!M24</f>
         <v/>
       </c>
       <c r="E34" s="33">
-        <f>'Матрица'!N26</f>
-        <v/>
-      </c>
-      <c r="F34" s="18">
-        <f>'Матрица'!O26</f>
+        <f>'Матрица'!N24</f>
+        <v/>
+      </c>
+      <c r="F34" s="13">
+        <f>'Матрица'!O24</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9">
-        <f>'Матрица'!A33</f>
+        <f>'Матрица'!A26</f>
         <v/>
       </c>
       <c r="B35" s="9">
-        <f>'Матрица'!C33</f>
+        <f>'Матрица'!C26</f>
         <v/>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -5655,25 +5671,25 @@
         </is>
       </c>
       <c r="D35" s="33">
-        <f>'Матрица'!M33</f>
+        <f>'Матрица'!M26</f>
         <v/>
       </c>
       <c r="E35" s="33">
-        <f>'Матрица'!N33</f>
+        <f>'Матрица'!N26</f>
         <v/>
       </c>
       <c r="F35" s="18">
-        <f>'Матрица'!O33</f>
+        <f>'Матрица'!O26</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9">
-        <f>'Матрица'!A34</f>
+        <f>'Матрица'!A33</f>
         <v/>
       </c>
       <c r="B36" s="9">
-        <f>'Матрица'!C34</f>
+        <f>'Матрица'!C33</f>
         <v/>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -5682,25 +5698,25 @@
         </is>
       </c>
       <c r="D36" s="33">
-        <f>'Матрица'!M34</f>
+        <f>'Матрица'!M33</f>
         <v/>
       </c>
       <c r="E36" s="33">
-        <f>'Матрица'!N34</f>
+        <f>'Матрица'!N33</f>
         <v/>
       </c>
       <c r="F36" s="18">
-        <f>'Матрица'!O34</f>
+        <f>'Матрица'!O33</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9">
-        <f>'Матрица'!A35</f>
+        <f>'Матрица'!A34</f>
         <v/>
       </c>
       <c r="B37" s="9">
-        <f>'Матрица'!C35</f>
+        <f>'Матрица'!C34</f>
         <v/>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -5709,25 +5725,25 @@
         </is>
       </c>
       <c r="D37" s="33">
-        <f>'Матрица'!M35</f>
+        <f>'Матрица'!M34</f>
         <v/>
       </c>
       <c r="E37" s="33">
-        <f>'Матрица'!N35</f>
+        <f>'Матрица'!N34</f>
         <v/>
       </c>
       <c r="F37" s="18">
-        <f>'Матрица'!O35</f>
+        <f>'Матрица'!O34</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <f>'Матрица'!A37</f>
+        <f>'Матрица'!A35</f>
         <v/>
       </c>
       <c r="B38" s="9">
-        <f>'Матрица'!C37</f>
+        <f>'Матрица'!C35</f>
         <v/>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -5736,143 +5752,170 @@
         </is>
       </c>
       <c r="D38" s="33">
-        <f>'Матрица'!M37</f>
+        <f>'Матрица'!M35</f>
         <v/>
       </c>
       <c r="E38" s="33">
-        <f>'Матрица'!N37</f>
+        <f>'Матрица'!N35</f>
         <v/>
       </c>
       <c r="F38" s="18">
-        <f>'Матрица'!O37</f>
+        <f>'Матрица'!O35</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9">
+        <f>'Матрица'!A37</f>
+        <v/>
+      </c>
+      <c r="B39" s="9">
+        <f>'Матрица'!C37</f>
+        <v/>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D39" s="33">
+        <f>'Матрица'!M37</f>
+        <v/>
+      </c>
+      <c r="E39" s="33">
+        <f>'Матрица'!N37</f>
+        <v/>
+      </c>
+      <c r="F39" s="18">
+        <f>'Матрица'!O37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9">
         <f>'Матрица'!A38</f>
         <v/>
       </c>
-      <c r="B39" s="9">
+      <c r="B40" s="9">
         <f>'Матрица'!C38</f>
         <v/>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="D39" s="33">
+      <c r="D40" s="33">
         <f>'Матрица'!M38</f>
         <v/>
       </c>
-      <c r="E39" s="33">
+      <c r="E40" s="33">
         <f>'Матрица'!N38</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F40" s="18">
         <f>'Матрица'!O38</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="42" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="42" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -5886,13 +5929,13 @@
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C42:F42"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C46:F46"/>
     <mergeCell ref="C47:F47"/>
     <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C50:F50"/>
     <mergeCell ref="C44:F44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1104,14 +1104,14 @@
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>Чтобы обращения по всем типам справочника регистрировались автоматически. Пороги надо подбирать заново: их величина — свойство пары «модель + примеры». Оценка в этой строке — только расширение классификатора и подбор порогов: 2–3 недели после появления размеченного корпуса (ADR-600). Анализ на живых данных и пересборка таблицы — 13–19 чел-дн в строке «Анализ всех типов…»; вместе с ним работа над классификатором — 23–34 чел-дн.</t>
+          <t>Чтобы обращения по всем типам справочника регистрировались автоматически. Пороги надо подбирать заново: их величина — свойство пары «модель + примеры». Оценка в этой строке — только расширение классификатора и подбор порогов: 1,5–2,5 недели после появления размеченного корпуса (ADR-600). Анализ на живых данных и пересборка таблицы — 13–19 чел-дн в строке «Анализ всех типов…»; вместе с ним работа над классификатором — 23–34 чел-дн.</t>
         </is>
       </c>
       <c r="M5" s="17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N5" s="17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O5" s="18" t="inlineStr">
         <is>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="B17" s="33" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" s="33" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D17" s="33">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$38)</f>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>≈7,5–11 недель: классификатор 10–15 + эмбеддинги 10–14 + реранкер 7–10 + судья 6–9 + полнота обезличивания 4–6</t>
+          <t>≈7–10 недель: классификатор 8–12 + эмбеддинги 10–14 + реранкер 7–10 + судья 6–9 + полнота обезличивания 4–6</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>ADR-600 называет итог ≈19–29 недель (≈95–145 чел-дн); сумма блоков 96,5–144,5 — округление в самом ADR-600</t>
+          <t>ADR-600 называет итог ≈19–28 недель (≈95–140 чел-дн); сумма блоков 94,5–141,5 — округление в самом ADR-600</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1789,22 +1789,22 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>PostgreSQL (слепки на прототипе, материализованное представление на MVP); Redis; клиент psycopg 3</t>
+          <t>Прототип: словари в памяти процесса из CSV. MVP: PostgreSQL (материализованное представление; клиент psycopg 3), Redis поверх — предварительно, по замеру задержки</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Слепки внешних систем в Postgres (пример Биллинга и ЛК: 200 счетов, 203 счётчика, 1323 начисления); профиль читается из них.</t>
+          <t>Пример Биллинга и ЛК (200 счетов, 203 счётчика, 1323 начисления) читается из CSV при старте в словари в памяти процесса (`app/billing/source.py`). Postgres и Redis для профиля на прототипе не используются.</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Не формальный Feature Store (Feast/Tecton): материализованная таблица плюс быстрый слой Redis. Одну и ту же таблицу читают и офлайн-оценка, и онлайн-инференс — против расхождения обучения и обслуживания.</t>
+          <t>Не формальный Feature Store (Feast/Tecton): избыточен для одной таблицы. Сравнивались также слепок в памяти (не работает для нескольких реплик), материализованное представление Postgres без Redis и чтение из Биллинга на каждый вопрос (нагрузка и задержка). Слой Redis поверх представления замером не обоснован: возможно, достаточно одного Postgres; решение по замеру задержки чтения на MVP.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему кэш профиля — таблица и Redis, а не Feature Store»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Кэш профиля абонента: где хранить и с чем сравнивали»</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes CronJob → Postgres (материализованное представление) + Redis.</t>
+          <t>Kubernetes CronJob → Postgres (материализованное представление); Redis поверх — предварительно, по замеру.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -213,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -277,6 +277,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1779,7 +1782,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Кэш профиля абонента (Postgres + Redis)</t>
+          <t>Кэш профиля абонента (Postgres)</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1789,7 +1792,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Прототип: словари в памяти процесса из CSV. MVP: PostgreSQL (материализованное представление; клиент psycopg 3), Redis поверх — предварительно, по замеру задержки</t>
+          <t>Прототип: словари в памяти процесса из CSV. MVP: PostgreSQL (материализованное представление; клиент psycopg 3), без Redis; возврат Redis — по итогам замера</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -1799,7 +1802,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Не формальный Feature Store (Feast/Tecton): избыточен для одной таблицы. Сравнивались также слепок в памяти (не работает для нескольких реплик), материализованное представление Postgres без Redis и чтение из Биллинга на каждый вопрос (нагрузка и задержка). Слой Redis поверх представления замером не обоснован: возможно, достаточно одного Postgres; решение по замеру задержки чтения на MVP.</t>
+          <t>Не формальный Feature Store (Feast/Tecton): избыточен для одной таблицы. Сравнивались также слепок в памяти (не работает для нескольких реплик), материализованное представление Postgres без Redis и чтение из Биллинга на каждый вопрос (нагрузка и задержка). Redis для профиля не берётся: выигрыш над индексным чтением Postgres не показан, второй источник данных — цена без пользы; на MVP закладывается замер чтения (1,5–2 чел-дн), Redis возвращается только если замер не уложится в бюджет.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -1814,28 +1817,28 @@
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Пересчёт агрегата по расписанию из Биллинга (XML-RPC) и Диспетчерской (REST).</t>
+          <t>Пересчёт агрегата по расписанию из Биллинга (XML-RPC) и Диспетчерской (REST); замер чтения профиля из Postgres под нагрузкой MVP (1,5–2 чел-дн, ADR-600).</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes CronJob → Postgres (материализованное представление); Redis поверх — предварительно, по замеру.</t>
+          <t>Kubernetes CronJob → Postgres (материализованное представление). Без Redis; возврат Redis — только по итогам замера.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Ответ читает готовый агрегат за O(1), без обращения к первичным системам; тот же примитив, что уже используется для резервного копирования.</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>5</v>
+          <t>Ответ читает готовый агрегат по индексу, без обращения к первичным системам; тот же примитив, что уже используется для резервного копирования.</t>
+        </is>
+      </c>
+      <c r="M13" s="22" t="n">
+        <v>6.5</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Оценка автора</t>
+          <t>Оценка автора; замер профиля — ADR-600</t>
         </is>
       </c>
       <c r="P13" s="14" t="inlineStr">
@@ -1850,7 +1853,7 @@
       <c r="U13" s="15" t="n"/>
       <c r="V13" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; Data_Flow_Diagrams</t>
+          <t>ADR-200; ADR-600; Data_Flow_Diagrams</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2855,7 @@
       <c r="A25" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -2926,7 +2929,7 @@
       <c r="A26" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3012,7 +3015,7 @@
       <c r="A27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3098,7 +3101,7 @@
       <c r="A28" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3184,7 +3187,7 @@
       <c r="A29" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3262,7 +3265,7 @@
       <c r="A30" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3332,7 +3335,7 @@
       <c r="A31" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3418,7 +3421,7 @@
       <c r="A32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
@@ -3492,7 +3495,7 @@
       <c r="A33" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
@@ -3547,7 +3550,7 @@
           <t>Без этого нельзя защищать бюджет.</t>
         </is>
       </c>
-      <c r="M33" s="24" t="n">
+      <c r="M33" s="25" t="n">
         <v>7.5</v>
       </c>
       <c r="N33" s="17" t="n">
@@ -3582,7 +3585,7 @@
       <c r="A34" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
@@ -3668,7 +3671,7 @@
       <c r="A35" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
@@ -3726,7 +3729,7 @@
       <c r="M35" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="N35" s="24" t="n">
+      <c r="N35" s="25" t="n">
         <v>7.5</v>
       </c>
       <c r="O35" s="18" t="inlineStr">
@@ -3762,7 +3765,7 @@
       <c r="A36" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
@@ -3848,7 +3851,7 @@
       <c r="A37" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
@@ -3950,7 +3953,7 @@
       <c r="A38" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
@@ -4033,39 +4036,39 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>Цвет ячеек с оценкой:</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="26" t="n"/>
-      <c r="D41" s="27" t="inlineStr">
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="28" t="inlineStr">
         <is>
           <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="28" t="n"/>
-      <c r="D42" s="27" t="inlineStr">
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="28" t="inlineStr">
         <is>
           <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="27" t="inlineStr">
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="28" t="inlineStr">
         <is>
           <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="30" t="n"/>
-      <c r="D44" s="27" t="inlineStr">
+      <c r="C44" s="31" t="n"/>
+      <c r="D44" s="28" t="inlineStr">
         <is>
           <t>изменений на этом этапе нет</t>
         </is>
@@ -4107,14 +4110,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Стоимость доработок по контурам</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>Единица — человеко-день. 1 неделя = 5 чел-дн; размер команды в ADR-600 не задан, поэтому считается как один исполнитель.</t>
         </is>
@@ -4183,43 +4186,43 @@
           <t>MVP — 8 000 абонентов</t>
         </is>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="34">
         <f>SUM('Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <f>SUM('Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="34">
         <f>B5/5</f>
         <v/>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="34">
         <f>C5/5</f>
         <v/>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="35">
         <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="36">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="36">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="J5" s="36">
+      <c r="J5" s="37">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="K5" s="36">
+      <c r="K5" s="37">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
@@ -4230,43 +4233,43 @@
           <t>Тираж — 90 000 абонентов</t>
         </is>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="34">
         <f>SUM('Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>SUM('Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <f>B6/5</f>
         <v/>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>C6/5</f>
         <v/>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="35">
         <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="35">
         <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="36">
         <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="36">
         <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="37">
         <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="37">
         <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
@@ -4277,49 +4280,49 @@
           <t>Итого</t>
         </is>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="38">
         <f>SUM(B5:B6)</f>
         <v/>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="38">
         <f>SUM(C5:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="38">
         <f>SUM(D5:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="38">
         <f>SUM(E5:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="38">
         <f>SUM(F5:F6)</f>
         <v/>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="38">
         <f>SUM(G5:G6)</f>
         <v/>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="38">
         <f>SUM(H5:H6)</f>
         <v/>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="38">
         <f>SUM(I5:I6)</f>
         <v/>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="38">
         <f>SUM(J5:J6)</f>
         <v/>
       </c>
-      <c r="K7" s="37">
+      <c r="K7" s="38">
         <f>SUM(K5:K6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>«Оценка автора» — работы, которых нет в ADR-600 (инфраструктура MVP, виджет, вынос шлюза и т. п.); поэтому итог MVP больше, чем «9–13 недель» ADR-600.</t>
         </is>
@@ -4331,9 +4334,9 @@
           <t>Ставка, ₽ за чел-день (не задана — введите)</t>
         </is>
       </c>
-      <c r="B9" s="38" t="n"/>
-      <c r="C9" s="39" t="n"/>
-      <c r="D9" s="40" t="n"/>
+      <c r="B9" s="39" t="n"/>
+      <c r="C9" s="40" t="n"/>
+      <c r="D9" s="41" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -4341,13 +4344,13 @@
           <t>Стоимость доработок MVP, ₽ (мин — макс)</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="39" t="n"/>
-      <c r="D10" s="41">
+      <c r="B10" s="39" t="n"/>
+      <c r="C10" s="40" t="n"/>
+      <c r="D10" s="42">
         <f>IF($D$9="","",B5*$D$9)</f>
         <v/>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="42">
         <f>IF($D$9="","",C5*$D$9)</f>
         <v/>
       </c>
@@ -4358,19 +4361,19 @@
           <t>Стоимость доработок тиража, ₽ (мин — макс)</t>
         </is>
       </c>
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="39" t="n"/>
-      <c r="D11" s="41">
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="42">
         <f>IF($D$9="","",B6*$D$9)</f>
         <v/>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="42">
         <f>IF($D$9="","",C6*$D$9)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>Сверка с блоками ADR-600 (MVP)</t>
         </is>
@@ -4419,21 +4422,21 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n">
+      <c r="B15" s="34" t="n">
         <v>7.5</v>
       </c>
-      <c r="C15" s="33" t="n">
+      <c r="C15" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="44">
         <f>IF(AND(D15=B15,E15=C15),"да","НЕТ")</f>
         <v/>
       </c>
@@ -4449,21 +4452,21 @@
           <t>Согласования</t>
         </is>
       </c>
-      <c r="B16" s="33" t="n">
+      <c r="B16" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C16" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="44">
         <f>IF(AND(D16=B16,E16=C16),"да","НЕТ")</f>
         <v/>
       </c>
@@ -4479,21 +4482,21 @@
           <t>Качество поиска и классификации</t>
         </is>
       </c>
-      <c r="B17" s="33" t="n">
+      <c r="B17" s="34" t="n">
         <v>35</v>
       </c>
-      <c r="C17" s="33" t="n">
+      <c r="C17" s="34" t="n">
         <v>51</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="44">
         <f>IF(AND(D17=B17,E17=C17),"да","НЕТ")</f>
         <v/>
       </c>
@@ -4509,21 +4512,21 @@
           <t>Основная разработка Этапа 2</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="C18" s="33" t="n">
+      <c r="C18" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="44">
         <f>IF(AND(D18=B18,E18=C18),"да","НЕТ")</f>
         <v/>
       </c>
@@ -4539,21 +4542,21 @@
           <t>Документация и ИБ</t>
         </is>
       </c>
-      <c r="B19" s="33" t="n">
+      <c r="B19" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="33" t="n">
+      <c r="C19" s="34" t="n">
         <v>7.5</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="F19" s="43">
+      <c r="F19" s="44">
         <f>IF(AND(D19=B19,E19=C19),"да","НЕТ")</f>
         <v/>
       </c>
@@ -4569,21 +4572,21 @@
           <t>Анализ типов на живых данных</t>
         </is>
       </c>
-      <c r="B20" s="33" t="n">
+      <c r="B20" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="C20" s="33" t="n">
+      <c r="C20" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="44">
         <f>IF(AND(D20=B20,E20=C20),"да","НЕТ")</f>
         <v/>
       </c>
@@ -4599,21 +4602,21 @@
           <t>Проверка Guardrails и провайдеров на живых данных</t>
         </is>
       </c>
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C21" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="44">
         <f>IF(AND(D21=B21,E21=C21),"да","НЕТ")</f>
         <v/>
       </c>
@@ -4629,23 +4632,23 @@
           <t>Итого по блокам</t>
         </is>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="38">
         <f>SUM(B15:B21)</f>
         <v/>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="38">
         <f>SUM(C15:C21)</f>
         <v/>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="38">
         <f>SUM(D15:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="38">
         <f>SUM(E15:E21)</f>
         <v/>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="45">
         <f>IF(AND(D22=B22,E22=C22),"да","НЕТ")</f>
         <v/>
       </c>
@@ -4656,7 +4659,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="43" t="inlineStr">
         <is>
           <t>Затраты, которые не выражаются человеко-днями</t>
         </is>
@@ -4715,10 +4718,10 @@
           <t>≈146 ₽/мес при базовом сценарии (10% визитов, 30% до модели) — ≈1 698 ₽/мес при максимальном (50%, 70%)</t>
         </is>
       </c>
-      <c r="D26" s="41" t="n">
+      <c r="D26" s="42" t="n">
         <v>146</v>
       </c>
-      <c r="E26" s="41" t="n">
+      <c r="E26" s="42" t="n">
         <v>1698</v>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -4748,8 +4751,8 @@
           <t>Не оценён отдельной строкой сметы</t>
         </is>
       </c>
-      <c r="D27" s="41" t="n"/>
-      <c r="E27" s="41" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
           <t>₽</t>
@@ -4777,8 +4780,8 @@
           <t>Не оценены</t>
         </is>
       </c>
-      <c r="D28" s="41" t="n"/>
-      <c r="E28" s="41" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
       <c r="F28" s="9" t="inlineStr">
         <is>
           <t>₽</t>
@@ -4806,10 +4809,10 @@
           <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером)</t>
         </is>
       </c>
-      <c r="D29" s="41" t="n">
+      <c r="D29" s="42" t="n">
         <v>927000</v>
       </c>
-      <c r="E29" s="41" t="n">
+      <c r="E29" s="42" t="n">
         <v>2368080</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -4839,8 +4842,8 @@
           <t>Не оценены</t>
         </is>
       </c>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
       <c r="F30" s="9" t="inlineStr">
         <is>
           <t>₽</t>
@@ -4853,7 +4856,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>Все суммы в ₽ — прогнозная модель, не смета: CAPEX/OPEX не утверждены владельцем (ADR-500). Закупка GPU — недели или месяцы лид-тайма, не разработка.</t>
         </is>
@@ -4888,116 +4891,116 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Источники и допущения</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B3" s="46" t="inlineStr">
+      <c r="B3" s="47" t="inlineStr">
         <is>
           <t>Единица стоимости</t>
         </is>
       </c>
-      <c r="C3" s="47" t="inlineStr">
+      <c r="C3" s="48" t="inlineStr">
         <is>
           <t>Человеко-день. 1 неделя = 5 чел-дн. Размер команды в ADR-600 не задан — принят один исполнитель.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Что сравнивается</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>Колонки «Сейчас» — то, что работает на прототипе. MVP и тираж — целевые контуры (ADR-100, ADR-200, ADR-500). Строки, где на этапе ничего не меняется, помечены «Без изменений» и серым.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="46" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Оценки, которые нужно подтвердить</t>
         </is>
       </c>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="C5" s="48" t="inlineStr">
         <is>
           <t>В ADR-600 трудозатраты даны по блокам работ, а не по контейнерам. Доли блоков по строкам распределены автором таблицы так, что сумма по блоку совпадает с оценкой ADR-600 (лист «Стоимость», сверка). Ниже — все ячейки, где цифра не взята прямо из ADR-600.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="46" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>Тираж: расхождение в ADR-600</t>
         </is>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" s="48" t="inlineStr">
         <is>
           <t>Сумма задач перехода к тиражу в ADR-600 — 17–26 чел-дн (3–5 + 5 + 2–3 + 5–10 + 2–3), сам документ округляет до «≈3,5–5 недель». В таблице — построчные значения.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="46" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>Нагрузка и деньги</t>
         </is>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>MVP — 8 000 абонентов; тираж — 90 000. Токены и стоимость GPU — из ADR-500 (прогнозная модель). Официальная смета не утверждена, GPU-сервер под эмбеддинги и оборудование кластера отдельной строкой не оценены.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B8" s="46" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>Внешние зависимости</t>
         </is>
       </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="C8" s="48" t="inlineStr">
         <is>
           <t>Сроки внедрения зависят от сигнатур API владельцев (Биллинг, Диспетчерская, микросервис обращений), согласования ИБ, поставки оборудования. Эти ожидания в человеко-днях не учтены.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>Ячейки с оценкой автора — подтвердить</t>
         </is>
@@ -5049,11 +5052,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>'Матрица'!M3</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>'Матрица'!N3</f>
         <v/>
       </c>
@@ -5076,11 +5079,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="34">
         <f>'Матрица'!M4</f>
         <v/>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="34">
         <f>'Матрица'!N4</f>
         <v/>
       </c>
@@ -5103,11 +5106,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="34">
         <f>'Матрица'!M5</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>'Матрица'!N5</f>
         <v/>
       </c>
@@ -5130,11 +5133,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="34">
         <f>'Матрица'!M6</f>
         <v/>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>'Матрица'!N6</f>
         <v/>
       </c>
@@ -5157,11 +5160,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <f>'Матрица'!M7</f>
         <v/>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>'Матрица'!N7</f>
         <v/>
       </c>
@@ -5184,11 +5187,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="34">
         <f>'Матрица'!M8</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <f>'Матрица'!N8</f>
         <v/>
       </c>
@@ -5211,11 +5214,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <f>'Матрица'!M9</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <f>'Матрица'!N9</f>
         <v/>
       </c>
@@ -5238,11 +5241,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="34">
         <f>'Матрица'!M10</f>
         <v/>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="34">
         <f>'Матрица'!N10</f>
         <v/>
       </c>
@@ -5265,11 +5268,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="34">
         <f>'Матрица'!M11</f>
         <v/>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="34">
         <f>'Матрица'!N11</f>
         <v/>
       </c>
@@ -5292,11 +5295,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <f>'Матрица'!M12</f>
         <v/>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <f>'Матрица'!N12</f>
         <v/>
       </c>
@@ -5319,11 +5322,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <f>'Матрица'!M13</f>
         <v/>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="34">
         <f>'Матрица'!N13</f>
         <v/>
       </c>
@@ -5346,11 +5349,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="34">
         <f>'Матрица'!M14</f>
         <v/>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="34">
         <f>'Матрица'!N14</f>
         <v/>
       </c>
@@ -5373,11 +5376,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="34">
         <f>'Матрица'!M15</f>
         <v/>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="34">
         <f>'Матрица'!N15</f>
         <v/>
       </c>
@@ -5400,11 +5403,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="34">
         <f>'Матрица'!M16</f>
         <v/>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="34">
         <f>'Матрица'!N16</f>
         <v/>
       </c>
@@ -5427,11 +5430,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="34">
         <f>'Матрица'!M17</f>
         <v/>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="34">
         <f>'Матрица'!N17</f>
         <v/>
       </c>
@@ -5454,11 +5457,11 @@
           <t>Тираж</t>
         </is>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <f>'Матрица'!S17</f>
         <v/>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <f>'Матрица'!T17</f>
         <v/>
       </c>
@@ -5481,11 +5484,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <f>'Матрица'!M18</f>
         <v/>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <f>'Матрица'!N18</f>
         <v/>
       </c>
@@ -5508,11 +5511,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="34">
         <f>'Матрица'!M19</f>
         <v/>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="34">
         <f>'Матрица'!N19</f>
         <v/>
       </c>
@@ -5535,11 +5538,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <f>'Матрица'!M20</f>
         <v/>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <f>'Матрица'!N20</f>
         <v/>
       </c>
@@ -5562,11 +5565,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <f>'Матрица'!M21</f>
         <v/>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <f>'Матрица'!N21</f>
         <v/>
       </c>
@@ -5589,11 +5592,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D32" s="33">
+      <c r="D32" s="34">
         <f>'Матрица'!M22</f>
         <v/>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="34">
         <f>'Матрица'!N22</f>
         <v/>
       </c>
@@ -5616,11 +5619,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="34">
         <f>'Матрица'!M23</f>
         <v/>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="34">
         <f>'Матрица'!N23</f>
         <v/>
       </c>
@@ -5643,11 +5646,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="34">
         <f>'Матрица'!M24</f>
         <v/>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="34">
         <f>'Матрица'!N24</f>
         <v/>
       </c>
@@ -5670,11 +5673,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="34">
         <f>'Матрица'!M26</f>
         <v/>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="34">
         <f>'Матрица'!N26</f>
         <v/>
       </c>
@@ -5697,11 +5700,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="34">
         <f>'Матрица'!M33</f>
         <v/>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="34">
         <f>'Матрица'!N33</f>
         <v/>
       </c>
@@ -5724,11 +5727,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D37" s="33">
+      <c r="D37" s="34">
         <f>'Матрица'!M34</f>
         <v/>
       </c>
-      <c r="E37" s="33">
+      <c r="E37" s="34">
         <f>'Матрица'!N34</f>
         <v/>
       </c>
@@ -5751,11 +5754,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <f>'Матрица'!M35</f>
         <v/>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <f>'Матрица'!N35</f>
         <v/>
       </c>
@@ -5778,11 +5781,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <f>'Матрица'!M37</f>
         <v/>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <f>'Матрица'!N37</f>
         <v/>
       </c>
@@ -5805,11 +5808,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="D40" s="33">
+      <c r="D40" s="34">
         <f>'Матрица'!M38</f>
         <v/>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="34">
         <f>'Матрица'!N38</f>
         <v/>
       </c>
@@ -5819,7 +5822,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="42" t="inlineStr">
+      <c r="B42" s="43" t="inlineStr">
         <is>
           <t>Документы-источники</t>
         </is>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>pgvector: не тянет фильтрацию по payload на нужном объёме. Milvus: тяжелее в эксплуатации при том же результате.</t>
+          <t>pgvector: не отклонён по качеству — на малом объёме (прототип: 190 фрагментов; база MVP не зафиксирована) вероятно справился бы; Qdrant выбран из-за алиасов коллекций (blue-green переиндексация уже в коде) и отдельной нагрузки от основной базы. Milvus: набор компонентов тяжелее без выигрыша на нашем объёме. Замеров нет, сравнение по документации.</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>pgvector: не отклонён по качеству — на малом объёме (прототип: 190 фрагментов; база MVP не зафиксирована) вероятно справился бы; Qdrant выбран из-за алиасов коллекций (blue-green переиндексация уже в коде) и отдельной нагрузки от основной базы. Milvus: набор компонентов тяжелее без выигрыша на нашем объёме. Замеров нет, сравнение по документации.</t>
+          <t>Объём заложен: несколько тысяч документов (3 000–5 000) × 10–20 частей на документ (допущение) = 30 000–100 000 векторов размерности 1 024 (BGE-M3), 123–410 МБ. Замер Qdrant на 100 000 случайных векторов: P50 27,5 мс / P99 64,9 мс без фильтра, 14,3 / 36,8 мс с фильтром по типу — в бюджете 100 мс. pgvector не отклонён по качеству: на этом объёме рабочая альтернатива (не измерялась), Qdrant выбран из-за алиасов коллекций (blue-green уже в коде) и отдельной нагрузки от основной базы. Milvus и OpenSearch — по документации, не измерялись.</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему ClickHouse для телеметрии»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «ClickHouse для телеметрии: выбор объёмом не подтверждён» (расчёт объёма и замер в Postgres)</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Произвольная нарезка аналитики (по абоненту, типу, модели) на объёме MVP в Postgres будет тормозить.</t>
+          <t>Довод «в Postgres будет тормозить» замером не подтвердился (2 млн строк — агрегаты за секунды). ClickHouse остаётся в схеме развёртывания, но по объёму не нужен: решение об оставлении Postgres не принято.</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Целевое хранилище телеметрии; переезд — смена DSN и диалекта запросов записи, не бизнес-логики.</t>
+          <t>Заложен в схеме развёртывания; переезд — смена DSN и диалекта запросов записи, не бизнес-логики. Если решено оставить Postgres, оценка строки (2–4 чел-дн) отпадает.</t>
         </is>
       </c>
       <c r="M16" s="12" t="n">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники и допущения" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -700,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>LLM Gateway (сейчас внутри Backend); Redis (лимиты); LLM Provider; Postgres / ClickHouse (события использования)</t>
+          <t>LLM Gateway (сейчас внутри Backend); Redis (лимиты); LLM Provider; Postgres (события использования)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>Python / LiteLLM (Router или прокси — решается при выносе; формат конфигурации совместим), отдельный Deployment; Redis для лимитов; Presidio; события использования — в ClickHouse; GigaChat Pro основной, YandexGPT резерв.</t>
+          <t>Python / LiteLLM (Router или прокси — решается при выносе; формат конфигурации совместим), отдельный Deployment; Redis для лимитов; Presidio; события использования — в Postgres; GigaChat Pro основной, YandexGPT резерв.</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Redis выбран против Memcached (нет структур для сессии), таблицы счётчиков в Postgres (нагрузка на основную базу) и счётчиков в памяти процесса (лимиты обнуляются при перезапуске, fail-open).</t>
+          <t>Redis выбран против Memcached (нет структур для сессии), таблицы счётчиков в Postgres (по нагрузке справился бы — 0,225 запроса/с; счётчик с окном пришлось бы писать вручную) и счётчиков в памяти процесса (лимиты обнуляются при перезапуске, fail-open).</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Postgres (обращения, слепки, события)</t>
+          <t>Postgres (обращения, слепки, события, телеметрия)</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>PostgreSQL выбран против MySQL/MariaDB (нет материализованных представлений) и SQLite (один файл, не для нескольких сервисов). Одна база вместо двух на объёме одного стенда.</t>
+          <t>PostgreSQL выбран против MySQL/MariaDB (нет материализованных представлений) и SQLite (один файл, не для нескольких сервисов). Телеметрия остаётся в Postgres, а не в ClickHouse: до ≈0,8 млн событий в год на тираже; замер 2 млн строк — 589 МБ, агрегаты за секунды (ADR-200).</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему PostgreSQL и Redis»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему PostgreSQL и Redis»; телеметрия — подраздел «Телеметрия: почему Postgres, а не ClickHouse»</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Postgres в Kubernetes только для состояния и обращений; слепки уходят — данные идут через API владельцев.</t>
+          <t>Postgres в Kubernetes для состояния, обращений и телеметрии (события использования, отчёты качества); слепки уходят — данные идут через API владельцев.</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема: своей копии чужих данных быть не должно.</t>
+          <t>Целевая схема: своей копии чужих данных быть не должно. Отдельная СУБД под телеметрию не нужна: объём мал (строка «ClickHouse» убрана, её оценка 2–4 чел-дн снята).</t>
         </is>
       </c>
       <c r="M15" s="12" t="n">
@@ -2040,78 +2040,94 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>ClickHouse (телеметрия)</t>
+          <t>Индексация базы знаний (ETL)</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>ClickHouse (MVP); LLM Gateway (события использования); Guardrails и судья (отчёты качества)</t>
+          <t>ETL индексации; Qdrant; embedding-inference; хранилище документов базы знаний</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Прототип — PostgreSQL (те же таблицы); MVP — ClickHouse</t>
+          <t>Python-скрипт `scripts/reindex_kb.py` (сервис `reindex` в docker compose); MVP — K8s CronJob (Celery Beat)</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Не развёрнут: те же таблицы (`usage_events`, `quality_reports`) лежат в Postgres; запись — best-effort, не роняет ответ.</t>
+          <t>Сервис `reindex` в compose: одноразовый прогон при подъёме стека (`scripts/reindex_kb.py`), запись в новую коллекцию и атомарное переключение алиаса; Backend только подключается к готовому индексу.</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>ClickHouse — целевой выбор против PostgreSQL (годится для стенда, при росте замедляется), TimescaleDB (остаётся строковым хранилищем) и OpenSearch (тяжелее без выигрыша). На прототипе ClickHouse не нужен: вторая СУБД ради объёма одного стенда.</t>
+          <t>Планировщик по расписанию выбран против Airflow (платформа ради одного задания) и cron внутри Backend (нет изоляции от ответов абонентам).</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «ClickHouse для телеметрии: выбор объёмом не подтверждён» (расчёт объёма и замер в Postgres)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему индексация — задание по расписанию, а не Airflow»</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Довод «в Postgres будет тормозить» замером не подтвердился (2 млн строк — агрегаты за секунды). ClickHouse остаётся в схеме развёртывания, но по объёму не нужен: решение об оставлении Postgres не принято.</t>
+          <t>Изоляция GPU между индексацией и онлайн-ответами не решена: массовая переиндексация может увеличить задержку ответа. Свежие документы попадают в индекс с задержкой до ночного окна.</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Аналитика токенов, стоимости и качества в ClickHouse, запись асинхронной пачкой.</t>
+          <t>Ночное окно 02:00–05:00: забор документов, очистка, эмбеддинги на GPU, полный реиндекс.</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>ClickHouse, StatefulSet + PVC.</t>
+          <t>Kubernetes CronJob (Celery Beat), окно обслуживания, жёсткая граница по времени.</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Заложен в схеме развёртывания; переезд — смена DSN и диалекта запросов записи, не бизнес-логики. Если решено оставить Postgres, оценка строки (2–4 чел-дн) отпадает.</t>
+          <t>Не успели — задание прерывается, продолжение в следующем окне; индекс не повреждается, алиас переключается после полного успеха.</t>
         </is>
       </c>
       <c r="M16" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O16" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="P16" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q16" s="15" t="n"/>
-      <c r="R16" s="15" t="n"/>
-      <c r="S16" s="16" t="n"/>
-      <c r="T16" s="16" t="n"/>
-      <c r="U16" s="15" t="n"/>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>Изоляция GPU между индексацией и онлайн-инференсом.</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>Приоритетные очереди либо отдельный GPU-пул.</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>Появляется вторая постоянная нагрузка на GPU (генерация), и индексация не должна её задерживать.</t>
+        </is>
+      </c>
+      <c r="S16" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" s="13" t="inlineStr">
+        <is>
+          <t>Оценка автора</t>
+        </is>
+      </c>
       <c r="V16" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-200</t>
+          <t>ADR-400; ADR-600; C4_Deployment</t>
         </is>
       </c>
     </row>
@@ -2126,94 +2142,94 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Индексация базы знаний (ETL)</t>
+          <t>Агент операций записи (Orchestrator, HITL, аудит)</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>ETL индексации; Qdrant; embedding-inference; хранилище документов базы знаний</t>
+          <t>Agent Orchestrator; Backend; Session State Store (Redis / PostgreSQL); LLM Gateway</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Python-скрипт `scripts/reindex_kb.py` (сервис `reindex` в docker compose); MVP — K8s CronJob (Celery Beat)</t>
+          <t>Python; собственный конечный автомат (`app/fsm.py`) на перечислениях; сессии в Redis / PostgreSQL</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Сервис `reindex` в compose: одноразовый прогон при подъёме стека (`scripts/reindex_kb.py`), запись в новую коллекцию и атомарное переключение алиаса; Backend только подключается к готовому индексу.</t>
+          <t>Свой конечный автомат (`app/fsm.py`), покрыт тестами, в продакшене не включён. Регистрация обращений идёт упрощённым путём напрямую в таблицу.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Планировщик по расписанию выбран против Airflow (платформа ради одного задания) и cron внутри Backend (нет изоляции от ответов абонентам).</t>
+          <t>LangGraph — кандидат, не выбран: усложнение ради возможностей, которые пока не нужны.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему индексация — задание по расписанию, а не Airflow»</t>
+          <t>ADR-200, раздел «Backend и оркестрация»: строка «Оркестрация агента» (свой FSM против LangGraph)</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Изоляция GPU между индексацией и онлайн-ответами не решена: массовая переиндексация может увеличить задержку ответа. Свежие документы попадают в индекс с задержкой до ночного окна.</t>
+          <t>Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Ночное окно 02:00–05:00: забор документов, очистка, эмбеддинги на GPU, полный реиндекс.</t>
+          <t>Включение агента: состояние ожидания подтверждения, идемпотентность, аудит (в том числе отказов абонента), проверка черновика до показа.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes CronJob (Celery Beat), окно обслуживания, жёсткая граница по времени.</t>
+          <t>Свой FSM, Draft Validator, Audit Writer, Session State Store.</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>Не успели — задание прерывается, продолжение в следующем окне; индекс не повреждается, алиас переключается после полного успеха.</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="n">
+          <t>Запись данных без подтверждённого сценария дороже по ошибке, чем консультация; ни одна запись без явного подтверждения абонента.</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="O17" s="13" t="inlineStr">
-        <is>
-          <t>Оценка автора</t>
+      <c r="O17" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>Изоляция GPU между индексацией и онлайн-инференсом.</t>
+          <t>Оценка function-calling для роли агента у провайдеров РФ.</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>Приоритетные очереди либо отдельный GPU-пул.</t>
+          <t>Прогон эталонных сценариев через кандидатов.</t>
         </is>
       </c>
       <c r="R17" s="9" t="inlineStr">
         <is>
-          <t>Появляется вторая постоянная нагрузка на GPU (генерация), и индексация не должна её задерживать.</t>
-        </is>
-      </c>
-      <c r="S17" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" s="12" t="n">
+          <t>От результата зависит, можно ли доверить агенту роль на self-hosted модели.</t>
+        </is>
+      </c>
+      <c r="S17" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="U17" s="13" t="inlineStr">
-        <is>
-          <t>Оценка автора</t>
+      <c r="T17" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="V17" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600; C4_Deployment</t>
+          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -2228,52 +2244,52 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Агент операций записи (Orchestrator, HITL, аудит)</t>
+          <t>Billing Adapter (запись в Биллинг)</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Agent Orchestrator; Backend; Session State Store (Redis / PostgreSQL); LLM Gateway</t>
+          <t>Billing Adapter; Биллинг (внешняя система); Agent Orchestrator (HITL Gate)</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Python; собственный конечный автомат (`app/fsm.py`) на перечислениях; сессии в Redis / PostgreSQL</t>
+          <t>Python; XML-RPC-клиент к API Биллинга; ключ идемпотентности</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Свой конечный автомат (`app/fsm.py`), покрыт тестами, в продакшене не включён. Регистрация обращений идёт упрощённым путём напрямую в таблицу.</t>
+          <t>Не реализован (запись отложена на Этап 2). Чтение идёт из слепка в Postgres.</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>LangGraph — кандидат, не выбран: усложнение ради возможностей, которые пока не нужны.</t>
+          <t>Прямой доступ к чужой БД запрещён: только через API владельца.</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Backend и оркестрация»: строка «Оркестрация агента» (свой FSM против LangGraph)</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос.</t>
+          <t>Сигнатуры API Биллинга от владельца ещё не получены; write-доступ к чужой legacy-системе — отдельная интеграция.</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Включение агента: состояние ожидания подтверждения, идемпотентность, аудит (в том числе отказов абонента), проверка черновика до показа.</t>
+          <t>Запись показаний и операций в Биллинг через XML-RPC с ключом идемпотентности.</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Свой FSM, Draft Validator, Audit Writer, Session State Store.</t>
+          <t>Отдельный контейнер `Billing Adapter`, XML-RPC API Биллинга.</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Запись данных без подтверждённого сценария дороже по ошибке, чем консультация; ни одна запись без явного подтверждения абонента.</t>
+          <t>Единственный разрешённый путь записи в Биллинг; повтор запроса не создаёт дубль.</t>
         </is>
       </c>
       <c r="M18" s="17" t="n">
@@ -2287,35 +2303,19 @@
           <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
-      <c r="P18" s="9" t="inlineStr">
-        <is>
-          <t>Оценка function-calling для роли агента у провайдеров РФ.</t>
-        </is>
-      </c>
-      <c r="Q18" s="9" t="inlineStr">
-        <is>
-          <t>Прогон эталонных сценариев через кандидатов.</t>
-        </is>
-      </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>От результата зависит, можно ли доверить агенту роль на self-hosted модели.</t>
-        </is>
-      </c>
-      <c r="S18" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U18" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+      <c r="P18" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="15" t="n"/>
+      <c r="S18" s="16" t="n"/>
+      <c r="T18" s="16" t="n"/>
+      <c r="U18" s="15" t="n"/>
       <c r="V18" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
+          <t>ADR-100; ADR-400</t>
         </is>
       </c>
     </row>
@@ -2330,59 +2330,59 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Billing Adapter (запись в Биллинг)</t>
+          <t>Сервис работы с обращениями</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Billing Adapter; Биллинг (внешняя система); Agent Orchestrator (HITL Gate)</t>
+          <t>Сервис работы с обращениями; Микросервис обращений и Диспетчерская (внешние); Agent Orchestrator; Postgres</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Python; XML-RPC-клиент к API Биллинга; ключ идемпотентности</t>
+          <t>Python; на прототипе запись в таблицу Postgres, на Этапе 2 — HTTP API владельца (сигнатуры не получены)</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Не реализован (запись отложена на Этап 2). Чтение идёт из слепка в Postgres.</t>
+          <t>Обращение пишется в собственную таблицу Postgres, минуя Orchestrator (`app/inquiries/store.py`).</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Прямой доступ к чужой БД запрещён: только через API владельца.</t>
+          <t>Целевой путь — внешний микросервис обращений; на прототипе доступа к нему нет.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»; ADR-100, таблица «Что явно отложено»</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры API Биллинга от владельца ещё не получены; write-доступ к чужой legacy-системе — отдельная интеграция.</t>
+          <t>Микросервис обращений и его API не готовы принимать реальные запросы; код типов обращений не согласован с владельцем.</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Запись показаний и операций в Биллинг через XML-RPC с ключом идемпотентности.</t>
+          <t>Регистрация через API микросервиса обращений; аварийные заявки — в Диспетчерскую (выбор маршрута по типу).</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>Отдельный контейнер `Billing Adapter`, XML-RPC API Биллинга.</t>
+          <t>Отдельный контейнер, Route Selector: emergency → Диспетчерская, остальные типы → микросервис.</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>Единственный разрешённый путь записи в Биллинг; повтор запроса не создаёт дубль.</t>
+          <t>Обращения должны попадать в систему-владельца, откуда их читают подрядчики и конвейер дообучения.</t>
         </is>
       </c>
       <c r="M19" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N19" s="17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O19" s="18" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       <c r="U19" s="15" t="n"/>
       <c r="V19" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-400</t>
+          <t>ADR-100; ADR-600</t>
         </is>
       </c>
     </row>
@@ -2416,59 +2416,59 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Сервис работы с обращениями</t>
+          <t>Document Generator (бланки заявлений)</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Сервис работы с обращениями; Микросервис обращений и Диспетчерская (внешние); Agent Orchestrator; Postgres</t>
+          <t>Document Generator; Backend (выдача бланка); S3 / MinIO (MVP)</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Python; на прототипе запись в таблицу Postgres, на Этапе 2 — HTTP API владельца (сигнатуры не получены)</t>
+          <t>Прототип — Python: шаблоны бланков и HTML-лист на печать; MVP — PDF-библиотека (не выбрана) + S3 / MinIO</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Обращение пишется в собственную таблицу Postgres, минуя Orchestrator (`app/inquiries/store.py`).</t>
+          <t>Готовый бланк отдаётся HTML-листом для печати из каталога (семь образцов по ПП РФ № 644/776).</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Целевой путь — внешний микросервис обращений; на прототипе доступа к нему нет.</t>
+          <t>PDF и S3/MinIO нужны только при путях записи — для консультации избыточны.</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»; ADR-100, таблица «Что явно отложено»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Документы Этапа 2: PDF и хранилище файлов (решение не принято)»</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>Микросервис обращений и его API не готовы принимать реальные запросы; код типов обращений не согласован с владельцем.</t>
+          <t>Настоящие бланки заявлений не согласованы с владельцем — используются образцы.</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>Регистрация через API микросервиса обращений; аварийные заявки — в Диспетчерскую (выбор маршрута по типу).</t>
+          <t>Рендер PDF из шаблона и слотов, хранение в объектном хранилище, ссылка с ограниченным сроком жизни.</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Отдельный контейнер, Route Selector: emergency → Диспетчерская, остальные типы → микросервис.</t>
+          <t>Генерация PDF (библиотека в ADR не выбрана) + S3 / MinIO.</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Обращения должны попадать в систему-владельца, откуда их читают подрядчики и конвейер дообучения.</t>
+          <t>Документ, вложенный в диалог, должен быть файлом, а не страницей печати.</t>
         </is>
       </c>
       <c r="M20" s="17" t="n">
         <v>3</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O20" s="18" t="inlineStr">
         <is>
@@ -2502,78 +2502,94 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Document Generator (бланки заявлений)</t>
+          <t>Оркестрация контейнеров</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Document Generator; Backend (выдача бланка); S3 / MinIO (MVP)</t>
+          <t>Все контейнеры (Backend, LLM Gateway, Qdrant, Redis, Postgres, ETL, GPU-сервисы)</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Прототип — Python: шаблоны бланков и HTML-лист на печать; MVP — PDF-библиотека (не выбрана) + S3 / MinIO</t>
+          <t>Прототип — Docker Compose на одной машине; MVP — Kubernetes (nginx Ingress, cert-manager)</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Готовый бланк отдаётся HTML-листом для печати из каталога (семь образцов по ПП РФ № 644/776).</t>
+          <t>`docker compose` на одной машине: postgres, redis, qdrant, reindex, backend.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>PDF и S3/MinIO нужны только при путях записи — для консультации избыточны.</t>
+          <t>Compose на нескольких хостах не переживает отказ узла; Docker Swarm — мёртвая экосистема. Для одного разработчика и одного хоста Kubernetes избыточен.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Документы Этапа 2: PDF и хранилище файлов (решение не принято)»</t>
+          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе»</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Настоящие бланки заявлений не согласованы с владельцем — используются образцы.</t>
+          <t>Целевая платформа (Kubernetes) пока только подразумевается, отдельного ADR нет.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Рендер PDF из шаблона и слотов, хранение в объектном хранилище, ссылка с ограниченным сроком жизни.</t>
+          <t>Kubernetes на собственном железе в закрытом контуре: пространства имён, Ingress, TLS-сертификаты.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>Генерация PDF (библиотека в ADR не выбрана) + S3 / MinIO.</t>
+          <t>Kubernetes, nginx Ingress, cert-manager.</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Документ, вложенный в диалог, должен быть файлом, а не страницей печати.</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="n">
+          <t>Отказоустойчивость и обновления без остановки; требование целевого развёртывания.</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>Оценка автора</t>
+        </is>
+      </c>
+      <c r="P21" s="9" t="inlineStr">
+        <is>
+          <t>Формализация целевой инфраплатформы отдельным ADR.</t>
+        </is>
+      </c>
+      <c r="Q21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>Kubernetes сейчас лишь подразумевается; для тиража нужна зафиксированная платформа, включая GPU-пулы.</t>
+        </is>
+      </c>
+      <c r="S21" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
-        </is>
-      </c>
-      <c r="P21" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q21" s="15" t="n"/>
-      <c r="R21" s="15" t="n"/>
-      <c r="S21" s="16" t="n"/>
-      <c r="T21" s="16" t="n"/>
-      <c r="U21" s="15" t="n"/>
+      <c r="U21" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="V21" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-600</t>
+          <t>ADR-200; ADR-600; C4_Deployment</t>
         </is>
       </c>
     </row>
@@ -2588,94 +2604,78 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Оркестрация контейнеров</t>
+          <t>Секреты и конфигурация</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Все контейнеры (Backend, LLM Gateway, Qdrant, Redis, Postgres, ClickHouse, ETL, GPU-сервисы)</t>
+          <t>Backend; LLM Gateway (ключи провайдеров); все контейнеры (конфигурация)</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Прототип — Docker Compose на одной машине; MVP — Kubernetes (nginx Ingress, cert-manager)</t>
+          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (опционально); MVP — Vault Agent Injector</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>`docker compose` на одной машине: postgres, redis, qdrant, reindex, backend.</t>
+          <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Опционально Vault в dev-режиме.</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Compose на нескольких хостах не переживает отказ узла; Docker Swarm — мёртвая экосистема. Для одного разработчика и одного хоста Kubernetes избыточен.</t>
+          <t>Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения. Хранение только в CI/CD без Vault дублирует секрет в двух местах.</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе»</t>
+          <t>ADR-200, раздел «Секреты и конфигурация»; ADR-400 («Что добавляется в контуре MVP»)</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Целевая платформа (Kubernetes) пока только подразумевается, отдельного ADR нет.</t>
+          <t>Dev-режим Vault сам по себе не безопаснее переменной окружения — это репетиция интеграции, а не защита.</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes на собственном железе в закрытом контуре: пространства имён, Ingress, TLS-сертификаты.</t>
+          <t>Vault Agent Injector: секреты попадают в под через sidecar.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes, nginx Ingress, cert-manager.</t>
+          <t>HashiCorp Vault в Kubernetes.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Отказоустойчивость и обновления без остановки; требование целевого развёртывания.</t>
+          <t>Единый источник истины и отзыв доступа без пересборки образа.</t>
         </is>
       </c>
       <c r="M22" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O22" s="13" t="inlineStr">
         <is>
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="P22" s="9" t="inlineStr">
-        <is>
-          <t>Формализация целевой инфраплатформы отдельным ADR.</t>
-        </is>
-      </c>
-      <c r="Q22" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>Kubernetes сейчас лишь подразумевается; для тиража нужна зафиксированная платформа, включая GPU-пулы.</t>
-        </is>
-      </c>
-      <c r="S22" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+      <c r="P22" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q22" s="15" t="n"/>
+      <c r="R22" s="15" t="n"/>
+      <c r="S22" s="16" t="n"/>
+      <c r="T22" s="16" t="n"/>
+      <c r="U22" s="15" t="n"/>
       <c r="V22" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-600; C4_Deployment</t>
+          <t>ADR-200; ADR-400</t>
         </is>
       </c>
     </row>
@@ -2690,59 +2690,59 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Секреты и конфигурация</t>
+          <t>Наблюдаемость (метрики, логи, алерты)</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Backend; LLM Gateway (ключи провайдеров); все контейнеры (конфигурация)</t>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); отдельные контейнеры Prometheus, Grafana, Loki, Alertmanager (MVP)</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (опционально); MVP — Vault Agent Injector</t>
+          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Prometheus, Grafana, Loki, Alertmanager</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Опционально Vault в dev-режиме.</t>
+          <t>Метрики Prometheus на отдельном порту, события потока в панели стенда. Дашбордов и сбора логов нет.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения. Хранение только в CI/CD без Vault дублирует секрет в двух местах.</t>
+          <t>Prometheus + Grafana + Loki + Alertmanager выбраны против ELK/OpenSearch, Zabbix и облачного мониторинга: закрытый контур (152-ФЗ), метрики Kubernetes и приложения, недорогие логи (Loki индексирует метки, а не текст). Сравнение по документации; пробного развёртывания альтернатив не было.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Секреты и конфигурация»; ADR-400 («Что добавляется в контуре MVP»)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Prometheus, Grafana, Loki и Alertmanager»</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Dev-режим Vault сам по себе не безопаснее переменной окружения — это репетиция интеграции, а не защита.</t>
+          <t>Метрики есть, но собирать и показывать их нечему.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Vault Agent Injector: секреты попадают в под через sidecar.</t>
+          <t>Полный стек наблюдаемости: метрики, дашборды, логи, оповещения; в логах только отчёт об обезличивании, без значений ПДн.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>HashiCorp Vault в Kubernetes.</t>
+          <t>Prometheus, Grafana, Loki, Alertmanager.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Единый источник истины и отзыв доступа без пересборки образа.</t>
+          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах.</t>
         </is>
       </c>
       <c r="M23" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       <c r="U23" s="15" t="n"/>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-400</t>
+          <t>C4_Deployment; ADR-500</t>
         </is>
       </c>
     </row>
@@ -2769,72 +2769,60 @@
       <c r="A24" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Контейнер</t>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Связь</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Наблюдаемость (метрики, логи, алерты)</t>
+          <t>Виджет ↔ Backend</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); отдельные контейнеры Prometheus, Grafana, Loki, Alertmanager (MVP)</t>
+          <t>AI-виджет; Backend</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Prometheus, Grafana, Loki, Alertmanager</t>
+          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Метрики Prometheus на отдельном порту, события потока в панели стенда. Дашбордов и сбора логов нет.</t>
+          <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Prometheus + Grafana + Loki + Alertmanager выбраны против ELK/OpenSearch, Zabbix и облачного мониторинга: закрытый контур (152-ФЗ), метрики Kubernetes и приложения, недорогие логи (Loki индексирует метки, а не текст). Сравнение по документации; пробного развёртывания альтернатив не было.</t>
+          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Prometheus, Grafana, Loki и Alertmanager»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Метрики есть, но собирать и показывать их нечему.</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>Полный стек наблюдаемости: метрики, дашборды, логи, оповещения; в логах только отчёт об обезличивании, без значений ПДн.</t>
-        </is>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>Prometheus, Grafana, Loki, Alertmanager.</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах.</t>
-        </is>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O24" s="13" t="inlineStr">
-        <is>
-          <t>Оценка автора</t>
-        </is>
-      </c>
+          <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="inlineStr">
+        <is>
+          <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
+        </is>
+      </c>
+      <c r="M24" s="16" t="n"/>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="15" t="n"/>
       <c r="P24" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -2847,7 +2835,7 @@
       <c r="U24" s="15" t="n"/>
       <c r="V24" s="9" t="inlineStr">
         <is>
-          <t>C4_Deployment; ADR-500</t>
+          <t>API_Spec.yaml</t>
         </is>
       </c>
     </row>
@@ -2862,53 +2850,65 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Виджет ↔ Backend</t>
+          <t>Backend ↔ Платформа ЛК (SSO)</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>AI-виджет; Backend</t>
+          <t>Backend; Платформа ЛК (внешняя)</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
+          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
+          <t>Не подключена: абонент выбирается из справочника стенда.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
+          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K25" s="15" t="n"/>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="n"/>
-      <c r="N25" s="16" t="n"/>
-      <c r="O25" s="15" t="n"/>
+          <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
+        </is>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
+        </is>
+      </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -2921,7 +2921,7 @@
       <c r="U25" s="15" t="n"/>
       <c r="V25" s="9" t="inlineStr">
         <is>
-          <t>API_Spec.yaml</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -2936,63 +2936,63 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Платформа ЛК (SSO)</t>
+          <t>Backend ↔ Биллинг (чтение фактов)</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Backend; Платформа ЛК (внешняя)</t>
+          <t>Backend; Кэш профиля (пересчёт из Биллинга); Биллинг (внешняя)</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
+          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Не подключена: абонент выбирается из справочника стенда.</t>
+          <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
+          <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
+          <t>Сигнатуры API Биллинга от владельца не получены.</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
+          <t>Свежие факты запрашиваются у Биллинга в момент вопроса.</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
+          <t>XML-RPC API Биллинга.</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
+          <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
+        </is>
+      </c>
+      <c r="M26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
@@ -3022,27 +3022,27 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Биллинг (чтение фактов)</t>
+          <t>Backend ↔ Диспетчерская</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Backend; Кэш профиля (пересчёт из Биллинга); Биллинг (внешняя)</t>
+          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
+          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
+          <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
+          <t>Прямой доступ к чужой БД запрещён.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -3052,22 +3052,22 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры API Биллинга от владельца не получены.</t>
+          <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>Свежие факты запрашиваются у Биллинга в момент вопроса.</t>
+          <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>XML-RPC API Биллинга.</t>
+          <t>REST API Диспетчерской.</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
+          <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
         </is>
       </c>
       <c r="M27" s="20" t="n">
@@ -3093,7 +3093,7 @@
       <c r="U27" s="15" t="n"/>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>ADR-100; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3108,65 +3108,57 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Диспетчерская</t>
+          <t>Backend ↔ LLM Gateway</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
+          <t>Backend; LLM Gateway</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
+          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
+          <t>Вызов внутри одного процесса.</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Прямой доступ к чужой БД запрещён.</t>
+          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
+          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
+          <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>REST API Диспетчерской.</t>
+          <t>HTTP внутри кластера.</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
-        </is>
-      </c>
-      <c r="M28" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+          <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
+        </is>
+      </c>
+      <c r="M28" s="19" t="n"/>
+      <c r="N28" s="19" t="n"/>
+      <c r="O28" s="9" t="n"/>
       <c r="P28" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3179,7 +3171,7 @@
       <c r="U28" s="15" t="n"/>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-400; ADR-600</t>
+          <t>ADR-200</t>
         </is>
       </c>
     </row>
@@ -3194,32 +3186,32 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ LLM Gateway</t>
+          <t>Backend ↔ Qdrant</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Backend; LLM Gateway</t>
+          <t>Backend; Qdrant</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
+          <t>qdrant-client по HTTP (порт 6333)</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Вызов внутри одного процесса.</t>
+          <t>HTTP (порт 6333); запись — отдельным сервисом, Backend только читает готовый индекс.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
+          <t>Клиент по HTTP, а не gRPC: задержка HTTP-вызова — единицы миллисекунд при бюджете поиска 100 мс, gRPC добавил бы зависимость без выигрыша.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -3227,24 +3219,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>HTTP внутри кластера.</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
-        </is>
-      </c>
-      <c r="M29" s="19" t="n"/>
-      <c r="N29" s="19" t="n"/>
-      <c r="O29" s="9" t="n"/>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K29" s="15" t="n"/>
+      <c r="L29" s="15" t="n"/>
+      <c r="M29" s="16" t="n"/>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="15" t="n"/>
       <c r="P29" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3272,62 +3256,78 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Qdrant</t>
+          <t>LLM Gateway ↔ LLM Provider</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Backend; Qdrant</t>
+          <t>LLM Gateway; внешний LLM Provider</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client по HTTP (порт 6333)</t>
+          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>HTTP (порт 6333); запись — отдельным сервисом, Backend только читает готовый индекс.</t>
+          <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Клиент по HTTP, а не gRPC: задержка HTTP-вызова — единицы миллисекунд при бюджете поиска 100 мс, gRPC добавил бы зависимость без выигрыша.</t>
+          <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
+          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="16" t="n"/>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q30" s="15" t="n"/>
-      <c r="R30" s="15" t="n"/>
-      <c r="S30" s="16" t="n"/>
-      <c r="T30" s="16" t="n"/>
-      <c r="U30" s="15" t="n"/>
+          <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>HTTPS, сертификаты НУЦ Минцифры.</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
+        </is>
+      </c>
+      <c r="M30" s="19" t="n"/>
+      <c r="N30" s="19" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="9" t="inlineStr">
+        <is>
+          <t>Вызов собственной модели внутри закрытого контура.</t>
+        </is>
+      </c>
+      <c r="Q30" s="9" t="inlineStr">
+        <is>
+          <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
+        </is>
+      </c>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
+        </is>
+      </c>
+      <c r="S30" s="19" t="n"/>
+      <c r="T30" s="19" t="n"/>
+      <c r="U30" s="9" t="n"/>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-400; ADR-300</t>
         </is>
       </c>
     </row>
@@ -3342,78 +3342,66 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>LLM Gateway ↔ LLM Provider</t>
+          <t>Индексация → Qdrant</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>LLM Gateway; внешний LLM Provider</t>
+          <t>ETL индексации; Qdrant</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
+          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
+          <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
+          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>HTTPS, сертификаты НУЦ Минцифры.</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
-        </is>
-      </c>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="9" t="n"/>
-      <c r="P31" s="9" t="inlineStr">
-        <is>
-          <t>Вызов собственной модели внутри закрытого контура.</t>
-        </is>
-      </c>
-      <c r="Q31" s="9" t="inlineStr">
-        <is>
-          <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
-        </is>
-      </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
-        </is>
-      </c>
-      <c r="S31" s="19" t="n"/>
-      <c r="T31" s="19" t="n"/>
-      <c r="U31" s="9" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
+          <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="n"/>
+      <c r="N31" s="16" t="n"/>
+      <c r="O31" s="15" t="n"/>
+      <c r="P31" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q31" s="15" t="n"/>
+      <c r="R31" s="15" t="n"/>
+      <c r="S31" s="16" t="n"/>
+      <c r="T31" s="16" t="n"/>
+      <c r="U31" s="15" t="n"/>
       <c r="V31" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
     </row>
@@ -3421,73 +3409,89 @@
       <c r="A32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>Связь</t>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Индексация → Qdrant</t>
+          <t>Смета CAPEX/OPEX, NFR, допущения о нагрузке</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>ETL индексации; Qdrant</t>
+          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
+          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
+          <t>Есть прогнозная модель, не смета: числа не утверждены владельцем (открытый P0).</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
+          <t>Не применимо: это работа, а не выбор технологии.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
+          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
+          <t>Разброс оценок нагрузки — 25-кратный; без статистики ЛК и колл-центра смета остаётся диапазоном.</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой.</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>Без этого нельзя защищать бюджет.</t>
+        </is>
+      </c>
+      <c r="M32" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N32" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: P0</t>
+        </is>
+      </c>
+      <c r="P32" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
-        </is>
-      </c>
-      <c r="M32" s="16" t="n"/>
-      <c r="N32" s="16" t="n"/>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
       <c r="Q32" s="15" t="n"/>
-      <c r="R32" s="15" t="n"/>
+      <c r="R32" s="15" t="inlineStr">
+        <is>
+          <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
+        </is>
+      </c>
       <c r="S32" s="16" t="n"/>
       <c r="T32" s="16" t="n"/>
       <c r="U32" s="15" t="n"/>
       <c r="V32" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3502,22 +3506,22 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Смета CAPEX/OPEX, NFR, допущения о нагрузке</t>
+          <t>Внедрение ответов владельцев данных</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
+          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
+          <t>Справочники и тексты в коде и данных; не технология</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Есть прогнозная модель, не смета: числа не утверждены владельцем (открытый P0).</t>
+          <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -3527,17 +3531,17 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
+          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>Разброс оценок нагрузки — 25-кратный; без статистики ЛК и колл-центра смета остаётся диапазоном.</t>
+          <t>Календарный срок определяет владелец, не команда.</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой.</t>
+          <t>Внедрение полученных ответов в справочники и тексты.</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
@@ -3547,18 +3551,18 @@
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>Без этого нельзя защищать бюджет.</t>
-        </is>
-      </c>
-      <c r="M33" s="25" t="n">
-        <v>7.5</v>
+          <t>Разработки не требуют — требуют ответа от водоканала.</t>
+        </is>
+      </c>
+      <c r="M33" s="17" t="n">
+        <v>4</v>
       </c>
       <c r="N33" s="17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O33" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: P0</t>
+          <t>Из блока ADR-600: Согласования</t>
         </is>
       </c>
       <c r="P33" s="14" t="inlineStr">
@@ -3567,17 +3571,13 @@
         </is>
       </c>
       <c r="Q33" s="15" t="n"/>
-      <c r="R33" s="15" t="inlineStr">
-        <is>
-          <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
-        </is>
-      </c>
+      <c r="R33" s="15" t="n"/>
       <c r="S33" s="16" t="n"/>
       <c r="T33" s="16" t="n"/>
       <c r="U33" s="15" t="n"/>
       <c r="V33" s="9" t="inlineStr">
         <is>
-          <t>ADR-500; ADR-600</t>
+          <t>ADR-600</t>
         </is>
       </c>
     </row>
@@ -3592,22 +3592,22 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Внедрение ответов владельцев данных</t>
+          <t>Документация и согласование ИБ</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
+          <t>Все (сквозная работа)</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Справочники и тексты в коде и данных; не технология</t>
+          <t>Документы и диаграммы пакета сдачи</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки.</t>
+          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -3617,17 +3617,17 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
+          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>Календарный срок определяет владелец, не команда.</t>
+          <t>Календарный срок определяет служба ИБ водоканала.</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>Внедрение полученных ответов в справочники и тексты.</t>
+          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
@@ -3637,33 +3637,41 @@
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>Разработки не требуют — требуют ответа от водоканала.</t>
+          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
         </is>
       </c>
       <c r="M34" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" s="17" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="N34" s="25" t="n">
+        <v>7.5</v>
       </c>
       <c r="O34" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Согласования</t>
-        </is>
-      </c>
-      <c r="P34" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q34" s="15" t="n"/>
-      <c r="R34" s="15" t="n"/>
-      <c r="S34" s="16" t="n"/>
-      <c r="T34" s="16" t="n"/>
-      <c r="U34" s="15" t="n"/>
+          <t>Из блока ADR-600: Документация и ИБ</t>
+        </is>
+      </c>
+      <c r="P34" s="9" t="inlineStr">
+        <is>
+          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
+        </is>
+      </c>
+      <c r="Q34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
+        </is>
+      </c>
+      <c r="S34" s="19" t="n"/>
+      <c r="T34" s="19" t="n"/>
+      <c r="U34" s="9" t="n"/>
       <c r="V34" s="9" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3678,86 +3686,78 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Документация и согласование ИБ</t>
+          <t>Выбор семейства собственной модели и закупка GPU</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Все (сквозная работа)</t>
+          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Документы и диаграммы пакета сдачи</t>
+          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
+          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии.</t>
+          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (разрыв размеров, русский слабее) и открытых весов GigaChat (менее зрелый инструментарий).</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
+          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>Календарный срок определяет служба ИБ водоканала.</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="n">
+          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K35" s="15" t="n"/>
+      <c r="L35" s="15" t="n"/>
+      <c r="M35" s="16" t="n"/>
+      <c r="N35" s="16" t="n"/>
+      <c r="O35" s="15" t="n"/>
+      <c r="P35" s="9" t="inlineStr">
+        <is>
+          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
+        </is>
+      </c>
+      <c r="Q35" s="9" t="inlineStr">
+        <is>
+          <t>Qwen2.5-32B INT4, vLLM.</t>
+        </is>
+      </c>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
+        </is>
+      </c>
+      <c r="S35" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="N35" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O35" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Документация и ИБ</t>
-        </is>
-      </c>
-      <c r="P35" s="9" t="inlineStr">
-        <is>
-          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
-        </is>
-      </c>
-      <c r="Q35" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R35" s="9" t="inlineStr">
-        <is>
-          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
-        </is>
-      </c>
-      <c r="S35" s="19" t="n"/>
-      <c r="T35" s="19" t="n"/>
-      <c r="U35" s="9" t="n"/>
+      <c r="U35" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="V35" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>ADR-300; ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3772,70 +3772,86 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Выбор семейства собственной модели и закупка GPU</t>
+          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
+          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
+          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
+          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (разрыв размеров, русский слабее) и открытых весов GigaChat (менее зрелый инструментарий).</t>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
+          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K36" s="15" t="n"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="16" t="n"/>
-      <c r="N36" s="16" t="n"/>
-      <c r="O36" s="15" t="n"/>
+          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»).</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="N36" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="O36" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Анализ типов на живых данных</t>
+        </is>
+      </c>
       <c r="P36" s="9" t="inlineStr">
         <is>
-          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
+          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
         </is>
       </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5-32B INT4, vLLM.</t>
+          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
         </is>
       </c>
       <c r="R36" s="9" t="inlineStr">
         <is>
-          <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
+          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
         </is>
       </c>
       <c r="S36" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="T36" s="20" t="n">
-        <v>5</v>
-      </c>
       <c r="U36" s="21" t="inlineStr">
         <is>
           <t>ADR-600</t>
@@ -3843,7 +3859,7 @@
       </c>
       <c r="V36" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-500; ADR-600</t>
+          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
         </is>
       </c>
     </row>
@@ -3858,224 +3874,122 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
+          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
+          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
+          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
+          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
+          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
+          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»).</t>
+          <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
+          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
+          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит.</t>
         </is>
       </c>
       <c r="M37" s="17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N37" s="17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Анализ типов на живых данных</t>
-        </is>
-      </c>
-      <c r="P37" s="9" t="inlineStr">
-        <is>
-          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
-        </is>
-      </c>
-      <c r="Q37" s="9" t="inlineStr">
-        <is>
-          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
-        </is>
-      </c>
-      <c r="R37" s="9" t="inlineStr">
-        <is>
-          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
-        </is>
-      </c>
-      <c r="S37" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T37" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
+        </is>
+      </c>
+      <c r="P37" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q37" s="15" t="n"/>
+      <c r="R37" s="15" t="n"/>
+      <c r="S37" s="16" t="n"/>
+      <c r="T37" s="16" t="n"/>
+      <c r="U37" s="15" t="n"/>
       <c r="V37" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>Сквозная работа</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
-        </is>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
-        </is>
-      </c>
-      <c r="L38" s="9" t="inlineStr">
-        <is>
-          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит.</t>
-        </is>
-      </c>
-      <c r="M38" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="N38" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="O38" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
-        </is>
-      </c>
-      <c r="P38" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q38" s="15" t="n"/>
-      <c r="R38" s="15" t="n"/>
-      <c r="S38" s="16" t="n"/>
-      <c r="T38" s="16" t="n"/>
-      <c r="U38" s="15" t="n"/>
-      <c r="V38" s="9" t="inlineStr">
-        <is>
           <t>ADR-300; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Цвет ячеек с оценкой:</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>Цвет ячеек с оценкой:</t>
+      <c r="C40" s="27" t="n"/>
+      <c r="D40" s="28" t="inlineStr">
+        <is>
+          <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="27" t="n"/>
+      <c r="C41" s="29" t="n"/>
       <c r="D41" s="28" t="inlineStr">
         <is>
-          <t>цифра прямо из ADR-600</t>
+          <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="29" t="n"/>
+      <c r="C42" s="30" t="n"/>
       <c r="D42" s="28" t="inlineStr">
         <is>
-          <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
+          <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="30" t="n"/>
+      <c r="C43" s="31" t="n"/>
       <c r="D43" s="28" t="inlineStr">
         <is>
-          <t>в ADR-600 нет, оценка автора — подтвердить</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" s="31" t="n"/>
-      <c r="D44" s="28" t="inlineStr">
-        <is>
           <t>изменений на этом этапе нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V38"/>
+  <autoFilter ref="A2:V37"/>
   <mergeCells count="4">
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
@@ -4187,11 +4101,11 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>SUM('Матрица'!$M$3:$M$38)</f>
+        <f>SUM('Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="C5" s="34">
-        <f>SUM('Матрица'!$N$3:$N$38)</f>
+        <f>SUM('Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="D5" s="34">
@@ -4203,27 +4117,27 @@
         <v/>
       </c>
       <c r="F5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"ADR-600",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="G5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"ADR-600",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="H5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока*",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="I5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока*",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="J5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Оценка автора",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="K5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Оценка автора",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -4234,11 +4148,11 @@
         </is>
       </c>
       <c r="B6" s="34">
-        <f>SUM('Матрица'!$S$3:$S$38)</f>
+        <f>SUM('Матрица'!$S$3:$S$37)</f>
         <v/>
       </c>
       <c r="C6" s="34">
-        <f>SUM('Матрица'!$T$3:$T$38)</f>
+        <f>SUM('Матрица'!$T$3:$T$37)</f>
         <v/>
       </c>
       <c r="D6" s="34">
@@ -4250,27 +4164,27 @@
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$S$3:$S$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"ADR-600",'Матрица'!$S$3:$S$37)</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$T$3:$T$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"ADR-600",'Матрица'!$T$3:$T$37)</f>
         <v/>
       </c>
       <c r="H6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$S$3:$S$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"Из блока*",'Матрица'!$S$3:$S$37)</f>
         <v/>
       </c>
       <c r="I6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$T$3:$T$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"Из блока*",'Матрица'!$T$3:$T$37)</f>
         <v/>
       </c>
       <c r="J6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$S$3:$S$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"Оценка автора",'Матрица'!$S$3:$S$37)</f>
         <v/>
       </c>
       <c r="K6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$T$3:$T$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$37,"Оценка автора",'Матрица'!$T$3:$T$37)</f>
         <v/>
       </c>
     </row>
@@ -4429,11 +4343,11 @@
         <v>10</v>
       </c>
       <c r="D15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F15" s="44">
@@ -4459,11 +4373,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F16" s="44">
@@ -4489,11 +4403,11 @@
         <v>51</v>
       </c>
       <c r="D17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F17" s="44">
@@ -4519,11 +4433,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F18" s="44">
@@ -4549,11 +4463,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F19" s="44">
@@ -4579,11 +4493,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F20" s="44">
@@ -4609,11 +4523,11 @@
         <v>16</v>
       </c>
       <c r="D21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$37)</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$37)</f>
         <v/>
       </c>
       <c r="F21" s="44">
@@ -4879,7 +4793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5418,28 +5332,28 @@
     </row>
     <row r="26">
       <c r="A26" s="9">
-        <f>'Матрица'!A17</f>
+        <f>'Матрица'!A16</f>
         <v/>
       </c>
       <c r="B26" s="9">
-        <f>'Матрица'!C17</f>
+        <f>'Матрица'!C16</f>
         <v/>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Тираж</t>
         </is>
       </c>
       <c r="D26" s="34">
-        <f>'Матрица'!M17</f>
+        <f>'Матрица'!S16</f>
         <v/>
       </c>
       <c r="E26" s="34">
-        <f>'Матрица'!N17</f>
+        <f>'Матрица'!T16</f>
         <v/>
       </c>
       <c r="F26" s="13">
-        <f>'Матрица'!O17</f>
+        <f>'Матрица'!U16</f>
         <v/>
       </c>
     </row>
@@ -5454,19 +5368,19 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="D27" s="34">
-        <f>'Матрица'!S17</f>
+        <f>'Матрица'!M17</f>
         <v/>
       </c>
       <c r="E27" s="34">
-        <f>'Матрица'!T17</f>
-        <v/>
-      </c>
-      <c r="F27" s="13">
-        <f>'Матрица'!U17</f>
+        <f>'Матрица'!N17</f>
+        <v/>
+      </c>
+      <c r="F27" s="18">
+        <f>'Матрица'!O17</f>
         <v/>
       </c>
     </row>
@@ -5573,7 +5487,7 @@
         <f>'Матрица'!N21</f>
         <v/>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="13">
         <f>'Матрица'!O21</f>
         <v/>
       </c>
@@ -5634,11 +5548,11 @@
     </row>
     <row r="34">
       <c r="A34" s="9">
-        <f>'Матрица'!A24</f>
+        <f>'Матрица'!A25</f>
         <v/>
       </c>
       <c r="B34" s="9">
-        <f>'Матрица'!C24</f>
+        <f>'Матрица'!C25</f>
         <v/>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -5647,25 +5561,25 @@
         </is>
       </c>
       <c r="D34" s="34">
-        <f>'Матрица'!M24</f>
+        <f>'Матрица'!M25</f>
         <v/>
       </c>
       <c r="E34" s="34">
-        <f>'Матрица'!N24</f>
-        <v/>
-      </c>
-      <c r="F34" s="13">
-        <f>'Матрица'!O24</f>
+        <f>'Матрица'!N25</f>
+        <v/>
+      </c>
+      <c r="F34" s="18">
+        <f>'Матрица'!O25</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9">
-        <f>'Матрица'!A26</f>
+        <f>'Матрица'!A32</f>
         <v/>
       </c>
       <c r="B35" s="9">
-        <f>'Матрица'!C26</f>
+        <f>'Матрица'!C32</f>
         <v/>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -5674,15 +5588,15 @@
         </is>
       </c>
       <c r="D35" s="34">
-        <f>'Матрица'!M26</f>
+        <f>'Матрица'!M32</f>
         <v/>
       </c>
       <c r="E35" s="34">
-        <f>'Матрица'!N26</f>
+        <f>'Матрица'!N32</f>
         <v/>
       </c>
       <c r="F35" s="18">
-        <f>'Матрица'!O26</f>
+        <f>'Матрица'!O32</f>
         <v/>
       </c>
     </row>
@@ -5742,11 +5656,11 @@
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <f>'Матрица'!A35</f>
+        <f>'Матрица'!A36</f>
         <v/>
       </c>
       <c r="B38" s="9">
-        <f>'Матрица'!C35</f>
+        <f>'Матрица'!C36</f>
         <v/>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -5755,15 +5669,15 @@
         </is>
       </c>
       <c r="D38" s="34">
-        <f>'Матрица'!M35</f>
+        <f>'Матрица'!M36</f>
         <v/>
       </c>
       <c r="E38" s="34">
-        <f>'Матрица'!N35</f>
+        <f>'Матрица'!N36</f>
         <v/>
       </c>
       <c r="F38" s="18">
-        <f>'Матрица'!O35</f>
+        <f>'Матрица'!O36</f>
         <v/>
       </c>
     </row>
@@ -5794,131 +5708,104 @@
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="9">
-        <f>'Матрица'!A38</f>
-        <v/>
-      </c>
-      <c r="B40" s="9">
-        <f>'Матрица'!C38</f>
-        <v/>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D40" s="34">
-        <f>'Матрица'!M38</f>
-        <v/>
-      </c>
-      <c r="E40" s="34">
-        <f>'Матрица'!N38</f>
-        <v/>
-      </c>
-      <c r="F40" s="18">
-        <f>'Матрица'!O38</f>
-        <v/>
+    <row r="41">
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Документы-источники</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="43" t="inlineStr">
-        <is>
-          <t>Документы-источники</t>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>ADR-100</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>ADR-100</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>C4_Deployment, C3/*</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Целевая схема развёртывания и компоненты</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>Код и docker-compose.yml</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>Целевая схема развёртывания и компоненты</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>Код и docker-compose.yml</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -5932,13 +5819,13 @@
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C42:F42"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C46:F46"/>
     <mergeCell ref="C47:F47"/>
     <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C50:F50"/>
     <mergeCell ref="C44:F44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Назначение: проверить ответ модели до показа абоненту — персональные данные, недопустимый тон, разглашение внутренних инструкций. Синхронно (до 50 мс): ПДн в ответе, тон, разглашение промпта — при нарушении поток обрывается. Асинхронно: судья обоснованности (локальная Qwen2.5-7B через Ollama), не блокирует выдачу.</t>
+          <t>Назначение: проверить ответ модели до показа абоненту — персональные данные, недопустимый тон, разглашение внутренних инструкций. Синхронно (бюджет 50 мс; замер 24.09.2026: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс — на длинных ответах бюджет не держится, проверяется весь накопленный текст): ПДн в ответе, тон, разглашение промпта — при нарушении поток обрывается. Асинхронно: судья обоснованности (локальная Qwen2.5-7B через Ollama), не блокирует выдачу.</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>YandexGPT Pro — управляемый API в РФ. Для тестов локально Qwen2.5-7B (Ollama). Время до первого куска ≈0,6 с (ориентир 0,5 с).</t>
+          <t>YandexGPT Pro — управляемый API в РФ. Для тестов локально Qwen2.5-7B (Ollama). Время до первого куска по 19 вызовам: медиана 0,78 с, P90 5,6 с, максимум 21,7 с (ориентир 0,5 с не достигнут); до конца ответа — медиана 2,6 с.</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>GigaChat технически недоступен на машине прототипа (нужны корневые сертификаты НУЦ; отключать проверку TLS недопустимо). Зарубежные провайдеры отклонены на всех этапах: 152-ФЗ. Собственная модель тиража: Qwen2.5-32B выбран против Llama 3.x и открытых весов GigaChat — лицензия Apache 2.0, сильный русский среди открытых моделей, одно семейство 7B (уже используется для тестов) → 32B без переделки, 32B в INT4 помещается на одну карту A100 (34 ГБ весов плюс запас под кэш). Выбор сделан по репутации модели, на своём эталонном наборе не проверен; прогон запланирован при переходе к тиражу (3–5 чел-дн, ADR-600).</t>
+          <t>GigaChat технически недоступен на машине прототипа (нужны корневые сертификаты НУЦ; отключать проверку TLS недопустимо). Зарубежные провайдеры отклонены на всех этапах: 152-ФЗ. Собственная модель тиража: Qwen2.5-32B выбран против Llama 3.x и открытых весов GigaChat — лицензия Apache 2.0, сильный русский среди открытых моделей, одно семейство 7B (уже используется для тестов) → 32B без переделки, 32B в INT4 помещается на одну карту A100 (в проекте заложено 34 ГБ весов плюс запас под кэш; на GPU не проверялось, а для INT4 по общим сведениям ожидается около 17–20 ГБ — 34 ГБ скорее соответствуют 8-битному представлению). Выбор сделан по репутации модели, на своём эталонном наборе не проверен; прогон запланирован при переходе к тиражу (3–5 чел-дн, ADR-600).</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>`multilingual-e5-small` на CPU: 0,46 ГБ, 22 мс на запрос — с запасом укладывается в бюджет 100 мс. Стек: библиотека sentence-transformers (`SentenceTransformerEmbedder`, `app/kb/search.py`); модель задаётся параметром `embedding_model` (`app/config.py`); тот же эмбеддер использует запасной классификатор Triage.</t>
+          <t>`multilingual-e5-small` на CPU: 0,46 ГБ, 22–37 мс на запрос (первый замер и повтор 24.09.2026) — укладывается в бюджет 100 мс с запасом ≈3–4,5 раза. Стек: библиотека sentence-transformers (`SentenceTransformerEmbedder`, `app/kb/search.py`); модель задаётся параметром `embedding_model` (`app/config.py`); тот же эмбеддер использует запасной классификатор Triage.</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Сравнение моделей проведено в ADR-300, раздел 2 (задержка и размер — замер `scripts/measure_search_models.py`); замер поиска на прототипе — `golden_set/measurement.json` (e5-small: 20 из 20 на вопросах корпуса, 12 из 30 на первом месте и 23 из 30 в первой тройке на живых формулировках). Почему BGE-M3 для MVP: многоязычная, длинные тексты, общий каркас с реранкером BGE-reranker-v2-m3 — это свойства модели, а не замер на своих данных; подробно и с перечнем кандидатов — ADR-300, «Почему BGE-M3 — кандидат для MVP и что будет сравниваться». Кандидаты: BGE-M3: 4,25 ГБ, 210 мс на CPU (вдвое выше бюджета), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
+          <t>Сравнение моделей проведено в ADR-300, раздел 2 (задержка и размер — замер `scripts/measure_search_models.py`); замер поиска на прототипе — `golden_set/measurement.json` (e5-small: 20 из 20 на вопросах корпуса, 12 из 30 на первом месте и 23 из 30 в первой тройке на живых формулировках). Почему BGE-M3 для MVP: многоязычная, длинные тексты, общий каркас с реранкером BGE-reranker-v2-m3 — это свойства модели, а не замер на своих данных; подробно и с перечнем кандидатов — ADR-300, «Почему BGE-M3 — кандидат для MVP и что будет сравниваться». Кандидаты: BGE-M3: 4,25 ГБ, 210–300 мс на CPU (в 2–3 раза выше бюджета; на GPU не измерялась), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Реализован и проверен, но выключен (`RERANKER_ENABLED=false`): кросс-энкодер BGE-reranker-v2-m3 на CPU считает 5,8–25 с при бюджете 100 мс.</t>
+          <t>Реализован и проверен, но выключен (`RERANKER_ENABLED=false`): кросс-энкодер BGE-reranker-v2-m3 на CPU считает 5,8–25 с (повтор 24.09.2026 — 7,2 с) при бюджете 100 мс; на GPU не измерялся.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU. BGE-reranker-v2-m3 выбран как целевой: многоязычный, из того же семейства, что BGE-M3, и проверен на 30 живых формулировках (первое место у 21 из 30 вместо 7, MRR 0,79 вместо 0,52). Другие реранкеры (jina-reranker-v2, mMiniLM, bge-reranker-v2-gemma) не измерялись.</t>
+          <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU. BGE-reranker-v2-m3 выбран как целевой: многоязычный, из того же семейства, что BGE-M3, и проверен на 30 живых формулировках (первое место у 21 из 30 вместо 7, MRR 0,79 вместо 0,52) — но замер устарел: сделан на корпусе из 20 фрагментов, где топ-20 — весь корпус; на текущем индексе косинус даёт 12 из 30, выигрыш реранкера над ним не измерялся, а на 30–100 тыс. векторов MVP зависит от полноты первой ступени. Другие реранкеры (jina-reranker-v2, mMiniLM, bge-reranker-v2-gemma) не измерялись.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -3919,14 +3919,14 @@
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит.</t>
+          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
         </is>
       </c>
       <c r="M37" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N37" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="B21" s="34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$37)</f>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>10–16 чел-дн (ADR-600): выборка 1–2, Guardrails 4–6, сравнение провайдеров 4–6, решение 1–2</t>
+          <t>11–18 чел-дн (ADR-600): выборка 1–2, Guardrails 4–6, оптимизация синхронной проверки 1–2, сравнение провайдеров 4–6, решение 1–2</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>ADR-600 называет итог ≈19–28 недель (≈95–140 чел-дн); сумма блоков 94,5–141,5 — округление в самом ADR-600</t>
+          <t>ADR-600 называет итог ≈19–29 недель (≈95–145 чел-дн); сумма блоков 95,5–143,5 — округление в самом ADR-600</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Включён в онлайн-поиске; замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (5–7 чел-дн) — после выбора модели эмбеддингов.</t>
+          <t>Включён в онлайн-поиске; замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (5–7 чел-дн); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -4629,14 +4629,14 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>≈146 ₽/мес при базовом сценарии (10% визитов, 30% до модели) — ≈1 698 ₽/мес при максимальном (50%, 70%)</t>
+          <t>≈162 ₽/мес при базовом сценарии (10% визитов, 30% до модели) — ≈1 886 ₽/мес при максимальном (50%, 70%), при измеренных 401 токене на запрос (19 вызовов). При 3 500 токенов на запрос (допущение отчёта о мощности, не проверено) — ≈1 400–16 500 ₽/мес. Спрос из отчёта о мощности при 3 500 токенов — ≈40 000 ₽/мес. Допущения о спросе данными водоканала не подтверждены</t>
         </is>
       </c>
       <c r="D26" s="42" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E26" s="42" t="n">
-        <v>1698</v>
+        <v>16464</v>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-500; Capacity_Report</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Не оценён отдельной строкой сметы</t>
+          <t>Не оценён отдельной строкой сметы; скорость на GPU не измерялась</t>
         </is>
       </c>
       <c r="D27" s="42" t="n"/>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером)</t>
+          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
         </is>
       </c>
       <c r="D29" s="42" t="n">
@@ -4793,7 +4793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="46" t="inlineStr">
         <is>
           <t>•</t>
@@ -4892,11 +4892,11 @@
       </c>
       <c r="C7" s="48" t="inlineStr">
         <is>
-          <t>MVP — 8 000 абонентов; тираж — 90 000. Токены и стоимость GPU — из ADR-500 (прогнозная модель). Официальная смета не утверждена, GPU-сервер под эмбеддинги и оборудование кластера отдельной строкой не оценены.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>MVP — 8 000 абонентов; тираж — 90 000. Токены и стоимость GPU — из ADR-500 (прогнозная модель). Официальная смета не утверждена, GPU-сервер под эмбеддинги и оборудование кластера отдельной строкой не оценены. Допущения о спросе данными водоканала не подтверждены; в ADR-500 и в отчёте о мощности они разные, стоимость токенов зависит от них на порядок. Токенов на запрос: измерено 401 (19 вызовов, фрагменты FAQ до 300 знаков), допущение отчёта — 3 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="46" t="inlineStr">
         <is>
           <t>•</t>
@@ -4904,115 +4904,95 @@
       </c>
       <c r="B8" s="47" t="inlineStr">
         <is>
+          <t>Замеры 24.09.2026 (повтор)</t>
+        </is>
+      </c>
+      <c r="C8" s="48" t="inlineStr">
+        <is>
+          <t>Время запроса на CPU: e5-small 36–37 мс (первый замер 22 мс), BGE-M3 300 мс (первый замер 210 мс), реранкер на 20 кандидатах 7,2 с; бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
+      <c r="A9" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>Что не измерялось</t>
+        </is>
+      </c>
+      <c r="C9" s="48" t="inlineStr">
+        <is>
+          <t>Скорость любых моделей на GPU. Качество BGE-M3 и других кандидатов на данных проекта. Выигрыш реранкера над текущим индексом (прежний замер — на корпусе из 20 фрагментов). Полнота обезличивания на живых данных. Длина запроса на базе из нескольких тысяч документов. Данные о спросе. Сравнения по документации (pgvector, Milvus, Feature Store, Airflow, Loki, Litestar и др.) замером не проверялись.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
           <t>Внешние зависимости</t>
         </is>
       </c>
-      <c r="C8" s="48" t="inlineStr">
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>Сроки внедрения зависят от сигнатур API владельцев (Биллинг, Диспетчерская, микросервис обращений), согласования ИБ, поставки оборудования. Эти ожидания в человеко-днях не учтены.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="43" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>Ячейки с оценкой автора — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Контейнер / связь</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Контур</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Мин</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Макс</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Основа оценки</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9">
-        <f>'Матрица'!A3</f>
-        <v/>
-      </c>
-      <c r="B12" s="9">
-        <f>'Матрица'!C3</f>
-        <v/>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D12" s="34">
-        <f>'Матрица'!M3</f>
-        <v/>
-      </c>
-      <c r="E12" s="34">
-        <f>'Матрица'!N3</f>
-        <v/>
-      </c>
-      <c r="F12" s="13">
-        <f>'Матрица'!O3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9">
-        <f>'Матрица'!A4</f>
-        <v/>
-      </c>
-      <c r="B13" s="9">
-        <f>'Матрица'!C4</f>
-        <v/>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="D13" s="34">
-        <f>'Матрица'!M4</f>
-        <v/>
-      </c>
-      <c r="E13" s="34">
-        <f>'Матрица'!N4</f>
-        <v/>
-      </c>
-      <c r="F13" s="18">
-        <f>'Матрица'!O4</f>
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9">
-        <f>'Матрица'!A5</f>
+        <f>'Матрица'!A3</f>
         <v/>
       </c>
       <c r="B14" s="9">
-        <f>'Матрица'!C5</f>
+        <f>'Матрица'!C3</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -5021,25 +5001,25 @@
         </is>
       </c>
       <c r="D14" s="34">
-        <f>'Матрица'!M5</f>
+        <f>'Матрица'!M3</f>
         <v/>
       </c>
       <c r="E14" s="34">
-        <f>'Матрица'!N5</f>
-        <v/>
-      </c>
-      <c r="F14" s="18">
-        <f>'Матрица'!O5</f>
+        <f>'Матрица'!N3</f>
+        <v/>
+      </c>
+      <c r="F14" s="13">
+        <f>'Матрица'!O3</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>'Матрица'!A6</f>
+        <f>'Матрица'!A4</f>
         <v/>
       </c>
       <c r="B15" s="9">
-        <f>'Матрица'!C6</f>
+        <f>'Матрица'!C4</f>
         <v/>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5048,25 +5028,25 @@
         </is>
       </c>
       <c r="D15" s="34">
-        <f>'Матрица'!M6</f>
+        <f>'Матрица'!M4</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>'Матрица'!N6</f>
-        <v/>
-      </c>
-      <c r="F15" s="13">
-        <f>'Матрица'!O6</f>
+        <f>'Матрица'!N4</f>
+        <v/>
+      </c>
+      <c r="F15" s="18">
+        <f>'Матрица'!O4</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9">
-        <f>'Матрица'!A7</f>
+        <f>'Матрица'!A5</f>
         <v/>
       </c>
       <c r="B16" s="9">
-        <f>'Матрица'!C7</f>
+        <f>'Матрица'!C5</f>
         <v/>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5075,25 +5055,25 @@
         </is>
       </c>
       <c r="D16" s="34">
-        <f>'Матрица'!M7</f>
+        <f>'Матрица'!M5</f>
         <v/>
       </c>
       <c r="E16" s="34">
-        <f>'Матрица'!N7</f>
+        <f>'Матрица'!N5</f>
         <v/>
       </c>
       <c r="F16" s="18">
-        <f>'Матрица'!O7</f>
+        <f>'Матрица'!O5</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9">
-        <f>'Матрица'!A8</f>
+        <f>'Матрица'!A6</f>
         <v/>
       </c>
       <c r="B17" s="9">
-        <f>'Матрица'!C8</f>
+        <f>'Матрица'!C6</f>
         <v/>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5102,25 +5082,25 @@
         </is>
       </c>
       <c r="D17" s="34">
-        <f>'Матрица'!M8</f>
+        <f>'Матрица'!M6</f>
         <v/>
       </c>
       <c r="E17" s="34">
-        <f>'Матрица'!N8</f>
-        <v/>
-      </c>
-      <c r="F17" s="18">
-        <f>'Матрица'!O8</f>
+        <f>'Матрица'!N6</f>
+        <v/>
+      </c>
+      <c r="F17" s="13">
+        <f>'Матрица'!O6</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>'Матрица'!A9</f>
+        <f>'Матрица'!A7</f>
         <v/>
       </c>
       <c r="B18" s="9">
-        <f>'Матрица'!C9</f>
+        <f>'Матрица'!C7</f>
         <v/>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5129,25 +5109,25 @@
         </is>
       </c>
       <c r="D18" s="34">
-        <f>'Матрица'!M9</f>
+        <f>'Матрица'!M7</f>
         <v/>
       </c>
       <c r="E18" s="34">
-        <f>'Матрица'!N9</f>
-        <v/>
-      </c>
-      <c r="F18" s="13">
-        <f>'Матрица'!O9</f>
+        <f>'Матрица'!N7</f>
+        <v/>
+      </c>
+      <c r="F18" s="18">
+        <f>'Матрица'!O7</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9">
-        <f>'Матрица'!A10</f>
+        <f>'Матрица'!A8</f>
         <v/>
       </c>
       <c r="B19" s="9">
-        <f>'Матрица'!C10</f>
+        <f>'Матрица'!C8</f>
         <v/>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5156,25 +5136,25 @@
         </is>
       </c>
       <c r="D19" s="34">
-        <f>'Матрица'!M10</f>
+        <f>'Матрица'!M8</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>'Матрица'!N10</f>
+        <f>'Матрица'!N8</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>'Матрица'!O10</f>
+        <f>'Матрица'!O8</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9">
-        <f>'Матрица'!A11</f>
+        <f>'Матрица'!A9</f>
         <v/>
       </c>
       <c r="B20" s="9">
-        <f>'Матрица'!C11</f>
+        <f>'Матрица'!C9</f>
         <v/>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5183,25 +5163,25 @@
         </is>
       </c>
       <c r="D20" s="34">
-        <f>'Матрица'!M11</f>
+        <f>'Матрица'!M9</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>'Матрица'!N11</f>
-        <v/>
-      </c>
-      <c r="F20" s="18">
-        <f>'Матрица'!O11</f>
+        <f>'Матрица'!N9</f>
+        <v/>
+      </c>
+      <c r="F20" s="13">
+        <f>'Матрица'!O9</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>'Матрица'!A12</f>
+        <f>'Матрица'!A10</f>
         <v/>
       </c>
       <c r="B21" s="9">
-        <f>'Матрица'!C12</f>
+        <f>'Матрица'!C10</f>
         <v/>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5210,25 +5190,25 @@
         </is>
       </c>
       <c r="D21" s="34">
-        <f>'Матрица'!M12</f>
+        <f>'Матрица'!M10</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>'Матрица'!N12</f>
-        <v/>
-      </c>
-      <c r="F21" s="13">
-        <f>'Матрица'!O12</f>
+        <f>'Матрица'!N10</f>
+        <v/>
+      </c>
+      <c r="F21" s="18">
+        <f>'Матрица'!O10</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9">
-        <f>'Матрица'!A13</f>
+        <f>'Матрица'!A11</f>
         <v/>
       </c>
       <c r="B22" s="9">
-        <f>'Матрица'!C13</f>
+        <f>'Матрица'!C11</f>
         <v/>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -5237,25 +5217,25 @@
         </is>
       </c>
       <c r="D22" s="34">
-        <f>'Матрица'!M13</f>
+        <f>'Матрица'!M11</f>
         <v/>
       </c>
       <c r="E22" s="34">
-        <f>'Матрица'!N13</f>
-        <v/>
-      </c>
-      <c r="F22" s="13">
-        <f>'Матрица'!O13</f>
+        <f>'Матрица'!N11</f>
+        <v/>
+      </c>
+      <c r="F22" s="18">
+        <f>'Матрица'!O11</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9">
-        <f>'Матрица'!A14</f>
+        <f>'Матрица'!A12</f>
         <v/>
       </c>
       <c r="B23" s="9">
-        <f>'Матрица'!C14</f>
+        <f>'Матрица'!C12</f>
         <v/>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5264,25 +5244,25 @@
         </is>
       </c>
       <c r="D23" s="34">
-        <f>'Матрица'!M14</f>
+        <f>'Матрица'!M12</f>
         <v/>
       </c>
       <c r="E23" s="34">
-        <f>'Матрица'!N14</f>
+        <f>'Матрица'!N12</f>
         <v/>
       </c>
       <c r="F23" s="13">
-        <f>'Матрица'!O14</f>
+        <f>'Матрица'!O12</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9">
-        <f>'Матрица'!A15</f>
+        <f>'Матрица'!A13</f>
         <v/>
       </c>
       <c r="B24" s="9">
-        <f>'Матрица'!C15</f>
+        <f>'Матрица'!C13</f>
         <v/>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -5291,25 +5271,25 @@
         </is>
       </c>
       <c r="D24" s="34">
-        <f>'Матрица'!M15</f>
+        <f>'Матрица'!M13</f>
         <v/>
       </c>
       <c r="E24" s="34">
-        <f>'Матрица'!N15</f>
+        <f>'Матрица'!N13</f>
         <v/>
       </c>
       <c r="F24" s="13">
-        <f>'Матрица'!O15</f>
+        <f>'Матрица'!O13</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9">
-        <f>'Матрица'!A16</f>
+        <f>'Матрица'!A14</f>
         <v/>
       </c>
       <c r="B25" s="9">
-        <f>'Матрица'!C16</f>
+        <f>'Матрица'!C14</f>
         <v/>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5318,52 +5298,52 @@
         </is>
       </c>
       <c r="D25" s="34">
-        <f>'Матрица'!M16</f>
+        <f>'Матрица'!M14</f>
         <v/>
       </c>
       <c r="E25" s="34">
-        <f>'Матрица'!N16</f>
+        <f>'Матрица'!N14</f>
         <v/>
       </c>
       <c r="F25" s="13">
-        <f>'Матрица'!O16</f>
+        <f>'Матрица'!O14</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9">
-        <f>'Матрица'!A16</f>
+        <f>'Матрица'!A15</f>
         <v/>
       </c>
       <c r="B26" s="9">
-        <f>'Матрица'!C16</f>
+        <f>'Матрица'!C15</f>
         <v/>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="D26" s="34">
-        <f>'Матрица'!S16</f>
+        <f>'Матрица'!M15</f>
         <v/>
       </c>
       <c r="E26" s="34">
-        <f>'Матрица'!T16</f>
+        <f>'Матрица'!N15</f>
         <v/>
       </c>
       <c r="F26" s="13">
-        <f>'Матрица'!U16</f>
+        <f>'Матрица'!O15</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9">
-        <f>'Матрица'!A17</f>
+        <f>'Матрица'!A16</f>
         <v/>
       </c>
       <c r="B27" s="9">
-        <f>'Матрица'!C17</f>
+        <f>'Матрица'!C16</f>
         <v/>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -5372,52 +5352,52 @@
         </is>
       </c>
       <c r="D27" s="34">
-        <f>'Матрица'!M17</f>
+        <f>'Матрица'!M16</f>
         <v/>
       </c>
       <c r="E27" s="34">
-        <f>'Матрица'!N17</f>
-        <v/>
-      </c>
-      <c r="F27" s="18">
-        <f>'Матрица'!O17</f>
+        <f>'Матрица'!N16</f>
+        <v/>
+      </c>
+      <c r="F27" s="13">
+        <f>'Матрица'!O16</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9">
-        <f>'Матрица'!A18</f>
+        <f>'Матрица'!A16</f>
         <v/>
       </c>
       <c r="B28" s="9">
-        <f>'Матрица'!C18</f>
+        <f>'Матрица'!C16</f>
         <v/>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Тираж</t>
         </is>
       </c>
       <c r="D28" s="34">
-        <f>'Матрица'!M18</f>
+        <f>'Матрица'!S16</f>
         <v/>
       </c>
       <c r="E28" s="34">
-        <f>'Матрица'!N18</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>'Матрица'!O18</f>
+        <f>'Матрица'!T16</f>
+        <v/>
+      </c>
+      <c r="F28" s="13">
+        <f>'Матрица'!U16</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9">
-        <f>'Матрица'!A19</f>
+        <f>'Матрица'!A17</f>
         <v/>
       </c>
       <c r="B29" s="9">
-        <f>'Матрица'!C19</f>
+        <f>'Матрица'!C17</f>
         <v/>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -5426,25 +5406,25 @@
         </is>
       </c>
       <c r="D29" s="34">
-        <f>'Матрица'!M19</f>
+        <f>'Матрица'!M17</f>
         <v/>
       </c>
       <c r="E29" s="34">
-        <f>'Матрица'!N19</f>
+        <f>'Матрица'!N17</f>
         <v/>
       </c>
       <c r="F29" s="18">
-        <f>'Матрица'!O19</f>
+        <f>'Матрица'!O17</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9">
-        <f>'Матрица'!A20</f>
+        <f>'Матрица'!A18</f>
         <v/>
       </c>
       <c r="B30" s="9">
-        <f>'Матрица'!C20</f>
+        <f>'Матрица'!C18</f>
         <v/>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -5453,25 +5433,25 @@
         </is>
       </c>
       <c r="D30" s="34">
-        <f>'Матрица'!M20</f>
+        <f>'Матрица'!M18</f>
         <v/>
       </c>
       <c r="E30" s="34">
-        <f>'Матрица'!N20</f>
+        <f>'Матрица'!N18</f>
         <v/>
       </c>
       <c r="F30" s="18">
-        <f>'Матрица'!O20</f>
+        <f>'Матрица'!O18</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9">
-        <f>'Матрица'!A21</f>
+        <f>'Матрица'!A19</f>
         <v/>
       </c>
       <c r="B31" s="9">
-        <f>'Матрица'!C21</f>
+        <f>'Матрица'!C19</f>
         <v/>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -5480,25 +5460,25 @@
         </is>
       </c>
       <c r="D31" s="34">
-        <f>'Матрица'!M21</f>
+        <f>'Матрица'!M19</f>
         <v/>
       </c>
       <c r="E31" s="34">
-        <f>'Матрица'!N21</f>
-        <v/>
-      </c>
-      <c r="F31" s="13">
-        <f>'Матрица'!O21</f>
+        <f>'Матрица'!N19</f>
+        <v/>
+      </c>
+      <c r="F31" s="18">
+        <f>'Матрица'!O19</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9">
-        <f>'Матрица'!A22</f>
+        <f>'Матрица'!A20</f>
         <v/>
       </c>
       <c r="B32" s="9">
-        <f>'Матрица'!C22</f>
+        <f>'Матрица'!C20</f>
         <v/>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -5507,25 +5487,25 @@
         </is>
       </c>
       <c r="D32" s="34">
-        <f>'Матрица'!M22</f>
+        <f>'Матрица'!M20</f>
         <v/>
       </c>
       <c r="E32" s="34">
-        <f>'Матрица'!N22</f>
-        <v/>
-      </c>
-      <c r="F32" s="13">
-        <f>'Матрица'!O22</f>
+        <f>'Матрица'!N20</f>
+        <v/>
+      </c>
+      <c r="F32" s="18">
+        <f>'Матрица'!O20</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9">
-        <f>'Матрица'!A23</f>
+        <f>'Матрица'!A21</f>
         <v/>
       </c>
       <c r="B33" s="9">
-        <f>'Матрица'!C23</f>
+        <f>'Матрица'!C21</f>
         <v/>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -5534,25 +5514,25 @@
         </is>
       </c>
       <c r="D33" s="34">
-        <f>'Матрица'!M23</f>
+        <f>'Матрица'!M21</f>
         <v/>
       </c>
       <c r="E33" s="34">
-        <f>'Матрица'!N23</f>
+        <f>'Матрица'!N21</f>
         <v/>
       </c>
       <c r="F33" s="13">
-        <f>'Матрица'!O23</f>
+        <f>'Матрица'!O21</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9">
-        <f>'Матрица'!A25</f>
+        <f>'Матрица'!A22</f>
         <v/>
       </c>
       <c r="B34" s="9">
-        <f>'Матрица'!C25</f>
+        <f>'Матрица'!C22</f>
         <v/>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -5561,25 +5541,25 @@
         </is>
       </c>
       <c r="D34" s="34">
-        <f>'Матрица'!M25</f>
+        <f>'Матрица'!M22</f>
         <v/>
       </c>
       <c r="E34" s="34">
-        <f>'Матрица'!N25</f>
-        <v/>
-      </c>
-      <c r="F34" s="18">
-        <f>'Матрица'!O25</f>
+        <f>'Матрица'!N22</f>
+        <v/>
+      </c>
+      <c r="F34" s="13">
+        <f>'Матрица'!O22</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9">
-        <f>'Матрица'!A32</f>
+        <f>'Матрица'!A23</f>
         <v/>
       </c>
       <c r="B35" s="9">
-        <f>'Матрица'!C32</f>
+        <f>'Матрица'!C23</f>
         <v/>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -5588,25 +5568,25 @@
         </is>
       </c>
       <c r="D35" s="34">
-        <f>'Матрица'!M32</f>
+        <f>'Матрица'!M23</f>
         <v/>
       </c>
       <c r="E35" s="34">
-        <f>'Матрица'!N32</f>
-        <v/>
-      </c>
-      <c r="F35" s="18">
-        <f>'Матрица'!O32</f>
+        <f>'Матрица'!N23</f>
+        <v/>
+      </c>
+      <c r="F35" s="13">
+        <f>'Матрица'!O23</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9">
-        <f>'Матрица'!A33</f>
+        <f>'Матрица'!A25</f>
         <v/>
       </c>
       <c r="B36" s="9">
-        <f>'Матрица'!C33</f>
+        <f>'Матрица'!C25</f>
         <v/>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -5615,25 +5595,25 @@
         </is>
       </c>
       <c r="D36" s="34">
-        <f>'Матрица'!M33</f>
+        <f>'Матрица'!M25</f>
         <v/>
       </c>
       <c r="E36" s="34">
-        <f>'Матрица'!N33</f>
+        <f>'Матрица'!N25</f>
         <v/>
       </c>
       <c r="F36" s="18">
-        <f>'Матрица'!O33</f>
+        <f>'Матрица'!O25</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9">
-        <f>'Матрица'!A34</f>
+        <f>'Матрица'!A32</f>
         <v/>
       </c>
       <c r="B37" s="9">
-        <f>'Матрица'!C34</f>
+        <f>'Матрица'!C32</f>
         <v/>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -5642,25 +5622,25 @@
         </is>
       </c>
       <c r="D37" s="34">
-        <f>'Матрица'!M34</f>
+        <f>'Матрица'!M32</f>
         <v/>
       </c>
       <c r="E37" s="34">
-        <f>'Матрица'!N34</f>
+        <f>'Матрица'!N32</f>
         <v/>
       </c>
       <c r="F37" s="18">
-        <f>'Матрица'!O34</f>
+        <f>'Матрица'!O32</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <f>'Матрица'!A36</f>
+        <f>'Матрица'!A33</f>
         <v/>
       </c>
       <c r="B38" s="9">
-        <f>'Матрица'!C36</f>
+        <f>'Матрица'!C33</f>
         <v/>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -5669,163 +5649,219 @@
         </is>
       </c>
       <c r="D38" s="34">
-        <f>'Матрица'!M36</f>
+        <f>'Матрица'!M33</f>
         <v/>
       </c>
       <c r="E38" s="34">
-        <f>'Матрица'!N36</f>
+        <f>'Матрица'!N33</f>
         <v/>
       </c>
       <c r="F38" s="18">
-        <f>'Матрица'!O36</f>
+        <f>'Матрица'!O33</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9">
+        <f>'Матрица'!A34</f>
+        <v/>
+      </c>
+      <c r="B39" s="9">
+        <f>'Матрица'!C34</f>
+        <v/>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D39" s="34">
+        <f>'Матрица'!M34</f>
+        <v/>
+      </c>
+      <c r="E39" s="34">
+        <f>'Матрица'!N34</f>
+        <v/>
+      </c>
+      <c r="F39" s="18">
+        <f>'Матрица'!O34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9">
+        <f>'Матрица'!A36</f>
+        <v/>
+      </c>
+      <c r="B40" s="9">
+        <f>'Матрица'!C36</f>
+        <v/>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D40" s="34">
+        <f>'Матрица'!M36</f>
+        <v/>
+      </c>
+      <c r="E40" s="34">
+        <f>'Матрица'!N36</f>
+        <v/>
+      </c>
+      <c r="F40" s="18">
+        <f>'Матрица'!O36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9">
         <f>'Матрица'!A37</f>
         <v/>
       </c>
-      <c r="B39" s="9">
+      <c r="B41" s="9">
         <f>'Матрица'!C37</f>
         <v/>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="D39" s="34">
+      <c r="D41" s="34">
         <f>'Матрица'!M37</f>
         <v/>
       </c>
-      <c r="E39" s="34">
+      <c r="E41" s="34">
         <f>'Матрица'!N37</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F41" s="18">
         <f>'Матрица'!O37</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="43" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="43" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>ADR-200</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="11" t="inlineStr">
         <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C47:F47"/>
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C43:F43"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C50:F50"/>
     <mergeCell ref="C44:F44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2050,22 +2050,22 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Python-скрипт `scripts/reindex_kb.py` (сервис `reindex` в docker compose); MVP — K8s CronJob (Celery Beat)</t>
+          <t>Python-скрипт `scripts/reindex_kb.py` (сервис `reindex` в docker compose): python-docx → нарезка частей до 300 знаков → Presidio (проверка ПДн) → sentence-transformers (e5-small, CPU) → qdrant-client (blue-green алиас); MVP — K8s CronJob, Celery в коде нет</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Сервис `reindex` в compose: одноразовый прогон при подъёме стека (`scripts/reindex_kb.py`), запись в новую коллекцию и атомарное переключение алиаса; Backend только подключается к готовому индексу.</t>
+          <t>Сервис `reindex` в compose: одноразовый прогон при подъёме стека (`scripts/reindex_kb.py`), запись в новую коллекцию и атомарное переключение алиаса; Backend только подключается к готовому индексу. Очереди задач и Celery в коде нет. В базе сейчас 27 источников (20 пар FAQ и 7 синтетических документов Word) → 51 фрагмент → 190 векторов.</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Планировщик по расписанию выбран против Airflow (платформа ради одного задания) и cron внутри Backend (нет изоляции от ответов абонентам).</t>
+          <t>Планировщик по расписанию выбран против Airflow (платформа ради одного задания) и cron внутри Backend (нет изоляции от ответов абонентам) — по документации, пробного внедрения не было. Celery Beat в коде не используется. Объём MVP — несколько тысяч документов (3 000–5 000), 30 000–100 000 частей (допущение); по замеру на CPU e5-small индексирует их за ≈14–46 мин, BGE-M3 — за ≈2,7–9,6 ч при окне 3 ч; на GPU скорость не измерялась.</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему индексация — задание по расписанию, а не Airflow»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему индексация — задание по расписанию, а не Airflow» и подраздел «Индексация базы знаний: что реализовано и какой объём»</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Ночное окно 02:00–05:00: забор документов, очистка, эмбеддинги на GPU, полный реиндекс.</t>
+          <t>Ночное окно 02:00–05:00: забор документов, очистка, эмбеддинги на GPU, полный реиндекс. Что «окна хватит» на 30–100 тыс. частей на GPU — допущение, скорость на GPU не измерялась; источник и формат настоящих документов владелец не назвал.</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes CronJob (Celery Beat), окно обслуживания, жёсткая граница по времени.</t>
+          <t>Kubernetes CronJob, окно обслуживания, жёсткая граница по времени. Разбор — python-docx; ПДн — Presidio; эмбеддинги — модель по итогам теста (BGE-M3 предварительно); запись — qdrant-client, blue-green алиас.</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Стоимость" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники и допущения" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объём по контейнерам" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$37</definedName>
@@ -213,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -334,6 +335,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5867,4 +5874,616 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>Объём и нагрузка по контейнерам</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="49" t="inlineStr">
+        <is>
+          <t>Нагрузка из `Capacity_Report.html` (допущения A1–A5, данных водоканала нет): MVP (10 тыс. абонентов) — базовый сценарий 18 000 запросов в месяц, пик 0,025 запроса/с, одновременно 0,08; высокий — 75 000, 0,10 запроса/с, 0,31. Тираж (100 тыс.) — базовый 180 000, 0,25 запроса/с, 0,75; высокий 750 000, 1,04 запроса/с, 3,12. Сценарии рассчитаны под 10 и 100 тысяч абонентов; в ADR-500 те же контуры — 8 000 и 90 000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Контейнер</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Что определяет объём</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Что заложено</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>AI-виджет</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Число одновременных пользователей</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Отдельного объёма нет: статические файлы, нагрузка — общая (см. Backend). Одновременно до 0,3 запроса на MVP и до 3 на тираже (расчёт).</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт по допущениям</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Capacity_Report, раздел 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Число запросов в секунду</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Общая нагрузка (см. выше). Реплик — 2–3 «для отказоустойчивости, не для пропускной способности». CPU и память пода не заданы; пропускная способность одной реплики и нагрузочные тесты не проводились.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Допущение; замеров нет</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Capacity_Report, раздел 7; ADR-600 (нагрузочные тесты в плане)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Классификатор обращений (Triage)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Число вопросов; размер набора примеров k-NN</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Один проход на вопрос (22–37 мс на CPU, замер). Набор примеров сейчас — 136 обращений; для MVP требуется не менее 100 на тип (около 1 500–2 000 текстов).</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Замер задержки; объём набора — план</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300; ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>LLM Gateway</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Число вопросов и лимиты</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Общая нагрузка. Лимиты по умолчанию в `app/config.py`: 20 запросов в минуту на абонента, 10 на сессию, 300 на сервис (5 запросов/с); расчётом не обоснованы. Сессия живёт 30 минут.</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Настройки прототипа</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>app/config.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>PII Filter</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Число вопросов и ответов</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Один проход на вопрос и один на ответ. Время проверки ответа ≈800 знаков — 30–45 мс (замер), на ≈2 000 знаков — 60–70 мс. Объём не задан.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Замер задержки</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>ADR-400</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Guardrails и судья качества</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Число ответов; оценка судьёй</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Судья: 39 млн токенов в месяц на MVP и 120 млн на тираже (30 млн — ночной прогон Golden Set, остальное — 5% выборка трафика); допущение: 5 вызовов судьи по ≈2 000 токенов на образец.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт по допущениям</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Capacity_Report, раздел 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>LLM Provider</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Токены генерации</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Токенов на запрос: измерено 401 (19 вызовов, фрагменты FAQ до 300 знаков), допущение отчёта — 3 500. Стоимость токенов на MVP — ≈160–16 500 ₽/мес по ADR-500, до ≈40 000 ₽/мес при спросе из отчёта. Агент Этапа 2 добавляет около +20% токенов.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Замер (401) и допущение (3 500)</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>ADR-500; Capacity_Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Эмбеддинги (модель поиска)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Вопросы; индексация базы знаний</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Один запрос на вопрос; при индексации 30 000–100 000 частей. Скорость на CPU измерена, на GPU — нет.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Замер на CPU; GPU не измерялся</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200; ADR-300</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Реранкер</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Вопросы × 20 кандидатов</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Одно переранжирование 20 кандидатов на вопрос. На CPU 7,2 с (замер); загрузка GPU ≈0,1% на MVP и ≈1% на тираже — расчёт, скорость на GPU не измерялась.</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт; GPU не измерялся</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300; Capacity_Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Векторная база (Qdrant)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Размер базы знаний</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Несколько тысяч документов (3 000–5 000), 30 000–100 000 векторов размерности 1 024, ≈0,3–1,0 ГБ. От числа абонентов не зависит. Поиск на 100 000 векторов: P99 65 мс без фильтра, 37 мс с фильтром (замер).</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Допущение объёма; замер поиска</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Кэш профиля абонента (Postgres)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Число абонентов и начислений</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>8 000 профилей на MVP, 90 000 на тираже. Размер строки не считался. По примеру прототипа (200 счетов, 1 323 начисления) ≈6,6 начисления на счёт — порядка 53 000 строк на 8 000 счетов, если структура та же.</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Допущение; размер не считался</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200; data_example</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Redis (квоты, состояние диалога)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Одновременные сессии и счётчики</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Сессия живёт 30 минут, одновременно до 0,3 запроса на MVP и до 3 на тираже; размер ключей не измерялся, объём по расчёту ничтожен.</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Не измерялся</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>app/config.py; Capacity_Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Postgres (обращения, слепки, события, телеметрия)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Диалоги, обращения, события</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Телеметрия: 6 000–70 600 строк в год на MVP, 68 000–794 000 на тираже (≈2–245 МБ в год; замер 2 млн строк — 589 МБ). Диалоги и обращения: в отчёте о мощности «единицы ГБ на MVP, десятки ГБ на тираже» без вывода; срок хранения диалогов и число обращений в месяц не заданы.</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Телеметрия — расчёт и замер; остальное не задано</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200; Capacity_Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Индексация базы знаний (ETL)</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Число частей и окно 02:00–05:00</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>30 000–100 000 частей. На CPU e5-small ≈14–46 мин, BGE-M3 ≈2,7–9,6 ч; на GPU не измерялось.</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт по замеру на CPU</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Агент записи, Billing Adapter, Сервис обращений, Document Generator (Этап 2)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Доля диалогов с записью</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Допущение A6: 25% диалогов ведут к записи — 1 125 диалогов в месяц на MVP, 11 250 на тираже (базовый сценарий); надбавка токенов ≈12 и ≈124 млн в месяц. Хранилище готовых документов (MinIO): «десятки ГБ на MVP, сотни на тираже» без вывода; число бланков в месяц не задано.</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Допущение</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Capacity_Report, раздел 8.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="50" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Оркестрация (Kubernetes), узлы</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Число и размер узлов</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Пулы general / gpu / data по схеме развёртывания; «1× GPU-узел». Число узлов, CPU, память и диск на под не заданы; GPU-сервер под эмбеддинги и реранкер не оценён.</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Не задан</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>C4_Deployment; ADR-500 (открытые пункты)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Наблюдаемость</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Метрики и логи</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Loki: ≈0,2 ГБ за 30 дней на MVP, ≈1,7 ГБ на тираже (допущение: 10 записей на запрос по ≈1 КБ). Объём метрик Prometheus не считался.</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Допущение</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Capacity_Report, раздел 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Секреты (Vault)</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Объёма нет.</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>ADR-400</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Стоимость" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники и допущения" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объём по контейнерам" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sizing" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$37</definedName>
@@ -22,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0#"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +76,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="14">
@@ -214,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -341,6 +348,30 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2544,7 +2575,7 @@
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes на собственном железе в закрытом контуре: пространства имён, Ingress, TLS-сертификаты.</t>
+          <t>Kubernetes на собственном железе в закрытом контуре: пространства имён, Ingress, TLS-сертификаты. Расчёт по допущениям (лист «Sizing»): 6 узлов на MVP (3 общих, 2 данных, 1 GPU), 8 на тираже (+1 узел под собственную модель); скорость на GPU не измерялась, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
@@ -4903,7 +4934,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8" ht="135" customHeight="1">
       <c r="A8" s="46" t="inlineStr">
         <is>
           <t>•</t>
@@ -4916,7 +4947,7 @@
       </c>
       <c r="C8" s="48" t="inlineStr">
         <is>
-          <t>Время запроса на CPU: e5-small 36–37 мс (первый замер 22 мс), BGE-M3 300 мс (первый замер 210 мс), реранкер на 20 кандидатах 7,2 с; бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром.</t>
+          <t>Время запроса на CPU: e5-small 36–37 мс (первый замер 22 мс), BGE-M3 300 мс (первый замер 210 мс), реранкер на 20 кандидатах 7,2 с; бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром. Backend, путь без модели: 117 запросов/с на процесс, 8,5 мс CPU на запрос. Память: обезличиватель 769 МиБ, эмбеддер e5-small +300 МиБ, контейнер Backend 1,32 ГиБ. Redis: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход. Prometheus: 84 ряда на процесс. Выбранные допущения и расчёт узлов — лист «Sizing».</t>
         </is>
       </c>
     </row>
@@ -5969,7 +6000,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="50" t="n">
         <v>2</v>
       </c>
@@ -5985,12 +6016,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Общая нагрузка (см. выше). Реплик — 2–3 «для отказоустойчивости, не для пропускной способности». CPU и память пода не заданы; пропускная способность одной реплики и нагрузочные тесты не проводились.</t>
+          <t>Общая нагрузка (см. выше). Замер: путь без модели — 117 запросов/с на один процесс (8,5 мс CPU на запрос), при 4 параллельных запросах медиана 36 мс. Выбрано: 2 реплики на MVP и 3 на тираже по 0,5 и 1 vCPU, ОЗУ 0,5 и 1 ГиБ (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Допущение; замеров нет</t>
+          <t>Замер пропускной способности; реплики выбраны</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -6059,7 +6090,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="50" t="n">
         <v>5</v>
       </c>
@@ -6075,12 +6106,12 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Один проход на вопрос и один на ответ. Время проверки ответа ≈800 знаков — 30–45 мс (замер), на ≈2 000 знаков — 60–70 мс. Объём не задан.</t>
+          <t>Один проход на вопрос и один на ответ. Время проверки ответа ≈800 знаков — 30–45 мс (замер), на ≈2 000 знаков — 60–70 мс. Память обезличивателя (Presidio + spaCy) — 769 МиБ (замер). Работает внутри шлюза, отдельного пода нет.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Замер задержки</t>
+          <t>Замер</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -6239,7 +6270,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="50" t="n">
         <v>11</v>
       </c>
@@ -6255,12 +6286,12 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>8 000 профилей на MVP, 90 000 на тираже. Размер строки не считался. По примеру прототипа (200 счетов, 1 323 начисления) ≈6,6 начисления на счёт — порядка 53 000 строк на 8 000 счетов, если структура та же.</t>
+          <t>8 000 профилей на MVP, 90 000 на тираже. Строка профиля с начислениями — 3 КБ (допущение): ≈24 МБ на MVP, ≈270 МБ на тираже. По примеру прототипа (200 счетов, 1 323 начисления) ≈6,6 начисления на счёт. Хранится в Postgres (см. ниже).</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Допущение; размер не считался</t>
+          <t>Допущение; выбрано и посчитано</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -6269,7 +6300,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="50" t="n">
         <v>12</v>
       </c>
@@ -6285,12 +6316,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Сессия живёт 30 минут, одновременно до 0,3 запроса на MVP и до 3 на тираже; размер ключей не измерялся, объём по расчёту ничтожен.</t>
+          <t>Сессия живёт 30 минут, одновременно до 0,3 запроса на MVP и до 3 на тираже; замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход; до 1 800 одновременных сессий ≈5 МБ. Выбрано: 1 экземпляр на MVP, 2 на тираже, 0,25 ГиБ (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Не измерялся</t>
+          <t>Замер; экземпляры выбраны</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -6299,7 +6330,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="90" customHeight="1">
       <c r="A17" s="50" t="n">
         <v>13</v>
       </c>
@@ -6315,17 +6346,17 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Телеметрия: 6 000–70 600 строк в год на MVP, 68 000–794 000 на тираже (≈2–245 МБ в год; замер 2 млн строк — 589 МБ). Диалоги и обращения: в отчёте о мощности «единицы ГБ на MVP, десятки ГБ на тираже» без вывода; срок хранения диалогов и число обращений в месяц не заданы.</t>
+          <t>Телеметрия: 6 000–70 600 строк в год на MVP, 68 000–794 000 на тираже (≈2–245 МБ в год; замер 2 млн строк — 589 МБ). Журнал диалогов при сроке хранения 90 суток (выбрано) — до 0,15 ГБ на MVP и 1,5 ГБ на тираже (4 КБ на диалог, высокий сценарий). Итого до 0,5 ГБ на MVP и до 5 ГБ на тираже, том 20 и 50 ГиБ (лист «Sizing»). Число обращений в месяц принято равным диалогам с записью (допущение A6).</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Телеметрия — расчёт и замер; остальное не задано</t>
+          <t>Расчёт и замер; срок хранения выбран</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; Capacity_Report</t>
+          <t>ADR-200; Sizing</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6390,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="90" customHeight="1">
       <c r="A19" s="50" t="n">
         <v>15</v>
       </c>
@@ -6375,12 +6406,12 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Допущение A6: 25% диалогов ведут к записи — 1 125 диалогов в месяц на MVP, 11 250 на тираже (базовый сценарий); надбавка токенов ≈12 и ≈124 млн в месяц. Хранилище готовых документов (MinIO): «десятки ГБ на MVP, сотни на тираже» без вывода; число бланков в месяц не задано.</t>
+          <t>Допущение A6: 25% диалогов ведут к записи — 1 125 диалогов в месяц на MVP, 11 250 на тираже (базовый сценарий); надбавка токенов ≈12 и ≈124 млн в месяц. Хранилище готовых документов (MinIO): ≈200 КБ на бланк (допущение) × 1 125 в месяц — 2,7 ГБ в год на MVP, 27 ГБ в год на тираже; том MinIO 100 и 200 ГиБ с копиями и документами базы знаний (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Допущение</t>
+          <t>Допущение; выбрано и посчитано</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -6389,7 +6420,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="75" customHeight="1">
       <c r="A20" s="50" t="n">
         <v>16</v>
       </c>
@@ -6405,21 +6436,21 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Пулы general / gpu / data по схеме развёртывания; «1× GPU-узел». Число узлов, CPU, память и диск на под не заданы; GPU-сервер под эмбеддинги и реранкер не оценён.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing»): MVP — 6 узлов (3 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ, 1 GPU-узел с видеокартой 24 ГБ), тираж — 8 (4 общих, 2 данных, 1 GPU, 1 узел под собственную модель с A100 80 ГБ). Диск под тома ≈176 ГиБ на MVP и ≈467 ГиБ на тираже. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Не задан</t>
+          <t>Расчёт по допущениям</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>C4_Deployment; ADR-500 (открытые пункты)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+          <t>Sizing; C4_Deployment</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="50" t="n">
         <v>17</v>
       </c>
@@ -6435,12 +6466,12 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Loki: ≈0,2 ГБ за 30 дней на MVP, ≈1,7 ГБ на тираже (допущение: 10 записей на запрос по ≈1 КБ). Объём метрик Prometheus не считался.</t>
+          <t>Loki: ≈0,2 ГБ за 30 дней на MVP, ≈1,7 ГБ на тираже (допущение: 10 записей на запрос по ≈1 КБ). Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Допущение</t>
+          <t>Допущение и замер</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -6486,4 +6517,2251 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="90" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>Расчётный sizing по компонентам (допущения, не результат нагрузочного теста)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>Синие ячейки — входные допущения, их можно менять; итоги и число узлов пересчитываются. Основание — в последней колонке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Расчётная нагрузка</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Пик MVP — 0,1 запроса/с, тираж — 1 запрос/с (высокий сценарий `Capacity_Report.html`, пересчитанный на 8 000 и 90 000 абонентов и округлённый вверх); одновременно 0,3 запроса на MVP и 3 на тираже (время ответа 3 с). До модели доходит 70% запросов (верхняя оценка ADR-500).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>CPU на запрос</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Путь без модели — 8,5 мс на запрос (замер: один процесс отдаёт 117 запросов/с). Путь с моделью — 0,9 с на ответ в 800 знаков (эмбеддинг 36 мс + обезличивание + проверка ответа на потоке 0,3–0,9 с; на ответе в 2 000 знаков 1,4–4,5 с, замер). При 0,7 запроса/с к модели это ≈0,63 ядра на тираже; на длинных ответах — до 3,2 ядра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Память</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Замер: обезличиватель (Presidio + spaCy `ru_core_news_md`) — 769 МиБ, эмбеддер e5-small — ещё 300 МиБ, контейнер Backend целиком — 1,32 ГиБ. На MVP эмбеддер уходит в отдельный сервис, обезличиватель остаётся в шлюзе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Данные</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Ключ квоты в Redis — 72 байта, с накладными ≈0,5 КБ (замер). Сессия диалога — 1,6 КБ на два хода, ≈0,8 КБ на ход (замер), живёт 30 минут. Диалог — 4 хода ≈ 4 КБ с метаданными (допущение A3 = 4). Срок хранения журнала диалогов принят 90 суток (требование ИБ неизвестно). Строка телеметрии — 308 байт с индексами (замер).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Отказоустойчивость</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Минимум 2 реплики у stateless-сервисов; у хранилищ — 1 экземпляр на MVP с ежедневной копией и 2 экземпляра на тираже. Узлов на один больше, чем нужно по запросам (N+1); GPU-узел один, потеря узла = отказ поиска до восстановления.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Узлы</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Загрузка узла по запросам не выше 70%. Класс узлов: общий — 8 vCPU / 16 ГиБ; данных — 8 vCPU / 32 ГиБ с NVMe; GPU — 8 vCPU / 32 ГиБ и видеокарта 24 ГБ; LLM (тираж) — 16 vCPU / 128 ГиБ и A100 80 ГБ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="M10" s="51" t="inlineStr">
+        <is>
+          <t>Тираж</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Пул</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Компонент</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Реплик</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>vCPU на под</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ОЗУ, ГиБ на под</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Диск, ГиБ на под</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Видеопамять, ГиБ на под</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>vCPU всего</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>ОЗУ всего, ГиБ</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Диск всего, ГиБ</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Видеопамять всего, ГиБ</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Реплик</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>vCPU на под</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>ОЗУ, ГиБ на под</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Диск, ГиБ на под</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>Видеопамять, ГиБ на под</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>vCPU всего</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>ОЗУ всего, ГиБ</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>Диск всего, ГиБ</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>Видеопамять всего, ГиБ</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>Основание</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Ingress (nginx)</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F12" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="53">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="J12" s="53">
+        <f>D12*F12</f>
+        <v/>
+      </c>
+      <c r="K12" s="53">
+        <f>D12*G12</f>
+        <v/>
+      </c>
+      <c r="L12" s="53">
+        <f>D12*H12</f>
+        <v/>
+      </c>
+      <c r="M12" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O12" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P12" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="53">
+        <f>M12*N12</f>
+        <v/>
+      </c>
+      <c r="S12" s="53">
+        <f>M12*O12</f>
+        <v/>
+      </c>
+      <c r="T12" s="53">
+        <f>M12*P12</f>
+        <v/>
+      </c>
+      <c r="U12" s="53">
+        <f>M12*Q12</f>
+        <v/>
+      </c>
+      <c r="V12" s="9" t="inlineStr">
+        <is>
+          <t>Допущение. Внешний трафик — единицы запросов в секунду.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Vault</t>
+        </is>
+      </c>
+      <c r="D13" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F13" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G13" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="53">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="J13" s="53">
+        <f>D13*F13</f>
+        <v/>
+      </c>
+      <c r="K13" s="53">
+        <f>D13*G13</f>
+        <v/>
+      </c>
+      <c r="L13" s="53">
+        <f>D13*H13</f>
+        <v/>
+      </c>
+      <c r="M13" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O13" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P13" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="53">
+        <f>M13*N13</f>
+        <v/>
+      </c>
+      <c r="S13" s="53">
+        <f>M13*O13</f>
+        <v/>
+      </c>
+      <c r="T13" s="53">
+        <f>M13*P13</f>
+        <v/>
+      </c>
+      <c r="U13" s="53">
+        <f>M13*Q13</f>
+        <v/>
+      </c>
+      <c r="V13" s="9" t="inlineStr">
+        <is>
+          <t>Допущение. Инжектор секретов и cert-manager — отдельной строкой не выделены (≈0,1 vCPU / 0,1 ГиБ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>AI-виджет (статические файлы)</t>
+        </is>
+      </c>
+      <c r="D14" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F14" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="53">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="J14" s="53">
+        <f>D14*F14</f>
+        <v/>
+      </c>
+      <c r="K14" s="53">
+        <f>D14*G14</f>
+        <v/>
+      </c>
+      <c r="L14" s="53">
+        <f>D14*H14</f>
+        <v/>
+      </c>
+      <c r="M14" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O14" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P14" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="53">
+        <f>M14*N14</f>
+        <v/>
+      </c>
+      <c r="S14" s="53">
+        <f>M14*O14</f>
+        <v/>
+      </c>
+      <c r="T14" s="53">
+        <f>M14*P14</f>
+        <v/>
+      </c>
+      <c r="U14" s="53">
+        <f>M14*Q14</f>
+        <v/>
+      </c>
+      <c r="V14" s="9" t="inlineStr">
+        <is>
+          <t>Допущение. На стенде три статических файла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Backend (API, классификация, поиск, сборка ответа)</t>
+        </is>
+      </c>
+      <c r="D15" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="53">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="J15" s="53">
+        <f>D15*F15</f>
+        <v/>
+      </c>
+      <c r="K15" s="53">
+        <f>D15*G15</f>
+        <v/>
+      </c>
+      <c r="L15" s="53">
+        <f>D15*H15</f>
+        <v/>
+      </c>
+      <c r="M15" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="53">
+        <f>M15*N15</f>
+        <v/>
+      </c>
+      <c r="S15" s="53">
+        <f>M15*O15</f>
+        <v/>
+      </c>
+      <c r="T15" s="53">
+        <f>M15*P15</f>
+        <v/>
+      </c>
+      <c r="U15" s="53">
+        <f>M15*Q15</f>
+        <v/>
+      </c>
+      <c r="V15" s="9" t="inlineStr">
+        <is>
+          <t>Замер: путь без модели — 117 запросов/с на процесс (8,5 мс CPU). 2 реплики нужны для отказоустойчивости, а не для пропускной способности; ОЗУ — допущение (эмбеддер и обезличиватель вынесены).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>LLM Gateway (лимиты, обезличивание, проверка ответа)</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G16" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="53">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="J16" s="53">
+        <f>D16*F16</f>
+        <v/>
+      </c>
+      <c r="K16" s="53">
+        <f>D16*G16</f>
+        <v/>
+      </c>
+      <c r="L16" s="53">
+        <f>D16*H16</f>
+        <v/>
+      </c>
+      <c r="M16" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P16" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="53">
+        <f>M16*N16</f>
+        <v/>
+      </c>
+      <c r="S16" s="53">
+        <f>M16*O16</f>
+        <v/>
+      </c>
+      <c r="T16" s="53">
+        <f>M16*P16</f>
+        <v/>
+      </c>
+      <c r="U16" s="53">
+        <f>M16*Q16</f>
+        <v/>
+      </c>
+      <c r="V16" s="9" t="inlineStr">
+        <is>
+          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,06 ядра на MVP, 0,63 на тираже; на ответах в 2 000 знаков до 3,2 ядра (3 реплики × 1 vCPU + предел 2). После оптимизации проверки на потоке запас вырастет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Billing Adapter, оркестратор записи (Этап 2)</t>
+        </is>
+      </c>
+      <c r="D17" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F17" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G17" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="53">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="J17" s="53">
+        <f>D17*F17</f>
+        <v/>
+      </c>
+      <c r="K17" s="53">
+        <f>D17*G17</f>
+        <v/>
+      </c>
+      <c r="L17" s="53">
+        <f>D17*H17</f>
+        <v/>
+      </c>
+      <c r="M17" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O17" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P17" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="53">
+        <f>M17*N17</f>
+        <v/>
+      </c>
+      <c r="S17" s="53">
+        <f>M17*O17</f>
+        <v/>
+      </c>
+      <c r="T17" s="53">
+        <f>M17*P17</f>
+        <v/>
+      </c>
+      <c r="U17" s="53">
+        <f>M17*Q17</f>
+        <v/>
+      </c>
+      <c r="V17" s="9" t="inlineStr">
+        <is>
+          <t>Допущение. 1 125 диалогов с записью в месяц на MVP, 11 250 на тираже (A6 = 25%) — нагрузка ничтожна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Document Generator (PDF, Этап 2)</t>
+        </is>
+      </c>
+      <c r="D18" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="53">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="J18" s="53">
+        <f>D18*F18</f>
+        <v/>
+      </c>
+      <c r="K18" s="53">
+        <f>D18*G18</f>
+        <v/>
+      </c>
+      <c r="L18" s="53">
+        <f>D18*H18</f>
+        <v/>
+      </c>
+      <c r="M18" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O18" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="53">
+        <f>M18*N18</f>
+        <v/>
+      </c>
+      <c r="S18" s="53">
+        <f>M18*O18</f>
+        <v/>
+      </c>
+      <c r="T18" s="53">
+        <f>M18*P18</f>
+        <v/>
+      </c>
+      <c r="U18" s="53">
+        <f>M18*Q18</f>
+        <v/>
+      </c>
+      <c r="V18" s="9" t="inlineStr">
+        <is>
+          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>ETL индексации (CronJob, окно 02:00–05:00)</t>
+        </is>
+      </c>
+      <c r="D19" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="53">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+      <c r="J19" s="53">
+        <f>D19*F19</f>
+        <v/>
+      </c>
+      <c r="K19" s="53">
+        <f>D19*G19</f>
+        <v/>
+      </c>
+      <c r="L19" s="53">
+        <f>D19*H19</f>
+        <v/>
+      </c>
+      <c r="M19" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="53">
+        <f>M19*N19</f>
+        <v/>
+      </c>
+      <c r="S19" s="53">
+        <f>M19*O19</f>
+        <v/>
+      </c>
+      <c r="T19" s="53">
+        <f>M19*P19</f>
+        <v/>
+      </c>
+      <c r="U19" s="53">
+        <f>M19*Q19</f>
+        <v/>
+      </c>
+      <c r="V19" s="9" t="inlineStr">
+        <is>
+          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Оценка качества (CronJob, ночной прогон)</t>
+        </is>
+      </c>
+      <c r="D20" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="53">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+      <c r="J20" s="53">
+        <f>D20*F20</f>
+        <v/>
+      </c>
+      <c r="K20" s="53">
+        <f>D20*G20</f>
+        <v/>
+      </c>
+      <c r="L20" s="53">
+        <f>D20*H20</f>
+        <v/>
+      </c>
+      <c r="M20" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O20" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="53">
+        <f>M20*N20</f>
+        <v/>
+      </c>
+      <c r="S20" s="53">
+        <f>M20*O20</f>
+        <v/>
+      </c>
+      <c r="T20" s="53">
+        <f>M20*P20</f>
+        <v/>
+      </c>
+      <c r="U20" s="53">
+        <f>M20*Q20</f>
+        <v/>
+      </c>
+      <c r="V20" s="9" t="inlineStr">
+        <is>
+          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Prometheus</t>
+        </is>
+      </c>
+      <c r="D21" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="53">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+      <c r="J21" s="53">
+        <f>D21*F21</f>
+        <v/>
+      </c>
+      <c r="K21" s="53">
+        <f>D21*G21</f>
+        <v/>
+      </c>
+      <c r="L21" s="53">
+        <f>D21*H21</f>
+        <v/>
+      </c>
+      <c r="M21" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O21" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="53">
+        <f>M21*N21</f>
+        <v/>
+      </c>
+      <c r="S21" s="53">
+        <f>M21*O21</f>
+        <v/>
+      </c>
+      <c r="T21" s="53">
+        <f>M21*P21</f>
+        <v/>
+      </c>
+      <c r="U21" s="53">
+        <f>M21*Q21</f>
+        <v/>
+      </c>
+      <c r="V21" s="9" t="inlineStr">
+        <is>
+          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Grafana</t>
+        </is>
+      </c>
+      <c r="D22" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F22" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G22" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="53">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+      <c r="J22" s="53">
+        <f>D22*F22</f>
+        <v/>
+      </c>
+      <c r="K22" s="53">
+        <f>D22*G22</f>
+        <v/>
+      </c>
+      <c r="L22" s="53">
+        <f>D22*H22</f>
+        <v/>
+      </c>
+      <c r="M22" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O22" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P22" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="53">
+        <f>M22*N22</f>
+        <v/>
+      </c>
+      <c r="S22" s="53">
+        <f>M22*O22</f>
+        <v/>
+      </c>
+      <c r="T22" s="53">
+        <f>M22*P22</f>
+        <v/>
+      </c>
+      <c r="U22" s="53">
+        <f>M22*Q22</f>
+        <v/>
+      </c>
+      <c r="V22" s="9" t="inlineStr">
+        <is>
+          <t>Допущение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Loki</t>
+        </is>
+      </c>
+      <c r="D23" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="53">
+        <f>D23*E23</f>
+        <v/>
+      </c>
+      <c r="J23" s="53">
+        <f>D23*F23</f>
+        <v/>
+      </c>
+      <c r="K23" s="53">
+        <f>D23*G23</f>
+        <v/>
+      </c>
+      <c r="L23" s="53">
+        <f>D23*H23</f>
+        <v/>
+      </c>
+      <c r="M23" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O23" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="53">
+        <f>M23*N23</f>
+        <v/>
+      </c>
+      <c r="S23" s="53">
+        <f>M23*O23</f>
+        <v/>
+      </c>
+      <c r="T23" s="53">
+        <f>M23*P23</f>
+        <v/>
+      </c>
+      <c r="U23" s="53">
+        <f>M23*Q23</f>
+        <v/>
+      </c>
+      <c r="V23" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт из `Capacity_Report.html`: 0,2 ГБ / 30 суток на MVP, 1,7 ГБ на тираже (допущение 10 записей на запрос по 1 КБ); 20 ГиБ с запасом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Alertmanager</t>
+        </is>
+      </c>
+      <c r="D24" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G24" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="53">
+        <f>D24*E24</f>
+        <v/>
+      </c>
+      <c r="J24" s="53">
+        <f>D24*F24</f>
+        <v/>
+      </c>
+      <c r="K24" s="53">
+        <f>D24*G24</f>
+        <v/>
+      </c>
+      <c r="L24" s="53">
+        <f>D24*H24</f>
+        <v/>
+      </c>
+      <c r="M24" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O24" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P24" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="53">
+        <f>M24*N24</f>
+        <v/>
+      </c>
+      <c r="S24" s="53">
+        <f>M24*O24</f>
+        <v/>
+      </c>
+      <c r="T24" s="53">
+        <f>M24*P24</f>
+        <v/>
+      </c>
+      <c r="U24" s="53">
+        <f>M24*Q24</f>
+        <v/>
+      </c>
+      <c r="V24" s="9" t="inlineStr">
+        <is>
+          <t>Допущение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="50" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Qdrant</t>
+        </is>
+      </c>
+      <c r="D25" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="53">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+      <c r="J25" s="53">
+        <f>D25*F25</f>
+        <v/>
+      </c>
+      <c r="K25" s="53">
+        <f>D25*G25</f>
+        <v/>
+      </c>
+      <c r="L25" s="53">
+        <f>D25*H25</f>
+        <v/>
+      </c>
+      <c r="M25" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="53">
+        <f>M25*N25</f>
+        <v/>
+      </c>
+      <c r="S25" s="53">
+        <f>M25*O25</f>
+        <v/>
+      </c>
+      <c r="T25" s="53">
+        <f>M25*P25</f>
+        <v/>
+      </c>
+      <c r="U25" s="53">
+        <f>M25*Q25</f>
+        <v/>
+      </c>
+      <c r="V25" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ, с индексом ≈1 ГБ; во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Postgres (обращения, профиль, телеметрия, журнал диалогов)</t>
+        </is>
+      </c>
+      <c r="D26" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="53">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+      <c r="J26" s="53">
+        <f>D26*F26</f>
+        <v/>
+      </c>
+      <c r="K26" s="53">
+        <f>D26*G26</f>
+        <v/>
+      </c>
+      <c r="L26" s="53">
+        <f>D26*H26</f>
+        <v/>
+      </c>
+      <c r="M26" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" s="52" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="53">
+        <f>M26*N26</f>
+        <v/>
+      </c>
+      <c r="S26" s="53">
+        <f>M26*O26</f>
+        <v/>
+      </c>
+      <c r="T26" s="53">
+        <f>M26*P26</f>
+        <v/>
+      </c>
+      <c r="U26" s="53">
+        <f>M26*Q26</f>
+        <v/>
+      </c>
+      <c r="V26" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт данных за 90 суток по высокому сценарию: журнал диалогов 4 КБ × 12 500 диалогов в месяц = 150 МБ (MVP) и × 125 000 = 1,5 ГБ (тираж); профиль 24 МБ и 270 МБ (3 КБ на абонента — допущение); телеметрия ≤ 0,25 ГБ в год (2,4 ГБ с запасом ×10); обращения ≈30–300 МБ в год. Итого до 0,5 ГБ (MVP) и до 5 ГБ (тираж); диск с запасом на журнал и копии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="50" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Redis (квоты и сессии)</t>
+        </is>
+      </c>
+      <c r="D27" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F27" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G27" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="53">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+      <c r="J27" s="53">
+        <f>D27*F27</f>
+        <v/>
+      </c>
+      <c r="K27" s="53">
+        <f>D27*G27</f>
+        <v/>
+      </c>
+      <c r="L27" s="53">
+        <f>D27*H27</f>
+        <v/>
+      </c>
+      <c r="M27" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O27" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P27" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="53">
+        <f>M27*N27</f>
+        <v/>
+      </c>
+      <c r="S27" s="53">
+        <f>M27*O27</f>
+        <v/>
+      </c>
+      <c r="T27" s="53">
+        <f>M27*P27</f>
+        <v/>
+      </c>
+      <c r="U27" s="53">
+        <f>M27*Q27</f>
+        <v/>
+      </c>
+      <c r="V27" s="9" t="inlineStr">
+        <is>
+          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 800 одновременных сессий (1 запрос/с × 30 мин) × 3 КБ ≈ 5 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>MinIO (документы, копии, снимки)</t>
+        </is>
+      </c>
+      <c r="D28" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F28" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="52" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="53">
+        <f>D28*E28</f>
+        <v/>
+      </c>
+      <c r="J28" s="53">
+        <f>D28*F28</f>
+        <v/>
+      </c>
+      <c r="K28" s="53">
+        <f>D28*G28</f>
+        <v/>
+      </c>
+      <c r="L28" s="53">
+        <f>D28*H28</f>
+        <v/>
+      </c>
+      <c r="M28" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O28" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="52" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q28" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="53">
+        <f>M28*N28</f>
+        <v/>
+      </c>
+      <c r="S28" s="53">
+        <f>M28*O28</f>
+        <v/>
+      </c>
+      <c r="T28" s="53">
+        <f>M28*P28</f>
+        <v/>
+      </c>
+      <c r="U28" s="53">
+        <f>M28*Q28</f>
+        <v/>
+      </c>
+      <c r="V28" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт: готовые бланки ≈200 КБ (допущение) × 1 125 в месяц = 2,7 ГБ в год (MVP) и × 11 250 = 27 ГБ в год (тираж), хранение 3 года; копии Postgres за 7 суток до 35 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="50" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Эмбеддинги (BGE-M3, inference)</t>
+        </is>
+      </c>
+      <c r="D29" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="53">
+        <f>D29*E29</f>
+        <v/>
+      </c>
+      <c r="J29" s="53">
+        <f>D29*F29</f>
+        <v/>
+      </c>
+      <c r="K29" s="53">
+        <f>D29*G29</f>
+        <v/>
+      </c>
+      <c r="L29" s="53">
+        <f>D29*H29</f>
+        <v/>
+      </c>
+      <c r="M29" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="P29" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" s="53">
+        <f>M29*N29</f>
+        <v/>
+      </c>
+      <c r="S29" s="53">
+        <f>M29*O29</f>
+        <v/>
+      </c>
+      <c r="T29" s="53">
+        <f>M29*P29</f>
+        <v/>
+      </c>
+      <c r="U29" s="53">
+        <f>M29*Q29</f>
+        <v/>
+      </c>
+      <c r="V29" s="9" t="inlineStr">
+        <is>
+          <t>Замер: веса 4,25 ГБ (fp32). Допущение: в fp16 ≈2,3 ГБ + запас — ≈3 ГБ видеопамяти. Скорость на GPU не измерялась.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="50" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Реранкер (BGE-reranker-v2-m3, inference)</t>
+        </is>
+      </c>
+      <c r="D30" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I30" s="53">
+        <f>D30*E30</f>
+        <v/>
+      </c>
+      <c r="J30" s="53">
+        <f>D30*F30</f>
+        <v/>
+      </c>
+      <c r="K30" s="53">
+        <f>D30*G30</f>
+        <v/>
+      </c>
+      <c r="L30" s="53">
+        <f>D30*H30</f>
+        <v/>
+      </c>
+      <c r="M30" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R30" s="53">
+        <f>M30*N30</f>
+        <v/>
+      </c>
+      <c r="S30" s="53">
+        <f>M30*O30</f>
+        <v/>
+      </c>
+      <c r="T30" s="53">
+        <f>M30*P30</f>
+        <v/>
+      </c>
+      <c r="U30" s="53">
+        <f>M30*Q30</f>
+        <v/>
+      </c>
+      <c r="V30" s="9" t="inlineStr">
+        <is>
+          <t>Замер: веса 2,14 ГБ. Допущение: ≈1,5 ГБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>gpu-llm</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
+        </is>
+      </c>
+      <c r="D31" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="52" t="n">
+        <v>64</v>
+      </c>
+      <c r="G31" s="52" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="53">
+        <f>D31*E31</f>
+        <v/>
+      </c>
+      <c r="J31" s="53">
+        <f>D31*F31</f>
+        <v/>
+      </c>
+      <c r="K31" s="53">
+        <f>D31*G31</f>
+        <v/>
+      </c>
+      <c r="L31" s="53">
+        <f>D31*H31</f>
+        <v/>
+      </c>
+      <c r="M31" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="O31" s="52" t="n">
+        <v>64</v>
+      </c>
+      <c r="P31" s="52" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q31" s="52" t="n">
+        <v>40</v>
+      </c>
+      <c r="R31" s="53">
+        <f>M31*N31</f>
+        <v/>
+      </c>
+      <c r="S31" s="53">
+        <f>M31*O31</f>
+        <v/>
+      </c>
+      <c r="T31" s="53">
+        <f>M31*P31</f>
+        <v/>
+      </c>
+      <c r="U31" s="53">
+        <f>M31*Q31</f>
+        <v/>
+      </c>
+      <c r="V31" s="9" t="inlineStr">
+        <is>
+          <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>Итог по пулам узлов</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>Загрузка узла по запросам, не выше</t>
+        </is>
+      </c>
+      <c r="Q33" s="54" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Пул</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Класс узла</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>vCPU узла</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>ОЗУ узла, ГиБ</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Видеопамять узла, ГиБ</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Запас на потерю узла (1 — да)</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>MVP: vCPU</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>MVP: ОЗУ</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>MVP: видеопамять</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>MVP: узлов</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Тираж: vCPU</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Тираж: ОЗУ</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>Тираж: видеопамять</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>Тираж: узлов</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="55">
+        <f>SUMIF($B$12:$B$31,$B35,$I$12:$I$31)</f>
+        <v/>
+      </c>
+      <c r="I35" s="55">
+        <f>SUMIF($B$12:$B$31,$B35,$J$12:$J$31)</f>
+        <v/>
+      </c>
+      <c r="J35" s="55">
+        <f>SUMIF($B$12:$B$31,$B35,$L$12:$L$31)</f>
+        <v/>
+      </c>
+      <c r="K35" s="56">
+        <f>IF(H35=0,0,ROUNDUP(MAX(H35/($Q$33*$D35),I35/($Q$33*$E35),IF($F35&gt;0,J35/($Q$33*$F35),0)),0)+$G35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="55">
+        <f>SUMIF($B$12:$B$31,$B35,$R$12:$R$31)</f>
+        <v/>
+      </c>
+      <c r="M35" s="55">
+        <f>SUMIF($B$12:$B$31,$B35,$S$12:$S$31)</f>
+        <v/>
+      </c>
+      <c r="N35" s="55">
+        <f>SUMIF($B$12:$B$31,$B35,$U$12:$U$31)</f>
+        <v/>
+      </c>
+      <c r="O35" s="56">
+        <f>IF(L35=0,0,ROUNDUP(MAX(L35/($Q$33*$D35),M35/($Q$33*$E35),IF($F35&gt;0,N35/($Q$33*$F35),0)),0)+$G35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Пул данных (NVMe)</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="55">
+        <f>SUMIF($B$12:$B$31,$B36,$I$12:$I$31)</f>
+        <v/>
+      </c>
+      <c r="I36" s="55">
+        <f>SUMIF($B$12:$B$31,$B36,$J$12:$J$31)</f>
+        <v/>
+      </c>
+      <c r="J36" s="55">
+        <f>SUMIF($B$12:$B$31,$B36,$L$12:$L$31)</f>
+        <v/>
+      </c>
+      <c r="K36" s="56">
+        <f>IF(H36=0,0,ROUNDUP(MAX(H36/($Q$33*$D36),I36/($Q$33*$E36),IF($F36&gt;0,J36/($Q$33*$F36),0)),0)+$G36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="55">
+        <f>SUMIF($B$12:$B$31,$B36,$R$12:$R$31)</f>
+        <v/>
+      </c>
+      <c r="M36" s="55">
+        <f>SUMIF($B$12:$B$31,$B36,$S$12:$S$31)</f>
+        <v/>
+      </c>
+      <c r="N36" s="55">
+        <f>SUMIF($B$12:$B$31,$B36,$U$12:$U$31)</f>
+        <v/>
+      </c>
+      <c r="O36" s="56">
+        <f>IF(L36=0,0,ROUNDUP(MAX(L36/($Q$33*$D36),M36/($Q$33*$E36),IF($F36&gt;0,N36/($Q$33*$F36),0)),0)+$G36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>GPU-пул (эмбеддинги, реранкер)</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="55">
+        <f>SUMIF($B$12:$B$31,$B37,$I$12:$I$31)</f>
+        <v/>
+      </c>
+      <c r="I37" s="55">
+        <f>SUMIF($B$12:$B$31,$B37,$J$12:$J$31)</f>
+        <v/>
+      </c>
+      <c r="J37" s="55">
+        <f>SUMIF($B$12:$B$31,$B37,$L$12:$L$31)</f>
+        <v/>
+      </c>
+      <c r="K37" s="56">
+        <f>IF(H37=0,0,ROUNDUP(MAX(H37/($Q$33*$D37),I37/($Q$33*$E37),IF($F37&gt;0,J37/($Q$33*$F37),0)),0)+$G37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="55">
+        <f>SUMIF($B$12:$B$31,$B37,$R$12:$R$31)</f>
+        <v/>
+      </c>
+      <c r="M37" s="55">
+        <f>SUMIF($B$12:$B$31,$B37,$S$12:$S$31)</f>
+        <v/>
+      </c>
+      <c r="N37" s="55">
+        <f>SUMIF($B$12:$B$31,$B37,$U$12:$U$31)</f>
+        <v/>
+      </c>
+      <c r="O37" s="56">
+        <f>IF(L37=0,0,ROUNDUP(MAX(L37/($Q$33*$D37),M37/($Q$33*$E37),IF($F37&gt;0,N37/($Q$33*$F37),0)),0)+$G37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>gpu-llm</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>GPU-пул генерации (тираж)</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="55">
+        <f>SUMIF($B$12:$B$31,$B38,$I$12:$I$31)</f>
+        <v/>
+      </c>
+      <c r="I38" s="55">
+        <f>SUMIF($B$12:$B$31,$B38,$J$12:$J$31)</f>
+        <v/>
+      </c>
+      <c r="J38" s="55">
+        <f>SUMIF($B$12:$B$31,$B38,$L$12:$L$31)</f>
+        <v/>
+      </c>
+      <c r="K38" s="56">
+        <f>IF(H38=0,0,ROUNDUP(MAX(H38/($Q$33*$D38),I38/($Q$33*$E38),IF($F38&gt;0,J38/($Q$33*$F38),0)),0)+$G38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="55">
+        <f>SUMIF($B$12:$B$31,$B38,$R$12:$R$31)</f>
+        <v/>
+      </c>
+      <c r="M38" s="55">
+        <f>SUMIF($B$12:$B$31,$B38,$S$12:$S$31)</f>
+        <v/>
+      </c>
+      <c r="N38" s="55">
+        <f>SUMIF($B$12:$B$31,$B38,$U$12:$U$31)</f>
+        <v/>
+      </c>
+      <c r="O38" s="56">
+        <f>IF(L38=0,0,ROUNDUP(MAX(L38/($Q$33*$D38),M38/($Q$33*$E38),IF($F38&gt;0,N38/($Q$33*$F38),0)),0)+$G38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Итого узлов</t>
+        </is>
+      </c>
+      <c r="K39" s="57">
+        <f>SUM(K35:K38)</f>
+        <v/>
+      </c>
+      <c r="O39" s="57">
+        <f>SUM(O35:O38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Диск под тома, ГиБ</t>
+        </is>
+      </c>
+      <c r="K40" s="58">
+        <f>SUM($K$12:$K$31)</f>
+        <v/>
+      </c>
+      <c r="O40" s="58">
+        <f>SUM($T$12:$T$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); нагрузочный тест не проводился.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="C4:U4"/>
+    <mergeCell ref="C5:U5"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="C8:U8"/>
+    <mergeCell ref="C3:U3"/>
+    <mergeCell ref="C7:U7"/>
+    <mergeCell ref="C6:U6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Python, без модели на основном пути. Тема (путь ответа): подстроки и регулярные выражения — `TOPIC_MARKERS`, `TARIFF_PATTERNS`, `WATER_QUALITY_PATTERNS`, `TEMPLATE_PATTERNS`, `ACCOUNT_PATTERNS` в `app/agents/triage.py`. Тип обращения (регистрация): словарь ключевых слов `KEYWORDS` в `app/taxonomy.py`, слова взяты из 136 настоящих обращений (охват 75%, точность 65%). Когда правила молчат — запасной k-NN по эмбеддингам (косинусная близость к размеченным примерам `EXAMPLES` в `app/agents/topic_fallback.py` и `app/agents/inquiry_type_fallback.py`); эмбеддер — `multilingual-e5-small` на CPU, тот же, что у поиска (вторая модель не грузится). Запасной классификатор типа знает 7 из 16 типов. Все правила и слова по каждому типу и теме, их проработка и этап сведены в таблице `Inquiry_Types.xlsx`.</t>
+          <t>Python, без модели на основном пути. Тема (путь ответа): подстроки и регулярные выражения — `TOPIC_MARKERS`, `TARIFF_PATTERNS`, `WATER_QUALITY_PATTERNS`, `TEMPLATE_PATTERNS`, `ACCOUNT_PATTERNS` в `app/agents/triage.py`. Тип обращения (регистрация): словарь ключевых слов `KEYWORDS` в `app/taxonomy.py`, слова взяты из 136 настоящих обращений (на отложенной трети выборки охват 75%, точность 65%; выборка мала). Когда правила молчат — запасной k-NN по эмбеддингам (косинусная близость к размеченным примерам `EXAMPLES` в `app/agents/topic_fallback.py` и `app/agents/inquiry_type_fallback.py`); эмбеддер — `multilingual-e5-small` на CPU, тот же, что у поиска (вторая модель не грузится). Запасной классификатор типа знает 7 из 16 типов. Все правила и слова по каждому типу и теме, их проработка и этап сведены в таблице `Inquiry_Types.xlsx`.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Свой клиент на каждого провайдера отклонён: дублирование ради контроля, который LiteLLM уже даёт (100+ адаптеров, единый интерфейс, повторы и circuit breaker). Отдельный прокси-сервер LiteLLM на прототипе не взят: это второй процесс со своим портом и конфигурацией, на машине с 15 ГБ памяти тесно; библиотека принимает тот же список моделей и цепочки запасных провайдеров, формат файла совместим с прокси. Смена провайдера — правка переменной `LLM_PROVIDER`, код не меняется: это условие ADR-200 (минимум два провайдера с автопереключением). Весь нужный инструментарий (LiteLLM, Presidio, sentence-transformers) существует в Python — тот же язык, что у Backend. Зарубежные провайдеры исключены: 152-ФЗ.</t>
+          <t>Свой клиент на каждого провайдера отклонён: дублирование ради контроля, который LiteLLM уже даёт (100+ адаптеров, единый интерфейс, повторы и circuit breaker). Отдельный прокси-сервер LiteLLM на прототипе не взят: это второй процесс со своим портом и конфигурацией, память отдельного процесса LiteLLM не измерялась (на машине 15 ГБ, контейнер Backend занимает 1,32 ГиБ); библиотека принимает тот же список моделей и цепочки запасных провайдеров, формат файла совместим с прокси. Смена провайдера — правка переменной `LLM_PROVIDER`, код не меняется: это условие ADR-200 (минимум два провайдера с автопереключением). Весь нужный инструментарий (LiteLLM, Presidio, sentence-transformers) существует в Python — тот же язык, что у Backend. Зарубежные провайдеры исключены: 152-ФЗ.</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Presidio + собственные распознаватели выбраны против «только регулярных выражений» (не находят ФИО), русского NER вроде Natasha (закрывает только ФИО) и внешнего сервиса (данные уходят за периметр, запрещено). Базовый набор Presidio один не годился: лицевой счёт определялся как телефон, одна почта получала три метки.</t>
+          <t>Presidio + собственные распознаватели выбраны против «только регулярных выражений» (не находят ФИО), русского NER вроде Natasha (по документации — имена и адреса, но не СНИЛС, ИНН, лицевой счёт, телефон, почту; не проверялась) и внешнего сервиса (данные уходят за периметр, запрещено). Базовый набор Presidio один не годился: лицевой счёт определялся как телефон, одна почта получала три метки.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Проверки на потоке — регулярные выражения (бюджет менее 50 мс на кусок; ML-модель токсичности и LLM-судья в бюджет не укладываются, внешний сервис уносит данные за периметр). Судья не может совпадать с отвечающей моделью: при совпадении оценка пропускается и это фиксируется.</t>
+          <t>Проверки на потоке — регулярные выражения (бюджет менее 50 мс на кусок; ML-модель токсичности не измерялась (на CPU есть риск), LLM-судья работает секундами — у YandexGPT первый кусок приходит за 0,3–21 с (19 вызовов), внешний сервис уносит данные за периметр). Судья не может совпадать с отвечающей моделью: при совпадении оценка пропускается и это фиксируется.</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Сравнение моделей проведено в ADR-300, раздел 2 (задержка и размер — замер `scripts/measure_search_models.py`); замер поиска на прототипе — `golden_set/measurement.json` (e5-small: 20 из 20 на вопросах корпуса, 12 из 30 на первом месте и 23 из 30 в первой тройке на живых формулировках). Почему BGE-M3 для MVP: многоязычная, длинные тексты, общий каркас с реранкером BGE-reranker-v2-m3 — это свойства модели, а не замер на своих данных; подробно и с перечнем кандидатов — ADR-300, «Почему BGE-M3 — кандидат для MVP и что будет сравниваться». Кандидаты: BGE-M3: 4,25 ГБ, 210–300 мс на CPU (в 2–3 раза выше бюджета; на GPU не измерялась), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
+          <t>Сравнение моделей проведено в ADR-300, раздел 2 (задержка и размер — замер `scripts/measure_search_models.py`); замер поиска на прототипе — `golden_set/measurement.json` (e5-small: 20 из 20 на вопросах корпуса, 12 из 30 на первом месте и 23 из 30 в первой тройке на живых формулировках). Почему BGE-M3 для MVP: многоязычная, длинные тексты, общий каркас с реранкером BGE-reranker-v2-m3 — это свойства модели, а не замер на своих данных; подробно и с перечнем кандидатов — ADR-300, «Почему BGE-M3 — кандидат для MVP и что будет сравниваться». Кандидаты: BGE-M3: 2,14 ГиБ (fp32; прежние 4,25 ГБ — две копии весов в кэше), 210–300 мс на CPU (в 2–3 раза выше бюджета; на GPU не измерялась), качество на русском не проверено на эталонном наборе. GigaChat Embeddings — только для офлайн-индексации: запрос минует обезличивание.</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Ответ читает готовый агрегат по индексу, без обращения к первичным системам; тот же примитив, что уже используется для резервного копирования.</t>
+          <t>Ответ читает готовый агрегат по индексу, без обращения к первичным системам; планировщик по расписанию (Kubernetes CronJob), предусмотренный в схеме развёртывания (кластера пока нет).</t>
         </is>
       </c>
       <c r="M13" s="22" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Compose на нескольких хостах не переживает отказ узла; Docker Swarm — мёртвая экосистема. Для одного разработчика и одного хоста Kubernetes избыточен.</t>
+          <t>Compose на нескольких хостах не переживает отказ узла; Docker Swarm — по общим сведениям, развитие замедлено (не проверялось). Для одного разработчика и одного хоста Kubernetes избыточен.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (разрыв размеров, русский слабее) и открытых весов GigaChat (менее зрелый инструментарий).</t>
+          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -8177,13 +8177,13 @@
         <v>1</v>
       </c>
       <c r="F29" s="52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G29" s="52" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" s="53">
         <f>D29*E29</f>
@@ -8208,13 +8208,13 @@
         <v>1</v>
       </c>
       <c r="O29" s="52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P29" s="52" t="n">
         <v>5</v>
       </c>
       <c r="Q29" s="52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R29" s="53">
         <f>M29*N29</f>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="V29" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 4,25 ГБ (fp32). Допущение: в fp16 ≈2,3 ГБ + запас — ≈3 ГБ видеопамяти. Скорость на GPU не измерялась.</t>
+          <t>Замер: веса 2,14 ГиБ (fp32; прежние 4,25 ГБ — две копии в кэше). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГБ. Допущение: ≈1,5 ГБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники и допущения" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объём по контейнерам" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sizing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прогноз стоимости" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$37</definedName>
@@ -23,9 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0#"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0#"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -221,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -372,6 +375,21 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2051,16 +2069,32 @@
           <t>Оценка автора</t>
         </is>
       </c>
-      <c r="P15" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q15" s="15" t="n"/>
-      <c r="R15" s="15" t="n"/>
-      <c r="S15" s="16" t="n"/>
-      <c r="T15" s="16" t="n"/>
-      <c r="U15" s="15" t="n"/>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>Срок хранения подробных событий 12 месяцев, сводная таблица по дням и секции по месяцам; замер на 4 млн строк.</t>
+        </is>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>Postgres: секционирование по месяцам, сводная таблица (материализованное представление или задание по расписанию).</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>На 12 млн строк агрегат по всей таблице занимает 39 с (замер); без ограничения срока хранения аналитика замедляется.</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" s="13" t="inlineStr">
+        <is>
+          <t>Оценка автора</t>
+        </is>
+      </c>
       <c r="V15" s="9" t="inlineStr">
         <is>
           <t>ADR-100; ADR-200</t>
@@ -3469,7 +3503,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Есть прогнозная модель, не смета: числа не утверждены владельцем (открытый P0).</t>
+          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 234–101 280 ₽ в месяц, на тираже 3 305 ₽–1,07 млн ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -3484,12 +3518,12 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>Разброс оценок нагрузки — 25-кратный; без статистики ЛК и колл-центра смета остаётся диапазоном.</t>
+          <t>Разброс стоимости токенов на MVP — ×82 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой.</t>
+          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой. Первый пересчёт сметы по данным обращений и ЛК (3–5 чел-дн, после получения данных) и повторный по пилоту (1–2 чел-дн): подставить данные в лист «Прогноз стоимости», пересчитать нагрузку, стоимость и sizing, обновить отчёт о мощности, ADR-500 и матрицу.</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -3503,10 +3537,10 @@
         </is>
       </c>
       <c r="M32" s="25" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="N32" s="17" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O32" s="18" t="inlineStr">
         <is>
@@ -4045,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4375,10 +4409,10 @@
         </is>
       </c>
       <c r="B15" s="34" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="C15" s="34" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D15" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$37)</f>
@@ -4394,7 +4428,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>1,5–2 недели (смета 1–2 дня, NFR 2–3 дня, допущения нагрузки 1 неделя)</t>
+          <t>≈2,5–3,5 недели: смета 1–2 дня, NFR 2–3 дня, допущения нагрузки 1 неделя, пересчёт по данным 3–5 + по пилоту 1–2 чел-дн</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4640,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>ADR-600 называет итог ≈19–29 недель (≈95–145 чел-дн); сумма блоков 95,5–143,5 — округление в самом ADR-600</t>
+          <t>ADR-600 называет итог ≈20–30 недель (≈100–150 чел-дн); сумма блоков 99,5–150,5 — округление в самом ADR-600</t>
         </is>
       </c>
     </row>
@@ -4667,14 +4701,14 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>≈162 ₽/мес при базовом сценарии (10% визитов, 30% до модели) — ≈1 886 ₽/мес при максимальном (50%, 70%), при измеренных 401 токене на запрос (19 вызовов). При 3 500 токенов на запрос (допущение отчёта о мощности, не проверено) — ≈1 400–16 500 ₽/мес. Спрос из отчёта о мощности при 3 500 токенов — ≈40 000 ₽/мес. Допущения о спросе данными водоканала не подтверждены</t>
+          <t>Минимум — 1 234 ₽/мес (7% абонентов в чате, 30% вопросов до модели, 401 токен на запрос, судья раз в неделю); максимум — 101 280 ₽/мес (35%, 70%, 3 500 токенов, судья каждую ночь). Допущения о спросе данными водоканала не подтверждены; разброс ×82</t>
         </is>
       </c>
       <c r="D26" s="42" t="n">
-        <v>162</v>
+        <v>1234</v>
       </c>
       <c r="E26" s="42" t="n">
-        <v>16464</v>
+        <v>101280</v>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
@@ -4683,36 +4717,40 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>ADR-500; Capacity_Report</t>
+          <t>Capacity_Report; лист «Прогноз стоимости»</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Тираж</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>GPU-сервер под эмбеддинги и реранкер</t>
+          <t>Токены генерации и судьи качества (тариф YandexGPT Pro 0,8 ₽ за 1000 токенов)</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Не оценён отдельной строкой сметы; скорость на GPU не измерялась</t>
-        </is>
-      </c>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="42" t="n"/>
+          <t>Минимум — 3 305 ₽/мес, максимум — 1,07 млн ₽/мес (0,66 вопроса/с в пике); при собственной модели заменяется CAPEX на карту</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E27" s="42" t="n">
+        <v>1065600</v>
+      </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>₽</t>
+          <t>₽/мес</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>ADR-500 (открытый пункт)</t>
+          <t>Capacity_Report; лист «Прогноз стоимости»</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4762,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
+          <t>GPU-сервер под эмбеддинги и реранкер</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Не оценены</t>
+          <t>Не оценён отдельной строкой сметы; скорость на GPU не измерялась</t>
         </is>
       </c>
       <c r="D28" s="42" t="n"/>
@@ -4748,25 +4786,21 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Карта A100 80 ГБ (покупка)</t>
+          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
-        </is>
-      </c>
-      <c r="D29" s="42" t="n">
-        <v>927000</v>
-      </c>
-      <c r="E29" s="42" t="n">
-        <v>2368080</v>
-      </c>
+          <t>Не оценены</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
       <c r="F29" s="9" t="inlineStr">
         <is>
           <t>₽</t>
@@ -4774,7 +4808,7 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
@@ -4786,29 +4820,62 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
+          <t>Карта A100 80 ГБ (покупка)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="n">
+        <v>927000</v>
+      </c>
+      <c r="E30" s="42" t="n">
+        <v>2368080</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>₽</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>ADR-500</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Тираж</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
           <t>Сервер-хост, электричество, размещение, обслуживание GPU</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Не оценены</t>
         </is>
       </c>
-      <c r="D30" s="42" t="n"/>
-      <c r="E30" s="42" t="n"/>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>₽</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="33" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>Все суммы в ₽ — прогнозная модель, не смета: CAPEX/OPEX не утверждены владельцем (ADR-500). Закупка GPU — недели или месяцы лид-тайма, не разработка.</t>
         </is>
@@ -4831,7 +4898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4917,7 +4984,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1">
+    <row r="7" ht="105" customHeight="1">
       <c r="A7" s="46" t="inlineStr">
         <is>
           <t>•</t>
@@ -4930,7 +4997,7 @@
       </c>
       <c r="C7" s="48" t="inlineStr">
         <is>
-          <t>MVP — 8 000 абонентов; тираж — 90 000. Токены и стоимость GPU — из ADR-500 (прогнозная модель). Официальная смета не утверждена, GPU-сервер под эмбеддинги и оборудование кластера отдельной строкой не оценены. Допущения о спросе данными водоканала не подтверждены; в ADR-500 и в отчёте о мощности они разные, стоимость токенов зависит от них на порядок. Токенов на запрос: измерено 401 (19 вызовов, фрагменты FAQ до 300 знаков), допущение отчёта — 3 500.</t>
+          <t>MVP — 8 000 абонентов; тираж — 90 000. Прогноз токенов и стоимости — минимум и максимум (лист «Прогноз стоимости», `Capacity_Report.html`): учтено, что не все абоненты приходят в чат (7–35%) и только 30–70% вопросов доходит до модели. Цена одна — публичный тариф YandexGPT Pro 0,8 ₽ за 1000 токенов из ADR-500 (не проверялся; тариф GigaChat Pro неизвестен). Цен на серверы и GPU нет. Допущения о спросе данными водоканала не подтверждены; токенов на запрос: измерено 401 (19 вызовов, фрагменты FAQ до 300 знаков), допущение максимума — 3 500. Пересчёт после получения данных — 3–5 чел-дн, по пилоту — 1–2 (блок P0 ADR-600).</t>
         </is>
       </c>
     </row>
@@ -5377,28 +5444,28 @@
     </row>
     <row r="27">
       <c r="A27" s="9">
-        <f>'Матрица'!A16</f>
+        <f>'Матрица'!A15</f>
         <v/>
       </c>
       <c r="B27" s="9">
-        <f>'Матрица'!C16</f>
+        <f>'Матрица'!C15</f>
         <v/>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Тираж</t>
         </is>
       </c>
       <c r="D27" s="34">
-        <f>'Матрица'!M16</f>
+        <f>'Матрица'!S15</f>
         <v/>
       </c>
       <c r="E27" s="34">
-        <f>'Матрица'!N16</f>
+        <f>'Матрица'!T15</f>
         <v/>
       </c>
       <c r="F27" s="13">
-        <f>'Матрица'!O16</f>
+        <f>'Матрица'!U15</f>
         <v/>
       </c>
     </row>
@@ -5413,56 +5480,56 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="D28" s="34">
-        <f>'Матрица'!S16</f>
+        <f>'Матрица'!M16</f>
         <v/>
       </c>
       <c r="E28" s="34">
-        <f>'Матрица'!T16</f>
+        <f>'Матрица'!N16</f>
         <v/>
       </c>
       <c r="F28" s="13">
-        <f>'Матрица'!U16</f>
+        <f>'Матрица'!O16</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9">
-        <f>'Матрица'!A17</f>
+        <f>'Матрица'!A16</f>
         <v/>
       </c>
       <c r="B29" s="9">
-        <f>'Матрица'!C17</f>
+        <f>'Матрица'!C16</f>
         <v/>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Тираж</t>
         </is>
       </c>
       <c r="D29" s="34">
-        <f>'Матрица'!M17</f>
+        <f>'Матрица'!S16</f>
         <v/>
       </c>
       <c r="E29" s="34">
-        <f>'Матрица'!N17</f>
-        <v/>
-      </c>
-      <c r="F29" s="18">
-        <f>'Матрица'!O17</f>
+        <f>'Матрица'!T16</f>
+        <v/>
+      </c>
+      <c r="F29" s="13">
+        <f>'Матрица'!U16</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9">
-        <f>'Матрица'!A18</f>
+        <f>'Матрица'!A17</f>
         <v/>
       </c>
       <c r="B30" s="9">
-        <f>'Матрица'!C18</f>
+        <f>'Матрица'!C17</f>
         <v/>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -5471,25 +5538,25 @@
         </is>
       </c>
       <c r="D30" s="34">
-        <f>'Матрица'!M18</f>
+        <f>'Матрица'!M17</f>
         <v/>
       </c>
       <c r="E30" s="34">
-        <f>'Матрица'!N18</f>
+        <f>'Матрица'!N17</f>
         <v/>
       </c>
       <c r="F30" s="18">
-        <f>'Матрица'!O18</f>
+        <f>'Матрица'!O17</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9">
-        <f>'Матрица'!A19</f>
+        <f>'Матрица'!A18</f>
         <v/>
       </c>
       <c r="B31" s="9">
-        <f>'Матрица'!C19</f>
+        <f>'Матрица'!C18</f>
         <v/>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -5498,25 +5565,25 @@
         </is>
       </c>
       <c r="D31" s="34">
-        <f>'Матрица'!M19</f>
+        <f>'Матрица'!M18</f>
         <v/>
       </c>
       <c r="E31" s="34">
-        <f>'Матрица'!N19</f>
+        <f>'Матрица'!N18</f>
         <v/>
       </c>
       <c r="F31" s="18">
-        <f>'Матрица'!O19</f>
+        <f>'Матрица'!O18</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9">
-        <f>'Матрица'!A20</f>
+        <f>'Матрица'!A19</f>
         <v/>
       </c>
       <c r="B32" s="9">
-        <f>'Матрица'!C20</f>
+        <f>'Матрица'!C19</f>
         <v/>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -5525,25 +5592,25 @@
         </is>
       </c>
       <c r="D32" s="34">
-        <f>'Матрица'!M20</f>
+        <f>'Матрица'!M19</f>
         <v/>
       </c>
       <c r="E32" s="34">
-        <f>'Матрица'!N20</f>
+        <f>'Матрица'!N19</f>
         <v/>
       </c>
       <c r="F32" s="18">
-        <f>'Матрица'!O20</f>
+        <f>'Матрица'!O19</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9">
-        <f>'Матрица'!A21</f>
+        <f>'Матрица'!A20</f>
         <v/>
       </c>
       <c r="B33" s="9">
-        <f>'Матрица'!C21</f>
+        <f>'Матрица'!C20</f>
         <v/>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -5552,25 +5619,25 @@
         </is>
       </c>
       <c r="D33" s="34">
-        <f>'Матрица'!M21</f>
+        <f>'Матрица'!M20</f>
         <v/>
       </c>
       <c r="E33" s="34">
-        <f>'Матрица'!N21</f>
-        <v/>
-      </c>
-      <c r="F33" s="13">
-        <f>'Матрица'!O21</f>
+        <f>'Матрица'!N20</f>
+        <v/>
+      </c>
+      <c r="F33" s="18">
+        <f>'Матрица'!O20</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9">
-        <f>'Матрица'!A22</f>
+        <f>'Матрица'!A21</f>
         <v/>
       </c>
       <c r="B34" s="9">
-        <f>'Матрица'!C22</f>
+        <f>'Матрица'!C21</f>
         <v/>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -5579,25 +5646,25 @@
         </is>
       </c>
       <c r="D34" s="34">
-        <f>'Матрица'!M22</f>
+        <f>'Матрица'!M21</f>
         <v/>
       </c>
       <c r="E34" s="34">
-        <f>'Матрица'!N22</f>
+        <f>'Матрица'!N21</f>
         <v/>
       </c>
       <c r="F34" s="13">
-        <f>'Матрица'!O22</f>
+        <f>'Матрица'!O21</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9">
-        <f>'Матрица'!A23</f>
+        <f>'Матрица'!A22</f>
         <v/>
       </c>
       <c r="B35" s="9">
-        <f>'Матрица'!C23</f>
+        <f>'Матрица'!C22</f>
         <v/>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -5606,25 +5673,25 @@
         </is>
       </c>
       <c r="D35" s="34">
-        <f>'Матрица'!M23</f>
+        <f>'Матрица'!M22</f>
         <v/>
       </c>
       <c r="E35" s="34">
-        <f>'Матрица'!N23</f>
+        <f>'Матрица'!N22</f>
         <v/>
       </c>
       <c r="F35" s="13">
-        <f>'Матрица'!O23</f>
+        <f>'Матрица'!O22</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9">
-        <f>'Матрица'!A25</f>
+        <f>'Матрица'!A23</f>
         <v/>
       </c>
       <c r="B36" s="9">
-        <f>'Матрица'!C25</f>
+        <f>'Матрица'!C23</f>
         <v/>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -5633,25 +5700,25 @@
         </is>
       </c>
       <c r="D36" s="34">
-        <f>'Матрица'!M25</f>
+        <f>'Матрица'!M23</f>
         <v/>
       </c>
       <c r="E36" s="34">
-        <f>'Матрица'!N25</f>
-        <v/>
-      </c>
-      <c r="F36" s="18">
-        <f>'Матрица'!O25</f>
+        <f>'Матрица'!N23</f>
+        <v/>
+      </c>
+      <c r="F36" s="13">
+        <f>'Матрица'!O23</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9">
-        <f>'Матрица'!A32</f>
+        <f>'Матрица'!A25</f>
         <v/>
       </c>
       <c r="B37" s="9">
-        <f>'Матрица'!C32</f>
+        <f>'Матрица'!C25</f>
         <v/>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -5660,25 +5727,25 @@
         </is>
       </c>
       <c r="D37" s="34">
-        <f>'Матрица'!M32</f>
+        <f>'Матрица'!M25</f>
         <v/>
       </c>
       <c r="E37" s="34">
-        <f>'Матрица'!N32</f>
+        <f>'Матрица'!N25</f>
         <v/>
       </c>
       <c r="F37" s="18">
-        <f>'Матрица'!O32</f>
+        <f>'Матрица'!O25</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <f>'Матрица'!A33</f>
+        <f>'Матрица'!A32</f>
         <v/>
       </c>
       <c r="B38" s="9">
-        <f>'Матрица'!C33</f>
+        <f>'Матрица'!C32</f>
         <v/>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -5687,25 +5754,25 @@
         </is>
       </c>
       <c r="D38" s="34">
-        <f>'Матрица'!M33</f>
+        <f>'Матрица'!M32</f>
         <v/>
       </c>
       <c r="E38" s="34">
-        <f>'Матрица'!N33</f>
+        <f>'Матрица'!N32</f>
         <v/>
       </c>
       <c r="F38" s="18">
-        <f>'Матрица'!O33</f>
+        <f>'Матрица'!O32</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9">
-        <f>'Матрица'!A34</f>
+        <f>'Матрица'!A33</f>
         <v/>
       </c>
       <c r="B39" s="9">
-        <f>'Матрица'!C34</f>
+        <f>'Матрица'!C33</f>
         <v/>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -5714,25 +5781,25 @@
         </is>
       </c>
       <c r="D39" s="34">
-        <f>'Матрица'!M34</f>
+        <f>'Матрица'!M33</f>
         <v/>
       </c>
       <c r="E39" s="34">
-        <f>'Матрица'!N34</f>
+        <f>'Матрица'!N33</f>
         <v/>
       </c>
       <c r="F39" s="18">
-        <f>'Матрица'!O34</f>
+        <f>'Матрица'!O33</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9">
-        <f>'Матрица'!A36</f>
+        <f>'Матрица'!A34</f>
         <v/>
       </c>
       <c r="B40" s="9">
-        <f>'Матрица'!C36</f>
+        <f>'Матрица'!C34</f>
         <v/>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -5741,143 +5808,170 @@
         </is>
       </c>
       <c r="D40" s="34">
-        <f>'Матрица'!M36</f>
+        <f>'Матрица'!M34</f>
         <v/>
       </c>
       <c r="E40" s="34">
-        <f>'Матрица'!N36</f>
+        <f>'Матрица'!N34</f>
         <v/>
       </c>
       <c r="F40" s="18">
-        <f>'Матрица'!O36</f>
+        <f>'Матрица'!O34</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9">
+        <f>'Матрица'!A36</f>
+        <v/>
+      </c>
+      <c r="B41" s="9">
+        <f>'Матрица'!C36</f>
+        <v/>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D41" s="34">
+        <f>'Матрица'!M36</f>
+        <v/>
+      </c>
+      <c r="E41" s="34">
+        <f>'Матрица'!N36</f>
+        <v/>
+      </c>
+      <c r="F41" s="18">
+        <f>'Матрица'!O36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9">
         <f>'Матрица'!A37</f>
         <v/>
       </c>
-      <c r="B41" s="9">
+      <c r="B42" s="9">
         <f>'Матрица'!C37</f>
         <v/>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="D41" s="34">
+      <c r="D42" s="34">
         <f>'Матрица'!M37</f>
         <v/>
       </c>
-      <c r="E41" s="34">
+      <c r="E42" s="34">
         <f>'Матрица'!N37</f>
         <v/>
       </c>
-      <c r="F41" s="18">
+      <c r="F42" s="18">
         <f>'Матрица'!O37</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="43" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -5885,6 +5979,7 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C52:F52"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C47:F47"/>
     <mergeCell ref="C45:F45"/>
@@ -5900,7 +5995,6 @@
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C50:F50"/>
-    <mergeCell ref="C44:F44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5934,7 +6028,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="49" t="inlineStr">
         <is>
-          <t>Нагрузка из `Capacity_Report.html` (допущения A1–A5, данных водоканала нет): MVP (10 тыс. абонентов) — базовый сценарий 18 000 запросов в месяц, пик 0,025 запроса/с, одновременно 0,08; высокий — 75 000, 0,10 запроса/с, 0,31. Тираж (100 тыс.) — базовый 180 000, 0,25 запроса/с, 0,75; высокий 750 000, 1,04 запроса/с, 3,12. Сценарии рассчитаны под 10 и 100 тысяч абонентов; в ADR-500 те же контуры — 8 000 и 90 000.</t>
+          <t>Нагрузка из модели `Capacity_Report.html` (лист «Прогноз стоимости», допущения спроса данными водоканала не подтверждены): MVP (8 000 абонентов) — 1 680–42 000 вопросов в месяц, пик 0,002–0,058 запроса/с, одновременно 0,007–0,17; тираж (90 000) — 18 900–472 500 вопросов, пик 0,026–0,656 запроса/с, одновременно 0,08–1,97 (минимум–максимум). Сценарии рассчитаны под 10 и 100 тысяч абонентов; в ADR-500 те же контуры — 8 000 и 90 000.</t>
         </is>
       </c>
     </row>
@@ -5970,7 +6064,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="50" t="n">
         <v>1</v>
       </c>
@@ -5986,7 +6080,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Отдельного объёма нет: статические файлы, нагрузка — общая (см. Backend). Одновременно до 0,3 запроса на MVP и до 3 на тираже (расчёт).</t>
+          <t>Отдельного объёма нет: статические файлы, нагрузка — общая (см. Backend). Одновременно до 0,17 запроса на MVP и до 2 на тираже (максимум прогноза).</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -6120,7 +6214,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="50" t="n">
         <v>6</v>
       </c>
@@ -6136,7 +6230,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Судья: 39 млн токенов в месяц на MVP и 120 млн на тираже (30 млн — ночной прогон Golden Set, остальное — 5% выборка трафика); допущение: 5 вызовов судьи по ≈2 000 токенов на образец.</t>
+          <t>Судья: 1,3–23,7 млн токенов в месяц на MVP и 1,9–174 млн на тираже (эталонный набор из 30 вопросов раз в неделю или каждую ночь плюс 1–5% выборка трафика); допущение: 5 вызовов судьи по ≈2 000 токенов на образец, не измерено.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -6146,11 +6240,11 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Capacity_Report, раздел 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Capacity_Report, лист «Прогноз стоимости»</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1">
       <c r="A11" s="50" t="n">
         <v>7</v>
       </c>
@@ -6166,7 +6260,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Токенов на запрос: измерено 401 (19 вызовов, фрагменты FAQ до 300 знаков), допущение отчёта — 3 500. Стоимость токенов на MVP — ≈160–16 500 ₽/мес по ADR-500, до ≈40 000 ₽/мес при спросе из отчёта. Агент Этапа 2 добавляет около +20% токенов.</t>
+          <t>Токенов на запрос: измерено 401 (19 вызовов, фрагменты FAQ до 300 знаков), допущение максимума — 3 500. Стоимость токенов (генерация и судья) — 1 234–101 280 ₽ в месяц на MVP и 3 305 ₽–1,07 млн ₽ на тираже (минимум–максимум); до модели доходит 30–70% вопросов. Агент Этапа 2 добавит до 44 800 ₽ (MVP) и 504 000 ₽ (тираж) в месяц в максимуме.</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -6226,12 +6320,12 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Одно переранжирование 20 кандидатов на вопрос. На CPU 7,2 с (замер); загрузка GPU ≈0,1% на MVP и ≈1% на тираже — расчёт, скорость на GPU не измерялась.</t>
+          <t>Одно переранжирование 20 кандидатов на вопрос (до 0,058 вопроса/с на MVP и 0,656 на тираже). На CPU 7,2 с (замер); загрузка GPU не оценивается: скорость на GPU не измерялась.</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Расчёт; GPU не измерялся</t>
+          <t>Замер на CPU; GPU не измерялся</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -6300,7 +6394,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="50" t="n">
         <v>12</v>
       </c>
@@ -6316,7 +6410,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Сессия живёт 30 минут, одновременно до 0,3 запроса на MVP и до 3 на тираже; замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход; до 1 800 одновременных сессий ≈5 МБ. Выбрано: 1 экземпляр на MVP, 2 на тираже, 0,25 ГиБ (лист «Sizing»).</t>
+          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут; до 1 200 одновременных сессий ≈4 МБ. Выбрано: 1 экземпляр на MVP, 2 на тираже, 0,25 ГиБ (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -6330,7 +6424,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="90" customHeight="1">
+    <row r="17" ht="120" customHeight="1">
       <c r="A17" s="50" t="n">
         <v>13</v>
       </c>
@@ -6346,7 +6440,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Телеметрия: 6 000–70 600 строк в год на MVP, 68 000–794 000 на тираже (≈2–245 МБ в год; замер 2 млн строк — 589 МБ). Журнал диалогов при сроке хранения 90 суток (выбрано) — до 0,15 ГБ на MVP и 1,5 ГБ на тираже (4 КБ на диалог, высокий сценарий). Итого до 0,5 ГБ на MVP и до 5 ГБ на тираже, том 20 и 50 ГиБ (лист «Sizing»). Число обращений в месяц принято равным диалогам с записью (допущение A6).</t>
+          <t>События использования: 6 048–352 800 строк в год на MVP и 68 040–3,97 млн на тираже (≈2–109 МБ и 21 МБ–1,2 ГБ в год; замер 2 млн строк — 589 МБ). Журнал диалогов при сроке хранения 90 суток (выбрано) — до 0,08 ГБ на MVP и 0,94 ГБ на тираже (4 КБ на диалог, максимум прогноза). Подробные события хранятся 12 месяцев (замер: 12 млн строк дают агрегат по всей таблице 39 с). Итого до 0,4 ГБ на MVP и до 4 ГБ на тираже, том 20 и 50 ГиБ (лист «Sizing»). Число обращений в месяц принято равным диалогам с записью.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -6390,7 +6484,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="90" customHeight="1">
+    <row r="19" ht="75" customHeight="1">
       <c r="A19" s="50" t="n">
         <v>15</v>
       </c>
@@ -6406,7 +6500,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Допущение A6: 25% диалогов ведут к записи — 1 125 диалогов в месяц на MVP, 11 250 на тираже (базовый сценарий); надбавка токенов ≈12 и ≈124 млн в месяц. Хранилище готовых документов (MinIO): ≈200 КБ на бланк (допущение) × 1 125 в месяц — 2,7 ГБ в год на MVP, 27 ГБ в год на тираже; том MinIO 100 и 200 ГиБ с копиями и документами базы знаний (лист «Sizing»).</t>
+          <t>Допущение A6: 15–40% диалогов ведут к записи — до 2 800 диалогов в месяц на MVP и 31 500 на тираже; надбавка токенов до ≈56 и ≈630 млн в месяц. Хранилище готовых документов (MinIO): ≈200 КБ на бланк (допущение) — до 6,7 ГБ в год на MVP и 76 ГБ в год на тираже; том MinIO 100 и 400 ГиБ с копиями и документами базы знаний (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -6436,7 +6530,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing»): MVP — 6 узлов (3 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ, 1 GPU-узел с видеокартой 24 ГБ), тираж — 8 (4 общих, 2 данных, 1 GPU, 1 узел под собственную модель с A100 80 ГБ). Диск под тома ≈176 ГиБ на MVP и ≈467 ГиБ на тираже. Стоимость серверов не оценена.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing»): MVP — 6 узлов (3 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ, 1 GPU-узел с видеокартой 24 ГБ), тираж — 8 (4 общих, 2 данных, 1 GPU, 1 узел под собственную модель с A100 80 ГБ). Диск под тома ≈176 ГиБ на MVP и ≈667 ГиБ на тираже. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -6466,7 +6560,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Loki: ≈0,2 ГБ за 30 дней на MVP, ≈1,7 ГБ на тираже (допущение: 10 записей на запрос по ≈1 КБ). Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
+          <t>Loki: 0,02–0,42 ГБ за 30 суток на MVP и 0,19–4,7 ГБ на тираже (допущение: 10 записей на вопрос по ≈1 КБ). Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -6574,7 +6668,7 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Пик MVP — 0,1 запроса/с, тираж — 1 запрос/с (высокий сценарий `Capacity_Report.html`, пересчитанный на 8 000 и 90 000 абонентов и округлённый вверх); одновременно 0,3 запроса на MVP и 3 на тираже (время ответа 3 с). До модели доходит 70% запросов (верхняя оценка ADR-500).</t>
+          <t>Расчётный пик — 0,1 запроса/с на MVP и 1 запрос/с на тираже; это выше максимума прогноза `Capacity_Report.html` (0,058 и 0,656 запроса/с), одновременно до 0,17 и 1,97 запроса (время ответа 3 с). До модели доходит 70% запросов (максимум прогноза).</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6680,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Путь без модели — 8,5 мс на запрос (замер: один процесс отдаёт 117 запросов/с). Путь с моделью — 0,9 с на ответ в 800 знаков (эмбеддинг 36 мс + обезличивание + проверка ответа на потоке 0,3–0,9 с; на ответе в 2 000 знаков 1,4–4,5 с, замер). При 0,7 запроса/с к модели это ≈0,63 ядра на тираже; на длинных ответах — до 3,2 ядра.</t>
+          <t>Путь без модели — 8,5 мс на запрос (замер: один процесс отдаёт 117 запросов/с). Путь с моделью — 0,9 с на ответ в 800 знаков (эмбеддинг 36 мс + обезличивание + проверка ответа на потоке 0,3–0,9 с; на ответе в 2 000 знаков 1,4–4,5 с, замер). При максимуме прогноза (0,46 запроса/с к модели на тираже) это ≈0,41 ядра; на ответах в 2 000 знаков — до 2,1 ядра.</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7262,7 @@
       </c>
       <c r="V16" s="9" t="inlineStr">
         <is>
-          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,06 ядра на MVP, 0,63 на тираже; на ответах в 2 000 знаков до 3,2 ядра (3 реплики × 1 vCPU + предел 2). После оптимизации проверки на потоке запас вырастет.</t>
+          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,04 ядра на MVP, 0,41 на тираже (максимум прогноза); на ответах в 2 000 знаков до 2,1 ядра (3 реплики × 1 vCPU + предел 2). После оптимизации проверки на потоке запас вырастет.</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7344,7 @@
       </c>
       <c r="V17" s="9" t="inlineStr">
         <is>
-          <t>Допущение. 1 125 диалогов с записью в месяц на MVP, 11 250 на тираже (A6 = 25%) — нагрузка ничтожна.</t>
+          <t>Допущение. До 2 800 диалогов с записью в месяц на MVP и 31 500 на тираже (максимум прогноза, A6 = 40%) — нагрузка ничтожна.</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7426,7 @@
       </c>
       <c r="V18" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью.</t>
+          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью (до 31 500 в месяц на тираже).</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7836,7 @@
       </c>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>Расчёт из `Capacity_Report.html`: 0,2 ГБ / 30 суток на MVP, 1,7 ГБ на тираже (допущение 10 записей на запрос по 1 КБ); 20 ГиБ с запасом.</t>
+          <t>Расчёт из `Capacity_Report.html`: 0,02–0,42 ГБ за 30 суток на MVP, 0,19–4,7 ГБ на тираже (допущение 10 записей на вопрос по 1 КБ); 20 ГиБ с запасом.</t>
         </is>
       </c>
     </row>
@@ -7910,7 +8004,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="75" customHeight="1">
       <c r="A26" s="50" t="n">
         <v>15</v>
       </c>
@@ -7988,7 +8082,7 @@
       </c>
       <c r="V26" s="9" t="inlineStr">
         <is>
-          <t>Расчёт данных за 90 суток по высокому сценарию: журнал диалогов 4 КБ × 12 500 диалогов в месяц = 150 МБ (MVP) и × 125 000 = 1,5 ГБ (тираж); профиль 24 МБ и 270 МБ (3 КБ на абонента — допущение); телеметрия ≤ 0,25 ГБ в год (2,4 ГБ с запасом ×10); обращения ≈30–300 МБ в год. Итого до 0,5 ГБ (MVP) и до 5 ГБ (тираж); диск с запасом на журнал и копии.</t>
+          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (3 КБ на абонента — допущение); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (2 КБ на строку, доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8164,7 @@
       </c>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 800 одновременных сессий (1 запрос/с × 30 мин) × 3 КБ ≈ 5 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
+          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8223,7 @@
         <v>1</v>
       </c>
       <c r="P28" s="52" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Q28" s="52" t="n">
         <v>0</v>
@@ -8152,7 +8246,7 @@
       </c>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>Расчёт: готовые бланки ≈200 КБ (допущение) × 1 125 в месяц = 2,7 ГБ в год (MVP) и × 11 250 = 27 ГБ в год (тираж), хранение 3 года; копии Postgres за 7 суток до 35 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
+          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
         </is>
       </c>
     </row>
@@ -8764,4 +8858,759 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>Прогноз нагрузки и стоимости токенов — минимум и максимум</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="49" t="inlineStr">
+        <is>
+          <t>Синие ячейки — входные допущения: после получения данных по обращениям подставьте новые значения, нагрузка и стоимость пересчитаются. Тариф — публичный тариф YandexGPT Pro из ADR-500, не проверялся; тариф GigaChat Pro неизвестен. Цен на серверы и GPU нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Входное допущение</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Минимум</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Максимум</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Откуда взято / чем подтвердить</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="56" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Доля абонентов, пришедших в чат хотя бы раз в месяц</t>
+        </is>
+      </c>
+      <c r="C5" s="54" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D5" s="54" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>70% абонентов обращаются раз в месяц (ADR-500) × доля визитов через чат 10–50%. Не все абоненты пойдут в диалог. Подтвердить: Статистика посещаемости личного кабинета и доля, доходящая до чата</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Диалогов на такого абонента в месяц</t>
+        </is>
+      </c>
+      <c r="C6" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Взято из прежнего отчёта (низкий и высокий сценарии). Подтвердить: Частота обращений в колл-центр на абонента</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Вопросов внутри одного диалога</t>
+        </is>
+      </c>
+      <c r="C7" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>3 вопроса за визит (ADR-500) и верхняя оценка прежнего отчёта. Подтвердить: Анализ живых обращений и пилот</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Доля вопросов, доходящих до модели</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="54" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Замер на двух наборах живых текстов: 30% (регистр обращений по телефону и почте) и 70% (форма вопросов Golden Set). Остальные закрывают правила и ответы без модели. Подтвердить: Анализ живых обращений (ADR-600)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Токенов на запрос к модели (вход + выход)</t>
+        </is>
+      </c>
+      <c r="C9" s="59" t="n">
+        <v>401</v>
+      </c>
+      <c r="D9" s="59" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Минимум — замер по 19 вызовам YandexGPT (короткие фрагменты FAQ). Максимум — допущение прежнего отчёта: система + 3 фрагмента по ≈800 токенов. Подтвердить: Пилот на базе из нескольких тысяч документов</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Доля суточных запросов в пиковый час</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D10" s="54" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Допущение прежнего отчёта; профиль ЖКХ (дни начисления и оплаты). Подтвердить: Статистика ЛК</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Время ответа, с</t>
+        </is>
+      </c>
+      <c r="C11" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Целевое значение (DoD). Подтвердить: —</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Вопросов в эталонном наборе для судьи</t>
+        </is>
+      </c>
+      <c r="C12" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Замер: `golden_set/quality.json`, 30 вопросов. Подтвердить: —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Прогонов эталонного набора в месяц</t>
+        </is>
+      </c>
+      <c r="C13" s="59" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Минимум — раз в неделю, максимум — каждую ночь. Подтвердить: Решение команды</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Вызовов судьи на образец</t>
+        </is>
+      </c>
+      <c r="C14" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Допущение прежнего отчёта, не измерено. Подтвердить: Первый прогон с провайдером</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Токенов на вызов судьи</t>
+        </is>
+      </c>
+      <c r="C15" s="59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Допущение прежнего отчёта, не измерено. Подтвердить: Первый прогон с провайдером</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>S_</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Доля ответов, оцениваемых судьёй в проде</t>
+        </is>
+      </c>
+      <c r="C16" s="54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" s="54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Допущение: 1–5% выборка трафика. Подтвердить: Решение команды</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Доля диалогов с записью (Этап 2)</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D17" s="54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Прежний отчёт: 15–40%. Подтвердить: Разметка обращений и пилот</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Токенов на диалог с записью сверх обычных (Этап 2)</t>
+        </is>
+      </c>
+      <c r="C18" s="59" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D18" s="59" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Прежний отчёт: 6 000–20 000. Подтвердить: Замер на пилоте</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Тариф, ₽ за 1000 токенов</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Абонентов, MVP</t>
+        </is>
+      </c>
+      <c r="C20" s="61" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Абонентов, тираж</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>MVP, минимум</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>MVP, максимум</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Тираж, минимум</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Тираж, максимум</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Пришло в чат за месяц, человек</t>
+        </is>
+      </c>
+      <c r="C24" s="42">
+        <f>$C$20*C5</f>
+        <v/>
+      </c>
+      <c r="D24" s="42">
+        <f>$C$20*D5</f>
+        <v/>
+      </c>
+      <c r="E24" s="42">
+        <f>$C$21*C5</f>
+        <v/>
+      </c>
+      <c r="F24" s="42">
+        <f>$C$21*D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Диалогов в месяц</t>
+        </is>
+      </c>
+      <c r="C25" s="42">
+        <f>C24*C6</f>
+        <v/>
+      </c>
+      <c r="D25" s="42">
+        <f>D24*D6</f>
+        <v/>
+      </c>
+      <c r="E25" s="42">
+        <f>E24*C6</f>
+        <v/>
+      </c>
+      <c r="F25" s="42">
+        <f>F24*D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Вопросов в месяц</t>
+        </is>
+      </c>
+      <c r="C26" s="42">
+        <f>C25*C7</f>
+        <v/>
+      </c>
+      <c r="D26" s="42">
+        <f>D25*D7</f>
+        <v/>
+      </c>
+      <c r="E26" s="42">
+        <f>E25*C7</f>
+        <v/>
+      </c>
+      <c r="F26" s="42">
+        <f>F25*D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Запросов к модели в месяц</t>
+        </is>
+      </c>
+      <c r="C27" s="42">
+        <f>C26*C8</f>
+        <v/>
+      </c>
+      <c r="D27" s="42">
+        <f>D26*D8</f>
+        <v/>
+      </c>
+      <c r="E27" s="42">
+        <f>E26*C8</f>
+        <v/>
+      </c>
+      <c r="F27" s="42">
+        <f>F26*D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Токенов генерации в месяц</t>
+        </is>
+      </c>
+      <c r="C28" s="42">
+        <f>C27*C9</f>
+        <v/>
+      </c>
+      <c r="D28" s="42">
+        <f>D27*D9</f>
+        <v/>
+      </c>
+      <c r="E28" s="42">
+        <f>E27*C9</f>
+        <v/>
+      </c>
+      <c r="F28" s="42">
+        <f>F27*D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Токенов судьи в месяц (эталонный набор + выборка трафика)</t>
+        </is>
+      </c>
+      <c r="C29" s="42">
+        <f>C12*C13*C14*C15+C27*C16*C14*C15</f>
+        <v/>
+      </c>
+      <c r="D29" s="42">
+        <f>D12*D13*D14*D15+D27*D16*D14*D15</f>
+        <v/>
+      </c>
+      <c r="E29" s="42">
+        <f>C12*C13*C14*C15+E27*C16*C14*C15</f>
+        <v/>
+      </c>
+      <c r="F29" s="42">
+        <f>D12*D13*D14*D15+F27*D16*D14*D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Генерация, ₽ в месяц</t>
+        </is>
+      </c>
+      <c r="C30" s="42">
+        <f>C28*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="D30" s="42">
+        <f>D28*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="E30" s="42">
+        <f>E28*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="F30" s="42">
+        <f>F28*$C$19/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Судья качества, ₽ в месяц</t>
+        </is>
+      </c>
+      <c r="C31" s="42">
+        <f>C29*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="D31" s="42">
+        <f>D29*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="E31" s="42">
+        <f>E29*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="F31" s="42">
+        <f>F29*$C$19/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Итого токены, ₽ в месяц</t>
+        </is>
+      </c>
+      <c r="C32" s="62">
+        <f>C30+C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="62">
+        <f>D30+D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="62">
+        <f>E30+E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="62">
+        <f>F30+F31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Итого токены, ₽ в год</t>
+        </is>
+      </c>
+      <c r="C33" s="62">
+        <f>C32*12</f>
+        <v/>
+      </c>
+      <c r="D33" s="62">
+        <f>D32*12</f>
+        <v/>
+      </c>
+      <c r="E33" s="62">
+        <f>E32*12</f>
+        <v/>
+      </c>
+      <c r="F33" s="62">
+        <f>F32*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Справочно: агент Этапа 2 добавит, ₽ в месяц</t>
+        </is>
+      </c>
+      <c r="C34" s="42">
+        <f>C25*C17*C18*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="D34" s="42">
+        <f>D25*D17*D18*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="E34" s="42">
+        <f>E25*C17*C18*$C$19/1000</f>
+        <v/>
+      </c>
+      <c r="F34" s="42">
+        <f>F25*D17*D18*$C$19/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Пик, вопросов в секунду</t>
+        </is>
+      </c>
+      <c r="C35" s="63">
+        <f>C26/30*C10/3600</f>
+        <v/>
+      </c>
+      <c r="D35" s="63">
+        <f>D26/30*D10/3600</f>
+        <v/>
+      </c>
+      <c r="E35" s="63">
+        <f>E26/30*C10/3600</f>
+        <v/>
+      </c>
+      <c r="F35" s="63">
+        <f>F26/30*D10/3600</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Одновременно обрабатывается</t>
+        </is>
+      </c>
+      <c r="C36" s="63">
+        <f>C35*C11</f>
+        <v/>
+      </c>
+      <c r="D36" s="63">
+        <f>D35*D11</f>
+        <v/>
+      </c>
+      <c r="E36" s="63">
+        <f>E35*C11</f>
+        <v/>
+      </c>
+      <c r="F36" s="63">
+        <f>F35*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Расчётная нагрузка sizing: 0,1 запроса/с на MVP и 1 запрос/с на тираже; должна быть не ниже строки «Пик».</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1944,7 +1944,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Redis выбран против Memcached (нет структур для сессии), таблицы счётчиков в Postgres (по нагрузке справился бы — 0,225 запроса/с; счётчик с окном пришлось бы писать вручную) и счётчиков в памяти процесса (лимиты обнуляются при перезапуске, fail-open).</t>
+          <t>Redis выбран против Memcached (нет структур для сессии), таблицы счётчиков в Postgres (по нагрузке справился бы — пик до 0,66 вопроса/с на тираже в максимуме прогноза; счётчик с окном пришлось бы писать вручную) и счётчиков в памяти процесса (лимиты обнуляются при перезапуске, fail-open).</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1232,7 +1232,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Свой клиент на каждого провайдера отклонён: дублирование ради контроля, который LiteLLM уже даёт (100+ адаптеров, единый интерфейс, повторы и circuit breaker). Отдельный прокси-сервер LiteLLM на прототипе не взят: это второй процесс со своим портом и конфигурацией, память отдельного процесса LiteLLM не измерялась (на машине 15 ГБ, контейнер Backend занимает 1,32 ГиБ); библиотека принимает тот же список моделей и цепочки запасных провайдеров, формат файла совместим с прокси. Смена провайдера — правка переменной `LLM_PROVIDER`, код не меняется: это условие ADR-200 (минимум два провайдера с автопереключением). Весь нужный инструментарий (LiteLLM, Presidio, sentence-transformers) существует в Python — тот же язык, что у Backend. Зарубежные провайдеры исключены: 152-ФЗ.</t>
+          <t>Свой клиент на каждого провайдера отклонён: дублирование ради контроля, который LiteLLM уже даёт (по документации библиотеки: 100+ адаптеров, единый интерфейс; в проекте настроены повторы и цепочки запасных, circuit breaker не настроен; переключение на запасного сработало на живом трафике — шесть вызовов ушли на локальную модель при пустом ключе). Отдельный прокси-сервер LiteLLM на прототипе не взят: это второй процесс со своим портом и конфигурацией, память отдельного процесса LiteLLM не измерялась (на машине 15 ГБ, контейнер Backend занимает 1,32 ГиБ); библиотека принимает тот же список моделей и цепочки запасных провайдеров, формат файла совместим с прокси. Смена провайдера — правка переменной `LLM_PROVIDER`, код не меняется: это условие ADR-200 (минимум два провайдера с автопереключением). Весь нужный инструментарий (LiteLLM, Presidio, sentence-transformers) существует в Python — тот же язык, что у Backend. Зарубежные провайдеры исключены: 152-ФЗ.</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Объём заложен: несколько тысяч документов (3 000–5 000) × 10–20 частей на документ (допущение) = 30 000–100 000 векторов размерности 1 024 (BGE-M3), 123–410 МБ. Замер Qdrant на 100 000 случайных векторов: P50 27,5 мс / P99 64,9 мс без фильтра, 14,3 / 36,8 мс с фильтром по типу — в бюджете 100 мс. pgvector не отклонён по качеству: на этом объёме рабочая альтернатива (не измерялась), Qdrant выбран из-за алиасов коллекций (blue-green уже в коде) и отдельной нагрузки от основной базы. Milvus и OpenSearch — по документации, не измерялись.</t>
+          <t>Объём заложен: несколько тысяч документов (3 000–5 000) × 10–20 частей на документ (допущение) = 30 000–100 000 векторов размерности 1 024 (BGE-M3), 123–410 МБ. Замер Qdrant на 100 000 случайных векторов: 477 МБ на диске, ОЗУ 527 МиБ; P50 27,5 мс / P99 64,9 мс без фильтра, 14,3 / 36,8 мс с фильтром по типу — в бюджете 100 мс. pgvector не отклонён по качеству: на этом объёме рабочая альтернатива (не измерялась), Qdrant выбран из-за алиасов коллекций (blue-green уже в коде) и отдельной нагрузки от основной базы. Milvus и OpenSearch — по документации, не измерялись.</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -6334,7 +6334,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="50" t="n">
         <v>10</v>
       </c>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Несколько тысяч документов (3 000–5 000), 30 000–100 000 векторов размерности 1 024, ≈0,3–1,0 ГБ. От числа абонентов не зависит. Поиск на 100 000 векторов: P99 65 мс без фильтра, 37 мс с фильтром (замер).</t>
+          <t>Несколько тысяч документов (3 000–5 000), 30 000–100 000 векторов размерности 1 024, ≈0,15–0,5 ГБ на диске (замер: 100 000 векторов — 477 МБ, ОЗУ 527 МиБ). От числа абонентов не зависит. Поиск на 100 000 векторов: P99 65 мс без фильтра, 37 мс с фильтром (замер).</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -6544,7 +6544,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21" ht="75" customHeight="1">
       <c r="A21" s="50" t="n">
         <v>17</v>
       </c>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Loki: 0,02–0,42 ГБ за 30 суток на MVP и 0,19–4,7 ГБ на тираже (допущение: 10 записей на вопрос по ≈1 КБ). Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
+          <t>Loki: сейчас ≈65 байт на вопрос (замер) — до 31 МБ за 30 суток на тираже; целевая трассировка до 10 КБ на вопрос (допущение) — 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже. Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -7758,7 +7758,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="50" t="n">
         <v>12</v>
       </c>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>Расчёт из `Capacity_Report.html`: 0,02–0,42 ГБ за 30 суток на MVP, 0,19–4,7 ГБ на тираже (допущение 10 записей на вопрос по 1 КБ); 20 ГиБ с запасом.</t>
+          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом.</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="45" customHeight="1">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="50" t="n">
         <v>14</v>
       </c>
@@ -8000,11 +8000,11 @@
       </c>
       <c r="V25" s="9" t="inlineStr">
         <is>
-          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ, с индексом ≈1 ГБ; во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="75" customHeight="1">
+          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
       <c r="A26" s="50" t="n">
         <v>15</v>
       </c>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="V26" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (3 КБ на абонента — допущение); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (2 КБ на строку, доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
+          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (заложено 3 КБ на абонента; по примеру прототипа — 0,7 КБ на счёт в CSV); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2234,12 +2234,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>LangGraph — кандидат, не выбран: усложнение ради возможностей, которые пока не нужны.</t>
+          <t>Свой автомат (7 состояний, 10 переходов, 200 строк, перебор всех состояний в тестах) против `transitions` (строковые ключи, дефект уже случался) и LangGraph (второй механизм подтверждения; возможности — ветвление по инструментам, контрольные точки, параллельные ветви — по документации, не пробовались). Вес LangGraph замерен: +34 МиБ ОЗУ и 2,3 с на импорт, ≈2,6% контейнера Backend — не довод против. LangGraph — по триггеру; проверить возможности нечем, пока нет агентного сценария. Другие движки не сравнивались.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Backend и оркестрация»: строка «Оркестрация агента» (свой FSM против LangGraph)</t>
+          <t>ADR-200, раздел «Backend и оркестрация»: строка «Оркестрация агента» и подраздел «Оркестрация агента: собственная таблица переходов, LangGraph — по триггеру»</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прогноз стоимости" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,12 +140,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2309,70 +2309,70 @@
       <c r="A18" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Контейнер</t>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Billing Adapter (запись в Биллинг)</t>
+          <t>Переход агента на LangGraph (по триггеру)</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Billing Adapter; Биллинг (внешняя система); Agent Orchestrator (HITL Gate)</t>
+          <t>Agent Orchestrator; Session State Store (Redis / PostgreSQL); Billing Adapter, Сервис работы с обращениями, Диспетчерская (как инструменты); LLM Gateway</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Python; XML-RPC-клиент к API Биллинга; ключ идемпотентности</t>
+          <t>Python; LangGraph `StateGraph`, `interrupt_before` (или без него); хранилище контрольных точек; отключённая телеметрия `langsmith`</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Не реализован (запись отложена на Этап 2). Чтение идёт из слепка в Postgres.</t>
+          <t>Не выполняется: автомат — собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов). Работа появляется только при наступлении триггера (ADR-200).</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Прямой доступ к чужой БД запрещён: только через API владельца.</t>
+          <t>Свой автомат против `transitions` и LangGraph — ADR-200, подраздел «Оркестрация агента». LangGraph нужен, если агент сам выбирает инструмент, если нужны контрольные точки шагов, если появились параллельные ветви со своим состоянием; для фиксированной заявки с одним подтверждением не нужен.</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
+          <t>ADR-200, подраздел «Оркестрация агента: собственная таблица переходов, LangGraph — по триггеру», в том числе «В каком случае LangGraph нужен — подробно»</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры API Биллинга от владельца ещё не получены; write-доступ к чужой legacy-системе — отдельная интеграция.</t>
+          <t>Оценка function-calling у GigaChat и YandexGPT не проведена; возможности LangGraph в проекте не пробовались; телеметрия библиотеки (`langsmith`) не проверена на соответствие 152-ФЗ.</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Запись показаний и операций в Биллинг через XML-RPC с ключом идемпотентности.</t>
+          <t>Перенос таблицы переходов в граф без изменения состава переходов; `interrupt_before` вместо проверки состояния или не применяется; контрольные точки (Redis с сохранением или Postgres) и удаление ПДн из состояния; при триггере 1 — инструменты (Биллинг, обращения, Диспетчерская) с ограничением шагов, идемпотентностью и аудитом; отключение внешней телеметрии библиотеки; регрессия.</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Отдельный контейнер `Billing Adapter`, XML-RPC API Биллинга.</t>
+          <t>Python; LangGraph `StateGraph`; хранилище контрольных точек — Redis с сохранением или Postgres.</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Единственный разрешённый путь записи в Биллинг; повтор запроса не создаёт дубль.</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N18" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
+          <t>Только по триггеру: возможности, ради которых берут библиотеку, на текущем сценарии проверить нечем. Работа не входит в итог сметы — показана отдельным столбцом.</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="O18" s="13" t="inlineStr">
+        <is>
+          <t>По триггеру (оценка автора)</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
@@ -2387,7 +2387,7 @@
       <c r="U18" s="15" t="n"/>
       <c r="V18" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-400</t>
+          <t>ADR-200; ADR-600</t>
         </is>
       </c>
     </row>
@@ -2402,59 +2402,59 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Сервис работы с обращениями</t>
+          <t>Billing Adapter (запись в Биллинг)</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Сервис работы с обращениями; Микросервис обращений и Диспетчерская (внешние); Agent Orchestrator; Postgres</t>
+          <t>Billing Adapter; Биллинг (внешняя система); Agent Orchestrator (HITL Gate)</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Python; на прототипе запись в таблицу Postgres, на Этапе 2 — HTTP API владельца (сигнатуры не получены)</t>
+          <t>Python; XML-RPC-клиент к API Биллинга; ключ идемпотентности</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Обращение пишется в собственную таблицу Postgres, минуя Orchestrator (`app/inquiries/store.py`).</t>
+          <t>Не реализован (запись отложена на Этап 2). Чтение идёт из слепка в Postgres.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Целевой путь — внешний микросервис обращений; на прототипе доступа к нему нет.</t>
+          <t>Прямой доступ к чужой БД запрещён: только через API владельца.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»; ADR-100, таблица «Что явно отложено»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>Микросервис обращений и его API не готовы принимать реальные запросы; код типов обращений не согласован с владельцем.</t>
+          <t>Сигнатуры API Биллинга от владельца ещё не получены; write-доступ к чужой legacy-системе — отдельная интеграция.</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Регистрация через API микросервиса обращений; аварийные заявки — в Диспетчерскую (выбор маршрута по типу).</t>
+          <t>Запись показаний и операций в Биллинг через XML-RPC с ключом идемпотентности.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>Отдельный контейнер, Route Selector: emergency → Диспетчерская, остальные типы → микросервис.</t>
+          <t>Отдельный контейнер `Billing Adapter`, XML-RPC API Биллинга.</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>Обращения должны попадать в систему-владельца, откуда их читают подрядчики и конвейер дообучения.</t>
+          <t>Единственный разрешённый путь записи в Биллинг; повтор запроса не создаёт дубль.</t>
         </is>
       </c>
       <c r="M19" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N19" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O19" s="18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
       <c r="U19" s="15" t="n"/>
       <c r="V19" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-600</t>
+          <t>ADR-100; ADR-400</t>
         </is>
       </c>
     </row>
@@ -2488,59 +2488,59 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Document Generator (бланки заявлений)</t>
+          <t>Сервис работы с обращениями</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Document Generator; Backend (выдача бланка); S3 / MinIO (MVP)</t>
+          <t>Сервис работы с обращениями; Микросервис обращений и Диспетчерская (внешние); Agent Orchestrator; Postgres</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Прототип — Python: шаблоны бланков и HTML-лист на печать; MVP — PDF-библиотека (не выбрана) + S3 / MinIO</t>
+          <t>Python; на прототипе запись в таблицу Postgres, на Этапе 2 — HTTP API владельца (сигнатуры не получены)</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Готовый бланк отдаётся HTML-листом для печати из каталога (семь образцов по ПП РФ № 644/776).</t>
+          <t>Обращение пишется в собственную таблицу Postgres, минуя Orchestrator (`app/inquiries/store.py`).</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>PDF и S3/MinIO нужны только при путях записи — для консультации избыточны.</t>
+          <t>Целевой путь — внешний микросервис обращений; на прототипе доступа к нему нет.</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Документы Этапа 2: PDF и хранилище файлов (решение не принято)»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»; ADR-100, таблица «Что явно отложено»</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>Настоящие бланки заявлений не согласованы с владельцем — используются образцы.</t>
+          <t>Микросервис обращений и его API не готовы принимать реальные запросы; код типов обращений не согласован с владельцем.</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>Рендер PDF из шаблона и слотов, хранение в объектном хранилище, ссылка с ограниченным сроком жизни.</t>
+          <t>Регистрация через API микросервиса обращений; аварийные заявки — в Диспетчерскую (выбор маршрута по типу).</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Генерация PDF (библиотека в ADR не выбрана) + S3 / MinIO.</t>
+          <t>Отдельный контейнер, Route Selector: emergency → Диспетчерская, остальные типы → микросервис.</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Документ, вложенный в диалог, должен быть файлом, а не страницей печати.</t>
+          <t>Обращения должны попадать в систему-владельца, откуда их читают подрядчики и конвейер дообучения.</t>
         </is>
       </c>
       <c r="M20" s="17" t="n">
         <v>3</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20" s="18" t="inlineStr">
         <is>
@@ -2574,94 +2574,78 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Оркестрация контейнеров</t>
+          <t>Document Generator (бланки заявлений)</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Все контейнеры (Backend, LLM Gateway, Qdrant, Redis, Postgres, ETL, GPU-сервисы)</t>
+          <t>Document Generator; Backend (выдача бланка); S3 / MinIO (MVP)</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Прототип — Docker Compose на одной машине; MVP — Kubernetes (nginx Ingress, cert-manager)</t>
+          <t>Прототип — Python: шаблоны бланков и HTML-лист на печать; MVP — PDF-библиотека (не выбрана) + S3 / MinIO</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>`docker compose` на одной машине: postgres, redis, qdrant, reindex, backend.</t>
+          <t>Готовый бланк отдаётся HTML-листом для печати из каталога (семь образцов по ПП РФ № 644/776).</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Compose на нескольких хостах не переживает отказ узла; Docker Swarm — по общим сведениям, развитие замедлено (не проверялось). Для одного разработчика и одного хоста Kubernetes избыточен.</t>
+          <t>PDF и S3/MinIO нужны только при путях записи — для консультации избыточны.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Документы Этапа 2: PDF и хранилище файлов (решение не принято)»</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Целевая платформа (Kubernetes) пока только подразумевается, отдельного ADR нет.</t>
+          <t>Настоящие бланки заявлений не согласованы с владельцем — используются образцы.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes на собственном железе в закрытом контуре: пространства имён, Ingress, TLS-сертификаты. Расчёт по допущениям (лист «Sizing»): 6 узлов на MVP (3 общих, 2 данных, 1 GPU), 8 на тираже (+1 узел под собственную модель); скорость на GPU не измерялась, стоимость серверов не оценена.</t>
+          <t>Рендер PDF из шаблона и слотов, хранение в объектном хранилище, ссылка с ограниченным сроком жизни.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes, nginx Ingress, cert-manager.</t>
+          <t>Генерация PDF (библиотека в ADR не выбрана) + S3 / MinIO.</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Отказоустойчивость и обновления без остановки; требование целевого развёртывания.</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N21" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O21" s="13" t="inlineStr">
-        <is>
-          <t>Оценка автора</t>
-        </is>
-      </c>
-      <c r="P21" s="9" t="inlineStr">
-        <is>
-          <t>Формализация целевой инфраплатформы отдельным ADR.</t>
-        </is>
-      </c>
-      <c r="Q21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>Kubernetes сейчас лишь подразумевается; для тиража нужна зафиксированная платформа, включая GPU-пулы.</t>
-        </is>
-      </c>
-      <c r="S21" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" s="20" t="n">
+          <t>Документ, вложенный в диалог, должен быть файлом, а не страницей печати.</t>
+        </is>
+      </c>
+      <c r="M21" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="U21" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+      <c r="N21" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
+        </is>
+      </c>
+      <c r="P21" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="15" t="n"/>
+      <c r="S21" s="16" t="n"/>
+      <c r="T21" s="16" t="n"/>
+      <c r="U21" s="15" t="n"/>
       <c r="V21" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-600; C4_Deployment</t>
+          <t>ADR-100; ADR-600</t>
         </is>
       </c>
     </row>
@@ -2676,78 +2660,94 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Секреты и конфигурация</t>
+          <t>Оркестрация контейнеров</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Backend; LLM Gateway (ключи провайдеров); все контейнеры (конфигурация)</t>
+          <t>Все контейнеры (Backend, LLM Gateway, Qdrant, Redis, Postgres, ETL, GPU-сервисы)</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (опционально); MVP — Vault Agent Injector</t>
+          <t>Прототип — Docker Compose на одной машине; MVP — Kubernetes (nginx Ingress, cert-manager)</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Опционально Vault в dev-режиме.</t>
+          <t>`docker compose` на одной машине: postgres, redis, qdrant, reindex, backend.</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения. Хранение только в CI/CD без Vault дублирует секрет в двух местах.</t>
+          <t>Compose на нескольких хостах не переживает отказ узла; Docker Swarm — по общим сведениям, развитие замедлено (не проверялось). Для одного разработчика и одного хоста Kubernetes избыточен.</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Секреты и конфигурация»; ADR-400 («Что добавляется в контуре MVP»)</t>
+          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе»</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Dev-режим Vault сам по себе не безопаснее переменной окружения — это репетиция интеграции, а не защита.</t>
+          <t>Целевая платформа (Kubernetes) пока только подразумевается, отдельного ADR нет.</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Vault Agent Injector: секреты попадают в под через sidecar.</t>
+          <t>Kubernetes на собственном железе в закрытом контуре: пространства имён, Ingress, TLS-сертификаты. Расчёт по допущениям (лист «Sizing»): 6 узлов на MVP (3 общих, 2 данных, 1 GPU), 8 на тираже (+1 узел под собственную модель); скорость на GPU не измерялась, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>HashiCorp Vault в Kubernetes.</t>
+          <t>Kubernetes, nginx Ingress, cert-manager.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Единый источник истины и отзыв доступа без пересборки образа.</t>
+          <t>Отказоустойчивость и обновления без остановки; требование целевого развёртывания.</t>
         </is>
       </c>
       <c r="M22" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O22" s="13" t="inlineStr">
+        <is>
+          <t>Оценка автора</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t>Формализация целевой инфраплатформы отдельным ADR.</t>
+        </is>
+      </c>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>Kubernetes сейчас лишь подразумевается; для тиража нужна зафиксированная платформа, включая GPU-пулы.</t>
+        </is>
+      </c>
+      <c r="S22" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" s="13" t="inlineStr">
-        <is>
-          <t>Оценка автора</t>
-        </is>
-      </c>
-      <c r="P22" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q22" s="15" t="n"/>
-      <c r="R22" s="15" t="n"/>
-      <c r="S22" s="16" t="n"/>
-      <c r="T22" s="16" t="n"/>
-      <c r="U22" s="15" t="n"/>
+      <c r="U22" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="V22" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-400</t>
+          <t>ADR-200; ADR-600; C4_Deployment</t>
         </is>
       </c>
     </row>
@@ -2762,59 +2762,59 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Наблюдаемость (метрики, логи, алерты)</t>
+          <t>Секреты и конфигурация</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); отдельные контейнеры Prometheus, Grafana, Loki, Alertmanager (MVP)</t>
+          <t>Backend; LLM Gateway (ключи провайдеров); все контейнеры (конфигурация)</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Prometheus, Grafana, Loki, Alertmanager</t>
+          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (опционально); MVP — Vault Agent Injector</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Метрики Prometheus на отдельном порту, события потока в панели стенда. Дашбордов и сбора логов нет.</t>
+          <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Опционально Vault в dev-режиме.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Prometheus + Grafana + Loki + Alertmanager выбраны против ELK/OpenSearch, Zabbix и облачного мониторинга: закрытый контур (152-ФЗ), метрики Kubernetes и приложения, недорогие логи (Loki индексирует метки, а не текст). Сравнение по документации; пробного развёртывания альтернатив не было.</t>
+          <t>Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения. Хранение только в CI/CD без Vault дублирует секрет в двух местах.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Prometheus, Grafana, Loki и Alertmanager»</t>
+          <t>ADR-200, раздел «Секреты и конфигурация»; ADR-400 («Что добавляется в контуре MVP»)</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Метрики есть, но собирать и показывать их нечему.</t>
+          <t>Dev-режим Vault сам по себе не безопаснее переменной окружения — это репетиция интеграции, а не защита.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Полный стек наблюдаемости: метрики, дашборды, логи, оповещения; в логах только отчёт об обезличивании, без значений ПДн.</t>
+          <t>Vault Agent Injector: секреты попадают в под через sidecar.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>Prometheus, Grafana, Loki, Alertmanager.</t>
+          <t>HashiCorp Vault в Kubernetes.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах.</t>
+          <t>Единый источник истины и отзыв доступа без пересборки образа.</t>
         </is>
       </c>
       <c r="M23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
       <c r="U23" s="15" t="n"/>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>C4_Deployment; ADR-500</t>
+          <t>ADR-200; ADR-400</t>
         </is>
       </c>
     </row>
@@ -2841,60 +2841,72 @@
       <c r="A24" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>Связь</t>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Виджет ↔ Backend</t>
+          <t>Наблюдаемость (метрики, логи, алерты)</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>AI-виджет; Backend</t>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); отдельные контейнеры Prometheus, Grafana, Loki, Alertmanager (MVP)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
+          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Prometheus, Grafana, Loki, Alertmanager</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
+          <t>Метрики Prometheus на отдельном порту, события потока в панели стенда. Дашбордов и сбора логов нет.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
+          <t>Prometheus + Grafana + Loki + Alertmanager выбраны против ELK/OpenSearch, Zabbix и облачного мониторинга: закрытый контур (152-ФЗ), метрики Kubernetes и приложения, недорогие логи (Loki индексирует метки, а не текст). Сравнение по документации; пробного развёртывания альтернатив не было.</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Prometheus, Grafana, Loki и Alertmanager»</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
-        </is>
-      </c>
-      <c r="M24" s="16" t="n"/>
-      <c r="N24" s="16" t="n"/>
-      <c r="O24" s="15" t="n"/>
+          <t>Метрики есть, но собирать и показывать их нечему.</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Полный стек наблюдаемости: метрики, дашборды, логи, оповещения; в логах только отчёт об обезличивании, без значений ПДн.</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Prometheus, Grafana, Loki, Alertmanager.</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах.</t>
+        </is>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O24" s="13" t="inlineStr">
+        <is>
+          <t>Оценка автора</t>
+        </is>
+      </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -2907,7 +2919,7 @@
       <c r="U24" s="15" t="n"/>
       <c r="V24" s="9" t="inlineStr">
         <is>
-          <t>API_Spec.yaml</t>
+          <t>C4_Deployment; ADR-500</t>
         </is>
       </c>
     </row>
@@ -2915,72 +2927,60 @@
       <c r="A25" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Платформа ЛК (SSO)</t>
+          <t>Виджет ↔ Backend</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Backend; Платформа ЛК (внешняя)</t>
+          <t>AI-виджет; Backend</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
+          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Не подключена: абонент выбирается из справочника стенда.</t>
+          <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
+          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
-        </is>
-      </c>
+          <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K25" s="15" t="n"/>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
+          <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="16" t="n"/>
+      <c r="O25" s="15" t="n"/>
       <c r="P25" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -2993,7 +2993,7 @@
       <c r="U25" s="15" t="n"/>
       <c r="V25" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>API_Spec.yaml</t>
         </is>
       </c>
     </row>
@@ -3001,70 +3001,70 @@
       <c r="A26" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Биллинг (чтение фактов)</t>
+          <t>Backend ↔ Платформа ЛК (SSO)</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Backend; Кэш профиля (пересчёт из Биллинга); Биллинг (внешняя)</t>
+          <t>Backend; Платформа ЛК (внешняя)</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
+          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
+          <t>Не подключена: абонент выбирается из справочника стенда.</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
+          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры API Биллинга от владельца не получены.</t>
+          <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>Свежие факты запрашиваются у Биллинга в момент вопроса.</t>
+          <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>XML-RPC API Биллинга.</t>
+          <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
-        </is>
-      </c>
-      <c r="M26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O26" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
+          <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
+        </is>
+      </c>
+      <c r="M26" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
@@ -3087,34 +3087,34 @@
       <c r="A27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Диспетчерская</t>
+          <t>Backend ↔ Биллинг (чтение фактов)</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
+          <t>Backend; Кэш профиля (пересчёт из Биллинга); Биллинг (внешняя)</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
+          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
+          <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Прямой доступ к чужой БД запрещён.</t>
+          <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -3124,22 +3124,22 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
+          <t>Сигнатуры API Биллинга от владельца не получены.</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
+          <t>Свежие факты запрашиваются у Биллинга в момент вопроса.</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>REST API Диспетчерской.</t>
+          <t>XML-RPC API Биллинга.</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
+          <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
         </is>
       </c>
       <c r="M27" s="20" t="n">
@@ -3165,7 +3165,7 @@
       <c r="U27" s="15" t="n"/>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-400; ADR-600</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3173,64 +3173,72 @@
       <c r="A28" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ LLM Gateway</t>
+          <t>Backend ↔ Диспетчерская</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Backend; LLM Gateway</t>
+          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
+          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Вызов внутри одного процесса.</t>
+          <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
+          <t>Прямой доступ к чужой БД запрещён.</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
+          <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>HTTP внутри кластера.</t>
+          <t>REST API Диспетчерской.</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="n"/>
-      <c r="N28" s="19" t="n"/>
-      <c r="O28" s="9" t="n"/>
+          <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
+        </is>
+      </c>
+      <c r="M28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3243,7 +3251,7 @@
       <c r="U28" s="15" t="n"/>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3251,39 +3259,39 @@
       <c r="A29" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Qdrant</t>
+          <t>Backend ↔ LLM Gateway</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Backend; Qdrant</t>
+          <t>Backend; LLM Gateway</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client по HTTP (порт 6333)</t>
+          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>HTTP (порт 6333); запись — отдельным сервисом, Backend только читает готовый индекс.</t>
+          <t>Вызов внутри одного процесса.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Клиент по HTTP, а не gRPC: задержка HTTP-вызова — единицы миллисекунд при бюджете поиска 100 мс, gRPC добавил бы зависимость без выигрыша.</t>
+          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
+          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -3291,16 +3299,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K29" s="15" t="n"/>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="16" t="n"/>
-      <c r="N29" s="16" t="n"/>
-      <c r="O29" s="15" t="n"/>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>HTTP внутри кластера.</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
+        </is>
+      </c>
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="19" t="n"/>
+      <c r="O29" s="9" t="n"/>
       <c r="P29" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3321,85 +3337,69 @@
       <c r="A30" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>LLM Gateway ↔ LLM Provider</t>
+          <t>Backend ↔ Qdrant</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>LLM Gateway; внешний LLM Provider</t>
+          <t>Backend; Qdrant</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
+          <t>qdrant-client по HTTP (порт 6333)</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
+          <t>HTTP (порт 6333); запись — отдельным сервисом, Backend только читает готовый индекс.</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
+          <t>Клиент по HTTP, а не gRPC: задержка HTTP-вызова — единицы миллисекунд при бюджете поиска 100 мс, gRPC добавил бы зависимость без выигрыша.</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>HTTPS, сертификаты НУЦ Минцифры.</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
-        </is>
-      </c>
-      <c r="M30" s="19" t="n"/>
-      <c r="N30" s="19" t="n"/>
-      <c r="O30" s="9" t="n"/>
-      <c r="P30" s="9" t="inlineStr">
-        <is>
-          <t>Вызов собственной модели внутри закрытого контура.</t>
-        </is>
-      </c>
-      <c r="Q30" s="9" t="inlineStr">
-        <is>
-          <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
-        </is>
-      </c>
-      <c r="R30" s="9" t="inlineStr">
-        <is>
-          <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
-        </is>
-      </c>
-      <c r="S30" s="19" t="n"/>
-      <c r="T30" s="19" t="n"/>
-      <c r="U30" s="9" t="n"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q30" s="15" t="n"/>
+      <c r="R30" s="15" t="n"/>
+      <c r="S30" s="16" t="n"/>
+      <c r="T30" s="16" t="n"/>
+      <c r="U30" s="15" t="n"/>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
     </row>
@@ -3407,73 +3407,85 @@
       <c r="A31" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>Связь</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Индексация → Qdrant</t>
+          <t>LLM Gateway ↔ LLM Provider</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>ETL индексации; Qdrant</t>
+          <t>LLM Gateway; внешний LLM Provider</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
+          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
+          <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
+          <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
+          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K31" s="15" t="n"/>
-      <c r="L31" s="15" t="inlineStr">
-        <is>
-          <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
-        </is>
-      </c>
-      <c r="M31" s="16" t="n"/>
-      <c r="N31" s="16" t="n"/>
-      <c r="O31" s="15" t="n"/>
-      <c r="P31" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q31" s="15" t="n"/>
-      <c r="R31" s="15" t="n"/>
-      <c r="S31" s="16" t="n"/>
-      <c r="T31" s="16" t="n"/>
-      <c r="U31" s="15" t="n"/>
+          <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>HTTPS, сертификаты НУЦ Минцифры.</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
+        </is>
+      </c>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="9" t="inlineStr">
+        <is>
+          <t>Вызов собственной модели внутри закрытого контура.</t>
+        </is>
+      </c>
+      <c r="Q31" s="9" t="inlineStr">
+        <is>
+          <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
+        </is>
+      </c>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
+        </is>
+      </c>
+      <c r="S31" s="19" t="n"/>
+      <c r="T31" s="19" t="n"/>
+      <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-400; ADR-300</t>
         </is>
       </c>
     </row>
@@ -3483,87 +3495,71 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Сквозная работа</t>
+          <t>Связь</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Смета CAPEX/OPEX, NFR, допущения о нагрузке</t>
+          <t>Индексация → Qdrant</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
+          <t>ETL индексации; Qdrant</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
+          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 234–101 280 ₽ в месяц, на тираже 3 305 ₽–1,07 млн ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
+          <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии.</t>
+          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>Разброс стоимости токенов на MVP — ×82 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой. Первый пересчёт сметы по данным обращений и ЛК (3–5 чел-дн, после получения данных) и повторный по пилоту (1–2 чел-дн): подставить данные в лист «Прогноз стоимости», пересчитать нагрузку, стоимость и sizing, обновить отчёт о мощности, ADR-500 и матрицу.</t>
-        </is>
-      </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>Без этого нельзя защищать бюджет.</t>
-        </is>
-      </c>
-      <c r="M32" s="25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N32" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="O32" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: P0</t>
-        </is>
-      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="inlineStr">
+        <is>
+          <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="n"/>
+      <c r="N32" s="16" t="n"/>
+      <c r="O32" s="15" t="n"/>
       <c r="P32" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
       <c r="Q32" s="15" t="n"/>
-      <c r="R32" s="15" t="inlineStr">
-        <is>
-          <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
-        </is>
-      </c>
+      <c r="R32" s="15" t="n"/>
       <c r="S32" s="16" t="n"/>
       <c r="T32" s="16" t="n"/>
       <c r="U32" s="15" t="n"/>
       <c r="V32" s="9" t="inlineStr">
         <is>
-          <t>ADR-500; ADR-600</t>
+          <t>ADR-200</t>
         </is>
       </c>
     </row>
@@ -3571,29 +3567,29 @@
       <c r="A33" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Внедрение ответов владельцев данных</t>
+          <t>Смета CAPEX/OPEX, NFR, допущения о нагрузке</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
+          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Справочники и тексты в коде и данных; не технология</t>
+          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки.</t>
+          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 234–101 280 ₽ в месяц, на тираже 3 305 ₽–1,07 млн ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -3603,17 +3599,17 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
+          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>Календарный срок определяет владелец, не команда.</t>
+          <t>Разброс стоимости токенов на MVP — ×82 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Внедрение полученных ответов в справочники и тексты.</t>
+          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой. Первый пересчёт сметы по данным обращений и ЛК (3–5 чел-дн, после получения данных) и повторный по пилоту (1–2 чел-дн): подставить данные в лист «Прогноз стоимости», пересчитать нагрузку, стоимость и sizing, обновить отчёт о мощности, ADR-500 и матрицу.</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
@@ -3623,18 +3619,18 @@
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>Разработки не требуют — требуют ответа от водоканала.</t>
-        </is>
-      </c>
-      <c r="M33" s="17" t="n">
-        <v>4</v>
+          <t>Без этого нельзя защищать бюджет.</t>
+        </is>
+      </c>
+      <c r="M33" s="25" t="n">
+        <v>11.5</v>
       </c>
       <c r="N33" s="17" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O33" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Согласования</t>
+          <t>Из блока ADR-600: P0</t>
         </is>
       </c>
       <c r="P33" s="14" t="inlineStr">
@@ -3643,13 +3639,17 @@
         </is>
       </c>
       <c r="Q33" s="15" t="n"/>
-      <c r="R33" s="15" t="n"/>
+      <c r="R33" s="15" t="inlineStr">
+        <is>
+          <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
+        </is>
+      </c>
       <c r="S33" s="16" t="n"/>
       <c r="T33" s="16" t="n"/>
       <c r="U33" s="15" t="n"/>
       <c r="V33" s="9" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3657,29 +3657,29 @@
       <c r="A34" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Документация и согласование ИБ</t>
+          <t>Внедрение ответов владельцев данных</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Все (сквозная работа)</t>
+          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Документы и диаграммы пакета сдачи</t>
+          <t>Справочники и тексты в коде и данных; не технология</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
+          <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки.</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
+          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>Календарный срок определяет служба ИБ водоканала.</t>
+          <t>Календарный срок определяет владелец, не команда.</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
+          <t>Внедрение полученных ответов в справочники и тексты.</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
@@ -3709,41 +3709,33 @@
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
+          <t>Разработки не требуют — требуют ответа от водоканала.</t>
         </is>
       </c>
       <c r="M34" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="N34" s="25" t="n">
-        <v>7.5</v>
+        <v>4</v>
+      </c>
+      <c r="N34" s="17" t="n">
+        <v>8</v>
       </c>
       <c r="O34" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Документация и ИБ</t>
-        </is>
-      </c>
-      <c r="P34" s="9" t="inlineStr">
-        <is>
-          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
-        </is>
-      </c>
-      <c r="Q34" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R34" s="9" t="inlineStr">
-        <is>
-          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
-        </is>
-      </c>
-      <c r="S34" s="19" t="n"/>
-      <c r="T34" s="19" t="n"/>
-      <c r="U34" s="9" t="n"/>
+          <t>Из блока ADR-600: Согласования</t>
+        </is>
+      </c>
+      <c r="P34" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q34" s="15" t="n"/>
+      <c r="R34" s="15" t="n"/>
+      <c r="S34" s="16" t="n"/>
+      <c r="T34" s="16" t="n"/>
+      <c r="U34" s="15" t="n"/>
       <c r="V34" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>ADR-600</t>
         </is>
       </c>
     </row>
@@ -3751,85 +3743,93 @@
       <c r="A35" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Выбор семейства собственной модели и закупка GPU</t>
+          <t>Документация и согласование ИБ</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
+          <t>Все (сквозная работа)</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
+          <t>Документы и диаграммы пакета сдачи</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
+          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
+          <t>Не применимо: это работа, а не выбор технологии.</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
+          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K35" s="15" t="n"/>
-      <c r="L35" s="15" t="n"/>
-      <c r="M35" s="16" t="n"/>
-      <c r="N35" s="16" t="n"/>
-      <c r="O35" s="15" t="n"/>
+          <t>Календарный срок определяет служба ИБ водоканала.</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
+        </is>
+      </c>
+      <c r="M35" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O35" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Документация и ИБ</t>
+        </is>
+      </c>
       <c r="P35" s="9" t="inlineStr">
         <is>
-          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
+          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
         </is>
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5-32B INT4, vLLM.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R35" s="9" t="inlineStr">
         <is>
-          <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
-        </is>
-      </c>
-      <c r="S35" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U35" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
+        </is>
+      </c>
+      <c r="S35" s="19" t="n"/>
+      <c r="T35" s="19" t="n"/>
+      <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-500; ADR-600</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3837,92 +3837,76 @@
       <c r="A36" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
+          <t>Выбор семейства собственной модели и закупка GPU</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
+          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
+          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
+          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
+          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
+          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»).</t>
-        </is>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
-        </is>
-      </c>
-      <c r="L36" s="9" t="inlineStr">
-        <is>
-          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="N36" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="O36" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Анализ типов на живых данных</t>
-        </is>
-      </c>
+          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="15" t="n"/>
+      <c r="M36" s="16" t="n"/>
+      <c r="N36" s="16" t="n"/>
+      <c r="O36" s="15" t="n"/>
       <c r="P36" s="9" t="inlineStr">
         <is>
-          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
+          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
         </is>
       </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
-          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
+          <t>Qwen2.5-32B INT4, vLLM.</t>
         </is>
       </c>
       <c r="R36" s="9" t="inlineStr">
         <is>
-          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
+          <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
         </is>
       </c>
       <c r="S36" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U36" s="21" t="inlineStr">
         <is>
@@ -3931,7 +3915,7 @@
       </c>
       <c r="V36" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
+          <t>ADR-300; ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3939,129 +3923,231 @@
       <c r="A37" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
+          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»).</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="N37" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Анализ типов на живых данных</t>
+        </is>
+      </c>
+      <c r="P37" s="9" t="inlineStr">
+        <is>
+          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
+        </is>
+      </c>
+      <c r="Q37" s="9" t="inlineStr">
+        <is>
+          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
+        </is>
+      </c>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
+        </is>
+      </c>
+      <c r="S37" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
+      <c r="V37" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
           <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
         </is>
       </c>
-      <c r="M37" s="17" t="n">
+      <c r="M38" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="N37" s="17" t="n">
+      <c r="N38" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="O37" s="18" t="inlineStr">
+      <c r="O38" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
         </is>
       </c>
-      <c r="P37" s="14" t="inlineStr">
+      <c r="P38" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="Q37" s="15" t="n"/>
-      <c r="R37" s="15" t="n"/>
-      <c r="S37" s="16" t="n"/>
-      <c r="T37" s="16" t="n"/>
-      <c r="U37" s="15" t="n"/>
-      <c r="V37" s="9" t="inlineStr">
+      <c r="Q38" s="15" t="n"/>
+      <c r="R38" s="15" t="n"/>
+      <c r="S38" s="16" t="n"/>
+      <c r="T38" s="16" t="n"/>
+      <c r="U38" s="15" t="n"/>
+      <c r="V38" s="9" t="inlineStr">
         <is>
           <t>ADR-300; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="C39" s="26" t="inlineStr">
+    <row r="40">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>Цвет ячеек с оценкой:</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="C40" s="27" t="n"/>
-      <c r="D40" s="28" t="inlineStr">
+    <row r="41">
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="28" t="inlineStr">
         <is>
           <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="C41" s="29" t="n"/>
-      <c r="D41" s="28" t="inlineStr">
+    <row r="42">
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="28" t="inlineStr">
         <is>
           <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="C42" s="30" t="n"/>
-      <c r="D42" s="28" t="inlineStr">
+    <row r="43">
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="28" t="inlineStr">
         <is>
           <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="C43" s="31" t="n"/>
-      <c r="D43" s="28" t="inlineStr">
+    <row r="44">
+      <c r="C44" s="31" t="n"/>
+      <c r="D44" s="28" t="inlineStr">
         <is>
           <t>изменений на этом этапе нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V37"/>
+  <autoFilter ref="A2:V38"/>
   <mergeCells count="4">
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
@@ -4079,7 +4165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4165,6 +4251,16 @@
           <t>Оценка автора (макс)</t>
         </is>
       </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>По триггеру, не в итоге (мин)</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>По триггеру, не в итоге (макс)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -4173,11 +4269,11 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>SUM('Матрица'!$M$3:$M$37)</f>
+        <f>SUM('Матрица'!$M$3:$M$38)-SUMIF('Матрица'!$O$3:$O$38,"По триггеру*",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="C5" s="34">
-        <f>SUM('Матрица'!$N$3:$N$37)</f>
+        <f>SUM('Матрица'!$N$3:$N$38)-SUMIF('Матрица'!$O$3:$O$38,"По триггеру*",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="D5" s="34">
@@ -4189,27 +4285,35 @@
         <v/>
       </c>
       <c r="F5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"ADR-600",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="G5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"ADR-600",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="H5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока*",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="I5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока*",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="J5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Оценка автора",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="K5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Оценка автора",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$N$3:$N$38)</f>
+        <v/>
+      </c>
+      <c r="L5" s="34">
+        <f>SUMIF('Матрица'!$O$3:$O$38,"По триггеру*",'Матрица'!$M$3:$M$38)</f>
+        <v/>
+      </c>
+      <c r="M5" s="34">
+        <f>SUMIF('Матрица'!$O$3:$O$38,"По триггеру*",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
     </row>
@@ -4220,11 +4324,11 @@
         </is>
       </c>
       <c r="B6" s="34">
-        <f>SUM('Матрица'!$S$3:$S$37)</f>
+        <f>SUM('Матрица'!$S$3:$S$38)-SUMIF('Матрица'!$U$3:$U$38,"По триггеру*",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
       <c r="C6" s="34">
-        <f>SUM('Матрица'!$T$3:$T$37)</f>
+        <f>SUM('Матрица'!$T$3:$T$38)-SUMIF('Матрица'!$U$3:$U$38,"По триггеру*",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
       <c r="D6" s="34">
@@ -4236,27 +4340,35 @@
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"ADR-600",'Матрица'!$S$3:$S$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"ADR-600",'Матрица'!$T$3:$T$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
       <c r="H6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"Из блока*",'Матрица'!$S$3:$S$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
       <c r="I6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"Из блока*",'Матрица'!$T$3:$T$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
       <c r="J6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"Оценка автора",'Матрица'!$S$3:$S$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$S$3:$S$38)</f>
         <v/>
       </c>
       <c r="K6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$37,"Оценка автора",'Матрица'!$T$3:$T$37)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$T$3:$T$38)</f>
+        <v/>
+      </c>
+      <c r="L6" s="34">
+        <f>SUMIF('Матрица'!$U$3:$U$38,"По триггеру*",'Матрица'!$S$3:$S$38)</f>
+        <v/>
+      </c>
+      <c r="M6" s="34">
+        <f>SUMIF('Матрица'!$U$3:$U$38,"По триггеру*",'Матрица'!$T$3:$T$38)</f>
         <v/>
       </c>
     </row>
@@ -4306,11 +4418,19 @@
         <f>SUM(K5:K6)</f>
         <v/>
       </c>
+      <c r="L7" s="38">
+        <f>SUM(L5:L6)</f>
+        <v/>
+      </c>
+      <c r="M7" s="38">
+        <f>SUM(M5:M6)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
         <is>
-          <t>«Оценка автора» — работы, которых нет в ADR-600 (инфраструктура MVP, виджет, вынос шлюза и т. п.); поэтому итог MVP больше, чем «9–13 недель» ADR-600.</t>
+          <t>«Оценка автора» — работы, которых нет в ADR-600 (инфраструктура MVP, виджет, вынос шлюза и т. п.); поэтому итог MVP больше, чем «9–13 недель» ADR-600. Столбцы «По триггеру» — работы, которые появятся только при наступлении триггера (переход агента на LangGraph); в итог не входят.</t>
         </is>
       </c>
     </row>
@@ -4415,11 +4535,11 @@
         <v>17</v>
       </c>
       <c r="D15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F15" s="44">
@@ -4445,11 +4565,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F16" s="44">
@@ -4475,11 +4595,11 @@
         <v>51</v>
       </c>
       <c r="D17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F17" s="44">
@@ -4505,11 +4625,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F18" s="44">
@@ -4535,11 +4655,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F19" s="44">
@@ -4565,11 +4685,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F20" s="44">
@@ -4595,11 +4715,11 @@
         <v>18</v>
       </c>
       <c r="D21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$38)</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$37,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$37)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$38)</f>
         <v/>
       </c>
       <c r="F21" s="44">
@@ -4898,7 +5018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5572,7 +5692,7 @@
         <f>'Матрица'!N18</f>
         <v/>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="13">
         <f>'Матрица'!O18</f>
         <v/>
       </c>
@@ -5653,7 +5773,7 @@
         <f>'Матрица'!N21</f>
         <v/>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="18">
         <f>'Матрица'!O21</f>
         <v/>
       </c>
@@ -5714,11 +5834,11 @@
     </row>
     <row r="37">
       <c r="A37" s="9">
-        <f>'Матрица'!A25</f>
+        <f>'Матрица'!A24</f>
         <v/>
       </c>
       <c r="B37" s="9">
-        <f>'Матрица'!C25</f>
+        <f>'Матрица'!C24</f>
         <v/>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -5727,25 +5847,25 @@
         </is>
       </c>
       <c r="D37" s="34">
-        <f>'Матрица'!M25</f>
+        <f>'Матрица'!M24</f>
         <v/>
       </c>
       <c r="E37" s="34">
-        <f>'Матрица'!N25</f>
-        <v/>
-      </c>
-      <c r="F37" s="18">
-        <f>'Матрица'!O25</f>
+        <f>'Матрица'!N24</f>
+        <v/>
+      </c>
+      <c r="F37" s="13">
+        <f>'Матрица'!O24</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <f>'Матрица'!A32</f>
+        <f>'Матрица'!A26</f>
         <v/>
       </c>
       <c r="B38" s="9">
-        <f>'Матрица'!C32</f>
+        <f>'Матрица'!C26</f>
         <v/>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -5754,15 +5874,15 @@
         </is>
       </c>
       <c r="D38" s="34">
-        <f>'Матрица'!M32</f>
+        <f>'Матрица'!M26</f>
         <v/>
       </c>
       <c r="E38" s="34">
-        <f>'Матрица'!N32</f>
+        <f>'Матрица'!N26</f>
         <v/>
       </c>
       <c r="F38" s="18">
-        <f>'Матрица'!O32</f>
+        <f>'Матрица'!O26</f>
         <v/>
       </c>
     </row>
@@ -5822,11 +5942,11 @@
     </row>
     <row r="41">
       <c r="A41" s="9">
-        <f>'Матрица'!A36</f>
+        <f>'Матрица'!A35</f>
         <v/>
       </c>
       <c r="B41" s="9">
-        <f>'Матрица'!C36</f>
+        <f>'Матрица'!C35</f>
         <v/>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -5835,15 +5955,15 @@
         </is>
       </c>
       <c r="D41" s="34">
-        <f>'Матрица'!M36</f>
+        <f>'Матрица'!M35</f>
         <v/>
       </c>
       <c r="E41" s="34">
-        <f>'Матрица'!N36</f>
+        <f>'Матрица'!N35</f>
         <v/>
       </c>
       <c r="F41" s="18">
-        <f>'Матрица'!O36</f>
+        <f>'Матрица'!O35</f>
         <v/>
       </c>
     </row>
@@ -5874,104 +5994,131 @@
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="43" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="9">
+        <f>'Матрица'!A38</f>
+        <v/>
+      </c>
+      <c r="B43" s="9">
+        <f>'Матрица'!C38</f>
+        <v/>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D43" s="34">
+        <f>'Матрица'!M38</f>
+        <v/>
+      </c>
+      <c r="E43" s="34">
+        <f>'Матрица'!N38</f>
+        <v/>
+      </c>
+      <c r="F43" s="18">
+        <f>'Матрица'!O38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -5982,9 +6129,9 @@
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C48:F48"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="C53:F53"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="C4:F4"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2331,7 +2331,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Не выполняется: автомат — собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов). Работа появляется только при наступлении триггера (ADR-200).</t>
+          <t>Не выполняется: автомат — собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов). Работа появляется только при наступлении одного из трёх триггеров (модель выбирает следующий шаг после вызова инструмента; шаг ждёт событие дольше 30 минут и должен продолжиться с того же шага; две и более одновременные ветви со своими повторами и слиянием). Проверяется при постановке сценария Этапа 2 в разработку, при его изменении и при пересмотре по метрикам Этапа 1; журнал проверки — в ADR-200; пока ни один сценарий не поставлен.</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>9 типов из 16 запасной классификатор не знает: refund, debt, payment, penalty, accrual_recalculation, inquiry_cancellation, meter_reacceptance, meter_reacceptance_auto, other. По ним работают только ключевые слова. Реальные тексты по этим типам — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет). Пороги k-NN подобраны замером на e5-small и не переносятся на другую модель.</t>
+          <t>9 типов из 16 запасной классификатор не знает: refund, debt, payment, penalty, accrual_recalculation, inquiry_cancellation, meter_reacceptance, meter_reacceptance_auto, other. По ним работают только ключевые слова. Реальные тексты по этим типам — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет). Пороги k-NN подобраны замером на e5-small и не переносятся на другую модель. Одна реплика — одна задача: тема берётся первая сработавшая, тип — первый из найденных; остальные части реплики теряются без предупреждения. Замер: 31 из 136 настоящих обращений (23%) подходят под несколько типов по ключевым словам (верхняя оценка многозадачности); доля реплик с двумя и более задачами не измерена — при доле выше 5% агент переводится на LangGraph (триггер 4, ADR-200).</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>Проверки на потоке подобраны без живых ответов модели: частота ложных блокировок и пропусков неизвестна. Судья слабый, оценка предварительная (provisional): пороги качества не откалиброваны на размеченном наборе.</t>
+          <t>Проверки на потоке подобраны без живых ответов модели: частота ложных блокировок и пропусков неизвестна. Судья слабый, оценка предварительная (provisional): пороги качества не откалиброваны на размеченном наборе. Проверки не ловят ложное «сделал»: на реплике «Передайте показания 1234 и скажите, нет ли долга…» модель ответила «Передал показания 1234. Проверил наличие долга — его нет», хотя записи и проверки долга в этом пути нет (один прогон из двух, результат недетерминирован).</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос.</t>
+          <t>Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос. Регистрация предлагается только по первому типу из реплики; условные и составные задачи («если долга нет, закажите поверку») не обрабатываются. Доля реплик с двумя и более задачами не измерена: выше 5% — переход на LangGraph (ADR-200).</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Не выполняется: автомат — собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов). Работа появляется только при наступлении одного из трёх триггеров (модель выбирает следующий шаг после вызова инструмента; шаг ждёт событие дольше 30 минут и должен продолжиться с того же шага; две и более одновременные ветви со своими повторами и слиянием). Проверяется при постановке сценария Этапа 2 в разработку, при его изменении и при пересмотре по метрикам Этапа 1; журнал проверки — в ADR-200; пока ни один сценарий не поставлен.</t>
+          <t>Не выполняется: автомат — собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов). Работа появляется только при наступлении одного из четырёх триггеров (модель выбирает следующий шаг после вызова инструмента; шаг ждёт событие дольше 30 минут и должен продолжиться с того же шага; две и более одновременные ветви со своими повторами и слиянием; доля реплик с двумя и более задачами выше 5%). Проверяется при постановке сценария Этапа 2 в разработку, при его изменении и при пересмотре по метрикам Этапа 1; журнал проверки — в ADR-200; пока ни один сценарий не поставлен.</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Оценка function-calling у GigaChat и YandexGPT не проведена; возможности LangGraph в проекте не пробовались; телеметрия библиотеки (`langsmith`) не проверена на соответствие 152-ФЗ.</t>
+          <t>Оценка function-calling у GigaChat и YandexGPT не проведена; возможности LangGraph в проекте не пробовались; телеметрия библиотеки (`langsmith`) не проверена на соответствие 152-ФЗ. Четвёртый триггер — доля реплик абонентов с двумя и более задачами выше 5% (измерение на выгрузке живых обращений и затем ежемесячно по чату). Оценка по триггерам: общая часть 5–9 чел-дн; с триггером 1 — 8–14, 2 — 7–12, 3 — 7–12, 4 — 8–14; все четыре — 15–25 (диапазон 7–25).</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблицы переходов в граф без изменения состава переходов; `interrupt_before` вместо проверки состояния или не применяется; контрольные точки (Redis с сохранением или Postgres) и удаление ПДн из состояния; при триггере 1 — инструменты (Биллинг, обращения, Диспетчерская) с ограничением шагов, идемпотентностью и аудитом; отключение внешней телеметрии библиотеки; регрессия.</t>
+          <t>Перенос таблицы переходов в граф без изменения состава переходов; `interrupt_before` вместо проверки состояния или не применяется; контрольные точки (Redis с сохранением или Postgres) и удаление ПДн из состояния; при триггере 1 — инструменты (Биллинг, обращения, Диспетчерская) с ограничением шагов, идемпотентностью и аудитом; отключение внешней телеметрии библиотеки; регрессия; при триггере 4 — детектор намерений и очередь задач, запрет фраз о выполненном действии.</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="M18" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O18" s="13" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»).</t>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки.</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прогноз стоимости" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>9 типов из 16 запасной классификатор не знает: refund, debt, payment, penalty, accrual_recalculation, inquiry_cancellation, meter_reacceptance, meter_reacceptance_auto, other. По ним работают только ключевые слова. Реальные тексты по этим типам — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет). Пороги k-NN подобраны замером на e5-small и не переносятся на другую модель. Одна реплика — одна задача: тема берётся первая сработавшая, тип — первый из найденных; остальные части реплики теряются без предупреждения. Замер: 31 из 136 настоящих обращений (23%) подходят под несколько типов по ключевым словам (верхняя оценка многозадачности); доля реплик с двумя и более задачами не измерена — при доле выше 5% агент переводится на LangGraph (триггер 4, ADR-200).</t>
+          <t>9 типов из 16 запасной классификатор не знает: refund, debt, payment, penalty, accrual_recalculation, inquiry_cancellation, meter_reacceptance, meter_reacceptance_auto, other. По ним работают только ключевые слова. Реальные тексты по этим типам — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет). Пороги k-NN подобраны замером на e5-small и не переносятся на другую модель. Классификация даёт одну тему и один тип на реплику; несколько задач в реплике разбирает детектор намерений (`app/agents/intents.py`, реализован на прототипе). Замер: 31 из 136 настоящих обращений (23%) подходят под несколько типов по ключевым словам — это пересечение слов; детектор на тех же текстах находит несколько задач в 1 из 136 (0,7%). Доля по разметке людьми не измерена — при доле выше 5% агент переводится на LangGraph (триггер 4, ADR-200).</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Назначение: проверить ответ модели до показа абоненту — персональные данные, недопустимый тон, разглашение внутренних инструкций. Синхронно (бюджет 50 мс; замер 24.09.2026: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс — на длинных ответах бюджет не держится, проверяется весь накопленный текст): ПДн в ответе, тон, разглашение промпта — при нарушении поток обрывается. Асинхронно: судья обоснованности (локальная Qwen2.5-7B через Ollama), не блокирует выдачу.</t>
+          <t>Назначение: проверить ответ модели до показа абоненту — персональные данные, недопустимый тон, разглашение внутренних инструкций. Синхронно (бюджет 50 мс; замер 24.09.2026: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс — на длинных ответах бюджет не держится, проверяется весь накопленный текст): ПДн в ответе, тон, разглашение промпта, ложное «сделал» (модель пишет, что выполнила операцию) — при нарушении поток обрывается. Асинхронно: судья обоснованности (локальная Qwen2.5-7B через Ollama), не блокирует выдачу.</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>Проверки на потоке подобраны без живых ответов модели: частота ложных блокировок и пропусков неизвестна. Судья слабый, оценка предварительная (provisional): пороги качества не откалиброваны на размеченном наборе. Проверки не ловят ложное «сделал»: на реплике «Передайте показания 1234 и скажите, нет ли долга…» модель ответила «Передал показания 1234. Проверил наличие долга — его нет», хотя записи и проверки долга в этом пути нет (один прогон из двух, результат недетерминирован).</t>
+          <t>Проверки на потоке подобраны без живых ответов модели: частота ложных блокировок и пропусков неизвестна. Судья слабый, оценка предварительная (provisional): пороги качества не откалиброваны на размеченном наборе. Ложное «сделал» ловится правилом `unperformed_action` (начало предложения с глаголом первого лица) и правилом в промпте; до них модель отвечала «Передал показания 1234. Проверил наличие долга — его нет». Перечень глаголов собран вручную, частота ложных блокировок и пропусков на живых ответах неизвестна.</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос. Регистрация предлагается только по первому типу из реплики; условные и составные задачи («если долга нет, закажите поверку») не обрабатываются. Доля реплик с двумя и более задачами не измерена: выше 5% — переход на LangGraph (ADR-200).</t>
+          <t>Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос. Реплика с несколькими задачами разбирается и отвечается по частям; регистрация предлагается по первой подходящей части, несколько черновиков не хранятся; из условий проверяется только наличие долга (ADR-200). Доля реплик с двумя и более задачами по разметке не измерена: выше 5% — переход на LangGraph.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Оценка function-calling у GigaChat и YandexGPT не проведена; возможности LangGraph в проекте не пробовались; телеметрия библиотеки (`langsmith`) не проверена на соответствие 152-ФЗ. Четвёртый триггер — доля реплик абонентов с двумя и более задачами выше 5% (измерение на выгрузке живых обращений и затем ежемесячно по чату). Оценка по триггерам: общая часть 5–9 чел-дн; с триггером 1 — 8–14, 2 — 7–12, 3 — 7–12, 4 — 8–14; все четыре — 15–25 (диапазон 7–25).</t>
+          <t>Оценка function-calling у GigaChat и YandexGPT не проведена; возможности LangGraph в проекте не пробовались; телеметрия библиотеки (`langsmith`) не проверена на соответствие 152-ФЗ. Четвёртый триггер — доля реплик абонентов с двумя и более задачами выше 5% (измерение на выгрузке живых обращений и затем ежемесячно по чату). Оценка по триггерам: общая часть 5–9 чел-дн; с триггером 1 — 8–14, 2 — 7–12, 3 — 7–12, 4 — 7–13; все четыре — 14–24 (диапазон 7–24).</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблицы переходов в граф без изменения состава переходов; `interrupt_before` вместо проверки состояния или не применяется; контрольные точки (Redis с сохранением или Postgres) и удаление ПДн из состояния; при триггере 1 — инструменты (Биллинг, обращения, Диспетчерская) с ограничением шагов, идемпотентностью и аудитом; отключение внешней телеметрии библиотеки; регрессия; при триггере 4 — детектор намерений и очередь задач, запрет фраз о выполненном действии.</t>
+          <t>Перенос таблицы переходов в граф без изменения состава переходов; `interrupt_before` вместо проверки состояния или не применяется; контрольные точки (Redis с сохранением или Postgres) и удаление ПДн из состояния; при триггере 1 — инструменты (Биллинг, обращения, Диспетчерская) с ограничением шагов, идемпотентностью и аудитом; отключение внешней телеметрии библиотеки; регрессия; при триггере 4 — перенос детектора намерений и очереди задач в граф, условные задачи.</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -2368,7 +2368,7 @@
         <v>7</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O18" s="13" t="inlineStr">
         <is>
@@ -4032,63 +4032,63 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
+          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
+          <t>Backend (оркестратор, детектор намерений); LLM Gateway (охранитель, правило в промпте); Session State Store; виджет (кнопки нескольких обращений)</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
+          <t>Python; `app/agents/intents.py` (правила на регулярных выражениях); `Orchestrator._stream_parts`; `unperformed_action` в `app/gateway/guardrails.py`; метрика `assistant_multi_intent_total`</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
+          <t>На прототипе реализовано: детектор намерений разбирает реплику на задачи правилами (`app/agents/intents.py`), оркестратор отвечает по каждой части, операции без выполнения получают прямой отказ, условие «если долга нет» проверяется по Биллингу; ложное «сделал» блокируется правилом в промпте и в охранителе (`unperformed_action`). Тесты: 22 + 16 + 8. Измерение на выгрузке обращений (`scripts/measure_intents.py`): несколько задач в 1 из 136 текстов (0,7%) — срабатывание детектора, не разметка людьми.</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
+          <t>Правила, а не модель: модель на каждой реплике стоила бы времени и токенов, а её разбиение нечем проверить. LangGraph реплику на задачи не разбирает — детектор нужен в любом случае (ADR-200, «Как реализовано: несколько задач в одной реплике»).</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
+          <t>ADR-200, подраздел «Как реализовано: несколько задач в одной реплике» (в разделе «Оркестрация агента»); ADR-100, раздел «Несколько задач в одной реплике»; ADR-400</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
+          <t>Предел 300 знаков, перечни глаголов и операций подобраны автором на 136 обращениях регистра, не на репликах чата; точность и полнота на размеченных репликах не измерены. Регистрация только по первой части, из условий проверяется лишь долг, путь `generate` не разбирается, второй бланк перезапишет первый.</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
+          <t>Проверка детектора на размеченных репликах чата (точность, полнота, подбор предела и перечней); регистрация нескольких обращений из одной реплики (несколько черновиков, подтверждение каждого, виджет); условия помимо долга; путь `generate`, лимиты и порядок частей.</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
+          <t>Python; правила на регулярных выражениях; метрика `assistant_multi_intent_total`; состояние диалога в Redis.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
+          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — условие перехода на LangGraph (триггер 4).</t>
         </is>
       </c>
       <c r="M38" s="17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N38" s="17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O38" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
+          <t>Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)</t>
         </is>
       </c>
       <c r="P38" s="14" t="inlineStr">
@@ -4103,51 +4103,137 @@
       <c r="U38" s="15" t="n"/>
       <c r="V38" s="9" t="inlineStr">
         <is>
+          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
+        </is>
+      </c>
+      <c r="M39" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N39" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="O39" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
+        </is>
+      </c>
+      <c r="P39" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q39" s="15" t="n"/>
+      <c r="R39" s="15" t="n"/>
+      <c r="S39" s="16" t="n"/>
+      <c r="T39" s="16" t="n"/>
+      <c r="U39" s="15" t="n"/>
+      <c r="V39" s="9" t="inlineStr">
+        <is>
           <t>ADR-300; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="C40" s="26" t="inlineStr">
+    <row r="41">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>Цвет ячеек с оценкой:</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="28" t="inlineStr">
+    <row r="42">
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="28" t="inlineStr">
         <is>
           <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="C42" s="29" t="n"/>
-      <c r="D42" s="28" t="inlineStr">
+    <row r="43">
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="28" t="inlineStr">
         <is>
           <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="28" t="inlineStr">
+    <row r="44">
+      <c r="C44" s="30" t="n"/>
+      <c r="D44" s="28" t="inlineStr">
         <is>
           <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="C44" s="31" t="n"/>
-      <c r="D44" s="28" t="inlineStr">
+    <row r="45">
+      <c r="C45" s="31" t="n"/>
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>изменений на этом этапе нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V38"/>
+  <autoFilter ref="A2:V39"/>
   <mergeCells count="4">
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
@@ -4165,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4269,11 +4355,11 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>SUM('Матрица'!$M$3:$M$38)-SUMIF('Матрица'!$O$3:$O$38,"По триггеру*",'Матрица'!$M$3:$M$38)</f>
+        <f>SUM('Матрица'!$M$3:$M$39)-SUMIF('Матрица'!$O$3:$O$39,"По триггеру*",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="C5" s="34">
-        <f>SUM('Матрица'!$N$3:$N$38)-SUMIF('Матрица'!$O$3:$O$38,"По триггеру*",'Матрица'!$N$3:$N$38)</f>
+        <f>SUM('Матрица'!$N$3:$N$39)-SUMIF('Матрица'!$O$3:$O$39,"По триггеру*",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="D5" s="34">
@@ -4285,35 +4371,35 @@
         <v/>
       </c>
       <c r="F5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"ADR-600",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="G5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"ADR-600",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"ADR-600",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="H5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока*",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="I5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока*",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока*",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="J5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Оценка автора",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="K5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Оценка автора",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Оценка автора",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="L5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"По триггеру*",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"По триггеру*",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="M5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"По триггеру*",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"По триггеру*",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
     </row>
@@ -4324,11 +4410,11 @@
         </is>
       </c>
       <c r="B6" s="34">
-        <f>SUM('Матрица'!$S$3:$S$38)-SUMIF('Матрица'!$U$3:$U$38,"По триггеру*",'Матрица'!$S$3:$S$38)</f>
+        <f>SUM('Матрица'!$S$3:$S$39)-SUMIF('Матрица'!$U$3:$U$39,"По триггеру*",'Матрица'!$S$3:$S$39)</f>
         <v/>
       </c>
       <c r="C6" s="34">
-        <f>SUM('Матрица'!$T$3:$T$38)-SUMIF('Матрица'!$U$3:$U$38,"По триггеру*",'Матрица'!$T$3:$T$38)</f>
+        <f>SUM('Матрица'!$T$3:$T$39)-SUMIF('Матрица'!$U$3:$U$39,"По триггеру*",'Матрица'!$T$3:$T$39)</f>
         <v/>
       </c>
       <c r="D6" s="34">
@@ -4340,35 +4426,35 @@
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$S$3:$S$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$39,"ADR-600",'Матрица'!$S$3:$S$39)</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"ADR-600",'Матрица'!$T$3:$T$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$39,"ADR-600",'Матрица'!$T$3:$T$39)</f>
         <v/>
       </c>
       <c r="H6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$S$3:$S$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$39,"Из блока*",'Матрица'!$S$3:$S$39)</f>
         <v/>
       </c>
       <c r="I6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"Из блока*",'Матрица'!$T$3:$T$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$39,"Из блока*",'Матрица'!$T$3:$T$39)</f>
         <v/>
       </c>
       <c r="J6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$S$3:$S$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$39,"Оценка автора",'Матрица'!$S$3:$S$39)</f>
         <v/>
       </c>
       <c r="K6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"Оценка автора",'Матрица'!$T$3:$T$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$39,"Оценка автора",'Матрица'!$T$3:$T$39)</f>
         <v/>
       </c>
       <c r="L6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"По триггеру*",'Матрица'!$S$3:$S$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$39,"По триггеру*",'Матрица'!$S$3:$S$39)</f>
         <v/>
       </c>
       <c r="M6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$38,"По триггеру*",'Матрица'!$T$3:$T$38)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$39,"По триггеру*",'Матрица'!$T$3:$T$39)</f>
         <v/>
       </c>
     </row>
@@ -4535,11 +4621,11 @@
         <v>17</v>
       </c>
       <c r="D15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="F15" s="44">
@@ -4565,11 +4651,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="E16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="F16" s="44">
@@ -4595,11 +4681,11 @@
         <v>51</v>
       </c>
       <c r="D17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="E17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="F17" s="44">
@@ -4625,11 +4711,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="E18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="F18" s="44">
@@ -4655,11 +4741,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="F19" s="44">
@@ -4685,11 +4771,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="F20" s="44">
@@ -4705,21 +4791,21 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Проверка Guardrails и провайдеров на живых данных</t>
+          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
         </is>
       </c>
       <c r="B21" s="34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C21" s="34" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$39)</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$38,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$38)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$39)</f>
         <v/>
       </c>
       <c r="F21" s="44">
@@ -4728,140 +4814,137 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>11–18 чел-дн (ADR-600): выборка 1–2, Guardrails 4–6, оптимизация синхронной проверки 1–2, сравнение провайдеров 4–6, решение 1–2</t>
+          <t>9–14 чел-дн (ADR-600): проверка детектора на репликах чата 3–4, несколько обращений из одной реплики 3–5, условия помимо долга 2–3, путь generate и лимиты 1–2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>Проверка Guardrails и провайдеров на живых данных</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" s="34">
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$39)</f>
+        <v/>
+      </c>
+      <c r="E22" s="34">
+        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$39)</f>
+        <v/>
+      </c>
+      <c r="F22" s="44">
+        <f>IF(AND(D22=B22,E22=C22),"да","НЕТ")</f>
+        <v/>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>11–18 чел-дн (ADR-600): выборка 1–2, Guardrails 4–6, оптимизация синхронной проверки 1–2, сравнение провайдеров 4–6, решение 1–2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>Итого по блокам</t>
         </is>
       </c>
-      <c r="B22" s="38">
-        <f>SUM(B15:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="38">
-        <f>SUM(C15:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="38">
-        <f>SUM(D15:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="38">
-        <f>SUM(E15:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="45">
-        <f>IF(AND(D22=B22,E22=C22),"да","НЕТ")</f>
-        <v/>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>ADR-600 называет итог ≈20–30 недель (≈100–150 чел-дн); сумма блоков 99,5–150,5 — округление в самом ADR-600</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="B23" s="38">
+        <f>SUM(B15:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="38">
+        <f>SUM(C15:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="38">
+        <f>SUM(D15:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="38">
+        <f>SUM(E15:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="45">
+        <f>IF(AND(D23=B23,E23=C23),"да","НЕТ")</f>
+        <v/>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>ADR-600 называет итог ≈22–33 недели (≈110–165 чел-дн); сумма блоков 108,5–164,5 — округление в самом ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
         <is>
           <t>Затраты, которые не выражаются человеко-днями</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Контур</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Значение / комментарий</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>От</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>До</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Единица</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Источник</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Токены генерации (YandexGPT Pro, 0,8 ₽ за 1000 токенов)</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Минимум — 1 234 ₽/мес (7% абонентов в чате, 30% вопросов до модели, 401 токен на запрос, судья раз в неделю); максимум — 101 280 ₽/мес (35%, 70%, 3 500 токенов, судья каждую ночь). Допущения о спросе данными водоканала не подтверждены; разброс ×82</t>
-        </is>
-      </c>
-      <c r="D26" s="42" t="n">
-        <v>1234</v>
-      </c>
-      <c r="E26" s="42" t="n">
-        <v>101280</v>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>₽/мес</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>Capacity_Report; лист «Прогноз стоимости»</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Токены генерации и судьи качества (тариф YandexGPT Pro 0,8 ₽ за 1000 токенов)</t>
+          <t>Токены генерации (YandexGPT Pro, 0,8 ₽ за 1000 токенов)</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Минимум — 3 305 ₽/мес, максимум — 1,07 млн ₽/мес (0,66 вопроса/с в пике); при собственной модели заменяется CAPEX на карту</t>
+          <t>Минимум — 1 234 ₽/мес (7% абонентов в чате, 30% вопросов до модели, 401 токен на запрос, судья раз в неделю); максимум — 101 280 ₽/мес (35%, 70%, 3 500 токенов, судья каждую ночь). Допущения о спросе данными водоканала не подтверждены; разброс ×82</t>
         </is>
       </c>
       <c r="D27" s="42" t="n">
-        <v>3305</v>
+        <v>1234</v>
       </c>
       <c r="E27" s="42" t="n">
-        <v>1065600</v>
+        <v>101280</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
@@ -4877,29 +4960,33 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Тираж</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>GPU-сервер под эмбеддинги и реранкер</t>
+          <t>Токены генерации и судьи качества (тариф YandexGPT Pro 0,8 ₽ за 1000 токенов)</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Не оценён отдельной строкой сметы; скорость на GPU не измерялась</t>
-        </is>
-      </c>
-      <c r="D28" s="42" t="n"/>
-      <c r="E28" s="42" t="n"/>
+          <t>Минимум — 3 305 ₽/мес, максимум — 1,07 млн ₽/мес (0,66 вопроса/с в пике); при собственной модели заменяется CAPEX на карту</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E28" s="42" t="n">
+        <v>1065600</v>
+      </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>₽</t>
+          <t>₽/мес</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>ADR-500 (открытый пункт)</t>
+          <t>Capacity_Report; лист «Прогноз стоимости»</t>
         </is>
       </c>
     </row>
@@ -4911,12 +4998,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
+          <t>GPU-сервер под эмбеддинги и реранкер</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Не оценены</t>
+          <t>Не оценён отдельной строкой сметы; скорость на GPU не измерялась</t>
         </is>
       </c>
       <c r="D29" s="42" t="n"/>
@@ -4935,25 +5022,21 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Карта A100 80 ГБ (покупка)</t>
+          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
-        </is>
-      </c>
-      <c r="D30" s="42" t="n">
-        <v>927000</v>
-      </c>
-      <c r="E30" s="42" t="n">
-        <v>2368080</v>
-      </c>
+          <t>Не оценены</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
       <c r="F30" s="9" t="inlineStr">
         <is>
           <t>₽</t>
@@ -4961,7 +5044,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
@@ -4973,29 +5056,62 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
+          <t>Карта A100 80 ГБ (покупка)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="n">
+        <v>927000</v>
+      </c>
+      <c r="E31" s="42" t="n">
+        <v>2368080</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>₽</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>ADR-500</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Тираж</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
           <t>Сервер-хост, электричество, размещение, обслуживание GPU</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Не оценены</t>
         </is>
       </c>
-      <c r="D31" s="42" t="n"/>
-      <c r="E31" s="42" t="n"/>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>₽</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="33" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>Все суммы в ₽ — прогнозная модель, не смета: CAPEX/OPEX не утверждены владельцем (ADR-500). Закупка GPU — недели или месяцы лид-тайма, не разработка.</t>
         </is>
@@ -5018,7 +5134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6021,104 +6137,131 @@
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="43" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9">
+        <f>'Матрица'!A39</f>
+        <v/>
+      </c>
+      <c r="B44" s="9">
+        <f>'Матрица'!C39</f>
+        <v/>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D44" s="34">
+        <f>'Матрица'!M39</f>
+        <v/>
+      </c>
+      <c r="E44" s="34">
+        <f>'Матрица'!N39</f>
+        <v/>
+      </c>
+      <c r="F44" s="18">
+        <f>'Матрица'!O39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="43" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -6137,7 +6280,7 @@
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C54:F54"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C5:F5"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2680,17 +2680,17 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Compose на нескольких хостах не переживает отказ узла; Docker Swarm — по общим сведениям, развитие замедлено (не проверялось). Для одного разработчика и одного хоста Kubernetes избыточен.</t>
+          <t>Compose на одном или нескольких хостах не переживает отказ узла и не обновляется без остановки; Docker Swarm слабее по GPU и заданиям, меньше сообщество; Nomad — реальная альтернатива, если некому эксплуатировать Kubernetes (проще, встроенная интеграция с Vault). Сравнение по документации, ни один вариант кроме Compose не разворачивался (ADR-200, «Почему Kubernetes»). Для одного разработчика и одного хоста Kubernetes избыточен.</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе»</t>
+          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе» и подраздел «Почему Kubernetes, а не другая оркестрация»</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Целевая платформа (Kubernetes) пока только подразумевается, отдельного ADR нет.</t>
+          <t>Kubernetes выбран предварительно: с владельцем инфраструктуры не согласованы готовый кластер, дистрибутив и эксплуатирующая команда (выделенного инженера нет, обучение и поддержка в смете не оценены). Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP. Реальная альтернатива — Nomad с Vault.</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Отказоустойчивость и обновления без остановки; требование целевого развёртывания.</t>
+          <t>Отказоустойчивость, обновление без остановки, пулы узлов с GPU, задания по расписанию, секреты через Vault Agent Injector. Нагрузка ради этого не нужна: запросы всех подов (11,2 vCPU, 23,6 ГиБ) помещаются на один сервер.</t>
         </is>
       </c>
       <c r="M22" s="12" t="n">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>Формализация целевой инфраплатформы отдельным ADR.</t>
+          <t>Согласование платформы с владельцем инфраструктуры (дистрибутив, эксплуатирующая команда, отечественное ПО); аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
         </is>
       </c>
       <c r="Q22" s="9" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="R22" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes сейчас лишь подразумевается; для тиража нужна зафиксированная платформа, включая GPU-пулы.</t>
+          <t>Для тиража нужна согласованная платформа, включая GPU-пулы; выбор Kubernetes пока предварительный.</t>
         </is>
       </c>
       <c r="S22" s="20" t="n">
@@ -9130,7 +9130,7 @@
     <row r="42">
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); нагрузочный тест не проводился.</t>
+          <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); управляющая часть Kubernetes размещена на трёх узлах общего пула (допущение); нагрузочный тест не проводился.</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes выбран предварительно: с владельцем инфраструктуры не согласованы готовый кластер, дистрибутив и эксплуатирующая команда (выделенного инженера нет, обучение и поддержка в смете не оценены). Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP. Реальная альтернатива — Nomad с Vault.</t>
+          <t>Kubernetes выбран предварительно. Со слов заказчика проекта личный кабинет водоканала уже работает на Kubernetes (документально не подтверждено): не согласовано, размещаемся ли в том же кластере или строим отдельный, его дистрибутив, GPU-узлы, тома и кто эксплуатирует наш контур (выделенного инженера под проект нет, обучение и поддержка в смете не оценены). Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>Согласование платформы с владельцем инфраструктуры (дистрибутив, эксплуатирующая команда, отечественное ПО); аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
+          <t>Согласование платформы с владельцем инфраструктуры: общий кластер (личный кабинет уже на Kubernetes) или отдельный, дистрибутив, эксплуатирующая команда, отечественное ПО; аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
         </is>
       </c>
       <c r="Q22" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прогноз стоимости" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -352,11 +352,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>BGE-M3 на GPU (общий сервис для онлайн-поиска и индексации) — предварительный выбор: окончательно модель выбирается по тесту 4–5 моделей (e5-small, e5-large, BGE-M3, модели, дообученные на русском) на размеченном наборе из живых обращений; пороги подбираются под каждую модель (ADR-600, «Тест моделей эмбеддингов для MVP»). Размеченный набор берётся из строки «Анализ всех типов…».</t>
+          <t>В кластере владельца GPU нет: на MVP — e5-small на CPU (36–37 мс на запрос, замер); BGE-M3 на GPU — только если владелец добавит GPU-узел (строка «GPU-узел в кластере владельца»). Модель выбирается по тесту 4–5 моделей (e5-small, e5-large, BGE-M3, модели, дообученные на русском) на размеченном наборе из живых обращений; пороги подбираются под каждую модель (ADR-600, «Тест моделей эмбеддингов для MVP»). Размеченный набор берётся из строки «Анализ всех типов…».</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>BGE-M3, сервис `embedding-inference` на узле с GPU.</t>
+          <t>Без GPU: sentence-transformers, e5-small на CPU (2 реплики). С GPU-узлом: BGE-M3, сервис `embedding-inference`.</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Включён в онлайн-поиске; замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (5–7 чел-дн); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только при GPU-узле. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (5–7 чел-дн); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>BGE-reranker-v2-m3, сервис `reranker-inference` на GPU.</t>
+          <t>Без GPU: выключен. С GPU-узлом: BGE-reranker-v2-m3, сервис `reranker-inference`.</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes выбран предварительно. Со слов заказчика проекта личный кабинет водоканала уже работает на Kubernetes (документально не подтверждено): не согласовано, размещаемся ли в том же кластере или строим отдельный, его дистрибутив, GPU-узлы, тома и кто эксплуатирует наш контур (выделенного инженера под проект нет, обучение и поддержка в смете не оценены). Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
+          <t>Решение заказчика проекта (24.09.2026, документально не подтверждено): личный кабинет уже на Kubernetes, размещаемся в том же кластере, эксплуатирует тот же отдел, GPU-узлов нет. Не известны дистрибутив и версия, квоты, классы хранилищ и быстрые диски, есть ли Vault и своя наблюдаемость, сетевые правила. Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes на собственном железе в закрытом контуре: пространства имён, Ingress, TLS-сертификаты. Расчёт по допущениям (лист «Sizing»): 6 узлов на MVP (3 общих, 2 данных, 1 GPU), 8 на тираже (+1 узел под собственную модель); скорость на GPU не измерялась, стоимость серверов не оценена.</t>
+          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 20 компонентов, секреты (Vault или механизм кластера). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes, nginx Ingress, cert-manager.</t>
+          <t>Kubernetes владельца (дистрибутив и версия неизвестны); Ingress и сертификаты — по правилам кластера; манифесты приложения.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="M22" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O22" s="13" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>Согласование платформы с владельцем инфраструктуры: общий кластер (личный кабинет уже на Kubernetes) или отдельный, дистрибутив, эксплуатирующая команда, отечественное ПО; аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
+          <t>Согласование платформы с владельцем инфраструктуры: решено размещаться в общем кластере с личным кабинетом (эксплуатирует тот же отдел, GPU нет); остаются дистрибутив и версия, квоты, Vault и наблюдаемость кластера, отечественное ПО; аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
         </is>
       </c>
       <c r="Q22" s="9" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>HashiCorp Vault в Kubernetes.</t>
+          <t>HashiCorp Vault в Kubernetes; используется ли Vault в кластере владельца, неизвестно — возможно, придётся взять их механизм секретов.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -3844,78 +3844,78 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Выбор семейства собственной модели и закупка GPU</t>
+          <t>GPU-узел в кластере владельца (по решению)</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
+          <t>Kubernetes-кластер владельца (новый GPU-узел); embedding-inference; reranker-inference; ETL индексации</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
+          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
+          <t>В кластере, где работает личный кабинет и где размещается наш контур, GPU-узлов нет (решение заказчика проекта, 24.09.2026). Без них MVP на CPU: эмбеддинги e5-small (36–37 мс на запрос), реранкер выключен, индексация считает эмбеддинги на CPU.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
+          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7,2 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Решение за владельцем до начала теста моделей (ADR-200, «Почему Kubernetes», ADR-600).</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
+          <t>ADR-200, подраздел «Почему Kubernetes, а не другая оркестрация» (пункт «GPU»); ADR-300, раздел 2; ADR-600, «GPU-узел в кластере владельца — по решению»</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
+          <t>Цена и сроки закупки сервера не оценены; скорость моделей на GPU не измерялась; отдел владельца GPU не эксплуатировал.</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>Закупка сервера с видеокартой и подключение к общему кластеру: драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом (3–5 чел-дн, без закупки).</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты.</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>Только по решению владельца: без GPU-узла тест BGE-M3 и реранкера смысла не имеет. Не входит в итог сметы — показана отдельным столбцом.</t>
+        </is>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" s="13" t="inlineStr">
+        <is>
+          <t>По триггеру (решение владельца: GPU-узел, оценка автора)</t>
+        </is>
+      </c>
+      <c r="P36" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="K36" s="15" t="n"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="16" t="n"/>
-      <c r="N36" s="16" t="n"/>
-      <c r="O36" s="15" t="n"/>
-      <c r="P36" s="9" t="inlineStr">
-        <is>
-          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
-        </is>
-      </c>
-      <c r="Q36" s="9" t="inlineStr">
-        <is>
-          <t>Qwen2.5-32B INT4, vLLM.</t>
-        </is>
-      </c>
-      <c r="R36" s="9" t="inlineStr">
-        <is>
-          <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
-        </is>
-      </c>
-      <c r="S36" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T36" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U36" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+      <c r="Q36" s="15" t="n"/>
+      <c r="R36" s="15" t="n"/>
+      <c r="S36" s="16" t="n"/>
+      <c r="T36" s="16" t="n"/>
+      <c r="U36" s="15" t="n"/>
       <c r="V36" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-500; ADR-600</t>
+          <t>ADR-200; ADR-300; ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3930,85 +3930,69 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
+          <t>Выбор семейства собственной модели и закупка GPU</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
+          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
+          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
+          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
+          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
+          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки.</t>
-        </is>
-      </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
-        </is>
-      </c>
-      <c r="L37" s="9" t="inlineStr">
-        <is>
-          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="N37" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="O37" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Анализ типов на живых данных</t>
-        </is>
-      </c>
+          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K37" s="15" t="n"/>
+      <c r="L37" s="15" t="n"/>
+      <c r="M37" s="16" t="n"/>
+      <c r="N37" s="16" t="n"/>
+      <c r="O37" s="15" t="n"/>
       <c r="P37" s="9" t="inlineStr">
         <is>
-          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
+          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
         </is>
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
+          <t>Qwen2.5-32B INT4, vLLM.</t>
         </is>
       </c>
       <c r="R37" s="9" t="inlineStr">
         <is>
-          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
+          <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
         </is>
       </c>
       <c r="S37" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U37" s="21" t="inlineStr">
         <is>
@@ -4017,7 +4001,7 @@
       </c>
       <c r="V37" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
+          <t>ADR-300; ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -4032,78 +4016,94 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
+          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Backend (оркестратор, детектор намерений); LLM Gateway (охранитель, правило в промпте); Session State Store; виджет (кнопки нескольких обращений)</t>
+          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Python; `app/agents/intents.py` (правила на регулярных выражениях); `Orchestrator._stream_parts`; `unperformed_action` в `app/gateway/guardrails.py`; метрика `assistant_multi_intent_total`</t>
+          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>На прототипе реализовано: детектор намерений разбирает реплику на задачи правилами (`app/agents/intents.py`), оркестратор отвечает по каждой части, операции без выполнения получают прямой отказ, условие «если долга нет» проверяется по Биллингу; ложное «сделал» блокируется правилом в промпте и в охранителе (`unperformed_action`). Тесты: 22 + 16 + 8. Измерение на выгрузке обращений (`scripts/measure_intents.py`): несколько задач в 1 из 136 текстов (0,7%) — срабатывание детектора, не разметка людьми.</t>
+          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Правила, а не модель: модель на каждой реплике стоила бы времени и токенов, а её разбиение нечем проверить. LangGraph реплику на задачи не разбирает — детектор нужен в любом случае (ADR-200, «Как реализовано: несколько задач в одной реплике»).</t>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Как реализовано: несколько задач в одной реплике» (в разделе «Оркестрация агента»); ADR-100, раздел «Несколько задач в одной реплике»; ADR-400</t>
+          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>Предел 300 знаков, перечни глаголов и операций подобраны автором на 136 обращениях регистра, не на репликах чата; точность и полнота на размеченных репликах не измерены. Регистрация только по первой части, из условий проверяется лишь долг, путь `generate` не разбирается, второй бланк перезапишет первый.</t>
+          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>Проверка детектора на размеченных репликах чата (точность, полнота, подбор предела и перечней); регистрация нескольких обращений из одной реплики (несколько черновиков, подтверждение каждого, виджет); условия помимо долга; путь `generate`, лимиты и порядок частей.</t>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки.</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>Python; правила на регулярных выражениях; метрика `assistant_multi_intent_total`; состояние диалога в Redis.</t>
+          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — условие перехода на LangGraph (триггер 4).</t>
+          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
         </is>
       </c>
       <c r="M38" s="17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N38" s="17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O38" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)</t>
-        </is>
-      </c>
-      <c r="P38" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q38" s="15" t="n"/>
-      <c r="R38" s="15" t="n"/>
-      <c r="S38" s="16" t="n"/>
-      <c r="T38" s="16" t="n"/>
-      <c r="U38" s="15" t="n"/>
+          <t>Из блока ADR-600: Анализ типов на живых данных</t>
+        </is>
+      </c>
+      <c r="P38" s="9" t="inlineStr">
+        <is>
+          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
+        </is>
+      </c>
+      <c r="Q38" s="9" t="inlineStr">
+        <is>
+          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
+        </is>
+      </c>
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
+        </is>
+      </c>
+      <c r="S38" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="V38" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
+          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
         </is>
       </c>
     </row>
@@ -4118,63 +4118,63 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
+          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
+          <t>Backend (оркестратор, детектор намерений); LLM Gateway (охранитель, правило в промпте); Session State Store; виджет (кнопки нескольких обращений)</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
+          <t>Python; `app/agents/intents.py` (правила на регулярных выражениях); `Orchestrator._stream_parts`; `unperformed_action` в `app/gateway/guardrails.py`; метрика `assistant_multi_intent_total`</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
+          <t>На прототипе реализовано: детектор намерений разбирает реплику на задачи правилами (`app/agents/intents.py`), оркестратор отвечает по каждой части, операции без выполнения получают прямой отказ, условие «если долга нет» проверяется по Биллингу; ложное «сделал» блокируется правилом в промпте и в охранителе (`unperformed_action`). Тесты: 22 + 16 + 8. Измерение на выгрузке обращений (`scripts/measure_intents.py`): несколько задач в 1 из 136 текстов (0,7%) — срабатывание детектора, не разметка людьми.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
+          <t>Правила, а не модель: модель на каждой реплике стоила бы времени и токенов, а её разбиение нечем проверить. LangGraph реплику на задачи не разбирает — детектор нужен в любом случае (ADR-200, «Как реализовано: несколько задач в одной реплике»).</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
+          <t>ADR-200, подраздел «Как реализовано: несколько задач в одной реплике» (в разделе «Оркестрация агента»); ADR-100, раздел «Несколько задач в одной реплике»; ADR-400</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
+          <t>Предел 300 знаков, перечни глаголов и операций подобраны автором на 136 обращениях регистра, не на репликах чата; точность и полнота на размеченных репликах не измерены. Регистрация только по первой части, из условий проверяется лишь долг, путь `generate` не разбирается, второй бланк перезапишет первый.</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
+          <t>Проверка детектора на размеченных репликах чата (точность, полнота, подбор предела и перечней); регистрация нескольких обращений из одной реплики (несколько черновиков, подтверждение каждого, виджет); условия помимо долга; путь `generate`, лимиты и порядок частей.</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
+          <t>Python; правила на регулярных выражениях; метрика `assistant_multi_intent_total`; состояние диалога в Redis.</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
+          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — условие перехода на LangGraph (триггер 4).</t>
         </is>
       </c>
       <c r="M39" s="17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N39" s="17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O39" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
+          <t>Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)</t>
         </is>
       </c>
       <c r="P39" s="14" t="inlineStr">
@@ -4189,51 +4189,137 @@
       <c r="U39" s="15" t="n"/>
       <c r="V39" s="9" t="inlineStr">
         <is>
+          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
+        </is>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="O40" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
+        </is>
+      </c>
+      <c r="P40" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q40" s="15" t="n"/>
+      <c r="R40" s="15" t="n"/>
+      <c r="S40" s="16" t="n"/>
+      <c r="T40" s="16" t="n"/>
+      <c r="U40" s="15" t="n"/>
+      <c r="V40" s="9" t="inlineStr">
+        <is>
           <t>ADR-300; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="C41" s="26" t="inlineStr">
+    <row r="42">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>Цвет ячеек с оценкой:</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="C42" s="27" t="n"/>
-      <c r="D42" s="28" t="inlineStr">
+    <row r="43">
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="28" t="inlineStr">
         <is>
           <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="28" t="inlineStr">
+    <row r="44">
+      <c r="C44" s="29" t="n"/>
+      <c r="D44" s="28" t="inlineStr">
         <is>
           <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="C44" s="30" t="n"/>
-      <c r="D44" s="28" t="inlineStr">
+    <row r="45">
+      <c r="C45" s="30" t="n"/>
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="C45" s="31" t="n"/>
-      <c r="D45" s="28" t="inlineStr">
+    <row r="46">
+      <c r="C46" s="31" t="n"/>
+      <c r="D46" s="28" t="inlineStr">
         <is>
           <t>изменений на этом этапе нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V39"/>
+  <autoFilter ref="A2:V40"/>
   <mergeCells count="4">
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
@@ -4355,11 +4441,11 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>SUM('Матрица'!$M$3:$M$39)-SUMIF('Матрица'!$O$3:$O$39,"По триггеру*",'Матрица'!$M$3:$M$39)</f>
+        <f>SUM('Матрица'!$M$3:$M$40)-SUMIF('Матрица'!$O$3:$O$40,"По триггеру*",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="C5" s="34">
-        <f>SUM('Матрица'!$N$3:$N$39)-SUMIF('Матрица'!$O$3:$O$39,"По триггеру*",'Матрица'!$N$3:$N$39)</f>
+        <f>SUM('Матрица'!$N$3:$N$40)-SUMIF('Матрица'!$O$3:$O$40,"По триггеру*",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="D5" s="34">
@@ -4371,35 +4457,35 @@
         <v/>
       </c>
       <c r="F5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"ADR-600",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"ADR-600",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="G5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"ADR-600",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"ADR-600",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="H5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока*",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока*",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="I5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока*",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока*",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="J5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Оценка автора",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Оценка автора",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="K5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Оценка автора",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Оценка автора",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="L5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"По триггеру*",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"По триггеру*",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="M5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"По триггеру*",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"По триггеру*",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
     </row>
@@ -4410,11 +4496,11 @@
         </is>
       </c>
       <c r="B6" s="34">
-        <f>SUM('Матрица'!$S$3:$S$39)-SUMIF('Матрица'!$U$3:$U$39,"По триггеру*",'Матрица'!$S$3:$S$39)</f>
+        <f>SUM('Матрица'!$S$3:$S$40)-SUMIF('Матрица'!$U$3:$U$40,"По триггеру*",'Матрица'!$S$3:$S$40)</f>
         <v/>
       </c>
       <c r="C6" s="34">
-        <f>SUM('Матрица'!$T$3:$T$39)-SUMIF('Матрица'!$U$3:$U$39,"По триггеру*",'Матрица'!$T$3:$T$39)</f>
+        <f>SUM('Матрица'!$T$3:$T$40)-SUMIF('Матрица'!$U$3:$U$40,"По триггеру*",'Матрица'!$T$3:$T$40)</f>
         <v/>
       </c>
       <c r="D6" s="34">
@@ -4426,35 +4512,35 @@
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$39,"ADR-600",'Матрица'!$S$3:$S$39)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$40,"ADR-600",'Матрица'!$S$3:$S$40)</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$39,"ADR-600",'Матрица'!$T$3:$T$39)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$40,"ADR-600",'Матрица'!$T$3:$T$40)</f>
         <v/>
       </c>
       <c r="H6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$39,"Из блока*",'Матрица'!$S$3:$S$39)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$40,"Из блока*",'Матрица'!$S$3:$S$40)</f>
         <v/>
       </c>
       <c r="I6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$39,"Из блока*",'Матрица'!$T$3:$T$39)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$40,"Из блока*",'Матрица'!$T$3:$T$40)</f>
         <v/>
       </c>
       <c r="J6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$39,"Оценка автора",'Матрица'!$S$3:$S$39)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$40,"Оценка автора",'Матрица'!$S$3:$S$40)</f>
         <v/>
       </c>
       <c r="K6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$39,"Оценка автора",'Матрица'!$T$3:$T$39)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$40,"Оценка автора",'Матрица'!$T$3:$T$40)</f>
         <v/>
       </c>
       <c r="L6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$39,"По триггеру*",'Матрица'!$S$3:$S$39)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$40,"По триггеру*",'Матрица'!$S$3:$S$40)</f>
         <v/>
       </c>
       <c r="M6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$39,"По триггеру*",'Матрица'!$T$3:$T$39)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$40,"По триггеру*",'Матрица'!$T$3:$T$40)</f>
         <v/>
       </c>
     </row>
@@ -4621,11 +4707,11 @@
         <v>17</v>
       </c>
       <c r="D15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="F15" s="44">
@@ -4651,11 +4737,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="E16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="F16" s="44">
@@ -4681,11 +4767,11 @@
         <v>51</v>
       </c>
       <c r="D17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="E17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="F17" s="44">
@@ -4711,11 +4797,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="E18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="F18" s="44">
@@ -4741,11 +4827,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="F19" s="44">
@@ -4771,11 +4857,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="F20" s="44">
@@ -4801,11 +4887,11 @@
         <v>14</v>
       </c>
       <c r="D21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="F21" s="44">
@@ -4831,11 +4917,11 @@
         <v>18</v>
       </c>
       <c r="D22" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$40)</f>
         <v/>
       </c>
       <c r="E22" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$39,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$39)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$40)</f>
         <v/>
       </c>
       <c r="F22" s="44">
@@ -4998,7 +5084,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>GPU-сервер под эмбеддинги и реранкер</t>
+          <t>GPU-сервер под эмбеддинги и реранкер (только если владелец добавит GPU-узел: в кластере GPU нет)</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -5134,7 +5220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6085,11 +6171,11 @@
     </row>
     <row r="42">
       <c r="A42" s="9">
-        <f>'Матрица'!A37</f>
+        <f>'Матрица'!A36</f>
         <v/>
       </c>
       <c r="B42" s="9">
-        <f>'Матрица'!C37</f>
+        <f>'Матрица'!C36</f>
         <v/>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -6098,15 +6184,15 @@
         </is>
       </c>
       <c r="D42" s="34">
-        <f>'Матрица'!M37</f>
+        <f>'Матрица'!M36</f>
         <v/>
       </c>
       <c r="E42" s="34">
-        <f>'Матрица'!N37</f>
-        <v/>
-      </c>
-      <c r="F42" s="18">
-        <f>'Матрица'!O37</f>
+        <f>'Матрица'!N36</f>
+        <v/>
+      </c>
+      <c r="F42" s="13">
+        <f>'Матрица'!O36</f>
         <v/>
       </c>
     </row>
@@ -6164,104 +6250,131 @@
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="43" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="9">
+        <f>'Матрица'!A40</f>
+        <v/>
+      </c>
+      <c r="B45" s="9">
+        <f>'Матрица'!C40</f>
+        <v/>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D45" s="34">
+        <f>'Матрица'!M40</f>
+        <v/>
+      </c>
+      <c r="E45" s="34">
+        <f>'Матрица'!N40</f>
+        <v/>
+      </c>
+      <c r="F45" s="18">
+        <f>'Матрица'!O40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -6271,10 +6384,9 @@
   <mergeCells count="16">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C53:F53"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C53:F53"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="C4:F4"/>
@@ -6284,6 +6396,7 @@
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C55:F55"/>
     <mergeCell ref="C50:F50"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6804,7 +6917,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="75" customHeight="1">
+    <row r="20" ht="105" customHeight="1">
       <c r="A20" s="50" t="n">
         <v>16</v>
       </c>
@@ -6820,7 +6933,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing»): MVP — 6 узлов (3 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ, 1 GPU-узел с видеокартой 24 ГБ), тираж — 8 (4 общих, 2 данных, 1 GPU, 1 узел под собственную модель с A100 80 ГБ). Диск под тома ≈176 ГиБ на MVP и ≈667 ГиБ на тираже. Стоимость серверов не оценена.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈172 ГиБ на MVP и ≈663 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -6909,7 +7022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7013,306 +7126,164 @@
     <row r="8" ht="32" customHeight="1">
       <c r="B8" s="11" t="inlineStr">
         <is>
+          <t>GPU в кластере</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7,2 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру (решение владельца, цена не оценена); переключатель на листе «Sizing».</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
           <t>Узлы</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Загрузка узла по запросам не выше 70%. Класс узлов: общий — 8 vCPU / 16 ГиБ; данных — 8 vCPU / 32 ГиБ с NVMe; GPU — 8 vCPU / 32 ГиБ и видеокарта 24 ГБ; LLM (тираж) — 16 vCPU / 128 ГиБ и A100 80 ГБ.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="D10" s="51" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>GPU-узел в кластере (1 — есть, 0 — нет)</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="52" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="M10" s="51" t="inlineStr">
+      <c r="M12" s="52" t="inlineStr">
         <is>
           <t>Тираж</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Пул</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Компонент</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Реплик</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>vCPU на под</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>ОЗУ, ГиБ на под</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Диск, ГиБ на под</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Видеопамять, ГиБ на под</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>vCPU всего</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>ОЗУ всего, ГиБ</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Диск всего, ГиБ</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Видеопамять всего, ГиБ</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Реплик</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>vCPU на под</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>ОЗУ, ГиБ на под</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>Диск, ГиБ на под</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>Видеопамять, ГиБ на под</t>
         </is>
       </c>
-      <c r="R11" s="5" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>vCPU всего</t>
         </is>
       </c>
-      <c r="S11" s="5" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>ОЗУ всего, ГиБ</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>Диск всего, ГиБ</t>
         </is>
       </c>
-      <c r="U11" s="5" t="inlineStr">
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>Видеопамять всего, ГиБ</t>
         </is>
       </c>
-      <c r="V11" s="5" t="inlineStr">
+      <c r="V13" s="5" t="inlineStr">
         <is>
           <t>Основание</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Ingress (nginx)</t>
-        </is>
-      </c>
-      <c r="D12" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F12" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="53">
-        <f>D12*E12</f>
-        <v/>
-      </c>
-      <c r="J12" s="53">
-        <f>D12*F12</f>
-        <v/>
-      </c>
-      <c r="K12" s="53">
-        <f>D12*G12</f>
-        <v/>
-      </c>
-      <c r="L12" s="53">
-        <f>D12*H12</f>
-        <v/>
-      </c>
-      <c r="M12" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O12" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P12" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="53">
-        <f>M12*N12</f>
-        <v/>
-      </c>
-      <c r="S12" s="53">
-        <f>M12*O12</f>
-        <v/>
-      </c>
-      <c r="T12" s="53">
-        <f>M12*P12</f>
-        <v/>
-      </c>
-      <c r="U12" s="53">
-        <f>M12*Q12</f>
-        <v/>
-      </c>
-      <c r="V12" s="9" t="inlineStr">
-        <is>
-          <t>Допущение. Внешний трафик — единицы запросов в секунду.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Vault</t>
-        </is>
-      </c>
-      <c r="D13" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F13" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G13" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="53">
-        <f>D13*E13</f>
-        <v/>
-      </c>
-      <c r="J13" s="53">
-        <f>D13*F13</f>
-        <v/>
-      </c>
-      <c r="K13" s="53">
-        <f>D13*G13</f>
-        <v/>
-      </c>
-      <c r="L13" s="53">
-        <f>D13*H13</f>
-        <v/>
-      </c>
-      <c r="M13" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O13" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P13" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="53">
-        <f>M13*N13</f>
-        <v/>
-      </c>
-      <c r="S13" s="53">
-        <f>M13*O13</f>
-        <v/>
-      </c>
-      <c r="T13" s="53">
-        <f>M13*P13</f>
-        <v/>
-      </c>
-      <c r="U13" s="53">
-        <f>M13*Q13</f>
-        <v/>
-      </c>
-      <c r="V13" s="9" t="inlineStr">
-        <is>
-          <t>Допущение. Инжектор секретов и cert-manager — отдельной строкой не выделены (≈0,1 vCPU / 0,1 ГиБ).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -7321,22 +7292,22 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>AI-виджет (статические файлы)</t>
-        </is>
-      </c>
-      <c r="D14" s="52" t="n">
+          <t>Ingress (nginx)</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F14" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="52" t="n">
+      <c r="E14" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F14" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G14" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="52" t="n">
+      <c r="H14" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="53">
@@ -7355,19 +7326,19 @@
         <f>D14*H14</f>
         <v/>
       </c>
-      <c r="M14" s="52" t="n">
+      <c r="M14" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="N14" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O14" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P14" s="52" t="n">
+      <c r="N14" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O14" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P14" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="52" t="n">
+      <c r="Q14" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="53">
@@ -7388,13 +7359,13 @@
       </c>
       <c r="V14" s="9" t="inlineStr">
         <is>
-          <t>Допущение. На стенде три статических файла.</t>
+          <t>Допущение. Внешний трафик — единицы запросов в секунду.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
@@ -7403,22 +7374,22 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Backend (API, классификация, поиск, сборка ответа)</t>
-        </is>
-      </c>
-      <c r="D15" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="52" t="n">
+          <t>Vault</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F15" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G15" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="53">
@@ -7437,19 +7408,19 @@
         <f>D15*H15</f>
         <v/>
       </c>
-      <c r="M15" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" s="52" t="n">
+      <c r="M15" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="52" t="n">
+      <c r="N15" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O15" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P15" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="P15" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="52" t="n">
+      <c r="Q15" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="53">
@@ -7470,13 +7441,13 @@
       </c>
       <c r="V15" s="9" t="inlineStr">
         <is>
-          <t>Замер: путь без модели — 117 запросов/с на процесс (8,5 мс CPU). 2 реплики нужны для отказоустойчивости, а не для пропускной способности; ОЗУ — допущение (эмбеддер и обезличиватель вынесены).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t>Допущение. Инжектор секретов и cert-manager — отдельной строкой не выделены (≈0,1 vCPU / 0,1 ГиБ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -7485,22 +7456,22 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>LLM Gateway (лимиты, обезличивание, проверка ответа)</t>
-        </is>
-      </c>
-      <c r="D16" s="52" t="n">
+          <t>AI-виджет (статические файлы)</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F16" s="52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G16" s="52" t="n">
+      <c r="E16" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="52" t="n">
+      <c r="H16" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="53">
@@ -7519,19 +7490,19 @@
         <f>D16*H16</f>
         <v/>
       </c>
-      <c r="M16" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P16" s="52" t="n">
+      <c r="M16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O16" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P16" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="52" t="n">
+      <c r="Q16" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="53">
@@ -7552,13 +7523,13 @@
       </c>
       <c r="V16" s="9" t="inlineStr">
         <is>
-          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,04 ядра на MVP, 0,41 на тираже (максимум прогноза); на ответах в 2 000 знаков до 2,1 ядра (3 реплики × 1 vCPU + предел 2). После оптимизации проверки на потоке запас вырастет.</t>
+          <t>Допущение. На стенде три статических файла.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
@@ -7567,22 +7538,22 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Billing Adapter, оркестратор записи (Этап 2)</t>
-        </is>
-      </c>
-      <c r="D17" s="52" t="n">
+          <t>Backend (API, классификация, поиск, сборка ответа)</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F17" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G17" s="52" t="n">
+      <c r="E17" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="52" t="n">
+      <c r="H17" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="53">
@@ -7601,19 +7572,19 @@
         <f>D17*H17</f>
         <v/>
       </c>
-      <c r="M17" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O17" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P17" s="52" t="n">
+      <c r="M17" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="52" t="n">
+      <c r="Q17" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="53">
@@ -7634,13 +7605,13 @@
       </c>
       <c r="V17" s="9" t="inlineStr">
         <is>
-          <t>Допущение. До 2 800 диалогов с записью в месяц на MVP и 31 500 на тираже (максимум прогноза, A6 = 40%) — нагрузка ничтожна.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>Замер: путь без модели — 117 запросов/с на процесс (8,5 мс CPU). 2 реплики нужны для отказоустойчивости, а не для пропускной способности; ОЗУ — допущение (эмбеддер и обезличиватель вынесены).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -7649,22 +7620,22 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Document Generator (PDF, Этап 2)</t>
-        </is>
-      </c>
-      <c r="D18" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="52" t="n">
+          <t>LLM Gateway (лимиты, обезличивание, проверка ответа)</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="51" t="n">
         <v>0.5</v>
       </c>
-      <c r="F18" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="52" t="n">
+      <c r="F18" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="52" t="n">
+      <c r="H18" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="53">
@@ -7683,19 +7654,19 @@
         <f>D18*H18</f>
         <v/>
       </c>
-      <c r="M18" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="N18" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O18" s="52" t="n">
+      <c r="M18" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="P18" s="52" t="n">
+      <c r="O18" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P18" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="52" t="n">
+      <c r="Q18" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="53">
@@ -7716,13 +7687,13 @@
       </c>
       <c r="V18" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью (до 31 500 в месяц на тираже).</t>
+          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,04 ядра на MVP, 0,41 на тираже (максимум прогноза); на ответах в 2 000 знаков до 2,1 ядра (3 реплики × 1 vCPU + предел 2). После оптимизации проверки на потоке запас вырастет.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
@@ -7731,22 +7702,22 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>ETL индексации (CronJob, окно 02:00–05:00)</t>
-        </is>
-      </c>
-      <c r="D19" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="52" t="n">
+          <t>Billing Adapter, оркестратор записи (Этап 2)</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="52" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="52" t="n">
+      <c r="E19" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G19" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="53">
@@ -7765,19 +7736,19 @@
         <f>D19*H19</f>
         <v/>
       </c>
-      <c r="M19" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="52" t="n">
+      <c r="M19" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="P19" s="52" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" s="52" t="n">
+      <c r="N19" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O19" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P19" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="53">
@@ -7798,13 +7769,13 @@
       </c>
       <c r="V19" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
+          <t>Допущение. До 2 800 диалогов с записью в месяц на MVP и 31 500 на тираже (максимум прогноза, A6 = 40%) — нагрузка ничтожна.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -7813,22 +7784,22 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Оценка качества (CronJob, ночной прогон)</t>
-        </is>
-      </c>
-      <c r="D20" s="52" t="n">
+          <t>Document Generator (PDF, Этап 2)</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="52" t="n">
+      <c r="E20" s="51" t="n">
         <v>0.5</v>
       </c>
-      <c r="F20" s="52" t="n">
+      <c r="F20" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="52" t="n">
+      <c r="G20" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="52" t="n">
+      <c r="H20" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="53">
@@ -7847,19 +7818,19 @@
         <f>D20*H20</f>
         <v/>
       </c>
-      <c r="M20" s="52" t="n">
+      <c r="M20" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O20" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O20" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="52" t="n">
+      <c r="P20" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="52" t="n">
+      <c r="Q20" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="53">
@@ -7880,13 +7851,13 @@
       </c>
       <c r="V20" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
+          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью (до 31 500 в месяц на тираже).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
@@ -7895,22 +7866,23 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Prometheus</t>
-        </is>
-      </c>
-      <c r="D21" s="52" t="n">
+          <t>ETL индексации (CronJob, окно 02:00–05:00) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D21" s="51">
+        <f>1*$C$10</f>
+        <v/>
+      </c>
+      <c r="E21" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F21" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" s="52" t="n">
+      <c r="F21" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="53">
@@ -7929,19 +7901,20 @@
         <f>D21*H21</f>
         <v/>
       </c>
-      <c r="M21" s="52" t="n">
+      <c r="M21" s="51">
+        <f>1*$C$10</f>
+        <v/>
+      </c>
+      <c r="N21" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O21" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" s="52" t="n">
+      <c r="O21" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="53">
@@ -7962,13 +7935,13 @@
       </c>
       <c r="V21" s="9" t="inlineStr">
         <is>
-          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
+          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -7977,22 +7950,22 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Grafana</t>
-        </is>
-      </c>
-      <c r="D22" s="52" t="n">
+          <t>Оценка качества (CronJob, ночной прогон)</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F22" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G22" s="52" t="n">
+      <c r="E22" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="52" t="n">
+      <c r="G22" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="53">
@@ -8011,19 +7984,19 @@
         <f>D22*H22</f>
         <v/>
       </c>
-      <c r="M22" s="52" t="n">
+      <c r="M22" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O22" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P22" s="52" t="n">
+      <c r="N22" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O22" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" s="52" t="n">
+      <c r="P22" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="53">
@@ -8044,13 +8017,13 @@
       </c>
       <c r="V22" s="9" t="inlineStr">
         <is>
-          <t>Допущение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
@@ -8059,22 +8032,22 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Loki</t>
-        </is>
-      </c>
-      <c r="D23" s="52" t="n">
+          <t>Prometheus</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="52" t="n">
+      <c r="E23" s="51" t="n">
         <v>0.5</v>
       </c>
-      <c r="F23" s="52" t="n">
+      <c r="F23" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="H23" s="52" t="n">
+      <c r="G23" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="53">
@@ -8093,19 +8066,19 @@
         <f>D23*H23</f>
         <v/>
       </c>
-      <c r="M23" s="52" t="n">
+      <c r="M23" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="52" t="n">
+      <c r="N23" s="51" t="n">
         <v>0.5</v>
       </c>
-      <c r="O23" s="52" t="n">
+      <c r="O23" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="P23" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="52" t="n">
+      <c r="P23" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="53">
@@ -8126,13 +8099,13 @@
       </c>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом.</t>
+          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -8141,22 +8114,22 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Alertmanager</t>
-        </is>
-      </c>
-      <c r="D24" s="52" t="n">
+          <t>Grafana</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G24" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="52" t="n">
+      <c r="E24" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F24" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G24" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="53">
@@ -8175,19 +8148,19 @@
         <f>D24*H24</f>
         <v/>
       </c>
-      <c r="M24" s="52" t="n">
+      <c r="M24" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O24" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P24" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="52" t="n">
+      <c r="N24" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O24" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P24" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="53">
@@ -8212,33 +8185,33 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Qdrant</t>
-        </is>
-      </c>
-      <c r="D25" s="52" t="n">
+          <t>Loki</t>
+        </is>
+      </c>
+      <c r="D25" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="52" t="n">
+      <c r="E25" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="H25" s="52" t="n">
+      <c r="G25" s="51" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="53">
@@ -8257,19 +8230,19 @@
         <f>D25*H25</f>
         <v/>
       </c>
-      <c r="M25" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" s="52" t="n">
+      <c r="M25" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O25" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="P25" s="52" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" s="52" t="n">
+      <c r="N25" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O25" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="51" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="53">
@@ -8290,37 +8263,37 @@
       </c>
       <c r="V25" s="9" t="inlineStr">
         <is>
-          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="90" customHeight="1">
+          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Postgres (обращения, профиль, телеметрия, журнал диалогов)</t>
-        </is>
-      </c>
-      <c r="D26" s="52" t="n">
+          <t>Alertmanager</t>
+        </is>
+      </c>
+      <c r="D26" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="H26" s="52" t="n">
+      <c r="E26" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F26" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="53">
@@ -8339,19 +8312,19 @@
         <f>D26*H26</f>
         <v/>
       </c>
-      <c r="M26" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" s="52" t="n">
+      <c r="M26" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="P26" s="52" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q26" s="52" t="n">
+      <c r="N26" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O26" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="53">
@@ -8372,13 +8345,13 @@
       </c>
       <c r="V26" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (заложено 3 КБ на абонента; по примеру прототипа — 0,7 КБ на счёт в CSV); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t>Допущение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="50" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
@@ -8387,22 +8360,22 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Redis (квоты и сессии)</t>
-        </is>
-      </c>
-      <c r="D27" s="52" t="n">
+          <t>Qdrant</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F27" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G27" s="52" t="n">
+      <c r="E27" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="52" t="n">
+      <c r="F27" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="53">
@@ -8421,19 +8394,19 @@
         <f>D27*H27</f>
         <v/>
       </c>
-      <c r="M27" s="52" t="n">
+      <c r="M27" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O27" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P27" s="52" t="n">
+      <c r="N27" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="52" t="n">
+      <c r="O27" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="53">
@@ -8454,13 +8427,13 @@
       </c>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="90" customHeight="1">
       <c r="A28" s="50" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -8469,22 +8442,22 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>MinIO (документы, копии, снимки)</t>
-        </is>
-      </c>
-      <c r="D28" s="52" t="n">
+          <t>Postgres (обращения, профиль, телеметрия, журнал диалогов)</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="52" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F28" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G28" s="52" t="n">
-        <v>100</v>
-      </c>
-      <c r="H28" s="52" t="n">
+      <c r="E28" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="51" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" s="51" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="53">
@@ -8503,19 +8476,19 @@
         <f>D28*H28</f>
         <v/>
       </c>
-      <c r="M28" s="52" t="n">
+      <c r="M28" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O28" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" s="52" t="n">
-        <v>400</v>
-      </c>
-      <c r="Q28" s="52" t="n">
+      <c r="O28" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q28" s="51" t="n">
         <v>0</v>
       </c>
       <c r="R28" s="53">
@@ -8536,38 +8509,38 @@
       </c>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (заложено 3 КБ на абонента; по примеру прототипа — 0,7 КБ на счёт в CSV); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Эмбеддинги (BGE-M3, inference)</t>
-        </is>
-      </c>
-      <c r="D29" s="52" t="n">
+          <t>Redis (квоты и сессии)</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="52" t="n">
+      <c r="E29" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F29" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G29" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="G29" s="52" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" s="52" t="n">
-        <v>2</v>
+      <c r="H29" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I29" s="53">
         <f>D29*E29</f>
@@ -8585,20 +8558,20 @@
         <f>D29*H29</f>
         <v/>
       </c>
-      <c r="M29" s="52" t="n">
+      <c r="M29" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O29" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P29" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="P29" s="52" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="52" t="n">
-        <v>2</v>
+      <c r="Q29" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="R29" s="53">
         <f>M29*N29</f>
@@ -8618,38 +8591,38 @@
       </c>
       <c r="V29" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32; прежние 4,25 ГБ — две копии в кэше). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="50" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Реранкер (BGE-reranker-v2-m3, inference)</t>
-        </is>
-      </c>
-      <c r="D30" s="52" t="n">
+          <t>MinIO (документы, копии, снимки)</t>
+        </is>
+      </c>
+      <c r="D30" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="52" t="n">
-        <v>1.5</v>
+      <c r="E30" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F30" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="51" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="I30" s="53">
         <f>D30*E30</f>
@@ -8667,20 +8640,20 @@
         <f>D30*H30</f>
         <v/>
       </c>
-      <c r="M30" s="52" t="n">
+      <c r="M30" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="52" t="n">
+      <c r="N30" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O30" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O30" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q30" s="52" t="n">
-        <v>1.5</v>
+      <c r="P30" s="51" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q30" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="R30" s="53">
         <f>M30*N30</f>
@@ -8700,38 +8673,39 @@
       </c>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>gpu-llm</t>
+          <t>gpu</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
-        </is>
-      </c>
-      <c r="D31" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="52" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" s="52" t="n">
-        <v>64</v>
-      </c>
-      <c r="G31" s="52" t="n">
-        <v>100</v>
-      </c>
-      <c r="H31" s="52" t="n">
-        <v>0</v>
+          <t>Эмбеддинги (BGE-M3, inference) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D31" s="51">
+        <f>1*$C$10</f>
+        <v/>
+      </c>
+      <c r="E31" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="I31" s="53">
         <f>D31*E31</f>
@@ -8749,20 +8723,21 @@
         <f>D31*H31</f>
         <v/>
       </c>
-      <c r="M31" s="52" t="n">
+      <c r="M31" s="51">
+        <f>1*$C$10</f>
+        <v/>
+      </c>
+      <c r="N31" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="52" t="n">
-        <v>8</v>
-      </c>
-      <c r="O31" s="52" t="n">
-        <v>64</v>
-      </c>
-      <c r="P31" s="52" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q31" s="52" t="n">
-        <v>40</v>
+      <c r="O31" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="R31" s="53">
         <f>M31*N31</f>
@@ -8782,367 +8757,702 @@
       </c>
       <c r="V31" s="9" t="inlineStr">
         <is>
+          <t>Замер: веса 2,14 ГиБ (fp32; прежние 4,25 ГБ — две копии в кэше). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="50" t="n">
+        <v>19</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Реранкер (BGE-reranker-v2-m3, inference) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D32" s="51">
+        <f>1*$C$10</f>
+        <v/>
+      </c>
+      <c r="E32" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I32" s="53">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+      <c r="J32" s="53">
+        <f>D32*F32</f>
+        <v/>
+      </c>
+      <c r="K32" s="53">
+        <f>D32*G32</f>
+        <v/>
+      </c>
+      <c r="L32" s="53">
+        <f>D32*H32</f>
+        <v/>
+      </c>
+      <c r="M32" s="51">
+        <f>1*$C$10</f>
+        <v/>
+      </c>
+      <c r="N32" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R32" s="53">
+        <f>M32*N32</f>
+        <v/>
+      </c>
+      <c r="S32" s="53">
+        <f>M32*O32</f>
+        <v/>
+      </c>
+      <c r="T32" s="53">
+        <f>M32*P32</f>
+        <v/>
+      </c>
+      <c r="U32" s="53">
+        <f>M32*Q32</f>
+        <v/>
+      </c>
+      <c r="V32" s="9" t="inlineStr">
+        <is>
+          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>gpu-llm</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="51" t="n">
+        <v>64</v>
+      </c>
+      <c r="G33" s="51" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="53">
+        <f>D33*E33</f>
+        <v/>
+      </c>
+      <c r="J33" s="53">
+        <f>D33*F33</f>
+        <v/>
+      </c>
+      <c r="K33" s="53">
+        <f>D33*G33</f>
+        <v/>
+      </c>
+      <c r="L33" s="53">
+        <f>D33*H33</f>
+        <v/>
+      </c>
+      <c r="M33" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" s="51" t="n">
+        <v>64</v>
+      </c>
+      <c r="P33" s="51" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="51" t="n">
+        <v>40</v>
+      </c>
+      <c r="R33" s="53">
+        <f>M33*N33</f>
+        <v/>
+      </c>
+      <c r="S33" s="53">
+        <f>M33*O33</f>
+        <v/>
+      </c>
+      <c r="T33" s="53">
+        <f>M33*P33</f>
+        <v/>
+      </c>
+      <c r="U33" s="53">
+        <f>M33*Q33</f>
+        <v/>
+      </c>
+      <c r="V33" s="9" t="inlineStr">
+        <is>
           <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="C33" s="43" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="50" t="n">
+        <v>21</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Эмбеддинги (e5-small на CPU) [вариант без GPU]</t>
+        </is>
+      </c>
+      <c r="D34" s="51">
+        <f>2*(1-$C$10)</f>
+        <v/>
+      </c>
+      <c r="E34" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G34" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="53">
+        <f>D34*E34</f>
+        <v/>
+      </c>
+      <c r="J34" s="53">
+        <f>D34*F34</f>
+        <v/>
+      </c>
+      <c r="K34" s="53">
+        <f>D34*G34</f>
+        <v/>
+      </c>
+      <c r="L34" s="53">
+        <f>D34*H34</f>
+        <v/>
+      </c>
+      <c r="M34" s="51">
+        <f>2*(1-$C$10)</f>
+        <v/>
+      </c>
+      <c r="N34" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P34" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="53">
+        <f>M34*N34</f>
+        <v/>
+      </c>
+      <c r="S34" s="53">
+        <f>M34*O34</f>
+        <v/>
+      </c>
+      <c r="T34" s="53">
+        <f>M34*P34</f>
+        <v/>
+      </c>
+      <c r="U34" s="53">
+        <f>M34*Q34</f>
+        <v/>
+      </c>
+      <c r="V34" s="9" t="inlineStr">
+        <is>
+          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7,2 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>ETL индексации: эмбеддинги на CPU (CronJob) [вариант без GPU]</t>
+        </is>
+      </c>
+      <c r="D35" s="51">
+        <f>1*(1-$C$10)</f>
+        <v/>
+      </c>
+      <c r="E35" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="53">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+      <c r="J35" s="53">
+        <f>D35*F35</f>
+        <v/>
+      </c>
+      <c r="K35" s="53">
+        <f>D35*G35</f>
+        <v/>
+      </c>
+      <c r="L35" s="53">
+        <f>D35*H35</f>
+        <v/>
+      </c>
+      <c r="M35" s="51">
+        <f>1*(1-$C$10)</f>
+        <v/>
+      </c>
+      <c r="N35" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="53">
+        <f>M35*N35</f>
+        <v/>
+      </c>
+      <c r="S35" s="53">
+        <f>M35*O35</f>
+        <v/>
+      </c>
+      <c r="T35" s="53">
+        <f>M35*P35</f>
+        <v/>
+      </c>
+      <c r="U35" s="53">
+        <f>M35*Q35</f>
+        <v/>
+      </c>
+      <c r="V35" s="9" t="inlineStr">
+        <is>
+          <t>Расчёт по замеру: e5-small ≈27 мс на часть (машина с 12 потоками) → 30–100 тыс. частей ≈14–46 мин; на поде с 4 vCPU время не измерялось и может быть в 2–3 раза больше (окно 3 часа). Только в варианте без GPU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Итог по пулам узлов</t>
         </is>
       </c>
-      <c r="P33" s="9" t="inlineStr">
+      <c r="P37" s="9" t="inlineStr">
         <is>
           <t>Загрузка узла по запросам, не выше</t>
         </is>
       </c>
-      <c r="Q33" s="54" t="n">
+      <c r="Q37" s="54" t="n">
         <v>0.7</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Пул</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Класс узла</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>vCPU узла</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>ОЗУ узла, ГиБ</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Видеопамять узла, ГиБ</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Запас на потерю узла (1 — да)</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>MVP: vCPU</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>MVP: ОЗУ</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>MVP: видеопамять</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>MVP: узлов</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>Тираж: vCPU</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Тираж: ОЗУ</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>Тираж: видеопамять</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>Тираж: узлов</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="55">
-        <f>SUMIF($B$12:$B$31,$B35,$I$12:$I$31)</f>
-        <v/>
-      </c>
-      <c r="I35" s="55">
-        <f>SUMIF($B$12:$B$31,$B35,$J$12:$J$31)</f>
-        <v/>
-      </c>
-      <c r="J35" s="55">
-        <f>SUMIF($B$12:$B$31,$B35,$L$12:$L$31)</f>
-        <v/>
-      </c>
-      <c r="K35" s="56">
-        <f>IF(H35=0,0,ROUNDUP(MAX(H35/($Q$33*$D35),I35/($Q$33*$E35),IF($F35&gt;0,J35/($Q$33*$F35),0)),0)+$G35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="55">
-        <f>SUMIF($B$12:$B$31,$B35,$R$12:$R$31)</f>
-        <v/>
-      </c>
-      <c r="M35" s="55">
-        <f>SUMIF($B$12:$B$31,$B35,$S$12:$S$31)</f>
-        <v/>
-      </c>
-      <c r="N35" s="55">
-        <f>SUMIF($B$12:$B$31,$B35,$U$12:$U$31)</f>
-        <v/>
-      </c>
-      <c r="O35" s="56">
-        <f>IF(L35=0,0,ROUNDUP(MAX(L35/($Q$33*$D35),M35/($Q$33*$E35),IF($F35&gt;0,N35/($Q$33*$F35),0)),0)+$G35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Пул данных (NVMe)</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="55">
-        <f>SUMIF($B$12:$B$31,$B36,$I$12:$I$31)</f>
-        <v/>
-      </c>
-      <c r="I36" s="55">
-        <f>SUMIF($B$12:$B$31,$B36,$J$12:$J$31)</f>
-        <v/>
-      </c>
-      <c r="J36" s="55">
-        <f>SUMIF($B$12:$B$31,$B36,$L$12:$L$31)</f>
-        <v/>
-      </c>
-      <c r="K36" s="56">
-        <f>IF(H36=0,0,ROUNDUP(MAX(H36/($Q$33*$D36),I36/($Q$33*$E36),IF($F36&gt;0,J36/($Q$33*$F36),0)),0)+$G36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="55">
-        <f>SUMIF($B$12:$B$31,$B36,$R$12:$R$31)</f>
-        <v/>
-      </c>
-      <c r="M36" s="55">
-        <f>SUMIF($B$12:$B$31,$B36,$S$12:$S$31)</f>
-        <v/>
-      </c>
-      <c r="N36" s="55">
-        <f>SUMIF($B$12:$B$31,$B36,$U$12:$U$31)</f>
-        <v/>
-      </c>
-      <c r="O36" s="56">
-        <f>IF(L36=0,0,ROUNDUP(MAX(L36/($Q$33*$D36),M36/($Q$33*$E36),IF($F36&gt;0,N36/($Q$33*$F36),0)),0)+$G36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>gpu</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>GPU-пул (эмбеддинги, реранкер)</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="G37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="55">
-        <f>SUMIF($B$12:$B$31,$B37,$I$12:$I$31)</f>
-        <v/>
-      </c>
-      <c r="I37" s="55">
-        <f>SUMIF($B$12:$B$31,$B37,$J$12:$J$31)</f>
-        <v/>
-      </c>
-      <c r="J37" s="55">
-        <f>SUMIF($B$12:$B$31,$B37,$L$12:$L$31)</f>
-        <v/>
-      </c>
-      <c r="K37" s="56">
-        <f>IF(H37=0,0,ROUNDUP(MAX(H37/($Q$33*$D37),I37/($Q$33*$E37),IF($F37&gt;0,J37/($Q$33*$F37),0)),0)+$G37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="55">
-        <f>SUMIF($B$12:$B$31,$B37,$R$12:$R$31)</f>
-        <v/>
-      </c>
-      <c r="M37" s="55">
-        <f>SUMIF($B$12:$B$31,$B37,$S$12:$S$31)</f>
-        <v/>
-      </c>
-      <c r="N37" s="55">
-        <f>SUMIF($B$12:$B$31,$B37,$U$12:$U$31)</f>
-        <v/>
-      </c>
-      <c r="O37" s="56">
-        <f>IF(L37=0,0,ROUNDUP(MAX(L37/($Q$33*$D37),M37/($Q$33*$E37),IF($F37&gt;0,N37/($Q$33*$F37),0)),0)+$G37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>gpu-llm</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>GPU-пул генерации (тираж)</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>128</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="G38" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="55">
-        <f>SUMIF($B$12:$B$31,$B38,$I$12:$I$31)</f>
-        <v/>
-      </c>
-      <c r="I38" s="55">
-        <f>SUMIF($B$12:$B$31,$B38,$J$12:$J$31)</f>
-        <v/>
-      </c>
-      <c r="J38" s="55">
-        <f>SUMIF($B$12:$B$31,$B38,$L$12:$L$31)</f>
-        <v/>
-      </c>
-      <c r="K38" s="56">
-        <f>IF(H38=0,0,ROUNDUP(MAX(H38/($Q$33*$D38),I38/($Q$33*$E38),IF($F38&gt;0,J38/($Q$33*$F38),0)),0)+$G38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="55">
-        <f>SUMIF($B$12:$B$31,$B38,$R$12:$R$31)</f>
-        <v/>
-      </c>
-      <c r="M38" s="55">
-        <f>SUMIF($B$12:$B$31,$B38,$S$12:$S$31)</f>
-        <v/>
-      </c>
-      <c r="N38" s="55">
-        <f>SUMIF($B$12:$B$31,$B38,$U$12:$U$31)</f>
-        <v/>
-      </c>
-      <c r="O38" s="56">
-        <f>IF(L38=0,0,ROUNDUP(MAX(L38/($Q$33*$D38),M38/($Q$33*$E38),IF($F38&gt;0,N38/($Q$33*$F38),0)),0)+$G38)</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Итого узлов</t>
-        </is>
-      </c>
-      <c r="K39" s="57">
-        <f>SUM(K35:K38)</f>
-        <v/>
-      </c>
-      <c r="O39" s="57">
-        <f>SUM(O35:O38)</f>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="55">
+        <f>SUMIF($B$14:$B$35,$B39,$I$14:$I$35)</f>
+        <v/>
+      </c>
+      <c r="I39" s="55">
+        <f>SUMIF($B$14:$B$35,$B39,$J$14:$J$35)</f>
+        <v/>
+      </c>
+      <c r="J39" s="55">
+        <f>SUMIF($B$14:$B$35,$B39,$L$14:$L$35)</f>
+        <v/>
+      </c>
+      <c r="K39" s="56">
+        <f>IF(H39=0,0,ROUNDUP(MAX(H39/($Q$37*$D39),I39/($Q$37*$E39),IF($F39&gt;0,J39/($Q$37*$F39),0)),0)+$G39)</f>
+        <v/>
+      </c>
+      <c r="L39" s="55">
+        <f>SUMIF($B$14:$B$35,$B39,$R$14:$R$35)</f>
+        <v/>
+      </c>
+      <c r="M39" s="55">
+        <f>SUMIF($B$14:$B$35,$B39,$S$14:$S$35)</f>
+        <v/>
+      </c>
+      <c r="N39" s="55">
+        <f>SUMIF($B$14:$B$35,$B39,$U$14:$U$35)</f>
+        <v/>
+      </c>
+      <c r="O39" s="56">
+        <f>IF(L39=0,0,ROUNDUP(MAX(L39/($Q$37*$D39),M39/($Q$37*$E39),IF($F39&gt;0,N39/($Q$37*$F39),0)),0)+$G39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Пул данных (NVMe)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="55">
+        <f>SUMIF($B$14:$B$35,$B40,$I$14:$I$35)</f>
+        <v/>
+      </c>
+      <c r="I40" s="55">
+        <f>SUMIF($B$14:$B$35,$B40,$J$14:$J$35)</f>
+        <v/>
+      </c>
+      <c r="J40" s="55">
+        <f>SUMIF($B$14:$B$35,$B40,$L$14:$L$35)</f>
+        <v/>
+      </c>
+      <c r="K40" s="56">
+        <f>IF(H40=0,0,ROUNDUP(MAX(H40/($Q$37*$D40),I40/($Q$37*$E40),IF($F40&gt;0,J40/($Q$37*$F40),0)),0)+$G40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="55">
+        <f>SUMIF($B$14:$B$35,$B40,$R$14:$R$35)</f>
+        <v/>
+      </c>
+      <c r="M40" s="55">
+        <f>SUMIF($B$14:$B$35,$B40,$S$14:$S$35)</f>
+        <v/>
+      </c>
+      <c r="N40" s="55">
+        <f>SUMIF($B$14:$B$35,$B40,$U$14:$U$35)</f>
+        <v/>
+      </c>
+      <c r="O40" s="56">
+        <f>IF(L40=0,0,ROUNDUP(MAX(L40/($Q$37*$D40),M40/($Q$37*$E40),IF($F40&gt;0,N40/($Q$37*$F40),0)),0)+$G40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>gpu</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>GPU-пул (эмбеддинги, реранкер)</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="55">
+        <f>SUMIF($B$14:$B$35,$B41,$I$14:$I$35)</f>
+        <v/>
+      </c>
+      <c r="I41" s="55">
+        <f>SUMIF($B$14:$B$35,$B41,$J$14:$J$35)</f>
+        <v/>
+      </c>
+      <c r="J41" s="55">
+        <f>SUMIF($B$14:$B$35,$B41,$L$14:$L$35)</f>
+        <v/>
+      </c>
+      <c r="K41" s="56">
+        <f>IF(H41=0,0,ROUNDUP(MAX(H41/($Q$37*$D41),I41/($Q$37*$E41),IF($F41&gt;0,J41/($Q$37*$F41),0)),0)+$G41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="55">
+        <f>SUMIF($B$14:$B$35,$B41,$R$14:$R$35)</f>
+        <v/>
+      </c>
+      <c r="M41" s="55">
+        <f>SUMIF($B$14:$B$35,$B41,$S$14:$S$35)</f>
+        <v/>
+      </c>
+      <c r="N41" s="55">
+        <f>SUMIF($B$14:$B$35,$B41,$U$14:$U$35)</f>
+        <v/>
+      </c>
+      <c r="O41" s="56">
+        <f>IF(L41=0,0,ROUNDUP(MAX(L41/($Q$37*$D41),M41/($Q$37*$E41),IF($F41&gt;0,N41/($Q$37*$F41),0)),0)+$G41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>gpu-llm</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>GPU-пул генерации (тираж)</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="55">
+        <f>SUMIF($B$14:$B$35,$B42,$I$14:$I$35)</f>
+        <v/>
+      </c>
+      <c r="I42" s="55">
+        <f>SUMIF($B$14:$B$35,$B42,$J$14:$J$35)</f>
+        <v/>
+      </c>
+      <c r="J42" s="55">
+        <f>SUMIF($B$14:$B$35,$B42,$L$14:$L$35)</f>
+        <v/>
+      </c>
+      <c r="K42" s="56">
+        <f>IF(H42=0,0,ROUNDUP(MAX(H42/($Q$37*$D42),I42/($Q$37*$E42),IF($F42&gt;0,J42/($Q$37*$F42),0)),0)+$G42)</f>
+        <v/>
+      </c>
+      <c r="L42" s="55">
+        <f>SUMIF($B$14:$B$35,$B42,$R$14:$R$35)</f>
+        <v/>
+      </c>
+      <c r="M42" s="55">
+        <f>SUMIF($B$14:$B$35,$B42,$S$14:$S$35)</f>
+        <v/>
+      </c>
+      <c r="N42" s="55">
+        <f>SUMIF($B$14:$B$35,$B42,$U$14:$U$35)</f>
+        <v/>
+      </c>
+      <c r="O42" s="56">
+        <f>IF(L42=0,0,ROUNDUP(MAX(L42/($Q$37*$D42),M42/($Q$37*$E42),IF($F42&gt;0,N42/($Q$37*$F42),0)),0)+$G42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Итого узлов</t>
+        </is>
+      </c>
+      <c r="K43" s="57">
+        <f>SUM(K39:K42)</f>
+        <v/>
+      </c>
+      <c r="O43" s="57">
+        <f>SUM(O39:O42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="11" t="inlineStr">
+        <is>
           <t>Диск под тома, ГиБ</t>
         </is>
       </c>
-      <c r="K40" s="58">
-        <f>SUM($K$12:$K$31)</f>
-        <v/>
-      </c>
-      <c r="O40" s="58">
-        <f>SUM($T$12:$T$31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="33" t="inlineStr">
+      <c r="K44" s="58">
+        <f>SUM($K$14:$K$35)</f>
+        <v/>
+      </c>
+      <c r="O44" s="58">
+        <f>SUM($T$14:$T$35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); управляющая часть Kubernetes размещена на трёх узлах общего пула (допущение); нагрузочный тест не проводился.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="D10:L10"/>
+  <mergeCells count="9">
     <mergeCell ref="C4:U4"/>
+    <mergeCell ref="M12:U12"/>
     <mergeCell ref="C5:U5"/>
-    <mergeCell ref="M10:U10"/>
     <mergeCell ref="C8:U8"/>
+    <mergeCell ref="C9:U9"/>
     <mergeCell ref="C3:U3"/>
     <mergeCell ref="C7:U7"/>
+    <mergeCell ref="D12:L12"/>
     <mergeCell ref="C6:U6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1607,7 +1607,7 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>В кластере владельца GPU нет: на MVP — e5-small на CPU (36–37 мс на запрос, замер); BGE-M3 на GPU — только если владелец добавит GPU-узел (строка «GPU-узел в кластере владельца»). Модель выбирается по тесту 4–5 моделей (e5-small, e5-large, BGE-M3, модели, дообученные на русском) на размеченном наборе из живых обращений; пороги подбираются под каждую модель (ADR-600, «Тест моделей эмбеддингов для MVP»). Размеченный набор берётся из строки «Анализ всех типов…».</t>
+          <t>В кластере владельца GPU нет: на MVP — e5-small на CPU (36–37 мс на запрос, замер); BGE-M3 на GPU — только если владелец после проверки на реальных данных решит добавить GPU-узел (строка «GPU-узел в кластере владельца»); сами тесты BGE-M3 идут офлайн на CPU. Модель выбирается по тесту 4–5 моделей (e5-small, e5-large, BGE-M3, модели, дообученные на русском) на размеченном наборе из живых обращений; пороги подбираются под каждую модель (ADR-600, «Тест моделей эмбеддингов для MVP»). Размеченный набор берётся из строки «Анализ всех типов…».</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только при GPU-узле. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (5–7 чел-дн); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Качество реранкеров проверяется офлайн на CPU. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (5–7 чел-дн); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>GPU-узел в кластере владельца (по решению)</t>
+          <t>GPU-узел в кластере владельца (решение после проверки на реальных данных)</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7,2 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Решение за владельцем до начала теста моделей (ADR-200, «Почему Kubernetes», ADR-600).</t>
+          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7,2 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Владелец примет решение о GPU-узле только после проверки на реальных данных (24.09.2026): тест моделей идёт на CPU, скорость на GPU — коротким замером на временной видеокарте (ADR-200, «Почему Kubernetes», ADR-600).</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Почему Kubernetes, а не другая оркестрация» (пункт «GPU»); ADR-300, раздел 2; ADR-600, «GPU-узел в кластере владельца — по решению»</t>
+          <t>ADR-200, подраздел «Почему Kubernetes, а не другая оркестрация» (пункт «GPU»); ADR-300, раздел 2; ADR-600, «GPU-узел в кластере владельца — решение после проверки на реальных данных»</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Закупка сервера с видеокартой и подключение к общему кластеру: драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом (3–5 чел-дн, без закупки).</t>
+          <t>Решение — после проверки на реальных данных. Порядок: (1) качество всех кандидатов, включая BGE-M3 и реранкеры, на размеченных живых обращениях офлайн на CPU; (2) короткий замер скорости на временной видеокарте на синтетических текстах (1–2 чел-дн, оценка автора, в итог не входит; где взять карту, не определено); (3) свод; (4) решение владельца. Критерий-предложение автора, не расчёт: покупать, если лучшая GPU-конфигурация даёт выигрыш не менее 5 п.п. по hit@3 (или MRR) над лучшей CPU-моделью и укладывается в 100 мс. Если решение — покупать: закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>Только по решению владельца: без GPU-узла тест BGE-M3 и реранкера смысла не имеет. Не входит в итог сметы — показана отдельным столбцом.</t>
+          <t>Тест BGE-M3 и реранкеров остаётся в плане при любом исходе: он и даёт основание для решения. Строка отражает работы на случай покупки и в итог сметы не входит.</t>
         </is>
       </c>
       <c r="M36" s="12" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="O36" s="13" t="inlineStr">
         <is>
-          <t>По триггеру (решение владельца: GPU-узел, оценка автора)</t>
+          <t>По триггеру (решение владельца после проверки на реальных данных; оценка автора)</t>
         </is>
       </c>
       <c r="P36" s="14" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7,2 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру (решение владельца, цена не оценена); переключатель на листе «Sizing».</t>
+          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7,2 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру: владелец решит только после проверки на реальных данных (цена не оценена); переключатель на листе «Sizing».</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Решение — после проверки на реальных данных. Порядок: (1) качество всех кандидатов, включая BGE-M3 и реранкеры, на размеченных живых обращениях офлайн на CPU; (2) короткий замер скорости на временной видеокарте на синтетических текстах (1–2 чел-дн, оценка автора, в итог не входит; где взять карту, не определено); (3) свод; (4) решение владельца. Критерий-предложение автора, не расчёт: покупать, если лучшая GPU-конфигурация даёт выигрыш не менее 5 п.п. по hit@3 (или MRR) над лучшей CPU-моделью и укладывается в 100 мс. Если решение — покупать: закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
+          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU; (2) CPU + Яндекс (управляемые модели, эмбеддинги через API; тарифы, качество и задержка не проверялись, нужно согласование с ИБ; что именно понимается под «Яндекс», уточнить); (3) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена); (4) покупка — по итогам аренды, решение владельца. «Не подошёл» — не укладывается в 100 мс P99 или качество на размеченных живых обращениях ниже требуемого (уровень задаёт владелец до теста). Критерий-предложение автора, не расчёт: покупать, если лучшая GPU-конфигурация даёт выигрыш не менее 5 п.п. по hit@3 (или MRR) над лучшей CPU-моделью и укладывается в 100 мс. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R37" s="9" t="inlineStr">
         <is>
-          <t>Аренда исключена не по цене, а по триггеру: облачный GPU считается внешним сервисом.</t>
+          <t>Аренда исключена не по цене, а по триггеру (речь о собственной модели генерации; для проверки эмбеддингов и реранкера на MVP аренда на месяц допустима): облачный GPU считается внешним сервисом.</t>
         </is>
       </c>
       <c r="S37" s="20" t="n">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU; (2) CPU + Яндекс (управляемые модели, эмбеддинги через API; тарифы, качество и задержка не проверялись, нужно согласование с ИБ; что именно понимается под «Яндекс», уточнить); (3) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена); (4) покупка — по итогам аренды, решение владельца. «Не подошёл» — не укладывается в 100 мс P99 или качество на размеченных живых обращениях ниже требуемого (уровень задаёт владелец до теста). Критерий-предложение автора, не расчёт: покупать, если лучшая GPU-конфигурация даёт выигрыш не менее 5 п.п. по hit@3 (или MRR) над лучшей CPU-моделью и укладывается в 100 мс. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
+          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. «Не подошёл» — поиск на CPU не укладывается в 100 мс P99 или качество поиска на размеченных живых обращениях ниже требуемого (уровень задаёт владелец до теста). Критерий-предложение автора, не расчёт: покупать, если лучшая GPU-конфигурация даёт выигрыш не менее 5 п.п. по hit@3 (или MRR) над лучшей CPU-моделью и укладывается в 100 мс. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. «Не подошёл» — поиск на CPU не укладывается в 100 мс P99 или качество поиска на размеченных живых обращениях ниже требуемого (уровень задаёт владелец до теста). Критерий-предложение автора, не расчёт: покупать, если лучшая GPU-конфигурация даёт выигрыш не менее 5 п.п. по hit@3 (или MRR) над лучшей CPU-моделью и укладывается в 100 мс. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
+          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны заказчиком проекта 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Качество реранкеров проверяется офлайн на CPU. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (5–7 чел-дн); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="M11" s="17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N11" s="17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O11" s="18" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="B17" s="34" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C17" s="34" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D17" s="34">
         <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$40)</f>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>≈7–10 недель: классификатор 8–12 + эмбеддинги 10–14 + реранкер 7–10 + судья 6–9 + полнота обезличивания 4–6</t>
+          <t>≈8–11 недель: классификатор 8–12 + эмбеддинги 10–14 + реранкер 10–15 + судья 6–9 + полнота обезличивания 4–6</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>ADR-600 называет итог ≈22–33 недели (≈110–165 чел-дн); сумма блоков 108,5–164,5 — округление в самом ADR-600</t>
+          <t>ADR-600 называет итог ≈22–34 недели (≈110–170 чел-дн); сумма блоков 111,5–169,5 — округление в самом ADR-600</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>1) Проверка работоспособности Guardrails на ограниченном объёме живых вопросов (порядка 100–200): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
+          <t>1) Проверка работоспособности Guardrails на живых вопросах — не менее 200 из единой выборки 300–400 (общей с тестами эмбеддингов и реранкера; ответы этого прогона без реранкера — базовая линия критерия Б): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1696,12 +1696,12 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Онлайн-роль зависит от GPU. Офлайн-роль (выбор представительного чанка среди дублей) не подтверждена: модель обучена на паре «запрос — документ», а запроса при индексации нет.</t>
+          <t>Онлайн-роль зависит от GPU. Офлайн-роль (выбор представительного чанка среди дублей) в коде не реализована и не подтверждена: модель обучена на паре «запрос — документ», а запроса при индексации нет.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (считается по каждому вопросу на одних и тех же 20 кандидатах: пустая выдача; меньше трёх; пустая из-за порядка — пуста при «реранкер → порог», но не пуста без реранкера; верный фрагмент отсечён порогом; условный пример на 10 вопросах — в ADR-600; у порядка «порог → реранкер» пустых из-за порядка по построению нет; вопросы без ответа в базе размечаются отдельно и считаются отдельно) (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы или пометка «ответа в базе нет» для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (считается по каждому вопросу на одних и тех же 20 кандидатах: пустая выдача; меньше трёх; пустая из-за порядка — пуста при «реранкер → порог», но не пуста без реранкера; верный фрагмент отсечён порогом; условный пример на 10 вопросах — в ADR-600; у порядка «порог → реранкер» пустых из-за порядка по построению нет; вопросы без ответа в базе размечаются отдельно и считаются отдельно) (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы или пометка «ответа в базе нет» для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порог пустых выдач (критерий В): не более 3% вопросов с ответом, пустых из-за порядка; рабочее значение автора. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (считается по каждому вопросу на одних и тех же 20 кандидатах: пустая выдача; меньше трёх; пустая из-за порядка — пуста при «реранкер → порог», но не пуста без реранкера; верный фрагмент отсечён порогом; условный пример на 10 вопросах — в ADR-600; у порядка «порог → реранкер» пустых из-за порядка по построению нет; вопросы без ответа в базе размечаются отдельно и считаются отдельно) (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы или пометка «ответа в базе нет» для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны заказчиком проекта 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
+          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны заказчиком проекта 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); Б — доля ответов, оценённых экспертом как верные и полезные, не ниже 80% на подвыборке не менее 200 (рабочее значение автора); В — пустых выдач из-за реранкера (пуста при «реранкер → порог», но не пуста без реранкера) не более 3% вопросов с ответом в базе (рабочее значение автора, только для реранкера; порядок «порог → реранкер» проходит по построению); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А, Б или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>Python / FastAPI, uvicorn без режима перезагрузки и без подключённых каталогов; Deployment в Kubernetes, секреты из Vault.</t>
+          <t>Python / FastAPI, uvicorn без режима перезагрузки и без подключённых каталогов; Deployment в Kubernetes, секреты из Kubernetes Secret (GitLab CI variables).</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Решение заказчика проекта (24.09.2026, документально не подтверждено): личный кабинет уже на Kubernetes, размещаемся в том же кластере, эксплуатирует тот же отдел, GPU-узлов нет. Не известны дистрибутив и версия, квоты, классы хранилищ и быстрые диски, есть ли Vault и своя наблюдаемость, сетевые правила. Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
+          <t>Решение заказчика проекта (24.09.2026, документально не подтверждено): личный кабинет уже на Kubernetes, размещаемся в том же кластере, эксплуатирует тот же отдел, GPU-узлов нет. Не известны дистрибутив и версия, квоты, классы хранилищ и быстрые диски, как настроено шифрование Kubernetes Secrets и права на них, есть ли своя наблюдаемость, сетевые правила. Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 20 компонентов, секреты (Vault или механизм кластера). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
+          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 17 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Отказоустойчивость, обновление без остановки, пулы узлов с GPU, задания по расписанию, секреты через Vault Agent Injector. Нагрузка ради этого не нужна: запросы всех подов (11,2 vCPU, 23,6 ГиБ) помещаются на один сервер.</t>
+          <t>Отказоустойчивость, обновление без остановки, пулы узлов с GPU, задания по расписанию. Нагрузка ради этого не нужна: запросы всех подов (11,2 vCPU, 23,6 ГиБ) помещаются на один сервер.</t>
         </is>
       </c>
       <c r="M22" s="12" t="n">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>Согласование платформы с владельцем инфраструктуры: решено размещаться в общем кластере с личным кабинетом (эксплуатирует тот же отдел, GPU нет); остаются дистрибутив и версия, квоты, Vault и наблюдаемость кластера, отечественное ПО; аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
+          <t>Согласование платформы с владельцем инфраструктуры: решено размещаться в общем кластере с личным кабинетом (эксплуатирует тот же отдел, GPU нет); остаются дистрибутив и версия, квоты, шифрование Secrets и наблюдаемость кластера, отечественное ПО; аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
         </is>
       </c>
       <c r="Q22" s="9" t="inlineStr">
@@ -2772,49 +2772,49 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (опционально); MVP — Vault Agent Injector</t>
+          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (необязательный локальный вариант); MVP — GitLab CI variables, Kubernetes Secret</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Опционально Vault в dev-режиме.</t>
+          <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Vault в dev-режиме — необязательный локальный вариант.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения. Хранение только в CI/CD без Vault дублирует секрет в двух местах.</t>
+          <t>Целевой механизм (решение заказчика проекта, 24.09.2026): GitLab CI variables (masked, protected) + деплой через pipeline → Kubernetes Secret. Сравнение (ADR-200, «Секреты в проде: GitLab CI variables и альтернативы»; по документации, без проверки на стенде владельца): Vault Agent Injector — есть аудит чтения, аренда и замена без пересборки, но нужна новая система (отказоустойчивость, разблокировка, резервные копии) и sidecar в каждом поде; External Secrets Operator или Vault CSI — то же плюс оператор; SOPS или Sealed Secrets — шифрованные секреты в Git, без аудита чтения; Kubernetes Secret вручную — без повторяемости и журнала. Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Секреты и конфигурация»; ADR-400 («Что добавляется в контуре MVP»)</t>
+          <t>ADR-200, раздел «Секреты и конфигурация» и подраздел «Секреты в проде: GitLab CI variables и альтернативы»; ADR-400 («Что добавляется в контуре MVP»)</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Dev-режим Vault сам по себе не безопаснее переменной окружения — это репетиция интеграции, а не защита.</t>
+          <t>Нет аудита чтения; значения видны ролям проекта GitLab с правом их читать (по документации Maintainer и выше); шифрование etcd в кластере неизвестно; замена секрета требует деплоя и перезапуска подов; маскирование в логах ограничено по формату значения. Настройки GitLab владельца, права на переменные и версия не проверялись. Прежний выбор Vault Agent Injector отменён как не обоснованный сравнением.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Vault Agent Injector: секреты попадают в под через sidecar.</t>
+          <t>Переменные проекта GitLab CI (masked, protected, по окружениям); job деплоя создаёт Kubernetes Secret без вывода значений в лог; подключение в поды через secretKeyRef или envFrom (изменений кода нет); регламент замены секрета; проверка, что значения не попадают в лог pipeline, образ и манифесты.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>HashiCorp Vault в Kubernetes; используется ли Vault в кластере владельца, неизвестно — возможно, придётся взять их механизм секретов.</t>
+          <t>GitLab CI/CD variables (masked, protected), pipeline деплоя, Kubernetes Secret; версия и редакция GitLab владельца неизвестны.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Единый источник истины и отзыв доступа без пересборки образа.</t>
+          <t>Ничего нового не ставится и не эксплуатируется: GitLab уже используется (со слов); приложение читает переменные окружения, как на прототипе. Vault — вариант по условиям пересмотра: аудит чтения, динамические секреты, замена без перезапуска (ADR-400).</t>
         </is>
       </c>
       <c r="M23" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈172 ГиБ на MVP и ≈663 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈171 ГиБ на MVP и ≈662 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Секреты (Vault)</t>
+          <t>Секреты (GitLab CI variables, Kubernetes Secret)</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -7126,259 +7126,189 @@
     <row r="8" ht="32" customHeight="1">
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>GPU в кластере</t>
+          <t>Секреты</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7,2 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру: владелец решит только после проверки на реальных данных (цена не оценена); переключатель на листе «Sizing».</t>
+          <t>Vault в расчёт не входит: целевой механизм — GitLab CI variables и Kubernetes Secret, отдельных подов нет (ADR-400). Если владелец выберет Vault, понадобится под Vault (допущение: 0,25 vCPU, 0,25 ГиБ, диск 1 ГиБ) и инжектор секретов.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="B9" s="11" t="inlineStr">
         <is>
+          <t>GPU в кластере</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7,2 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру: владелец решит только после проверки на реальных данных (цена не оценена); переключатель на листе «Sizing».</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
           <t>Узлы</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Загрузка узла по запросам не выше 70%. Класс узлов: общий — 8 vCPU / 16 ГиБ; данных — 8 vCPU / 32 ГиБ с NVMe; GPU — 8 vCPU / 32 ГиБ и видеокарта 24 ГБ; LLM (тираж) — 16 vCPU / 128 ГиБ и A100 80 ГБ.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>GPU-узел в кластере (1 — есть, 0 — нет)</t>
         </is>
       </c>
-      <c r="C10" s="51" t="n">
+      <c r="C11" s="51" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="D12" s="52" t="inlineStr">
+    <row r="13">
+      <c r="D13" s="52" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="M12" s="52" t="inlineStr">
+      <c r="M13" s="52" t="inlineStr">
         <is>
           <t>Тираж</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Пул</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Компонент</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Реплик</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>vCPU на под</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>ОЗУ, ГиБ на под</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Диск, ГиБ на под</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Видеопамять, ГиБ на под</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>vCPU всего</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>ОЗУ всего, ГиБ</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Диск всего, ГиБ</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Видеопамять всего, ГиБ</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Реплик</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>vCPU на под</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>ОЗУ, ГиБ на под</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>Диск, ГиБ на под</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>Видеопамять, ГиБ на под</t>
         </is>
       </c>
-      <c r="R13" s="5" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>vCPU всего</t>
         </is>
       </c>
-      <c r="S13" s="5" t="inlineStr">
+      <c r="S14" s="5" t="inlineStr">
         <is>
           <t>ОЗУ всего, ГиБ</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr">
+      <c r="T14" s="5" t="inlineStr">
         <is>
           <t>Диск всего, ГиБ</t>
         </is>
       </c>
-      <c r="U13" s="5" t="inlineStr">
+      <c r="U14" s="5" t="inlineStr">
         <is>
           <t>Видеопамять всего, ГиБ</t>
         </is>
       </c>
-      <c r="V13" s="5" t="inlineStr">
+      <c r="V14" s="5" t="inlineStr">
         <is>
           <t>Основание</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Ingress (nginx)</t>
-        </is>
-      </c>
-      <c r="D14" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F14" s="51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G14" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="53">
-        <f>D14*E14</f>
-        <v/>
-      </c>
-      <c r="J14" s="53">
-        <f>D14*F14</f>
-        <v/>
-      </c>
-      <c r="K14" s="53">
-        <f>D14*G14</f>
-        <v/>
-      </c>
-      <c r="L14" s="53">
-        <f>D14*H14</f>
-        <v/>
-      </c>
-      <c r="M14" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" s="51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O14" s="51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P14" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="53">
-        <f>M14*N14</f>
-        <v/>
-      </c>
-      <c r="S14" s="53">
-        <f>M14*O14</f>
-        <v/>
-      </c>
-      <c r="T14" s="53">
-        <f>M14*P14</f>
-        <v/>
-      </c>
-      <c r="U14" s="53">
-        <f>M14*Q14</f>
-        <v/>
-      </c>
-      <c r="V14" s="9" t="inlineStr">
-        <is>
-          <t>Допущение. Внешний трафик — единицы запросов в секунду.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Ingress (nginx)</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="n">
         <v>2</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Vault</t>
-        </is>
-      </c>
-      <c r="D15" s="51" t="n">
-        <v>1</v>
       </c>
       <c r="E15" s="51" t="n">
         <v>0.25</v>
@@ -7387,7 +7317,7 @@
         <v>0.25</v>
       </c>
       <c r="G15" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="51" t="n">
         <v>0</v>
@@ -7409,7 +7339,7 @@
         <v/>
       </c>
       <c r="M15" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" s="51" t="n">
         <v>0.25</v>
@@ -7418,7 +7348,7 @@
         <v>0.25</v>
       </c>
       <c r="P15" s="51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="51" t="n">
         <v>0</v>
@@ -7441,13 +7371,13 @@
       </c>
       <c r="V15" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Инжектор секретов и cert-manager — отдельной строкой не выделены (≈0,1 vCPU / 0,1 ГиБ).</t>
+          <t>Допущение. Внешний трафик — единицы запросов в секунду.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -7529,7 +7459,7 @@
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
@@ -7611,7 +7541,7 @@
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -7693,7 +7623,7 @@
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
@@ -7775,7 +7705,7 @@
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -7857,7 +7787,7 @@
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
@@ -7870,7 +7800,7 @@
         </is>
       </c>
       <c r="D21" s="51">
-        <f>1*$C$10</f>
+        <f>1*$C$11</f>
         <v/>
       </c>
       <c r="E21" s="51" t="n">
@@ -7902,7 +7832,7 @@
         <v/>
       </c>
       <c r="M21" s="51">
-        <f>1*$C$10</f>
+        <f>1*$C$11</f>
         <v/>
       </c>
       <c r="N21" s="51" t="n">
@@ -7941,7 +7871,7 @@
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -8023,7 +7953,7 @@
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
@@ -8105,7 +8035,7 @@
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -8187,7 +8117,7 @@
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
@@ -8269,7 +8199,7 @@
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -8351,7 +8281,7 @@
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
@@ -8433,7 +8363,7 @@
     </row>
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -8515,7 +8445,7 @@
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
@@ -8597,7 +8527,7 @@
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
@@ -8679,7 +8609,7 @@
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
@@ -8692,7 +8622,7 @@
         </is>
       </c>
       <c r="D31" s="51">
-        <f>1*$C$10</f>
+        <f>1*$C$11</f>
         <v/>
       </c>
       <c r="E31" s="51" t="n">
@@ -8724,7 +8654,7 @@
         <v/>
       </c>
       <c r="M31" s="51">
-        <f>1*$C$10</f>
+        <f>1*$C$11</f>
         <v/>
       </c>
       <c r="N31" s="51" t="n">
@@ -8763,7 +8693,7 @@
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
@@ -8776,7 +8706,7 @@
         </is>
       </c>
       <c r="D32" s="51">
-        <f>1*$C$10</f>
+        <f>1*$C$11</f>
         <v/>
       </c>
       <c r="E32" s="51" t="n">
@@ -8808,7 +8738,7 @@
         <v/>
       </c>
       <c r="M32" s="51">
-        <f>1*$C$10</f>
+        <f>1*$C$11</f>
         <v/>
       </c>
       <c r="N32" s="51" t="n">
@@ -8847,7 +8777,7 @@
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
@@ -8929,7 +8859,7 @@
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
@@ -8942,7 +8872,7 @@
         </is>
       </c>
       <c r="D34" s="51">
-        <f>2*(1-$C$10)</f>
+        <f>2*(1-$C$11)</f>
         <v/>
       </c>
       <c r="E34" s="51" t="n">
@@ -8974,7 +8904,7 @@
         <v/>
       </c>
       <c r="M34" s="51">
-        <f>2*(1-$C$10)</f>
+        <f>2*(1-$C$11)</f>
         <v/>
       </c>
       <c r="N34" s="51" t="n">
@@ -9013,7 +8943,7 @@
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
@@ -9026,7 +8956,7 @@
         </is>
       </c>
       <c r="D35" s="51">
-        <f>1*(1-$C$10)</f>
+        <f>1*(1-$C$11)</f>
         <v/>
       </c>
       <c r="E35" s="51" t="n">
@@ -9058,7 +8988,7 @@
         <v/>
       </c>
       <c r="M35" s="51">
-        <f>1*(1-$C$10)</f>
+        <f>1*(1-$C$11)</f>
         <v/>
       </c>
       <c r="N35" s="51" t="n">
@@ -9206,15 +9136,15 @@
         <v>1</v>
       </c>
       <c r="H39" s="55">
-        <f>SUMIF($B$14:$B$35,$B39,$I$14:$I$35)</f>
+        <f>SUMIF($B$15:$B$35,$B39,$I$15:$I$35)</f>
         <v/>
       </c>
       <c r="I39" s="55">
-        <f>SUMIF($B$14:$B$35,$B39,$J$14:$J$35)</f>
+        <f>SUMIF($B$15:$B$35,$B39,$J$15:$J$35)</f>
         <v/>
       </c>
       <c r="J39" s="55">
-        <f>SUMIF($B$14:$B$35,$B39,$L$14:$L$35)</f>
+        <f>SUMIF($B$15:$B$35,$B39,$L$15:$L$35)</f>
         <v/>
       </c>
       <c r="K39" s="56">
@@ -9222,15 +9152,15 @@
         <v/>
       </c>
       <c r="L39" s="55">
-        <f>SUMIF($B$14:$B$35,$B39,$R$14:$R$35)</f>
+        <f>SUMIF($B$15:$B$35,$B39,$R$15:$R$35)</f>
         <v/>
       </c>
       <c r="M39" s="55">
-        <f>SUMIF($B$14:$B$35,$B39,$S$14:$S$35)</f>
+        <f>SUMIF($B$15:$B$35,$B39,$S$15:$S$35)</f>
         <v/>
       </c>
       <c r="N39" s="55">
-        <f>SUMIF($B$14:$B$35,$B39,$U$14:$U$35)</f>
+        <f>SUMIF($B$15:$B$35,$B39,$U$15:$U$35)</f>
         <v/>
       </c>
       <c r="O39" s="56">
@@ -9262,15 +9192,15 @@
         <v>1</v>
       </c>
       <c r="H40" s="55">
-        <f>SUMIF($B$14:$B$35,$B40,$I$14:$I$35)</f>
+        <f>SUMIF($B$15:$B$35,$B40,$I$15:$I$35)</f>
         <v/>
       </c>
       <c r="I40" s="55">
-        <f>SUMIF($B$14:$B$35,$B40,$J$14:$J$35)</f>
+        <f>SUMIF($B$15:$B$35,$B40,$J$15:$J$35)</f>
         <v/>
       </c>
       <c r="J40" s="55">
-        <f>SUMIF($B$14:$B$35,$B40,$L$14:$L$35)</f>
+        <f>SUMIF($B$15:$B$35,$B40,$L$15:$L$35)</f>
         <v/>
       </c>
       <c r="K40" s="56">
@@ -9278,15 +9208,15 @@
         <v/>
       </c>
       <c r="L40" s="55">
-        <f>SUMIF($B$14:$B$35,$B40,$R$14:$R$35)</f>
+        <f>SUMIF($B$15:$B$35,$B40,$R$15:$R$35)</f>
         <v/>
       </c>
       <c r="M40" s="55">
-        <f>SUMIF($B$14:$B$35,$B40,$S$14:$S$35)</f>
+        <f>SUMIF($B$15:$B$35,$B40,$S$15:$S$35)</f>
         <v/>
       </c>
       <c r="N40" s="55">
-        <f>SUMIF($B$14:$B$35,$B40,$U$14:$U$35)</f>
+        <f>SUMIF($B$15:$B$35,$B40,$U$15:$U$35)</f>
         <v/>
       </c>
       <c r="O40" s="56">
@@ -9318,15 +9248,15 @@
         <v>0</v>
       </c>
       <c r="H41" s="55">
-        <f>SUMIF($B$14:$B$35,$B41,$I$14:$I$35)</f>
+        <f>SUMIF($B$15:$B$35,$B41,$I$15:$I$35)</f>
         <v/>
       </c>
       <c r="I41" s="55">
-        <f>SUMIF($B$14:$B$35,$B41,$J$14:$J$35)</f>
+        <f>SUMIF($B$15:$B$35,$B41,$J$15:$J$35)</f>
         <v/>
       </c>
       <c r="J41" s="55">
-        <f>SUMIF($B$14:$B$35,$B41,$L$14:$L$35)</f>
+        <f>SUMIF($B$15:$B$35,$B41,$L$15:$L$35)</f>
         <v/>
       </c>
       <c r="K41" s="56">
@@ -9334,15 +9264,15 @@
         <v/>
       </c>
       <c r="L41" s="55">
-        <f>SUMIF($B$14:$B$35,$B41,$R$14:$R$35)</f>
+        <f>SUMIF($B$15:$B$35,$B41,$R$15:$R$35)</f>
         <v/>
       </c>
       <c r="M41" s="55">
-        <f>SUMIF($B$14:$B$35,$B41,$S$14:$S$35)</f>
+        <f>SUMIF($B$15:$B$35,$B41,$S$15:$S$35)</f>
         <v/>
       </c>
       <c r="N41" s="55">
-        <f>SUMIF($B$14:$B$35,$B41,$U$14:$U$35)</f>
+        <f>SUMIF($B$15:$B$35,$B41,$U$15:$U$35)</f>
         <v/>
       </c>
       <c r="O41" s="56">
@@ -9374,15 +9304,15 @@
         <v>0</v>
       </c>
       <c r="H42" s="55">
-        <f>SUMIF($B$14:$B$35,$B42,$I$14:$I$35)</f>
+        <f>SUMIF($B$15:$B$35,$B42,$I$15:$I$35)</f>
         <v/>
       </c>
       <c r="I42" s="55">
-        <f>SUMIF($B$14:$B$35,$B42,$J$14:$J$35)</f>
+        <f>SUMIF($B$15:$B$35,$B42,$J$15:$J$35)</f>
         <v/>
       </c>
       <c r="J42" s="55">
-        <f>SUMIF($B$14:$B$35,$B42,$L$14:$L$35)</f>
+        <f>SUMIF($B$15:$B$35,$B42,$L$15:$L$35)</f>
         <v/>
       </c>
       <c r="K42" s="56">
@@ -9390,15 +9320,15 @@
         <v/>
       </c>
       <c r="L42" s="55">
-        <f>SUMIF($B$14:$B$35,$B42,$R$14:$R$35)</f>
+        <f>SUMIF($B$15:$B$35,$B42,$R$15:$R$35)</f>
         <v/>
       </c>
       <c r="M42" s="55">
-        <f>SUMIF($B$14:$B$35,$B42,$S$14:$S$35)</f>
+        <f>SUMIF($B$15:$B$35,$B42,$S$15:$S$35)</f>
         <v/>
       </c>
       <c r="N42" s="55">
-        <f>SUMIF($B$14:$B$35,$B42,$U$14:$U$35)</f>
+        <f>SUMIF($B$15:$B$35,$B42,$U$15:$U$35)</f>
         <v/>
       </c>
       <c r="O42" s="56">
@@ -9428,11 +9358,11 @@
         </is>
       </c>
       <c r="K44" s="58">
-        <f>SUM($K$14:$K$35)</f>
+        <f>SUM($K$15:$K$35)</f>
         <v/>
       </c>
       <c r="O44" s="58">
-        <f>SUM($T$14:$T$35)</f>
+        <f>SUM($T$15:$T$35)</f>
         <v/>
       </c>
     </row>
@@ -9444,16 +9374,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C4:U4"/>
-    <mergeCell ref="M12:U12"/>
+    <mergeCell ref="D13:L13"/>
     <mergeCell ref="C5:U5"/>
     <mergeCell ref="C8:U8"/>
     <mergeCell ref="C9:U9"/>
     <mergeCell ref="C3:U3"/>
     <mergeCell ref="C7:U7"/>
-    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="M13:U13"/>
     <mergeCell ref="C6:U6"/>
+    <mergeCell ref="C10:U10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2695,7 +2695,7 @@
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 17 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
+          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 16 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -2853,47 +2853,47 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); отдельные контейнеры Prometheus, Grafana, Loki, Alertmanager (MVP)</t>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana — владельца (не наш контейнер); отдельные контейнеры Prometheus, Loki, Alertmanager — верхняя оценка до ответа владельца (MVP)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Prometheus, Grafana, Loki, Alertmanager</t>
+          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Grafana владельца, дашборды и алерты как код; источник данных и Prometheus, Loki, Alertmanager — по ответу владельца</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Метрики Prometheus на отдельном порту, события потока в панели стенда. Дашбордов и сбора логов нет.</t>
+          <t>Метрики Prometheus на отдельном порту 9100 (в Compose порт не опубликован: с хоста недоступен, внутри контейнера отдаётся), события потока в панели стенда. Дашбордов, сбора логов и алертов нет.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Prometheus + Grafana + Loki + Alertmanager выбраны против ELK/OpenSearch, Zabbix и облачного мониторинга: закрытый контур (152-ФЗ), метрики Kubernetes и приложения, недорогие логи (Loki индексирует метки, а не текст). Сравнение по документации; пробного развёртывания альтернатив не было.</t>
+          <t>Решение заказчика проекта (24.09.2026, со слов): в реальном контуре используется Grafana — своя не разворачивается. Варианты по источнику данных: A — Prometheus владельца, B — свой Prometheus как источник для их Grafana, C — Zabbix как источник, D — своя четвёрка (прежний выбор, запасной). ELK/OpenSearch отклонён как тяжёлый, облачный мониторинг — из-за 152-ФЗ. Прежнее «Zabbix отклонён: ориентирован на хосты» не проверялось. Сравнение по документации; пробного развёртывания не было.</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Prometheus, Grafana, Loki и Alertmanager»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Наблюдаемость: Grafana владельца и источники данных»</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Метрики есть, но собирать и показывать их нечему.</t>
+          <t>Неизвестно, какие источники подключены к Grafana владельца, есть ли Prometheus, собирающий метрики подов, есть ли Alertmanager и как собираются логи; как принимаются дашборды. Метрики есть, но собирать и показывать их нечему.</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>Полный стек наблюдаемости: метрики, дашборды, логи, оповещения; в логах только отчёт об обезличивании, без значений ПДн.</t>
+          <t>Дашборды нашего сервиса как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; правила 9 алертов как код; правило сбора метрик с порта 9100 (ServiceMonitor или аннотации) либо свой Prometheus как источник; в логах только отчёт об обезличивании, без значений ПДн. Оценка не пересматривалась: развёртывание своей Grafana отпало, но добавились согласование и интеграция с чужой.</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Prometheus, Grafana, Loki, Alertmanager.</t>
+          <t>Grafana владельца; prometheus-client (порт 9100); источник данных и Prometheus, Loki, Alertmanager — по ответу владельца (для расчёта узлов оставлены как верхняя оценка, без Grafana).</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах.</t>
+          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах; Grafana уже есть у владельца, дублировать её незачем.</t>
         </is>
       </c>
       <c r="M24" s="12" t="n">
@@ -2919,7 +2919,7 @@
       <c r="U24" s="15" t="n"/>
       <c r="V24" s="9" t="inlineStr">
         <is>
-          <t>C4_Deployment; ADR-500</t>
+          <t>C4_Deployment; ADR-200; ADR-500</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈171 ГиБ на MVP и ≈662 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -7138,246 +7138,176 @@
     <row r="9" ht="32" customHeight="1">
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>GPU в кластере</t>
+          <t>Наблюдаемость</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7,2 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру: владелец решит только после проверки на реальных данных (цена не оценена); переключатель на листе «Sizing».</t>
+          <t>Grafana в расчёт не входит: в реальном контуре используется Grafana владельца (решение заказчика проекта, со слов). Prometheus, Loki и Alertmanager оставлены как верхняя оценка до ответа владельца, какие источники данных у него подключены; если у него они есть, эти поды из расчёта уходят.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="B10" s="11" t="inlineStr">
         <is>
+          <t>GPU в кластере</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7,2 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру: владелец решит только после проверки на реальных данных (цена не оценена); переключатель на листе «Sizing».</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
           <t>Узлы</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Загрузка узла по запросам не выше 70%. Класс узлов: общий — 8 vCPU / 16 ГиБ; данных — 8 vCPU / 32 ГиБ с NVMe; GPU — 8 vCPU / 32 ГиБ и видеокарта 24 ГБ; LLM (тираж) — 16 vCPU / 128 ГиБ и A100 80 ГБ.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>GPU-узел в кластере (1 — есть, 0 — нет)</t>
         </is>
       </c>
-      <c r="C11" s="51" t="n">
+      <c r="C12" s="51" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="D13" s="52" t="inlineStr">
+    <row r="14">
+      <c r="D14" s="52" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="M13" s="52" t="inlineStr">
+      <c r="M14" s="52" t="inlineStr">
         <is>
           <t>Тираж</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Пул</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Компонент</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Реплик</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>vCPU на под</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>ОЗУ, ГиБ на под</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Диск, ГиБ на под</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Видеопамять, ГиБ на под</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>vCPU всего</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>ОЗУ всего, ГиБ</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Диск всего, ГиБ</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Видеопамять всего, ГиБ</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>Реплик</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>vCPU на под</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>ОЗУ, ГиБ на под</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>Диск, ГиБ на под</t>
         </is>
       </c>
-      <c r="Q14" s="5" t="inlineStr">
+      <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>Видеопамять, ГиБ на под</t>
         </is>
       </c>
-      <c r="R14" s="5" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>vCPU всего</t>
         </is>
       </c>
-      <c r="S14" s="5" t="inlineStr">
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>ОЗУ всего, ГиБ</t>
         </is>
       </c>
-      <c r="T14" s="5" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>Диск всего, ГиБ</t>
         </is>
       </c>
-      <c r="U14" s="5" t="inlineStr">
+      <c r="U15" s="5" t="inlineStr">
         <is>
           <t>Видеопамять всего, ГиБ</t>
         </is>
       </c>
-      <c r="V14" s="5" t="inlineStr">
+      <c r="V15" s="5" t="inlineStr">
         <is>
           <t>Основание</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Ingress (nginx)</t>
-        </is>
-      </c>
-      <c r="D15" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F15" s="51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G15" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="53">
-        <f>D15*E15</f>
-        <v/>
-      </c>
-      <c r="J15" s="53">
-        <f>D15*F15</f>
-        <v/>
-      </c>
-      <c r="K15" s="53">
-        <f>D15*G15</f>
-        <v/>
-      </c>
-      <c r="L15" s="53">
-        <f>D15*H15</f>
-        <v/>
-      </c>
-      <c r="M15" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" s="51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O15" s="51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P15" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="53">
-        <f>M15*N15</f>
-        <v/>
-      </c>
-      <c r="S15" s="53">
-        <f>M15*O15</f>
-        <v/>
-      </c>
-      <c r="T15" s="53">
-        <f>M15*P15</f>
-        <v/>
-      </c>
-      <c r="U15" s="53">
-        <f>M15*Q15</f>
-        <v/>
-      </c>
-      <c r="V15" s="9" t="inlineStr">
-        <is>
-          <t>Допущение. Внешний трафик — единицы запросов в секунду.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -7386,17 +7316,17 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>AI-виджет (статические файлы)</t>
+          <t>Ingress (nginx)</t>
         </is>
       </c>
       <c r="D16" s="51" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="51" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="F16" s="51" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="G16" s="51" t="n">
         <v>0</v>
@@ -7424,10 +7354,10 @@
         <v>2</v>
       </c>
       <c r="N16" s="51" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="O16" s="51" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="P16" s="51" t="n">
         <v>0</v>
@@ -7453,13 +7383,13 @@
       </c>
       <c r="V16" s="9" t="inlineStr">
         <is>
-          <t>Допущение. На стенде три статических файла.</t>
+          <t>Допущение. Внешний трафик — единицы запросов в секунду.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
@@ -7468,17 +7398,17 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Backend (API, классификация, поиск, сборка ответа)</t>
+          <t>AI-виджет (статические файлы)</t>
         </is>
       </c>
       <c r="D17" s="51" t="n">
         <v>2</v>
       </c>
       <c r="E17" s="51" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F17" s="51" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="51" t="n">
         <v>0</v>
@@ -7503,13 +7433,13 @@
         <v/>
       </c>
       <c r="M17" s="51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" s="51" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O17" s="51" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P17" s="51" t="n">
         <v>0</v>
@@ -7535,13 +7465,13 @@
       </c>
       <c r="V17" s="9" t="inlineStr">
         <is>
-          <t>Замер: путь без модели — 117 запросов/с на процесс (8,5 мс CPU). 2 реплики нужны для отказоустойчивости, а не для пропускной способности; ОЗУ — допущение (эмбеддер и обезличиватель вынесены).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t>Допущение. На стенде три статических файла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -7550,7 +7480,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>LLM Gateway (лимиты, обезличивание, проверка ответа)</t>
+          <t>Backend (API, классификация, поиск, сборка ответа)</t>
         </is>
       </c>
       <c r="D18" s="51" t="n">
@@ -7560,7 +7490,7 @@
         <v>0.5</v>
       </c>
       <c r="F18" s="51" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="51" t="n">
         <v>0</v>
@@ -7591,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="51" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="P18" s="51" t="n">
         <v>0</v>
@@ -7617,13 +7547,13 @@
       </c>
       <c r="V18" s="9" t="inlineStr">
         <is>
-          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,04 ядра на MVP, 0,41 на тираже (максимум прогноза); на ответах в 2 000 знаков до 2,1 ядра (3 реплики × 1 vCPU + предел 2). После оптимизации проверки на потоке запас вырастет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+          <t>Замер: путь без модели — 117 запросов/с на процесс (8,5 мс CPU). 2 реплики нужны для отказоустойчивости, а не для пропускной способности; ОЗУ — допущение (эмбеддер и обезличиватель вынесены).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
@@ -7632,17 +7562,17 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Billing Adapter, оркестратор записи (Этап 2)</t>
+          <t>LLM Gateway (лимиты, обезличивание, проверка ответа)</t>
         </is>
       </c>
       <c r="D19" s="51" t="n">
         <v>2</v>
       </c>
       <c r="E19" s="51" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="51" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="G19" s="51" t="n">
         <v>0</v>
@@ -7667,13 +7597,13 @@
         <v/>
       </c>
       <c r="M19" s="51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" s="51" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="O19" s="51" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="P19" s="51" t="n">
         <v>0</v>
@@ -7699,13 +7629,13 @@
       </c>
       <c r="V19" s="9" t="inlineStr">
         <is>
-          <t>Допущение. До 2 800 диалогов с записью в месяц на MVP и 31 500 на тираже (максимум прогноза, A6 = 40%) — нагрузка ничтожна.</t>
+          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,04 ядра на MVP, 0,41 на тираже (максимум прогноза); на ответах в 2 000 знаков до 2,1 ядра (3 реплики × 1 vCPU + предел 2). После оптимизации проверки на потоке запас вырастет.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -7714,17 +7644,17 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Document Generator (PDF, Этап 2)</t>
+          <t>Billing Adapter, оркестратор записи (Этап 2)</t>
         </is>
       </c>
       <c r="D20" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="51" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F20" s="51" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G20" s="51" t="n">
         <v>0</v>
@@ -7752,10 +7682,10 @@
         <v>2</v>
       </c>
       <c r="N20" s="51" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="O20" s="51" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="P20" s="51" t="n">
         <v>0</v>
@@ -7781,13 +7711,13 @@
       </c>
       <c r="V20" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью (до 31 500 в месяц на тираже).</t>
+          <t>Допущение. До 2 800 диалогов с записью в месяц на MVP и 31 500 на тираже (максимум прогноза, A6 = 40%) — нагрузка ничтожна.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
@@ -7796,21 +7726,20 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>ETL индексации (CronJob, окно 02:00–05:00) [вариант с GPU]</t>
-        </is>
-      </c>
-      <c r="D21" s="51">
-        <f>1*$C$11</f>
-        <v/>
+          <t>Document Generator (PDF, Этап 2)</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="E21" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="G21" s="51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" s="51" t="n">
         <v>0</v>
@@ -7831,18 +7760,17 @@
         <f>D21*H21</f>
         <v/>
       </c>
-      <c r="M21" s="51">
-        <f>1*$C$11</f>
-        <v/>
+      <c r="M21" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="N21" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O21" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="P21" s="51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="51" t="n">
         <v>0</v>
@@ -7865,13 +7793,13 @@
       </c>
       <c r="V21" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
+          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью (до 31 500 в месяц на тираже).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -7880,20 +7808,21 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Оценка качества (CronJob, ночной прогон)</t>
-        </is>
-      </c>
-      <c r="D22" s="51" t="n">
+          <t>ETL индексации (CronJob, окно 02:00–05:00) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D22" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="E22" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F22" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" s="51" t="n">
         <v>0</v>
@@ -7914,17 +7843,18 @@
         <f>D22*H22</f>
         <v/>
       </c>
-      <c r="M22" s="51" t="n">
+      <c r="M22" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="N22" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="O22" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="51" t="n">
         <v>0</v>
@@ -7947,13 +7877,13 @@
       </c>
       <c r="V22" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
+          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
@@ -7962,7 +7892,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>Оценка качества (CronJob, ночной прогон)</t>
         </is>
       </c>
       <c r="D23" s="51" t="n">
@@ -7975,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H23" s="51" t="n">
         <v>0</v>
@@ -8006,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="51" t="n">
         <v>0</v>
@@ -8029,13 +7959,13 @@
       </c>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
+          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -8044,20 +7974,20 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Grafana</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D24" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="51" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F24" s="51" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G24" s="51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H24" s="51" t="n">
         <v>0</v>
@@ -8082,13 +8012,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="51" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="O24" s="51" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P24" s="51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q24" s="51" t="n">
         <v>0</v>
@@ -8111,13 +8041,13 @@
       </c>
       <c r="V24" s="9" t="inlineStr">
         <is>
-          <t>Допущение.</t>
+          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
@@ -8199,7 +8129,7 @@
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -8281,7 +8211,7 @@
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
@@ -8363,7 +8293,7 @@
     </row>
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
@@ -8445,7 +8375,7 @@
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
@@ -8527,7 +8457,7 @@
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
@@ -8609,7 +8539,7 @@
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
@@ -8622,7 +8552,7 @@
         </is>
       </c>
       <c r="D31" s="51">
-        <f>1*$C$11</f>
+        <f>1*$C$12</f>
         <v/>
       </c>
       <c r="E31" s="51" t="n">
@@ -8654,7 +8584,7 @@
         <v/>
       </c>
       <c r="M31" s="51">
-        <f>1*$C$11</f>
+        <f>1*$C$12</f>
         <v/>
       </c>
       <c r="N31" s="51" t="n">
@@ -8693,7 +8623,7 @@
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
@@ -8706,7 +8636,7 @@
         </is>
       </c>
       <c r="D32" s="51">
-        <f>1*$C$11</f>
+        <f>1*$C$12</f>
         <v/>
       </c>
       <c r="E32" s="51" t="n">
@@ -8738,7 +8668,7 @@
         <v/>
       </c>
       <c r="M32" s="51">
-        <f>1*$C$11</f>
+        <f>1*$C$12</f>
         <v/>
       </c>
       <c r="N32" s="51" t="n">
@@ -8777,7 +8707,7 @@
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
@@ -8859,7 +8789,7 @@
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
@@ -8872,7 +8802,7 @@
         </is>
       </c>
       <c r="D34" s="51">
-        <f>2*(1-$C$11)</f>
+        <f>2*(1-$C$12)</f>
         <v/>
       </c>
       <c r="E34" s="51" t="n">
@@ -8904,7 +8834,7 @@
         <v/>
       </c>
       <c r="M34" s="51">
-        <f>2*(1-$C$11)</f>
+        <f>2*(1-$C$12)</f>
         <v/>
       </c>
       <c r="N34" s="51" t="n">
@@ -8943,7 +8873,7 @@
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
@@ -8956,7 +8886,7 @@
         </is>
       </c>
       <c r="D35" s="51">
-        <f>1*(1-$C$11)</f>
+        <f>1*(1-$C$12)</f>
         <v/>
       </c>
       <c r="E35" s="51" t="n">
@@ -8988,7 +8918,7 @@
         <v/>
       </c>
       <c r="M35" s="51">
-        <f>1*(1-$C$11)</f>
+        <f>1*(1-$C$12)</f>
         <v/>
       </c>
       <c r="N35" s="51" t="n">
@@ -9136,15 +9066,15 @@
         <v>1</v>
       </c>
       <c r="H39" s="55">
-        <f>SUMIF($B$15:$B$35,$B39,$I$15:$I$35)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$I$16:$I$35)</f>
         <v/>
       </c>
       <c r="I39" s="55">
-        <f>SUMIF($B$15:$B$35,$B39,$J$15:$J$35)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$J$16:$J$35)</f>
         <v/>
       </c>
       <c r="J39" s="55">
-        <f>SUMIF($B$15:$B$35,$B39,$L$15:$L$35)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$L$16:$L$35)</f>
         <v/>
       </c>
       <c r="K39" s="56">
@@ -9152,15 +9082,15 @@
         <v/>
       </c>
       <c r="L39" s="55">
-        <f>SUMIF($B$15:$B$35,$B39,$R$15:$R$35)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$R$16:$R$35)</f>
         <v/>
       </c>
       <c r="M39" s="55">
-        <f>SUMIF($B$15:$B$35,$B39,$S$15:$S$35)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$S$16:$S$35)</f>
         <v/>
       </c>
       <c r="N39" s="55">
-        <f>SUMIF($B$15:$B$35,$B39,$U$15:$U$35)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$U$16:$U$35)</f>
         <v/>
       </c>
       <c r="O39" s="56">
@@ -9192,15 +9122,15 @@
         <v>1</v>
       </c>
       <c r="H40" s="55">
-        <f>SUMIF($B$15:$B$35,$B40,$I$15:$I$35)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$I$16:$I$35)</f>
         <v/>
       </c>
       <c r="I40" s="55">
-        <f>SUMIF($B$15:$B$35,$B40,$J$15:$J$35)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$J$16:$J$35)</f>
         <v/>
       </c>
       <c r="J40" s="55">
-        <f>SUMIF($B$15:$B$35,$B40,$L$15:$L$35)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$L$16:$L$35)</f>
         <v/>
       </c>
       <c r="K40" s="56">
@@ -9208,15 +9138,15 @@
         <v/>
       </c>
       <c r="L40" s="55">
-        <f>SUMIF($B$15:$B$35,$B40,$R$15:$R$35)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$R$16:$R$35)</f>
         <v/>
       </c>
       <c r="M40" s="55">
-        <f>SUMIF($B$15:$B$35,$B40,$S$15:$S$35)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$S$16:$S$35)</f>
         <v/>
       </c>
       <c r="N40" s="55">
-        <f>SUMIF($B$15:$B$35,$B40,$U$15:$U$35)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$U$16:$U$35)</f>
         <v/>
       </c>
       <c r="O40" s="56">
@@ -9248,15 +9178,15 @@
         <v>0</v>
       </c>
       <c r="H41" s="55">
-        <f>SUMIF($B$15:$B$35,$B41,$I$15:$I$35)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$I$16:$I$35)</f>
         <v/>
       </c>
       <c r="I41" s="55">
-        <f>SUMIF($B$15:$B$35,$B41,$J$15:$J$35)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$J$16:$J$35)</f>
         <v/>
       </c>
       <c r="J41" s="55">
-        <f>SUMIF($B$15:$B$35,$B41,$L$15:$L$35)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$L$16:$L$35)</f>
         <v/>
       </c>
       <c r="K41" s="56">
@@ -9264,15 +9194,15 @@
         <v/>
       </c>
       <c r="L41" s="55">
-        <f>SUMIF($B$15:$B$35,$B41,$R$15:$R$35)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$R$16:$R$35)</f>
         <v/>
       </c>
       <c r="M41" s="55">
-        <f>SUMIF($B$15:$B$35,$B41,$S$15:$S$35)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$S$16:$S$35)</f>
         <v/>
       </c>
       <c r="N41" s="55">
-        <f>SUMIF($B$15:$B$35,$B41,$U$15:$U$35)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$U$16:$U$35)</f>
         <v/>
       </c>
       <c r="O41" s="56">
@@ -9304,15 +9234,15 @@
         <v>0</v>
       </c>
       <c r="H42" s="55">
-        <f>SUMIF($B$15:$B$35,$B42,$I$15:$I$35)</f>
+        <f>SUMIF($B$16:$B$35,$B42,$I$16:$I$35)</f>
         <v/>
       </c>
       <c r="I42" s="55">
-        <f>SUMIF($B$15:$B$35,$B42,$J$15:$J$35)</f>
+        <f>SUMIF($B$16:$B$35,$B42,$J$16:$J$35)</f>
         <v/>
       </c>
       <c r="J42" s="55">
-        <f>SUMIF($B$15:$B$35,$B42,$L$15:$L$35)</f>
+        <f>SUMIF($B$16:$B$35,$B42,$L$16:$L$35)</f>
         <v/>
       </c>
       <c r="K42" s="56">
@@ -9320,15 +9250,15 @@
         <v/>
       </c>
       <c r="L42" s="55">
-        <f>SUMIF($B$15:$B$35,$B42,$R$15:$R$35)</f>
+        <f>SUMIF($B$16:$B$35,$B42,$R$16:$R$35)</f>
         <v/>
       </c>
       <c r="M42" s="55">
-        <f>SUMIF($B$15:$B$35,$B42,$S$15:$S$35)</f>
+        <f>SUMIF($B$16:$B$35,$B42,$S$16:$S$35)</f>
         <v/>
       </c>
       <c r="N42" s="55">
-        <f>SUMIF($B$15:$B$35,$B42,$U$15:$U$35)</f>
+        <f>SUMIF($B$16:$B$35,$B42,$U$16:$U$35)</f>
         <v/>
       </c>
       <c r="O42" s="56">
@@ -9358,11 +9288,11 @@
         </is>
       </c>
       <c r="K44" s="58">
-        <f>SUM($K$15:$K$35)</f>
+        <f>SUM($K$16:$K$35)</f>
         <v/>
       </c>
       <c r="O44" s="58">
-        <f>SUM($T$15:$T$35)</f>
+        <f>SUM($T$16:$T$35)</f>
         <v/>
       </c>
     </row>
@@ -9374,15 +9304,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="C4:U4"/>
-    <mergeCell ref="D13:L13"/>
+    <mergeCell ref="C11:U11"/>
     <mergeCell ref="C5:U5"/>
+    <mergeCell ref="M14:U14"/>
+    <mergeCell ref="D14:L14"/>
     <mergeCell ref="C8:U8"/>
     <mergeCell ref="C9:U9"/>
     <mergeCell ref="C3:U3"/>
     <mergeCell ref="C7:U7"/>
-    <mergeCell ref="M13:U13"/>
     <mergeCell ref="C6:U6"/>
     <mergeCell ref="C10:U10"/>
   </mergeCells>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2695,7 +2695,7 @@
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 16 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
+          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 15 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 5 узлов на MVP (3 общих и 2 данных; на границе округления, возможно 6), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -2853,22 +2853,22 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana — владельца (не наш контейнер); отдельные контейнеры Prometheus, Loki, Alertmanager — верхняя оценка до ответа владельца (MVP)</t>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); отдельные контейнеры Prometheus и Loki — верхняя оценка до ответа владельца (MVP)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Grafana владельца, дашборды и алерты как код; источник данных и Prometheus, Loki, Alertmanager — по ответу владельца</t>
+          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Zabbix и Grafana владельца (Jaeger — по необходимости), дашборды и триггеры как код</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Метрики Prometheus на отдельном порту 9100 (в Compose порт не опубликован: с хоста недоступен, внутри контейнера отдаётся), события потока в панели стенда. Дашбордов, сбора логов и алертов нет.</t>
+          <t>Метрики Prometheus на отдельном порту 9100 (в Compose порт не опубликован: с хоста недоступен, внутри контейнера отдаётся), события потока в панели стенда. Дашбордов, сбора логов, трассировки и алертов нет.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Решение заказчика проекта (24.09.2026, со слов): в реальном контуре используется Grafana — своя не разворачивается. Варианты по источнику данных: A — Prometheus владельца, B — свой Prometheus как источник для их Grafana, C — Zabbix как источник, D — своя четвёрка (прежний выбор, запасной). ELK/OpenSearch отклонён как тяжёлый, облачный мониторинг — из-за 152-ФЗ. Прежнее «Zabbix отклонён: ориентирован на хосты» не проверялось. Сравнение по документации; пробного развёртывания не было.</t>
+          <t>Факты со слов заказчика проекта (24.09.2026): в реальном контуре работают Grafana, Zabbix и Jaeger; алерты не настроены. Основной вариант C — Zabbix собирает метрики с порта 9100, Grafana владельца показывает, алерты — триггеры Zabbix; запасной B — свой Prometheus как источник для Grafana (если Zabbix не справится с задержкой P99: квантили по гистограммам штатно не считает — по документации, не проверялось). Prometheus владельца снят (не назван), своя четвёрка и ELK/облако отклонены. Прежнее «Zabbix отклонён: ориентирован на хосты» не проверялось. Сравнение по документации.</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -2878,22 +2878,22 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Неизвестно, какие источники подключены к Grafana владельца, есть ли Prometheus, собирающий метрики подов, есть ли Alertmanager и как собираются логи; как принимаются дашборды. Метрики есть, но собирать и показывать их нечему.</t>
+          <t>Алерты не настроены: 9 описанных алертов (в том числе «Утечка ПДн в ответе») принимать некому — нет каналов и получателей; предложение автора: настроенный алерт об утечке ПДн — условие включения MVP (согласовать с ИБ). Не известны версии Zabbix, Grafana, Jaeger, подключение Zabbix к Grafana, возможность считать квантили, сбор логов. Трассировки в нашем коде нет (Jaeger в контуре есть).</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>Дашборды нашего сервиса как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; правила 9 алертов как код; правило сбора метрик с порта 9100 (ServiceMonitor или аннотации) либо свой Prometheus как источник; в логах только отчёт об обезличивании, без значений ПДн. Оценка не пересматривалась: развёртывание своей Grafana отпало, но добавились согласование и интеграция с чужой.</t>
+          <t>Дашборды как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; 9 алертов как триггеры и действия Zabbix; сбор метрик с порта 9100; проверка расчёта P99 в Zabbix до начала работ; определение получателей и каналов оповещения; в логах только отчёт об обезличивании. Оценка не пересматривалась (5–8): развёртывание своей связки отпало, добавились интеграция с Zabbix и настройка оповещений. Трассировка OpenTelemetry → Jaeger — по необходимости, 2–4 чел-дн, оценка автора, в итог не входит.</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Grafana владельца; prometheus-client (порт 9100); источник данных и Prometheus, Loki, Alertmanager — по ответу владельца (для расчёта узлов оставлены как верхняя оценка, без Grafana).</t>
+          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); Prometheus и Loki — верхняя оценка до ответа владельца.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах; Grafana уже есть у владельца, дублировать её незачем.</t>
+          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах; мониторинг и Grafana уже есть у владельца, дублировать их незачем.</t>
         </is>
       </c>
       <c r="M24" s="12" t="n">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="105" customHeight="1">
+    <row r="20" ht="120" customHeight="1">
       <c r="A20" s="50" t="n">
         <v>16</v>
       </c>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 5 узлов (3 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ; на границе округления, возможно 6), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -7022,7 +7022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Grafana в расчёт не входит: в реальном контуре используется Grafana владельца (решение заказчика проекта, со слов). Prometheus, Loki и Alertmanager оставлены как верхняя оценка до ответа владельца, какие источники данных у него подключены; если у него они есть, эти поды из расчёта уходят.</t>
+          <t>В реальном контуре работают Grafana, Zabbix и Jaeger (решение заказчика проекта, со слов); алерты не настроены. Grafana и Alertmanager в расчёт не входят. Prometheus (запасной источник для задержки P99) и Loki (как собираются логи, неизвестно) оставлены как верхняя оценка до ответа владельца.</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Загрузка узла по запросам не выше 70%. Класс узлов: общий — 8 vCPU / 16 ГиБ; данных — 8 vCPU / 32 ГиБ с NVMe; GPU — 8 vCPU / 32 ГиБ и видеокарта 24 ГБ; LLM (тираж) — 16 vCPU / 128 ГиБ и A100 80 ГБ.</t>
+          <t>Загрузка узла по запросам не выше 70%. Класс узлов: общий — 8 vCPU / 16 ГиБ; данных — 8 vCPU / 32 ГиБ с NVMe; GPU — 8 vCPU / 32 ГиБ и видеокарта 24 ГБ; LLM (тираж) — 16 vCPU / 128 ГиБ и A100 80 ГБ. Число узлов общего пула на MVP на 24 сентября 2026 находится на границе округления: расчётная нагрузка 11,2 vCPU при допустимых 11,2 на двух узлах; любое допущение, выросшее на 0,1 vCPU, добавляет узел (итог 6 вместо 5).</t>
         </is>
       </c>
     </row>
@@ -8127,31 +8127,31 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="50" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Alertmanager</t>
+          <t>Qdrant</t>
         </is>
       </c>
       <c r="D26" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F26" s="51" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H26" s="51" t="n">
         <v>0</v>
@@ -8173,16 +8173,16 @@
         <v/>
       </c>
       <c r="M26" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="51" t="n">
-        <v>0.1</v>
-      </c>
       <c r="O26" s="51" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="P26" s="51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="51" t="n">
         <v>0</v>
@@ -8205,11 +8205,11 @@
       </c>
       <c r="V26" s="9" t="inlineStr">
         <is>
-          <t>Допущение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
+          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
       <c r="A27" s="50" t="n">
         <v>12</v>
       </c>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Qdrant</t>
+          <t>Postgres (обращения, профиль, телеметрия, журнал диалогов)</t>
         </is>
       </c>
       <c r="D27" s="51" t="n">
@@ -8233,7 +8233,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H27" s="51" t="n">
         <v>0</v>
@@ -8264,7 +8264,7 @@
         <v>2</v>
       </c>
       <c r="P27" s="51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Q27" s="51" t="n">
         <v>0</v>
@@ -8287,11 +8287,11 @@
       </c>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="90" customHeight="1">
+          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (заложено 3 КБ на абонента; по примеру прототипа — 0,7 КБ на счёт в CSV); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="50" t="n">
         <v>13</v>
       </c>
@@ -8302,20 +8302,20 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Postgres (обращения, профиль, телеметрия, журнал диалогов)</t>
+          <t>Redis (квоты и сессии)</t>
         </is>
       </c>
       <c r="D28" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F28" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G28" s="51" t="n">
         <v>1</v>
-      </c>
-      <c r="F28" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="51" t="n">
-        <v>20</v>
       </c>
       <c r="H28" s="51" t="n">
         <v>0</v>
@@ -8340,13 +8340,13 @@
         <v>2</v>
       </c>
       <c r="N28" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O28" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P28" s="51" t="n">
         <v>1</v>
-      </c>
-      <c r="O28" s="51" t="n">
-        <v>2</v>
-      </c>
-      <c r="P28" s="51" t="n">
-        <v>50</v>
       </c>
       <c r="Q28" s="51" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (заложено 3 КБ на абонента; по примеру прототипа — 0,7 КБ на счёт в CSV); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
+          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
         </is>
       </c>
     </row>
@@ -8384,20 +8384,20 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Redis (квоты и сессии)</t>
+          <t>MinIO (документы, копии, снимки)</t>
         </is>
       </c>
       <c r="D29" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="51" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="F29" s="51" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G29" s="51" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H29" s="51" t="n">
         <v>0</v>
@@ -8419,16 +8419,16 @@
         <v/>
       </c>
       <c r="M29" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N29" s="51" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="O29" s="51" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P29" s="51" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="Q29" s="51" t="n">
         <v>0</v>
@@ -8451,38 +8451,39 @@
       </c>
       <c r="V29" s="9" t="inlineStr">
         <is>
-          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="50" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>gpu</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>MinIO (документы, копии, снимки)</t>
-        </is>
-      </c>
-      <c r="D30" s="51" t="n">
+          <t>Эмбеддинги (BGE-M3, inference) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D30" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="E30" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="51" t="n">
-        <v>0.25</v>
-      </c>
       <c r="F30" s="51" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="51" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H30" s="51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="53">
         <f>D30*E30</f>
@@ -8500,20 +8501,21 @@
         <f>D30*H30</f>
         <v/>
       </c>
-      <c r="M30" s="51" t="n">
+      <c r="M30" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="N30" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="O30" s="51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P30" s="51" t="n">
-        <v>400</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" s="53">
         <f>M30*N30</f>
@@ -8533,7 +8535,7 @@
       </c>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
+          <t>Замер: веса 2,14 ГиБ (fp32; прежние 4,25 ГБ — две копии в кэше). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
         </is>
       </c>
     </row>
@@ -8548,7 +8550,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Эмбеддинги (BGE-M3, inference) [вариант с GPU]</t>
+          <t>Реранкер (BGE-reranker-v2-m3, inference) [вариант с GPU]</t>
         </is>
       </c>
       <c r="D31" s="51">
@@ -8559,13 +8561,13 @@
         <v>1</v>
       </c>
       <c r="F31" s="51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H31" s="51" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I31" s="53">
         <f>D31*E31</f>
@@ -8591,13 +8593,13 @@
         <v>1</v>
       </c>
       <c r="O31" s="51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P31" s="51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="51" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R31" s="53">
         <f>M31*N31</f>
@@ -8617,7 +8619,7 @@
       </c>
       <c r="V31" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32; прежние 4,25 ГБ — две копии в кэше). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
+          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
         </is>
       </c>
     </row>
@@ -8627,29 +8629,28 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>gpu-llm</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Реранкер (BGE-reranker-v2-m3, inference) [вариант с GPU]</t>
-        </is>
-      </c>
-      <c r="D32" s="51">
-        <f>1*$C$12</f>
-        <v/>
+          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
+        </is>
+      </c>
+      <c r="D32" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F32" s="51" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="G32" s="51" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H32" s="51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I32" s="53">
         <f>D32*E32</f>
@@ -8667,21 +8668,20 @@
         <f>D32*H32</f>
         <v/>
       </c>
-      <c r="M32" s="51">
-        <f>1*$C$12</f>
-        <v/>
+      <c r="M32" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="N32" s="51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O32" s="51" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="P32" s="51" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="Q32" s="51" t="n">
-        <v>1.5</v>
+        <v>40</v>
       </c>
       <c r="R32" s="53">
         <f>M32*N32</f>
@@ -8701,35 +8701,36 @@
       </c>
       <c r="V32" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="50" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>gpu-llm</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
-        </is>
-      </c>
-      <c r="D33" s="51" t="n">
-        <v>0</v>
+          <t>Эмбеддинги (e5-small на CPU) [вариант без GPU]</t>
+        </is>
+      </c>
+      <c r="D33" s="51">
+        <f>2*(1-$C$12)</f>
+        <v/>
       </c>
       <c r="E33" s="51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F33" s="51" t="n">
-        <v>64</v>
+        <v>1.5</v>
       </c>
       <c r="G33" s="51" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H33" s="51" t="n">
         <v>0</v>
@@ -8750,20 +8751,21 @@
         <f>D33*H33</f>
         <v/>
       </c>
-      <c r="M33" s="51" t="n">
+      <c r="M33" s="51">
+        <f>2*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="N33" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="51" t="n">
-        <v>8</v>
-      </c>
       <c r="O33" s="51" t="n">
-        <v>64</v>
+        <v>1.5</v>
       </c>
       <c r="P33" s="51" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="51" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R33" s="53">
         <f>M33*N33</f>
@@ -8783,7 +8785,7 @@
       </c>
       <c r="V33" s="9" t="inlineStr">
         <is>
-          <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
+          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7,2 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
         </is>
       </c>
     </row>
@@ -8798,21 +8800,21 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Эмбеддинги (e5-small на CPU) [вариант без GPU]</t>
+          <t>ETL индексации: эмбеддинги на CPU (CronJob) [вариант без GPU]</t>
         </is>
       </c>
       <c r="D34" s="51">
-        <f>2*(1-$C$12)</f>
+        <f>1*(1-$C$12)</f>
         <v/>
       </c>
       <c r="E34" s="51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34" s="51" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G34" s="51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H34" s="51" t="n">
         <v>0</v>
@@ -8834,17 +8836,17 @@
         <v/>
       </c>
       <c r="M34" s="51">
-        <f>2*(1-$C$12)</f>
+        <f>1*(1-$C$12)</f>
         <v/>
       </c>
       <c r="N34" s="51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O34" s="51" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="P34" s="51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q34" s="51" t="n">
         <v>0</v>
@@ -8867,197 +8869,169 @@
       </c>
       <c r="V34" s="9" t="inlineStr">
         <is>
-          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7,2 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="50" t="n">
-        <v>20</v>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
+          <t>Расчёт по замеру: e5-small ≈27 мс на часть (машина с 12 потоками) → 30–100 тыс. частей ≈14–46 мин; на поде с 4 vCPU время не измерялось и может быть в 2–3 раза больше (окно 3 часа). Только в варианте без GPU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>Итог по пулам узлов</t>
+        </is>
+      </c>
+      <c r="P36" s="9" t="inlineStr">
+        <is>
+          <t>Загрузка узла по запросам, не выше</t>
+        </is>
+      </c>
+      <c r="Q36" s="54" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Пул</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Класс узла</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>vCPU узла</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>ОЗУ узла, ГиБ</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Видеопамять узла, ГиБ</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Запас на потерю узла (1 — да)</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>MVP: vCPU</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>MVP: ОЗУ</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>MVP: видеопамять</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>MVP: узлов</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Тираж: vCPU</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Тираж: ОЗУ</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>Тираж: видеопамять</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>Тираж: узлов</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>general</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>ETL индексации: эмбеддинги на CPU (CronJob) [вариант без GPU]</t>
-        </is>
-      </c>
-      <c r="D35" s="51">
-        <f>1*(1-$C$12)</f>
-        <v/>
-      </c>
-      <c r="E35" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="H35" s="51" t="n">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F38" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="53">
-        <f>D35*E35</f>
-        <v/>
-      </c>
-      <c r="J35" s="53">
-        <f>D35*F35</f>
-        <v/>
-      </c>
-      <c r="K35" s="53">
-        <f>D35*G35</f>
-        <v/>
-      </c>
-      <c r="L35" s="53">
-        <f>D35*H35</f>
-        <v/>
-      </c>
-      <c r="M35" s="51">
-        <f>1*(1-$C$12)</f>
-        <v/>
-      </c>
-      <c r="N35" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="O35" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="P35" s="51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="53">
-        <f>M35*N35</f>
-        <v/>
-      </c>
-      <c r="S35" s="53">
-        <f>M35*O35</f>
-        <v/>
-      </c>
-      <c r="T35" s="53">
-        <f>M35*P35</f>
-        <v/>
-      </c>
-      <c r="U35" s="53">
-        <f>M35*Q35</f>
-        <v/>
-      </c>
-      <c r="V35" s="9" t="inlineStr">
-        <is>
-          <t>Расчёт по замеру: e5-small ≈27 мс на часть (машина с 12 потоками) → 30–100 тыс. частей ≈14–46 мин; на поде с 4 vCPU время не измерялось и может быть в 2–3 раза больше (окно 3 часа). Только в варианте без GPU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" s="43" t="inlineStr">
-        <is>
-          <t>Итог по пулам узлов</t>
-        </is>
-      </c>
-      <c r="P37" s="9" t="inlineStr">
-        <is>
-          <t>Загрузка узла по запросам, не выше</t>
-        </is>
-      </c>
-      <c r="Q37" s="54" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Пул</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Класс узла</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>vCPU узла</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>ОЗУ узла, ГиБ</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>Видеопамять узла, ГиБ</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>Запас на потерю узла (1 — да)</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>MVP: vCPU</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>MVP: ОЗУ</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>MVP: видеопамять</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>MVP: узлов</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Тираж: vCPU</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Тираж: ОЗУ</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>Тираж: видеопамять</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>Тираж: узлов</t>
-        </is>
+      <c r="G38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="55">
+        <f>SUMIF($B$16:$B$34,$B38,$I$16:$I$34)</f>
+        <v/>
+      </c>
+      <c r="I38" s="55">
+        <f>SUMIF($B$16:$B$34,$B38,$J$16:$J$34)</f>
+        <v/>
+      </c>
+      <c r="J38" s="55">
+        <f>SUMIF($B$16:$B$34,$B38,$L$16:$L$34)</f>
+        <v/>
+      </c>
+      <c r="K38" s="56">
+        <f>IF(H38=0,0,ROUNDUP(MAX(H38/($Q$36*$D38),I38/($Q$36*$E38),IF($F38&gt;0,J38/($Q$36*$F38),0)),0)+$G38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="55">
+        <f>SUMIF($B$16:$B$34,$B38,$R$16:$R$34)</f>
+        <v/>
+      </c>
+      <c r="M38" s="55">
+        <f>SUMIF($B$16:$B$34,$B38,$S$16:$S$34)</f>
+        <v/>
+      </c>
+      <c r="N38" s="55">
+        <f>SUMIF($B$16:$B$34,$B38,$U$16:$U$34)</f>
+        <v/>
+      </c>
+      <c r="O38" s="56">
+        <f>IF(L38=0,0,ROUNDUP(MAX(L38/($Q$36*$D38),M38/($Q$36*$E38),IF($F38&gt;0,N38/($Q$36*$F38),0)),0)+$G38)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
+          <t>Пул данных (NVMe)</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
         <v>8</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>0</v>
@@ -9066,47 +9040,47 @@
         <v>1</v>
       </c>
       <c r="H39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$I$16:$I$35)</f>
+        <f>SUMIF($B$16:$B$34,$B39,$I$16:$I$34)</f>
         <v/>
       </c>
       <c r="I39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$J$16:$J$35)</f>
+        <f>SUMIF($B$16:$B$34,$B39,$J$16:$J$34)</f>
         <v/>
       </c>
       <c r="J39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$L$16:$L$35)</f>
+        <f>SUMIF($B$16:$B$34,$B39,$L$16:$L$34)</f>
         <v/>
       </c>
       <c r="K39" s="56">
-        <f>IF(H39=0,0,ROUNDUP(MAX(H39/($Q$37*$D39),I39/($Q$37*$E39),IF($F39&gt;0,J39/($Q$37*$F39),0)),0)+$G39)</f>
+        <f>IF(H39=0,0,ROUNDUP(MAX(H39/($Q$36*$D39),I39/($Q$36*$E39),IF($F39&gt;0,J39/($Q$36*$F39),0)),0)+$G39)</f>
         <v/>
       </c>
       <c r="L39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$R$16:$R$35)</f>
+        <f>SUMIF($B$16:$B$34,$B39,$R$16:$R$34)</f>
         <v/>
       </c>
       <c r="M39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$S$16:$S$35)</f>
+        <f>SUMIF($B$16:$B$34,$B39,$S$16:$S$34)</f>
         <v/>
       </c>
       <c r="N39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$U$16:$U$35)</f>
+        <f>SUMIF($B$16:$B$34,$B39,$U$16:$U$34)</f>
         <v/>
       </c>
       <c r="O39" s="56">
-        <f>IF(L39=0,0,ROUNDUP(MAX(L39/($Q$37*$D39),M39/($Q$37*$E39),IF($F39&gt;0,N39/($Q$37*$F39),0)),0)+$G39)</f>
+        <f>IF(L39=0,0,ROUNDUP(MAX(L39/($Q$36*$D39),M39/($Q$36*$E39),IF($F39&gt;0,N39/($Q$36*$F39),0)),0)+$G39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>gpu</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Пул данных (NVMe)</t>
+          <t>GPU-пул (эмбеддинги, реранкер)</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
@@ -9116,188 +9090,132 @@
         <v>32</v>
       </c>
       <c r="F40" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G40" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="H40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$I$16:$I$35)</f>
+        <f>SUMIF($B$16:$B$34,$B40,$I$16:$I$34)</f>
         <v/>
       </c>
       <c r="I40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$J$16:$J$35)</f>
+        <f>SUMIF($B$16:$B$34,$B40,$J$16:$J$34)</f>
         <v/>
       </c>
       <c r="J40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$L$16:$L$35)</f>
+        <f>SUMIF($B$16:$B$34,$B40,$L$16:$L$34)</f>
         <v/>
       </c>
       <c r="K40" s="56">
-        <f>IF(H40=0,0,ROUNDUP(MAX(H40/($Q$37*$D40),I40/($Q$37*$E40),IF($F40&gt;0,J40/($Q$37*$F40),0)),0)+$G40)</f>
+        <f>IF(H40=0,0,ROUNDUP(MAX(H40/($Q$36*$D40),I40/($Q$36*$E40),IF($F40&gt;0,J40/($Q$36*$F40),0)),0)+$G40)</f>
         <v/>
       </c>
       <c r="L40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$R$16:$R$35)</f>
+        <f>SUMIF($B$16:$B$34,$B40,$R$16:$R$34)</f>
         <v/>
       </c>
       <c r="M40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$S$16:$S$35)</f>
+        <f>SUMIF($B$16:$B$34,$B40,$S$16:$S$34)</f>
         <v/>
       </c>
       <c r="N40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$U$16:$U$35)</f>
+        <f>SUMIF($B$16:$B$34,$B40,$U$16:$U$34)</f>
         <v/>
       </c>
       <c r="O40" s="56">
-        <f>IF(L40=0,0,ROUNDUP(MAX(L40/($Q$37*$D40),M40/($Q$37*$E40),IF($F40&gt;0,N40/($Q$37*$F40),0)),0)+$G40)</f>
+        <f>IF(L40=0,0,ROUNDUP(MAX(L40/($Q$36*$D40),M40/($Q$36*$E40),IF($F40&gt;0,N40/($Q$36*$F40),0)),0)+$G40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>gpu-llm</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>GPU-пул (эмбеддинги, реранкер)</t>
+          <t>GPU-пул генерации (тираж)</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$I$16:$I$35)</f>
+        <f>SUMIF($B$16:$B$34,$B41,$I$16:$I$34)</f>
         <v/>
       </c>
       <c r="I41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$J$16:$J$35)</f>
+        <f>SUMIF($B$16:$B$34,$B41,$J$16:$J$34)</f>
         <v/>
       </c>
       <c r="J41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$L$16:$L$35)</f>
+        <f>SUMIF($B$16:$B$34,$B41,$L$16:$L$34)</f>
         <v/>
       </c>
       <c r="K41" s="56">
-        <f>IF(H41=0,0,ROUNDUP(MAX(H41/($Q$37*$D41),I41/($Q$37*$E41),IF($F41&gt;0,J41/($Q$37*$F41),0)),0)+$G41)</f>
+        <f>IF(H41=0,0,ROUNDUP(MAX(H41/($Q$36*$D41),I41/($Q$36*$E41),IF($F41&gt;0,J41/($Q$36*$F41),0)),0)+$G41)</f>
         <v/>
       </c>
       <c r="L41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$R$16:$R$35)</f>
+        <f>SUMIF($B$16:$B$34,$B41,$R$16:$R$34)</f>
         <v/>
       </c>
       <c r="M41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$S$16:$S$35)</f>
+        <f>SUMIF($B$16:$B$34,$B41,$S$16:$S$34)</f>
         <v/>
       </c>
       <c r="N41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$U$16:$U$35)</f>
+        <f>SUMIF($B$16:$B$34,$B41,$U$16:$U$34)</f>
         <v/>
       </c>
       <c r="O41" s="56">
-        <f>IF(L41=0,0,ROUNDUP(MAX(L41/($Q$37*$D41),M41/($Q$37*$E41),IF($F41&gt;0,N41/($Q$37*$F41),0)),0)+$G41)</f>
+        <f>IF(L41=0,0,ROUNDUP(MAX(L41/($Q$36*$D41),M41/($Q$36*$E41),IF($F41&gt;0,N41/($Q$36*$F41),0)),0)+$G41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>gpu-llm</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>GPU-пул генерации (тираж)</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>128</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$I$16:$I$35)</f>
-        <v/>
-      </c>
-      <c r="I42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$J$16:$J$35)</f>
-        <v/>
-      </c>
-      <c r="J42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$L$16:$L$35)</f>
-        <v/>
-      </c>
-      <c r="K42" s="56">
-        <f>IF(H42=0,0,ROUNDUP(MAX(H42/($Q$37*$D42),I42/($Q$37*$E42),IF($F42&gt;0,J42/($Q$37*$F42),0)),0)+$G42)</f>
-        <v/>
-      </c>
-      <c r="L42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$R$16:$R$35)</f>
-        <v/>
-      </c>
-      <c r="M42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$S$16:$S$35)</f>
-        <v/>
-      </c>
-      <c r="N42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$U$16:$U$35)</f>
-        <v/>
-      </c>
-      <c r="O42" s="56">
-        <f>IF(L42=0,0,ROUNDUP(MAX(L42/($Q$37*$D42),M42/($Q$37*$E42),IF($F42&gt;0,N42/($Q$37*$F42),0)),0)+$G42)</f>
+          <t>Итого узлов</t>
+        </is>
+      </c>
+      <c r="K42" s="57">
+        <f>SUM(K38:K41)</f>
+        <v/>
+      </c>
+      <c r="O42" s="57">
+        <f>SUM(O38:O41)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Итого узлов</t>
-        </is>
-      </c>
-      <c r="K43" s="57">
-        <f>SUM(K39:K42)</f>
-        <v/>
-      </c>
-      <c r="O43" s="57">
-        <f>SUM(O39:O42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="11" t="inlineStr">
-        <is>
           <t>Диск под тома, ГиБ</t>
         </is>
       </c>
-      <c r="K44" s="58">
-        <f>SUM($K$16:$K$35)</f>
-        <v/>
-      </c>
-      <c r="O44" s="58">
-        <f>SUM($T$16:$T$35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="33" t="inlineStr">
+      <c r="K43" s="58">
+        <f>SUM($K$16:$K$34)</f>
+        <v/>
+      </c>
+      <c r="O43" s="58">
+        <f>SUM($T$16:$T$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); управляющая часть Kubernetes размещена на трёх узлах общего пула (допущение); нагрузочный тест не проводился.</t>
         </is>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2883,7 +2883,7 @@
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>Дашборды как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; 9 алертов как триггеры и действия Zabbix; сбор метрик с порта 9100; проверка расчёта P99 в Zabbix до начала работ; определение получателей и каналов оповещения; в логах только отчёт об обезличивании. Оценка не пересматривалась (5–8): развёртывание своей связки отпало, добавились интеграция с Zabbix и настройка оповещений. Трассировка OpenTelemetry → Jaeger — по необходимости, 2–4 чел-дн, оценка автора, в итог не входит.</t>
+          <t>Дашборды как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; 9 алертов как триггеры и действия Zabbix; сбор метрик с порта 9100; проверка расчёта P99 в Zabbix до начала работ; определение получателей и каналов оповещения; в логах только отчёт об обезличивании. Проверка на стенде владельца до выбора между Zabbix (C) и своим Prometheus (B): сбор с порта 9100, расчёт P99, доставка алерта, плагин Grafana, нагрузка на Zabbix (1–2 чел-дн, предложение автора). Алерты: триггеры Zabbix (при B — Grafana Alerting; Alertmanager не разворачиваем); алерт об утечке ПДн — сразу, без подавления повторов, получатель от ИБ; алерт о недоступности источника метрик. Трассировка: на MVP без Jaeger — две гистограммы (поиск, вызов провайдера) 0,5–1 чел-дн в пределах оценки; OpenTelemetry → Jaeger — только если P99 разобрать не удаётся, 2–4 чел-дн, оценка автора, в итог не входит. Оценка не пересматривалась (5–8): развёртывание своей связки отпало, добавились интеграция с Zabbix и настройка оповещений.</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прогноз стоимости" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2927,60 +2927,64 @@
       <c r="A25" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>Связь</t>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Виджет ↔ Backend</t>
+          <t>Алерты и оповещения</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>AI-виджет; Backend</t>
+          <t>Zabbix владельца (триггеры, действия); Backend и LLM Gateway (метрики блокировок и утечек); Grafana владельца (запасной вариант)</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
+          <t>Триггеры и действия Zabbix; Grafana Alerting — запасной вариант</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
+          <t>9 алертов описаны (от «Утечка ПДн в ответе» до «ИБ + деградация»), спецификации дашборда в репозитории нет. В реальном контуре алерты не настроены (со слов заказчика проекта, 24.09.2026): каналов оповещения и получателей нет. В нашем коде есть метрики блокировок и утечек, правил и доставки нет.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
+          <t>Триггеры и действия Zabbix (выбраны при основном варианте C) — против Grafana Alerting (при запасном варианте B, если в Zabbix настроить нельзя) и Alertmanager (не разворачиваем: дублирует Zabbix и Grafana владельца). Сравнение по документации, у владельца не проверялось; каналы оповещения не настроены.</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
+          <t>ADR-200, подраздел «Наблюдаемость: Grafana владельца и источники данных», блок «Алерты: сравнение вариантов»</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K25" s="15" t="n"/>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="n"/>
-      <c r="N25" s="16" t="n"/>
-      <c r="O25" s="15" t="n"/>
+          <t>Получатели, канал, регламент реакции и эскалация не определены; без них алерты «Утечка ПДн в ответе» и «ИБ + деградация» на MVP не сработают. Версия Zabbix и его возможности по оповещениям неизвестны. Настроены ли алерты в Zabbix вообще или только для нашего сервиса — неизвестно.</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>9 алертов как триггеры и действия Zabbix (при запасном варианте B — правила Grafana Alerting); требования к любому варианту: алерт об утечке ПДн приходит сразу и без подавления повторов получателю от ИБ; алерт о недоступности источника метрик; получатели, канал, регламент и эскалация определены до включения MVP (предложение автора, согласовать с ИБ); пороги срабатывания — по замеру на живых данных.</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Zabbix владельца (триггеры, действия, каналы); Grafana Alerting — запасной вариант.</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Без алерта об утечке ПДн нарушение 152-ФЗ обнаружится не сразу; оценка входит в строку «Наблюдаемость (метрики, логи, алерты)», отдельно не считается.</t>
+        </is>
+      </c>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="9" t="n"/>
       <c r="P25" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -2993,7 +2997,7 @@
       <c r="U25" s="15" t="n"/>
       <c r="V25" s="9" t="inlineStr">
         <is>
-          <t>API_Spec.yaml</t>
+          <t>ADR-200; ADR-400</t>
         </is>
       </c>
     </row>
@@ -3001,70 +3005,70 @@
       <c r="A26" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Связь</t>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Платформа ЛК (SSO)</t>
+          <t>Трассировка (Jaeger)</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Backend; Платформа ЛК (внешняя)</t>
+          <t>Backend; LLM Gateway; клиенты Qdrant, Postgres, Redis; Jaeger владельца</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
+          <t>OpenTelemetry (Python), OTLP, Jaeger владельца — по условию</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Не подключена: абонент выбирается из справочника стенда.</t>
+          <t>Jaeger в реальном контуре есть (со слов заказчика проекта, 24.09.2026). В нашем коде трассировки нет (библиотек OpenTelemetry и Jaeger в проекте нет). Гистограммы задержки есть для ответа, первого куска, проверки ответа и обезличивания; для поиска в базе знаний и вызова провайдера — нет.</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
+          <t>Вариант 1 — без трассировки, метрики по стадиям (по умолчанию для MVP) — против варианта 2 — OpenTelemetry → Jaeger владельца (по условию: P99 по метрикам разобрать не удаётся) и варианта 3 — свой Jaeger (отклонён: в контуре он есть). Сравнение по документации; приём OTLP в Jaeger владельца не проверялся.</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
+          <t>ADR-200, подраздел «Наблюдаемость: Grafana владельца и источники данных», блок «Трассировка (Jaeger): сравнение вариантов»; ADR-600, «Трассировка OpenTelemetry → Jaeger — по необходимости»</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
+          <t>Без гистограмм поиска и вызова провайдера задержку P99 по стадиям не разобрать. Принимает ли Jaeger владельца OTLP, версия и права — неизвестно. Трассы не должны содержать ПДн в атрибутах спанов.</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
+          <t>На MVP без трассировки: две гистограммы (поиск в базе знаний, вызов провайдера) — 0,5–1 чел-дн внутри оценки строки «Наблюдаемость» (оценка автора). Инструментация OpenTelemetry (FastAPI, HTTP-клиенты, клиенты Qdrant, Postgres, Redis) с отправкой по OTLP в Jaeger владельца — только если после гистограмм P99 разобрать не удаётся: 2–4 чел-дн, оценка автора, в итог не входит.</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
+          <t>OpenTelemetry (Python), OTLP, Jaeger владельца — по условию.</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
+          <t>Трассировка полезна для разбора P99 и TTFT по стадиям, но на четырёх стадиях линейной цепочки метрик обычно хватает; не тратим работу без необходимости.</t>
+        </is>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" s="13" t="inlineStr">
+        <is>
+          <t>По триггеру (P99 по метрикам разобрать не удаётся; оценка автора)</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
@@ -3079,7 +3083,7 @@
       <c r="U26" s="15" t="n"/>
       <c r="V26" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>ADR-200; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3094,65 +3098,53 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Биллинг (чтение фактов)</t>
+          <t>Виджет ↔ Backend</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Backend; Кэш профиля (пересчёт из Биллинга); Биллинг (внешняя)</t>
+          <t>AI-виджет; Backend</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
+          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
+          <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
+          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры API Биллинга от владельца не получены.</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>Свежие факты запрашиваются у Биллинга в момент вопроса.</t>
-        </is>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>XML-RPC API Биллинга.</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
-        </is>
-      </c>
-      <c r="M27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+          <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K27" s="15" t="n"/>
+      <c r="L27" s="15" t="inlineStr">
+        <is>
+          <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="n"/>
+      <c r="N27" s="16" t="n"/>
+      <c r="O27" s="15" t="n"/>
       <c r="P27" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3165,7 +3157,7 @@
       <c r="U27" s="15" t="n"/>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>API_Spec.yaml</t>
         </is>
       </c>
     </row>
@@ -3180,63 +3172,63 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Диспетчерская</t>
+          <t>Backend ↔ Платформа ЛК (SSO)</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
+          <t>Backend; Платформа ЛК (внешняя)</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
+          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
+          <t>Не подключена: абонент выбирается из справочника стенда.</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Прямой доступ к чужой БД запрещён.</t>
+          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
+          <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
+          <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>REST API Диспетчерской.</t>
+          <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
-        </is>
-      </c>
-      <c r="M28" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
+          <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
+        </is>
+      </c>
+      <c r="M28" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
@@ -3251,7 +3243,7 @@
       <c r="U28" s="15" t="n"/>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-400; ADR-600</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3266,57 +3258,65 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ LLM Gateway</t>
+          <t>Backend ↔ Биллинг (чтение фактов)</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Backend; LLM Gateway</t>
+          <t>Backend; Кэш профиля (пересчёт из Биллинга); Биллинг (внешняя)</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
+          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Вызов внутри одного процесса.</t>
+          <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
+          <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Сигнатуры API Биллинга от владельца не получены.</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
+          <t>Свежие факты запрашиваются у Биллинга в момент вопроса.</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>HTTP внутри кластера.</t>
+          <t>XML-RPC API Биллинга.</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
-        </is>
-      </c>
-      <c r="M29" s="19" t="n"/>
-      <c r="N29" s="19" t="n"/>
-      <c r="O29" s="9" t="n"/>
+          <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3329,7 +3329,7 @@
       <c r="U29" s="15" t="n"/>
       <c r="V29" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3344,49 +3344,65 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Qdrant</t>
+          <t>Backend ↔ Диспетчерская</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Backend; Qdrant</t>
+          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client по HTTP (порт 6333)</t>
+          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>HTTP (порт 6333); запись — отдельным сервисом, Backend только читает готовый индекс.</t>
+          <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Клиент по HTTP, а не gRPC: задержка HTTP-вызова — единицы миллисекунд при бюджете поиска 100 мс, gRPC добавил бы зависимость без выигрыша.</t>
+          <t>Прямой доступ к чужой БД запрещён.</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="16" t="n"/>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="15" t="n"/>
+          <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>REST API Диспетчерской.</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
+        </is>
+      </c>
+      <c r="M30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3399,7 +3415,7 @@
       <c r="U30" s="15" t="n"/>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3414,78 +3430,70 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>LLM Gateway ↔ LLM Provider</t>
+          <t>Backend ↔ LLM Gateway</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>LLM Gateway; внешний LLM Provider</t>
+          <t>Backend; LLM Gateway</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
+          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
+          <t>Вызов внутри одного процесса.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
+          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
+          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
+          <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>HTTPS, сертификаты НУЦ Минцифры.</t>
+          <t>HTTP внутри кластера.</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
+          <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
         </is>
       </c>
       <c r="M31" s="19" t="n"/>
       <c r="N31" s="19" t="n"/>
       <c r="O31" s="9" t="n"/>
-      <c r="P31" s="9" t="inlineStr">
-        <is>
-          <t>Вызов собственной модели внутри закрытого контура.</t>
-        </is>
-      </c>
-      <c r="Q31" s="9" t="inlineStr">
-        <is>
-          <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
-        </is>
-      </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
-        </is>
-      </c>
-      <c r="S31" s="19" t="n"/>
-      <c r="T31" s="19" t="n"/>
-      <c r="U31" s="9" t="n"/>
+      <c r="P31" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q31" s="15" t="n"/>
+      <c r="R31" s="15" t="n"/>
+      <c r="S31" s="16" t="n"/>
+      <c r="T31" s="16" t="n"/>
+      <c r="U31" s="15" t="n"/>
       <c r="V31" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
     </row>
@@ -3500,32 +3508,32 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Индексация → Qdrant</t>
+          <t>Backend ↔ Qdrant</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>ETL индексации; Qdrant</t>
+          <t>Backend; Qdrant</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
+          <t>qdrant-client по HTTP (порт 6333)</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
+          <t>HTTP (порт 6333); запись — отдельным сервисом, Backend только читает готовый индекс.</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
+          <t>Клиент по HTTP, а не gRPC: задержка HTTP-вызова — единицы миллисекунд при бюджете поиска 100 мс, gRPC добавил бы зависимость без выигрыша.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -3539,11 +3547,7 @@
         </is>
       </c>
       <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
-        </is>
-      </c>
+      <c r="L32" s="15" t="n"/>
       <c r="M32" s="16" t="n"/>
       <c r="N32" s="16" t="n"/>
       <c r="O32" s="15" t="n"/>
@@ -3567,89 +3571,85 @@
       <c r="A33" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>Сквозная работа</t>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>Связь</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Смета CAPEX/OPEX, NFR, допущения о нагрузке</t>
+          <t>LLM Gateway ↔ LLM Provider</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
+          <t>LLM Gateway; внешний LLM Provider</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
+          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 234–101 280 ₽ в месяц, на тираже 3 305 ₽–1,07 млн ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
+          <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии.</t>
+          <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
+          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>Разброс стоимости токенов на MVP — ×82 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
+          <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой. Первый пересчёт сметы по данным обращений и ЛК (3–5 чел-дн, после получения данных) и повторный по пилоту (1–2 чел-дн): подставить данные в лист «Прогноз стоимости», пересчитать нагрузку, стоимость и sizing, обновить отчёт о мощности, ADR-500 и матрицу.</t>
+          <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HTTPS, сертификаты НУЦ Минцифры.</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>Без этого нельзя защищать бюджет.</t>
-        </is>
-      </c>
-      <c r="M33" s="25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N33" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="O33" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: P0</t>
-        </is>
-      </c>
-      <c r="P33" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q33" s="15" t="n"/>
-      <c r="R33" s="15" t="inlineStr">
-        <is>
-          <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
-        </is>
-      </c>
-      <c r="S33" s="16" t="n"/>
-      <c r="T33" s="16" t="n"/>
-      <c r="U33" s="15" t="n"/>
+          <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
+        </is>
+      </c>
+      <c r="M33" s="19" t="n"/>
+      <c r="N33" s="19" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>Вызов собственной модели внутри закрытого контура.</t>
+        </is>
+      </c>
+      <c r="Q33" s="9" t="inlineStr">
+        <is>
+          <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
+        </is>
+      </c>
+      <c r="R33" s="9" t="inlineStr">
+        <is>
+          <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
+        </is>
+      </c>
+      <c r="S33" s="19" t="n"/>
+      <c r="T33" s="19" t="n"/>
+      <c r="U33" s="9" t="n"/>
       <c r="V33" s="9" t="inlineStr">
         <is>
-          <t>ADR-500; ADR-600</t>
+          <t>ADR-400; ADR-300</t>
         </is>
       </c>
     </row>
@@ -3657,72 +3657,60 @@
       <c r="A34" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>Сквозная работа</t>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>Связь</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Внедрение ответов владельцев данных</t>
+          <t>Индексация → Qdrant</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
+          <t>ETL индексации; Qdrant</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Справочники и тексты в коде и данных; не технология</t>
+          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки.</t>
+          <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии.</t>
+          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>Календарный срок определяет владелец, не команда.</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>Внедрение полученных ответов в справочники и тексты.</t>
-        </is>
-      </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>Разработки не требуют — требуют ответа от водоканала.</t>
-        </is>
-      </c>
-      <c r="M34" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="O34" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Согласования</t>
-        </is>
-      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="inlineStr">
+        <is>
+          <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
+        </is>
+      </c>
+      <c r="M34" s="16" t="n"/>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="15" t="n"/>
       <c r="P34" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3735,7 +3723,7 @@
       <c r="U34" s="15" t="n"/>
       <c r="V34" s="9" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-200</t>
         </is>
       </c>
     </row>
@@ -3750,22 +3738,22 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Документация и согласование ИБ</t>
+          <t>Смета CAPEX/OPEX, NFR, допущения о нагрузке</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Все (сквозная работа)</t>
+          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Документы и диаграммы пакета сдачи</t>
+          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
+          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 234–101 280 ₽ в месяц, на тираже 3 305 ₽–1,07 млн ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -3775,17 +3763,17 @@
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
+          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>Календарный срок определяет служба ИБ водоканала.</t>
+          <t>Разброс стоимости токенов на MVP — ×82 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
+          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой. Первый пересчёт сметы по данным обращений и ЛК (3–5 чел-дн, после получения данных) и повторный по пилоту (1–2 чел-дн): подставить данные в лист «Прогноз стоимости», пересчитать нагрузку, стоимость и sizing, обновить отчёт о мощности, ADR-500 и матрицу.</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr">
@@ -3795,41 +3783,37 @@
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="N35" s="25" t="n">
-        <v>7.5</v>
+          <t>Без этого нельзя защищать бюджет.</t>
+        </is>
+      </c>
+      <c r="M35" s="25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N35" s="17" t="n">
+        <v>17</v>
       </c>
       <c r="O35" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Документация и ИБ</t>
-        </is>
-      </c>
-      <c r="P35" s="9" t="inlineStr">
-        <is>
-          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
-        </is>
-      </c>
-      <c r="Q35" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R35" s="9" t="inlineStr">
-        <is>
-          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
-        </is>
-      </c>
-      <c r="S35" s="19" t="n"/>
-      <c r="T35" s="19" t="n"/>
-      <c r="U35" s="9" t="n"/>
+          <t>Из блока ADR-600: P0</t>
+        </is>
+      </c>
+      <c r="P35" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q35" s="15" t="n"/>
+      <c r="R35" s="15" t="inlineStr">
+        <is>
+          <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="n"/>
+      <c r="T35" s="16" t="n"/>
+      <c r="U35" s="15" t="n"/>
       <c r="V35" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3844,63 +3828,63 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>GPU-узел в кластере владельца (решение после проверки на реальных данных)</t>
+          <t>Внедрение ответов владельцев данных</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes-кластер владельца (новый GPU-узел); embedding-inference; reranker-inference; ETL индексации</t>
+          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты</t>
+          <t>Справочники и тексты в коде и данных; не технология</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>В кластере, где работает личный кабинет и где размещается наш контур, GPU-узлов нет (решение заказчика проекта, 24.09.2026). Без них MVP на CPU: эмбеддинги e5-small (36–37 мс на запрос), реранкер выключен, индексация считает эмбеддинги на CPU.</t>
+          <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки.</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7,2 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Владелец примет решение о GPU-узле только после проверки на реальных данных (24.09.2026): тест моделей идёт на CPU, скорость на GPU — коротким замером на временной видеокарте (ADR-200, «Почему Kubernetes», ADR-600).</t>
+          <t>Не применимо: это работа, а не выбор технологии.</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Почему Kubernetes, а не другая оркестрация» (пункт «GPU»); ADR-300, раздел 2; ADR-600, «GPU-узел в кластере владельца — решение после проверки на реальных данных»</t>
+          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Цена и сроки закупки сервера не оценены; скорость моделей на GPU не измерялась; отдел владельца GPU не эксплуатировал.</t>
+          <t>Календарный срок определяет владелец, не команда.</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны заказчиком проекта 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); Б — доля ответов, оценённых экспертом как верные и полезные, не ниже 80% на подвыборке не менее 200 (рабочее значение автора); В — пустых выдач из-за реранкера (пуста при «реранкер → порог», но не пуста без реранкера) не более 3% вопросов с ответом в базе (рабочее значение автора, только для реранкера; порядок «порог → реранкер» проходит по построению); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А, Б или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
+          <t>Внедрение полученных ответов в справочники и тексты.</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>Тест BGE-M3 и реранкеров остаётся в плане при любом исходе: он и даёт основание для решения. Строка отражает работы на случай покупки и в итог сметы не входит.</t>
-        </is>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" s="13" t="inlineStr">
-        <is>
-          <t>По триггеру (решение владельца после проверки на реальных данных; оценка автора)</t>
+          <t>Разработки не требуют — требуют ответа от водоканала.</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O36" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Согласования</t>
         </is>
       </c>
       <c r="P36" s="14" t="inlineStr">
@@ -3915,7 +3899,7 @@
       <c r="U36" s="15" t="n"/>
       <c r="V36" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-300; ADR-500; ADR-600</t>
+          <t>ADR-600</t>
         </is>
       </c>
     </row>
@@ -3930,78 +3914,86 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Выбор семейства собственной модели и закупка GPU</t>
+          <t>Документация и согласование ИБ</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
+          <t>Все (сквозная работа)</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
+          <t>Документы и диаграммы пакета сдачи</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
+          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
+          <t>Не применимо: это работа, а не выбор технологии.</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
+          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
-        </is>
-      </c>
-      <c r="J37" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K37" s="15" t="n"/>
-      <c r="L37" s="15" t="n"/>
-      <c r="M37" s="16" t="n"/>
-      <c r="N37" s="16" t="n"/>
-      <c r="O37" s="15" t="n"/>
+          <t>Календарный срок определяет служба ИБ водоканала.</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O37" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Документация и ИБ</t>
+        </is>
+      </c>
       <c r="P37" s="9" t="inlineStr">
         <is>
-          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
+          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
         </is>
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5-32B INT4, vLLM.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R37" s="9" t="inlineStr">
         <is>
-          <t>Аренда исключена не по цене, а по триггеру (речь о собственной модели генерации; для проверки эмбеддингов и реранкера на MVP аренда на месяц допустима): облачный GPU считается внешним сервисом.</t>
-        </is>
-      </c>
-      <c r="S37" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T37" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U37" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
+        </is>
+      </c>
+      <c r="S37" s="19" t="n"/>
+      <c r="T37" s="19" t="n"/>
+      <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-500; ADR-600</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -4016,94 +4008,78 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
+          <t>GPU-узел в кластере владельца (решение после проверки на реальных данных)</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
+          <t>Kubernetes-кластер владельца (новый GPU-узел); embedding-inference; reranker-inference; ETL индексации</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
+          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
+          <t>В кластере, где работает личный кабинет и где размещается наш контур, GPU-узлов нет (решение заказчика проекта, 24.09.2026). Без них MVP на CPU: эмбеддинги e5-small (36–37 мс на запрос), реранкер выключен, индексация считает эмбеддинги на CPU.</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
+          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7,2 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Владелец примет решение о GPU-узле только после проверки на реальных данных (24.09.2026): тест моделей идёт на CPU, скорость на GPU — коротким замером на временной видеокарте (ADR-200, «Почему Kubernetes», ADR-600).</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
+          <t>ADR-200, подраздел «Почему Kubernetes, а не другая оркестрация» (пункт «GPU»); ADR-300, раздел 2; ADR-600, «GPU-узел в кластере владельца — решение после проверки на реальных данных»</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
+          <t>Цена и сроки закупки сервера не оценены; скорость моделей на GPU не измерялась; отдел владельца GPU не эксплуатировал.</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки.</t>
+          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны заказчиком проекта 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); Б — доля ответов, оценённых экспертом как верные и полезные, не ниже 80% на подвыборке не менее 200 (рабочее значение автора); В — пустых выдач из-за реранкера (пуста при «реранкер → порог», но не пуста без реранкера) не более 3% вопросов с ответом в базе (рабочее значение автора, только для реранкера; порядок «порог → реранкер» проходит по построению); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А, Б или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
+          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты.</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
-        </is>
-      </c>
-      <c r="M38" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="N38" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="O38" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Анализ типов на живых данных</t>
-        </is>
-      </c>
-      <c r="P38" s="9" t="inlineStr">
-        <is>
-          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
-        </is>
-      </c>
-      <c r="Q38" s="9" t="inlineStr">
-        <is>
-          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
-        </is>
-      </c>
-      <c r="R38" s="9" t="inlineStr">
-        <is>
-          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
-        </is>
-      </c>
-      <c r="S38" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T38" s="20" t="n">
+          <t>Тест BGE-M3 и реранкеров остаётся в плане при любом исходе: он и даёт основание для решения. Строка отражает работы на случай покупки и в итог сметы не входит.</t>
+        </is>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="U38" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+      <c r="N38" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O38" s="13" t="inlineStr">
+        <is>
+          <t>По триггеру (решение владельца после проверки на реальных данных; оценка автора)</t>
+        </is>
+      </c>
+      <c r="P38" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q38" s="15" t="n"/>
+      <c r="R38" s="15" t="n"/>
+      <c r="S38" s="16" t="n"/>
+      <c r="T38" s="16" t="n"/>
+      <c r="U38" s="15" t="n"/>
       <c r="V38" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
+          <t>ADR-200; ADR-300; ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -4118,78 +4094,78 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
+          <t>Выбор семейства собственной модели и закупка GPU</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Backend (оркестратор, детектор намерений); LLM Gateway (охранитель, правило в промпте); Session State Store; виджет (кнопки нескольких обращений)</t>
+          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Python; `app/agents/intents.py` (правила на регулярных выражениях); `Orchestrator._stream_parts`; `unperformed_action` в `app/gateway/guardrails.py`; метрика `assistant_multi_intent_total`</t>
+          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>На прототипе реализовано: детектор намерений разбирает реплику на задачи правилами (`app/agents/intents.py`), оркестратор отвечает по каждой части, операции без выполнения получают прямой отказ, условие «если долга нет» проверяется по Биллингу; ложное «сделал» блокируется правилом в промпте и в охранителе (`unperformed_action`). Тесты: 22 + 16 + 8. Измерение на выгрузке обращений (`scripts/measure_intents.py`): несколько задач в 1 из 136 текстов (0,7%) — срабатывание детектора, не разметка людьми.</t>
+          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Правила, а не модель: модель на каждой реплике стоила бы времени и токенов, а её разбиение нечем проверить. LangGraph реплику на задачи не разбирает — детектор нужен в любом случае (ADR-200, «Как реализовано: несколько задач в одной реплике»).</t>
+          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Как реализовано: несколько задач в одной реплике» (в разделе «Оркестрация агента»); ADR-100, раздел «Несколько задач в одной реплике»; ADR-400</t>
+          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>Предел 300 знаков, перечни глаголов и операций подобраны автором на 136 обращениях регистра, не на репликах чата; точность и полнота на размеченных репликах не измерены. Регистрация только по первой части, из условий проверяется лишь долг, путь `generate` не разбирается, второй бланк перезапишет первый.</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Проверка детектора на размеченных репликах чата (точность, полнота, подбор предела и перечней); регистрация нескольких обращений из одной реплики (несколько черновиков, подтверждение каждого, виджет); условия помимо долга; путь `generate`, лимиты и порядок частей.</t>
-        </is>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>Python; правила на регулярных выражениях; метрика `assistant_multi_intent_total`; состояние диалога в Redis.</t>
-        </is>
-      </c>
-      <c r="L39" s="9" t="inlineStr">
-        <is>
-          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — условие перехода на LangGraph (триггер 4).</t>
-        </is>
-      </c>
-      <c r="M39" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="N39" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="O39" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)</t>
-        </is>
-      </c>
-      <c r="P39" s="14" t="inlineStr">
+          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="Q39" s="15" t="n"/>
-      <c r="R39" s="15" t="n"/>
-      <c r="S39" s="16" t="n"/>
-      <c r="T39" s="16" t="n"/>
-      <c r="U39" s="15" t="n"/>
+      <c r="K39" s="15" t="n"/>
+      <c r="L39" s="15" t="n"/>
+      <c r="M39" s="16" t="n"/>
+      <c r="N39" s="16" t="n"/>
+      <c r="O39" s="15" t="n"/>
+      <c r="P39" s="9" t="inlineStr">
+        <is>
+          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
+        </is>
+      </c>
+      <c r="Q39" s="9" t="inlineStr">
+        <is>
+          <t>Qwen2.5-32B INT4, vLLM.</t>
+        </is>
+      </c>
+      <c r="R39" s="9" t="inlineStr">
+        <is>
+          <t>Аренда исключена не по цене, а по триггеру (речь о собственной модели генерации; для проверки эмбеддингов и реранкера на MVP аренда на месяц допустима): облачный GPU считается внешним сервисом.</t>
+        </is>
+      </c>
+      <c r="S39" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="V39" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
+          <t>ADR-300; ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -4204,122 +4180,310 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
+          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки.</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
+        </is>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="O40" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Анализ типов на живых данных</t>
+        </is>
+      </c>
+      <c r="P40" s="9" t="inlineStr">
+        <is>
+          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
+        </is>
+      </c>
+      <c r="Q40" s="9" t="inlineStr">
+        <is>
+          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
+        </is>
+      </c>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
+        </is>
+      </c>
+      <c r="S40" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T40" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
+      <c r="V40" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Backend (оркестратор, детектор намерений); LLM Gateway (охранитель, правило в промпте); Session State Store; виджет (кнопки нескольких обращений)</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Python; `app/agents/intents.py` (правила на регулярных выражениях); `Orchestrator._stream_parts`; `unperformed_action` в `app/gateway/guardrails.py`; метрика `assistant_multi_intent_total`</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>На прототипе реализовано: детектор намерений разбирает реплику на задачи правилами (`app/agents/intents.py`), оркестратор отвечает по каждой части, операции без выполнения получают прямой отказ, условие «если долга нет» проверяется по Биллингу; ложное «сделал» блокируется правилом в промпте и в охранителе (`unperformed_action`). Тесты: 22 + 16 + 8. Измерение на выгрузке обращений (`scripts/measure_intents.py`): несколько задач в 1 из 136 текстов (0,7%) — срабатывание детектора, не разметка людьми.</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Правила, а не модель: модель на каждой реплике стоила бы времени и токенов, а её разбиение нечем проверить. LangGraph реплику на задачи не разбирает — детектор нужен в любом случае (ADR-200, «Как реализовано: несколько задач в одной реплике»).</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>ADR-200, подраздел «Как реализовано: несколько задач в одной реплике» (в разделе «Оркестрация агента»); ADR-100, раздел «Несколько задач в одной реплике»; ADR-400</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Предел 300 знаков, перечни глаголов и операций подобраны автором на 136 обращениях регистра, не на репликах чата; точность и полнота на размеченных репликах не измерены. Регистрация только по первой части, из условий проверяется лишь долг, путь `generate` не разбирается, второй бланк перезапишет первый.</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Проверка детектора на размеченных репликах чата (точность, полнота, подбор предела и перечней); регистрация нескольких обращений из одной реплики (несколько черновиков, подтверждение каждого, виджет); условия помимо долга; путь `generate`, лимиты и порядок частей.</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>Python; правила на регулярных выражениях; метрика `assistant_multi_intent_total`; состояние диалога в Redis.</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — условие перехода на LangGraph (триггер 4).</t>
+        </is>
+      </c>
+      <c r="M41" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="N41" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O41" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)</t>
+        </is>
+      </c>
+      <c r="P41" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q41" s="15" t="n"/>
+      <c r="R41" s="15" t="n"/>
+      <c r="S41" s="16" t="n"/>
+      <c r="T41" s="16" t="n"/>
+      <c r="U41" s="15" t="n"/>
+      <c r="V41" s="9" t="inlineStr">
+        <is>
+          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
           <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>1) Проверка работоспособности Guardrails на живых вопросах — не менее 200 из единой выборки 300–400 (общей с тестами эмбеддингов и реранкера; ответы этого прогона без реранкера — базовая линия критерия Б): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
         </is>
       </c>
-      <c r="L40" s="9" t="inlineStr">
+      <c r="L42" s="9" t="inlineStr">
         <is>
           <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
         </is>
       </c>
-      <c r="M40" s="17" t="n">
+      <c r="M42" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="N40" s="17" t="n">
+      <c r="N42" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="O40" s="18" t="inlineStr">
+      <c r="O42" s="18" t="inlineStr">
         <is>
           <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
         </is>
       </c>
-      <c r="P40" s="14" t="inlineStr">
+      <c r="P42" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="Q40" s="15" t="n"/>
-      <c r="R40" s="15" t="n"/>
-      <c r="S40" s="16" t="n"/>
-      <c r="T40" s="16" t="n"/>
-      <c r="U40" s="15" t="n"/>
-      <c r="V40" s="9" t="inlineStr">
+      <c r="Q42" s="15" t="n"/>
+      <c r="R42" s="15" t="n"/>
+      <c r="S42" s="16" t="n"/>
+      <c r="T42" s="16" t="n"/>
+      <c r="U42" s="15" t="n"/>
+      <c r="V42" s="9" t="inlineStr">
         <is>
           <t>ADR-300; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="C42" s="26" t="inlineStr">
+    <row r="44">
+      <c r="C44" s="26" t="inlineStr">
         <is>
           <t>Цвет ячеек с оценкой:</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="C43" s="27" t="n"/>
-      <c r="D43" s="28" t="inlineStr">
+    <row r="45">
+      <c r="C45" s="27" t="n"/>
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="28" t="inlineStr">
+    <row r="46">
+      <c r="C46" s="29" t="n"/>
+      <c r="D46" s="28" t="inlineStr">
         <is>
           <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="28" t="inlineStr">
+    <row r="47">
+      <c r="C47" s="30" t="n"/>
+      <c r="D47" s="28" t="inlineStr">
         <is>
           <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="C46" s="31" t="n"/>
-      <c r="D46" s="28" t="inlineStr">
+    <row r="48">
+      <c r="C48" s="31" t="n"/>
+      <c r="D48" s="28" t="inlineStr">
         <is>
           <t>изменений на этом этапе нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V40"/>
+  <autoFilter ref="A2:V42"/>
   <mergeCells count="4">
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
@@ -4441,11 +4605,11 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>SUM('Матрица'!$M$3:$M$40)-SUMIF('Матрица'!$O$3:$O$40,"По триггеру*",'Матрица'!$M$3:$M$40)</f>
+        <f>SUM('Матрица'!$M$3:$M$42)-SUMIF('Матрица'!$O$3:$O$42,"По триггеру*",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="C5" s="34">
-        <f>SUM('Матрица'!$N$3:$N$40)-SUMIF('Матрица'!$O$3:$O$40,"По триггеру*",'Матрица'!$N$3:$N$40)</f>
+        <f>SUM('Матрица'!$N$3:$N$42)-SUMIF('Матрица'!$O$3:$O$42,"По триггеру*",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="D5" s="34">
@@ -4457,35 +4621,35 @@
         <v/>
       </c>
       <c r="F5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"ADR-600",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"ADR-600",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="G5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"ADR-600",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"ADR-600",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="H5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока*",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока*",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="I5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока*",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока*",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="J5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Оценка автора",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Оценка автора",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="K5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Оценка автора",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Оценка автора",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="L5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"По триггеру*",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"По триггеру*",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="M5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"По триггеру*",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"По триггеру*",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
     </row>
@@ -4496,11 +4660,11 @@
         </is>
       </c>
       <c r="B6" s="34">
-        <f>SUM('Матрица'!$S$3:$S$40)-SUMIF('Матрица'!$U$3:$U$40,"По триггеру*",'Матрица'!$S$3:$S$40)</f>
+        <f>SUM('Матрица'!$S$3:$S$42)-SUMIF('Матрица'!$U$3:$U$42,"По триггеру*",'Матрица'!$S$3:$S$42)</f>
         <v/>
       </c>
       <c r="C6" s="34">
-        <f>SUM('Матрица'!$T$3:$T$40)-SUMIF('Матрица'!$U$3:$U$40,"По триггеру*",'Матрица'!$T$3:$T$40)</f>
+        <f>SUM('Матрица'!$T$3:$T$42)-SUMIF('Матрица'!$U$3:$U$42,"По триггеру*",'Матрица'!$T$3:$T$42)</f>
         <v/>
       </c>
       <c r="D6" s="34">
@@ -4512,35 +4676,35 @@
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$40,"ADR-600",'Матрица'!$S$3:$S$40)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$42,"ADR-600",'Матрица'!$S$3:$S$42)</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$40,"ADR-600",'Матрица'!$T$3:$T$40)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$42,"ADR-600",'Матрица'!$T$3:$T$42)</f>
         <v/>
       </c>
       <c r="H6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$40,"Из блока*",'Матрица'!$S$3:$S$40)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$42,"Из блока*",'Матрица'!$S$3:$S$42)</f>
         <v/>
       </c>
       <c r="I6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$40,"Из блока*",'Матрица'!$T$3:$T$40)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$42,"Из блока*",'Матрица'!$T$3:$T$42)</f>
         <v/>
       </c>
       <c r="J6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$40,"Оценка автора",'Матрица'!$S$3:$S$40)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$42,"Оценка автора",'Матрица'!$S$3:$S$42)</f>
         <v/>
       </c>
       <c r="K6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$40,"Оценка автора",'Матрица'!$T$3:$T$40)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$42,"Оценка автора",'Матрица'!$T$3:$T$42)</f>
         <v/>
       </c>
       <c r="L6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$40,"По триггеру*",'Матрица'!$S$3:$S$40)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$42,"По триггеру*",'Матрица'!$S$3:$S$42)</f>
         <v/>
       </c>
       <c r="M6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$40,"По триггеру*",'Матрица'!$T$3:$T$40)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$42,"По триггеру*",'Матрица'!$T$3:$T$42)</f>
         <v/>
       </c>
     </row>
@@ -4707,11 +4871,11 @@
         <v>17</v>
       </c>
       <c r="D15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="F15" s="44">
@@ -4737,11 +4901,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="E16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="F16" s="44">
@@ -4767,11 +4931,11 @@
         <v>56</v>
       </c>
       <c r="D17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="E17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="F17" s="44">
@@ -4797,11 +4961,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="E18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="F18" s="44">
@@ -4827,11 +4991,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="F19" s="44">
@@ -4857,11 +5021,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="F20" s="44">
@@ -4887,11 +5051,11 @@
         <v>14</v>
       </c>
       <c r="D21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="F21" s="44">
@@ -4917,11 +5081,11 @@
         <v>18</v>
       </c>
       <c r="D22" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$42)</f>
         <v/>
       </c>
       <c r="E22" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$40,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$40)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$42)</f>
         <v/>
       </c>
       <c r="F22" s="44">
@@ -5220,7 +5384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6083,18 +6247,18 @@
         <f>'Матрица'!N26</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="13">
         <f>'Матрица'!O26</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9">
-        <f>'Матрица'!A33</f>
+        <f>'Матрица'!A28</f>
         <v/>
       </c>
       <c r="B39" s="9">
-        <f>'Матрица'!C33</f>
+        <f>'Матрица'!C28</f>
         <v/>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -6103,25 +6267,25 @@
         </is>
       </c>
       <c r="D39" s="34">
-        <f>'Матрица'!M33</f>
+        <f>'Матрица'!M28</f>
         <v/>
       </c>
       <c r="E39" s="34">
-        <f>'Матрица'!N33</f>
+        <f>'Матрица'!N28</f>
         <v/>
       </c>
       <c r="F39" s="18">
-        <f>'Матрица'!O33</f>
+        <f>'Матрица'!O28</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9">
-        <f>'Матрица'!A34</f>
+        <f>'Матрица'!A35</f>
         <v/>
       </c>
       <c r="B40" s="9">
-        <f>'Матрица'!C34</f>
+        <f>'Матрица'!C35</f>
         <v/>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -6130,25 +6294,25 @@
         </is>
       </c>
       <c r="D40" s="34">
-        <f>'Матрица'!M34</f>
+        <f>'Матрица'!M35</f>
         <v/>
       </c>
       <c r="E40" s="34">
-        <f>'Матрица'!N34</f>
+        <f>'Матрица'!N35</f>
         <v/>
       </c>
       <c r="F40" s="18">
-        <f>'Матрица'!O34</f>
+        <f>'Матрица'!O35</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9">
-        <f>'Матрица'!A35</f>
+        <f>'Матрица'!A36</f>
         <v/>
       </c>
       <c r="B41" s="9">
-        <f>'Матрица'!C35</f>
+        <f>'Матрица'!C36</f>
         <v/>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -6157,25 +6321,25 @@
         </is>
       </c>
       <c r="D41" s="34">
-        <f>'Матрица'!M35</f>
+        <f>'Матрица'!M36</f>
         <v/>
       </c>
       <c r="E41" s="34">
-        <f>'Матрица'!N35</f>
+        <f>'Матрица'!N36</f>
         <v/>
       </c>
       <c r="F41" s="18">
-        <f>'Матрица'!O35</f>
+        <f>'Матрица'!O36</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9">
-        <f>'Матрица'!A36</f>
+        <f>'Матрица'!A37</f>
         <v/>
       </c>
       <c r="B42" s="9">
-        <f>'Матрица'!C36</f>
+        <f>'Матрица'!C37</f>
         <v/>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -6184,15 +6348,15 @@
         </is>
       </c>
       <c r="D42" s="34">
-        <f>'Матрица'!M36</f>
+        <f>'Матрица'!M37</f>
         <v/>
       </c>
       <c r="E42" s="34">
-        <f>'Матрица'!N36</f>
-        <v/>
-      </c>
-      <c r="F42" s="13">
-        <f>'Матрица'!O36</f>
+        <f>'Матрица'!N37</f>
+        <v/>
+      </c>
+      <c r="F42" s="18">
+        <f>'Матрица'!O37</f>
         <v/>
       </c>
     </row>
@@ -6218,18 +6382,18 @@
         <f>'Матрица'!N38</f>
         <v/>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="13">
         <f>'Матрица'!O38</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9">
-        <f>'Матрица'!A39</f>
+        <f>'Матрица'!A40</f>
         <v/>
       </c>
       <c r="B44" s="9">
-        <f>'Матрица'!C39</f>
+        <f>'Матрица'!C40</f>
         <v/>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -6238,25 +6402,25 @@
         </is>
       </c>
       <c r="D44" s="34">
-        <f>'Матрица'!M39</f>
+        <f>'Матрица'!M40</f>
         <v/>
       </c>
       <c r="E44" s="34">
-        <f>'Матрица'!N39</f>
+        <f>'Матрица'!N40</f>
         <v/>
       </c>
       <c r="F44" s="18">
-        <f>'Матрица'!O39</f>
+        <f>'Матрица'!O40</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9">
-        <f>'Матрица'!A40</f>
+        <f>'Матрица'!A41</f>
         <v/>
       </c>
       <c r="B45" s="9">
-        <f>'Матрица'!C40</f>
+        <f>'Матрица'!C41</f>
         <v/>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -6265,116 +6429,143 @@
         </is>
       </c>
       <c r="D45" s="34">
-        <f>'Матрица'!M40</f>
+        <f>'Матрица'!M41</f>
         <v/>
       </c>
       <c r="E45" s="34">
-        <f>'Матрица'!N40</f>
+        <f>'Матрица'!N41</f>
         <v/>
       </c>
       <c r="F45" s="18">
-        <f>'Матрица'!O40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="43" t="inlineStr">
+        <f>'Матрица'!O41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9">
+        <f>'Матрица'!A42</f>
+        <v/>
+      </c>
+      <c r="B46" s="9">
+        <f>'Матрица'!C42</f>
+        <v/>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D46" s="34">
+        <f>'Матрица'!M42</f>
+        <v/>
+      </c>
+      <c r="E46" s="34">
+        <f>'Матрица'!N42</f>
+        <v/>
+      </c>
+      <c r="F46" s="18">
+        <f>'Матрица'!O42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="43" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -6385,8 +6576,8 @@
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C48:F48"/>
     <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C56:F56"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="C4:F4"/>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -3523,12 +3523,12 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>HTTP (порт 6333); запись — отдельным сервисом, Backend только читает готовый индекс.</t>
+          <t>gRPC (порт 6334) по умолчанию с 24.09.2026, REST (порт 6333) — переключатель QDRANT_PREFER_GRPC=false; запись — отдельным сервисом, Backend только читает готовый индекс. Без TLS и без ключа API. Лимит выдачи: до 500 точек — все точки, выше — top_k × 5.</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Клиент по HTTP, а не gRPC: задержка HTTP-вызова — единицы миллисекунд при бюджете поиска 100 мс, gRPC добавил бы зависимость без выигрыша.</t>
+          <t>Клиент по gRPC (с 24.09.2026), а не по REST: замер — gRPC стабильно 6–13 мс, REST через qdrant-client от 6 до 60 мс (топ-20 с payload: 60 мс); прежний довод «HTTP — единицы миллисекунд» не подтвердился. На прототипе (190 точек) REST быстрее (13 против 26 мс). Один хост, Windows; повторить в кластере.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -3538,19 +3538,27 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="16" t="n"/>
-      <c r="N32" s="16" t="n"/>
-      <c r="O32" s="15" t="n"/>
+          <t>Разброс REST не объяснён. Границы точного перебора (500 точек) и PARTS_HEADROOM (5) — допущения, на реальном корпусе не измерялись. Трафик внутри кластера без TLS и без ключа — решение за ИБ. Замер сделан не на платформе кластера владельца.</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>gRPC-клиент (сделан на прототипе, 0,5–1 чел-дн, оценка автора); ограниченный лимит выдачи; повторить замер REST и gRPC в кластере владельца, подобрать PARTS_HEADROOM и границу точного перебора на реальном корпусе, проверить порт 6334 и NetworkPolicy — в пределах теста моделей эмбеддингов.</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>qdrant-client по gRPC (prefer_grpc, порт 6334).</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>Стабильные 6–13 мс вместо разброса 6–60 мс; на объёме MVP P99 вдвое ниже (топ-100 с payload: 19,5 против 40,1 мс).</t>
+        </is>
+      </c>
+      <c r="M32" s="19" t="n"/>
+      <c r="N32" s="19" t="n"/>
+      <c r="O32" s="9" t="n"/>
       <c r="P32" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3563,7 +3571,7 @@
       <c r="U32" s="15" t="n"/>
       <c r="V32" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-200; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -3523,7 +3523,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>gRPC (порт 6334) по умолчанию с 24.09.2026, REST (порт 6333) — переключатель QDRANT_PREFER_GRPC=false; запись — отдельным сервисом, Backend только читает готовый индекс. Без TLS и без ключа API. Лимит выдачи: до 500 точек — все точки, выше — top_k × 5.</t>
+          <t>gRPC (порт 6334) по умолчанию с 24.09.2026, REST (порт 6333) — переключатель QDRANT_PREFER_GRPC=false; запись — отдельным сервисом, Backend только читает готовый индекс. Без TLS и без ключа API. Лимит выдачи: до 300 точек — все точки, выше — top_k × 10.</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>Разброс REST не объяснён. Границы точного перебора (500 точек) и PARTS_HEADROOM (5) — допущения, на реальном корпусе не измерялись. Трафик внутри кластера без TLS и без ключа — решение за ИБ. Замер сделан не на платформе кластера владельца.</t>
+          <t>Разброс REST не объяснён. Граница точного перебора (300 точек) и PARTS_HEADROOM (10) выбраны по синтетическому замеру (ADR-200, «Значения допущений хранилища»); на реальном корпусе не проверялись. Трафик внутри кластера без TLS и без ключа — решение за ИБ. Замер сделан не на платформе кластера владельца.</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>gRPC-клиент (сделан на прототипе, 0,5–1 чел-дн, оценка автора); ограниченный лимит выдачи; повторить замер REST и gRPC в кластере владельца, подобрать PARTS_HEADROOM и границу точного перебора на реальном корпусе, проверить порт 6334 и NetworkPolicy — в пределах теста моделей эмбеддингов.</t>
+          <t>gRPC-клиент (сделан на прототипе, 0,5–1 чел-дн, оценка автора); ограниченный лимит выдачи; повторить замер REST и gRPC в кластере владельца, перепроверить PARTS_HEADROOM и границу точного перебора на реальном корпусе, проверить порт 6334 и NetworkPolicy — в пределах теста моделей эмбеддингов.</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -5525,7 +5525,7 @@
       </c>
       <c r="C9" s="48" t="inlineStr">
         <is>
-          <t>Скорость любых моделей на GPU. Качество BGE-M3 и других кандидатов на данных проекта. Выигрыш реранкера над текущим индексом (прежний замер — на корпусе из 20 фрагментов). Полнота обезличивания на живых данных. Длина запроса на базе из нескольких тысяч документов. Данные о спросе. Сравнения по документации (pgvector, Milvus, Feature Store, Airflow, Loki, Litestar и др.) замером не проверялись.</t>
+          <t>Скорость любых моделей на GPU. Качество BGE-M3 и других кандидатов на данных проекта. Выигрыш реранкера над текущим индексом (единственный замер сделан на корпусе из 20 фрагментов). Полнота обезличивания на живых данных. Длина запроса на базе из нескольких тысяч документов. Данные о спросе. Сравнения по документации (pgvector, Milvus, Feature Store, Airflow, Loki, Litestar и др.) замером не проверялись.</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32; прежние 4,25 ГБ — две копии в кэше). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
+          <t>Замер: веса 2,14 ГиБ (fp32); на диске 4,25 ГБ — две копии в кэше. Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Взято из прежнего отчёта (низкий и высокий сценарии). Подтвердить: Частота обращений в колл-центр на абонента</t>
+          <t>Допущение: 1,0 диалога в месяц (минимум) и 2,5 (максимум), не измерено. Подтвердить: Частота обращений в колл-центр на абонента</t>
         </is>
       </c>
     </row>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>3 вопроса за визит (ADR-500) и верхняя оценка прежнего отчёта. Подтвердить: Анализ живых обращений и пилот</t>
+          <t>Минимум — 3 вопроса за визит (ADR-500); максимум 6 — допущение, не измерено. Подтвердить: Анализ живых обращений и пилот</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Минимум — замер по 19 вызовам YandexGPT (короткие фрагменты FAQ). Максимум — допущение прежнего отчёта: система + 3 фрагмента по ≈800 токенов. Подтвердить: Пилот на базе из нескольких тысяч документов</t>
+          <t>Минимум — замер по 19 вызовам YandexGPT (короткие фрагменты FAQ). Максимум — допущение: системный текст + 3 фрагмента по ≈800 токенов. Подтвердить: Пилот на базе из нескольких тысяч документов</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Допущение прежнего отчёта; профиль ЖКХ (дни начисления и оплаты). Подтвердить: Статистика ЛК</t>
+          <t>Допущение: профиль ЖКХ (дни начисления и оплаты). Подтвердить: Статистика ЛК</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Допущение прежнего отчёта, не измерено. Подтвердить: Первый прогон с провайдером</t>
+          <t>Допущение, не измерено. Подтвердить: Первый прогон с провайдером</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Допущение прежнего отчёта, не измерено. Подтвердить: Первый прогон с провайдером</t>
+          <t>Допущение, не измерено. Подтвердить: Первый прогон с провайдером</t>
         </is>
       </c>
     </row>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Прежний отчёт: 15–40%. Подтвердить: Разметка обращений и пилот</t>
+          <t>Допущение: 15–40% диалогов, не измерено. Подтвердить: Разметка обращений и пилот</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Прежний отчёт: 6 000–20 000. Подтвердить: Замер на пилоте</t>
+          <t>Допущение: 6 000–20 000 токенов, не измерено. Подтвердить: Замер на пилоте</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1587,7 +1587,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>`multilingual-e5-small` на CPU: 0,46 ГБ, 22–37 мс на запрос (первый замер и повтор 24.09.2026) — укладывается в бюджет 100 мс с запасом ≈3–4,5 раза. Стек: библиотека sentence-transformers (`SentenceTransformerEmbedder`, `app/kb/search.py`); модель задаётся параметром `embedding_model` (`app/config.py`); тот же эмбеддер использует запасной классификатор Triage.</t>
+          <t>`multilingual-e5-small` на CPU: 0,46 ГБ, 22–37 мс на запрос (замеры 24.09.2026) — укладывается в бюджет 100 мс с запасом ≈3–4,5 раза. Стек: библиотека sentence-transformers (`SentenceTransformerEmbedder`, `app/kb/search.py`); модель задаётся параметром `embedding_model` (`app/config.py`); тот же эмбеддер использует запасной классификатор Triage.</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="B8" s="47" t="inlineStr">
         <is>
-          <t>Замеры 24.09.2026 (повтор)</t>
+          <t>Замеры 24.09.2026</t>
         </is>
       </c>
       <c r="C8" s="48" t="inlineStr">
         <is>
-          <t>Время запроса на CPU: e5-small 36–37 мс (первый замер 22 мс), BGE-M3 300 мс (первый замер 210 мс), реранкер на 20 кандидатах 7,2 с; бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром. Backend, путь без модели: 117 запросов/с на процесс, 8,5 мс CPU на запрос. Память: обезличиватель 769 МиБ, эмбеддер e5-small +300 МиБ, контейнер Backend 1,32 ГиБ. Redis: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход. Prometheus: 84 ряда на процесс. Выбранные допущения и расчёт узлов — лист «Sizing».</t>
+          <t>Время запроса на CPU: e5-small 22–37 мс, BGE-M3 210–300 мс, реранкер на 20 кандидатах 7,2 с; бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром. Backend, путь без модели: 117 запросов/с на процесс, 8,5 мс CPU на запрос. Память: обезличиватель 769 МиБ, эмбеддер e5-small +300 МиБ, контейнер Backend 1,32 ГиБ. Redis: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход. Prometheus: 84 ряда на процесс. Выбранные допущения и расчёт узлов — лист «Sizing».</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1681,7 +1681,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Реализован и проверен, но выключен (`RERANKER_ENABLED=false`): кросс-энкодер BGE-reranker-v2-m3 на CPU считает 5,8–25 с (повтор 24.09.2026 — 7,2 с) при бюджете 100 мс; на GPU не измерялся.</t>
+          <t>Реализован и проверен, но выключен (`RERANKER_ENABLED=false`): кросс-энкодер BGE-reranker-v2-m3 на CPU считает 5,8–25 с (последний замер 24.09.2026 — 7,2 с) при бюджете 100 мс; на GPU не измерялся.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2695,7 +2695,7 @@
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 15 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 5 узлов на MVP (3 общих и 2 данных; на границе округления, возможно 6), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
+          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 16 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -7116,7 +7116,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="120" customHeight="1">
+    <row r="20" ht="105" customHeight="1">
       <c r="A20" s="50" t="n">
         <v>16</v>
       </c>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 5 узлов (3 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ; на границе округления, возможно 6), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -7221,7 +7221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Загрузка узла по запросам не выше 70%. Класс узлов: общий — 8 vCPU / 16 ГиБ; данных — 8 vCPU / 32 ГиБ с NVMe; GPU — 8 vCPU / 32 ГиБ и видеокарта 24 ГБ; LLM (тираж) — 16 vCPU / 128 ГиБ и A100 80 ГБ. Число узлов общего пула на MVP на 24 сентября 2026 находится на границе округления: расчётная нагрузка 11,2 vCPU при допустимых 11,2 на двух узлах; любое допущение, выросшее на 0,1 vCPU, добавляет узел (итог 6 вместо 5).</t>
+          <t>Загрузка узла по запросам не выше 70%. Класс узлов: общий — 8 vCPU / 16 ГиБ; данных — 8 vCPU / 32 ГиБ с NVMe; GPU — 8 vCPU / 32 ГиБ и видеокарта 24 ГБ; LLM (тираж) — 16 vCPU / 128 ГиБ и A100 80 ГБ.</t>
         </is>
       </c>
     </row>
@@ -7925,17 +7925,17 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Document Generator (PDF, Этап 2)</t>
+          <t>Inquiry Service (маршрутизация обращений, Этап 2)</t>
         </is>
       </c>
       <c r="D21" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F21" s="51" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F21" s="51" t="n">
-        <v>1</v>
       </c>
       <c r="G21" s="51" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>2</v>
       </c>
       <c r="N21" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O21" s="51" t="n">
         <v>0.5</v>
-      </c>
-      <c r="O21" s="51" t="n">
-        <v>1</v>
       </c>
       <c r="P21" s="51" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="V21" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью (до 31 500 в месяц на тираже).</t>
+          <t>Допущение автора, не измерялось. Маршрутизация обращений в микросервис обращений и Диспетчерскую; до 2 800 диалогов с записью в месяц на MVP — нагрузка ничтожна.</t>
         </is>
       </c>
     </row>
@@ -8007,21 +8007,20 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>ETL индексации (CronJob, окно 02:00–05:00) [вариант с GPU]</t>
-        </is>
-      </c>
-      <c r="D22" s="51">
-        <f>1*$C$12</f>
-        <v/>
+          <t>Document Generator (PDF, Этап 2)</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="E22" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="G22" s="51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H22" s="51" t="n">
         <v>0</v>
@@ -8042,18 +8041,17 @@
         <f>D22*H22</f>
         <v/>
       </c>
-      <c r="M22" s="51">
-        <f>1*$C$12</f>
-        <v/>
+      <c r="M22" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="N22" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O22" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O22" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="P22" s="51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="51" t="n">
         <v>0</v>
@@ -8076,7 +8074,7 @@
       </c>
       <c r="V22" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
+          <t>Допущение. Библиотека PDF не выбрана; ≈1 бланк на диалог с записью (до 31 500 в месяц на тираже).</t>
         </is>
       </c>
     </row>
@@ -8091,20 +8089,21 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Оценка качества (CronJob, ночной прогон)</t>
-        </is>
-      </c>
-      <c r="D23" s="51" t="n">
+          <t>ETL индексации (CronJob, окно 02:00–05:00) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D23" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="E23" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F23" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H23" s="51" t="n">
         <v>0</v>
@@ -8125,17 +8124,18 @@
         <f>D23*H23</f>
         <v/>
       </c>
-      <c r="M23" s="51" t="n">
+      <c r="M23" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="N23" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="O23" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" s="51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q23" s="51" t="n">
         <v>0</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
+          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>Оценка качества (CronJob, ночной прогон)</t>
         </is>
       </c>
       <c r="D24" s="51" t="n">
@@ -8186,7 +8186,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H24" s="51" t="n">
         <v>0</v>
@@ -8217,7 +8217,7 @@
         <v>1</v>
       </c>
       <c r="P24" s="51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="51" t="n">
         <v>0</v>
@@ -8240,11 +8240,11 @@
       </c>
       <c r="V24" s="9" t="inlineStr">
         <is>
-          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="50" t="n">
         <v>10</v>
       </c>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Loki</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D25" s="51" t="n">
@@ -8268,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H25" s="51" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P25" s="51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q25" s="51" t="n">
         <v>0</v>
@@ -8322,35 +8322,35 @@
       </c>
       <c r="V25" s="9" t="inlineStr">
         <is>
-          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="50" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Qdrant</t>
+          <t>Loki</t>
         </is>
       </c>
       <c r="D26" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="G26" s="51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H26" s="51" t="n">
         <v>0</v>
@@ -8372,16 +8372,16 @@
         <v/>
       </c>
       <c r="M26" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O26" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="P26" s="51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q26" s="51" t="n">
         <v>0</v>
@@ -8404,11 +8404,11 @@
       </c>
       <c r="V26" s="9" t="inlineStr">
         <is>
-          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="90" customHeight="1">
+          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="50" t="n">
         <v>12</v>
       </c>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Postgres (обращения, профиль, телеметрия, журнал диалогов)</t>
+          <t>Qdrant</t>
         </is>
       </c>
       <c r="D27" s="51" t="n">
@@ -8432,7 +8432,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H27" s="51" t="n">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>2</v>
       </c>
       <c r="P27" s="51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="Q27" s="51" t="n">
         <v>0</v>
@@ -8486,11 +8486,11 @@
       </c>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (заложено 3 КБ на абонента; по примеру прототипа — 0,7 КБ на счёт в CSV); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="90" customHeight="1">
       <c r="A28" s="50" t="n">
         <v>13</v>
       </c>
@@ -8501,20 +8501,20 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Redis (квоты и сессии)</t>
+          <t>Postgres (обращения, профиль, телеметрия, журнал диалогов)</t>
         </is>
       </c>
       <c r="D28" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="51" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F28" s="51" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="G28" s="51" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H28" s="51" t="n">
         <v>0</v>
@@ -8539,13 +8539,13 @@
         <v>2</v>
       </c>
       <c r="N28" s="51" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O28" s="51" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="P28" s="51" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="Q28" s="51" t="n">
         <v>0</v>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
+          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (заложено 3 КБ на абонента; по примеру прототипа — 0,7 КБ на счёт в CSV); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
         </is>
       </c>
     </row>
@@ -8583,20 +8583,20 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>MinIO (документы, копии, снимки)</t>
+          <t>Redis (квоты и сессии)</t>
         </is>
       </c>
       <c r="D29" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F29" s="51" t="n">
         <v>0.25</v>
       </c>
-      <c r="F29" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="G29" s="51" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H29" s="51" t="n">
         <v>0</v>
@@ -8618,16 +8618,16 @@
         <v/>
       </c>
       <c r="M29" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O29" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P29" s="51" t="n">
         <v>1</v>
-      </c>
-      <c r="N29" s="51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O29" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" s="51" t="n">
-        <v>400</v>
       </c>
       <c r="Q29" s="51" t="n">
         <v>0</v>
@@ -8650,39 +8650,38 @@
       </c>
       <c r="V29" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="50" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Эмбеддинги (BGE-M3, inference) [вариант с GPU]</t>
-        </is>
-      </c>
-      <c r="D30" s="51">
-        <f>1*$C$12</f>
-        <v/>
+          <t>MinIO (документы, копии, снимки)</t>
+        </is>
+      </c>
+      <c r="D30" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="E30" s="51" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F30" s="51" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="G30" s="51" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="H30" s="51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="53">
         <f>D30*E30</f>
@@ -8700,21 +8699,20 @@
         <f>D30*H30</f>
         <v/>
       </c>
-      <c r="M30" s="51">
-        <f>1*$C$12</f>
-        <v/>
+      <c r="M30" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="N30" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O30" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O30" s="51" t="n">
-        <v>4</v>
-      </c>
       <c r="P30" s="51" t="n">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="Q30" s="51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R30" s="53">
         <f>M30*N30</f>
@@ -8734,7 +8732,7 @@
       </c>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32); на диске 4,25 ГБ — две копии в кэше. Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
+          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8747,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Реранкер (BGE-reranker-v2-m3, inference) [вариант с GPU]</t>
+          <t>Эмбеддинги (BGE-M3, inference) [вариант с GPU]</t>
         </is>
       </c>
       <c r="D31" s="51">
@@ -8760,13 +8758,13 @@
         <v>1</v>
       </c>
       <c r="F31" s="51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31" s="51" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I31" s="53">
         <f>D31*E31</f>
@@ -8792,13 +8790,13 @@
         <v>1</v>
       </c>
       <c r="O31" s="51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P31" s="51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q31" s="51" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R31" s="53">
         <f>M31*N31</f>
@@ -8818,7 +8816,7 @@
       </c>
       <c r="V31" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+          <t>Замер: веса 2,14 ГиБ (fp32); на диске 4,25 ГБ — две копии в кэше. Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
         </is>
       </c>
     </row>
@@ -8828,28 +8826,29 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>gpu-llm</t>
+          <t>gpu</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
-        </is>
-      </c>
-      <c r="D32" s="51" t="n">
-        <v>0</v>
+          <t>Реранкер (BGE-reranker-v2-m3, inference) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D32" s="51">
+        <f>1*$C$12</f>
+        <v/>
       </c>
       <c r="E32" s="51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F32" s="51" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="G32" s="51" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H32" s="51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I32" s="53">
         <f>D32*E32</f>
@@ -8867,20 +8866,21 @@
         <f>D32*H32</f>
         <v/>
       </c>
-      <c r="M32" s="51" t="n">
+      <c r="M32" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="N32" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="51" t="n">
-        <v>8</v>
-      </c>
       <c r="O32" s="51" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="P32" s="51" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="51" t="n">
-        <v>40</v>
+        <v>1.5</v>
       </c>
       <c r="R32" s="53">
         <f>M32*N32</f>
@@ -8900,36 +8900,35 @@
       </c>
       <c r="V32" s="9" t="inlineStr">
         <is>
-          <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="50" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>gpu-llm</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Эмбеддинги (e5-small на CPU) [вариант без GPU]</t>
-        </is>
-      </c>
-      <c r="D33" s="51">
-        <f>2*(1-$C$12)</f>
-        <v/>
+          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="E33" s="51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F33" s="51" t="n">
-        <v>1.5</v>
+        <v>64</v>
       </c>
       <c r="G33" s="51" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H33" s="51" t="n">
         <v>0</v>
@@ -8950,21 +8949,20 @@
         <f>D33*H33</f>
         <v/>
       </c>
-      <c r="M33" s="51">
-        <f>2*(1-$C$12)</f>
-        <v/>
+      <c r="M33" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="N33" s="51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O33" s="51" t="n">
-        <v>1.5</v>
+        <v>64</v>
       </c>
       <c r="P33" s="51" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Q33" s="51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R33" s="53">
         <f>M33*N33</f>
@@ -8984,7 +8982,7 @@
       </c>
       <c r="V33" s="9" t="inlineStr">
         <is>
-          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7,2 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
+          <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
         </is>
       </c>
     </row>
@@ -8999,21 +8997,21 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>ETL индексации: эмбеддинги на CPU (CronJob) [вариант без GPU]</t>
+          <t>Эмбеддинги (e5-small на CPU) [вариант без GPU]</t>
         </is>
       </c>
       <c r="D34" s="51">
-        <f>1*(1-$C$12)</f>
+        <f>2*(1-$C$12)</f>
         <v/>
       </c>
       <c r="E34" s="51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" s="51" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="G34" s="51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H34" s="51" t="n">
         <v>0</v>
@@ -9035,17 +9033,17 @@
         <v/>
       </c>
       <c r="M34" s="51">
-        <f>1*(1-$C$12)</f>
+        <f>2*(1-$C$12)</f>
         <v/>
       </c>
       <c r="N34" s="51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O34" s="51" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="P34" s="51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="51" t="n">
         <v>0</v>
@@ -9068,169 +9066,197 @@
       </c>
       <c r="V34" s="9" t="inlineStr">
         <is>
+          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7,2 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>ETL индексации: эмбеддинги на CPU (CronJob) [вариант без GPU]</t>
+        </is>
+      </c>
+      <c r="D35" s="51">
+        <f>1*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="E35" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="53">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+      <c r="J35" s="53">
+        <f>D35*F35</f>
+        <v/>
+      </c>
+      <c r="K35" s="53">
+        <f>D35*G35</f>
+        <v/>
+      </c>
+      <c r="L35" s="53">
+        <f>D35*H35</f>
+        <v/>
+      </c>
+      <c r="M35" s="51">
+        <f>1*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="N35" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="53">
+        <f>M35*N35</f>
+        <v/>
+      </c>
+      <c r="S35" s="53">
+        <f>M35*O35</f>
+        <v/>
+      </c>
+      <c r="T35" s="53">
+        <f>M35*P35</f>
+        <v/>
+      </c>
+      <c r="U35" s="53">
+        <f>M35*Q35</f>
+        <v/>
+      </c>
+      <c r="V35" s="9" t="inlineStr">
+        <is>
           <t>Расчёт по замеру: e5-small ≈27 мс на часть (машина с 12 потоками) → 30–100 тыс. частей ≈14–46 мин; на поде с 4 vCPU время не измерялось и может быть в 2–3 раза больше (окно 3 часа). Только в варианте без GPU.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="C36" s="43" t="inlineStr">
+    <row r="37">
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Итог по пулам узлов</t>
         </is>
       </c>
-      <c r="P36" s="9" t="inlineStr">
+      <c r="P37" s="9" t="inlineStr">
         <is>
           <t>Загрузка узла по запросам, не выше</t>
         </is>
       </c>
-      <c r="Q36" s="54" t="n">
+      <c r="Q37" s="54" t="n">
         <v>0.7</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Пул</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Класс узла</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>vCPU узла</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>ОЗУ узла, ГиБ</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>Видеопамять узла, ГиБ</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Запас на потерю узла (1 — да)</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>MVP: vCPU</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>MVP: ОЗУ</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>MVP: видеопамять</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>MVP: узлов</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>Тираж: vCPU</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Тираж: ОЗУ</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>Тираж: видеопамять</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>Тираж: узлов</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="55">
-        <f>SUMIF($B$16:$B$34,$B38,$I$16:$I$34)</f>
-        <v/>
-      </c>
-      <c r="I38" s="55">
-        <f>SUMIF($B$16:$B$34,$B38,$J$16:$J$34)</f>
-        <v/>
-      </c>
-      <c r="J38" s="55">
-        <f>SUMIF($B$16:$B$34,$B38,$L$16:$L$34)</f>
-        <v/>
-      </c>
-      <c r="K38" s="56">
-        <f>IF(H38=0,0,ROUNDUP(MAX(H38/($Q$36*$D38),I38/($Q$36*$E38),IF($F38&gt;0,J38/($Q$36*$F38),0)),0)+$G38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="55">
-        <f>SUMIF($B$16:$B$34,$B38,$R$16:$R$34)</f>
-        <v/>
-      </c>
-      <c r="M38" s="55">
-        <f>SUMIF($B$16:$B$34,$B38,$S$16:$S$34)</f>
-        <v/>
-      </c>
-      <c r="N38" s="55">
-        <f>SUMIF($B$16:$B$34,$B38,$U$16:$U$34)</f>
-        <v/>
-      </c>
-      <c r="O38" s="56">
-        <f>IF(L38=0,0,ROUNDUP(MAX(L38/($Q$36*$D38),M38/($Q$36*$E38),IF($F38&gt;0,N38/($Q$36*$F38),0)),0)+$G38)</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Пул данных (NVMe)</t>
+          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
         <v>8</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>0</v>
@@ -9239,47 +9265,47 @@
         <v>1</v>
       </c>
       <c r="H39" s="55">
-        <f>SUMIF($B$16:$B$34,$B39,$I$16:$I$34)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$I$16:$I$35)</f>
         <v/>
       </c>
       <c r="I39" s="55">
-        <f>SUMIF($B$16:$B$34,$B39,$J$16:$J$34)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$J$16:$J$35)</f>
         <v/>
       </c>
       <c r="J39" s="55">
-        <f>SUMIF($B$16:$B$34,$B39,$L$16:$L$34)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$L$16:$L$35)</f>
         <v/>
       </c>
       <c r="K39" s="56">
-        <f>IF(H39=0,0,ROUNDUP(MAX(H39/($Q$36*$D39),I39/($Q$36*$E39),IF($F39&gt;0,J39/($Q$36*$F39),0)),0)+$G39)</f>
+        <f>IF(H39=0,0,ROUNDUP(MAX(H39/($Q$37*$D39),I39/($Q$37*$E39),IF($F39&gt;0,J39/($Q$37*$F39),0)),0)+$G39)</f>
         <v/>
       </c>
       <c r="L39" s="55">
-        <f>SUMIF($B$16:$B$34,$B39,$R$16:$R$34)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$R$16:$R$35)</f>
         <v/>
       </c>
       <c r="M39" s="55">
-        <f>SUMIF($B$16:$B$34,$B39,$S$16:$S$34)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$S$16:$S$35)</f>
         <v/>
       </c>
       <c r="N39" s="55">
-        <f>SUMIF($B$16:$B$34,$B39,$U$16:$U$34)</f>
+        <f>SUMIF($B$16:$B$35,$B39,$U$16:$U$35)</f>
         <v/>
       </c>
       <c r="O39" s="56">
-        <f>IF(L39=0,0,ROUNDUP(MAX(L39/($Q$36*$D39),M39/($Q$36*$E39),IF($F39&gt;0,N39/($Q$36*$F39),0)),0)+$G39)</f>
+        <f>IF(L39=0,0,ROUNDUP(MAX(L39/($Q$37*$D39),M39/($Q$37*$E39),IF($F39&gt;0,N39/($Q$37*$F39),0)),0)+$G39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>GPU-пул (эмбеддинги, реранкер)</t>
+          <t>Пул данных (NVMe)</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
@@ -9289,132 +9315,188 @@
         <v>32</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="55">
-        <f>SUMIF($B$16:$B$34,$B40,$I$16:$I$34)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$I$16:$I$35)</f>
         <v/>
       </c>
       <c r="I40" s="55">
-        <f>SUMIF($B$16:$B$34,$B40,$J$16:$J$34)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$J$16:$J$35)</f>
         <v/>
       </c>
       <c r="J40" s="55">
-        <f>SUMIF($B$16:$B$34,$B40,$L$16:$L$34)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$L$16:$L$35)</f>
         <v/>
       </c>
       <c r="K40" s="56">
-        <f>IF(H40=0,0,ROUNDUP(MAX(H40/($Q$36*$D40),I40/($Q$36*$E40),IF($F40&gt;0,J40/($Q$36*$F40),0)),0)+$G40)</f>
+        <f>IF(H40=0,0,ROUNDUP(MAX(H40/($Q$37*$D40),I40/($Q$37*$E40),IF($F40&gt;0,J40/($Q$37*$F40),0)),0)+$G40)</f>
         <v/>
       </c>
       <c r="L40" s="55">
-        <f>SUMIF($B$16:$B$34,$B40,$R$16:$R$34)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$R$16:$R$35)</f>
         <v/>
       </c>
       <c r="M40" s="55">
-        <f>SUMIF($B$16:$B$34,$B40,$S$16:$S$34)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$S$16:$S$35)</f>
         <v/>
       </c>
       <c r="N40" s="55">
-        <f>SUMIF($B$16:$B$34,$B40,$U$16:$U$34)</f>
+        <f>SUMIF($B$16:$B$35,$B40,$U$16:$U$35)</f>
         <v/>
       </c>
       <c r="O40" s="56">
-        <f>IF(L40=0,0,ROUNDUP(MAX(L40/($Q$36*$D40),M40/($Q$36*$E40),IF($F40&gt;0,N40/($Q$36*$F40),0)),0)+$G40)</f>
+        <f>IF(L40=0,0,ROUNDUP(MAX(L40/($Q$37*$D40),M40/($Q$37*$E40),IF($F40&gt;0,N40/($Q$37*$F40),0)),0)+$G40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>gpu-llm</t>
+          <t>gpu</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>GPU-пул генерации (тираж)</t>
+          <t>GPU-пул (эмбеддинги, реранкер)</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="55">
-        <f>SUMIF($B$16:$B$34,$B41,$I$16:$I$34)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$I$16:$I$35)</f>
         <v/>
       </c>
       <c r="I41" s="55">
-        <f>SUMIF($B$16:$B$34,$B41,$J$16:$J$34)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$J$16:$J$35)</f>
         <v/>
       </c>
       <c r="J41" s="55">
-        <f>SUMIF($B$16:$B$34,$B41,$L$16:$L$34)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$L$16:$L$35)</f>
         <v/>
       </c>
       <c r="K41" s="56">
-        <f>IF(H41=0,0,ROUNDUP(MAX(H41/($Q$36*$D41),I41/($Q$36*$E41),IF($F41&gt;0,J41/($Q$36*$F41),0)),0)+$G41)</f>
+        <f>IF(H41=0,0,ROUNDUP(MAX(H41/($Q$37*$D41),I41/($Q$37*$E41),IF($F41&gt;0,J41/($Q$37*$F41),0)),0)+$G41)</f>
         <v/>
       </c>
       <c r="L41" s="55">
-        <f>SUMIF($B$16:$B$34,$B41,$R$16:$R$34)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$R$16:$R$35)</f>
         <v/>
       </c>
       <c r="M41" s="55">
-        <f>SUMIF($B$16:$B$34,$B41,$S$16:$S$34)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$S$16:$S$35)</f>
         <v/>
       </c>
       <c r="N41" s="55">
-        <f>SUMIF($B$16:$B$34,$B41,$U$16:$U$34)</f>
+        <f>SUMIF($B$16:$B$35,$B41,$U$16:$U$35)</f>
         <v/>
       </c>
       <c r="O41" s="56">
-        <f>IF(L41=0,0,ROUNDUP(MAX(L41/($Q$36*$D41),M41/($Q$36*$E41),IF($F41&gt;0,N41/($Q$36*$F41),0)),0)+$G41)</f>
+        <f>IF(L41=0,0,ROUNDUP(MAX(L41/($Q$37*$D41),M41/($Q$37*$E41),IF($F41&gt;0,N41/($Q$37*$F41),0)),0)+$G41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Итого узлов</t>
-        </is>
-      </c>
-      <c r="K42" s="57">
-        <f>SUM(K38:K41)</f>
-        <v/>
-      </c>
-      <c r="O42" s="57">
-        <f>SUM(O38:O41)</f>
+          <t>gpu-llm</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>GPU-пул генерации (тираж)</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="55">
+        <f>SUMIF($B$16:$B$35,$B42,$I$16:$I$35)</f>
+        <v/>
+      </c>
+      <c r="I42" s="55">
+        <f>SUMIF($B$16:$B$35,$B42,$J$16:$J$35)</f>
+        <v/>
+      </c>
+      <c r="J42" s="55">
+        <f>SUMIF($B$16:$B$35,$B42,$L$16:$L$35)</f>
+        <v/>
+      </c>
+      <c r="K42" s="56">
+        <f>IF(H42=0,0,ROUNDUP(MAX(H42/($Q$37*$D42),I42/($Q$37*$E42),IF($F42&gt;0,J42/($Q$37*$F42),0)),0)+$G42)</f>
+        <v/>
+      </c>
+      <c r="L42" s="55">
+        <f>SUMIF($B$16:$B$35,$B42,$R$16:$R$35)</f>
+        <v/>
+      </c>
+      <c r="M42" s="55">
+        <f>SUMIF($B$16:$B$35,$B42,$S$16:$S$35)</f>
+        <v/>
+      </c>
+      <c r="N42" s="55">
+        <f>SUMIF($B$16:$B$35,$B42,$U$16:$U$35)</f>
+        <v/>
+      </c>
+      <c r="O42" s="56">
+        <f>IF(L42=0,0,ROUNDUP(MAX(L42/($Q$37*$D42),M42/($Q$37*$E42),IF($F42&gt;0,N42/($Q$37*$F42),0)),0)+$G42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="11" t="inlineStr">
         <is>
+          <t>Итого узлов</t>
+        </is>
+      </c>
+      <c r="K43" s="57">
+        <f>SUM(K39:K42)</f>
+        <v/>
+      </c>
+      <c r="O43" s="57">
+        <f>SUM(O39:O42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="11" t="inlineStr">
+        <is>
           <t>Диск под тома, ГиБ</t>
         </is>
       </c>
-      <c r="K43" s="58">
-        <f>SUM($K$16:$K$34)</f>
-        <v/>
-      </c>
-      <c r="O43" s="58">
-        <f>SUM($T$16:$T$34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="33" t="inlineStr">
+      <c r="K44" s="58">
+        <f>SUM($K$16:$K$35)</f>
+        <v/>
+      </c>
+      <c r="O44" s="58">
+        <f>SUM($T$16:$T$35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); управляющая часть Kubernetes размещена на трёх узлах общего пула (допущение); нагрузочный тест не проводился.</t>
         </is>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1691,17 +1691,17 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 3 «Переранжирование» и подраздел «Почему BGE-reranker-v2-m3 — кандидат для MVP и что будет сравниваться»; замер — golden_set/reranking.json</t>
+          <t>ADR-300, раздел 3 «Переранжирование» и подраздел «Почему BGE-reranker-v2-m3 — кандидат для MVP и что будет сравниваться»; офлайн-роль — там же, подраздел «Офлайн-роль при индексации: отсев дублей (не решено)»; замер — golden_set/reranking.json</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Онлайн-роль зависит от GPU. Офлайн-роль (выбор представительного чанка среди дублей) в коде не реализована и не подтверждена: модель обучена на паре «запрос — документ», а запроса при индексации нет.</t>
+          <t>Онлайн-роль зависит от GPU. Офлайн-роль (выбор представительного чанка среди дублей) в коде не реализована и не подтверждена: модель обучена на паре «запрос — документ», а запроса при индексации нет. Отдельной офлайн-модели не выбрано: на схеме ETL указана та же BGE-reranker-v2-m3 (блок «Reranker Client (offline)» после блока «Quality &amp; Dedup Filter»: MinHash/SimHash, Жаккар ≥ 0,9, quality_score). Расчёт по замеру: 7,2 с на 20 кандидатов ≈ 0,36 с на пару, за окно 3 ч ≈ 30 000 пар; на паре «фрагмент — фрагмент» время не измерялось. Варианты отсева: quality_score, центроид, кросс-энкодер, косинусный порог (ADR-300, раздел 3); доля дублей в корпусе не измерялась.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порог пустых выдач (критерий В): не более 3% вопросов с ответом, пустых из-за порядка; рабочее значение автора. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (считается по каждому вопросу на одних и тех же 20 кандидатах: пустая выдача; меньше трёх; пустая из-за порядка — пуста при «реранкер → порог», но не пуста без реранкера; верный фрагмент отсечён порогом; условный пример на 10 вопросах — в ADR-600; у порядка «порог → реранкер» пустых из-за порядка по построению нет; вопросы без ответа в базе размечаются отдельно и считаются отдельно) (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы или пометка «ответа в базе нет» для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли, при неподтверждении — замена на quality_score или центроидное сходство (2–3 чел-дн). Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порог пустых выдач (критерий В): не более 3% вопросов с ответом, пустых из-за порядка; рабочее значение автора. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (считается по каждому вопросу на одних и тех же 20 кандидатах: пустая выдача; меньше трёх; пустая из-за порядка — пуста при «реранкер → порог», но не пуста без реранкера; верный фрагмент отсечён порогом; условный пример на 10 вопросах — в ADR-600; у порядка «порог → реранкер» пустых из-за порядка по построению нет; вопросы без ответа в базе размечаются отдельно и считаются отдельно) (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы или пометка «ответа в базе нет» для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли (2–3 чел-дн): доля кластеров дублей на реальных документах, четыре способа выбора представителя (quality_score, центроид, кросс-энкодер, косинусный порог), проверка экспертом, что нужный текст не потерян; при неподтверждении кросс-энкодера офлайн-роль снимается, отсев строится на остальных способах; состав работы — предложение автора от 25.09.2026, порог «заметно лучше» не определён. Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Планировщик по расписанию выбран против Airflow (платформа ради одного задания) и cron внутри Backend (нет изоляции от ответов абонентам) — по документации, пробного внедрения не было. Celery Beat в коде не используется. Объём MVP — несколько тысяч документов (3 000–5 000), 30 000–100 000 частей (допущение); по замеру на CPU e5-small индексирует их за ≈14–46 мин, BGE-M3 — за ≈2,7–9,6 ч при окне 3 ч; на GPU скорость не измерялась.</t>
+          <t>Планировщик по расписанию выбран против Airflow (платформа ради одного задания) и cron внутри Backend (нет изоляции от ответов абонентам) — по документации, пробного внедрения не было. Celery Beat в коде не используется. Объём MVP — несколько тысяч документов (3 000–5 000), 30 000–100 000 частей (допущение); по замеру на CPU e5-small индексирует их за ≈14–46 мин, BGE-M3 — за ≈2,7–9,6 ч при окне 3 ч; на GPU скорость не измерялась. Отсев дублей при индексации: в коде нет, решение не принято. Варианты (ADR-300, раздел 3): А — MinHash/SimHash + quality_score; Б — центроидное сходство; В — кросс-энкодер офлайн (проект схемы ETL); Г — косинусный порог между частями (предложение автора 25.09.2026). Сравнение — «замер офлайн-роли реранкера», 2–3 чел-дн (ADR-600).</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему индексация — задание по расписанию, а не Airflow» и подраздел «Индексация базы знаний: что реализовано и какой объём»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему индексация — задание по расписанию, а не Airflow» и подраздел «Индексация базы знаний: что реализовано и какой объём»; отсев дублей — ADR-300, раздел 3, подраздел «Офлайн-роль при индексации: отсев дублей (не решено)»</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Ночное окно 02:00–05:00: забор документов, очистка, эмбеддинги на GPU, полный реиндекс. Что «окна хватит» на 30–100 тыс. частей на GPU — допущение, скорость на GPU не измерялась; источник и формат настоящих документов владелец не назвал.</t>
+          <t>Ночное окно 02:00–05:00: забор документов, очистка, эмбеддинги на GPU, полный реиндекс. Что «окна хватит» на 30–100 тыс. частей на GPU — допущение, скорость на GPU не измерялась; источник и формат настоящих документов владелец не назвал. Отсев дублей: способ не выбран (строка «Реранкер», замер офлайн-роли 2–3 чел-дн), в оценку 4–6 чел-дн отдельно не выделен.</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1838,63 +1838,63 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Кэш профиля абонента (Postgres)</t>
+          <t>Данные абонента (чтение из Биллинга и Диспетчерской)</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Кэш профиля; Backend (читает); K8s CronJob (пересчёт, MVP); Биллинг и Диспетчерская (источники)</t>
+          <t>Backend (читает); Биллинг и Диспетчерская (источники, внешние); Redis (кэш — только после замера)</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Прототип: словари в памяти процесса из CSV. MVP: PostgreSQL (материализованное представление; клиент psycopg 3), без Redis; возврат Redis — по итогам замера</t>
+          <t>Прототип: словари в памяти процесса из CSV. MVP: клиенты XML-RPC (Биллинг) и REST (Диспетчерская) в Backend, параллельные вызовы, таймауты и повторы; без Postgres-представления; кэш Redis — по итогам замера</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Пример Биллинга и ЛК (200 счетов, 203 счётчика, 1323 начисления) читается из CSV при старте в словари в памяти процесса (`app/billing/source.py`). Postgres и Redis для профиля на прототипе не используются.</t>
+          <t>Пример Биллинга и ЛК (200 счетов, 203 счётчика, 1323 начисления) читается из CSV при старте в словари в памяти процесса (`app/billing/source.py`). Postgres и Redis для данных абонента на прототипе не используются. Источник стоит за интерфейсом, на MVP его заменяет клиент к настоящим API (оценка автора, не проверялось).</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Не формальный Feature Store (Feast/Tecton): избыточен для одной таблицы. Сравнивались также слепок в памяти (не работает для нескольких реплик), материализованное представление Postgres без Redis и чтение из Биллинга на каждый вопрос (нагрузка и задержка). Redis для профиля не берётся: выигрыш над индексным чтением Postgres не показан, второй источник данных — цена без пользы; на MVP закладывается замер чтения (1,5–2 чел-дн), Redis возвращается только если замер не уложится в бюджет.</t>
+          <t>Заказчик проекта 25.09.2026: данные абонента нужны онлайн из систем. Поэтому основной путь — чтение из Биллинга (XML-RPC) и Диспетчерской (REST) на каждый вопрос; вызовы параллельные, только за нужными данными; при отказе системы — ответ «данных сейчас нет», без подстановки старых. Отклонены: слепок в памяти (данные не обновляются, у реплик разный возраст), предрасчёт по расписанию в материализованном представлении Postgres (был в плане; данные отстают на период пересчёта), Feature Store (Feast/Tecton — избыточен и свежесть не решает). Кэш Redis с коротким сроком жизни — только после замера: включается, если время вызова API не укладывается в бюджет ответа либо лимиты владельца ниже нагрузки. Задержка и лимиты API не измерялись (доступа нет). Сравнение по требованиям и документации, не по пробному внедрению.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Кэш профиля абонента: где хранить и с чем сравнивали»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Данные абонента: читаем из систем в момент вопроса, кэш — после замера»; замер — ADR-600, «Замер чтения данных абонента из систем»</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>Периодического пересчёта из живых систем на прототипе нет: данные — слепок из присланного примера.</t>
+          <t>Скорость, лимиты и доступность API Биллинга и Диспетчерской неизвестны, доступа к ним нет; задержка ответа теперь зависит от чужих систем. Доля вопросов, которым нужны данные абонента, не измерена. Нагрузка на системы владельца пропорциональна числу вопросов: до 0,058 вызова/с на MVP и 0,656 на тираже в максимуме прогноза (верхняя оценка — один вызов на вопрос).</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Пересчёт агрегата по расписанию из Биллинга (XML-RPC) и Диспетчерской (REST); замер чтения профиля из Postgres под нагрузкой MVP (1,5–2 чел-дн, ADR-600).</t>
+          <t>Чтение из Биллинга и Диспетчерской в момент вопроса; таймауты, повторы и ответ «данных сейчас нет» при отказе системы; замер времени вызовов и лимитов API (ADR-600, «Замер чтения данных абонента из систем»); кэш Redis — по итогам замера. Сами клиенты API — в строках «Backend ↔ Биллинг» и «Backend ↔ Диспетчерская».</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes CronJob → Postgres (материализованное представление). Без Redis; возврат Redis — только по итогам замера.</t>
+          <t>Клиенты XML-RPC и REST в Backend, параллельные вызовы (asyncio), таймауты и повторы. Без Postgres-представления и без задания по расписанию. Redis со сроком жизни в минуты — только по итогам замера.</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Ответ читает готовый агрегат по индексу, без обращения к первичным системам; планировщик по расписанию (Kubernetes CronJob), предусмотренный в схеме развёртывания (кластера пока нет).</t>
+          <t>Данные абонента (баланс, начисления, показания, заявки) меняются; ответ по предрасчитанной сводке может оказаться неверным (требование заказчика 25.09.2026).</t>
         </is>
       </c>
       <c r="M13" s="22" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Оценка автора; замер профиля — ADR-600</t>
+          <t>Оценка автора; замер API — ADR-600</t>
         </is>
       </c>
       <c r="P13" s="14" t="inlineStr">
@@ -1909,7 +1909,7 @@
       <c r="U13" s="15" t="n"/>
       <c r="V13" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-600; Data_Flow_Diagrams</t>
+          <t>ADR-200; ADR-600</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>PostgreSQL выбран против MySQL/MariaDB (нет материализованных представлений) и SQLite (один файл, не для нескольких сервисов). Телеметрия остаётся в Postgres, а не в ClickHouse: до ≈0,8 млн событий в год на тираже; замер 2 млн строк — 589 МБ, агрегаты за секунды (ADR-200).</t>
+          <t>PostgreSQL выбран против MySQL/MariaDB (нечего добавить к PostgreSQL) и SQLite (один файл, не для нескольких сервисов). Телеметрия остаётся в Postgres, а не в ClickHouse: до ≈0,8 млн событий в год на тираже; замер 2 млн строк — 589 МБ, агрегаты за секунды (ADR-200).</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Backend; Кэш профиля (пересчёт из Биллинга); Биллинг (внешняя)</t>
+          <t>Backend; Биллинг (внешняя)</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>Свежие факты запрашиваются у Биллинга в момент вопроса.</t>
+          <t>Данные абонента запрашиваются у Биллинга в момент вопроса (предрасчёта нет, решение 25.09.2026).</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>Единственный способ доступа к Биллингу; обходит задержку кэша ради свежести.</t>
+          <t>Единственный способ доступа к Биллингу; данные нужны онлайн, а не с отставанием предрасчёта.</t>
         </is>
       </c>
       <c r="M29" s="20" t="n">
@@ -6966,33 +6966,33 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="105" customHeight="1">
       <c r="A15" s="50" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Кэш профиля абонента (Postgres)</t>
+          <t>Данные абонента (чтение из Биллинга и Диспетчерской)</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Число абонентов и начислений</t>
+          <t>Число вопросов</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>8 000 профилей на MVP, 90 000 на тираже. Строка профиля с начислениями — 3 КБ (допущение): ≈24 МБ на MVP, ≈270 МБ на тираже. По примеру прототипа (200 счетов, 1 323 начисления) ≈6,6 начисления на счёт. Хранится в Postgres (см. ниже).</t>
+          <t>Данные не хранятся: читаются из систем в момент вопроса (решение 25 сентября 2026). Верхняя оценка нагрузки на каждую систему — один вызов на вопрос, то есть до 0,058 вызова/с на MVP и 0,656 на тираже в максимуме прогноза (по пути ответа вызовов может быть меньше; доля вопросов, которым нужны данные абонента, не измерена). Скорость и лимиты API владельца неизвестны. Кэш в Redis — только после замера, объём не оценивался.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Допущение; выбрано и посчитано</t>
+          <t>Допущение; замер API не проводился</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; data_example</t>
+          <t>ADR-200; ADR-600</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="90" customHeight="1">
+    <row r="28" ht="105" customHeight="1">
       <c r="A28" s="50" t="n">
         <v>13</v>
       </c>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Postgres (обращения, профиль, телеметрия, журнал диалогов)</t>
+          <t>Postgres (обращения, телеметрия, журнал диалогов)</t>
         </is>
       </c>
       <c r="D28" s="51" t="n">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; профиль 24 МБ и 270 МБ (заложено 3 КБ на абонента; по примеру прототипа — 0,7 КБ на счёт в CSV); события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
+          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Данные абонента в Postgres не хранятся: они читаются из Биллинга и Диспетчерской в момент вопроса (решение 25 сентября 2026; прежняя строка профиля 24 МБ и 270 МБ снята). Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прогноз стоимости" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$2:$V$43</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Матрица'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Настоящие бланки заявлений не согласованы с владельцем — используются образцы.</t>
+          <t>Настоящие бланки заявлений не согласованы с владельцем — используются образцы; на MVP шаблоны берутся из сервиса шаблонов (отдельная строка).</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Рендер PDF из шаблона и слотов, хранение в объектном хранилище, ссылка с ограниченным сроком жизни.</t>
+          <t>Рендер PDF из шаблона и слотов, хранение в объектном хранилище, ссылка с ограниченным сроком жизни. Шаблоны получает от сервиса шаблонов (отдельная строка), а не из кода.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
@@ -2660,94 +2660,78 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Оркестрация контейнеров</t>
+          <t>Сервис шаблонов заявлений (Template Service)</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Все контейнеры (Backend, LLM Gateway, Qdrant, Redis, Postgres, ETL, GPU-сервисы)</t>
+          <t>Template Service; Backend (TemplateResponder); Document Generator; MinIO или файловый сервер владельца (источник)</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Прототип — Docker Compose на одной машине; MVP — Kubernetes (nginx Ingress, cert-manager)</t>
+          <t>Прототип — Python-модуль `app/documents/templates.py`; MVP — Python (FastAPI) + клиент S3 и/или смонтированный каталог файлового сервера (только чтение), описатель шаблона в YAML или JSON</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>`docker compose` на одной машине: postgres, redis, qdrant, reindex, backend.</t>
+          <t>Отдельного контейнера нет: семь образцов заявлений заданы в коде (`app/documents/templates.py`) — текст с полями, вопросы абоненту, приложения, основание. Образцы ориентировочные, настоящих бланков владельца нет.</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Compose на одном или нескольких хостах не переживает отказ узла и не обновляется без остановки; Docker Swarm слабее по GPU и заданиям, меньше сообщество; Nomad — реальная альтернатива, если некому эксплуатировать Kubernetes (проще, встроенная интеграция с Vault). Сравнение по документации, ни один вариант кроме Compose не разворачивался (ADR-200, «Почему Kubernetes»). Для одного разработчика и одного хоста Kubernetes избыточен.</t>
+          <t>Решение заказчика проекта 25.09.2026: шаблоны тянутся из хранилища или с файлового сервера отдельным контейнером. Сравнивались: в коде (прототип; замена бланка — выпуск приложения), файлы в образе или ConfigMap (тоже выпуск; ConfigMap ограничен ≈1 МБ по документации Kubernetes), отдельный контейнер + MinIO (уже в стеке; версии и права — средствами S3 по документации), отдельный контейнер + файловый сервер владельца (владелец кладёт форму туда, где уже работает; доступ, протокол и учётная запись неизвестны), таблица в Postgres (смешивает файлы форм с данными). Источник основной не выбран — зависит от ответа владельца; кандидат — MinIO. Сравнение по документации и общим сведениям, стенда нет.</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе» и подраздел «Почему Kubernetes, а не другая оркестрация»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Шаблоны заявлений: отдельный контейнер, шаблоны из хранилища или файлового сервера»; работы — ADR-600, «Сервис шаблонов заявлений (MVP)»</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Решение заказчика проекта (24.09.2026, документально не подтверждено): личный кабинет уже на Kubernetes, размещаемся в том же кластере, эксплуатирует тот же отдел, GPU-узлов нет. Не известны дистрибутив и версия, квоты, классы хранилищ и быстрые диски, как настроено шифрование Kubernetes Secrets и права на них, есть ли своя наблюдаемость, сетевые правила. Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
+          <t>Формат форм (Word, PDF-форма, HTML), источник (MinIO или файловый сервер), протокол и доступ, кто утверждает и обновляет формы, обязательные приложения — ответы владельца, не получены. Формат связан с выбором библиотеки PDF: если формы придут в Word, основным кандидатом становится LibreOffice headless. При недоступности источника контейнер отдаёт кэш, а без кэша Backend возвращается к встроенным образцам с пометкой «ориентировочный образец».</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 16 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
+          <t>Отдельный контейнер `template-service`: API (список, получение по коду и версии), источники MinIO и файловый сервер (только чтение), кэш с проверкой изменения, проверка при загрузке (известные поля, нет ПДн), версия шаблона в следе операции; Backend берёт шаблон из сервиса, встроенные образцы остаются запасным путём; перенос настоящих форм владельца. Работа: формат шаблона и описателя 2–3, контейнер 3–5, интеграция Backend 1,5–2,5, перенос форм 2–4, безопасность и сеть 1–2 чел-дн (ADR-600).</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes владельца (дистрибутив и версия неизвестны); Ingress и сертификаты — по правилам кластера; манифесты приложения.</t>
+          <t>Python (FastAPI); клиент S3 (boto3 или minio) и/или смонтированный каталог файлового сервера, только чтение; описатель шаблона — YAML или JSON рядом с файлом; Deployment, 2 реплики.</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Отказоустойчивость, обновление без остановки, пулы узлов с GPU, задания по расписанию. Нагрузка ради этого не нужна: запросы всех подов (11,2 vCPU, 23,6 ГиБ) помещаются на один сервер.</t>
-        </is>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>9</v>
+          <t>Официальная форма принадлежит водоканалу и меняется; замена бланка не должна требовать выпуска приложения.</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N22" s="22" t="n">
+        <v>16.5</v>
       </c>
       <c r="O22" s="13" t="inlineStr">
         <is>
-          <t>Оценка автора</t>
-        </is>
-      </c>
-      <c r="P22" s="9" t="inlineStr">
-        <is>
-          <t>Согласование платформы с владельцем инфраструктуры: решено размещаться в общем кластере с личным кабинетом (эксплуатирует тот же отдел, GPU нет); остаются дистрибутив и версия, квоты, шифрование Secrets и наблюдаемость кластера, отечественное ПО; аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
-        </is>
-      </c>
-      <c r="Q22" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>Для тиража нужна согласованная платформа, включая GPU-пулы; выбор Kubernetes пока предварительный.</t>
-        </is>
-      </c>
-      <c r="S22" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+          <t>Оценка автора; формат форм и источник неизвестны</t>
+        </is>
+      </c>
+      <c r="P22" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q22" s="15" t="n"/>
+      <c r="R22" s="15" t="n"/>
+      <c r="S22" s="16" t="n"/>
+      <c r="T22" s="16" t="n"/>
+      <c r="U22" s="15" t="n"/>
       <c r="V22" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-600; C4_Deployment</t>
+          <t>ADR-200; ADR-600; ADR-100</t>
         </is>
       </c>
     </row>
@@ -2762,78 +2746,94 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Секреты и конфигурация</t>
+          <t>Оркестрация контейнеров</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Backend; LLM Gateway (ключи провайдеров); все контейнеры (конфигурация)</t>
+          <t>Все контейнеры (Backend, LLM Gateway, Qdrant, Redis, Postgres, ETL, GPU-сервисы)</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (необязательный локальный вариант); MVP — GitLab CI variables, Kubernetes Secret</t>
+          <t>Прототип — Docker Compose на одной машине; MVP — Kubernetes (nginx Ingress, cert-manager)</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Vault в dev-режиме — необязательный локальный вариант.</t>
+          <t>`docker compose` на одной машине: postgres, redis, qdrant, reindex, backend.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Целевой механизм (решение заказчика проекта, 24.09.2026): GitLab CI variables (masked, protected) + деплой через pipeline → Kubernetes Secret. Сравнение (ADR-200, «Секреты в проде: GitLab CI variables и альтернативы»; по документации, без проверки на стенде владельца): Vault Agent Injector — есть аудит чтения, аренда и замена без пересборки, но нужна новая система (отказоустойчивость, разблокировка, резервные копии) и sidecar в каждом поде; External Secrets Operator или Vault CSI — то же плюс оператор; SOPS или Sealed Secrets — шифрованные секреты в Git, без аудита чтения; Kubernetes Secret вручную — без повторяемости и журнала. Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения.</t>
+          <t>Compose на одном или нескольких хостах не переживает отказ узла и не обновляется без остановки; Docker Swarm слабее по GPU и заданиям, меньше сообщество; Nomad — реальная альтернатива, если некому эксплуатировать Kubernetes (проще, встроенная интеграция с Vault). Сравнение по документации, ни один вариант кроме Compose не разворачивался (ADR-200, «Почему Kubernetes»). Для одного разработчика и одного хоста Kubernetes избыточен.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Секреты и конфигурация» и подраздел «Секреты в проде: GitLab CI variables и альтернативы»; ADR-400 («Что добавляется в контуре MVP»)</t>
+          <t>ADR-200, раздел «Backend и оркестрация»: строки «Оркестрация контейнеров» и «Оркестрация на прототипе» и подраздел «Почему Kubernetes, а не другая оркестрация»</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Нет аудита чтения; значения видны ролям проекта GitLab с правом их читать (по документации Maintainer и выше); шифрование etcd в кластере неизвестно; замена секрета требует деплоя и перезапуска подов; маскирование в логах ограничено по формату значения. Настройки GitLab владельца, права на переменные и версия не проверялись. Прежний выбор Vault Agent Injector отменён как не обоснованный сравнением.</t>
+          <t>Решение заказчика проекта (24.09.2026, документально не подтверждено): личный кабинет уже на Kubernetes, размещаемся в том же кластере, эксплуатирует тот же отдел, GPU-узлов нет. Не известны дистрибутив и версия, квоты, классы хранилищ и быстрые диски, как настроено шифрование Kubernetes Secrets и права на них, есть ли своя наблюдаемость, сетевые правила. Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Переменные проекта GitLab CI (masked, protected, по окружениям); job деплоя создаёт Kubernetes Secret без вывода значений в лог; подключение в поды через secretKeyRef или envFrom (изменений кода нет); регламент замены секрета; проверка, что значения не попадают в лог pipeline, образ и манифесты.</t>
+          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 17 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>GitLab CI/CD variables (masked, protected), pipeline деплоя, Kubernetes Secret; версия и редакция GitLab владельца неизвестны.</t>
+          <t>Kubernetes владельца (дистрибутив и версия неизвестны); Ingress и сертификаты — по правилам кластера; манифесты приложения.</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Ничего нового не ставится и не эксплуатируется: GitLab уже используется (со слов); приложение читает переменные окружения, как на прототипе. Vault — вариант по условиям пересмотра: аудит чтения, динамические секреты, замена без перезапуска (ADR-400).</t>
+          <t>Отказоустойчивость, обновление без остановки, пулы узлов с GPU, задания по расписанию. Нагрузка ради этого не нужна: запросы всех подов (11,2 vCPU, 23,6 ГиБ) помещаются на один сервер.</t>
         </is>
       </c>
       <c r="M23" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>Оценка автора</t>
+        </is>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
+        <is>
+          <t>Согласование платформы с владельцем инфраструктуры: решено размещаться в общем кластере с личным кабинетом (эксплуатирует тот же отдел, GPU нет); остаются дистрибутив и версия, квоты, шифрование Secrets и наблюдаемость кластера, отечественное ПО; аргументация записана в ADR-200; при необходимости отдельный ADR.</t>
+        </is>
+      </c>
+      <c r="Q23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>Для тиража нужна согласованная платформа, включая GPU-пулы; выбор Kubernetes пока предварительный.</t>
+        </is>
+      </c>
+      <c r="S23" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="N23" s="12" t="n">
+      <c r="T23" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="O23" s="13" t="inlineStr">
-        <is>
-          <t>Оценка автора</t>
-        </is>
-      </c>
-      <c r="P23" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q23" s="15" t="n"/>
-      <c r="R23" s="15" t="n"/>
-      <c r="S23" s="16" t="n"/>
-      <c r="T23" s="16" t="n"/>
-      <c r="U23" s="15" t="n"/>
+      <c r="U23" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-400</t>
+          <t>ADR-200; ADR-600; C4_Deployment</t>
         </is>
       </c>
     </row>
@@ -2848,59 +2848,59 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Наблюдаемость (метрики, логи, алерты)</t>
+          <t>Секреты и конфигурация</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); отдельные контейнеры Prometheus и Loki — верхняя оценка до ответа владельца (MVP)</t>
+          <t>Backend; LLM Gateway (ключи провайдеров); все контейнеры (конфигурация)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Zabbix и Grafana владельца (Jaeger — по необходимости), дашборды и триггеры как код</t>
+          <t>Переменные окружения оболочки (передаются через Compose `${VAR}`); Vault dev-режим (необязательный локальный вариант); MVP — GitLab CI variables, Kubernetes Secret</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Метрики Prometheus на отдельном порту 9100 (в Compose порт не опубликован: с хоста недоступен, внутри контейнера отдаётся), события потока в панели стенда. Дашбордов, сбора логов, трассировки и алертов нет.</t>
+          <t>Переменные окружения оболочки, `.env` приложение не читает; через `docker compose` передаются в контейнер. Vault в dev-режиме — необязательный локальный вариант.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Факты со слов заказчика проекта (24.09.2026): в реальном контуре работают Grafana, Zabbix и Jaeger; алерты не настроены. Основной вариант C — Zabbix собирает метрики с порта 9100, Grafana владельца показывает, алерты — триггеры Zabbix; запасной B — свой Prometheus как источник для Grafana (если Zabbix не справится с задержкой P99: квантили по гистограммам штатно не считает — по документации, не проверялось). Prometheus владельца снят (не назван), своя четвёрка и ELK/облако отклонены. Прежнее «Zabbix отклонён: ориентирован на хосты» не проверялось. Сравнение по документации.</t>
+          <t>Целевой механизм (решение заказчика проекта, 24.09.2026): GitLab CI variables (masked, protected) + деплой через pipeline → Kubernetes Secret. Сравнение (ADR-200, «Секреты в проде: GitLab CI variables и альтернативы»; по документации, без проверки на стенде владельца): Vault Agent Injector — есть аудит чтения, аренда и замена без пересборки, но нужна новая система (отказоустойчивость, разблокировка, резервные копии) и sidecar в каждом поде; External Secrets Operator или Vault CSI — то же плюс оператор; SOPS или Sealed Secrets — шифрованные секреты в Git, без аудита чтения; Kubernetes Secret вручную — без повторяемости и журнала. Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения.</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Наблюдаемость: Grafana владельца и источники данных»</t>
+          <t>ADR-200, раздел «Секреты и конфигурация» и подраздел «Секреты в проде: GitLab CI variables и альтернативы»; ADR-400 («Что добавляется в контуре MVP»)</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Алерты не настроены: 9 описанных алертов (в том числе «Утечка ПДн в ответе») принимать некому — нет каналов и получателей; предложение автора: настроенный алерт об утечке ПДн — условие включения MVP (согласовать с ИБ). Не известны версии Zabbix, Grafana, Jaeger, подключение Zabbix к Grafana, возможность считать квантили, сбор логов. Трассировки в нашем коде нет (Jaeger в контуре есть).</t>
+          <t>Нет аудита чтения; значения видны ролям проекта GitLab с правом их читать (по документации Maintainer и выше); шифрование etcd в кластере неизвестно; замена секрета требует деплоя и перезапуска подов; маскирование в логах ограничено по формату значения. Настройки GitLab владельца, права на переменные и версия не проверялись. Прежний выбор Vault Agent Injector отменён как не обоснованный сравнением.</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>Дашборды как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; 9 алертов как триггеры и действия Zabbix; сбор метрик с порта 9100; проверка расчёта P99 в Zabbix до начала работ; определение получателей и каналов оповещения; в логах только отчёт об обезличивании. Проверка на стенде владельца до выбора между Zabbix (C) и своим Prometheus (B): сбор с порта 9100, расчёт P99, доставка алерта, плагин Grafana, нагрузка на Zabbix (1–2 чел-дн, предложение автора). Алерты: триггеры Zabbix (при B — Grafana Alerting; Alertmanager не разворачиваем); алерт об утечке ПДн — сразу, без подавления повторов, получатель от ИБ; алерт о недоступности источника метрик. Трассировка: на MVP без Jaeger — две гистограммы (поиск, вызов провайдера) 0,5–1 чел-дн в пределах оценки; OpenTelemetry → Jaeger — только если P99 разобрать не удаётся, 2–4 чел-дн, оценка автора, в итог не входит. Оценка не пересматривалась (5–8): развёртывание своей связки отпало, добавились интеграция с Zabbix и настройка оповещений.</t>
+          <t>Переменные проекта GitLab CI (masked, protected, по окружениям); job деплоя создаёт Kubernetes Secret без вывода значений в лог; подключение в поды через secretKeyRef или envFrom (изменений кода нет); регламент замены секрета; проверка, что значения не попадают в лог pipeline, образ и манифесты.</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); Prometheus и Loki — верхняя оценка до ответа владельца.</t>
+          <t>GitLab CI/CD variables (masked, protected), pipeline деплоя, Kubernetes Secret; версия и редакция GitLab владельца неизвестны.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах; мониторинг и Grafana уже есть у владельца, дублировать их незачем.</t>
+          <t>Ничего нового не ставится и не эксплуатируется: GitLab уже используется (со слов); приложение читает переменные окружения, как на прототипе. Vault — вариант по условиям пересмотра: аудит чтения, динамические секреты, замена без перезапуска (ADR-400).</t>
         </is>
       </c>
       <c r="M24" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O24" s="13" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       <c r="U24" s="15" t="n"/>
       <c r="V24" s="9" t="inlineStr">
         <is>
-          <t>C4_Deployment; ADR-200; ADR-500</t>
+          <t>ADR-200; ADR-400</t>
         </is>
       </c>
     </row>
@@ -2927,64 +2927,72 @@
       <c r="A25" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>Сквозная работа</t>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Контейнер</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Алерты и оповещения</t>
+          <t>Наблюдаемость (метрики, логи, алерты)</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Zabbix владельца (триггеры, действия); Backend и LLM Gateway (метрики блокировок и утечек); Grafana владельца (запасной вариант)</t>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); отдельные контейнеры Prometheus и Loki — верхняя оценка до ответа владельца (MVP)</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Триггеры и действия Zabbix; Grafana Alerting — запасной вариант</t>
+          <t>prometheus-client (метрики на отдельном порту 9100); MVP — Zabbix и Grafana владельца (Jaeger — по необходимости), дашборды и триггеры как код</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>9 алертов описаны (от «Утечка ПДн в ответе» до «ИБ + деградация»), спецификации дашборда в репозитории нет. В реальном контуре алерты не настроены (со слов заказчика проекта, 24.09.2026): каналов оповещения и получателей нет. В нашем коде есть метрики блокировок и утечек, правил и доставки нет.</t>
+          <t>Метрики Prometheus на отдельном порту 9100 (в Compose порт не опубликован: с хоста недоступен, внутри контейнера отдаётся), события потока в панели стенда. Дашбордов, сбора логов, трассировки и алертов нет.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Триггеры и действия Zabbix (выбраны при основном варианте C) — против Grafana Alerting (при запасном варианте B, если в Zabbix настроить нельзя) и Alertmanager (не разворачиваем: дублирует Zabbix и Grafana владельца). Сравнение по документации, у владельца не проверялось; каналы оповещения не настроены.</t>
+          <t>Факты со слов заказчика проекта (24.09.2026): в реальном контуре работают Grafana, Zabbix и Jaeger; алерты не настроены. Основной вариант C — Zabbix собирает метрики с порта 9100, Grafana владельца показывает, алерты — триггеры Zabbix; запасной B — свой Prometheus как источник для Grafana (если Zabbix не справится с задержкой P99: квантили по гистограммам штатно не считает — по документации, не проверялось). Prometheus владельца снят (не назван), своя четвёрка и ELK/облако отклонены. Прежнее «Zabbix отклонён: ориентирован на хосты» не проверялось. Сравнение по документации.</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Наблюдаемость: Grafana владельца и источники данных», блок «Алерты: сравнение вариантов»</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Наблюдаемость: Grafana владельца и источники данных»</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Получатели, канал, регламент реакции и эскалация не определены; без них алерты «Утечка ПДн в ответе» и «ИБ + деградация» на MVP не сработают. Версия Zabbix и его возможности по оповещениям неизвестны. Настроены ли алерты в Zabbix вообще или только для нашего сервиса — неизвестно.</t>
+          <t>Алерты не настроены: 9 описанных алертов (в том числе «Утечка ПДн в ответе») принимать некому — нет каналов и получателей; предложение автора: настроенный алерт об утечке ПДн — условие включения MVP (согласовать с ИБ). Не известны версии Zabbix, Grafana, Jaeger, подключение Zabbix к Grafana, возможность считать квантили, сбор логов. Трассировки в нашем коде нет (Jaeger в контуре есть).</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>9 алертов как триггеры и действия Zabbix (при запасном варианте B — правила Grafana Alerting); требования к любому варианту: алерт об утечке ПДн приходит сразу и без подавления повторов получателю от ИБ; алерт о недоступности источника метрик; получатели, канал, регламент и эскалация определены до включения MVP (предложение автора, согласовать с ИБ); пороги срабатывания — по замеру на живых данных.</t>
+          <t>Дашборды как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; 9 алертов как триггеры и действия Zabbix; сбор метрик с порта 9100; проверка расчёта P99 в Zabbix до начала работ; определение получателей и каналов оповещения; в логах только отчёт об обезличивании. Проверка на стенде владельца до выбора между Zabbix (C) и своим Prometheus (B): сбор с порта 9100, расчёт P99, доставка алерта, плагин Grafana, нагрузка на Zabbix (1–2 чел-дн, предложение автора). Алерты: триггеры Zabbix (при B — Grafana Alerting; Alertmanager не разворачиваем); алерт об утечке ПДн — сразу, без подавления повторов, получатель от ИБ; алерт о недоступности источника метрик. Трассировка: на MVP без Jaeger — две гистограммы (поиск, вызов провайдера) 0,5–1 чел-дн в пределах оценки; OpenTelemetry → Jaeger — только если P99 разобрать не удаётся, 2–4 чел-дн, оценка автора, в итог не входит. Оценка не пересматривалась (5–8): развёртывание своей связки отпало, добавились интеграция с Zabbix и настройка оповещений.</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Zabbix владельца (триггеры, действия, каналы); Grafana Alerting — запасной вариант.</t>
+          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); Prometheus и Loki — верхняя оценка до ответа владельца.</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>Без алерта об утечке ПДн нарушение 152-ФЗ обнаружится не сразу; оценка входит в строку «Наблюдаемость (метрики, логи, алерты)», отдельно не считается.</t>
-        </is>
-      </c>
-      <c r="M25" s="19" t="n"/>
-      <c r="N25" s="19" t="n"/>
-      <c r="O25" s="9" t="n"/>
+          <t>Без этого нельзя измерять задержку ответа (P99), долю отказов и утечки ПДн на реальных абонентах; мониторинг и Grafana уже есть у владельца, дублировать их незачем.</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" s="13" t="inlineStr">
+        <is>
+          <t>Оценка автора</t>
+        </is>
+      </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -2997,7 +3005,7 @@
       <c r="U25" s="15" t="n"/>
       <c r="V25" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-400</t>
+          <t>C4_Deployment; ADR-200; ADR-500</t>
         </is>
       </c>
     </row>
@@ -3012,65 +3020,57 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Трассировка (Jaeger)</t>
+          <t>Алерты и оповещения</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Backend; LLM Gateway; клиенты Qdrant, Postgres, Redis; Jaeger владельца</t>
+          <t>Zabbix владельца (триггеры, действия); Backend и LLM Gateway (метрики блокировок и утечек); Grafana владельца (запасной вариант)</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>OpenTelemetry (Python), OTLP, Jaeger владельца — по условию</t>
+          <t>Триггеры и действия Zabbix; Grafana Alerting — запасной вариант</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Jaeger в реальном контуре есть (со слов заказчика проекта, 24.09.2026). В нашем коде трассировки нет (библиотек OpenTelemetry и Jaeger в проекте нет). Гистограммы задержки есть для ответа, первого куска, проверки ответа и обезличивания; для поиска в базе знаний и вызова провайдера — нет.</t>
+          <t>9 алертов описаны (от «Утечка ПДн в ответе» до «ИБ + деградация»), спецификации дашборда в репозитории нет. В реальном контуре алерты не настроены (со слов заказчика проекта, 24.09.2026): каналов оповещения и получателей нет. В нашем коде есть метрики блокировок и утечек, правил и доставки нет.</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Вариант 1 — без трассировки, метрики по стадиям (по умолчанию для MVP) — против варианта 2 — OpenTelemetry → Jaeger владельца (по условию: P99 по метрикам разобрать не удаётся) и варианта 3 — свой Jaeger (отклонён: в контуре он есть). Сравнение по документации; приём OTLP в Jaeger владельца не проверялся.</t>
+          <t>Триггеры и действия Zabbix (выбраны при основном варианте C) — против Grafana Alerting (при запасном варианте B, если в Zabbix настроить нельзя) и Alertmanager (не разворачиваем: дублирует Zabbix и Grafana владельца). Сравнение по документации, у владельца не проверялось; каналы оповещения не настроены.</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Наблюдаемость: Grafana владельца и источники данных», блок «Трассировка (Jaeger): сравнение вариантов»; ADR-600, «Трассировка OpenTelemetry → Jaeger — по необходимости»</t>
+          <t>ADR-200, подраздел «Наблюдаемость: Grafana владельца и источники данных», блок «Алерты: сравнение вариантов»</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>Без гистограмм поиска и вызова провайдера задержку P99 по стадиям не разобрать. Принимает ли Jaeger владельца OTLP, версия и права — неизвестно. Трассы не должны содержать ПДн в атрибутах спанов.</t>
+          <t>Получатели, канал, регламент реакции и эскалация не определены; без них алерты «Утечка ПДн в ответе» и «ИБ + деградация» на MVP не сработают. Версия Zabbix и его возможности по оповещениям неизвестны. Настроены ли алерты в Zabbix вообще или только для нашего сервиса — неизвестно.</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>На MVP без трассировки: две гистограммы (поиск в базе знаний, вызов провайдера) — 0,5–1 чел-дн внутри оценки строки «Наблюдаемость» (оценка автора). Инструментация OpenTelemetry (FastAPI, HTTP-клиенты, клиенты Qdrant, Postgres, Redis) с отправкой по OTLP в Jaeger владельца — только если после гистограмм P99 разобрать не удаётся: 2–4 чел-дн, оценка автора, в итог не входит.</t>
+          <t>9 алертов как триггеры и действия Zabbix (при запасном варианте B — правила Grafana Alerting); требования к любому варианту: алерт об утечке ПДн приходит сразу и без подавления повторов получателю от ИБ; алерт о недоступности источника метрик; получатели, канал, регламент и эскалация определены до включения MVP (предложение автора, согласовать с ИБ); пороги срабатывания — по замеру на живых данных.</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>OpenTelemetry (Python), OTLP, Jaeger владельца — по условию.</t>
+          <t>Zabbix владельца (триггеры, действия, каналы); Grafana Alerting — запасной вариант.</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Трассировка полезна для разбора P99 и TTFT по стадиям, но на четырёх стадиях линейной цепочки метрик обычно хватает; не тратим работу без необходимости.</t>
-        </is>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" s="13" t="inlineStr">
-        <is>
-          <t>По триггеру (P99 по метрикам разобрать не удаётся; оценка автора)</t>
-        </is>
-      </c>
+          <t>Без алерта об утечке ПДн нарушение 152-ФЗ обнаружится не сразу; оценка входит в строку «Наблюдаемость (метрики, логи, алерты)», отдельно не считается.</t>
+        </is>
+      </c>
+      <c r="M26" s="19" t="n"/>
+      <c r="N26" s="19" t="n"/>
+      <c r="O26" s="9" t="n"/>
       <c r="P26" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3083,7 +3083,7 @@
       <c r="U26" s="15" t="n"/>
       <c r="V26" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-600</t>
+          <t>ADR-200; ADR-400</t>
         </is>
       </c>
     </row>
@@ -3091,60 +3091,72 @@
       <c r="A27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>Связь</t>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Виджет ↔ Backend</t>
+          <t>Трассировка (Jaeger)</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>AI-виджет; Backend</t>
+          <t>Backend; LLM Gateway; клиенты Qdrant, Postgres, Redis; Jaeger владельца</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
+          <t>OpenTelemetry (Python), OTLP, Jaeger владельца — по условию</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
+          <t>Jaeger в реальном контуре есть (со слов заказчика проекта, 24.09.2026). В нашем коде трассировки нет (библиотек OpenTelemetry и Jaeger в проекте нет). Гистограммы задержки есть для ответа, первого куска, проверки ответа и обезличивания; для поиска в базе знаний и вызова провайдера — нет.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
+          <t>Вариант 1 — без трассировки, метрики по стадиям (по умолчанию для MVP) — против варианта 2 — OpenTelemetry → Jaeger владельца (по условию: P99 по метрикам разобрать не удаётся) и варианта 3 — свой Jaeger (отклонён: в контуре он есть). Сравнение по документации; приём OTLP в Jaeger владельца не проверялся.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
+          <t>ADR-200, подраздел «Наблюдаемость: Grafana владельца и источники данных», блок «Трассировка (Jaeger): сравнение вариантов»; ADR-600, «Трассировка OpenTelemetry → Jaeger — по необходимости»</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K27" s="15" t="n"/>
-      <c r="L27" s="15" t="inlineStr">
-        <is>
-          <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="n"/>
-      <c r="N27" s="16" t="n"/>
-      <c r="O27" s="15" t="n"/>
+          <t>Без гистограмм поиска и вызова провайдера задержку P99 по стадиям не разобрать. Принимает ли Jaeger владельца OTLP, версия и права — неизвестно. Трассы не должны содержать ПДн в атрибутах спанов.</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>На MVP без трассировки: две гистограммы (поиск в базе знаний, вызов провайдера) — 0,5–1 чел-дн внутри оценки строки «Наблюдаемость» (оценка автора). Инструментация OpenTelemetry (FastAPI, HTTP-клиенты, клиенты Qdrant, Postgres, Redis) с отправкой по OTLP в Jaeger владельца — только если после гистограмм P99 разобрать не удаётся: 2–4 чел-дн, оценка автора, в итог не входит.</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>OpenTelemetry (Python), OTLP, Jaeger владельца — по условию.</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>Трассировка полезна для разбора P99 и TTFT по стадиям, но на четырёх стадиях линейной цепочки метрик обычно хватает; не тратим работу без необходимости.</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" s="13" t="inlineStr">
+        <is>
+          <t>По триггеру (P99 по метрикам разобрать не удаётся; оценка автора)</t>
+        </is>
+      </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3157,7 +3169,7 @@
       <c r="U27" s="15" t="n"/>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>API_Spec.yaml</t>
+          <t>ADR-200; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3172,65 +3184,53 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Платформа ЛК (SSO)</t>
+          <t>Виджет ↔ Backend</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Backend; Платформа ЛК (внешняя)</t>
+          <t>AI-виджет; Backend</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
+          <t>HTTP/JSON; поток SSE (`text/event-stream`); контракт OpenAPI 3</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Не подключена: абонент выбирается из справочника стенда.</t>
+          <t>HTTP + поток SSE; контракт описан в OpenAPI (`API_Spec.yaml`), идентификатор абонента — в метаданных запроса.</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
+          <t>SSE выбран против WebSocket и периодического опроса: данные идут только от сервера, обычный HTTP проходит через Ingress, формат текстовый. Особенность: EventSource умеет только GET, поэтому виджет читает поток через fetch (POST).</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Протокол потока ответа: SSE»</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
-        </is>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
-        </is>
-      </c>
+          <t>Идентификатор абонента передаёт сам клиент — для стенда допустимо, для продакшена нет.</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="n"/>
+      <c r="L28" s="15" t="inlineStr">
+        <is>
+          <t>Протокол тот же; токен SSO — в строке про связь с ЛК.</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="n"/>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="15" t="n"/>
       <c r="P28" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3243,7 +3243,7 @@
       <c r="U28" s="15" t="n"/>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>API_Spec.yaml</t>
         </is>
       </c>
     </row>
@@ -3258,63 +3258,63 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Биллинг (чтение фактов)</t>
+          <t>Backend ↔ Платформа ЛК (SSO)</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Backend; Биллинг (внешняя)</t>
+          <t>Backend; Платформа ЛК (внешняя)</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
+          <t>SSO личного кабинета (протокол не выбран); на прототипе — идентификатор в метаданных запроса</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
+          <t>Не подключена: абонент выбирается из справочника стенда.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
+          <t>Сравнение не проводилось: интеграция с ЛК не начата, протокол SSO ещё не известен.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам» (протокол SSO не выбран)</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры API Биллинга от владельца не получены.</t>
+          <t>Настоящей SSO-сессии нет; Auth &amp; Session Middleware — целевой компонент.</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>Данные абонента запрашиваются у Биллинга в момент вопроса (предрасчёта нет, решение 25.09.2026).</t>
+          <t>Профиль и сессия абонента берутся из личного кабинета при открытии диалога.</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>XML-RPC API Биллинга.</t>
+          <t>SSO Платформы ЛК, Auth &amp; Session Middleware в Backend.</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>Единственный способ доступа к Биллингу; данные нужны онлайн, а не с отставанием предрасчёта.</t>
-        </is>
-      </c>
-      <c r="M29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
+          <t>Идентификатор абонента должен приходить от доверенной системы, а не от клиента.</t>
+        </is>
+      </c>
+      <c r="M29" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Основная разработка Этапа 2</t>
         </is>
       </c>
       <c r="P29" s="14" t="inlineStr">
@@ -3344,27 +3344,27 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Диспетчерская</t>
+          <t>Backend ↔ Биллинг (чтение фактов)</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
+          <t>Backend; Биллинг (внешняя)</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
+          <t>XML-RPC API Биллинга; на прототипе — слепок в PostgreSQL</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
+          <t>Чтение из слепка Биллинга в Postgres; для лицевого счёта: долг, начисления, показания, поверка.</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>Прямой доступ к чужой БД запрещён.</t>
+          <t>Прямое чтение чужой БД запрещено: только через API владельца.</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
@@ -3374,22 +3374,22 @@
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
+          <t>Сигнатуры API Биллинга от владельца не получены.</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
+          <t>Данные абонента запрашиваются у Биллинга в момент вопроса (предрасчёта нет, решение 25.09.2026).</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>REST API Диспетчерской.</t>
+          <t>XML-RPC API Биллинга.</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
+          <t>Единственный способ доступа к Биллингу; данные нужны онлайн, а не с отставанием предрасчёта.</t>
         </is>
       </c>
       <c r="M30" s="20" t="n">
@@ -3415,7 +3415,7 @@
       <c r="U30" s="15" t="n"/>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-400; ADR-600</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3430,57 +3430,65 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ LLM Gateway</t>
+          <t>Backend ↔ Диспетчерская</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Backend; LLM Gateway</t>
+          <t>Backend; Сервис работы с обращениями; Диспетчерская (внешняя)</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
+          <t>REST API Диспетчерской; на прототипе — локальные данные графика отключений</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Вызов внутри одного процесса.</t>
+          <t>Данные графика плановых отключений (1939 записей) читаются локально; запись аварийной заявки — заглушка.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
+          <t>Прямой доступ к чужой БД запрещён.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
+          <t>ADR-400, раздел «Сравнение вариантов по слоям безопасности», подраздел «Как выбран способ доступа к внешним системам»</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Сигнатуры REST API Диспетчерской от владельца не получены.</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
+          <t>Чтение статуса аварийной заявки и зоны по API; запись аварийной заявки после подтверждения абонента.</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>HTTP внутри кластера.</t>
+          <t>REST API Диспетчерской.</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
-        </is>
-      </c>
-      <c r="M31" s="19" t="n"/>
-      <c r="N31" s="19" t="n"/>
-      <c r="O31" s="9" t="n"/>
+          <t>Единственный разрешённый путь; аварии должны попадать сразу в диспетчерскую.</t>
+        </is>
+      </c>
+      <c r="M31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="P31" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
@@ -3493,7 +3501,7 @@
       <c r="U31" s="15" t="n"/>
       <c r="V31" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3508,52 +3516,52 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Backend ↔ Qdrant</t>
+          <t>Backend ↔ LLM Gateway</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Backend; Qdrant</t>
+          <t>Backend; LLM Gateway</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client по HTTP (порт 6333)</t>
+          <t>Вызов функции Python в одном процессе; на MVP — HTTP, OpenAI-совместимый протокол</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>gRPC (порт 6334) по умолчанию с 24.09.2026, REST (порт 6333) — переключатель QDRANT_PREFER_GRPC=false; запись — отдельным сервисом, Backend только читает готовый индекс. Без TLS и без ключа API. Лимит выдачи: до 300 точек — все точки, выше — top_k × 10.</t>
+          <t>Вызов внутри одного процесса.</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Клиент по gRPC (с 24.09.2026), а не по REST: замер — gRPC стабильно 6–13 мс, REST через qdrant-client от 6 до 60 мс (топ-20 с payload: 60 мс); прежний довод «HTTP — единицы миллисекунд» не подтвердился. На прототипе (190 точек) REST быстрее (13 против 26 мс). Один хост, Windows; повторить в кластере.</t>
+          <t>Вынос шлюза в отдельный контейнер — следствие целевой схемы развёртывания (C4_Deployment.html); формат конфигурации LiteLLM совместим с прокси, поэтому вынос не требует переписывания.</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
+          <t>ADR-200, раздел «LLM-хостинг», подраздел «Как устроен шлюз к модели»</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>Разброс REST не объяснён. Граница точного перебора (300 точек) и PARTS_HEADROOM (10) выбраны по синтетическому замеру (ADR-200, «Значения допущений хранилища»); на реальном корпусе не проверялись. Трафик внутри кластера без TLS и без ключа — решение за ИБ. Замер сделан не на платформе кластера владельца.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>gRPC-клиент (сделан на прототипе, 0,5–1 чел-дн, оценка автора); ограниченный лимит выдачи; повторить замер REST и gRPC в кластере владельца, перепроверить PARTS_HEADROOM и границу точного перебора на реальном корпусе, проверить порт 6334 и NetworkPolicy — в пределах теста моделей эмбеддингов.</t>
+          <t>Вызов по сети между контейнерами; OpenAI-совместимый протокол.</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client по gRPC (prefer_grpc, порт 6334).</t>
+          <t>HTTP внутри кластера.</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>Стабильные 6–13 мс вместо разброса 6–60 мс; на объёме MVP P99 вдвое ниже (топ-100 с payload: 19,5 против 40,1 мс).</t>
+          <t>Следствие выноса шлюза в отдельный контейнер (см. строку LLM Gateway).</t>
         </is>
       </c>
       <c r="M32" s="19" t="n"/>
@@ -3571,7 +3579,7 @@
       <c r="U32" s="15" t="n"/>
       <c r="V32" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-400; ADR-600</t>
+          <t>ADR-200</t>
         </is>
       </c>
     </row>
@@ -3586,78 +3594,70 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>LLM Gateway ↔ LLM Provider</t>
+          <t>Backend ↔ Qdrant</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>LLM Gateway; внешний LLM Provider</t>
+          <t>Backend; Qdrant</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
+          <t>qdrant-client по HTTP (порт 6333)</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
+          <t>gRPC (порт 6334) по умолчанию с 24.09.2026, REST (порт 6333) — переключатель QDRANT_PREFER_GRPC=false; запись — отдельным сервисом, Backend только читает готовый индекс. Без TLS и без ключа API. Лимит выдачи: до 300 точек — все точки, выше — top_k × 10.</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
+          <t>Клиент по gRPC (с 24.09.2026), а не по REST: замер — gRPC стабильно 6–13 мс, REST через qdrant-client от 6 до 60 мс (топ-20 с payload: 60 мс); прежний довод «HTTP — единицы миллисекунд» не подтвердился. На прототипе (190 точек) REST быстрее (13 против 26 мс). Один хост, Windows; повторить в кластере.</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (клиент по HTTP, а не gRPC)</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
+          <t>Разброс REST не объяснён. Граница точного перебора (300 точек) и PARTS_HEADROOM (10) выбраны по синтетическому замеру (ADR-200, «Значения допущений хранилища»); на реальном корпусе не проверялись. Трафик внутри кластера без TLS и без ключа — решение за ИБ. Замер сделан не на платформе кластера владельца.</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
+          <t>gRPC-клиент (сделан на прототипе, 0,5–1 чел-дн, оценка автора); ограниченный лимит выдачи; повторить замер REST и gRPC в кластере владельца, перепроверить PARTS_HEADROOM и границу точного перебора на реальном корпусе, проверить порт 6334 и NetworkPolicy — в пределах теста моделей эмбеддингов.</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>HTTPS, сертификаты НУЦ Минцифры.</t>
+          <t>qdrant-client по gRPC (prefer_grpc, порт 6334).</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
+          <t>Стабильные 6–13 мс вместо разброса 6–60 мс; на объёме MVP P99 вдвое ниже (топ-100 с payload: 19,5 против 40,1 мс).</t>
         </is>
       </c>
       <c r="M33" s="19" t="n"/>
       <c r="N33" s="19" t="n"/>
       <c r="O33" s="9" t="n"/>
-      <c r="P33" s="9" t="inlineStr">
-        <is>
-          <t>Вызов собственной модели внутри закрытого контура.</t>
-        </is>
-      </c>
-      <c r="Q33" s="9" t="inlineStr">
-        <is>
-          <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
-        </is>
-      </c>
-      <c r="R33" s="9" t="inlineStr">
-        <is>
-          <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
-        </is>
-      </c>
-      <c r="S33" s="19" t="n"/>
-      <c r="T33" s="19" t="n"/>
-      <c r="U33" s="9" t="n"/>
+      <c r="P33" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q33" s="15" t="n"/>
+      <c r="R33" s="15" t="n"/>
+      <c r="S33" s="16" t="n"/>
+      <c r="T33" s="16" t="n"/>
+      <c r="U33" s="15" t="n"/>
       <c r="V33" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-300</t>
+          <t>ADR-200; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3672,66 +3672,78 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Индексация → Qdrant</t>
+          <t>LLM Gateway ↔ LLM Provider</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>ETL индексации; Qdrant</t>
+          <t>LLM Gateway; внешний LLM Provider</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
+          <t>HTTPS с проверкой сертификата; LiteLLM (OpenAI-совместимый интерфейс)</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
+          <t>HTTPS с проверкой сертификата: YandexGPT (сертификаты доступны). Проверка TLS не отключается никогда.</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
+          <t>Отключить проверку сертификата ради GigaChat отклонено — по каналу идут данные абонента; вместо этого переключаемся на другого провайдера.</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
+          <t>ADR-400, раздел «Закрыто сейчас» (TLS не отключается); ADR-300, раздел 4</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="K34" s="15" t="n"/>
-      <c r="L34" s="15" t="inlineStr">
-        <is>
-          <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
-        </is>
-      </c>
-      <c r="M34" s="16" t="n"/>
-      <c r="N34" s="16" t="n"/>
-      <c r="O34" s="15" t="n"/>
-      <c r="P34" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q34" s="15" t="n"/>
-      <c r="R34" s="15" t="n"/>
-      <c r="S34" s="16" t="n"/>
-      <c r="T34" s="16" t="n"/>
-      <c r="U34" s="15" t="n"/>
+          <t>Для GigaChat нужны корневые сертификаты НУЦ Минцифры — на машине прототипа их нет.</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Канал к GigaChat с корневыми сертификатами НУЦ в образе шлюза; автопереключение на резерв.</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>HTTPS, сертификаты НУЦ Минцифры.</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>Основной провайдер MVP — GigaChat Pro (входит в работу по строке LLM Provider).</t>
+        </is>
+      </c>
+      <c r="M34" s="19" t="n"/>
+      <c r="N34" s="19" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="inlineStr">
+        <is>
+          <t>Вызов собственной модели внутри закрытого контура.</t>
+        </is>
+      </c>
+      <c r="Q34" s="9" t="inlineStr">
+        <is>
+          <t>OpenAI-совместимый интерфейс vLLM внутри сети водоканала.</t>
+        </is>
+      </c>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>Данные не покидают периметр вообще, а не только территорию РФ.</t>
+        </is>
+      </c>
+      <c r="S34" s="19" t="n"/>
+      <c r="T34" s="19" t="n"/>
+      <c r="U34" s="9" t="n"/>
       <c r="V34" s="9" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-400; ADR-300</t>
         </is>
       </c>
     </row>
@@ -3739,89 +3751,73 @@
       <c r="A35" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Сквозная работа</t>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Связь</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Смета CAPEX/OPEX, NFR, допущения о нагрузке</t>
+          <t>Индексация → Qdrant</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
+          <t>ETL индексации; Qdrant</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
+          <t>qdrant-client: upsert в новую коллекцию + переключение алиаса (blue-green)</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 234–101 280 ₽ в месяц, на тираже 3 305 ₽–1,07 млн ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
+          <t>Запись в новую физическую коллекцию и атомарное переключение алиаса (blue-green); удалённые документы уходят при полной пересборке.</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии.</t>
+          <t>Blue-green против обновления на месте: обновление на месте оставляет интервалы с неполным индексом; цена blue-green — двойное хранение на время сборки.</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
+          <t>ADR-200, раздел «Сравнение вариантов по слоям», подраздел «Почему Qdrant, а не другая векторная база» (blue-green, а не обновление на месте)</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>Разброс стоимости токенов на MVP — ×82 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой. Первый пересчёт сметы по данным обращений и ЛК (3–5 чел-дн, после получения данных) и повторный по пилоту (1–2 чел-дн): подставить данные в лист «Прогноз стоимости», пересчитать нагрузку, стоимость и sizing, обновить отчёт о мощности, ADR-500 и матрицу.</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>Без этого нельзя защищать бюджет.</t>
-        </is>
-      </c>
-      <c r="M35" s="25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N35" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="O35" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: P0</t>
-        </is>
-      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K35" s="15" t="n"/>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <t>Механизм переносится как есть; окно 02:00–05:00 описано в строке про индексацию.</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="n"/>
+      <c r="N35" s="16" t="n"/>
+      <c r="O35" s="15" t="n"/>
       <c r="P35" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
       <c r="Q35" s="15" t="n"/>
-      <c r="R35" s="15" t="inlineStr">
-        <is>
-          <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
-        </is>
-      </c>
+      <c r="R35" s="15" t="n"/>
       <c r="S35" s="16" t="n"/>
       <c r="T35" s="16" t="n"/>
       <c r="U35" s="15" t="n"/>
       <c r="V35" s="9" t="inlineStr">
         <is>
-          <t>ADR-500; ADR-600</t>
+          <t>ADR-200</t>
         </is>
       </c>
     </row>
@@ -3836,22 +3832,22 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Внедрение ответов владельцев данных</t>
+          <t>Смета CAPEX/OPEX, NFR, допущения о нагрузке</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
+          <t>Все (сквозная работа); GPU-пул и кластер — как предмет сметы</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Справочники и тексты в коде и данных; не технология</t>
+          <t>Расчётные таблицы (Capacity_Report.html), формулы sizing</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки.</t>
+          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 234–101 280 ₽ в месяц, на тираже 3 305 ₽–1,07 млн ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -3861,17 +3857,17 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
+          <t>Не применимо: это работа, а не выбор технологии; расчёт — Capacity_Report.html, стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Календарный срок определяет владелец, не команда.</t>
+          <t>Разброс стоимости токенов на MVP — ×82 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Внедрение полученных ответов в справочники и тексты.</t>
+          <t>Смета по ценам поставщика, расчёт NFR под конкретную GPU-конфигурацию, подтверждение допущений статистикой. Первый пересчёт сметы по данным обращений и ЛК (3–5 чел-дн, после получения данных) и повторный по пилоту (1–2 чел-дн): подставить данные в лист «Прогноз стоимости», пересчитать нагрузку, стоимость и sizing, обновить отчёт о мощности, ADR-500 и матрицу.</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -3881,18 +3877,18 @@
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>Разработки не требуют — требуют ответа от водоканала.</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="n">
-        <v>4</v>
+          <t>Без этого нельзя защищать бюджет.</t>
+        </is>
+      </c>
+      <c r="M36" s="25" t="n">
+        <v>11.5</v>
       </c>
       <c r="N36" s="17" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O36" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Согласования</t>
+          <t>Из блока ADR-600: P0</t>
         </is>
       </c>
       <c r="P36" s="14" t="inlineStr">
@@ -3901,13 +3897,17 @@
         </is>
       </c>
       <c r="Q36" s="15" t="n"/>
-      <c r="R36" s="15" t="n"/>
+      <c r="R36" s="15" t="inlineStr">
+        <is>
+          <t>Пересчёт NFR под 90 000 абонентов уже сделан.</t>
+        </is>
+      </c>
       <c r="S36" s="16" t="n"/>
       <c r="T36" s="16" t="n"/>
       <c r="U36" s="15" t="n"/>
       <c r="V36" s="9" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -3922,22 +3922,22 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Документация и согласование ИБ</t>
+          <t>Внедрение ответов владельцев данных</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Все (сквозная работа)</t>
+          <t>Backend (Triage, ответчики); Document Generator; Сервис работы с обращениями</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Документы и диаграммы пакета сдачи</t>
+          <t>Справочники и тексты в коде и данных; не технология</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
+          <t>Пункты, ждущие ответа водоканала: коды типов обращений, текст о качестве воды, четыре процесса вне справочника, настоящие бланки (сами бланки теперь через сервис шаблонов — отдельная строка; здесь остаётся ответ владельца о формате, месте и приложениях).</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
+          <t>Не применимо: это работа, а не выбор технологии; перечень пунктов — ADR-600, раздел «Ждут ответа владельцев систем»</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>Календарный срок определяет служба ИБ водоканала.</t>
+          <t>Календарный срок определяет владелец, не команда.</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
+          <t>Внедрение полученных ответов в справочники и тексты.</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
@@ -3967,41 +3967,33 @@
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
+          <t>Разработки не требуют — требуют ответа от водоканала.</t>
         </is>
       </c>
       <c r="M37" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="N37" s="25" t="n">
-        <v>7.5</v>
+        <v>4</v>
+      </c>
+      <c r="N37" s="17" t="n">
+        <v>8</v>
       </c>
       <c r="O37" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Документация и ИБ</t>
-        </is>
-      </c>
-      <c r="P37" s="9" t="inlineStr">
-        <is>
-          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
-        </is>
-      </c>
-      <c r="Q37" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R37" s="9" t="inlineStr">
-        <is>
-          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
-        </is>
-      </c>
-      <c r="S37" s="19" t="n"/>
-      <c r="T37" s="19" t="n"/>
-      <c r="U37" s="9" t="n"/>
+          <t>Из блока ADR-600: Согласования</t>
+        </is>
+      </c>
+      <c r="P37" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q37" s="15" t="n"/>
+      <c r="R37" s="15" t="n"/>
+      <c r="S37" s="16" t="n"/>
+      <c r="T37" s="16" t="n"/>
+      <c r="U37" s="15" t="n"/>
       <c r="V37" s="9" t="inlineStr">
         <is>
-          <t>ADR-400; ADR-600</t>
+          <t>ADR-600</t>
         </is>
       </c>
     </row>
@@ -4016,78 +4008,86 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>GPU-узел в кластере владельца (решение после проверки на реальных данных)</t>
+          <t>Документация и согласование ИБ</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes-кластер владельца (новый GPU-узел); embedding-inference; reranker-inference; ETL индексации</t>
+          <t>Все (сквозная работа)</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты</t>
+          <t>Документы и диаграммы пакета сдачи</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>В кластере, где работает личный кабинет и где размещается наш контур, GPU-узлов нет (решение заказчика проекта, 24.09.2026). Без них MVP на CPU: эмбеддинги e5-small (36–37 мс на запрос), реранкер выключен, индексация считает эмбеддинги на CPU.</t>
+          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7,2 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Владелец примет решение о GPU-узле только после проверки на реальных данных (24.09.2026): тест моделей идёт на CPU, скорость на GPU — коротким замером на временной видеокарте (ADR-200, «Почему Kubernetes», ADR-600).</t>
+          <t>Не применимо: это работа, а не выбор технологии.</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Почему Kubernetes, а не другая оркестрация» (пункт «GPU»); ADR-300, раздел 2; ADR-600, «GPU-узел в кластере владельца — решение после проверки на реальных данных»</t>
+          <t>Не применимо: это работа, а не выбор технологии; состав — ADR-600, раздел «Документация и согласование ИБ»</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>Цена и сроки закупки сервера не оценены; скорость моделей на GPU не измерялась; отдел владельца GPU не эксплуатировал.</t>
+          <t>Календарный срок определяет служба ИБ водоканала.</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны заказчиком проекта 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); Б — доля ответов, оценённых экспертом как верные и полезные, не ниже 80% на подвыборке не менее 200 (рабочее значение автора); В — пустых выдач из-за реранкера (пуста при «реранкер → порог», но не пуста без реранкера) не более 3% вопросов с ответом в базе (рабочее значение автора, только для реранкера; порядок «порог → реранкер» проходит по построению); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А, Б или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
+          <t>Полная сверка диаграмм с кодом, нагрузочные и security-сценарии, резюме для CTO.</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>Тест BGE-M3 и реранкеров остаётся в плане при любом исходе: он и даёт основание для решения. Строка отражает работы на случай покупки и в итог сметы не входит.</t>
-        </is>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" s="12" t="n">
+          <t>Условие перехода к Этапу 2 — согласование ИБ (ADR-100/600).</t>
+        </is>
+      </c>
+      <c r="M38" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="O38" s="13" t="inlineStr">
-        <is>
-          <t>По триггеру (решение владельца после проверки на реальных данных; оценка автора)</t>
-        </is>
-      </c>
-      <c r="P38" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q38" s="15" t="n"/>
-      <c r="R38" s="15" t="n"/>
-      <c r="S38" s="16" t="n"/>
-      <c r="T38" s="16" t="n"/>
-      <c r="U38" s="15" t="n"/>
+      <c r="N38" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O38" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Документация и ИБ</t>
+        </is>
+      </c>
+      <c r="P38" s="9" t="inlineStr">
+        <is>
+          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
+        </is>
+      </c>
+      <c r="Q38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
+        </is>
+      </c>
+      <c r="S38" s="19" t="n"/>
+      <c r="T38" s="19" t="n"/>
+      <c r="U38" s="9" t="n"/>
       <c r="V38" s="9" t="inlineStr">
         <is>
-          <t>ADR-200; ADR-300; ADR-500; ADR-600</t>
+          <t>ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
@@ -4102,78 +4102,78 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Выбор семейства собственной модели и закупка GPU</t>
+          <t>GPU-узел в кластере владельца (решение после проверки на реальных данных)</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
+          <t>Kubernetes-кластер владельца (новый GPU-узел); embedding-inference; reranker-inference; ETL индексации</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
+          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
+          <t>В кластере, где работает личный кабинет и где размещается наш контур, GPU-узлов нет (решение заказчика проекта, 24.09.2026). Без них MVP на CPU: эмбеддинги e5-small (36–37 мс на запрос), реранкер выключен, индексация считает эмбеддинги на CPU.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
+          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7,2 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Владелец примет решение о GPU-узле только после проверки на реальных данных (24.09.2026): тест моделей идёт на CPU, скорость на GPU — коротким замером на временной видеокарте (ADR-200, «Почему Kubernetes», ADR-600).</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
+          <t>ADR-200, подраздел «Почему Kubernetes, а не другая оркестрация» (пункт «GPU»); ADR-300, раздел 2; ADR-600, «GPU-узел в кластере владельца — решение после проверки на реальных данных»</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
+          <t>Цена и сроки закупки сервера не оценены; скорость моделей на GPU не измерялась; отдел владельца GPU не эксплуатировал.</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны заказчиком проекта 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); Б — доля ответов, оценённых экспертом как верные и полезные, не ниже 80% на подвыборке не менее 200 (рабочее значение автора); В — пустых выдач из-за реранкера (пуста при «реранкер → порог», но не пуста без реранкера) не более 3% вопросов с ответом в базе (рабочее значение автора, только для реранкера; порядок «порог → реранкер» проходит по построению); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А, Б или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>Kubernetes: плагин устройств GPU, метки узлов и taints; драйвер видеокарты.</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>Тест BGE-M3 и реранкеров остаётся в плане при любом исходе: он и даёт основание для решения. Строка отражает работы на случай покупки и в итог сметы не входит.</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" s="13" t="inlineStr">
+        <is>
+          <t>По триггеру (решение владельца после проверки на реальных данных; оценка автора)</t>
+        </is>
+      </c>
+      <c r="P39" s="14" t="inlineStr">
         <is>
           <t>Без изменений</t>
         </is>
       </c>
-      <c r="K39" s="15" t="n"/>
-      <c r="L39" s="15" t="n"/>
-      <c r="M39" s="16" t="n"/>
-      <c r="N39" s="16" t="n"/>
-      <c r="O39" s="15" t="n"/>
-      <c r="P39" s="9" t="inlineStr">
-        <is>
-          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
-        </is>
-      </c>
-      <c r="Q39" s="9" t="inlineStr">
-        <is>
-          <t>Qwen2.5-32B INT4, vLLM.</t>
-        </is>
-      </c>
-      <c r="R39" s="9" t="inlineStr">
-        <is>
-          <t>Аренда исключена не по цене, а по триггеру (речь о собственной модели генерации; для проверки эмбеддингов и реранкера на MVP аренда на месяц допустима): облачный GPU считается внешним сервисом.</t>
-        </is>
-      </c>
-      <c r="S39" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U39" s="21" t="inlineStr">
-        <is>
-          <t>ADR-600</t>
-        </is>
-      </c>
+      <c r="Q39" s="15" t="n"/>
+      <c r="R39" s="15" t="n"/>
+      <c r="S39" s="16" t="n"/>
+      <c r="T39" s="16" t="n"/>
+      <c r="U39" s="15" t="n"/>
       <c r="V39" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-500; ADR-600</t>
+          <t>ADR-200; ADR-300; ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -4188,85 +4188,69 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
+          <t>Выбор семейства собственной модели и закупка GPU</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
+          <t>LLM Provider (собственная модель, тираж); LLM Gateway; GPU-пул</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
+          <t>Qwen2.5-32B INT4; vLLM; 1× GPU A100 80 ГБ</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
+          <t>Выбор Qwen2.5 сделан по репутации, на эталонном наборе не проверен.</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
+          <t>Qwen2.5 (Apache 2.0, сильный русский, 7B→32B без переделки) против Llama 3.x (русский слабее — по репутации; довод «нет варианта под одну карту A100» не подтверждён: 70B в INT4 тоже поместилась бы на 80 ГБ) и открытых весов GigaChat (менее зрелый инструментарий — по общим сведениям, не проверялось).</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
+          <t>ADR-300, раздел 4, подраздел «Сравнение семейства self-hosted-модели тиража»; стоимость — ADR-500</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки.</t>
-        </is>
-      </c>
-      <c r="K40" s="9" t="inlineStr">
-        <is>
-          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
-        </is>
-      </c>
-      <c r="L40" s="9" t="inlineStr">
-        <is>
-          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
-        </is>
-      </c>
-      <c r="M40" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="N40" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="O40" s="18" t="inlineStr">
-        <is>
-          <t>Из блока ADR-600: Анализ типов на живых данных</t>
-        </is>
-      </c>
+          <t>Закупка оборудования — недели или месяцы, это снабжение, не разработка.</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="K40" s="15" t="n"/>
+      <c r="L40" s="15" t="n"/>
+      <c r="M40" s="16" t="n"/>
+      <c r="N40" s="16" t="n"/>
+      <c r="O40" s="15" t="n"/>
       <c r="P40" s="9" t="inlineStr">
         <is>
-          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
+          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
         </is>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
-          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
+          <t>Qwen2.5-32B INT4, vLLM.</t>
         </is>
       </c>
       <c r="R40" s="9" t="inlineStr">
         <is>
-          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
+          <t>Аренда исключена не по цене, а по триггеру (речь о собственной модели генерации; для проверки эмбеддингов и реранкера на MVP аренда на месяц допустима): облачный GPU считается внешним сервисом.</t>
         </is>
       </c>
       <c r="S40" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U40" s="21" t="inlineStr">
         <is>
@@ -4275,7 +4259,7 @@
       </c>
       <c r="V40" s="9" t="inlineStr">
         <is>
-          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
+          <t>ADR-300; ADR-500; ADR-600</t>
         </is>
       </c>
     </row>
@@ -4290,78 +4274,94 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
+          <t>Анализ всех типов обращений на живых данных и повторный выбор моделей</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Backend (оркестратор, детектор намерений); LLM Gateway (охранитель, правило в промпте); Session State Store; виджет (кнопки нескольких обращений)</t>
+          <t>Backend (Triage, ответчики); embedding-inference; reranker-inference; Qdrant (переиндексация при смене модели); LLM Gateway (пороги)</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>Python; `app/agents/intents.py` (правила на регулярных выражениях); `Orchestrator._stream_parts`; `unperformed_action` в `app/gateway/guardrails.py`; метрика `assistant_multi_intent_total`</t>
+          <t>Скрипты замера (`scripts/`), `golden_set/`, PII Filter; результат — Inquiry_Types.xlsx</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>На прототипе реализовано: детектор намерений разбирает реплику на задачи правилами (`app/agents/intents.py`), оркестратор отвечает по каждой части, операции без выполнения получают прямой отказ, условие «если долга нет» проверяется по Биллингу; ложное «сделал» блокируется правилом в промпте и в охранителе (`unperformed_action`). Тесты: 22 + 16 + 8. Измерение на выгрузке обращений (`scripts/measure_intents.py`): несколько задач в 1 из 136 текстов (0,7%) — срабатывание детектора, не разметка людьми.</t>
+          <t>Замер на 136 настоящих обращениях (по 9 текстов на тип; `Inquiry_Types.xlsx`): слова подбирались на тех же текстах, на отложенной трети охват 75%, точность 65%. Модели выбраны по репутации и замеру задержки.</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>Правила, а не модель: модель на каждой реплике стоила бы времени и токенов, а её разбиение нечем проверить. LangGraph реплику на задачи не разбирает — детектор нужен в любом случае (ADR-200, «Как реализовано: несколько задач в одной реплике»).</t>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение моделей входит в её состав.</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Как реализовано: несколько задач в одной реплике» (в разделе «Оркестрация агента»); ADR-100, раздел «Несколько задач в одной реплике»; ADR-400</t>
+          <t>ADR-300, разделы 1–2 (решение); ADR-600, раздел «Анализ типов обращений на живых данных»</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>Предел 300 знаков, перечни глаголов и операций подобраны автором на 136 обращениях регистра, не на репликах чата; точность и полнота на размеченных репликах не измерены. Регистрация только по первой части, из условий проверяется лишь долг, путь `generate` не разбирается, второй бланк перезапишет первый.</t>
+          <t>Метка типа в выгрузке поставлена оператором, знавшим больше, чем написано в тексте; выборка мала; у девяти типов нет запасного k-NN; качество BGE-M3 против e5-small не сравнивалось; пороги k-NN не переносятся на другую модель.</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Проверка детектора на размеченных репликах чата (точность, полнота, подбор предела и перечней); регистрация нескольких обращений из одной реплики (несколько черновиков, подтверждение каждого, виджет); условия помимо долга; путь `generate`, лимиты и порядок частей.</t>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки.</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>Python; правила на регулярных выражениях; метрика `assistant_multi_intent_total`; состояние диалога в Redis.</t>
+          <t>Скрипты замера (`scripts/measure_classifier.py`, `measure_search_models.py`), `golden_set/`, PII Filter; результат — обновлённый `Inquiry_Types.xlsx`.</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — условие перехода на LangGraph (триггер 4).</t>
+          <t>Выбор моделей по репутации нельзя защищать без замера качества на живых данных; смена модели эмбеддингов — самое дорогое решение для отмены (полная переиндексация). Зафиксировано в ADR-300 и ADR-600. Оценка не включает сравнение моделей и расширение классификатора — они учтены в строках «Эмбеддинги» и «Классификатор обращений».</t>
         </is>
       </c>
       <c r="M41" s="17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N41" s="17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O41" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)</t>
-        </is>
-      </c>
-      <c r="P41" s="14" t="inlineStr">
-        <is>
-          <t>Без изменений</t>
-        </is>
-      </c>
-      <c r="Q41" s="15" t="n"/>
-      <c r="R41" s="15" t="n"/>
-      <c r="S41" s="16" t="n"/>
-      <c r="T41" s="16" t="n"/>
-      <c r="U41" s="15" t="n"/>
+          <t>Из блока ADR-600: Анализ типов на живых данных</t>
+        </is>
+      </c>
+      <c r="P41" s="9" t="inlineStr">
+        <is>
+          <t>Повторное решение по моделям для тиража по живой статистике MVP.</t>
+        </is>
+      </c>
+      <c r="Q41" s="9" t="inlineStr">
+        <is>
+          <t>Те же скрипты замера; при смене модели — переиндексация и пересчёт порогов k-NN.</t>
+        </is>
+      </c>
+      <c r="R41" s="9" t="inlineStr">
+        <is>
+          <t>Проверить, что модель MVP годится при нагрузке тиража; при необходимости пересчитать пороги и sizing.</t>
+        </is>
+      </c>
+      <c r="S41" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T41" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" s="21" t="inlineStr">
+        <is>
+          <t>ADR-600</t>
+        </is>
+      </c>
       <c r="V41" s="9" t="inlineStr">
         <is>
-          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
+          <t>ADR-300; ADR-600; Inquiry_Types.xlsx</t>
         </is>
       </c>
     </row>
@@ -4376,63 +4376,63 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
+          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
+          <t>Backend (оркестратор, детектор намерений); LLM Gateway (охранитель, правило в промпте); Session State Store; виджет (кнопки нескольких обращений)</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
+          <t>Python; `app/agents/intents.py` (правила на регулярных выражениях); `Orchestrator._stream_parts`; `unperformed_action` в `app/gateway/guardrails.py`; метрика `assistant_multi_intent_total`</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
+          <t>На прототипе реализовано: детектор намерений разбирает реплику на задачи правилами (`app/agents/intents.py`), оркестратор отвечает по каждой части, операции без выполнения получают прямой отказ, условие «если долга нет» проверяется по Биллингу; ложное «сделал» блокируется правилом в промпте и в охранителе (`unperformed_action`). Тесты: 22 + 16 + 8. Измерение на выгрузке обращений (`scripts/measure_intents.py`): несколько задач в 1 из 136 текстов (0,7%) — срабатывание детектора, не разметка людьми.</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
+          <t>Правила, а не модель: модель на каждой реплике стоила бы времени и токенов, а её разбиение нечем проверить. LangGraph реплику на задачи не разбирает — детектор нужен в любом случае (ADR-200, «Как реализовано: несколько задач в одной реплике»).</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
+          <t>ADR-200, подраздел «Как реализовано: несколько задач в одной реплике» (в разделе «Оркестрация агента»); ADR-100, раздел «Несколько задач в одной реплике»; ADR-400</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
+          <t>Предел 300 знаков, перечни глаголов и операций подобраны автором на 136 обращениях регистра, не на репликах чата; точность и полнота на размеченных репликах не измерены. Регистрация только по первой части, из условий проверяется лишь долг, путь `generate` не разбирается, второй бланк перезапишет первый.</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>1) Проверка работоспособности Guardrails на живых вопросах — не менее 200 из единой выборки 300–400 (общей с тестами эмбеддингов и реранкера; ответы этого прогона без реранкера — базовая линия критерия Б): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
+          <t>Проверка детектора на размеченных репликах чата (точность, полнота, подбор предела и перечней); регистрация нескольких обращений из одной реплики (несколько черновиков, подтверждение каждого, виджет); условия помимо долга; путь `generate`, лимиты и порядок частей.</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
+          <t>Python; правила на регулярных выражениях; метрика `assistant_multi_intent_total`; состояние диалога в Redis.</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
+          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — условие перехода на LangGraph (триггер 4).</t>
         </is>
       </c>
       <c r="M42" s="17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N42" s="17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O42" s="18" t="inlineStr">
         <is>
-          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
+          <t>Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)</t>
         </is>
       </c>
       <c r="P42" s="14" t="inlineStr">
@@ -4447,51 +4447,137 @@
       <c r="U42" s="15" t="n"/>
       <c r="V42" s="9" t="inlineStr">
         <is>
+          <t>ADR-100; ADR-200; ADR-400; ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Сквозная работа</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Проверка на живых данных: Guardrails и выбор провайдера (YandexGPT, GigaChat)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>LLM Gateway; Guardrails; LLM Provider (YandexGPT, GigaChat); Backend; PII Filter</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Проверки Guardrails и выбор провайдеров сделаны без живых вопросов и ответов: на прототипе работает YandexGPT (и локальная модель для тестов), GigaChat недоступен.</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Не применимо: это работа, а не выбор технологии; сравнение YandexGPT и GigaChat на живых данных — её содержание.</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>ADR-300, раздел 4 (провайдеры, «Выбор провайдера для MVP предварительный»); ADR-400, «Проверка работоспособности Guardrails на живых данных»; ADR-600, раздел «Проверка Guardrails и выбор провайдера на живых данных»</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Неизвестны частота ложных блокировок и пропусков Guardrails на живых ответах; неизвестно, какой из двух провайдеров лучше на вопросах абонентов и кто из них должен быть запасным.</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>1) Проверка работоспособности Guardrails на живых вопросах — не менее 200 из единой выборки 300–400 (общей с тестами эмбеддингов и реранкера; ответы этого прогона без реранкера — базовая линия критерия Б): разметка нарушений, ложные срабатывания и пропуски, правка шаблонов. 2) Тест YandexGPT и GigaChat Pro на той же выборке: качество, время до первого куска и полного ответа, доля блокировок, сбои, стоимость. 3) Решение об основном и запасном провайдере, запись в ADR-300, настройка цепочек переключения.</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>Скрипты замера (`scripts/run_quality_eval.py`, `scripts/check_yandex.py`), судья качества, метрики Prometheus, LiteLLM Router (цепочки переключения), PII Filter; результат — решение в ADR-300 и конфигурация.</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>Без живых данных нельзя обосновать ни пороги проверок ответа, ни выбор основного и запасного провайдера. Настройка GigaChat (сертификаты НУЦ, ключ) учтена в строке «LLM Provider» и сюда не входит. Сюда же входит оптимизация синхронной проверки: проверять новый кусок с перекрытием, а не весь накопленный текст, и замер на ответах 500–3 000 знаков (1–2 чел-дн).</t>
+        </is>
+      </c>
+      <c r="M43" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N43" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="O43" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных</t>
+        </is>
+      </c>
+      <c r="P43" s="14" t="inlineStr">
+        <is>
+          <t>Без изменений</t>
+        </is>
+      </c>
+      <c r="Q43" s="15" t="n"/>
+      <c r="R43" s="15" t="n"/>
+      <c r="S43" s="16" t="n"/>
+      <c r="T43" s="16" t="n"/>
+      <c r="U43" s="15" t="n"/>
+      <c r="V43" s="9" t="inlineStr">
+        <is>
           <t>ADR-300; ADR-400; ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="C44" s="26" t="inlineStr">
+    <row r="45">
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t>Цвет ячеек с оценкой:</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="28" t="inlineStr">
+    <row r="46">
+      <c r="C46" s="27" t="n"/>
+      <c r="D46" s="28" t="inlineStr">
         <is>
           <t>цифра прямо из ADR-600</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="C46" s="29" t="n"/>
-      <c r="D46" s="28" t="inlineStr">
+    <row r="47">
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="28" t="inlineStr">
         <is>
           <t>цифра блока ADR-600 (или его доля, распределённая автором) — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="28" t="inlineStr">
+    <row r="48">
+      <c r="C48" s="30" t="n"/>
+      <c r="D48" s="28" t="inlineStr">
         <is>
           <t>в ADR-600 нет, оценка автора — подтвердить</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="C48" s="31" t="n"/>
-      <c r="D48" s="28" t="inlineStr">
+    <row r="49">
+      <c r="C49" s="31" t="n"/>
+      <c r="D49" s="28" t="inlineStr">
         <is>
           <t>изменений на этом этапе нет</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V42"/>
+  <autoFilter ref="A2:V43"/>
   <mergeCells count="4">
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
@@ -4613,11 +4699,11 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>SUM('Матрица'!$M$3:$M$42)-SUMIF('Матрица'!$O$3:$O$42,"По триггеру*",'Матрица'!$M$3:$M$42)</f>
+        <f>SUM('Матрица'!$M$3:$M$43)-SUMIF('Матрица'!$O$3:$O$43,"По триггеру*",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="C5" s="34">
-        <f>SUM('Матрица'!$N$3:$N$42)-SUMIF('Матрица'!$O$3:$O$42,"По триггеру*",'Матрица'!$N$3:$N$42)</f>
+        <f>SUM('Матрица'!$N$3:$N$43)-SUMIF('Матрица'!$O$3:$O$43,"По триггеру*",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="D5" s="34">
@@ -4629,35 +4715,35 @@
         <v/>
       </c>
       <c r="F5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"ADR-600",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"ADR-600",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="G5" s="35">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"ADR-600",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"ADR-600",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="H5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока*",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока*",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="I5" s="36">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока*",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока*",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="J5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Оценка автора",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Оценка автора",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="K5" s="37">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Оценка автора",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Оценка автора",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="L5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"По триггеру*",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"По триггеру*",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="M5" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"По триггеру*",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"По триггеру*",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
     </row>
@@ -4668,11 +4754,11 @@
         </is>
       </c>
       <c r="B6" s="34">
-        <f>SUM('Матрица'!$S$3:$S$42)-SUMIF('Матрица'!$U$3:$U$42,"По триггеру*",'Матрица'!$S$3:$S$42)</f>
+        <f>SUM('Матрица'!$S$3:$S$43)-SUMIF('Матрица'!$U$3:$U$43,"По триггеру*",'Матрица'!$S$3:$S$43)</f>
         <v/>
       </c>
       <c r="C6" s="34">
-        <f>SUM('Матрица'!$T$3:$T$42)-SUMIF('Матрица'!$U$3:$U$42,"По триггеру*",'Матрица'!$T$3:$T$42)</f>
+        <f>SUM('Матрица'!$T$3:$T$43)-SUMIF('Матрица'!$U$3:$U$43,"По триггеру*",'Матрица'!$T$3:$T$43)</f>
         <v/>
       </c>
       <c r="D6" s="34">
@@ -4684,35 +4770,35 @@
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$42,"ADR-600",'Матрица'!$S$3:$S$42)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$43,"ADR-600",'Матрица'!$S$3:$S$43)</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>SUMIF('Матрица'!$U$3:$U$42,"ADR-600",'Матрица'!$T$3:$T$42)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$43,"ADR-600",'Матрица'!$T$3:$T$43)</f>
         <v/>
       </c>
       <c r="H6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$42,"Из блока*",'Матрица'!$S$3:$S$42)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$43,"Из блока*",'Матрица'!$S$3:$S$43)</f>
         <v/>
       </c>
       <c r="I6" s="36">
-        <f>SUMIF('Матрица'!$U$3:$U$42,"Из блока*",'Матрица'!$T$3:$T$42)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$43,"Из блока*",'Матрица'!$T$3:$T$43)</f>
         <v/>
       </c>
       <c r="J6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$42,"Оценка автора",'Матрица'!$S$3:$S$42)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$43,"Оценка автора",'Матрица'!$S$3:$S$43)</f>
         <v/>
       </c>
       <c r="K6" s="37">
-        <f>SUMIF('Матрица'!$U$3:$U$42,"Оценка автора",'Матрица'!$T$3:$T$42)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$43,"Оценка автора",'Матрица'!$T$3:$T$43)</f>
         <v/>
       </c>
       <c r="L6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$42,"По триггеру*",'Матрица'!$S$3:$S$42)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$43,"По триггеру*",'Матрица'!$S$3:$S$43)</f>
         <v/>
       </c>
       <c r="M6" s="34">
-        <f>SUMIF('Матрица'!$U$3:$U$42,"По триггеру*",'Матрица'!$T$3:$T$42)</f>
+        <f>SUMIF('Матрица'!$U$3:$U$43,"По триггеру*",'Матрица'!$T$3:$T$43)</f>
         <v/>
       </c>
     </row>
@@ -4879,11 +4965,11 @@
         <v>17</v>
       </c>
       <c r="D15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: P0",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E15" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: P0",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F15" s="44">
@@ -4909,11 +4995,11 @@
         <v>8</v>
       </c>
       <c r="D16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Согласования",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E16" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Согласования",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F16" s="44">
@@ -4939,11 +5025,11 @@
         <v>56</v>
       </c>
       <c r="D17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E17" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Качество поиска и классификации",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F17" s="44">
@@ -4969,11 +5055,11 @@
         <v>30</v>
       </c>
       <c r="D18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E18" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Основная разработка Этапа 2",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F18" s="44">
@@ -4999,11 +5085,11 @@
         <v>7.5</v>
       </c>
       <c r="D19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F19" s="44">
@@ -5029,11 +5115,11 @@
         <v>19</v>
       </c>
       <c r="D20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F20" s="44">
@@ -5059,11 +5145,11 @@
         <v>14</v>
       </c>
       <c r="D21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F21" s="44">
@@ -5089,11 +5175,11 @@
         <v>18</v>
       </c>
       <c r="D22" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E22" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$42,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$42)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F22" s="44">
@@ -5392,7 +5478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6235,11 +6321,11 @@
     </row>
     <row r="38">
       <c r="A38" s="9">
-        <f>'Матрица'!A26</f>
+        <f>'Матрица'!A25</f>
         <v/>
       </c>
       <c r="B38" s="9">
-        <f>'Матрица'!C26</f>
+        <f>'Матрица'!C25</f>
         <v/>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -6248,25 +6334,25 @@
         </is>
       </c>
       <c r="D38" s="34">
-        <f>'Матрица'!M26</f>
+        <f>'Матрица'!M25</f>
         <v/>
       </c>
       <c r="E38" s="34">
-        <f>'Матрица'!N26</f>
+        <f>'Матрица'!N25</f>
         <v/>
       </c>
       <c r="F38" s="13">
-        <f>'Матрица'!O26</f>
+        <f>'Матрица'!O25</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9">
-        <f>'Матрица'!A28</f>
+        <f>'Матрица'!A27</f>
         <v/>
       </c>
       <c r="B39" s="9">
-        <f>'Матрица'!C28</f>
+        <f>'Матрица'!C27</f>
         <v/>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -6275,25 +6361,25 @@
         </is>
       </c>
       <c r="D39" s="34">
-        <f>'Матрица'!M28</f>
+        <f>'Матрица'!M27</f>
         <v/>
       </c>
       <c r="E39" s="34">
-        <f>'Матрица'!N28</f>
-        <v/>
-      </c>
-      <c r="F39" s="18">
-        <f>'Матрица'!O28</f>
+        <f>'Матрица'!N27</f>
+        <v/>
+      </c>
+      <c r="F39" s="13">
+        <f>'Матрица'!O27</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9">
-        <f>'Матрица'!A35</f>
+        <f>'Матрица'!A29</f>
         <v/>
       </c>
       <c r="B40" s="9">
-        <f>'Матрица'!C35</f>
+        <f>'Матрица'!C29</f>
         <v/>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -6302,15 +6388,15 @@
         </is>
       </c>
       <c r="D40" s="34">
-        <f>'Матрица'!M35</f>
+        <f>'Матрица'!M29</f>
         <v/>
       </c>
       <c r="E40" s="34">
-        <f>'Матрица'!N35</f>
+        <f>'Матрица'!N29</f>
         <v/>
       </c>
       <c r="F40" s="18">
-        <f>'Матрица'!O35</f>
+        <f>'Матрица'!O29</f>
         <v/>
       </c>
     </row>
@@ -6390,18 +6476,18 @@
         <f>'Матрица'!N38</f>
         <v/>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="18">
         <f>'Матрица'!O38</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9">
-        <f>'Матрица'!A40</f>
+        <f>'Матрица'!A39</f>
         <v/>
       </c>
       <c r="B44" s="9">
-        <f>'Матрица'!C40</f>
+        <f>'Матрица'!C39</f>
         <v/>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -6410,15 +6496,15 @@
         </is>
       </c>
       <c r="D44" s="34">
-        <f>'Матрица'!M40</f>
+        <f>'Матрица'!M39</f>
         <v/>
       </c>
       <c r="E44" s="34">
-        <f>'Матрица'!N40</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
-        <f>'Матрица'!O40</f>
+        <f>'Матрица'!N39</f>
+        <v/>
+      </c>
+      <c r="F44" s="13">
+        <f>'Матрица'!O39</f>
         <v/>
       </c>
     </row>
@@ -6476,104 +6562,131 @@
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="43" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="9">
+        <f>'Матрица'!A43</f>
+        <v/>
+      </c>
+      <c r="B47" s="9">
+        <f>'Матрица'!C43</f>
+        <v/>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D47" s="34">
+        <f>'Матрица'!M43</f>
+        <v/>
+      </c>
+      <c r="E47" s="34">
+        <f>'Матрица'!N43</f>
+        <v/>
+      </c>
+      <c r="F47" s="18">
+        <f>'Матрица'!O43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="43" t="inlineStr">
         <is>
           <t>Документы-источники</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>ADR-100</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ADR-200</t>
+          <t>ADR-100</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
+          <t>Что сдано и что отложено; таблица «целевой компонент — замена на прототипе»</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ADR-300</t>
+          <t>ADR-200</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
+          <t>Стек по слоям, альтернативы, сравнение Python/Go/Node.js</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ADR-400</t>
+          <t>ADR-300</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Безопасность по контурам, открытые пункты</t>
+          <t>Модели: классификация, эмбеддинги, реранкер, генерация, судья</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-400</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
+          <t>Безопасность по контурам, открытые пункты</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>ADR-600</t>
+          <t>ADR-500</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>План развития и укрупнённые оценки трудозатрат</t>
+          <t>Ресурсы и стоимость: прототип, MVP, тираж</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>C4_Deployment, C3/*</t>
+          <t>ADR-600</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Целевая схема развёртывания и компоненты</t>
+          <t>План развития и укрупнённые оценки трудозатрат</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="11" t="inlineStr">
         <is>
+          <t>C4_Deployment, C3/*</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Целевая схема развёртывания и компоненты</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="11" t="inlineStr">
+        <is>
           <t>Код и docker-compose.yml</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>Проверка колонки «Сейчас»</t>
         </is>
@@ -6587,12 +6700,12 @@
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C56:F56"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C49:F49"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C54:F54"/>
     <mergeCell ref="C51:F51"/>
+    <mergeCell ref="C57:F57"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C55:F55"/>
@@ -6609,7 +6722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7116,91 +7229,121 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="105" customHeight="1">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="50" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Оркестрация (Kubernetes), узлы</t>
+          <t>Сервис шаблонов заявлений (Template Service)</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Число и размер узлов</t>
+          <t>Число выданных бланков</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
+          <t>Шаблоны — файлы размером порядка килобайт, семь на прототипе; читаются с кэшем, чтение из хранилища — при первом обращении и при обновлении. Нагрузка и объём ничтожны, но не измерялись; источник (MinIO или файловый сервер) не выбран.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по допущениям</t>
+          <t>Допущение; не измерялось</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Sizing; C4_Deployment</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="75" customHeight="1">
+          <t>ADR-200; ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="105" customHeight="1">
       <c r="A21" s="50" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Наблюдаемость</t>
+          <t>Оркестрация (Kubernetes), узлы</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Метрики и логи</t>
+          <t>Число и размер узлов</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Loki: сейчас ≈65 байт на вопрос (замер) — до 31 МБ за 30 суток на тираже; целевая трассировка до 10 КБ на вопрос (допущение) — 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже. Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Допущение и замер</t>
+          <t>Расчёт по допущениям</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Capacity_Report, раздел 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+          <t>Sizing; C4_Deployment</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="75" customHeight="1">
       <c r="A22" s="50" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
+          <t>Наблюдаемость</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Метрики и логи</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Loki: сейчас ≈65 байт на вопрос (замер) — до 31 МБ за 30 суток на тираже; целевая трассировка до 10 КБ на вопрос (допущение) — 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже. Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Допущение и замер</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Capacity_Report, раздел 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="50" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
           <t>Секреты (GitLab CI variables, Kubernetes Secret)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Объёма нет.</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Не применимо</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>ADR-400</t>
         </is>
@@ -7221,7 +7364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8078,7 +8221,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="50" t="n">
         <v>8</v>
       </c>
@@ -8089,21 +8232,20 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>ETL индексации (CronJob, окно 02:00–05:00) [вариант с GPU]</t>
-        </is>
-      </c>
-      <c r="D23" s="51">
-        <f>1*$C$12</f>
-        <v/>
+          <t>Template Service (шаблоны заявлений, MVP)</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="E23" s="51" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F23" s="51" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G23" s="51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H23" s="51" t="n">
         <v>0</v>
@@ -8124,18 +8266,17 @@
         <f>D23*H23</f>
         <v/>
       </c>
-      <c r="M23" s="51">
-        <f>1*$C$12</f>
-        <v/>
+      <c r="M23" s="51" t="n">
+        <v>2</v>
       </c>
       <c r="N23" s="51" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="O23" s="51" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="P23" s="51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="51" t="n">
         <v>0</v>
@@ -8158,7 +8299,7 @@
       </c>
       <c r="V23" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
+          <t>Допущение автора, не измерялось. Читает шаблоны из MinIO или с файлового сервера и держит их в кэше; нагрузка ничтожна (килобайты, чтение с кэшем), 2 реплики — для отказоустойчивости. Сами шаблоны — в томе MinIO (учтены там).</t>
         </is>
       </c>
     </row>
@@ -8173,20 +8314,21 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Оценка качества (CronJob, ночной прогон)</t>
-        </is>
-      </c>
-      <c r="D24" s="51" t="n">
+          <t>ETL индексации (CronJob, окно 02:00–05:00) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D24" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="E24" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F24" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" s="51" t="n">
         <v>0</v>
@@ -8207,17 +8349,18 @@
         <f>D24*H24</f>
         <v/>
       </c>
-      <c r="M24" s="51" t="n">
+      <c r="M24" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="N24" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="O24" s="51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24" s="51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="51" t="n">
         <v>0</v>
@@ -8240,7 +8383,7 @@
       </c>
       <c r="V24" s="9" t="inlineStr">
         <is>
-          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
+          <t>Допущение. Эмбеддинги считает GPU-сервис; 5 ГиБ — временные файлы документов. Время индексации на GPU не измерялось.</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8398,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Prometheus</t>
+          <t>Оценка качества (CronJob, ночной прогон)</t>
         </is>
       </c>
       <c r="D25" s="51" t="n">
@@ -8268,7 +8411,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H25" s="51" t="n">
         <v>0</v>
@@ -8299,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="P25" s="51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="51" t="n">
         <v>0</v>
@@ -8322,11 +8465,11 @@
       </c>
       <c r="V25" s="9" t="inlineStr">
         <is>
-          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t>Допущение. Ходит во внешний API судьи; локальной нагрузки почти нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="50" t="n">
         <v>11</v>
       </c>
@@ -8337,7 +8480,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Loki</t>
+          <t>Prometheus</t>
         </is>
       </c>
       <c r="D26" s="51" t="n">
@@ -8350,7 +8493,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H26" s="51" t="n">
         <v>0</v>
@@ -8381,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="P26" s="51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="51" t="n">
         <v>0</v>
@@ -8404,35 +8547,35 @@
       </c>
       <c r="V26" s="9" t="inlineStr">
         <is>
-          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
+          <t>Замер: 84 ряда на процесс приложения; допущение: до 20 000 рядов с метриками кластера, хранение 15 суток ≈2,6 ГБ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="50" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Qdrant</t>
+          <t>Loki</t>
         </is>
       </c>
       <c r="D27" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="G27" s="51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H27" s="51" t="n">
         <v>0</v>
@@ -8454,16 +8597,16 @@
         <v/>
       </c>
       <c r="M27" s="51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O27" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O27" s="51" t="n">
-        <v>2</v>
-      </c>
       <c r="P27" s="51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q27" s="51" t="n">
         <v>0</v>
@@ -8486,11 +8629,11 @@
       </c>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="105" customHeight="1">
+          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="50" t="n">
         <v>13</v>
       </c>
@@ -8501,7 +8644,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Postgres (обращения, телеметрия, журнал диалогов)</t>
+          <t>Qdrant</t>
         </is>
       </c>
       <c r="D28" s="51" t="n">
@@ -8514,7 +8657,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H28" s="51" t="n">
         <v>0</v>
@@ -8545,7 +8688,7 @@
         <v>2</v>
       </c>
       <c r="P28" s="51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="51" t="n">
         <v>0</v>
@@ -8568,11 +8711,11 @@
       </c>
       <c r="V28" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Данные абонента в Postgres не хранятся: они читаются из Биллинга и Диспетчерской в момент вопроса (решение 25 сентября 2026; прежняя строка профиля 24 МБ и 270 МБ снята). Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t>Расчёт: 30–100 тыс. векторов × 1 024 × 4 байта = 123–410 МБ. Замер: 100 000 векторов — 477 МБ на диске и 527 МиБ ОЗУ (718 МиБ при загрузке); во время blue-green две коллекции и копия — 10 ГиБ. Замер: 100 000 векторов, P99 65 мс. От числа абонентов не зависит; вторая реплика на тираже — для отказоустойчивости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="105" customHeight="1">
       <c r="A29" s="50" t="n">
         <v>14</v>
       </c>
@@ -8583,20 +8726,20 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Redis (квоты и сессии)</t>
+          <t>Postgres (обращения, телеметрия, журнал диалогов)</t>
         </is>
       </c>
       <c r="D29" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="51" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F29" s="51" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="G29" s="51" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H29" s="51" t="n">
         <v>0</v>
@@ -8621,13 +8764,13 @@
         <v>2</v>
       </c>
       <c r="N29" s="51" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O29" s="51" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="P29" s="51" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="Q29" s="51" t="n">
         <v>0</v>
@@ -8650,7 +8793,7 @@
       </c>
       <c r="V29" s="9" t="inlineStr">
         <is>
-          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
+          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Данные абонента в Postgres не хранятся: они читаются из Биллинга и Диспетчерской в момент вопроса (решение 25 сентября 2026; прежняя строка профиля 24 МБ и 270 МБ снята). Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
         </is>
       </c>
     </row>
@@ -8665,20 +8808,20 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>MinIO (документы, копии, снимки)</t>
+          <t>Redis (квоты и сессии)</t>
         </is>
       </c>
       <c r="D30" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F30" s="51" t="n">
         <v>0.25</v>
       </c>
-      <c r="F30" s="51" t="n">
-        <v>0.5</v>
-      </c>
       <c r="G30" s="51" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H30" s="51" t="n">
         <v>0</v>
@@ -8700,16 +8843,16 @@
         <v/>
       </c>
       <c r="M30" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O30" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P30" s="51" t="n">
         <v>1</v>
-      </c>
-      <c r="N30" s="51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O30" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" s="51" t="n">
-        <v>400</v>
       </c>
       <c r="Q30" s="51" t="n">
         <v>0</v>
@@ -8732,39 +8875,38 @@
       </c>
       <c r="V30" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+          <t>Замер: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход, срок жизни 30 минут. До 1 200 одновременных сессий (0,656 запроса/с × 30 мин) × 3 КБ ≈ 4 МБ: объём ничтожен. Отказ Redis отклоняет запросы (fail-closed), поэтому на тираже 2 экземпляра.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="50" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Эмбеддинги (BGE-M3, inference) [вариант с GPU]</t>
-        </is>
-      </c>
-      <c r="D31" s="51">
-        <f>1*$C$12</f>
-        <v/>
+          <t>MinIO (документы, копии, снимки)</t>
+        </is>
+      </c>
+      <c r="D31" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="E31" s="51" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F31" s="51" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="51" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="H31" s="51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="53">
         <f>D31*E31</f>
@@ -8782,21 +8924,20 @@
         <f>D31*H31</f>
         <v/>
       </c>
-      <c r="M31" s="51">
-        <f>1*$C$12</f>
-        <v/>
+      <c r="M31" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="N31" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O31" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="O31" s="51" t="n">
-        <v>4</v>
-      </c>
       <c r="P31" s="51" t="n">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="Q31" s="51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R31" s="53">
         <f>M31*N31</f>
@@ -8816,7 +8957,7 @@
       </c>
       <c r="V31" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32); на диске 4,25 ГБ — две копии в кэше. Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
+          <t>Расчёт по максимуму прогноза: готовые бланки ≈200 КБ (допущение) × 2 800 в месяц = 6,7 ГБ в год (MVP) и × 31 500 = 76 ГБ в год (тираж), хранение 3 года — 20 и 227 ГБ; копии Postgres за 7 суток до 42 ГБ; документы базы знаний ≈1 ГБ; снимки Qdrant.</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8972,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Реранкер (BGE-reranker-v2-m3, inference) [вариант с GPU]</t>
+          <t>Эмбеддинги (BGE-M3, inference) [вариант с GPU]</t>
         </is>
       </c>
       <c r="D32" s="51">
@@ -8842,13 +8983,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" s="51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H32" s="51" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I32" s="53">
         <f>D32*E32</f>
@@ -8874,13 +9015,13 @@
         <v>1</v>
       </c>
       <c r="O32" s="51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P32" s="51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q32" s="51" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="R32" s="53">
         <f>M32*N32</f>
@@ -8900,7 +9041,7 @@
       </c>
       <c r="V32" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+          <t>Замер: веса 2,14 ГиБ (fp32); на диске 4,25 ГБ — две копии в кэше. Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈2 ГиБ видеопамяти. Скорость на GPU не измерялась.</t>
         </is>
       </c>
     </row>
@@ -8910,28 +9051,29 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>gpu-llm</t>
+          <t>gpu</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
-        </is>
-      </c>
-      <c r="D33" s="51" t="n">
-        <v>0</v>
+          <t>Реранкер (BGE-reranker-v2-m3, inference) [вариант с GPU]</t>
+        </is>
+      </c>
+      <c r="D33" s="51">
+        <f>1*$C$12</f>
+        <v/>
       </c>
       <c r="E33" s="51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F33" s="51" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="G33" s="51" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H33" s="51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I33" s="53">
         <f>D33*E33</f>
@@ -8949,20 +9091,21 @@
         <f>D33*H33</f>
         <v/>
       </c>
-      <c r="M33" s="51" t="n">
+      <c r="M33" s="51">
+        <f>1*$C$12</f>
+        <v/>
+      </c>
+      <c r="N33" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="51" t="n">
-        <v>8</v>
-      </c>
       <c r="O33" s="51" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="P33" s="51" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="Q33" s="51" t="n">
-        <v>40</v>
+        <v>1.5</v>
       </c>
       <c r="R33" s="53">
         <f>M33*N33</f>
@@ -8982,36 +9125,35 @@
       </c>
       <c r="V33" s="9" t="inlineStr">
         <is>
-          <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="50" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>gpu-llm</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Эмбеддинги (e5-small на CPU) [вариант без GPU]</t>
-        </is>
-      </c>
-      <c r="D34" s="51">
-        <f>2*(1-$C$12)</f>
-        <v/>
+          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
+        </is>
+      </c>
+      <c r="D34" s="51" t="n">
+        <v>0</v>
       </c>
       <c r="E34" s="51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F34" s="51" t="n">
-        <v>1.5</v>
+        <v>64</v>
       </c>
       <c r="G34" s="51" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H34" s="51" t="n">
         <v>0</v>
@@ -9032,21 +9174,20 @@
         <f>D34*H34</f>
         <v/>
       </c>
-      <c r="M34" s="51">
-        <f>2*(1-$C$12)</f>
-        <v/>
+      <c r="M34" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="N34" s="51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O34" s="51" t="n">
-        <v>1.5</v>
+        <v>64</v>
       </c>
       <c r="P34" s="51" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Q34" s="51" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R34" s="53">
         <f>M34*N34</f>
@@ -9066,7 +9207,7 @@
       </c>
       <c r="V34" s="9" t="inlineStr">
         <is>
-          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7,2 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
+          <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
         </is>
       </c>
     </row>
@@ -9081,21 +9222,21 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>ETL индексации: эмбеддинги на CPU (CronJob) [вариант без GPU]</t>
+          <t>Эмбеддинги (e5-small на CPU) [вариант без GPU]</t>
         </is>
       </c>
       <c r="D35" s="51">
-        <f>1*(1-$C$12)</f>
+        <f>2*(1-$C$12)</f>
         <v/>
       </c>
       <c r="E35" s="51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35" s="51" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="G35" s="51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" s="51" t="n">
         <v>0</v>
@@ -9117,17 +9258,17 @@
         <v/>
       </c>
       <c r="M35" s="51">
-        <f>1*(1-$C$12)</f>
+        <f>2*(1-$C$12)</f>
         <v/>
       </c>
       <c r="N35" s="51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O35" s="51" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="P35" s="51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="51" t="n">
         <v>0</v>
@@ -9150,169 +9291,197 @@
       </c>
       <c r="V35" s="9" t="inlineStr">
         <is>
+          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7,2 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="50" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>ETL индексации: эмбеддинги на CPU (CronJob) [вариант без GPU]</t>
+        </is>
+      </c>
+      <c r="D36" s="51">
+        <f>1*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="E36" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="53">
+        <f>D36*E36</f>
+        <v/>
+      </c>
+      <c r="J36" s="53">
+        <f>D36*F36</f>
+        <v/>
+      </c>
+      <c r="K36" s="53">
+        <f>D36*G36</f>
+        <v/>
+      </c>
+      <c r="L36" s="53">
+        <f>D36*H36</f>
+        <v/>
+      </c>
+      <c r="M36" s="51">
+        <f>1*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="N36" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q36" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="53">
+        <f>M36*N36</f>
+        <v/>
+      </c>
+      <c r="S36" s="53">
+        <f>M36*O36</f>
+        <v/>
+      </c>
+      <c r="T36" s="53">
+        <f>M36*P36</f>
+        <v/>
+      </c>
+      <c r="U36" s="53">
+        <f>M36*Q36</f>
+        <v/>
+      </c>
+      <c r="V36" s="9" t="inlineStr">
+        <is>
           <t>Расчёт по замеру: e5-small ≈27 мс на часть (машина с 12 потоками) → 30–100 тыс. частей ≈14–46 мин; на поде с 4 vCPU время не измерялось и может быть в 2–3 раза больше (окно 3 часа). Только в варианте без GPU.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="C37" s="43" t="inlineStr">
+    <row r="38">
+      <c r="C38" s="43" t="inlineStr">
         <is>
           <t>Итог по пулам узлов</t>
         </is>
       </c>
-      <c r="P37" s="9" t="inlineStr">
+      <c r="P38" s="9" t="inlineStr">
         <is>
           <t>Загрузка узла по запросам, не выше</t>
         </is>
       </c>
-      <c r="Q37" s="54" t="n">
+      <c r="Q38" s="54" t="n">
         <v>0.7</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Пул</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Класс узла</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>vCPU узла</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>ОЗУ узла, ГиБ</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Видеопамять узла, ГиБ</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Запас на потерю узла (1 — да)</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>MVP: vCPU</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>MVP: ОЗУ</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>MVP: видеопамять</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>MVP: узлов</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>Тираж: vCPU</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Тираж: ОЗУ</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>Тираж: видеопамять</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>Тираж: узлов</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>general</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$I$16:$I$35)</f>
-        <v/>
-      </c>
-      <c r="I39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$J$16:$J$35)</f>
-        <v/>
-      </c>
-      <c r="J39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$L$16:$L$35)</f>
-        <v/>
-      </c>
-      <c r="K39" s="56">
-        <f>IF(H39=0,0,ROUNDUP(MAX(H39/($Q$37*$D39),I39/($Q$37*$E39),IF($F39&gt;0,J39/($Q$37*$F39),0)),0)+$G39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$R$16:$R$35)</f>
-        <v/>
-      </c>
-      <c r="M39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$S$16:$S$35)</f>
-        <v/>
-      </c>
-      <c r="N39" s="55">
-        <f>SUMIF($B$16:$B$35,$B39,$U$16:$U$35)</f>
-        <v/>
-      </c>
-      <c r="O39" s="56">
-        <f>IF(L39=0,0,ROUNDUP(MAX(L39/($Q$37*$D39),M39/($Q$37*$E39),IF($F39&gt;0,N39/($Q$37*$F39),0)),0)+$G39)</f>
-        <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Пул данных (NVMe)</t>
+          <t>Общий пул (платформа, приложение, наблюдаемость)</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
         <v>8</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F40" s="10" t="n">
         <v>0</v>
@@ -9321,47 +9490,47 @@
         <v>1</v>
       </c>
       <c r="H40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$I$16:$I$35)</f>
+        <f>SUMIF($B$16:$B$36,$B40,$I$16:$I$36)</f>
         <v/>
       </c>
       <c r="I40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$J$16:$J$35)</f>
+        <f>SUMIF($B$16:$B$36,$B40,$J$16:$J$36)</f>
         <v/>
       </c>
       <c r="J40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$L$16:$L$35)</f>
+        <f>SUMIF($B$16:$B$36,$B40,$L$16:$L$36)</f>
         <v/>
       </c>
       <c r="K40" s="56">
-        <f>IF(H40=0,0,ROUNDUP(MAX(H40/($Q$37*$D40),I40/($Q$37*$E40),IF($F40&gt;0,J40/($Q$37*$F40),0)),0)+$G40)</f>
+        <f>IF(H40=0,0,ROUNDUP(MAX(H40/($Q$38*$D40),I40/($Q$38*$E40),IF($F40&gt;0,J40/($Q$38*$F40),0)),0)+$G40)</f>
         <v/>
       </c>
       <c r="L40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$R$16:$R$35)</f>
+        <f>SUMIF($B$16:$B$36,$B40,$R$16:$R$36)</f>
         <v/>
       </c>
       <c r="M40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$S$16:$S$35)</f>
+        <f>SUMIF($B$16:$B$36,$B40,$S$16:$S$36)</f>
         <v/>
       </c>
       <c r="N40" s="55">
-        <f>SUMIF($B$16:$B$35,$B40,$U$16:$U$35)</f>
+        <f>SUMIF($B$16:$B$36,$B40,$U$16:$U$36)</f>
         <v/>
       </c>
       <c r="O40" s="56">
-        <f>IF(L40=0,0,ROUNDUP(MAX(L40/($Q$37*$D40),M40/($Q$37*$E40),IF($F40&gt;0,N40/($Q$37*$F40),0)),0)+$G40)</f>
+        <f>IF(L40=0,0,ROUNDUP(MAX(L40/($Q$38*$D40),M40/($Q$38*$E40),IF($F40&gt;0,N40/($Q$38*$F40),0)),0)+$G40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>GPU-пул (эмбеддинги, реранкер)</t>
+          <t>Пул данных (NVMe)</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
@@ -9371,132 +9540,188 @@
         <v>32</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$I$16:$I$35)</f>
+        <f>SUMIF($B$16:$B$36,$B41,$I$16:$I$36)</f>
         <v/>
       </c>
       <c r="I41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$J$16:$J$35)</f>
+        <f>SUMIF($B$16:$B$36,$B41,$J$16:$J$36)</f>
         <v/>
       </c>
       <c r="J41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$L$16:$L$35)</f>
+        <f>SUMIF($B$16:$B$36,$B41,$L$16:$L$36)</f>
         <v/>
       </c>
       <c r="K41" s="56">
-        <f>IF(H41=0,0,ROUNDUP(MAX(H41/($Q$37*$D41),I41/($Q$37*$E41),IF($F41&gt;0,J41/($Q$37*$F41),0)),0)+$G41)</f>
+        <f>IF(H41=0,0,ROUNDUP(MAX(H41/($Q$38*$D41),I41/($Q$38*$E41),IF($F41&gt;0,J41/($Q$38*$F41),0)),0)+$G41)</f>
         <v/>
       </c>
       <c r="L41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$R$16:$R$35)</f>
+        <f>SUMIF($B$16:$B$36,$B41,$R$16:$R$36)</f>
         <v/>
       </c>
       <c r="M41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$S$16:$S$35)</f>
+        <f>SUMIF($B$16:$B$36,$B41,$S$16:$S$36)</f>
         <v/>
       </c>
       <c r="N41" s="55">
-        <f>SUMIF($B$16:$B$35,$B41,$U$16:$U$35)</f>
+        <f>SUMIF($B$16:$B$36,$B41,$U$16:$U$36)</f>
         <v/>
       </c>
       <c r="O41" s="56">
-        <f>IF(L41=0,0,ROUNDUP(MAX(L41/($Q$37*$D41),M41/($Q$37*$E41),IF($F41&gt;0,N41/($Q$37*$F41),0)),0)+$G41)</f>
+        <f>IF(L41=0,0,ROUNDUP(MAX(L41/($Q$38*$D41),M41/($Q$38*$E41),IF($F41&gt;0,N41/($Q$38*$F41),0)),0)+$G41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>gpu-llm</t>
+          <t>gpu</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>GPU-пул генерации (тираж)</t>
+          <t>GPU-пул (эмбеддинги, реранкер)</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$I$16:$I$35)</f>
+        <f>SUMIF($B$16:$B$36,$B42,$I$16:$I$36)</f>
         <v/>
       </c>
       <c r="I42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$J$16:$J$35)</f>
+        <f>SUMIF($B$16:$B$36,$B42,$J$16:$J$36)</f>
         <v/>
       </c>
       <c r="J42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$L$16:$L$35)</f>
+        <f>SUMIF($B$16:$B$36,$B42,$L$16:$L$36)</f>
         <v/>
       </c>
       <c r="K42" s="56">
-        <f>IF(H42=0,0,ROUNDUP(MAX(H42/($Q$37*$D42),I42/($Q$37*$E42),IF($F42&gt;0,J42/($Q$37*$F42),0)),0)+$G42)</f>
+        <f>IF(H42=0,0,ROUNDUP(MAX(H42/($Q$38*$D42),I42/($Q$38*$E42),IF($F42&gt;0,J42/($Q$38*$F42),0)),0)+$G42)</f>
         <v/>
       </c>
       <c r="L42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$R$16:$R$35)</f>
+        <f>SUMIF($B$16:$B$36,$B42,$R$16:$R$36)</f>
         <v/>
       </c>
       <c r="M42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$S$16:$S$35)</f>
+        <f>SUMIF($B$16:$B$36,$B42,$S$16:$S$36)</f>
         <v/>
       </c>
       <c r="N42" s="55">
-        <f>SUMIF($B$16:$B$35,$B42,$U$16:$U$35)</f>
+        <f>SUMIF($B$16:$B$36,$B42,$U$16:$U$36)</f>
         <v/>
       </c>
       <c r="O42" s="56">
-        <f>IF(L42=0,0,ROUNDUP(MAX(L42/($Q$37*$D42),M42/($Q$37*$E42),IF($F42&gt;0,N42/($Q$37*$F42),0)),0)+$G42)</f>
+        <f>IF(L42=0,0,ROUNDUP(MAX(L42/($Q$38*$D42),M42/($Q$38*$E42),IF($F42&gt;0,N42/($Q$38*$F42),0)),0)+$G42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Итого узлов</t>
-        </is>
-      </c>
-      <c r="K43" s="57">
-        <f>SUM(K39:K42)</f>
-        <v/>
-      </c>
-      <c r="O43" s="57">
-        <f>SUM(O39:O42)</f>
+          <t>gpu-llm</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>GPU-пул генерации (тираж)</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="55">
+        <f>SUMIF($B$16:$B$36,$B43,$I$16:$I$36)</f>
+        <v/>
+      </c>
+      <c r="I43" s="55">
+        <f>SUMIF($B$16:$B$36,$B43,$J$16:$J$36)</f>
+        <v/>
+      </c>
+      <c r="J43" s="55">
+        <f>SUMIF($B$16:$B$36,$B43,$L$16:$L$36)</f>
+        <v/>
+      </c>
+      <c r="K43" s="56">
+        <f>IF(H43=0,0,ROUNDUP(MAX(H43/($Q$38*$D43),I43/($Q$38*$E43),IF($F43&gt;0,J43/($Q$38*$F43),0)),0)+$G43)</f>
+        <v/>
+      </c>
+      <c r="L43" s="55">
+        <f>SUMIF($B$16:$B$36,$B43,$R$16:$R$36)</f>
+        <v/>
+      </c>
+      <c r="M43" s="55">
+        <f>SUMIF($B$16:$B$36,$B43,$S$16:$S$36)</f>
+        <v/>
+      </c>
+      <c r="N43" s="55">
+        <f>SUMIF($B$16:$B$36,$B43,$U$16:$U$36)</f>
+        <v/>
+      </c>
+      <c r="O43" s="56">
+        <f>IF(L43=0,0,ROUNDUP(MAX(L43/($Q$38*$D43),M43/($Q$38*$E43),IF($F43&gt;0,N43/($Q$38*$F43),0)),0)+$G43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="11" t="inlineStr">
         <is>
+          <t>Итого узлов</t>
+        </is>
+      </c>
+      <c r="K44" s="57">
+        <f>SUM(K40:K43)</f>
+        <v/>
+      </c>
+      <c r="O44" s="57">
+        <f>SUM(O40:O43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
           <t>Диск под тома, ГиБ</t>
         </is>
       </c>
-      <c r="K44" s="58">
-        <f>SUM($K$16:$K$35)</f>
-        <v/>
-      </c>
-      <c r="O44" s="58">
-        <f>SUM($T$16:$T$35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="33" t="inlineStr">
+      <c r="K45" s="58">
+        <f>SUM($K$16:$K$36)</f>
+        <v/>
+      </c>
+      <c r="O45" s="58">
+        <f>SUM($T$16:$T$36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="33" t="inlineStr">
         <is>
           <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); управляющая часть Kubernetes размещена на трёх узлах общего пула (допущение); нагрузочный тест не проводился.</t>
         </is>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1490,7 +1490,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>GigaChat технически недоступен на машине прототипа (нужны корневые сертификаты НУЦ; отключать проверку TLS недопустимо). Зарубежные провайдеры отклонены на всех этапах: 152-ФЗ. Собственная модель тиража: Qwen2.5-32B выбран против Llama 3.x и открытых весов GigaChat — лицензия Apache 2.0, сильный русский среди открытых моделей, одно семейство 7B (уже используется для тестов) → 32B без переделки, 32B в INT4 помещается на одну карту A100 (в проекте заложено 34 ГБ весов плюс запас под кэш; на GPU не проверялось, а для INT4 по общим сведениям ожидается около 17–20 ГБ — 34 ГБ скорее соответствуют 8-битному представлению). Выбор сделан по репутации модели, на своём эталонном наборе не проверен; прогон запланирован при переходе к тиражу (3–5 чел-дн, ADR-600).</t>
+          <t>GigaChat технически недоступен на машине прототипа (нужны корневые сертификаты НУЦ; отключать проверку TLS недопустимо). Зарубежные провайдеры отклонены на всех этапах: 152-ФЗ. Собственная модель тиража (вариант, решение не принято (25.09.2026): после замеров и оценки реальной работы на MVP): Qwen2.5-32B выбран против Llama 3.x и открытых весов GigaChat — лицензия Apache 2.0, сильный русский среди открытых моделей, одно семейство 7B (уже используется для тестов) → 32B без переделки, 32B в INT4 помещается на одну карту A100 (в проекте заложено 34 ГБ весов плюс запас под кэш; на GPU не проверялось, а для INT4 по общим сведениям ожидается около 17–20 ГБ — 34 ГБ скорее соответствуют 8-битному представлению). Выбор сделан по репутации модели, на своём эталонном наборе не проверен; прогон запланирован при переходе к тиражу (3–5 чел-дн, ADR-600).</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>Собственная модель в закрытом контуре, внешние API остаются до срабатывания триггера.</t>
+          <t>Внешние API; собственная модель в закрытом контуре — вариант, решение не принято (25.09.2026): после замеров и оценки реальной работы на MVP. Оценка справа — на случай «да».</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="R9" s="9" t="inlineStr">
         <is>
-          <t>Включается по триггеру (нагрузка, требование ИБ отказаться от внешних API, падение SLA провайдера), не по дате. Одна карта с запасом покрывает пик 3,4–6,75 запроса.</t>
+          <t>Не автоматический запуск: поводы вынести вопрос — нагрузка, требование ИБ отказаться от внешних API, падение SLA провайдера (не по дате). Если примут: одна карта с запасом покрывает пик 3,4–6,75 запроса.</t>
         </is>
       </c>
       <c r="S9" s="20" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 17 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 7 на тираже (+1 GPU-узел под собственную модель); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
+          <t>Размещение в существующем кластере владельца, где работает личный кабинет (эксплуатирует тот же отдел; GPU-узлов нет): пространство имён, квоты, сетевые правила, Ingress, классы хранилищ, манифесты для 17 компонентов, секреты (Kubernetes Secret из GitLab CI variables). Расчёт по допущениям (лист «Sizing», базовый вариант без GPU): 6 узлов на MVP (4 общих и 2 данных), 6 на тираже без собственной модели и 7 с ней (решение о собственной видеокарте не принято); в общем кластере это верхняя оценка заказываемых узлов, стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
@@ -4233,7 +4233,7 @@
       <c r="O40" s="15" t="n"/>
       <c r="P40" s="9" t="inlineStr">
         <is>
-          <t>Сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
+          <t>Только если решат брать собственную модель (решение не принято (25.09.2026): после замеров и оценки реальной работы на MVP): сравнение семейств на эталонном наборе; закупка и ввод GPU-сервера 1× A100 80 ГБ.</t>
         </is>
       </c>
       <c r="Q40" s="9" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="R40" s="9" t="inlineStr">
         <is>
-          <t>Аренда исключена не по цене, а по триггеру (речь о собственной модели генерации; для проверки эмбеддингов и реранкера на MVP аренда на месяц допустима): облачный GPU считается внешним сервисом.</t>
+          <t>Если поводом станет требование ИБ отказаться от внешних API, аренда исключена не по цене, а по существу (речь о собственной модели генерации; для проверки эмбеддингов и реранкера на MVP аренда на месяц допустима): облачный GPU считается внешним сервисом. Сама покупка не решена — после замеров и оценки MVP.</t>
         </is>
       </c>
       <c r="S40" s="20" t="n">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Минимум — 3 305 ₽/мес, максимум — 1,07 млн ₽/мес (0,66 вопроса/с в пике); при собственной модели заменяется CAPEX на карту</t>
+          <t>Минимум — 3 305 ₽/мес, максимум — 1,07 млн ₽/мес (0,66 вопроса/с в пике); если примут собственную модель — вместо токенов CAPEX на карту</t>
         </is>
       </c>
       <c r="D28" s="42" t="n">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Карта A100 80 ГБ (покупка)</t>
+          <t>Карта A100 80 ГБ (покупка, только если решат брать собственную модель)</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена триггером). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
+          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена, если поводом станет требование ИБ). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
         </is>
       </c>
       <c r="D31" s="42" t="n">
@@ -7259,7 +7259,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="105" customHeight="1">
+    <row r="21" ht="120" customHeight="1">
       <c r="A21" s="50" t="n">
         <v>17</v>
       </c>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 7 (+1 узел под собственную модель с A100 80 ГБ). Вариант с GPU-узлом: 6 и 8 узлов (3 общих, 2 данных, 1 GPU; на тираже ещё узел под модель). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 6 без собственной модели и 7 с ней (+1 узел с A100 80 ГБ; решение о собственной видеокарте не принято). Вариант с GPU-узлом для поиска: 6 узлов на MVP и 7 на тираже без собственной модели (8 с ней). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -9129,7 +9129,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="50" t="n">
         <v>19</v>
       </c>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — по триггеру</t>
+          <t>Собственная модель (Qwen2.5-32B INT4, vLLM) — вариант, решение не принято</t>
         </is>
       </c>
       <c r="D34" s="51" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="V34" s="9" t="inlineStr">
         <is>
-          <t>Только на тираже по триггеру. Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
+          <t>Только на тираже и только если будет принято решение о собственной видеокарте (после замеров и оценки реальной работы на MVP). Видеопамять 40 ГБ — допущение (веса INT4 ожидаются 17–20 ГБ, заложено 34 ГБ, плюс кэш); проверка на карте не проводилась.</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>GPU-пул генерации (тираж)</t>
+          <t>GPU-пул генерации (тираж; только если решат брать)</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2249,7 +2249,7 @@
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Включение агента: состояние ожидания подтверждения, идемпотентность, аудит (в том числе отказов абонента), проверка черновика до показа.</t>
+          <t>Начало работ — по триггеру Этапа 2: четыре условия сразу, с числовыми порогами (ADR-600, «Критерий перехода…»: hit@3 ≥ 85%, hit@1 ≥ 60%, верных ответов ≥ 80%, скорость не хуже прототипа, 4 недели подряд — предложение автора, утверждает владелец). Включение агента: состояние ожидания подтверждения, идемпотентность, аудит (в том числе отказов абонента), проверка черновика до показа.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос. Реплика с несколькими задачами разбирается и отвечается по частям; регистрация предлагается по первой подходящей части, несколько черновиков не хранятся; из условий проверяется только наличие долга (ADR-200). Доля реплик с двумя и более задачами по разметке не измерена: выше 5% — переход на LangGraph.</t>
+          <t>Форма компонента не выбрана (решение заказчика 25.09.2026): агент — отдельный контейнер, либо самописный модуль в Backend, как `registration.py` сейчас; решается после анализа всех обращений (сколько типов запросов на запись, сценарии); сравнение вариантов А/Б/В — ADR-200, «Агент записи или самописный модуль». Оценка справа — для варианта с отдельным контейнером. Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос. Реплика с несколькими задачами разбирается и отвечается по частям; регистрация предлагается по первой подходящей части, несколько черновиков не хранятся; из условий проверяется только наличие долга (ADR-200). Доля реплик с двумя и более задачами по разметке не измерена: выше 5% — переход на LangGraph.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки.</t>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки. Свод по операциям записи (решение заказчика 25.09.2026): сколько типов запросов на запись и какие у них сценарии — на этом решается, нужен ли агент (контейнер или LangGraph) или достаточно самописного модуля в Backend (ADR-200, «Агент записи или самописный модуль»); в пределах оценки, отдельно не считалась (оценка автора).</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>9 типов из 16 запасной классификатор не знает: refund, debt, payment, penalty, accrual_recalculation, inquiry_cancellation, meter_reacceptance, meter_reacceptance_auto, other. По ним работают только ключевые слова. Реальные тексты по этим типам — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет). Пороги k-NN подобраны замером на e5-small и не переносятся на другую модель. Классификация даёт одну тему и один тип на реплику; несколько задач в реплике разбирает детектор намерений (`app/agents/intents.py`, реализован на прототипе). Замер: 31 из 136 настоящих обращений (23%) подходят под несколько типов по ключевым словам — это пересечение слов; детектор на тех же текстах находит несколько задач в 1 из 136 (0,7%). Доля по разметке людьми не измерена — при доле выше 5% агент переводится на LangGraph (триггер 4, ADR-200).</t>
+          <t>9 типов из 16 запасной классификатор не знает: refund, debt, payment, penalty, accrual_recalculation, inquiry_cancellation, meter_reacceptance, meter_reacceptance_auto, other. По ним работают только ключевые слова. Реальные тексты по этим типам — споры, а не заявки, нужен размеченный корпус вопросов-заявок (его пока нет). Пороги k-NN подобраны замером на e5-small и не переносятся на другую модель. Классификация даёт одну тему и один тип на реплику; несколько задач в реплике разбирает детектор намерений (`app/agents/intents.py`, реализован на прототипе). Замер: 31 из 136 настоящих обращений (23%) подходят под несколько типов по ключевым словам — это пересечение слов; детектор на тех же текстах находит несколько задач в 1 из 136 (0,7%). Доля по разметке людьми не измерена — при доле выше 5% дорабатывается детектор намерений (LangGraph реплику на задачи не разбирает, ADR-200).</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Свой автомат (7 состояний, 10 переходов, 200 строк, перебор всех состояний в тестах) против `transitions` (строковые ключи, дефект уже случался) и LangGraph (второй механизм подтверждения; возможности — ветвление по инструментам, контрольные точки, параллельные ветви — по документации, не пробовались). Вес LangGraph замерен: +34 МиБ ОЗУ и 2,3 с на импорт, ≈2,6% контейнера Backend — не довод против. LangGraph — по триггеру; проверить возможности нечем, пока нет агентного сценария. Другие движки не сравнивались.</t>
+          <t>Свой автомат (7 состояний, 10 переходов, 200 строк, перебор всех состояний в тестах) против `transitions` (строковые ключи, дефект уже случался) и LangGraph (второй механизм подтверждения; возможности — ветвление по инструментам, контрольные точки, параллельные ветви — по документации, не пробовались). Вес LangGraph замерен: +34 МиБ ОЗУ и 2,3 с на импорт, ≈2,6% контейнера Backend — не довод против. LangGraph берётся только если на реальных данных измерено, что без него работает хуже (три признака в ADR-200); таких измерений нет. Другие движки не сравнивались.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Форма компонента не выбрана (решение заказчика 25.09.2026): агент — отдельный контейнер, либо самописный модуль в Backend, как `registration.py` сейчас; решается после анализа всех обращений (сколько типов запросов на запись, сценарии); сравнение вариантов А/Б/В — ADR-200, «Агент записи или самописный модуль». Оценка справа — для варианта с отдельным контейнером. Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос. Реплика с несколькими задачами разбирается и отвечается по частям; регистрация предлагается по первой подходящей части, несколько черновиков не хранятся; из условий проверяется только наличие долга (ADR-200). Доля реплик с двумя и более задачами по разметке не измерена: выше 5% — переход на LangGraph.</t>
+          <t>Форма компонента не выбрана: агент — отдельный контейнер, либо самописный модуль в Backend, как `registration.py` сейчас; решается после анализа всех обращений (сколько типов запросов на запись, сценарии); сравнение вариантов А/Б/В — ADR-200, «Агент записи или самописный модуль». Оценка справа — для варианта с отдельным контейнером. Оценка function-calling у провайдеров РФ для роли агента — открытый вопрос. Реплика с несколькими задачами разбирается и отвечается по частям; регистрация предлагается по первой подходящей части, несколько черновиков не хранятся; из условий проверяется только наличие долга (ADR-200). Доля реплик с двумя и более задачами по разметке не измерена: выше 5% — дорабатывается детектор намерений.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -2331,27 +2331,27 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Не выполняется: автомат — собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов). Работа появляется только при наступлении одного из четырёх триггеров (модель выбирает следующий шаг после вызова инструмента; шаг ждёт событие дольше 30 минут и должен продолжиться с того же шага; две и более одновременные ветви со своими повторами и слиянием; доля реплик с двумя и более задачами выше 5%). Проверяется при постановке сценария Этапа 2 в разработку, при его изменении и при пересмотре по метрикам Этапа 1; журнал проверки — в ADR-200; пока ни один сценарий не поставлен.</t>
+          <t>Не выполняется: автомат — собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов). Работа появляется только если на реальных данных измерено, что без LangGraph работает хуже, и более простое средство не помогло. Три признака (ADR-200): выбор шага моделью даёт выигрыш, которого правила не дают; операции записи теряются из-за потери состояния; ошибки в собственной логике переходов. Пороги не заданы. Возможности библиотеки (ветвление, контрольные точки, параллельные ветви) сами по себе не повод; доля многозадачных реплик — метрика детектора, не признак. Журнал проверки — в ADR-200; пока ни один сценарий не поставлен и измерений нет.</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Свой автомат против `transitions` и LangGraph — ADR-200, подраздел «Оркестрация агента». LangGraph нужен, если агент сам выбирает инструмент, если нужны контрольные точки шагов, если появились параллельные ветви со своим состоянием; для фиксированной заявки с одним подтверждением не нужен.</t>
+          <t>Свой автомат против `transitions` и LangGraph — ADR-200, подраздел «Оркестрация агента». Прежние четыре условия (выбор шага моделью, ожидание дольше сессии, параллельные ветви, доля многозадачных реплик &gt; 5%) сняты как описывающие возможности библиотеки, а не ухудшение без неё: ожидание снимается хранением состояния в Postgres, параллельные ветви — `asyncio.gather`, реплику на задачи разбирает детектор. Для фиксированной заявки с одним подтверждением LangGraph не нужен.</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Оркестрация агента: собственная таблица переходов, LangGraph — по триггеру», в том числе «В каком случае LangGraph нужен — подробно»</t>
+          <t>ADR-200, подраздел «Оркестрация агента: собственная таблица переходов, LangGraph — по триггеру», в том числе «Почему сейчас LangGraph не нужен» и признаки необходимости</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Оценка function-calling у GigaChat и YandexGPT не проведена; возможности LangGraph в проекте не пробовались; телеметрия библиотеки (`langsmith`) не проверена на соответствие 152-ФЗ. Четвёртый триггер — доля реплик абонентов с двумя и более задачами выше 5% (измерение на выгрузке живых обращений и затем ежемесячно по чату). Оценка по триггерам: общая часть 5–9 чел-дн; с триггером 1 — 8–14, 2 — 7–12, 3 — 7–12, 4 — 7–13; все четыре — 14–24 (диапазон 7–24).</t>
+          <t>Оценка function-calling у GigaChat и YandexGPT не проведена (предусловие признака 1); возможности LangGraph в проекте не пробовались; телеметрия библиотеки (`langsmith`) не проверена на соответствие 152-ФЗ. Пороги признаков 1–3 не заданы — выбираются при анализе обращений. Оценка по признакам: общая часть 5–9 чел-дн; с признаком 1 — 8–14, 2 — 7–12, 3 — 5–9; признаки 1 и 2 вместе — 10–17 (диапазон 5–17).</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблицы переходов в граф без изменения состава переходов; `interrupt_before` вместо проверки состояния или не применяется; контрольные точки (Redis с сохранением или Postgres) и удаление ПДн из состояния; при триггере 1 — инструменты (Биллинг, обращения, Диспетчерская) с ограничением шагов, идемпотентностью и аудитом; отключение внешней телеметрии библиотеки; регрессия; при триггере 4 — перенос детектора намерений и очереди задач в граф, условные задачи.</t>
+          <t>Перенос таблицы переходов в граф без изменения состава переходов; `interrupt_before` вместо проверки состояния или не применяется; при признаке 2 — контрольные точки (Redis с сохранением или Postgres) и удаление ПДн из состояния; при признаке 1 — инструменты (Биллинг, обращения, Диспетчерская) с ограничением шагов, идемпотентностью и аудитом; отключение внешней телеметрии библиотеки; регрессия.</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Только по триггеру: возможности, ради которых берут библиотеку, на текущем сценарии проверить нечем. Работа не входит в итог сметы — показана отдельным столбцом.</t>
+          <t>Только если измерено, что без него работает хуже: возможности, ради которых берут библиотеку, сами по себе не доказывают необходимости. Работа не входит в итог сметы — показана отдельным столбцом.</t>
         </is>
       </c>
       <c r="M18" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="O18" s="13" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — триггер 4 перехода агента на LangGraph (выше 5%, ADR-200); в пределах оценки. Свод по операциям записи (решение заказчика 25.09.2026): сколько типов запросов на запись и какие у них сценарии — на этом решается, нужен ли агент (контейнер или LangGraph) или достаточно самописного модуля в Backend (ADR-200, «Агент записи или самописный модуль»); в пределах оценки, отдельно не считалась (оценка автора).</t>
+          <t>Выгрузка живых обращений (не менее 100 на тип), обезличивание, разметка, анализ всех 16 типов и 6 тем; заново собрать таблицу типов и тем; после этого заново выбрать модели эмбеддингов и запасного классификатора для MVP (сравнение — в строке «Эмбеддинги»). Для каждой реплики размечается число задач и считается доля реплик с двумя и более — метрика детектора намерений (выше 5% — доработка детектора, ADR-200); в пределах оценки. Свод по операциям записи: сколько типов запросов на запись и какие у них сценарии — на этом решается, нужен ли агент (контейнер или LangGraph) или достаточно самописного модуля в Backend (ADR-200, «Агент записи или самописный модуль»); в пределах оценки, отдельно не считалась (оценка автора).</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — условие перехода на LangGraph (триггер 4).</t>
+          <t>Без этого вторая задача реплики теряется, а модель может написать, что выполнила операцию; доля многозадачных реплик по разметке людьми — метрика детектора намерений (выше 5% — доработка детектора; LangGraph этого не решает).</t>
         </is>
       </c>
       <c r="M42" s="17" t="n">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2239,7 +2239,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, раздел «Backend и оркестрация»: строка «Оркестрация агента» и подраздел «Оркестрация агента: собственная таблица переходов, LangGraph — по триггеру»</t>
+          <t>ADR-200, раздел «Backend и оркестрация»: строка «Оркестрация агента» и подраздел «Оркестрация агента: LangGraph на MVP, собственная таблица переходов — прототип»</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Переход агента на LangGraph (по триггеру)</t>
+          <t>LangGraph для оркестрации записи</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -2331,48 +2331,48 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Не выполняется: автомат — собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов). Работа появляется только если на реальных данных измерено, что без LangGraph работает хуже, и более простое средство не помогло. Три признака (ADR-200): выбор шага моделью даёт выигрыш, которого правила не дают; операции записи теряются из-за потери состояния; ошибки в собственной логике переходов. Пороги не заданы. Возможности библиотеки (ветвление, контрольные точки, параллельные ветви) сами по себе не повод; доля многозадачных реплик — метрика детектора, не признак. Журнал проверки — в ADR-200; пока ни один сценарий не поставлен и измерений нет.</t>
+          <t>Собственная таблица переходов (`app/fsm.py`, 7 состояний, 10 переходов), покрыта тестами; LangGraph не подключён и не пробовался.</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Свой автомат против `transitions` и LangGraph — ADR-200, подраздел «Оркестрация агента». Прежние четыре условия (выбор шага моделью, ожидание дольше сессии, параллельные ветви, доля многозадачных реплик &gt; 5%) сняты как описывающие возможности библиотеки, а не ухудшение без неё: ожидание снимается хранением состояния в Postgres, параллельные ветви — `asyncio.gather`, реплику на задачи разбирает детектор. Для фиксированной заявки с одним подтверждением LangGraph не нужен.</t>
+          <t>Свой автомат против `transitions` и LangGraph — ADR-200, подраздел «Оркестрация агента». Решение плановое: LangGraph с MVP, без условий-триггеров, потому что ресурсов почти не требует (+34 МиБ ОЗУ, +2,3 с на импорт, замер; GPU не нужна). Необходимость измерением не показана — решение не доказано, а принято планово; прежние условия перехода (по возможностям библиотеки, затем по признакам необходимости) сняты.</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>ADR-200, подраздел «Оркестрация агента: собственная таблица переходов, LangGraph — по триггеру», в том числе «Почему сейчас LangGraph не нужен» и признаки необходимости</t>
+          <t>ADR-200, подраздел «Оркестрация агента: LangGraph на MVP, собственная таблица переходов — прототип», включая условия внедрения; работы — ADR-600, «LangGraph для оркестрации записи»</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Оценка function-calling у GigaChat и YandexGPT не проведена (предусловие признака 1); возможности LangGraph в проекте не пробовались; телеметрия библиотеки (`langsmith`) не проверена на соответствие 152-ФЗ. Пороги признаков 1–3 не заданы — выбираются при анализе обращений. Оценка по признакам: общая часть 5–9 чел-дн; с признаком 1 — 8–14, 2 — 7–12, 3 — 5–9; признаки 1 и 2 вместе — 10–17 (диапазон 5–17).</t>
+          <t>Лишняя зависимость (согласование ИБ); риск второго механизма подтверждения при неверном `interrupt_before`; телеметрия `langsmith` за периметр не проверена на 152-ФЗ; задержка шага графа не измерена; возможности библиотеки в проекте не пробовались.</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Перенос таблицы переходов в граф без изменения состава переходов; `interrupt_before` вместо проверки состояния или не применяется; при признаке 2 — контрольные точки (Redis с сохранением или Postgres) и удаление ПДн из состояния; при признаке 1 — инструменты (Биллинг, обращения, Диспетчерская) с ограничением шагов, идемпотентностью и аудитом; отключение внешней телеметрии библиотеки; регрессия.</t>
+          <t>Граф с тем же составом переходов, что `app/fsm.py`; тесты перебора всех состояний на графе; `interrupt_before` вместо проверки состояния или не применяется; отключение внешней телеметрии; согласование ИБ; замер задержки и регрессия. Опции по решению при проектировании сценария (вне оценки): контрольные точки состояния 2–3, выбор инструмента моделью 3–5 чел-дн (предусловие — тест function-calling).</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Python; LangGraph `StateGraph`; хранилище контрольных точек — Redis с сохранением или Postgres.</t>
+          <t>Python; LangGraph `StateGraph`; состояние — Redis с сохранением или Postgres (если включены контрольные точки).</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Только если измерено, что без него работает хуже: возможности, ради которых берут библиотеку, сами по себе не доказывают необходимости. Работа не входит в итог сметы — показана отдельным столбцом.</t>
-        </is>
-      </c>
-      <c r="M18" s="12" t="n">
+          <t>Ресурсов почти не требует; граф даёт единое описание переходов и опции на будущее. Правило подтверждения остаётся одним.</t>
+        </is>
+      </c>
+      <c r="M18" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="N18" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="O18" s="13" t="inlineStr">
-        <is>
-          <t>По триггеру (оценка автора)</t>
+      <c r="N18" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="O18" s="18" t="inlineStr">
+        <is>
+          <t>Из блока ADR-600: LangGraph для оркестрации записи</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5075,21 +5075,21 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Документация и ИБ</t>
+          <t>LangGraph для оркестрации записи</t>
         </is>
       </c>
       <c r="B19" s="34" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="34" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$43)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: LangGraph для оркестрации записи",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E19" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$43)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: LangGraph для оркестрации записи",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F19" s="44">
@@ -5098,28 +5098,28 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>1–1,5 недели</t>
+          <t>5–9 чел-дн (ADR-600): граф с тем же составом переходов 2–3, подтверждение 1–2, зависимость и ИБ 1–2, замер задержки 1–2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Анализ типов на живых данных</t>
+          <t>Документация и ИБ</t>
         </is>
       </c>
       <c r="B20" s="34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C20" s="34" t="n">
-        <v>19</v>
+        <v>7.5</v>
       </c>
       <c r="D20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$43)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Документация и ИБ",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E20" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$43)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Документация и ИБ",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F20" s="44">
@@ -5128,28 +5128,28 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>13–19 чел-дн (ADR-600, дополнительно к блоку «Качество поиска и классификации»)</t>
+          <t>1–1,5 недели</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
+          <t>Анализ типов на живых данных</t>
         </is>
       </c>
       <c r="B21" s="34" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C21" s="34" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$43)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E21" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$43)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Анализ типов на живых данных",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F21" s="44">
@@ -5158,28 +5158,28 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>9–14 чел-дн (ADR-600): проверка детектора на репликах чата 3–4, несколько обращений из одной реплики 3–5, условия помимо долга 2–3, путь generate и лимиты 1–2</t>
+          <t>13–19 чел-дн (ADR-600, дополнительно к блоку «Качество поиска и классификации»)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Проверка Guardrails и провайдеров на живых данных</t>
+          <t>Несколько задач в одной реплике (доработка после прототипа)</t>
         </is>
       </c>
       <c r="B22" s="34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22" s="34" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D22" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$43)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$M$3:$M$43)</f>
         <v/>
       </c>
       <c r="E22" s="34">
-        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$43)</f>
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Несколько задач в одной реплике (доработка после прототипа)",'Матрица'!$N$3:$N$43)</f>
         <v/>
       </c>
       <c r="F22" s="44">
@@ -5188,140 +5188,137 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>11–18 чел-дн (ADR-600): выборка 1–2, Guardrails 4–6, оптимизация синхронной проверки 1–2, сравнение провайдеров 4–6, решение 1–2</t>
+          <t>9–14 чел-дн (ADR-600): проверка детектора на репликах чата 3–4, несколько обращений из одной реплики 3–5, условия помимо долга 2–3, путь generate и лимиты 1–2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>Проверка Guardrails и провайдеров на живых данных</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" s="34">
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$M$3:$M$43)</f>
+        <v/>
+      </c>
+      <c r="E23" s="34">
+        <f>SUMIF('Матрица'!$O$3:$O$43,"Из блока ADR-600: Проверка Guardrails и провайдеров на живых данных",'Матрица'!$N$3:$N$43)</f>
+        <v/>
+      </c>
+      <c r="F23" s="44">
+        <f>IF(AND(D23=B23,E23=C23),"да","НЕТ")</f>
+        <v/>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>11–18 чел-дн (ADR-600): выборка 1–2, Guardrails 4–6, оптимизация синхронной проверки 1–2, сравнение провайдеров 4–6, решение 1–2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
           <t>Итого по блокам</t>
         </is>
       </c>
-      <c r="B23" s="38">
-        <f>SUM(B15:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="38">
-        <f>SUM(C15:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="38">
-        <f>SUM(D15:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="38">
-        <f>SUM(E15:E22)</f>
-        <v/>
-      </c>
-      <c r="F23" s="45">
-        <f>IF(AND(D23=B23,E23=C23),"да","НЕТ")</f>
-        <v/>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>ADR-600 называет итог ≈22–34 недели (≈110–170 чел-дн); сумма блоков 111,5–169,5 — округление в самом ADR-600</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="B24" s="38">
+        <f>SUM(B15:B23)</f>
+        <v/>
+      </c>
+      <c r="C24" s="38">
+        <f>SUM(C15:C23)</f>
+        <v/>
+      </c>
+      <c r="D24" s="38">
+        <f>SUM(D15:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="38">
+        <f>SUM(E15:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="45">
+        <f>IF(AND(D24=B24,E24=C24),"да","НЕТ")</f>
+        <v/>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>ADR-600 называет итог ≈23–36 недель (≈115–180 чел-дн); сумма блоков 116,5–178,5 — округление в самом ADR-600</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>Затраты, которые не выражаются человеко-днями</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Контур</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Значение / комментарий</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>От</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>До</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Единица</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Источник</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Токены генерации (YandexGPT Pro, 0,8 ₽ за 1000 токенов)</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Минимум — 1 234 ₽/мес (7% абонентов в чате, 30% вопросов до модели, 401 токен на запрос, судья раз в неделю); максимум — 101 280 ₽/мес (35%, 70%, 3 500 токенов, судья каждую ночь). Допущения о спросе данными водоканала не подтверждены; разброс ×82</t>
-        </is>
-      </c>
-      <c r="D27" s="42" t="n">
-        <v>1234</v>
-      </c>
-      <c r="E27" s="42" t="n">
-        <v>101280</v>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>₽/мес</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>Capacity_Report; лист «Прогноз стоимости»</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Токены генерации и судьи качества (тариф YandexGPT Pro 0,8 ₽ за 1000 токенов)</t>
+          <t>Токены генерации (YandexGPT Pro, 0,8 ₽ за 1000 токенов)</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Минимум — 3 305 ₽/мес, максимум — 1,07 млн ₽/мес (0,66 вопроса/с в пике); если примут собственную модель — вместо токенов CAPEX на карту</t>
+          <t>Минимум — 1 234 ₽/мес (7% абонентов в чате, 30% вопросов до модели, 401 токен на запрос, судья раз в неделю); максимум — 101 280 ₽/мес (35%, 70%, 3 500 токенов, судья каждую ночь). Допущения о спросе данными водоканала не подтверждены; разброс ×82</t>
         </is>
       </c>
       <c r="D28" s="42" t="n">
-        <v>3305</v>
+        <v>1234</v>
       </c>
       <c r="E28" s="42" t="n">
-        <v>1065600</v>
+        <v>101280</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
@@ -5337,29 +5334,33 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>Тираж</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>GPU-сервер под эмбеддинги и реранкер (только если владелец добавит GPU-узел: в кластере GPU нет)</t>
+          <t>Токены генерации и судьи качества (тариф YandexGPT Pro 0,8 ₽ за 1000 токенов)</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Не оценён отдельной строкой сметы; скорость на GPU не измерялась</t>
-        </is>
-      </c>
-      <c r="D29" s="42" t="n"/>
-      <c r="E29" s="42" t="n"/>
+          <t>Минимум — 3 305 ₽/мес, максимум — 1,07 млн ₽/мес (0,66 вопроса/с в пике); если примут собственную модель — вместо токенов CAPEX на карту</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E29" s="42" t="n">
+        <v>1065600</v>
+      </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>₽</t>
+          <t>₽/мес</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>ADR-500 (открытый пункт)</t>
+          <t>Capacity_Report; лист «Прогноз стоимости»</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5372,12 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
+          <t>GPU-сервер под эмбеддинги и реранкер (только если владелец добавит GPU-узел: в кластере GPU нет)</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Не оценены</t>
+          <t>Не оценён отдельной строкой сметы; скорость на GPU не измерялась</t>
         </is>
       </c>
       <c r="D30" s="42" t="n"/>
@@ -5395,25 +5396,21 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Тираж</t>
+          <t>MVP</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Карта A100 80 ГБ (покупка, только если решат брать собственную модель)</t>
+          <t>Kubernetes-кластер, хранилища, наблюдаемость (железо, размещение, обслуживание)</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена, если поводом станет требование ИБ). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
-        </is>
-      </c>
-      <c r="D31" s="42" t="n">
-        <v>927000</v>
-      </c>
-      <c r="E31" s="42" t="n">
-        <v>2368080</v>
-      </c>
+          <t>Не оценены</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
       <c r="F31" s="9" t="inlineStr">
         <is>
           <t>₽</t>
@@ -5421,7 +5418,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>ADR-500</t>
+          <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
@@ -5433,29 +5430,62 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
+          <t>Карта A100 80 ГБ (покупка, только если решат брать собственную модель)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>OEM ≈927 000 ₽; оригинал/сертифицированная ≈2 368 080 ₽ (аренда 35–50 тыс. ₽/мес исключена, если поводом станет требование ИБ). Источник цен в проекте не зафиксирован, коммерческих предложений нет — подтвердить</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="n">
+        <v>927000</v>
+      </c>
+      <c r="E32" s="42" t="n">
+        <v>2368080</v>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>₽</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>ADR-500</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Тираж</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
           <t>Сервер-хост, электричество, размещение, обслуживание GPU</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Не оценены</t>
         </is>
       </c>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="42" t="n"/>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>₽</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>ADR-500 (открытый пункт)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="33" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>Все суммы в ₽ — прогнозная модель, не смета: CAPEX/OPEX не утверждены владельцем (ADR-500). Закупка GPU — недели или месяцы лид-тайма, не разработка.</t>
         </is>
@@ -6152,7 +6182,7 @@
         <f>'Матрица'!N18</f>
         <v/>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="18">
         <f>'Матрица'!O18</f>
         <v/>
       </c>
@@ -7996,7 +8026,7 @@
         <v>0.25</v>
       </c>
       <c r="F20" s="51" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="51" t="n">
         <v>0</v>
@@ -8027,7 +8057,7 @@
         <v>0.25</v>
       </c>
       <c r="O20" s="51" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P20" s="51" t="n">
         <v>0</v>
@@ -8053,7 +8083,7 @@
       </c>
       <c r="V20" s="9" t="inlineStr">
         <is>
-          <t>Допущение. До 2 800 диалогов с записью в месяц на MVP и 31 500 на тираже (максимум прогноза, A6 = 40%) — нагрузка ничтожна.</t>
+          <t>Допущение; ОЗУ 0,5 ГиБ с запасом на LangGraph (+34 МиБ, замер). До 2 800 диалогов с записью в месяц на MVP и 31 500 на тираже (максимум прогноза, A6 = 40%) — нагрузка ничтожна.</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); отдельные контейнеры Prometheus и Loki — верхняя оценка до ответа владельца (MVP)</t>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); Loki — логи (решение принято); Prometheus — запасной источник для P99 (верхняя оценка до проверки Zabbix)</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); Prometheus и Loki — верхняя оценка до ответа владельца.</t>
+          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); Loki — логи (решение принято); Prometheus — запасной источник для P99.</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>В реальном контуре работают Grafana, Zabbix и Jaeger (решение заказчика проекта, со слов); алерты не настроены. Grafana и Alertmanager в расчёт не входят. Prometheus (запасной источник для задержки P99) и Loki (как собираются логи, неизвестно) оставлены как верхняя оценка до ответа владельца.</t>
+          <t>В реальном контуре работают Grafana, Zabbix и Jaeger (решение заказчика проекта, со слов); алерты не настроены. Grafana и Alertmanager в расчёт не входят. Loki (логи) заложен как основной компонент — решение принято; Prometheus (запасной источник для задержки P99) оставлен как верхняя оценка до проверки Zabbix. Сборщик логов подов в расчёт не включён.</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2071,7 +2071,7 @@
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>Срок хранения подробных событий 12 месяцев, сводная таблица по дням и секции по месяцам; замер на 4 млн строк.</t>
+          <t>Срок хранения подробных событий 12 месяцев, сводная таблица по дням и секции по месяцам; замер на ≈1,7 млн строк.</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 234–101 280 ₽ в месяц, на тираже 3 305 ₽–1,07 млн ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
+          <t>Есть прогнозная модель с минимальным и максимальным сценарием (`Capacity_Report.html`, лист «Прогноз стоимости»): токены на MVP 1 476–22 320 ₽ в месяц, на тираже 6 022–177 300 ₽; цен на серверы и GPU нет. Это не смета: числа не утверждены владельцем (открытый P0).</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Разброс стоимости токенов на MVP — ×82 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
+          <t>Разброс стоимости токенов на MVP — ×15 между минимумом и максимумом; без статистики ЛК, колл-центра и живых обращений смета остаётся диапазоном.</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -5311,14 +5311,14 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Минимум — 1 234 ₽/мес (7% абонентов в чате, 30% вопросов до модели, 401 токен на запрос, судья раз в неделю); максимум — 101 280 ₽/мес (35%, 70%, 3 500 токенов, судья каждую ночь). Допущения о спросе данными водоканала не подтверждены; разброс ×82</t>
+          <t>Минимум — 1 476 ₽/мес (7% абонентов в чате, судья раз в неделю); максимум — 22 320 ₽/мес (35% абонентов, судья каждую ночь); в обоих сценариях 30% вопросов до модели и 1 000 токенов на запрос (решение 25 сентября 2026). Допущения о спросе данными водоканала не подтверждены; разброс ×15</t>
         </is>
       </c>
       <c r="D28" s="42" t="n">
-        <v>1234</v>
+        <v>1476</v>
       </c>
       <c r="E28" s="42" t="n">
-        <v>101280</v>
+        <v>22320</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
@@ -5344,14 +5344,14 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Минимум — 3 305 ₽/мес, максимум — 1,07 млн ₽/мес (0,66 вопроса/с в пике); если примут собственную модель — вместо токенов CAPEX на карту</t>
+          <t>Минимум — 6 022 ₽/мес, максимум — 177 300 ₽/мес (0,66 вопроса/с в пике); если примут собственную модель — вместо токенов CAPEX на карту</t>
         </is>
       </c>
       <c r="D29" s="42" t="n">
-        <v>3305</v>
+        <v>6022</v>
       </c>
       <c r="E29" s="42" t="n">
-        <v>1065600</v>
+        <v>177300</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C7" s="48" t="inlineStr">
         <is>
-          <t>MVP — 8 000 абонентов; тираж — 90 000. Прогноз токенов и стоимости — минимум и максимум (лист «Прогноз стоимости», `Capacity_Report.html`): учтено, что не все абоненты приходят в чат (7–35%) и только 30–70% вопросов доходит до модели. Цена одна — публичный тариф YandexGPT Pro 0,8 ₽ за 1000 токенов из ADR-500 (не проверялся; тариф GigaChat Pro неизвестен). Цен на серверы и GPU нет. Допущения о спросе данными водоканала не подтверждены; токенов на запрос: измерено 401 (19 вызовов, фрагменты FAQ до 300 знаков), допущение максимума — 3 500. Пересчёт после получения данных — 3–5 чел-дн, по пилоту — 1–2 (блок P0 ADR-600).</t>
+          <t>MVP — 8 000 абонентов; тираж — 90 000. Прогноз токенов и стоимости — минимум и максимум (лист «Прогноз стоимости», `Capacity_Report.html`): учтено, что не все абоненты приходят в чат (7–35%) и до модели доходят 30% вопросов (принято в обоих сценариях). Цена одна — публичный тариф YandexGPT Pro 0,8 ₽ за 1000 токенов из ADR-500 (не проверялся; тариф GigaChat Pro неизвестен). Цен на серверы и GPU нет. Допущения о спросе данными водоканала не подтверждены; токенов на запрос принято 1 000 в обоих сценариях (замер 401 на 19 вызовах с короткими фрагментами FAQ в расчёт не берётся). Пересчёт после получения данных — 3–5 чел-дн, по пилоту — 1–2 (блок P0 ADR-600).</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Судья: 1,3–23,7 млн токенов в месяц на MVP и 1,9–174 млн на тираже (эталонный набор из 30 вопросов раз в неделю или каждую ночь плюс 1–5% выборка трафика); допущение: 5 вызовов судьи по ≈2 000 токенов на образец, не измерено.</t>
+          <t>Судья: 1,3–15,3 млн токенов в месяц на MVP и 1,9–79,9 млн на тираже (эталонный набор из 30 вопросов раз в неделю или каждую ночь плюс 1–5% выборка трафика); допущение: 5 вызовов судьи по ≈2 000 токенов на образец, не измерено.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -6989,7 +6989,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="75" customHeight="1">
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="50" t="n">
         <v>7</v>
       </c>
@@ -7005,12 +7005,12 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Токенов на запрос: измерено 401 (19 вызовов, фрагменты FAQ до 300 знаков), допущение максимума — 3 500. Стоимость токенов (генерация и судья) — 1 234–101 280 ₽ в месяц на MVP и 3 305 ₽–1,07 млн ₽ на тираже (минимум–максимум); до модели доходит 30–70% вопросов. Агент Этапа 2 добавит до 44 800 ₽ (MVP) и 504 000 ₽ (тираж) в месяц в максимуме.</t>
+          <t>Токенов на запрос принято 1 000 в обоих сценариях (замер 401 на 19 вызовах с короткими фрагментами FAQ до 300 знаков в расчёт не берётся). Стоимость токенов (генерация и судья) — 1 476–22 320 ₽ в месяц на MVP и 6 022–177 300 ₽ на тираже (минимум–максимум); до модели доходит 30% вопросов (принято в обоих сценариях). Агент Этапа 2 добавит до 44 800 ₽ (MVP) и 504 000 ₽ (тираж) в месяц в максимуме.</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Замер (401) и допущение (3 500)</t>
+          <t>Принятое допущение (1 000 токенов); замер 401 на коротких фрагментах</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>События использования: 6 048–352 800 строк в год на MVP и 68 040–3,97 млн на тираже (≈2–109 МБ и 21 МБ–1,2 ГБ в год; замер 2 млн строк — 589 МБ). Журнал диалогов при сроке хранения 90 суток (выбрано) — до 0,08 ГБ на MVP и 0,94 ГБ на тираже (4 КБ на диалог, максимум прогноза). Подробные события хранятся 12 месяцев (замер: 12 млн строк дают агрегат по всей таблице 39 с). Итого до 0,4 ГБ на MVP и до 4 ГБ на тираже, том 20 и 50 ГиБ (лист «Sizing»). Число обращений в месяц принято равным диалогам с записью.</t>
+          <t>События использования: 6 048–151 200 строк в год на MVP и 68 040–1,70 млн на тираже (≈2–47 МБ и 21–524 МБ в год; замер 2 млн строк — 589 МБ). Журнал диалогов при сроке хранения 90 суток (выбрано) — до 0,08 ГБ на MVP и 0,94 ГБ на тираже (4 КБ на диалог, максимум прогноза). Подробные события хранятся 12 месяцев (замер: 12 млн строк дают агрегат по всей таблице 39 с). Итого до 0,2 ГБ на MVP и до 2,2 ГБ на тираже; том 20 и 50 ГиБ выбран с запасом до пересчёта и не менялся (лист «Sizing»). Число обращений в месяц принято равным диалогам с записью.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="V29" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; события использования 0,11 ГБ и 1,2 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Данные абонента в Postgres не хранятся: они читаются из Биллинга и Диспетчерской в момент вопроса (решение 25 сентября 2026; прежняя строка профиля 24 МБ и 270 МБ снята). Итого до 0,4 ГБ (MVP) и до 4 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск с запасом на журнал и копии.</t>
+          <t>Расчёт по максимуму прогноза: журнал диалогов за 90 суток (4 КБ на диалог) — 84 МБ на MVP и 0,95 ГБ на тираже; события использования 0,05 ГБ и 0,52 ГБ в год (308 байт на строку, замер); обращения (заложено 2 КБ на строку, замер по 8 строкам — 0,58 КБ; доля записи 40%) 0,07 и 0,76 ГБ в год. Данные абонента в Postgres не хранятся: они читаются из Биллинга и Диспетчерской в момент вопроса (решение 25 сентября 2026; прежняя строка профиля 24 МБ и 270 МБ снята). Итого до 0,2 ГБ (MVP) и до 2,2 ГБ (тираж; подробные события хранятся 12 месяцев, старше — сводная таблица); диск 20 и 50 ГиБ выбран до пересчёта 25 сентября 2026 и оставлен с запасом на журнал и копии.</t>
         </is>
       </c>
     </row>
@@ -9921,11 +9921,11 @@
         <v>0.3</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Замер на двух наборах живых текстов: 30% (регистр обращений по телефону и почте) и 70% (форма вопросов Golden Set). Остальные закрывают правила и ответы без модели. Подтвердить: Анализ живых обращений (ADR-600)</t>
+          <t>Принято 30% в обоих сценариях (25 сентября 2026). Замер на регистре обращений по телефону и почте дал 30%; 70% (форма вопросов Golden Set) в расчёт не берётся. Остальные закрывают правила и ответы без модели. Подтвердить: Анализ живых обращений (ADR-600)</t>
         </is>
       </c>
     </row>
@@ -9941,14 +9941,14 @@
         </is>
       </c>
       <c r="C9" s="59" t="n">
-        <v>401</v>
+        <v>1000</v>
       </c>
       <c r="D9" s="59" t="n">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Минимум — замер по 19 вызовам YandexGPT (короткие фрагменты FAQ). Максимум — допущение: системный текст + 3 фрагмента по ≈800 токенов. Подтвердить: Пилот на базе из нескольких тысяч документов</t>
+          <t>Принято 1 000 в обоих сценариях (25 сентября 2026). Замер по 19 вызовам YandexGPT дал 401 на коротких фрагментах FAQ; 3 500 (допущение: системный текст + 3 фрагмента по ≈800 токенов) в расчёт не берётся. Подтвердить: Пилот на базе из нескольких тысяч документов</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -7305,7 +7305,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 6 без собственной модели и 7 с ней (+1 узел с A100 80 ГБ; решение о собственной видеокарте не принято). Вариант с GPU-узлом для поиска: 6 узлов на MVP и 7 на тираже без собственной модели (8 с ней). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
+          <t>Расчёт по выбранным допущениям (лист «Sizing», базовый вариант без GPU: в кластере владельца GPU нет): MVP — 6 узлов (4 общих 8 vCPU/16 ГиБ, 2 данных 8 vCPU/32 ГиБ), тираж — 6 без собственной модели и 7 с ней (предположительно — A100 80 ГБ; решение о собственной видеокарте не принято). Вариант с GPU-узлом для поиска: 6 узлов на MVP и 7 на тираже без собственной модели (8 с ней). Диск под тома ≈170 ГиБ на MVP и ≈661 ГиБ на тираже. Расчёт для отдельного кластера — верхняя оценка для общего. Стоимость серверов не оценена.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Алерты не настроены: 9 описанных алертов (в том числе «Утечка ПДн в ответе») принимать некому — нет каналов и получателей; предложение автора: настроенный алерт об утечке ПДн — условие включения MVP (согласовать с ИБ). Не известны версии Zabbix, Grafana, Jaeger, подключение Zabbix к Grafana, возможность считать квантили, сбор логов. Трассировки в нашем коде нет (Jaeger в контуре есть).</t>
+          <t>Алерты не настроены: 9 описанных алертов (в том числе «Утечка ПДн в ответе») принимать некому — нет каналов и получателей; предложение автора: настроенный алерт об утечке ПДн — условие включения MVP (согласовать с ИБ). Не известны версии Zabbix, Grafana, Jaeger, подключение Zabbix к Grafana, возможность считать квантили, сбор логов кластера (если он есть, Loki не нужен), допустимость лицензии AGPL-3.0 у Loki. Трассировки в нашем коде нет (Jaeger в контуре есть).</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); Loki — логи (решение принято); Prometheus — запасной источник для P99 (верхняя оценка до проверки Zabbix)</t>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); единое хранилище логов (VictoriaLogs или OpenSearch, выбор не сделан); Prometheus — запасной источник для P99 (верхняя оценка до проверки Zabbix)</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Алерты не настроены: 9 описанных алертов (в том числе «Утечка ПДн в ответе») принимать некому — нет каналов и получателей; предложение автора: настроенный алерт об утечке ПДн — условие включения MVP (согласовать с ИБ). Не известны версии Zabbix, Grafana, Jaeger, подключение Zabbix к Grafana, возможность считать квантили, сбор логов кластера (если он есть, Loki не нужен), допустимость лицензии AGPL-3.0 у Loki. Трассировки в нашем коде нет (Jaeger в контуре есть).</t>
+          <t>Алерты не настроены: 9 описанных алертов (в том числе «Утечка ПДн в ответе») принимать некому — нет каналов и получателей; предложение автора: настроенный алерт об утечке ПДн — условие включения MVP (согласовать с ИБ). Не известны версии Zabbix, Grafana, Jaeger, подключение Zabbix к Grafana, возможность считать квантили, как хранятся логи каждого контейнера сейчас, можно ли установить плагин VictoriaLogs в Grafana владельца (версия не ниже 10.4.0, права администратора), примет ли ИБ молодой продукт. Трассировки в нашем коде нет (Jaeger в контуре есть).</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); Loki — логи (решение принято); Prometheus — запасной источник для P99.</t>
+          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); единое хранилище логов: VictoriaLogs (рекомендация автора) или OpenSearch, выбор не сделан; Prometheus — запасной источник для P99.</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); единое хранилище логов (VictoriaLogs или OpenSearch, выбор не сделан); Prometheus — запасной источник для P99 (верхняя оценка до проверки Zabbix)</t>
+          <t>Backend и LLM Gateway (метрики); все контейнеры (логи); Grafana и Zabbix — владельца (не наши контейнеры); VictoriaLogs — единое хранилище логов (решение принято); Prometheus — запасной источник для P99 (верхняя оценка до проверки Zabbix)</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>Дашборды как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; 9 алертов как триггеры и действия Zabbix; сбор метрик с порта 9100; проверка расчёта P99 в Zabbix до начала работ; определение получателей и каналов оповещения; в логах только отчёт об обезличивании. Проверка на стенде владельца до выбора между Zabbix (C) и своим Prometheus (B): сбор с порта 9100, расчёт P99, доставка алерта, плагин Grafana, нагрузка на Zabbix (1–2 чел-дн, предложение автора). Алерты: триггеры Zabbix (при B — Grafana Alerting; Alertmanager не разворачиваем); алерт об утечке ПДн — сразу, без подавления повторов, получатель от ИБ; алерт о недоступности источника метрик. Трассировка: на MVP без Jaeger — две гистограммы (поиск, вызов провайдера) 0,5–1 чел-дн в пределах оценки; OpenTelemetry → Jaeger — только если P99 разобрать не удаётся, 2–4 чел-дн, оценка автора, в итог не входит. Оценка не пересматривалась (5–8): развёртывание своей связки отпало, добавились интеграция с Zabbix и настройка оповещений.</t>
+          <t>Дашборды как код (JSON, импорт в Grafana владельца): 5 Golden Signals и 8 метрик ИИ; 9 алертов как триггеры и действия Zabbix; сбор метрик с порта 9100; проверка расчёта P99 в Zabbix до начала работ; определение получателей и каналов оповещения; в логах только отчёт об обезличивании. Проверка на стенде владельца до выбора между Zabbix (C) и своим Prometheus (B): сбор с порта 9100, расчёт P99, доставка алерта, плагин Grafana, нагрузка на Zabbix (1–2 чел-дн, предложение автора). Алерты: триггеры Zabbix (при B — Grafana Alerting; Alertmanager не разворачиваем); алерт об утечке ПДн — сразу, без подавления повторов, получатель от ИБ; алерт о недоступности источника метрик. Трассировка: на MVP без Jaeger — две гистограммы (поиск, вызов провайдера) 0,5–1 чел-дн в пределах оценки; OpenTelemetry → Jaeger — только если P99 разобрать не удаётся, 2–4 чел-дн, оценка автора, в итог не входит. Логи: развёртывание VictoriaLogs (один узел, том 20 ГиБ), сборщик подов (например Fluent Bit, не выбран), плагин в Grafana владельца, пробный запуск на 1–10% логов с замером ОЗУ и диска. Оценка не пересматривалась (5–8): развёртывание своей связки отпало, добавились интеграция с Zabbix и настройка оповещений.</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); единое хранилище логов: VictoriaLogs (рекомендация автора) или OpenSearch, выбор не сделан; Prometheus — запасной источник для P99.</t>
+          <t>Zabbix и Grafana владельца; prometheus-client (порт 9100); Jaeger — по необходимости (OpenTelemetry, OTLP); VictoriaLogs — единое хранилище логов (решение 25.09.2026); Prometheus — запасной источник для P99.</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C9" s="48" t="inlineStr">
         <is>
-          <t>Скорость любых моделей на GPU. Качество BGE-M3 и других кандидатов на данных проекта. Выигрыш реранкера над текущим индексом (единственный замер сделан на корпусе из 20 фрагментов). Полнота обезличивания на живых данных. Длина запроса на базе из нескольких тысяч документов. Данные о спросе. Сравнения по документации (pgvector, Milvus, Feature Store, Airflow, Loki, Litestar и др.) замером не проверялись.</t>
+          <t>Скорость любых моделей на GPU. Качество BGE-M3 и других кандидатов на данных проекта. Выигрыш реранкера над текущим индексом (единственный замер сделан на корпусе из 20 фрагментов). Полнота обезличивания на живых данных. Длина запроса на базе из нескольких тысяч документов. Данные о спросе. Сравнения по документации (pgvector, Milvus, Feature Store, Airflow, хранилища логов, Litestar и др.) замером не проверялись.</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Loki: сейчас ≈65 байт на вопрос (замер) — до 31 МБ за 30 суток на тираже; целевая трассировка до 10 КБ на вопрос (допущение) — 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже. Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
+          <t>VictoriaLogs: сейчас ≈65 байт на вопрос (замер) — до 31 МБ за 30 суток на тираже; целевая трассировка до 10 КБ на вопрос (допущение) — 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже. Prometheus: 84 ряда на процесс приложения (замер), до 20 000 рядов с метриками кластера (допущение), хранение 15 суток ≈2,6 ГБ; том 10 ГиБ (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>В реальном контуре работают Grafana, Zabbix и Jaeger (решение заказчика проекта, со слов); алерты не настроены. Grafana и Alertmanager в расчёт не входят. Loki (логи) заложен как основной компонент — решение принято; Prometheus (запасной источник для задержки P99) оставлен как верхняя оценка до проверки Zabbix. Сборщик логов подов в расчёт не включён.</t>
+          <t>В реальном контуре работают Grafana, Zabbix и Jaeger (решение заказчика проекта, со слов); алерты не настроены. Grafana и Alertmanager в расчёт не входят. VictoriaLogs (единое хранилище логов) — решение принято 25 сентября 2026, ресурсы заложены прежние, как для Loki (оценка автора, до пробного запуска); Prometheus (запасной источник для задержки P99) оставлен как верхняя оценка до проверки Zabbix. Сборщик логов подов в расчёт не включён.</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27" ht="75" customHeight="1">
       <c r="A27" s="50" t="n">
         <v>12</v>
       </c>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Loki</t>
+          <t>VictoriaLogs</t>
         </is>
       </c>
       <c r="D27" s="51" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="V27" s="9" t="inlineStr">
         <is>
-          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом.</t>
+          <t>Замер: сейчас Backend пишет одну строку (≈65 байт) на вопрос — 2,7 МБ за 30 суток на MVP в максимуме и 31 МБ на тираже. Заложена целевая трассировка до 10 КБ на вопрос (допущение): 0,02–0,42 ГБ на MVP и 0,19–4,7 ГБ на тираже за 30 суток; 20 ГиБ с запасом. Ресурсы (0,5 vCPU, 1 ГиБ) прежние, заложены до пробного запуска; разработчик заявляет расход ниже, чем у Loki и Elasticsearch (не проверено). Срок хранения 30 суток (по умолчанию у продукта 7).</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU. BGE-reranker-v2-m3 выбран как целевой: многоязычный, из того же семейства, что BGE-M3, и проверен на 30 живых формулировках (первое место у 21 из 30 вместо 7, MRR 0,79 вместо 0,52) — но замер устарел: сделан на корпусе из 20 фрагментов, где топ-20 — весь корпус; на текущем индексе косинус даёт 12 из 30, выигрыш реранкера над ним не измерялся, а на 30–100 тыс. векторов MVP зависит от полноты первой ступени. Другие реранкеры (jina-reranker-v2, mMiniLM, bge-reranker-v2-gemma) не измерялись.</t>
+          <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU. BGE-reranker-v2-m3 выбран как целевой: многоязычный, из того же семейства, что BGE-M3, и проверен на 30 живых формулировках (первое место у 21 из 30 вместо 7, MRR 0,79 вместо 0,52) — но замер устарел: сделан на корпусе из 20 фрагментов, где топ-20 — весь корпус; на текущем индексе косинус даёт 12 из 30, выигрыш реранкера над ним не измерялся, а на 30–100 тыс. векторов MVP зависит от полноты первой ступени. Замер 26.09.2026 на текущем индексе (30 вопросов с ответом, CPU без GPU): BGE-reranker-v2-m3 hit@1 22 (косинус 12), hit@3 26 (23), MRR 0,82 (0,59), 20 пар — 27 с; gte-multilingual-reranker-base 18/27/0,74, 11 с; DiTy (русский, MIT) 18/24/0,72, 6,7 с; mMARCO-mMiniLM 17/21/0,67, 2,6 с, но hit@3 ниже косинуса. Ни одна не укладывается в 100 мс: лучший результат 835 мс (mMiniLM, 10 кандидатов, до 256 токенов, INT8). Кандидат для CPU — DiTy (2,8 с на 10 кандидатов); jina-reranker-v2 исключён по лицензии (CC-BY-NC-4.0); gte — только после согласия ИБ на исполнение чужого кода; bge-reranker-v2-gemma и Qwen3-Reranker-0.6B не измерялись. Подробности — ADR-300, «Замер реранкеров на CPU».</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -5611,7 +5611,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="135" customHeight="1">
+    <row r="8" ht="150" customHeight="1">
       <c r="A8" s="46" t="inlineStr">
         <is>
           <t>•</t>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="C8" s="48" t="inlineStr">
         <is>
-          <t>Время запроса на CPU: e5-small 22–37 мс, BGE-M3 210–300 мс, реранкер на 20 кандидатах 7,2 с; бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром. Backend, путь без модели: 117 запросов/с на процесс, 8,5 мс CPU на запрос. Память: обезличиватель 769 МиБ, эмбеддер e5-small +300 МиБ, контейнер Backend 1,32 ГиБ. Redis: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход. Prometheus: 84 ряда на процесс. Выбранные допущения и расчёт узлов — лист «Sizing».</t>
+          <t>Время запроса на CPU: e5-small 22–37 мс, BGE-M3 210–300 мс, реранкер на 20 кандидатах 7,2 с; бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром. Backend (Load_Report, 26.09.2026): путь без модели — 18 запросов/с на ядро, 47 мс CPU на запрос; путь с моделью (заглушка провайдера) — 1,3 ответа/с на ядро, 0,65 с CPU на ответ. Память: обезличиватель 769 МиБ, эмбеддер e5-small +300 МиБ, контейнер Backend 1,32 ГиБ. Redis: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход. Prometheus: 84 ряда на процесс. Выбранные допущения и расчёт узлов — лист «Sizing».</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="50" t="n">
         <v>2</v>
       </c>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Общая нагрузка (см. выше). Замер: путь без модели — 117 запросов/с на один процесс (8,5 мс CPU на запрос), при 4 параллельных запросах медиана 36 мс. Выбрано: 2 реплики на MVP и 3 на тираже по 0,5 и 1 vCPU, ОЗУ 0,5 и 1 ГиБ (лист «Sizing»).</t>
+          <t>Общая нагрузка (см. выше). Замер 26.09.2026 (Load_Report): путь без модели — 18 запросов/с на одно ядро (47 мс CPU на запрос, медиана 55 мс), путь с моделью при заглушке провайдера — 1,3 ответа/с на ядро (0,65 с CPU на ответ в 616 знаков, 126 мс до первого куска); при 4 параллельных запросах медиана без модели 220 мс. Выбрано: 2 реплики на MVP и 3 на тираже по 0,5 и 1 vCPU, ОЗУ 0,5 и 1 ГиБ (лист «Sizing»).</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Capacity_Report, раздел 7; ADR-600 (нагрузочные тесты в плане)</t>
+          <t>Load_Report; Capacity_Report, раздел 7</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Расчётный пик — 0,1 запроса/с на MVP и 1 запрос/с на тираже; это выше максимума прогноза `Capacity_Report.html` (0,058 и 0,656 запроса/с), одновременно до 0,17 и 1,97 запроса (время ответа 3 с). До модели доходит 70% запросов (максимум прогноза).</t>
+          <t>Расчётный пик — 0,1 запроса/с на MVP и 1 запрос/с на тираже; это выше максимума прогноза `Capacity_Report.html` (0,058 и 0,656 запроса/с), одновременно до 0,17 и 1,97 запроса (время ответа 3 с). До модели доходит 30% запросов (принято в обоих сценариях).</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Путь без модели — 8,5 мс на запрос (замер: один процесс отдаёт 117 запросов/с). Путь с моделью — 0,9 с на ответ в 800 знаков (эмбеддинг 36 мс + обезличивание + проверка ответа на потоке 0,3–0,9 с; на ответе в 2 000 знаков 1,4–4,5 с, замер). При максимуме прогноза (0,46 запроса/с к модели на тираже) это ≈0,41 ядра; на ответах в 2 000 знаков — до 2,1 ядра.</t>
+          <t>Путь без модели — 47 мс на запрос (замер 26.09.2026: 18 запросов/с на ядро, `Load_Report.md`). Путь с моделью — 0,65 с на ответ в 616 знаков (тот же замер) и 0,9 с на ответ в 800 знаков (эмбеддинг 36 мс + обезличивание + проверка ответа на потоке 0,3–0,9 с; на ответе в 2 000 знаков 1,4–4,5 с, замер). При максимуме прогноза (0,20 запроса/с к модели на тираже) это ≈0,18 ядра; на ответах в 2 000 знаков — до 0,9 ядра.</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="50" t="n">
         <v>3</v>
       </c>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V18" s="9" t="inlineStr">
         <is>
-          <t>Замер: путь без модели — 117 запросов/с на процесс (8,5 мс CPU). 2 реплики нужны для отказоустойчивости, а не для пропускной способности; ОЗУ — допущение (эмбеддер и обезличиватель вынесены).</t>
+          <t>Замер 26.09.2026: путь без модели — 18 запросов/с на ядро (47 мс CPU), путь с моделью — 1,3 ответа/с на ядро. 2 реплики нужны для отказоустойчивости, а не для пропускной способности; ОЗУ — допущение (эмбеддер и обезличиватель вынесены).</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="V19" s="9" t="inlineStr">
         <is>
-          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,04 ядра на MVP, 0,41 на тираже (максимум прогноза); на ответах в 2 000 знаков до 2,1 ядра (3 реплики × 1 vCPU + предел 2). После оптимизации проверки на потоке запас вырастет.</t>
+          <t>Замер ОЗУ: обезличиватель 769 МиБ. CPU: 0,9 с на ответ в 800 знаков — 0,02 ядра на MVP, 0,18 на тираже (максимум прогноза); на ответах в 2 000 знаков до 0,9 ядра (3 реплики × 1 vCPU). После оптимизации проверки на потоке запас вырастет.</t>
         </is>
       </c>
     </row>

--- a/AI_docs/Tech_Stack_Matrix.xlsx
+++ b/AI_docs/Tech_Stack_Matrix.xlsx
@@ -1681,12 +1681,12 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Реализован и проверен, но выключен (`RERANKER_ENABLED=false`): кросс-энкодер BGE-reranker-v2-m3 на CPU считает 5,8–25 с (последний замер 24.09.2026 — 7,2 с) при бюджете 100 мс; на GPU не измерялся.</t>
+          <t>Реализован и проверен, но выключен (`RERANKER_ENABLED=false`): кросс-энкодер BGE-reranker-v2-m3 на CPU считает 5,8–25 с (замер 24.09.2026 — 7,2 с; 26.09.2026 на фрагментах текущего индекса — 27 с) при бюджете 100 мс; на GPU не измерялся.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU. BGE-reranker-v2-m3 выбран как целевой: многоязычный, из того же семейства, что BGE-M3, и проверен на 30 живых формулировках (первое место у 21 из 30 вместо 7, MRR 0,79 вместо 0,52) — но замер устарел: сделан на корпусе из 20 фрагментов, где топ-20 — весь корпус; на текущем индексе косинус даёт 12 из 30, выигрыш реранкера над ним не измерялся, а на 30–100 тыс. векторов MVP зависит от полноты первой ступени. Замер 26.09.2026 на текущем индексе (30 вопросов с ответом, CPU без GPU): BGE-reranker-v2-m3 hit@1 22 (косинус 12), hit@3 26 (23), MRR 0,82 (0,59), 20 пар — 27 с; gte-multilingual-reranker-base 18/27/0,74, 11 с; DiTy (русский, MIT) 18/24/0,72, 6,7 с; mMARCO-mMiniLM 17/21/0,67, 2,6 с, но hit@3 ниже косинуса. Ни одна не укладывается в 100 мс: лучший результат 835 мс (mMiniLM, 10 кандидатов, до 256 токенов, INT8). Кандидат для CPU — DiTy (2,8 с на 10 кандидатов); jina-reranker-v2 исключён по лицензии (CC-BY-NC-4.0); gte — только после согласия ИБ на исполнение чужого кода; bge-reranker-v2-gemma и Qwen3-Reranker-0.6B не измерялись. Подробности — ADR-300, «Замер реранкеров на CPU».</t>
+          <t>Поиск без переранжирования (топ-3 сразу из косинуса) — единственный вариант на CPU. BGE-reranker-v2-m3 выбран как целевой: многоязычный, из того же семейства, что BGE-M3, и проверен на 30 живых формулировках (первое место у 21 из 30 вместо 7, MRR 0,79 вместо 0,52) — но замер устарел: сделан на корпусе из 20 фрагментов, где топ-20 — весь корпус; на текущем индексе косинус даёт 12 из 30, выигрыш реранкера над ним измерен 26.09.2026 (ниже), а на 30–100 тыс. векторов MVP зависит от полноты первой ступени. Замер 26.09.2026 на текущем индексе (30 вопросов с ответом, CPU без GPU): BGE-reranker-v2-m3 hit@1 22 (косинус 12), hit@3 26 (23), MRR 0,82 (0,59), 20 пар — 27 с; gte-multilingual-reranker-base 18/27/0,74, 11 с; DiTy (русский, MIT) 18/24/0,72, 6,7 с; mMARCO-mMiniLM 17/21/0,67, 2,6 с, но hit@3 ниже косинуса. Ни одна не укладывается в 100 мс: лучший результат 835 мс (mMiniLM, 10 кандидатов, до 256 токенов, INT8). Кандидат для CPU — DiTy (2,8 с на 10 кандидатов); jina-reranker-v2 исключён по лицензии (CC-BY-NC-4.0); gte — только после согласия ИБ на исполнение чужого кода; bge-reranker-v2-gemma и Qwen3-Reranker-0.6B не измерялись. Подробности — ADR-300, «Замер реранкеров на CPU».</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Онлайн-роль зависит от GPU. Офлайн-роль (выбор представительного чанка среди дублей) в коде не реализована и не подтверждена: модель обучена на паре «запрос — документ», а запроса при индексации нет. Отдельной офлайн-модели не выбрано: на схеме ETL указана та же BGE-reranker-v2-m3 (блок «Reranker Client (offline)» после блока «Quality &amp; Dedup Filter»: MinHash/SimHash, Жаккар ≥ 0,9, quality_score). Расчёт по замеру: 7,2 с на 20 кандидатов ≈ 0,36 с на пару, за окно 3 ч ≈ 30 000 пар; на паре «фрагмент — фрагмент» время не измерялось. Варианты отсева: quality_score, центроид, кросс-энкодер, косинусный порог (ADR-300, раздел 3); доля дублей в корпусе не измерялась.</t>
+          <t>Онлайн-роль зависит от GPU. Офлайн-роль (выбор представительного чанка среди дублей) в коде не реализована и не подтверждена: модель обучена на паре «запрос — документ», а запроса при индексации нет. Отдельной офлайн-модели не выбрано: на схеме ETL указана та же BGE-reranker-v2-m3 (блок «Reranker Client (offline)» после блока «Quality &amp; Dedup Filter»: MinHash/SimHash, Жаккар ≥ 0,9, quality_score). Расчёт по замеру 26.09.2026: 27 с на 20 кандидатов на фрагментах текущего индекса ≈ 1,25 с на пару, за окно 3 ч ≈ 8 600 пар (по замеру 24.09 на коротких фрагментах: 0,36 с и ≈ 30 000 пар); на паре «фрагмент — фрагмент» время не измерялось. Варианты отсева: quality_score, центроид, кросс-энкодер, косинусный порог (ADR-300, раздел 3); доля дублей в корпусе не измерялась.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Без GPU-узла остаётся выключенным (на CPU 7,2 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порог пустых выдач (критерий В): не более 3% вопросов с ответом, пустых из-за порядка; рабочее значение автора. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (считается по каждому вопросу на одних и тех же 20 кандидатах: пустая выдача; меньше трёх; пустая из-за порядка — пуста при «реранкер → порог», но не пуста без реранкера; верный фрагмент отсечён порогом; условный пример на 10 вопросах — в ADR-600; у порядка «порог → реранкер» пустых из-за порядка по построению нет; вопросы без ответа в базе размечаются отдельно и считаются отдельно) (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы или пометка «ответа в базе нет» для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли (2–3 чел-дн): доля кластеров дублей на реальных документах, четыре способа выбора представителя (quality_score, центроид, кросс-энкодер, косинусный порог), проверка экспертом, что нужный текст не потерян; при неподтверждении кросс-энкодера офлайн-роль снимается, отсев строится на остальных способах; состав работы — предложение автора от 25.09.2026, порог «заметно лучше» не определён. Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первым шагом — повторный замер базовой линии на текущем индексе, прежний сделан на корпусе из 20 фрагментов — после выбора модели эмбеддингов.</t>
+          <t>Без GPU-узла остаётся выключенным (на CPU 7–27 с при бюджете 100 мс); включается только если владелец после проверки на реальных данных решит купить GPU-узел. Порядок теста (24.09.2026): (1) базовая линия качества ответов без реранкера на реальных данных — не менее 200 обращений, оценка эксперта (1,5–2 чел-дн); (2) разбор ошибок: верного фрагмента нет в топ-20 / есть в топ-20, но не в топ-3 (реранкер может исправить только их) / ошибка генерации (1–2 чел-дн); (3) тест 2–3 реранкеров офлайн на CPU на тех же вопросах, оценка изменившихся ответов (2–4 чел-дн); (4) решение о GPU: реранкер включается и GPU арендуется, только если без реранкера не проходят пороги А и Б, а реранкер их исправляет. Порог пустых выдач (критерий В): не более 3% вопросов с ответом, пустых из-за порядка; рабочее значение автора. Порядок в коде: кандидаты по косинусу → реранкер → первые три → отсев по косинусному порогу 0,872; реранкер может поднять наверх фрагменты с низким косинусом, они отсекутся, выдача станет неполной или пустой — не измерялось. В тесте сравниваются порядки «реранкер → порог» и «порог → реранкер» по hit@1, hit@3, MRR и доле пустых выдач (считается по каждому вопросу на одних и тех же 20 кандидатах: пустая выдача; меньше трёх; пустая из-за порядка — пуста при «реранкер → порог», но не пуста без реранкера; верный фрагмент отсечён порогом; условный пример на 10 вопросах — в ADR-600; у порядка «порог → реранкер» пустых из-за порядка по построению нет; вопросы без ответа в базе размечаются отдельно и считаются отдельно) (в пределах шагов 4–5, оценка автора; правка порядка в коде, если понадобится, ≈0,5 чел-дн внутри оценки). Добавлено 3–5 чел-дн к прежним 5–7 (оценка автора). Единая выборка 300–400 обращений для эмбеддингов, реранкера и проверки провайдеров; ответы генерируются один раз в блоке проверки провайдеров (он идёт раньше), здесь оценивается только качество; если выборки разные — +0,5–1 чел-дн, вне итога. Время эксперта водоканала (не чел-дн команды): 29–52 ч ≈ 4–6,5 рабочих дня — верный фрагмент базы или пометка «ответа в базе нет» для 300–400 обращений 15–33 ч, оценка 200 ответов 10–13 ч, оценка изменившихся ответов 3–4 ч, подтверждение порогов 1–2 ч (оценка автора); наличие эксперта неизвестно. Замер офлайн-роли (2–3 чел-дн): доля кластеров дублей на реальных документах, четыре способа выбора представителя (quality_score, центроид, кросс-энкодер, косинусный порог), проверка экспертом, что нужный текст не потерян; при неподтверждении кросс-энкодера офлайн-роль снимается, отсев строится на остальных способах; состав работы — предложение автора от 25.09.2026, порог «заметно лучше» не определён. Тест 2–3 моделей реранкера на размеченном наборе с порогом под каждую (8–12 чел-дн вместе с базовой линией ответов и разбором ошибок, см. порядок ниже); первый шаг (повторный замер базовой линии на текущем индексе, скрипты замера) выполнен 26.09.2026; остальное — после выбора модели эмбеддингов.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>PostgreSQL выбран против MySQL/MariaDB (нечего добавить к PostgreSQL) и SQLite (один файл, не для нескольких сервисов). Телеметрия остаётся в Postgres, а не в ClickHouse: до ≈0,8 млн событий в год на тираже; замер 2 млн строк — 589 МБ, агрегаты за секунды (ADR-200).</t>
+          <t>PostgreSQL выбран против MySQL/MariaDB (нечего добавить к PostgreSQL) и SQLite (один файл, не для нескольких сервисов). Телеметрия остаётся в Postgres, а не в ClickHouse: до ≈1,7 млн событий в год на тираже; замер 2 млн строк — 589 МБ, агрегаты за секунды (ADR-200).</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Решение заказчика проекта 25.09.2026: шаблоны тянутся из хранилища или с файлового сервера отдельным контейнером. Сравнивались: в коде (прототип; замена бланка — выпуск приложения), файлы в образе или ConfigMap (тоже выпуск; ConfigMap ограничен ≈1 МБ по документации Kubernetes), отдельный контейнер + MinIO (уже в стеке; версии и права — средствами S3 по документации), отдельный контейнер + файловый сервер владельца (владелец кладёт форму туда, где уже работает; доступ, протокол и учётная запись неизвестны), таблица в Postgres (смешивает файлы форм с данными). Источник основной не выбран — зависит от ответа владельца; кандидат — MinIO. Сравнение по документации и общим сведениям, стенда нет.</t>
+          <t>Принято 25.09.2026: шаблоны тянутся из хранилища или с файлового сервера отдельным контейнером. Сравнивались: в коде (прототип; замена бланка — выпуск приложения), файлы в образе или ConfigMap (тоже выпуск; ConfigMap ограничен ≈1 МБ по документации Kubernetes), отдельный контейнер + MinIO (уже в стеке; версии и права — средствами S3 по документации), отдельный контейнер + файловый сервер владельца (владелец кладёт форму туда, где уже работает; доступ, протокол и учётная запись неизвестны), таблица в Postgres (смешивает файлы форм с данными). Источник основной не выбран — зависит от ответа владельца; кандидат — MinIO. Сравнение по документации и общим сведениям, стенда нет.</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Решение заказчика проекта (24.09.2026, документально не подтверждено): личный кабинет уже на Kubernetes, размещаемся в том же кластере, эксплуатирует тот же отдел, GPU-узлов нет. Не известны дистрибутив и версия, квоты, классы хранилищ и быстрые диски, как настроено шифрование Kubernetes Secrets и права на них, есть ли своя наблюдаемость, сетевые правила. Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
+          <t>Принято 24.09.2026 (со слов заказчика проекта, документально не подтверждено): личный кабинет уже на Kubernetes, размещаемся в том же кластере, эксплуатирует тот же отдел, GPU-узлов нет. Не известны дистрибутив и версия, квоты, классы хранилищ и быстрые диски, как настроено шифрование Kubernetes Secrets и права на них, есть ли своя наблюдаемость, сетевые правила. Управляющая часть кластера в расчёт узлов не заложена — размещена на узлах общего пула (допущение). Накладные расходы кластера — порядка 1 vCPU и 2 ГиБ на узел (допущение): более половины полезной нагрузки на MVP; в общем кластере владельца управляющая часть и системные поды общие, расчёт узлов — верхняя оценка. Nomad с Vault — план Б, менее вероятный.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Целевой механизм (решение заказчика проекта, 24.09.2026): GitLab CI variables (masked, protected) + деплой через pipeline → Kubernetes Secret. Сравнение (ADR-200, «Секреты в проде: GitLab CI variables и альтернативы»; по документации, без проверки на стенде владельца): Vault Agent Injector — есть аудит чтения, аренда и замена без пересборки, но нужна новая система (отказоустойчивость, разблокировка, резервные копии) и sidecar в каждом поде; External Secrets Operator или Vault CSI — то же плюс оператор; SOPS или Sealed Secrets — шифрованные секреты в Git, без аудита чтения; Kubernetes Secret вручную — без повторяемости и журнала. Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения.</t>
+          <t>Целевой механизм (принято 24.09.2026): GitLab CI variables (masked, protected) + деплой через pipeline → Kubernetes Secret. Сравнение (ADR-200, «Секреты в проде: GitLab CI variables и альтернативы»; по документации, без проверки на стенде владельца): Vault Agent Injector — есть аудит чтения, аренда и замена без пересборки, но нужна новая система (отказоустойчивость, разблокировка, резервные копии) и sidecar в каждом поде; External Secrets Operator или Vault CSI — то же плюс оператор; SOPS или Sealed Secrets — шифрованные секреты в Git, без аудита чтения; Kubernetes Secret вручную — без повторяемости и журнала. Файл `.env` на диске отклонён: секрет в открытом виде лишний, когда есть переменные окружения.</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ по триггерам self-hosted-перехода не было.</t>
+          <t>Сверка диаграммы Backend с кодом сделана частично; согласования с ИБ критериев решения о собственной модели не было.</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="P38" s="9" t="inlineStr">
         <is>
-          <t>Согласование перечня триггеров self-hosted-перехода с ИБ.</t>
+          <t>Согласование критериев решения о собственной модели с ИБ.</t>
         </is>
       </c>
       <c r="Q38" s="9" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="R38" s="9" t="inlineStr">
         <is>
-          <t>Триггеры должны быть согласованы до срабатывания, а не после.</t>
+          <t>Критерии должны быть согласованы до решения, а не после.</t>
         </is>
       </c>
       <c r="S38" s="19" t="n"/>
@@ -4117,12 +4117,12 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>В кластере, где работает личный кабинет и где размещается наш контур, GPU-узлов нет (решение заказчика проекта, 24.09.2026). Без них MVP на CPU: эмбеддинги e5-small (36–37 мс на запрос), реранкер выключен, индексация считает эмбеддинги на CPU.</t>
+          <t>В кластере, где работает личный кабинет и где размещается наш контур, GPU-узлов нет (со слов заказчика проекта, 24.09.2026). Без них MVP на CPU: эмбеддинги e5-small (36–37 мс на запрос), реранкер выключен, индексация считает эмбеддинги на CPU.</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7,2 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Владелец примет решение о GPU-узле только после проверки на реальных данных (24.09.2026): тест моделей идёт на CPU, скорость на GPU — коротким замером на временной видеокарте (ADR-200, «Почему Kubernetes», ADR-600).</t>
+          <t>Без GPU: BGE-M3 (300 мс) и реранкер (7–27 с на 20 кандидатах) не укладываются в бюджет 100 мс на CPU. С GPU-узлом: возможны BGE-M3, реранкер, позже собственная модель. Владелец примет решение о GPU-узле только после проверки на реальных данных (24.09.2026): тест моделей идёт на CPU, скорость на GPU — коротким замером на временной видеокарте (ADR-200, «Почему Kubernetes», ADR-600).</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны заказчиком проекта 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); Б — доля ответов, оценённых экспертом как верные и полезные, не ниже 80% на подвыборке не менее 200 (рабочее значение автора); В — пустых выдач из-за реранкера (пуста при «реранкер → порог», но не пуста без реранкера) не более 3% вопросов с ответом в базе (рабочее значение автора, только для реранкера; порядок «порог → реранкер» проходит по построению); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А, Б или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
+          <t>Решение — после проверки на реальных данных. Лестница (каждый следующий вариант — только если предыдущий не подошёл): (1) CPU + YandexGPT — базовый: поиск на CPU (e5-small), реранкер выключен, генерация через внешний API (на прототипе YandexGPT; новых потоков данных вовне нет); (2) аренда GPU на месяц — замер скорости, качество на обезличенных текстах, пилот (2–4 чел-дн оценка автора, цена аренды не оценена, нужно согласование с ИБ); (3) покупка — по итогам аренды, решение владельца. Критерии (выбраны 24.09.2026): А — hit@3 ≥ 85% и hit@1 ≥ 60% на размеченном наборе живых обращений (рабочие значения, предложение автора, подтверждает владелец после разметки первых 100 обращений); Б — доля ответов, оценённых экспертом как верные и полезные, не ниже 80% на подвыборке не менее 200 (рабочее значение автора); В — пустых выдач из-за реранкера (пуста при «реранкер → порог», но не пуста без реранкера) не более 3% вопросов с ответом в базе (рабочее значение автора, только для реранкера; порядок «порог → реранкер» проходит по построению); D — GPU оправдан при выигрыше над лучшим CPU не менее 5 п.п. по hit@3 или MRR; С — скорость не ниже прототипа: до первого куска ответа медиана ≤ 0,78 с, до конца ответа ≤ 2,6 с (замер прототипа 24.09.2026 на 19 вызовах), поиск P99 ≤ 100 мс. Вариант 1 не подходит при нарушении А, Б или С. Набор для проверки — от 300–400 размеченных обращений (на 30 доверительный интервал ±18 п.п.), сравнение парное. Если решение — покупать (после аренды): закупка сервера и подключение к общему кластеру (драйверы, плагин устройств, метки и запреты размещения, квоты, согласование с отделом) — 3–5 чел-дн без закупки.</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
         <is>
-          <t>«Оценка автора» — работы, которых нет в ADR-600 (инфраструктура MVP, виджет, вынос шлюза и т. п.); поэтому итог MVP больше, чем «9–13 недель» ADR-600. Столбцы «По триггеру» — работы, которые появятся только при наступлении триггера (переход агента на LangGraph); в итог не входят.</t>
+          <t>«Оценка автора» — работы, которых нет в ADR-600 (инфраструктура MVP, виджет, вынос шлюза и т. п.); поэтому итог MVP больше, чем «9–13 недель» ADR-600. Столбцы «По триггеру» — работы, которые появятся только при наступлении триггера (трассировка Jaeger, если гистограмм не хватит; подключение GPU-узла, если владелец решит его купить); в итог не входят.</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="C8" s="48" t="inlineStr">
         <is>
-          <t>Время запроса на CPU: e5-small 22–37 мс, BGE-M3 210–300 мс, реранкер на 20 кандидатах 7,2 с; бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром. Backend (Load_Report, 26.09.2026): путь без модели — 18 запросов/с на ядро, 47 мс CPU на запрос; путь с моделью (заглушка провайдера) — 1,3 ответа/с на ядро, 0,65 с CPU на ответ. Память: обезличиватель 769 МиБ, эмбеддер e5-small +300 МиБ, контейнер Backend 1,32 ГиБ. Redis: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход. Prometheus: 84 ряда на процесс. Выбранные допущения и расчёт узлов — лист «Sizing».</t>
+          <t>Время запроса на CPU: e5-small 22–37 мс, BGE-M3 210–300 мс, реранкер на 20 кандидатах 7–27 с (замеры 24.09 и 26.09); бюджет поиска 100 мс. Синхронная проверка Guardrails: на ответе ≈800 знаков P95 ≈49 мс, на ≈2 000 знаков P95 ≈120 мс (бюджет 50 мс). YandexGPT, 19 вызовов: время до первого куска — медиана 0,78 с, P90 5,6 с; до конца ответа — медиана 2,6 с. Postgres, 2 млн строк телеметрии: 589 МБ, агрегаты 0,35–1,5 с. Qdrant, 100 000 векторов размерности 1 024: P99 65 мс без фильтра, 37 мс с фильтром. Backend (Load_Report, 26.09.2026): путь без модели — 18 запросов/с на ядро, 47 мс CPU на запрос; путь с моделью (заглушка провайдера) — 1,3 ответа/с на ядро, 0,65 с CPU на ответ. Память: обезличиватель 769 МиБ, эмбеддер e5-small +300 МиБ, контейнер Backend 1,32 ГиБ. Redis: ключ квоты ≈0,5 КБ, сессия ≈0,8 КБ на ход. Prometheus: 84 ряда на процесс. Выбранные допущения и расчёт узлов — лист «Sizing».</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C9" s="48" t="inlineStr">
         <is>
-          <t>Скорость любых моделей на GPU. Качество BGE-M3 и других кандидатов на данных проекта. Выигрыш реранкера над текущим индексом (единственный замер сделан на корпусе из 20 фрагментов). Полнота обезличивания на живых данных. Длина запроса на базе из нескольких тысяч документов. Данные о спросе. Сравнения по документации (pgvector, Milvus, Feature Store, Airflow, хранилища логов, Litestar и др.) замером не проверялись.</t>
+          <t>Скорость любых моделей на GPU. Качество BGE-M3 и других кандидатов на данных проекта. Качество реранкеров на выборке из 300–400 живых обращений (замер 26.09.2026 сделан на 30 вопросах эталонного набора). Полнота обезличивания на живых данных. Длина запроса на базе из нескольких тысяч документов. Данные о спросе. Сравнения по документации (pgvector, Milvus, Feature Store, Airflow, хранилища логов, Litestar и др.) замером не проверялись.</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Одно переранжирование 20 кандидатов на вопрос (до 0,058 вопроса/с на MVP и 0,656 на тираже). На CPU 7,2 с (замер); загрузка GPU не оценивается: скорость на GPU не измерялась.</t>
+          <t>Одно переранжирование 20 кандидатов на вопрос (до 0,058 вопроса/с на MVP и 0,656 на тираже). На CPU 7–27 с (замеры 24 и 26.09); загрузка GPU не оценивается: скорость на GPU не измерялась.</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>В реальном контуре работают Grafana, Zabbix и Jaeger (решение заказчика проекта, со слов); алерты не настроены. Grafana и Alertmanager в расчёт не входят. VictoriaLogs (единое хранилище логов) — решение принято 25 сентября 2026, ресурсы заложены прежние, как для Loki (оценка автора, до пробного запуска); Prometheus (запасной источник для задержки P99) оставлен как верхняя оценка до проверки Zabbix. Сборщик логов подов в расчёт не включён.</t>
+          <t>В реальном контуре работают Grafana, Zabbix и Jaeger (со слов заказчика проекта); алерты не настроены. Grafana и Alertmanager в расчёт не входят. VictoriaLogs (единое хранилище логов) — решение принято 25 сентября 2026, ресурсы заложены прежние, как для Loki (оценка автора, до пробного запуска); Prometheus (запасной источник для задержки P99) оставлен как верхняя оценка до проверки Zabbix. Сборщик логов подов в расчёт не включён.</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7,2 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру: владелец решит только после проверки на реальных данных (цена не оценена); переключатель на листе «Sizing».</t>
+          <t>В кластере владельца, где уже работает личный кабинет, GPU-узлов нет (со слов заказчика проекта). Базовый вариант расчёта — **без GPU**: эмбеддинги `multilingual-e5-small` на CPU (36–37 мс на запрос, замер), реранкер выключен (на CPU 7–27 с), индексация считает эмбеддинги на CPU. Вариант **с GPU** — покупка и подключение узла к кластеру: владелец решит только после проверки на реальных данных (цена не оценена); переключатель на листе «Sizing».</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="V33" s="9" t="inlineStr">
         <is>
-          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7,2 с на 20 кандидатов.</t>
+          <t>Замер: веса 2,14 ГиБ (fp32). Расчёт: в fp16 ≈1,1 ГиБ + запас — ≈1,5 ГиБ видеопамяти. Скорость на GPU не измерялась; на CPU 7–27 с на 20 кандидатов.</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="V35" s="9" t="inlineStr">
         <is>
-          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7,2 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
+          <t>Замер: e5-small — 36–37 мс на запрос на CPU и +300 МиБ ОЗУ; BGE-M3 на CPU (300 мс) в бюджет 100 мс не укладывается, реранкер на CPU (7–27 с) не годится и выключен. 2 реплики для отказоустойчивости. Только в варианте без GPU.</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
     <row r="47">
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); управляющая часть Kubernetes размещена на трёх узлах общего пула (допущение); нагрузочный тест не проводился.</t>
+          <t>Не покрыто: скорость моделей на GPU (видеопамять и время индексации — допущения); стоимость серверов и обслуживания; системные поды Kubernetes (≈1 vCPU и 2 ГиБ на узел); управляющая часть Kubernetes размещена на трёх узлах общего пула (допущение); нагрузочный тест кластера не проводился (замер одного процесса Backend — Load_Report.md).</t>
         </is>
       </c>
     </row>
